--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.96931818181818</v>
+        <v>25.75714285714286</v>
       </c>
       <c r="D2" t="n">
-        <v>184.3045454545455</v>
+        <v>184.5428571428571</v>
       </c>
       <c r="E2" t="n">
-        <v>1.198863636363636</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="F2" t="n">
-        <v>72.93863636363636</v>
+        <v>72.94285714285715</v>
       </c>
       <c r="G2" t="n">
-        <v>6104289.772727272</v>
+        <v>6193214.285714285</v>
       </c>
       <c r="H2" t="n">
-        <v>77.51022727272726</v>
+        <v>77.7</v>
       </c>
       <c r="I2" t="n">
-        <v>27.89659090909091</v>
+        <v>27.84285714285715</v>
       </c>
       <c r="J2" t="n">
-        <v>183.0840909090909</v>
+        <v>183.264935064935</v>
       </c>
       <c r="K2" t="n">
-        <v>2.380681818181818</v>
+        <v>2.344155844155844</v>
       </c>
       <c r="L2" t="n">
-        <v>82.68522727272727</v>
+        <v>82.57532467532469</v>
       </c>
       <c r="M2" t="n">
-        <v>38743181.81818181</v>
+        <v>38316883.11688311</v>
       </c>
       <c r="N2" t="n">
-        <v>84.55795454545455</v>
+        <v>84.55974025974025</v>
       </c>
       <c r="O2" t="n">
-        <v>26.42966036414566</v>
+        <v>26.54104041616646</v>
       </c>
       <c r="P2" t="n">
-        <v>184.9304761904762</v>
+        <v>184.7348299319728</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.330964635854342</v>
+        <v>1.335388155262105</v>
       </c>
       <c r="R2" t="n">
-        <v>69.99121323529413</v>
+        <v>70.03281512605042</v>
       </c>
       <c r="S2" t="n">
-        <v>3309505.558473389</v>
+        <v>3335327.781112445</v>
       </c>
       <c r="T2" t="n">
-        <v>73.83022584033614</v>
+        <v>73.8702581032413</v>
       </c>
       <c r="U2" t="n">
-        <v>27.4938266886093</v>
+        <v>27.46499447642305</v>
       </c>
       <c r="V2" t="n">
-        <v>182.4515390145282</v>
+        <v>182.3110756439328</v>
       </c>
       <c r="W2" t="n">
-        <v>1.918102338482773</v>
+        <v>1.937458573172858</v>
       </c>
       <c r="X2" t="n">
-        <v>78.96189536108014</v>
+        <v>79.01235246235247</v>
       </c>
       <c r="Y2" t="n">
-        <v>23249631.7752296</v>
+        <v>23844299.66858539</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.2590188193449</v>
+        <v>81.30223268794695</v>
       </c>
     </row>
     <row r="3">
@@ -647,76 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24.67012987012987</v>
+        <v>24.73181818181818</v>
       </c>
       <c r="D3" t="n">
-        <v>184.774025974026</v>
+        <v>185.019696969697</v>
       </c>
       <c r="E3" t="n">
-        <v>1.068831168831169</v>
+        <v>1.063636363636364</v>
       </c>
       <c r="F3" t="n">
-        <v>69.61688311688312</v>
+        <v>69.83636363636363</v>
       </c>
       <c r="G3" t="n">
-        <v>2894285.714285714</v>
+        <v>2975833.333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>75.32337662337662</v>
+        <v>75.5439393939394</v>
       </c>
       <c r="I3" t="n">
-        <v>26.23545454545455</v>
+        <v>26.16060606060606</v>
       </c>
       <c r="J3" t="n">
-        <v>183.5736363636364</v>
+        <v>183.3848484848485</v>
       </c>
       <c r="K3" t="n">
-        <v>1.617272727272727</v>
+        <v>1.615151515151515</v>
       </c>
       <c r="L3" t="n">
-        <v>76.33636363636364</v>
+        <v>76.28282828282828</v>
       </c>
       <c r="M3" t="n">
-        <v>12513090.90909091</v>
+        <v>12461010.1010101</v>
       </c>
       <c r="N3" t="n">
-        <v>79.51090909090908</v>
+        <v>79.4969696969697</v>
       </c>
       <c r="O3" t="n">
-        <v>25.21638707508273</v>
+        <v>25.23322081836575</v>
       </c>
       <c r="P3" t="n">
-        <v>184.593419865159</v>
+        <v>184.4230924067881</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.106499177151351</v>
+        <v>1.117838783599653</v>
       </c>
       <c r="R3" t="n">
-        <v>68.52573171594911</v>
+        <v>68.38258443783806</v>
       </c>
       <c r="S3" t="n">
-        <v>2359444.897895985</v>
+        <v>2260378.02190429</v>
       </c>
       <c r="T3" t="n">
-        <v>73.46028870485392</v>
+        <v>73.27418297617572</v>
       </c>
       <c r="U3" t="n">
-        <v>25.26045917486922</v>
+        <v>25.33106574985469</v>
       </c>
       <c r="V3" t="n">
-        <v>181.9281685064062</v>
+        <v>182.0266687108216</v>
       </c>
       <c r="W3" t="n">
-        <v>1.571801725205773</v>
+        <v>1.59366858356197</v>
       </c>
       <c r="X3" t="n">
-        <v>74.77021995992236</v>
+        <v>74.74005921472855</v>
       </c>
       <c r="Y3" t="n">
-        <v>11508767.54879581</v>
+        <v>11493538.01718053</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.13635406991254</v>
+        <v>79.09131933693986</v>
       </c>
     </row>
     <row r="4">
@@ -729,76 +729,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.32007575757576</v>
+        <v>25.3008658008658</v>
       </c>
       <c r="D4" t="n">
-        <v>184.4032828282828</v>
+        <v>184.4738816738817</v>
       </c>
       <c r="E4" t="n">
-        <v>1.785606060606061</v>
+        <v>1.754978354978355</v>
       </c>
       <c r="F4" t="n">
-        <v>80.18093434343434</v>
+        <v>79.97301587301588</v>
       </c>
       <c r="G4" t="n">
-        <v>32740675.50505051</v>
+        <v>31599733.04473305</v>
       </c>
       <c r="H4" t="n">
-        <v>83.91527777777777</v>
+        <v>83.74733044733044</v>
       </c>
       <c r="I4" t="n">
-        <v>25.84431818181818</v>
+        <v>25.77922077922078</v>
       </c>
       <c r="J4" t="n">
-        <v>186.2375</v>
+        <v>186.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.235227272727273</v>
+        <v>1.225974025974026</v>
       </c>
       <c r="L4" t="n">
-        <v>76.16022727272727</v>
+        <v>76.05454545454545</v>
       </c>
       <c r="M4" t="n">
-        <v>13589204.54545454</v>
+        <v>13493376.62337662</v>
       </c>
       <c r="N4" t="n">
-        <v>79.38636363636363</v>
+        <v>79.3987012987013</v>
       </c>
       <c r="O4" t="n">
-        <v>24.41531288156288</v>
+        <v>24.44167626024769</v>
       </c>
       <c r="P4" t="n">
-        <v>184.9628663003663</v>
+        <v>185.1718472004186</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.539888583638584</v>
+        <v>1.529103436246293</v>
       </c>
       <c r="R4" t="n">
-        <v>76.22067562067562</v>
+        <v>76.28516774231061</v>
       </c>
       <c r="S4" t="n">
-        <v>21966995.34493284</v>
+        <v>22503626.54805512</v>
       </c>
       <c r="T4" t="n">
-        <v>82.03118030118029</v>
+        <v>82.00816210244781</v>
       </c>
       <c r="U4" t="n">
-        <v>25.07500434882884</v>
+        <v>25.10075684978936</v>
       </c>
       <c r="V4" t="n">
-        <v>184.7674292753385</v>
+        <v>184.6815733071538</v>
       </c>
       <c r="W4" t="n">
-        <v>1.219184687431591</v>
+        <v>1.22042159766618</v>
       </c>
       <c r="X4" t="n">
-        <v>72.01683930051286</v>
+        <v>72.04932010284178</v>
       </c>
       <c r="Y4" t="n">
-        <v>5636406.245113675</v>
+        <v>5788223.678626155</v>
       </c>
       <c r="Z4" t="n">
-        <v>75.79466071316884</v>
+        <v>75.75028893535087</v>
       </c>
     </row>
     <row r="5">
@@ -811,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.53409090909091</v>
+        <v>25.53246753246754</v>
       </c>
       <c r="D5" t="n">
-        <v>183.9772727272727</v>
+        <v>183.8571428571429</v>
       </c>
       <c r="E5" t="n">
-        <v>1.034090909090909</v>
+        <v>1.038961038961039</v>
       </c>
       <c r="F5" t="n">
-        <v>72.38636363636364</v>
+        <v>72.37662337662339</v>
       </c>
       <c r="G5" t="n">
-        <v>4504545.454545455</v>
+        <v>4474025.974025974</v>
       </c>
       <c r="H5" t="n">
-        <v>76.01136363636363</v>
+        <v>76.05194805194806</v>
       </c>
       <c r="I5" t="n">
-        <v>25.52840909090909</v>
+        <v>25.28961038961039</v>
       </c>
       <c r="J5" t="n">
-        <v>183.5920454545455</v>
+        <v>183.5194805194805</v>
       </c>
       <c r="K5" t="n">
-        <v>1.353409090909091</v>
+        <v>1.346753246753247</v>
       </c>
       <c r="L5" t="n">
-        <v>73.40568181818182</v>
+        <v>73.22077922077922</v>
       </c>
       <c r="M5" t="n">
-        <v>7352272.727272728</v>
+        <v>7368311.688311689</v>
       </c>
       <c r="N5" t="n">
-        <v>77.5443181818182</v>
+        <v>77.66493506493508</v>
       </c>
       <c r="O5" t="n">
-        <v>24.95436507936508</v>
+        <v>25.06424792139078</v>
       </c>
       <c r="P5" t="n">
-        <v>182.1184752747253</v>
+        <v>182.1354003139717</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.133648758648758</v>
+        <v>1.131577417291703</v>
       </c>
       <c r="R5" t="n">
-        <v>69.99778693528694</v>
+        <v>70.0292168149311</v>
       </c>
       <c r="S5" t="n">
-        <v>3049588.039275539</v>
+        <v>3060825.48403977</v>
       </c>
       <c r="T5" t="n">
-        <v>74.91550925925927</v>
+        <v>74.85582010582011</v>
       </c>
       <c r="U5" t="n">
-        <v>25.58548541434411</v>
+        <v>25.83945585815151</v>
       </c>
       <c r="V5" t="n">
-        <v>182.2128460609439</v>
+        <v>182.2817141795403</v>
       </c>
       <c r="W5" t="n">
-        <v>1.291151523597176</v>
+        <v>1.321755587407761</v>
       </c>
       <c r="X5" t="n">
-        <v>71.43976673789174</v>
+        <v>71.60149165649166</v>
       </c>
       <c r="Y5" t="n">
-        <v>4134585.859113712</v>
+        <v>4130323.399426661</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.88763610182087</v>
+        <v>76.81114455592716</v>
       </c>
     </row>
     <row r="6">
@@ -893,76 +893,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.53409090909091</v>
+        <v>24.45454545454546</v>
       </c>
       <c r="D6" t="n">
-        <v>185.4318181818182</v>
+        <v>185.5064935064935</v>
       </c>
       <c r="E6" t="n">
-        <v>1.272727272727273</v>
+        <v>1.25974025974026</v>
       </c>
       <c r="F6" t="n">
-        <v>75.04545454545455</v>
+        <v>74.75324675324676</v>
       </c>
       <c r="G6" t="n">
-        <v>11312500</v>
+        <v>10753246.75324675</v>
       </c>
       <c r="H6" t="n">
-        <v>79.71590909090909</v>
+        <v>79.57142857142857</v>
       </c>
       <c r="I6" t="n">
-        <v>24.76136363636364</v>
+        <v>24.62337662337663</v>
       </c>
       <c r="J6" t="n">
-        <v>187.1022727272727</v>
+        <v>187.3766233766234</v>
       </c>
       <c r="K6" t="n">
-        <v>1.045454545454545</v>
+        <v>1.038961038961039</v>
       </c>
       <c r="L6" t="n">
-        <v>73.22727272727272</v>
+        <v>73.16883116883118</v>
       </c>
       <c r="M6" t="n">
-        <v>5114772.727272728</v>
+        <v>5062337.662337663</v>
       </c>
       <c r="N6" t="n">
-        <v>77.31818181818181</v>
+        <v>77.32467532467533</v>
       </c>
       <c r="O6" t="n">
-        <v>22.95725779967159</v>
+        <v>23.04809054656345</v>
       </c>
       <c r="P6" t="n">
-        <v>184.7881506568145</v>
+        <v>184.8191109547267</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.199683908045977</v>
+        <v>1.212904058174994</v>
       </c>
       <c r="R6" t="n">
-        <v>71.18593185550083</v>
+        <v>71.26351395730707</v>
       </c>
       <c r="S6" t="n">
-        <v>6894173.850574713</v>
+        <v>7002015.012901713</v>
       </c>
       <c r="T6" t="n">
-        <v>78.07766420361247</v>
+        <v>78.05814684494487</v>
       </c>
       <c r="U6" t="n">
-        <v>25.23056374045344</v>
+        <v>25.29097394513361</v>
       </c>
       <c r="V6" t="n">
-        <v>182.9242851456822</v>
+        <v>183.0837984082522</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07821222078575</v>
+        <v>1.083890889689209</v>
       </c>
       <c r="X6" t="n">
-        <v>70.69103840467811</v>
+        <v>70.58646147347828</v>
       </c>
       <c r="Y6" t="n">
-        <v>3164777.944618018</v>
+        <v>3076779.189453559</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.7301565455242</v>
+        <v>74.6091898981815</v>
       </c>
     </row>
     <row r="7">
@@ -975,76 +975,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>24.97727272727273</v>
+        <v>24.92207792207792</v>
       </c>
       <c r="D7" t="n">
-        <v>183.9772727272727</v>
+        <v>184.038961038961</v>
       </c>
       <c r="E7" t="n">
-        <v>1.125</v>
+        <v>1.116883116883117</v>
       </c>
       <c r="F7" t="n">
-        <v>72.88636363636363</v>
+        <v>72.85714285714286</v>
       </c>
       <c r="G7" t="n">
-        <v>4686079.545454545</v>
+        <v>4697077.922077922</v>
       </c>
       <c r="H7" t="n">
-        <v>76.55681818181819</v>
+        <v>76.6103896103896</v>
       </c>
       <c r="I7" t="n">
-        <v>26.18636363636364</v>
+        <v>26.18441558441559</v>
       </c>
       <c r="J7" t="n">
-        <v>182.5409090909091</v>
+        <v>182.4324675324676</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7125</v>
+        <v>1.7</v>
       </c>
       <c r="L7" t="n">
-        <v>80.72272727272728</v>
+        <v>80.58311688311689</v>
       </c>
       <c r="M7" t="n">
-        <v>35875681.81818182</v>
+        <v>35072207.79220779</v>
       </c>
       <c r="N7" t="n">
-        <v>82.60454545454546</v>
+        <v>82.4909090909091</v>
       </c>
       <c r="O7" t="n">
-        <v>24.08346688034188</v>
+        <v>24.05835368335368</v>
       </c>
       <c r="P7" t="n">
-        <v>182.8111645299145</v>
+        <v>182.74185999186</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.045800264550265</v>
+        <v>1.041761148904006</v>
       </c>
       <c r="R7" t="n">
-        <v>70.58381664631665</v>
+        <v>70.55081690795977</v>
       </c>
       <c r="S7" t="n">
-        <v>3419376.717032967</v>
+        <v>3384843.232164661</v>
       </c>
       <c r="T7" t="n">
-        <v>75.36137184574685</v>
+        <v>75.3547953369382</v>
       </c>
       <c r="U7" t="n">
-        <v>24.8723784868812</v>
+        <v>24.70533731834042</v>
       </c>
       <c r="V7" t="n">
-        <v>180.7384918913073</v>
+        <v>180.9094669233988</v>
       </c>
       <c r="W7" t="n">
-        <v>1.526548378522063</v>
+        <v>1.512483861168072</v>
       </c>
       <c r="X7" t="n">
-        <v>75.77367782572891</v>
+        <v>75.60444132464256</v>
       </c>
       <c r="Y7" t="n">
-        <v>16078138.33966601</v>
+        <v>15968914.05485639</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.16112704052912</v>
+        <v>79.08295471298568</v>
       </c>
     </row>
     <row r="8">
@@ -1057,76 +1057,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.15909090909091</v>
+        <v>25.16883116883117</v>
       </c>
       <c r="D8" t="n">
-        <v>184.2159090909091</v>
+        <v>184.1688311688311</v>
       </c>
       <c r="E8" t="n">
-        <v>1.193181818181818</v>
+        <v>1.194805194805195</v>
       </c>
       <c r="F8" t="n">
-        <v>72.13636363636363</v>
+        <v>72.1038961038961</v>
       </c>
       <c r="G8" t="n">
-        <v>3732954.545454545</v>
+        <v>3715584.415584415</v>
       </c>
       <c r="H8" t="n">
-        <v>76.04545454545455</v>
+        <v>76</v>
       </c>
       <c r="I8" t="n">
-        <v>26.32727272727273</v>
+        <v>26.14025974025974</v>
       </c>
       <c r="J8" t="n">
-        <v>182.5181818181819</v>
+        <v>182.4363636363637</v>
       </c>
       <c r="K8" t="n">
-        <v>2.140909090909091</v>
+        <v>2.096103896103896</v>
       </c>
       <c r="L8" t="n">
-        <v>78.7090909090909</v>
+        <v>78.55064935064934</v>
       </c>
       <c r="M8" t="n">
-        <v>21836590.90909091</v>
+        <v>21361298.7012987</v>
       </c>
       <c r="N8" t="n">
-        <v>80.61931818181819</v>
+        <v>80.65584415584415</v>
       </c>
       <c r="O8" t="n">
-        <v>26.04532414424656</v>
+        <v>26.03209458849853</v>
       </c>
       <c r="P8" t="n">
-        <v>183.1759994316029</v>
+        <v>183.2602555080387</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.157476790450929</v>
+        <v>1.165195149677908</v>
       </c>
       <c r="R8" t="n">
-        <v>70.18014320449666</v>
+        <v>70.11228188888286</v>
       </c>
       <c r="S8" t="n">
-        <v>2674243.747631679</v>
+        <v>2659948.519460835</v>
       </c>
       <c r="T8" t="n">
-        <v>74.09126799924215</v>
+        <v>74.10430628484816</v>
       </c>
       <c r="U8" t="n">
-        <v>25.44432462492808</v>
+        <v>25.39790946145626</v>
       </c>
       <c r="V8" t="n">
-        <v>183.1988411452851</v>
+        <v>183.0843898803259</v>
       </c>
       <c r="W8" t="n">
-        <v>1.967550752249028</v>
+        <v>1.95192613443845</v>
       </c>
       <c r="X8" t="n">
-        <v>76.30858608584902</v>
+        <v>76.29772475745382</v>
       </c>
       <c r="Y8" t="n">
-        <v>16928452.01693262</v>
+        <v>17108203.40396695</v>
       </c>
       <c r="Z8" t="n">
-        <v>80.43082664063267</v>
+        <v>80.3989667101736</v>
       </c>
     </row>
     <row r="9">
@@ -1139,76 +1139,76 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.72323232323232</v>
+        <v>26.78863636363636</v>
       </c>
       <c r="D9" t="n">
-        <v>183.9272727272727</v>
+        <v>183.7431818181818</v>
       </c>
       <c r="E9" t="n">
-        <v>1.732323232323232</v>
+        <v>1.723863636363636</v>
       </c>
       <c r="F9" t="n">
-        <v>77.44242424242424</v>
+        <v>77.53522727272727</v>
       </c>
       <c r="G9" t="n">
-        <v>17936565.65656566</v>
+        <v>18098636.36363636</v>
       </c>
       <c r="H9" t="n">
-        <v>79.7929292929293</v>
+        <v>79.77954545454546</v>
       </c>
       <c r="I9" t="n">
-        <v>24.86776859504132</v>
+        <v>24.83636363636364</v>
       </c>
       <c r="J9" t="n">
-        <v>184.801652892562</v>
+        <v>184.9181818181818</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>69.91735537190083</v>
+        <v>69.95454545454545</v>
       </c>
       <c r="M9" t="n">
-        <v>2747314.049586777</v>
+        <v>2783863.636363636</v>
       </c>
       <c r="N9" t="n">
-        <v>74.55371900826447</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>26.36574225418619</v>
+        <v>26.28077821777764</v>
       </c>
       <c r="P9" t="n">
-        <v>182.0992498263666</v>
+        <v>182.1002924182987</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.769734558178494</v>
+        <v>1.769360468859897</v>
       </c>
       <c r="R9" t="n">
-        <v>76.45813842907666</v>
+        <v>76.40745118725668</v>
       </c>
       <c r="S9" t="n">
-        <v>15930104.30886175</v>
+        <v>15846594.62019674</v>
       </c>
       <c r="T9" t="n">
-        <v>79.51491332635497</v>
+        <v>79.5338229466948</v>
       </c>
       <c r="U9" t="n">
-        <v>25.70307692307692</v>
+        <v>25.77338461538462</v>
       </c>
       <c r="V9" t="n">
-        <v>181.7978385251113</v>
+        <v>181.8730769230769</v>
       </c>
       <c r="W9" t="n">
-        <v>1.036020343293071</v>
+        <v>1.035076923076923</v>
       </c>
       <c r="X9" t="n">
-        <v>67.48634456452638</v>
+        <v>67.49861538461539</v>
       </c>
       <c r="Y9" t="n">
-        <v>1625925.047679593</v>
+        <v>1620358.461538462</v>
       </c>
       <c r="Z9" t="n">
-        <v>72.29641449459632</v>
+        <v>72.28969230769231</v>
       </c>
     </row>
     <row r="10">
@@ -1221,76 +1221,76 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>23.98863636363636</v>
+        <v>23.94805194805195</v>
       </c>
       <c r="D10" t="n">
-        <v>184.5227272727273</v>
+        <v>184.7662337662337</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>71.97402597402598</v>
       </c>
       <c r="G10" t="n">
-        <v>5391477.272727273</v>
+        <v>5398051.948051949</v>
       </c>
       <c r="H10" t="n">
-        <v>77.80681818181819</v>
+        <v>77.83116883116884</v>
       </c>
       <c r="I10" t="n">
-        <v>25.75537190082645</v>
+        <v>25.52090909090909</v>
       </c>
       <c r="J10" t="n">
-        <v>187.2752066115702</v>
+        <v>187.4727272727272</v>
       </c>
       <c r="K10" t="n">
-        <v>1.52396694214876</v>
+        <v>1.486363636363637</v>
       </c>
       <c r="L10" t="n">
-        <v>78.25785123966942</v>
+        <v>78.13363636363637</v>
       </c>
       <c r="M10" t="n">
-        <v>19109917.3553719</v>
+        <v>18975909.09090909</v>
       </c>
       <c r="N10" t="n">
-        <v>81.68429752066116</v>
+        <v>81.75272727272727</v>
       </c>
       <c r="O10" t="n">
-        <v>23.22237078139252</v>
+        <v>23.30908309082222</v>
       </c>
       <c r="P10" t="n">
-        <v>183.2658117968988</v>
+        <v>183.3037849107414</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.069461842505321</v>
+        <v>1.073890457368718</v>
       </c>
       <c r="R10" t="n">
-        <v>68.05325554879903</v>
+        <v>67.99492941840768</v>
       </c>
       <c r="S10" t="n">
-        <v>2579401.92687747</v>
+        <v>2511074.729618208</v>
       </c>
       <c r="T10" t="n">
-        <v>74.7467338096686</v>
+        <v>74.56220127698388</v>
       </c>
       <c r="U10" t="n">
-        <v>25.38361215493627</v>
+        <v>25.54789929635582</v>
       </c>
       <c r="V10" t="n">
-        <v>186.6604602760729</v>
+        <v>186.5524322296062</v>
       </c>
       <c r="W10" t="n">
-        <v>1.364253017513887</v>
+        <v>1.378456097043054</v>
       </c>
       <c r="X10" t="n">
-        <v>74.84356183488593</v>
+        <v>74.94643653689306</v>
       </c>
       <c r="Y10" t="n">
-        <v>13401761.69949945</v>
+        <v>13650326.75833828</v>
       </c>
       <c r="Z10" t="n">
-        <v>78.7814826112257</v>
+        <v>78.73000124271864</v>
       </c>
     </row>
     <row r="11">
@@ -1303,1880 +1303,2106 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25.70012626262626</v>
+        <v>25.62976992143659</v>
       </c>
       <c r="D11" t="n">
-        <v>186.4155303030303</v>
+        <v>186.3258978675645</v>
       </c>
       <c r="E11" t="n">
-        <v>1.789520202020202</v>
+        <v>1.77847923681257</v>
       </c>
       <c r="F11" t="n">
-        <v>80.31452020202019</v>
+        <v>80.13959034792367</v>
       </c>
       <c r="G11" t="n">
-        <v>30109873.73737373</v>
+        <v>29548007.85634119</v>
       </c>
       <c r="H11" t="n">
-        <v>83.91856060606059</v>
+        <v>83.84778338945006</v>
       </c>
       <c r="I11" t="n">
-        <v>25.81904761904762</v>
+        <v>25.95555555555556</v>
       </c>
       <c r="J11" t="n">
-        <v>181.2777777777778</v>
+        <v>181.0648148148148</v>
       </c>
       <c r="K11" t="n">
-        <v>1.044444444444445</v>
+        <v>1.051851851851852</v>
       </c>
       <c r="L11" t="n">
-        <v>71.04126984126985</v>
+        <v>71.02962962962964</v>
       </c>
       <c r="M11" t="n">
-        <v>3379007.936507937</v>
+        <v>3338935.185185185</v>
       </c>
       <c r="N11" t="n">
-        <v>73.44603174603175</v>
+        <v>73.29814814814814</v>
       </c>
       <c r="O11" t="n">
-        <v>24.95681017266487</v>
+        <v>25.06312241407207</v>
       </c>
       <c r="P11" t="n">
-        <v>183.9841642974366</v>
+        <v>184.076849219374</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.787877817072325</v>
+        <v>1.808753130080361</v>
       </c>
       <c r="R11" t="n">
-        <v>76.4989776367797</v>
+        <v>76.60997515197744</v>
       </c>
       <c r="S11" t="n">
-        <v>16456180.72429097</v>
+        <v>16744923.02698996</v>
       </c>
       <c r="T11" t="n">
-        <v>81.71066422809329</v>
+        <v>81.66740469788144</v>
       </c>
       <c r="U11" t="n">
-        <v>26.30193732193732</v>
+        <v>26.42016144349478</v>
       </c>
       <c r="V11" t="n">
-        <v>183.4291900691901</v>
+        <v>183.3278822412156</v>
       </c>
       <c r="W11" t="n">
-        <v>1.247944647944648</v>
+        <v>1.264577397910731</v>
       </c>
       <c r="X11" t="n">
-        <v>69.90273504273503</v>
+        <v>70.08405508072174</v>
       </c>
       <c r="Y11" t="n">
-        <v>2647104.029304029</v>
+        <v>2746374.45394112</v>
       </c>
       <c r="Z11" t="n">
-        <v>72.62474562474563</v>
+        <v>72.65479582146249</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.73181818181818</v>
+      </c>
+      <c r="D12" t="n">
+        <v>185.019696969697</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.063636363636364</v>
+      </c>
+      <c r="F12" t="n">
+        <v>69.83636363636363</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2975833.333333333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75.5439393939394</v>
+      </c>
+      <c r="I12" t="n">
+        <v>25.3008658008658</v>
+      </c>
+      <c r="J12" t="n">
+        <v>184.4738816738817</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.754978354978355</v>
+      </c>
+      <c r="L12" t="n">
+        <v>79.97301587301588</v>
+      </c>
+      <c r="M12" t="n">
+        <v>31599733.04473305</v>
+      </c>
+      <c r="N12" t="n">
+        <v>83.74733044733044</v>
+      </c>
+      <c r="O12" t="n">
+        <v>25.23322081836575</v>
+      </c>
+      <c r="P12" t="n">
+        <v>184.4230924067881</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.117838783599653</v>
+      </c>
+      <c r="R12" t="n">
+        <v>68.38258443783806</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2260378.02190429</v>
+      </c>
+      <c r="T12" t="n">
+        <v>73.27418297617572</v>
+      </c>
+      <c r="U12" t="n">
+        <v>24.44167626024769</v>
+      </c>
+      <c r="V12" t="n">
+        <v>185.1718472004186</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.529103436246293</v>
+      </c>
+      <c r="X12" t="n">
+        <v>76.28516774231061</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22503626.54805512</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>82.00816210244781</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24.62337662337663</v>
+      </c>
+      <c r="D13" t="n">
+        <v>187.3766233766234</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.038961038961039</v>
+      </c>
+      <c r="F13" t="n">
+        <v>73.16883116883118</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5062337.662337663</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77.32467532467533</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.78863636363636</v>
+      </c>
+      <c r="J13" t="n">
+        <v>183.7431818181818</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.723863636363636</v>
+      </c>
+      <c r="L13" t="n">
+        <v>77.53522727272727</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18098636.36363636</v>
+      </c>
+      <c r="N13" t="n">
+        <v>79.77954545454546</v>
+      </c>
+      <c r="O13" t="n">
+        <v>25.29097394513361</v>
+      </c>
+      <c r="P13" t="n">
+        <v>183.0837984082522</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.083890889689209</v>
+      </c>
+      <c r="R13" t="n">
+        <v>70.58646147347828</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3076779.189453559</v>
+      </c>
+      <c r="T13" t="n">
+        <v>74.6091898981815</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.28077821777764</v>
+      </c>
+      <c r="V13" t="n">
+        <v>182.1002924182987</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.769360468859897</v>
+      </c>
+      <c r="X13" t="n">
+        <v>76.40745118725668</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15846594.62019674</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>79.5338229466948</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27.84285714285715</v>
+      </c>
+      <c r="D14" t="n">
+        <v>183.264935064935</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.344155844155844</v>
+      </c>
+      <c r="F14" t="n">
+        <v>82.57532467532469</v>
+      </c>
+      <c r="G14" t="n">
+        <v>38316883.11688311</v>
+      </c>
+      <c r="H14" t="n">
+        <v>84.55974025974025</v>
+      </c>
+      <c r="I14" t="n">
+        <v>23.94805194805195</v>
+      </c>
+      <c r="J14" t="n">
+        <v>184.7662337662337</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>71.97402597402598</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5398051.948051949</v>
+      </c>
+      <c r="N14" t="n">
+        <v>77.83116883116884</v>
+      </c>
+      <c r="O14" t="n">
+        <v>27.46499447642305</v>
+      </c>
+      <c r="P14" t="n">
+        <v>182.3110756439328</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.937458573172858</v>
+      </c>
+      <c r="R14" t="n">
+        <v>79.01235246235247</v>
+      </c>
+      <c r="S14" t="n">
+        <v>23844299.66858539</v>
+      </c>
+      <c r="T14" t="n">
+        <v>81.30223268794695</v>
+      </c>
+      <c r="U14" t="n">
+        <v>23.30908309082222</v>
+      </c>
+      <c r="V14" t="n">
+        <v>183.3037849107414</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.073890457368718</v>
+      </c>
+      <c r="X14" t="n">
+        <v>67.99492941840768</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2511074.729618208</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>74.56220127698388</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.28961038961039</v>
+      </c>
+      <c r="D15" t="n">
+        <v>183.5194805194805</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.346753246753247</v>
+      </c>
+      <c r="F15" t="n">
+        <v>73.22077922077922</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7368311.688311689</v>
+      </c>
+      <c r="H15" t="n">
+        <v>77.66493506493508</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25.75714285714286</v>
+      </c>
+      <c r="J15" t="n">
+        <v>184.5428571428571</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="L15" t="n">
+        <v>72.94285714285715</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6193214.285714285</v>
+      </c>
+      <c r="N15" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>25.83945585815151</v>
+      </c>
+      <c r="P15" t="n">
+        <v>182.2817141795403</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.321755587407761</v>
+      </c>
+      <c r="R15" t="n">
+        <v>71.60149165649166</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4130323.399426661</v>
+      </c>
+      <c r="T15" t="n">
+        <v>76.81114455592716</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.54104041616646</v>
+      </c>
+      <c r="V15" t="n">
+        <v>184.7348299319728</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.335388155262105</v>
+      </c>
+      <c r="X15" t="n">
+        <v>70.03281512605042</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3335327.781112445</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>73.8702581032413</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>25.74204545454545</v>
+        <v>26.16060606060606</v>
       </c>
       <c r="D16" t="n">
-        <v>186.9363636363636</v>
+        <v>183.3848484848485</v>
       </c>
       <c r="E16" t="n">
-        <v>1.214772727272727</v>
+        <v>1.615151515151515</v>
       </c>
       <c r="F16" t="n">
-        <v>73.25</v>
+        <v>76.28282828282828</v>
       </c>
       <c r="G16" t="n">
-        <v>5306079.545454546</v>
+        <v>12461010.1010101</v>
       </c>
       <c r="H16" t="n">
-        <v>77.25454545454545</v>
+        <v>79.4969696969697</v>
       </c>
       <c r="I16" t="n">
-        <v>25.44285714285714</v>
+        <v>24.83636363636364</v>
       </c>
       <c r="J16" t="n">
-        <v>183.563492063492</v>
+        <v>184.9181818181818</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>66.64603174603175</v>
+        <v>69.95454545454545</v>
       </c>
       <c r="M16" t="n">
-        <v>1211587.301587302</v>
+        <v>2783863.636363636</v>
       </c>
       <c r="N16" t="n">
-        <v>70.44444444444444</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>24.18748135890846</v>
+        <v>25.33106574985469</v>
       </c>
       <c r="P16" t="n">
-        <v>185.0565917079616</v>
+        <v>182.0266687108216</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.13142152900961</v>
+        <v>1.59366858356197</v>
       </c>
       <c r="R16" t="n">
-        <v>70.81202993245441</v>
+        <v>74.74005921472855</v>
       </c>
       <c r="S16" t="n">
-        <v>3964935.51087704</v>
+        <v>11493538.01718053</v>
       </c>
       <c r="T16" t="n">
-        <v>77.16509865602913</v>
+        <v>79.09131933693986</v>
       </c>
       <c r="U16" t="n">
-        <v>24.89280560709132</v>
+        <v>25.77338461538462</v>
       </c>
       <c r="V16" t="n">
-        <v>183.361605854463</v>
+        <v>181.8730769230769</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.035076923076923</v>
       </c>
       <c r="X16" t="n">
-        <v>64.58005875077303</v>
+        <v>67.49861538461539</v>
       </c>
       <c r="Y16" t="n">
-        <v>1031453.133374562</v>
+        <v>1620358.461538462</v>
       </c>
       <c r="Z16" t="n">
-        <v>69.26774582560297</v>
+        <v>72.28969230769231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>25.96931818181818</v>
+        <v>25.77922077922078</v>
       </c>
       <c r="D17" t="n">
-        <v>184.3045454545455</v>
+        <v>186.4</v>
       </c>
       <c r="E17" t="n">
-        <v>1.198863636363636</v>
+        <v>1.225974025974026</v>
       </c>
       <c r="F17" t="n">
-        <v>72.93863636363636</v>
+        <v>76.05454545454545</v>
       </c>
       <c r="G17" t="n">
-        <v>6104289.772727272</v>
+        <v>13493376.62337662</v>
       </c>
       <c r="H17" t="n">
-        <v>77.51022727272726</v>
+        <v>79.3987012987013</v>
       </c>
       <c r="I17" t="n">
-        <v>26.08051948051948</v>
+        <v>25.52090909090909</v>
       </c>
       <c r="J17" t="n">
-        <v>184.2207792207792</v>
+        <v>187.4727272727272</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>1.486363636363637</v>
       </c>
       <c r="L17" t="n">
-        <v>65.64805194805194</v>
+        <v>78.13363636363637</v>
       </c>
       <c r="M17" t="n">
-        <v>1164110.389610389</v>
+        <v>18975909.09090909</v>
       </c>
       <c r="N17" t="n">
-        <v>68.99999999999999</v>
+        <v>81.75272727272727</v>
       </c>
       <c r="O17" t="n">
-        <v>26.42966036414566</v>
+        <v>25.10075684978936</v>
       </c>
       <c r="P17" t="n">
-        <v>184.9304761904762</v>
+        <v>184.6815733071538</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.330964635854342</v>
+        <v>1.22042159766618</v>
       </c>
       <c r="R17" t="n">
-        <v>69.99121323529413</v>
+        <v>72.04932010284178</v>
       </c>
       <c r="S17" t="n">
-        <v>3309505.558473389</v>
+        <v>5788223.678626155</v>
       </c>
       <c r="T17" t="n">
-        <v>73.83022584033614</v>
+        <v>75.75028893535087</v>
       </c>
       <c r="U17" t="n">
-        <v>26.15596963423051</v>
+        <v>25.54789929635582</v>
       </c>
       <c r="V17" t="n">
-        <v>182.3768115942029</v>
+        <v>186.5524322296062</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.378456097043054</v>
       </c>
       <c r="X17" t="n">
-        <v>64.2716816195077</v>
+        <v>74.94643653689306</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000485.480702872</v>
+        <v>13650326.75833828</v>
       </c>
       <c r="Z17" t="n">
-        <v>67.93227867140909</v>
+        <v>78.73000124271864</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.52840909090909</v>
+        <v>26.14025974025974</v>
       </c>
       <c r="D18" t="n">
-        <v>183.5920454545455</v>
+        <v>182.4363636363637</v>
       </c>
       <c r="E18" t="n">
-        <v>1.353409090909091</v>
+        <v>2.096103896103896</v>
       </c>
       <c r="F18" t="n">
-        <v>73.40568181818182</v>
+        <v>78.55064935064934</v>
       </c>
       <c r="G18" t="n">
-        <v>7352272.727272728</v>
+        <v>21361298.7012987</v>
       </c>
       <c r="H18" t="n">
-        <v>77.5443181818182</v>
+        <v>80.65584415584415</v>
       </c>
       <c r="I18" t="n">
-        <v>28.87142857142857</v>
+        <v>25.53246753246754</v>
       </c>
       <c r="J18" t="n">
-        <v>183.4142857142857</v>
+        <v>183.8571428571429</v>
       </c>
       <c r="K18" t="n">
-        <v>1.157142857142857</v>
+        <v>1.038961038961039</v>
       </c>
       <c r="L18" t="n">
-        <v>67.78571428571429</v>
+        <v>72.37662337662339</v>
       </c>
       <c r="M18" t="n">
-        <v>1045500</v>
+        <v>4474025.974025974</v>
       </c>
       <c r="N18" t="n">
-        <v>69.98571428571428</v>
+        <v>76.05194805194806</v>
       </c>
       <c r="O18" t="n">
-        <v>25.58548541434411</v>
+        <v>25.39790946145626</v>
       </c>
       <c r="P18" t="n">
-        <v>182.2128460609439</v>
+        <v>183.0843898803259</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.291151523597176</v>
+        <v>1.95192613443845</v>
       </c>
       <c r="R18" t="n">
-        <v>71.43976673789174</v>
+        <v>76.29772475745382</v>
       </c>
       <c r="S18" t="n">
-        <v>4134585.859113712</v>
+        <v>17108203.40396695</v>
       </c>
       <c r="T18" t="n">
-        <v>76.88763610182087</v>
+        <v>80.3989667101736</v>
       </c>
       <c r="U18" t="n">
-        <v>25.22084760994699</v>
+        <v>25.06424792139078</v>
       </c>
       <c r="V18" t="n">
-        <v>185.1004652191609</v>
+        <v>182.1354003139717</v>
       </c>
       <c r="W18" t="n">
-        <v>1.035889359088117</v>
+        <v>1.131577417291703</v>
       </c>
       <c r="X18" t="n">
-        <v>65.26384562297606</v>
+        <v>70.0292168149311</v>
       </c>
       <c r="Y18" t="n">
-        <v>999487.5229727715</v>
+        <v>3060825.48403977</v>
       </c>
       <c r="Z18" t="n">
-        <v>68.73200984890426</v>
+        <v>74.85582010582011</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>26.78567493112947</v>
+        <v>26.18441558441559</v>
       </c>
       <c r="D19" t="n">
-        <v>185.6598714416896</v>
+        <v>182.4324675324676</v>
       </c>
       <c r="E19" t="n">
-        <v>1.085123966942149</v>
+        <v>1.7</v>
       </c>
       <c r="F19" t="n">
-        <v>69.30918273645547</v>
+        <v>80.58311688311689</v>
       </c>
       <c r="G19" t="n">
-        <v>1959320.477502296</v>
+        <v>35072207.79220779</v>
       </c>
       <c r="H19" t="n">
-        <v>72.65656565656565</v>
+        <v>82.4909090909091</v>
       </c>
       <c r="I19" t="n">
-        <v>27.89450056116723</v>
+        <v>24.45454545454546</v>
       </c>
       <c r="J19" t="n">
-        <v>180.9455667789001</v>
+        <v>185.5064935064935</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.25974025974026</v>
       </c>
       <c r="L19" t="n">
-        <v>67.60897867564535</v>
+        <v>74.75324675324676</v>
       </c>
       <c r="M19" t="n">
-        <v>1260000</v>
+        <v>10753246.75324675</v>
       </c>
       <c r="N19" t="n">
-        <v>69.80953984287318</v>
+        <v>79.57142857142857</v>
       </c>
       <c r="O19" t="n">
-        <v>27.35946734424995</v>
+        <v>24.70533731834042</v>
       </c>
       <c r="P19" t="n">
-        <v>185.3063988843831</v>
+        <v>180.9094669233988</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.12314477354003</v>
+        <v>1.512483861168072</v>
       </c>
       <c r="R19" t="n">
-        <v>70.03460688191913</v>
+        <v>75.60444132464256</v>
       </c>
       <c r="S19" t="n">
-        <v>2126572.170747566</v>
+        <v>15968914.05485639</v>
       </c>
       <c r="T19" t="n">
-        <v>73.13433396642883</v>
+        <v>79.08295471298568</v>
       </c>
       <c r="U19" t="n">
-        <v>25.19443532313097</v>
+        <v>23.04809054656345</v>
       </c>
       <c r="V19" t="n">
-        <v>178.4018239248674</v>
+        <v>184.8191109547267</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.212904058174994</v>
       </c>
       <c r="X19" t="n">
-        <v>65.03192696192696</v>
+        <v>71.26351395730707</v>
       </c>
       <c r="Y19" t="n">
-        <v>1260961.610129001</v>
+        <v>7002015.012901713</v>
       </c>
       <c r="Z19" t="n">
-        <v>69.59661227661228</v>
+        <v>78.05814684494487</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.53409090909091</v>
+        <v>25.16883116883117</v>
       </c>
       <c r="D20" t="n">
-        <v>183.9772727272727</v>
+        <v>184.1688311688311</v>
       </c>
       <c r="E20" t="n">
-        <v>1.034090909090909</v>
+        <v>1.194805194805195</v>
       </c>
       <c r="F20" t="n">
-        <v>72.38636363636364</v>
+        <v>72.1038961038961</v>
       </c>
       <c r="G20" t="n">
-        <v>4504545.454545455</v>
+        <v>3715584.415584415</v>
       </c>
       <c r="H20" t="n">
-        <v>76.01136363636363</v>
+        <v>76</v>
       </c>
       <c r="I20" t="n">
-        <v>26.86</v>
+        <v>25.95555555555556</v>
       </c>
       <c r="J20" t="n">
-        <v>181.6572727272727</v>
+        <v>181.0648148148148</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>1.051851851851852</v>
       </c>
       <c r="L20" t="n">
-        <v>67.4309090909091</v>
+        <v>71.02962962962964</v>
       </c>
       <c r="M20" t="n">
-        <v>1277590.909090909</v>
+        <v>3338935.185185185</v>
       </c>
       <c r="N20" t="n">
-        <v>70.28545454545454</v>
+        <v>73.29814814814814</v>
       </c>
       <c r="O20" t="n">
-        <v>24.95436507936508</v>
+        <v>26.03209458849853</v>
       </c>
       <c r="P20" t="n">
-        <v>182.1184752747253</v>
+        <v>183.2602555080387</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.133648758648758</v>
+        <v>1.165195149677908</v>
       </c>
       <c r="R20" t="n">
-        <v>69.99778693528694</v>
+        <v>70.11228188888286</v>
       </c>
       <c r="S20" t="n">
-        <v>3049588.039275539</v>
+        <v>2659948.519460835</v>
       </c>
       <c r="T20" t="n">
-        <v>74.91550925925927</v>
+        <v>74.10430628484816</v>
       </c>
       <c r="U20" t="n">
-        <v>25.63088518888519</v>
+        <v>26.42016144349478</v>
       </c>
       <c r="V20" t="n">
-        <v>179.4868835053835</v>
+        <v>183.3278822412156</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.264577397910731</v>
       </c>
       <c r="X20" t="n">
-        <v>66.03421056721056</v>
+        <v>70.08405508072174</v>
       </c>
       <c r="Y20" t="n">
-        <v>1188850.593850594</v>
+        <v>2746374.45394112</v>
       </c>
       <c r="Z20" t="n">
-        <v>70.69366881266882</v>
+        <v>72.65479582146249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>26.18636363636364</v>
+        <v>24.92207792207792</v>
       </c>
       <c r="D21" t="n">
-        <v>182.5409090909091</v>
+        <v>184.038961038961</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7125</v>
+        <v>1.116883116883117</v>
       </c>
       <c r="F21" t="n">
-        <v>80.72272727272728</v>
+        <v>72.85714285714286</v>
       </c>
       <c r="G21" t="n">
-        <v>35875681.81818182</v>
+        <v>4697077.922077922</v>
       </c>
       <c r="H21" t="n">
-        <v>82.60454545454546</v>
+        <v>76.6103896103896</v>
       </c>
       <c r="I21" t="n">
-        <v>26.41558441558441</v>
+        <v>25.62976992143659</v>
       </c>
       <c r="J21" t="n">
-        <v>184.3896103896104</v>
+        <v>186.3258978675645</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>1.77847923681257</v>
       </c>
       <c r="L21" t="n">
-        <v>67.1948051948052</v>
+        <v>80.13959034792367</v>
       </c>
       <c r="M21" t="n">
-        <v>1326623.376623377</v>
+        <v>29548007.85634119</v>
       </c>
       <c r="N21" t="n">
-        <v>70.55844155844156</v>
+        <v>83.84778338945006</v>
       </c>
       <c r="O21" t="n">
-        <v>24.8723784868812</v>
+        <v>24.05835368335368</v>
       </c>
       <c r="P21" t="n">
-        <v>180.7384918913073</v>
+        <v>182.74185999186</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.526548378522063</v>
+        <v>1.041761148904006</v>
       </c>
       <c r="R21" t="n">
-        <v>75.77367782572891</v>
+        <v>70.55081690795977</v>
       </c>
       <c r="S21" t="n">
-        <v>16078138.33966601</v>
+        <v>3384843.232164661</v>
       </c>
       <c r="T21" t="n">
-        <v>79.16112704052912</v>
+        <v>75.3547953369382</v>
       </c>
       <c r="U21" t="n">
-        <v>24.41948883414722</v>
+        <v>25.06312241407207</v>
       </c>
       <c r="V21" t="n">
-        <v>183.4407367511715</v>
+        <v>184.076849219374</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.808753130080361</v>
       </c>
       <c r="X21" t="n">
-        <v>64.15824666706655</v>
+        <v>76.60997515197744</v>
       </c>
       <c r="Y21" t="n">
-        <v>1029831.372285409</v>
+        <v>16744923.02698996</v>
       </c>
       <c r="Z21" t="n">
-        <v>69.70320721376621</v>
+        <v>81.66740469788144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>25.53409090909091</v>
+        <v>25.61428571428572</v>
       </c>
       <c r="D22" t="n">
-        <v>182.8522727272727</v>
+        <v>187.1350649350649</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>1.206493506493507</v>
       </c>
       <c r="F22" t="n">
-        <v>67.30000000000001</v>
+        <v>73.09090909090909</v>
       </c>
       <c r="G22" t="n">
-        <v>1397642.045454545</v>
+        <v>5204350.64935065</v>
       </c>
       <c r="H22" t="n">
-        <v>71.20227272727273</v>
+        <v>77.32987012987012</v>
       </c>
       <c r="I22" t="n">
-        <v>24.86776859504132</v>
+        <v>25.2</v>
       </c>
       <c r="J22" t="n">
-        <v>184.801652892562</v>
+        <v>183.6740740740741</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>69.91735537190083</v>
+        <v>66.58703703703704</v>
       </c>
       <c r="M22" t="n">
-        <v>2747314.049586777</v>
+        <v>1224768.518518518</v>
       </c>
       <c r="N22" t="n">
-        <v>74.55371900826447</v>
+        <v>70.55185185185185</v>
       </c>
       <c r="O22" t="n">
-        <v>23.55517977618334</v>
+        <v>24.13351906856619</v>
       </c>
       <c r="P22" t="n">
-        <v>182.0915905886342</v>
+        <v>184.803806672453</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>1.131562492781169</v>
       </c>
       <c r="R22" t="n">
-        <v>64.00166367709002</v>
+        <v>70.74169880479262</v>
       </c>
       <c r="S22" t="n">
-        <v>1151393.808676019</v>
+        <v>3987255.490691773</v>
       </c>
       <c r="T22" t="n">
-        <v>71.1175412293853</v>
+        <v>77.17005063794633</v>
       </c>
       <c r="U22" t="n">
-        <v>25.70307692307692</v>
+        <v>24.87493987493987</v>
       </c>
       <c r="V22" t="n">
-        <v>181.7978385251113</v>
+        <v>183.4552068302069</v>
       </c>
       <c r="W22" t="n">
-        <v>1.036020343293071</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>67.48634456452638</v>
+        <v>64.39673520923522</v>
       </c>
       <c r="Y22" t="n">
-        <v>1625925.047679593</v>
+        <v>1007061.988936989</v>
       </c>
       <c r="Z22" t="n">
-        <v>72.29641449459632</v>
+        <v>69.19237012987013</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>24.67012987012987</v>
+        <v>24.62337662337663</v>
       </c>
       <c r="D23" t="n">
-        <v>184.774025974026</v>
+        <v>187.3766233766234</v>
       </c>
       <c r="E23" t="n">
-        <v>1.068831168831169</v>
+        <v>1.038961038961039</v>
       </c>
       <c r="F23" t="n">
-        <v>69.61688311688312</v>
+        <v>73.16883116883118</v>
       </c>
       <c r="G23" t="n">
-        <v>2894285.714285714</v>
+        <v>5062337.662337663</v>
       </c>
       <c r="H23" t="n">
-        <v>75.32337662337662</v>
-      </c>
-      <c r="I23" t="n">
-        <v>26.27272727272727</v>
-      </c>
-      <c r="J23" t="n">
-        <v>183.2363636363637</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>70.37272727272727</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2475000</v>
-      </c>
-      <c r="N23" t="n">
-        <v>74.32727272727273</v>
-      </c>
+        <v>77.32467532467533</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>25.21638707508273</v>
+        <v>25.29097394513361</v>
       </c>
       <c r="P23" t="n">
-        <v>184.593419865159</v>
+        <v>183.0837984082522</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.106499177151351</v>
+        <v>1.083890889689209</v>
       </c>
       <c r="R23" t="n">
-        <v>68.52573171594911</v>
+        <v>70.58646147347828</v>
       </c>
       <c r="S23" t="n">
-        <v>2359444.897895985</v>
+        <v>3076779.189453559</v>
       </c>
       <c r="T23" t="n">
-        <v>73.46028870485392</v>
+        <v>74.6091898981815</v>
       </c>
       <c r="U23" t="n">
-        <v>25.62051158181593</v>
+        <v>27.5</v>
       </c>
       <c r="V23" t="n">
-        <v>181.8859912671869</v>
+        <v>182.8333333333333</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>68.5828369255543</v>
+        <v>67.16666666666667</v>
       </c>
       <c r="Y23" t="n">
-        <v>2021058.55165366</v>
+        <v>1137500</v>
       </c>
       <c r="Z23" t="n">
-        <v>73.32199616003963</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>23.66022727272727</v>
+        <v>25.75714285714286</v>
       </c>
       <c r="D24" t="n">
-        <v>184.1909090909091</v>
+        <v>184.5428571428571</v>
       </c>
       <c r="E24" t="n">
-        <v>1.152272727272727</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="F24" t="n">
-        <v>68.21590909090909</v>
+        <v>72.94285714285715</v>
       </c>
       <c r="G24" t="n">
-        <v>2279204.545454545</v>
+        <v>6193214.285714285</v>
       </c>
       <c r="H24" t="n">
-        <v>75.2715909090909</v>
+        <v>77.7</v>
       </c>
       <c r="I24" t="n">
-        <v>25.81904761904762</v>
+        <v>26.01060606060606</v>
       </c>
       <c r="J24" t="n">
-        <v>181.2777777777778</v>
+        <v>184.1075757575757</v>
       </c>
       <c r="K24" t="n">
-        <v>1.044444444444445</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>71.04126984126985</v>
+        <v>65.63939393939394</v>
       </c>
       <c r="M24" t="n">
-        <v>3379007.936507937</v>
+        <v>1166545.454545454</v>
       </c>
       <c r="N24" t="n">
-        <v>73.44603174603175</v>
+        <v>68.98333333333333</v>
       </c>
       <c r="O24" t="n">
-        <v>24.65211410541157</v>
+        <v>26.54104041616646</v>
       </c>
       <c r="P24" t="n">
-        <v>183.7964656070138</v>
+        <v>184.7348299319728</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.163153532624104</v>
+        <v>1.335388155262105</v>
       </c>
       <c r="R24" t="n">
-        <v>68.57053335988506</v>
+        <v>70.03281512605042</v>
       </c>
       <c r="S24" t="n">
-        <v>2403303.461797939</v>
+        <v>3335327.781112445</v>
       </c>
       <c r="T24" t="n">
-        <v>75.02834098236198</v>
+        <v>73.8702581032413</v>
       </c>
       <c r="U24" t="n">
-        <v>26.30193732193732</v>
+        <v>26.18196457326892</v>
       </c>
       <c r="V24" t="n">
-        <v>183.4291900691901</v>
+        <v>182.4396135265701</v>
       </c>
       <c r="W24" t="n">
-        <v>1.247944647944648</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>69.90273504273503</v>
+        <v>64.31696188942566</v>
       </c>
       <c r="Y24" t="n">
-        <v>2647104.029304029</v>
+        <v>1003643.317230274</v>
       </c>
       <c r="Z24" t="n">
-        <v>72.62474562474563</v>
+        <v>68.0107353730542</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>25.84431818181818</v>
+        <v>25.28961038961039</v>
       </c>
       <c r="D25" t="n">
-        <v>186.2375</v>
+        <v>183.5194805194805</v>
       </c>
       <c r="E25" t="n">
-        <v>1.235227272727273</v>
+        <v>1.346753246753247</v>
       </c>
       <c r="F25" t="n">
-        <v>76.16022727272727</v>
+        <v>73.22077922077922</v>
       </c>
       <c r="G25" t="n">
-        <v>13589204.54545454</v>
+        <v>7368311.688311689</v>
       </c>
       <c r="H25" t="n">
-        <v>79.38636363636363</v>
+        <v>77.66493506493508</v>
       </c>
       <c r="I25" t="n">
-        <v>26.32467532467533</v>
+        <v>28.75</v>
       </c>
       <c r="J25" t="n">
-        <v>182.3246753246753</v>
+        <v>183.4833333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="L25" t="n">
-        <v>68.09090909090909</v>
+        <v>67.7</v>
       </c>
       <c r="M25" t="n">
-        <v>1386038.961038961</v>
+        <v>1041250</v>
       </c>
       <c r="N25" t="n">
-        <v>71.15584415584416</v>
+        <v>69.95</v>
       </c>
       <c r="O25" t="n">
-        <v>25.07500434882884</v>
+        <v>25.83945585815151</v>
       </c>
       <c r="P25" t="n">
-        <v>184.7674292753385</v>
+        <v>182.2817141795403</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.219184687431591</v>
+        <v>1.321755587407761</v>
       </c>
       <c r="R25" t="n">
-        <v>72.01683930051286</v>
+        <v>71.60149165649166</v>
       </c>
       <c r="S25" t="n">
-        <v>5636406.245113675</v>
+        <v>4130323.399426661</v>
       </c>
       <c r="T25" t="n">
-        <v>75.79466071316884</v>
+        <v>76.81114455592716</v>
       </c>
       <c r="U25" t="n">
-        <v>24.05117623117623</v>
+        <v>25.29765554493816</v>
       </c>
       <c r="V25" t="n">
-        <v>182.15185999186</v>
+        <v>185.003876089021</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.028537585602803</v>
       </c>
       <c r="X25" t="n">
-        <v>66.85603581603581</v>
+        <v>65.28115322680542</v>
       </c>
       <c r="Y25" t="n">
-        <v>1492421.041921042</v>
+        <v>1006235.443468233</v>
       </c>
       <c r="Z25" t="n">
-        <v>72.97322751322751</v>
+        <v>68.66067815705496</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>24.10227272727273</v>
+        <v>26.95424242424243</v>
       </c>
       <c r="D26" t="n">
-        <v>184.7272727272727</v>
+        <v>185.3758585858586</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>1.083636363636364</v>
       </c>
       <c r="F26" t="n">
-        <v>71.06818181818181</v>
+        <v>69.25010101010102</v>
       </c>
       <c r="G26" t="n">
-        <v>4321590.909090909</v>
+        <v>1925252.525252525</v>
       </c>
       <c r="H26" t="n">
-        <v>76.45454545454545</v>
+        <v>72.48222222222223</v>
       </c>
       <c r="I26" t="n">
-        <v>25.81298701298701</v>
+        <v>27.79040404040404</v>
       </c>
       <c r="J26" t="n">
-        <v>181.7987012987013</v>
+        <v>180.6546717171717</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>67.54415584415585</v>
+        <v>67.53737373737374</v>
       </c>
       <c r="M26" t="n">
-        <v>1533863.636363636</v>
+        <v>1260000</v>
       </c>
       <c r="N26" t="n">
-        <v>71.94415584415584</v>
+        <v>69.83118686868687</v>
       </c>
       <c r="O26" t="n">
-        <v>23.19467686999546</v>
+        <v>27.38291407867495</v>
       </c>
       <c r="P26" t="n">
-        <v>184.6840424242036</v>
+        <v>185.4870387728214</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>1.1271259175607</v>
       </c>
       <c r="R26" t="n">
-        <v>67.5394128219981</v>
+        <v>69.98390090344438</v>
       </c>
       <c r="S26" t="n">
-        <v>2556680.846396925</v>
+        <v>2094229.387822323</v>
       </c>
       <c r="T26" t="n">
-        <v>74.71708972995049</v>
+        <v>73.07276736307172</v>
       </c>
       <c r="U26" t="n">
-        <v>26.58976060976061</v>
+        <v>25.10873973852235</v>
       </c>
       <c r="V26" t="n">
-        <v>181.9976401376401</v>
+        <v>178.3820519154758</v>
       </c>
       <c r="W26" t="n">
-        <v>1.114663114663115</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>66.7907018907019</v>
+        <v>64.90591783216783</v>
       </c>
       <c r="Y26" t="n">
-        <v>1349302.142302142</v>
+        <v>1252055.211817168</v>
       </c>
       <c r="Z26" t="n">
-        <v>70.48701964701965</v>
+        <v>69.53118881118883</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>02s0k9od</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>25.72537878787879</v>
+        <v>24.92207792207792</v>
       </c>
       <c r="D27" t="n">
-        <v>185.1551767676768</v>
+        <v>184.038961038961</v>
       </c>
       <c r="E27" t="n">
-        <v>1.326515151515151</v>
+        <v>1.116883116883117</v>
       </c>
       <c r="F27" t="n">
-        <v>71.22108585858585</v>
+        <v>72.85714285714286</v>
       </c>
       <c r="G27" t="n">
-        <v>3141243.686868687</v>
+        <v>4697077.922077922</v>
       </c>
       <c r="H27" t="n">
-        <v>76.6205808080808</v>
-      </c>
-      <c r="I27" t="n">
-        <v>25.89047619047619</v>
-      </c>
-      <c r="J27" t="n">
-        <v>183.2238095238095</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1.104761904761905</v>
-      </c>
-      <c r="L27" t="n">
-        <v>68.51904761904761</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1678769.841269841</v>
-      </c>
-      <c r="N27" t="n">
-        <v>72.43333333333334</v>
-      </c>
+        <v>76.6103896103896</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>24.82486140880104</v>
+        <v>24.05835368335368</v>
       </c>
       <c r="P27" t="n">
-        <v>183.8016459937551</v>
+        <v>182.74185999186</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.210687961419386</v>
+        <v>1.041761148904006</v>
       </c>
       <c r="R27" t="n">
-        <v>69.95947136884443</v>
+        <v>70.55081690795977</v>
       </c>
       <c r="S27" t="n">
-        <v>3162273.132161097</v>
+        <v>3384843.232164661</v>
       </c>
       <c r="T27" t="n">
-        <v>75.82969602550872</v>
-      </c>
-      <c r="U27" t="n">
-        <v>23.94467120181406</v>
-      </c>
-      <c r="V27" t="n">
-        <v>184.4581349206349</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>64.31975623582767</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1139713.860544218</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>70.93358843537415</v>
-      </c>
+        <v>75.3547953369382</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>25.53409090909091</v>
+        <v>25.53246753246754</v>
       </c>
       <c r="D28" t="n">
-        <v>182.8522727272727</v>
+        <v>183.8571428571429</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>1.038961038961039</v>
       </c>
       <c r="F28" t="n">
-        <v>67.30000000000001</v>
+        <v>72.37662337662339</v>
       </c>
       <c r="G28" t="n">
-        <v>1397642.045454545</v>
+        <v>4474025.974025974</v>
       </c>
       <c r="H28" t="n">
-        <v>71.20227272727273</v>
+        <v>76.05194805194806</v>
       </c>
       <c r="I28" t="n">
-        <v>26.27272727272727</v>
+        <v>26.76363636363637</v>
       </c>
       <c r="J28" t="n">
-        <v>183.2363636363637</v>
+        <v>181.659595959596</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>70.37272727272727</v>
+        <v>67.35757575757576</v>
       </c>
       <c r="M28" t="n">
-        <v>2475000</v>
+        <v>1273585.858585858</v>
       </c>
       <c r="N28" t="n">
-        <v>74.32727272727273</v>
+        <v>70.34747474747475</v>
       </c>
       <c r="O28" t="n">
-        <v>23.55517977618334</v>
+        <v>25.06424792139078</v>
       </c>
       <c r="P28" t="n">
-        <v>182.0915905886342</v>
+        <v>182.1354003139717</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>1.131577417291703</v>
       </c>
       <c r="R28" t="n">
-        <v>64.00166367709002</v>
+        <v>70.0292168149311</v>
       </c>
       <c r="S28" t="n">
-        <v>1151393.808676019</v>
+        <v>3060825.48403977</v>
       </c>
       <c r="T28" t="n">
-        <v>71.1175412293853</v>
+        <v>74.85582010582011</v>
       </c>
       <c r="U28" t="n">
-        <v>25.62051158181593</v>
+        <v>25.82098354320577</v>
       </c>
       <c r="V28" t="n">
-        <v>181.8859912671869</v>
+        <v>179.4209816726483</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>68.5828369255543</v>
+        <v>66.02912285245618</v>
       </c>
       <c r="Y28" t="n">
-        <v>2021058.55165366</v>
+        <v>1158056.215389549</v>
       </c>
       <c r="Z28" t="n">
-        <v>73.32199616003963</v>
+        <v>70.37074312518757</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>27.89450056116723</v>
+        <v>26.18441558441559</v>
       </c>
       <c r="D29" t="n">
-        <v>180.9455667789001</v>
+        <v>182.4324675324676</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="F29" t="n">
-        <v>67.60897867564535</v>
+        <v>80.58311688311689</v>
       </c>
       <c r="G29" t="n">
-        <v>1260000</v>
+        <v>35072207.79220779</v>
       </c>
       <c r="H29" t="n">
-        <v>69.80953984287318</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>82.4909090909091</v>
+      </c>
+      <c r="I29" t="n">
+        <v>26.24242424242424</v>
+      </c>
+      <c r="J29" t="n">
+        <v>184.4090909090909</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>67.10606060606061</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1326515.151515152</v>
+      </c>
+      <c r="N29" t="n">
+        <v>70.63636363636364</v>
+      </c>
       <c r="O29" t="n">
-        <v>25.19443532313097</v>
+        <v>24.70533731834042</v>
       </c>
       <c r="P29" t="n">
-        <v>178.4018239248674</v>
+        <v>180.9094669233988</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>1.512483861168072</v>
       </c>
       <c r="R29" t="n">
-        <v>65.03192696192696</v>
+        <v>75.60444132464256</v>
       </c>
       <c r="S29" t="n">
-        <v>1260961.610129001</v>
+        <v>15968914.05485639</v>
       </c>
       <c r="T29" t="n">
-        <v>69.59661227661228</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+        <v>79.08295471298568</v>
+      </c>
+      <c r="U29" t="n">
+        <v>24.67607030650509</v>
+      </c>
+      <c r="V29" t="n">
+        <v>183.4741928763668</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>64.1912877782443</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1015003.267666311</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>69.38707508272725</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>25.81298701298701</v>
+        <v>25.51038961038961</v>
       </c>
       <c r="D30" t="n">
-        <v>181.7987012987013</v>
+        <v>182.8454545454545</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>67.54415584415585</v>
+        <v>67.27142857142857</v>
       </c>
       <c r="G30" t="n">
-        <v>1533863.636363636</v>
+        <v>1397662.337662338</v>
       </c>
       <c r="H30" t="n">
-        <v>71.94415584415584</v>
+        <v>71.24545454545455</v>
       </c>
       <c r="I30" t="n">
-        <v>25.89047619047619</v>
+        <v>24.83636363636364</v>
       </c>
       <c r="J30" t="n">
-        <v>183.2238095238095</v>
+        <v>184.9181818181818</v>
       </c>
       <c r="K30" t="n">
-        <v>1.104761904761905</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>68.51904761904761</v>
+        <v>69.95454545454545</v>
       </c>
       <c r="M30" t="n">
-        <v>1678769.841269841</v>
+        <v>2783863.636363636</v>
       </c>
       <c r="N30" t="n">
-        <v>72.43333333333334</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>26.58976060976061</v>
+        <v>23.49163402992381</v>
       </c>
       <c r="P30" t="n">
-        <v>181.9976401376401</v>
+        <v>182.0213416251058</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.114663114663115</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>66.7907018907019</v>
+        <v>63.81737753572194</v>
       </c>
       <c r="S30" t="n">
-        <v>1349302.142302142</v>
+        <v>1122069.114677355</v>
       </c>
       <c r="T30" t="n">
-        <v>70.48701964701965</v>
+        <v>70.9140947383451</v>
       </c>
       <c r="U30" t="n">
-        <v>23.94467120181406</v>
+        <v>25.77338461538462</v>
       </c>
       <c r="V30" t="n">
-        <v>184.4581349206349</v>
+        <v>181.8730769230769</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.035076923076923</v>
       </c>
       <c r="X30" t="n">
-        <v>64.31975623582767</v>
+        <v>67.49861538461539</v>
       </c>
       <c r="Y30" t="n">
-        <v>1139713.860544218</v>
+        <v>1620358.461538462</v>
       </c>
       <c r="Z30" t="n">
-        <v>70.93358843537415</v>
+        <v>72.28969230769231</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>25.72537878787879</v>
+        <v>24.73181818181818</v>
       </c>
       <c r="D31" t="n">
-        <v>185.1551767676768</v>
+        <v>185.019696969697</v>
       </c>
       <c r="E31" t="n">
-        <v>1.326515151515151</v>
+        <v>1.063636363636364</v>
       </c>
       <c r="F31" t="n">
-        <v>71.22108585858585</v>
+        <v>69.83636363636363</v>
       </c>
       <c r="G31" t="n">
-        <v>3141243.686868687</v>
+        <v>2975833.333333333</v>
       </c>
       <c r="H31" t="n">
-        <v>76.6205808080808</v>
+        <v>75.5439393939394</v>
       </c>
       <c r="I31" t="n">
-        <v>25.44285714285714</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="J31" t="n">
-        <v>183.563492063492</v>
+        <v>183.4343434343435</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>66.64603174603175</v>
+        <v>70.31313131313131</v>
       </c>
       <c r="M31" t="n">
-        <v>1211587.301587302</v>
+        <v>2490404.04040404</v>
       </c>
       <c r="N31" t="n">
-        <v>70.44444444444444</v>
+        <v>74.50505050505051</v>
       </c>
       <c r="O31" t="n">
-        <v>24.82486140880104</v>
+        <v>25.23322081836575</v>
       </c>
       <c r="P31" t="n">
-        <v>183.8016459937551</v>
+        <v>184.4230924067881</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.210687961419386</v>
+        <v>1.117838783599653</v>
       </c>
       <c r="R31" t="n">
-        <v>69.95947136884443</v>
+        <v>68.38258443783806</v>
       </c>
       <c r="S31" t="n">
-        <v>3162273.132161097</v>
+        <v>2260378.02190429</v>
       </c>
       <c r="T31" t="n">
-        <v>75.82969602550872</v>
+        <v>73.27418297617572</v>
       </c>
       <c r="U31" t="n">
-        <v>24.89280560709132</v>
+        <v>25.71167953535103</v>
       </c>
       <c r="V31" t="n">
-        <v>183.361605854463</v>
+        <v>181.7177680746521</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>64.58005875077303</v>
+        <v>68.69204102839369</v>
       </c>
       <c r="Y31" t="n">
-        <v>1031453.133374562</v>
+        <v>2048259.5018374</v>
       </c>
       <c r="Z31" t="n">
-        <v>69.26774582560297</v>
+        <v>73.30221795559959</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>28.87142857142857</v>
+        <v>23.68961038961039</v>
       </c>
       <c r="D32" t="n">
-        <v>183.4142857142857</v>
+        <v>184.1142857142857</v>
       </c>
       <c r="E32" t="n">
-        <v>1.157142857142857</v>
+        <v>1.148051948051948</v>
       </c>
       <c r="F32" t="n">
-        <v>67.78571428571429</v>
+        <v>68.29870129870129</v>
       </c>
       <c r="G32" t="n">
-        <v>1045500</v>
+        <v>2328506.493506494</v>
       </c>
       <c r="H32" t="n">
-        <v>69.98571428571428</v>
+        <v>75.29740259740258</v>
       </c>
       <c r="I32" t="n">
-        <v>26.41558441558441</v>
+        <v>25.95555555555556</v>
       </c>
       <c r="J32" t="n">
-        <v>184.3896103896104</v>
+        <v>181.0648148148148</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>1.051851851851852</v>
       </c>
       <c r="L32" t="n">
-        <v>67.1948051948052</v>
+        <v>71.02962962962964</v>
       </c>
       <c r="M32" t="n">
-        <v>1326623.376623377</v>
+        <v>3338935.185185185</v>
       </c>
       <c r="N32" t="n">
-        <v>70.55844155844156</v>
+        <v>73.29814814814814</v>
       </c>
       <c r="O32" t="n">
-        <v>25.22084760994699</v>
+        <v>24.62027326332751</v>
       </c>
       <c r="P32" t="n">
-        <v>185.1004652191609</v>
+        <v>183.9102464080158</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.035889359088117</v>
+        <v>1.162651656332309</v>
       </c>
       <c r="R32" t="n">
-        <v>65.26384562297606</v>
+        <v>68.53894288748768</v>
       </c>
       <c r="S32" t="n">
-        <v>999487.5229727715</v>
+        <v>2391602.765864311</v>
       </c>
       <c r="T32" t="n">
-        <v>68.73200984890426</v>
+        <v>75.09786588460416</v>
       </c>
       <c r="U32" t="n">
-        <v>24.41948883414722</v>
+        <v>26.42016144349478</v>
       </c>
       <c r="V32" t="n">
-        <v>183.4407367511715</v>
+        <v>183.3278822412156</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.264577397910731</v>
       </c>
       <c r="X32" t="n">
-        <v>64.15824666706655</v>
+        <v>70.08405508072174</v>
       </c>
       <c r="Y32" t="n">
-        <v>1029831.372285409</v>
+        <v>2746374.45394112</v>
       </c>
       <c r="Z32" t="n">
-        <v>69.70320721376621</v>
+        <v>72.65479582146249</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>26.86</v>
+        <v>25.77922077922078</v>
       </c>
       <c r="D33" t="n">
-        <v>181.6572727272727</v>
+        <v>186.4</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>1.225974025974026</v>
       </c>
       <c r="F33" t="n">
-        <v>67.4309090909091</v>
+        <v>76.05454545454545</v>
       </c>
       <c r="G33" t="n">
-        <v>1277590.909090909</v>
+        <v>13493376.62337662</v>
       </c>
       <c r="H33" t="n">
-        <v>70.28545454545454</v>
+        <v>79.3987012987013</v>
       </c>
       <c r="I33" t="n">
-        <v>25.74204545454545</v>
+        <v>26.1969696969697</v>
       </c>
       <c r="J33" t="n">
-        <v>186.9363636363636</v>
+        <v>182.7878787878788</v>
       </c>
       <c r="K33" t="n">
-        <v>1.214772727272727</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>73.25</v>
+        <v>68.07575757575758</v>
       </c>
       <c r="M33" t="n">
-        <v>5306079.545454546</v>
+        <v>1400757.575757576</v>
       </c>
       <c r="N33" t="n">
-        <v>77.25454545454545</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="O33" t="n">
-        <v>25.63088518888519</v>
+        <v>25.10075684978936</v>
       </c>
       <c r="P33" t="n">
-        <v>179.4868835053835</v>
+        <v>184.6815733071538</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>1.22042159766618</v>
       </c>
       <c r="R33" t="n">
-        <v>66.03421056721056</v>
+        <v>72.04932010284178</v>
       </c>
       <c r="S33" t="n">
-        <v>1188850.593850594</v>
+        <v>5788223.678626155</v>
       </c>
       <c r="T33" t="n">
-        <v>70.69366881266882</v>
+        <v>75.75028893535087</v>
       </c>
       <c r="U33" t="n">
-        <v>24.18748135890846</v>
+        <v>24.05353276353277</v>
       </c>
       <c r="V33" t="n">
-        <v>185.0565917079616</v>
+        <v>182.0722317188984</v>
       </c>
       <c r="W33" t="n">
-        <v>1.13142152900961</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>70.81202993245441</v>
+        <v>66.81969610636277</v>
       </c>
       <c r="Y33" t="n">
-        <v>3964935.51087704</v>
+        <v>1479275.166191833</v>
       </c>
       <c r="Z33" t="n">
-        <v>77.16509865602913</v>
+        <v>72.92555555555556</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>24.1038961038961</v>
+      </c>
+      <c r="D34" t="n">
+        <v>184.6883116883117</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>70.97402597402598</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4262337.662337663</v>
+      </c>
+      <c r="H34" t="n">
+        <v>76.32467532467533</v>
+      </c>
+      <c r="I34" t="n">
+        <v>25.76666666666667</v>
+      </c>
+      <c r="J34" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>67.48333333333333</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1530416.666666667</v>
+      </c>
+      <c r="N34" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="O34" t="n">
+        <v>23.11903957556132</v>
+      </c>
+      <c r="P34" t="n">
+        <v>184.7916149872672</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>67.45391022021457</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2546674.661892053</v>
+      </c>
+      <c r="T34" t="n">
+        <v>74.78012225294833</v>
+      </c>
+      <c r="U34" t="n">
+        <v>26.51497712164379</v>
+      </c>
+      <c r="V34" t="n">
+        <v>181.952375032375</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.120953120953121</v>
+      </c>
+      <c r="X34" t="n">
+        <v>66.77504964171631</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1358160.191660192</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>70.61306138306138</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>26.32467532467533</v>
+        <v>23.94805194805195</v>
       </c>
       <c r="D35" t="n">
-        <v>182.3246753246753</v>
+        <v>184.7662337662337</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>68.09090909090909</v>
+        <v>71.97402597402598</v>
       </c>
       <c r="G35" t="n">
-        <v>1386038.961038961</v>
+        <v>5398051.948051949</v>
       </c>
       <c r="H35" t="n">
-        <v>71.15584415584416</v>
-      </c>
-      <c r="I35" t="n">
-        <v>26.78567493112947</v>
-      </c>
-      <c r="J35" t="n">
-        <v>185.6598714416896</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1.085123966942149</v>
-      </c>
-      <c r="L35" t="n">
-        <v>69.30918273645547</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1959320.477502296</v>
-      </c>
-      <c r="N35" t="n">
-        <v>72.65656565656565</v>
-      </c>
+        <v>77.83116883116884</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>24.05117623117623</v>
+        <v>23.30908309082222</v>
       </c>
       <c r="P35" t="n">
-        <v>182.15185999186</v>
+        <v>183.3037849107414</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>1.073890457368718</v>
       </c>
       <c r="R35" t="n">
-        <v>66.85603581603581</v>
+        <v>67.99492941840768</v>
       </c>
       <c r="S35" t="n">
-        <v>1492421.041921042</v>
+        <v>2511074.729618208</v>
       </c>
       <c r="T35" t="n">
-        <v>72.97322751322751</v>
+        <v>74.56220127698388</v>
       </c>
       <c r="U35" t="n">
-        <v>27.35946734424995</v>
+        <v>29</v>
       </c>
       <c r="V35" t="n">
-        <v>185.3063988843831</v>
+        <v>181.6</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12314477354003</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>70.03460688191913</v>
+        <v>70.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>2126572.170747566</v>
+        <v>1820000</v>
       </c>
       <c r="Z35" t="n">
-        <v>73.13433396642883</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>24.10227272727273</v>
+        <v>25.81471861471862</v>
       </c>
       <c r="D36" t="n">
-        <v>184.7272727272727</v>
+        <v>185.3487734487734</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>1.33030303030303</v>
       </c>
       <c r="F36" t="n">
-        <v>71.06818181818181</v>
+        <v>71.23838383838384</v>
       </c>
       <c r="G36" t="n">
-        <v>4321590.909090909</v>
+        <v>3140707.070707071</v>
       </c>
       <c r="H36" t="n">
-        <v>76.45454545454545</v>
+        <v>76.56637806637806</v>
       </c>
       <c r="I36" t="n">
-        <v>23.66022727272727</v>
+        <v>25.73888888888889</v>
       </c>
       <c r="J36" t="n">
-        <v>184.1909090909091</v>
+        <v>183.3111111111111</v>
       </c>
       <c r="K36" t="n">
-        <v>1.152272727272727</v>
+        <v>1.105555555555555</v>
       </c>
       <c r="L36" t="n">
-        <v>68.21590909090909</v>
+        <v>68.40555555555555</v>
       </c>
       <c r="M36" t="n">
-        <v>2279204.545454545</v>
+        <v>1680231.481481481</v>
       </c>
       <c r="N36" t="n">
-        <v>75.2715909090909</v>
+        <v>72.52222222222223</v>
       </c>
       <c r="O36" t="n">
-        <v>23.19467686999546</v>
+        <v>24.74489655511328</v>
       </c>
       <c r="P36" t="n">
-        <v>184.6840424242036</v>
+        <v>183.581002014841</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>1.191335692171605</v>
       </c>
       <c r="R36" t="n">
-        <v>67.5394128219981</v>
+        <v>69.99214310285518</v>
       </c>
       <c r="S36" t="n">
-        <v>2556680.846396925</v>
+        <v>3188339.623568725</v>
       </c>
       <c r="T36" t="n">
-        <v>74.71708972995049</v>
+        <v>75.9262460071748</v>
       </c>
       <c r="U36" t="n">
-        <v>24.65211410541157</v>
+        <v>24.0771164021164</v>
       </c>
       <c r="V36" t="n">
-        <v>183.7964656070138</v>
+        <v>184.4344907407408</v>
       </c>
       <c r="W36" t="n">
-        <v>1.163153532624104</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>68.57053335988506</v>
+        <v>64.64804894179895</v>
       </c>
       <c r="Y36" t="n">
-        <v>2403303.461797939</v>
+        <v>1181832.837301587</v>
       </c>
       <c r="Z36" t="n">
-        <v>75.02834098236198</v>
+        <v>71.0891865079365</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>26.08051948051948</v>
+        <v>25.16883116883117</v>
       </c>
       <c r="D37" t="n">
-        <v>184.2207792207792</v>
+        <v>184.1688311688311</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>1.194805194805195</v>
       </c>
       <c r="F37" t="n">
-        <v>65.64805194805194</v>
+        <v>72.1038961038961</v>
       </c>
       <c r="G37" t="n">
-        <v>1164110.389610389</v>
+        <v>3715584.415584415</v>
       </c>
       <c r="H37" t="n">
-        <v>68.99999999999999</v>
+        <v>76</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -3185,29 +3411,2099 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>26.15596963423051</v>
+        <v>26.03209458849853</v>
       </c>
       <c r="P37" t="n">
-        <v>182.3768115942029</v>
+        <v>183.2602555080387</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>1.165195149677908</v>
       </c>
       <c r="R37" t="n">
-        <v>64.2716816195077</v>
+        <v>70.11228188888286</v>
       </c>
       <c r="S37" t="n">
-        <v>1000485.480702872</v>
+        <v>2659948.519460835</v>
       </c>
       <c r="T37" t="n">
-        <v>67.93227867140909</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+        <v>74.10430628484816</v>
+      </c>
+      <c r="U37" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>775000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>25.51038961038961</v>
+      </c>
+      <c r="D38" t="n">
+        <v>182.8454545454545</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>67.27142857142857</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1397662.337662338</v>
+      </c>
+      <c r="H38" t="n">
+        <v>71.24545454545455</v>
+      </c>
+      <c r="I38" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="J38" t="n">
+        <v>183.4343434343435</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>70.31313131313131</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2490404.04040404</v>
+      </c>
+      <c r="N38" t="n">
+        <v>74.50505050505051</v>
+      </c>
+      <c r="O38" t="n">
+        <v>23.49163402992381</v>
+      </c>
+      <c r="P38" t="n">
+        <v>182.0213416251058</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>63.81737753572194</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1122069.114677355</v>
+      </c>
+      <c r="T38" t="n">
+        <v>70.9140947383451</v>
+      </c>
+      <c r="U38" t="n">
+        <v>25.71167953535103</v>
+      </c>
+      <c r="V38" t="n">
+        <v>181.7177680746521</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>68.69204102839369</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2048259.5018374</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>73.30221795559959</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>27.79040404040404</v>
+      </c>
+      <c r="D39" t="n">
+        <v>180.6546717171717</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>67.53737373737374</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>69.83118686868687</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>25.10873973852235</v>
+      </c>
+      <c r="P39" t="n">
+        <v>178.3820519154758</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>64.90591783216783</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1252055.211817168</v>
+      </c>
+      <c r="T39" t="n">
+        <v>69.53118881118883</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>25.76666666666667</v>
+      </c>
+      <c r="D40" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>67.48333333333333</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1530416.666666667</v>
+      </c>
+      <c r="H40" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="I40" t="n">
+        <v>25.73888888888889</v>
+      </c>
+      <c r="J40" t="n">
+        <v>183.3111111111111</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.105555555555555</v>
+      </c>
+      <c r="L40" t="n">
+        <v>68.40555555555555</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1680231.481481481</v>
+      </c>
+      <c r="N40" t="n">
+        <v>72.52222222222223</v>
+      </c>
+      <c r="O40" t="n">
+        <v>26.51497712164379</v>
+      </c>
+      <c r="P40" t="n">
+        <v>181.952375032375</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.120953120953121</v>
+      </c>
+      <c r="R40" t="n">
+        <v>66.77504964171631</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1358160.191660192</v>
+      </c>
+      <c r="T40" t="n">
+        <v>70.61306138306138</v>
+      </c>
+      <c r="U40" t="n">
+        <v>24.0771164021164</v>
+      </c>
+      <c r="V40" t="n">
+        <v>184.4344907407408</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>64.64804894179895</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1181832.837301587</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>71.0891865079365</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>25.81471861471862</v>
+      </c>
+      <c r="D41" t="n">
+        <v>185.3487734487734</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.33030303030303</v>
+      </c>
+      <c r="F41" t="n">
+        <v>71.23838383838384</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3140707.070707071</v>
+      </c>
+      <c r="H41" t="n">
+        <v>76.56637806637806</v>
+      </c>
+      <c r="I41" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>183.6740740740741</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>66.58703703703704</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1224768.518518518</v>
+      </c>
+      <c r="N41" t="n">
+        <v>70.55185185185185</v>
+      </c>
+      <c r="O41" t="n">
+        <v>24.74489655511328</v>
+      </c>
+      <c r="P41" t="n">
+        <v>183.581002014841</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.191335692171605</v>
+      </c>
+      <c r="R41" t="n">
+        <v>69.99214310285518</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3188339.623568725</v>
+      </c>
+      <c r="T41" t="n">
+        <v>75.9262460071748</v>
+      </c>
+      <c r="U41" t="n">
+        <v>24.87493987493987</v>
+      </c>
+      <c r="V41" t="n">
+        <v>183.4552068302069</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>64.39673520923522</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1007061.988936989</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>69.19237012987013</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="D42" t="n">
+        <v>183.4833333333333</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F42" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1041250</v>
+      </c>
+      <c r="H42" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="I42" t="n">
+        <v>26.24242424242424</v>
+      </c>
+      <c r="J42" t="n">
+        <v>184.4090909090909</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>67.10606060606061</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1326515.151515152</v>
+      </c>
+      <c r="N42" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="O42" t="n">
+        <v>25.29765554493816</v>
+      </c>
+      <c r="P42" t="n">
+        <v>185.003876089021</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.028537585602803</v>
+      </c>
+      <c r="R42" t="n">
+        <v>65.28115322680542</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1006235.443468233</v>
+      </c>
+      <c r="T42" t="n">
+        <v>68.66067815705496</v>
+      </c>
+      <c r="U42" t="n">
+        <v>24.67607030650509</v>
+      </c>
+      <c r="V42" t="n">
+        <v>183.4741928763668</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>64.1912877782443</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1015003.267666311</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>69.38707508272725</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>26.76363636363637</v>
+      </c>
+      <c r="D43" t="n">
+        <v>181.659595959596</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>67.35757575757576</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1273585.858585858</v>
+      </c>
+      <c r="H43" t="n">
+        <v>70.34747474747475</v>
+      </c>
+      <c r="I43" t="n">
+        <v>25.61428571428572</v>
+      </c>
+      <c r="J43" t="n">
+        <v>187.1350649350649</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.206493506493507</v>
+      </c>
+      <c r="L43" t="n">
+        <v>73.09090909090909</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5204350.64935065</v>
+      </c>
+      <c r="N43" t="n">
+        <v>77.32987012987012</v>
+      </c>
+      <c r="O43" t="n">
+        <v>25.82098354320577</v>
+      </c>
+      <c r="P43" t="n">
+        <v>179.4209816726483</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>66.02912285245618</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1158056.215389549</v>
+      </c>
+      <c r="T43" t="n">
+        <v>70.37074312518757</v>
+      </c>
+      <c r="U43" t="n">
+        <v>24.13351906856619</v>
+      </c>
+      <c r="V43" t="n">
+        <v>184.803806672453</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.131562492781169</v>
+      </c>
+      <c r="X43" t="n">
+        <v>70.74169880479262</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>3987255.490691773</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>77.17005063794633</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V44" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>775000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>26.1969696969697</v>
+      </c>
+      <c r="D45" t="n">
+        <v>182.7878787878788</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>68.07575757575758</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1400757.575757576</v>
+      </c>
+      <c r="H45" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="I45" t="n">
+        <v>26.95424242424243</v>
+      </c>
+      <c r="J45" t="n">
+        <v>185.3758585858586</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.083636363636364</v>
+      </c>
+      <c r="L45" t="n">
+        <v>69.25010101010102</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1925252.525252525</v>
+      </c>
+      <c r="N45" t="n">
+        <v>72.48222222222223</v>
+      </c>
+      <c r="O45" t="n">
+        <v>24.05353276353277</v>
+      </c>
+      <c r="P45" t="n">
+        <v>182.0722317188984</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>66.81969610636277</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1479275.166191833</v>
+      </c>
+      <c r="T45" t="n">
+        <v>72.92555555555556</v>
+      </c>
+      <c r="U45" t="n">
+        <v>27.38291407867495</v>
+      </c>
+      <c r="V45" t="n">
+        <v>185.4870387728214</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.1271259175607</v>
+      </c>
+      <c r="X45" t="n">
+        <v>69.98390090344438</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2094229.387822323</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>73.07276736307172</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>24.1038961038961</v>
+      </c>
+      <c r="D46" t="n">
+        <v>184.6883116883117</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>70.97402597402598</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4262337.662337663</v>
+      </c>
+      <c r="H46" t="n">
+        <v>76.32467532467533</v>
+      </c>
+      <c r="I46" t="n">
+        <v>23.68961038961039</v>
+      </c>
+      <c r="J46" t="n">
+        <v>184.1142857142857</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1.148051948051948</v>
+      </c>
+      <c r="L46" t="n">
+        <v>68.29870129870129</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2328506.493506494</v>
+      </c>
+      <c r="N46" t="n">
+        <v>75.29740259740258</v>
+      </c>
+      <c r="O46" t="n">
+        <v>23.11903957556132</v>
+      </c>
+      <c r="P46" t="n">
+        <v>184.7916149872672</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>67.45391022021457</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2546674.661892053</v>
+      </c>
+      <c r="T46" t="n">
+        <v>74.78012225294833</v>
+      </c>
+      <c r="U46" t="n">
+        <v>24.62027326332751</v>
+      </c>
+      <c r="V46" t="n">
+        <v>183.9102464080158</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.162651656332309</v>
+      </c>
+      <c r="X46" t="n">
+        <v>68.53894288748768</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2391602.765864311</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>75.09786588460416</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>26.01060606060606</v>
+      </c>
+      <c r="D47" t="n">
+        <v>184.1075757575757</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>65.63939393939394</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1166545.454545454</v>
+      </c>
+      <c r="H47" t="n">
+        <v>68.98333333333333</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>26.18196457326892</v>
+      </c>
+      <c r="P47" t="n">
+        <v>182.4396135265701</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>64.31696188942566</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1003643.317230274</v>
+      </c>
+      <c r="T47" t="n">
+        <v>68.0107353730542</v>
+      </c>
+      <c r="U47" t="n">
+        <v>29</v>
+      </c>
+      <c r="V47" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>26.24242424242424</v>
+      </c>
+      <c r="D48" t="n">
+        <v>184.4090909090909</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>67.10606060606061</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1326515.151515152</v>
+      </c>
+      <c r="H48" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="I48" t="n">
+        <v>27.79040404040404</v>
+      </c>
+      <c r="J48" t="n">
+        <v>180.6546717171717</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>67.53737373737374</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="N48" t="n">
+        <v>69.83118686868687</v>
+      </c>
+      <c r="O48" t="n">
+        <v>24.67607030650509</v>
+      </c>
+      <c r="P48" t="n">
+        <v>183.4741928763668</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>64.1912877782443</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1015003.267666311</v>
+      </c>
+      <c r="T48" t="n">
+        <v>69.38707508272725</v>
+      </c>
+      <c r="U48" t="n">
+        <v>25.10873973852235</v>
+      </c>
+      <c r="V48" t="n">
+        <v>178.3820519154758</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>64.90591783216783</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1252055.211817168</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>69.53118881118883</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="D49" t="n">
+        <v>183.4833333333333</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F49" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1041250</v>
+      </c>
+      <c r="H49" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="I49" t="n">
+        <v>25.81471861471862</v>
+      </c>
+      <c r="J49" t="n">
+        <v>185.3487734487734</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.33030303030303</v>
+      </c>
+      <c r="L49" t="n">
+        <v>71.23838383838384</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3140707.070707071</v>
+      </c>
+      <c r="N49" t="n">
+        <v>76.56637806637806</v>
+      </c>
+      <c r="O49" t="n">
+        <v>25.29765554493816</v>
+      </c>
+      <c r="P49" t="n">
+        <v>185.003876089021</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.028537585602803</v>
+      </c>
+      <c r="R49" t="n">
+        <v>65.28115322680542</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1006235.443468233</v>
+      </c>
+      <c r="T49" t="n">
+        <v>68.66067815705496</v>
+      </c>
+      <c r="U49" t="n">
+        <v>24.74489655511328</v>
+      </c>
+      <c r="V49" t="n">
+        <v>183.581002014841</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.191335692171605</v>
+      </c>
+      <c r="X49" t="n">
+        <v>69.99214310285518</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>3188339.623568725</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>75.9262460071748</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>25.51038961038961</v>
+      </c>
+      <c r="D50" t="n">
+        <v>182.8454545454545</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>67.27142857142857</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1397662.337662338</v>
+      </c>
+      <c r="H50" t="n">
+        <v>71.24545454545455</v>
+      </c>
+      <c r="I50" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>183.6740740740741</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>66.58703703703704</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1224768.518518518</v>
+      </c>
+      <c r="N50" t="n">
+        <v>70.55185185185185</v>
+      </c>
+      <c r="O50" t="n">
+        <v>23.49163402992381</v>
+      </c>
+      <c r="P50" t="n">
+        <v>182.0213416251058</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>63.81737753572194</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1122069.114677355</v>
+      </c>
+      <c r="T50" t="n">
+        <v>70.9140947383451</v>
+      </c>
+      <c r="U50" t="n">
+        <v>24.87493987493987</v>
+      </c>
+      <c r="V50" t="n">
+        <v>183.4552068302069</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>64.39673520923522</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1007061.988936989</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>69.19237012987013</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>26.95424242424243</v>
+      </c>
+      <c r="D51" t="n">
+        <v>185.3758585858586</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.083636363636364</v>
+      </c>
+      <c r="F51" t="n">
+        <v>69.25010101010102</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1925252.525252525</v>
+      </c>
+      <c r="H51" t="n">
+        <v>72.48222222222223</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>27.38291407867495</v>
+      </c>
+      <c r="P51" t="n">
+        <v>185.4870387728214</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.1271259175607</v>
+      </c>
+      <c r="R51" t="n">
+        <v>69.98390090344438</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2094229.387822323</v>
+      </c>
+      <c r="T51" t="n">
+        <v>73.07276736307172</v>
+      </c>
+      <c r="U51" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>775000</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>25.76666666666667</v>
+      </c>
+      <c r="D52" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>67.48333333333333</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1530416.666666667</v>
+      </c>
+      <c r="H52" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="I52" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="J52" t="n">
+        <v>183.4343434343435</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>70.31313131313131</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2490404.04040404</v>
+      </c>
+      <c r="N52" t="n">
+        <v>74.50505050505051</v>
+      </c>
+      <c r="O52" t="n">
+        <v>26.51497712164379</v>
+      </c>
+      <c r="P52" t="n">
+        <v>181.952375032375</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.120953120953121</v>
+      </c>
+      <c r="R52" t="n">
+        <v>66.77504964171631</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1358160.191660192</v>
+      </c>
+      <c r="T52" t="n">
+        <v>70.61306138306138</v>
+      </c>
+      <c r="U52" t="n">
+        <v>25.71167953535103</v>
+      </c>
+      <c r="V52" t="n">
+        <v>181.7177680746521</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="X52" t="n">
+        <v>68.69204102839369</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2048259.5018374</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>73.30221795559959</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>23.68961038961039</v>
+      </c>
+      <c r="D53" t="n">
+        <v>184.1142857142857</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.148051948051948</v>
+      </c>
+      <c r="F53" t="n">
+        <v>68.29870129870129</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2328506.493506494</v>
+      </c>
+      <c r="H53" t="n">
+        <v>75.29740259740258</v>
+      </c>
+      <c r="I53" t="n">
+        <v>26.01060606060606</v>
+      </c>
+      <c r="J53" t="n">
+        <v>184.1075757575757</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>65.63939393939394</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1166545.454545454</v>
+      </c>
+      <c r="N53" t="n">
+        <v>68.98333333333333</v>
+      </c>
+      <c r="O53" t="n">
+        <v>24.62027326332751</v>
+      </c>
+      <c r="P53" t="n">
+        <v>183.9102464080158</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.162651656332309</v>
+      </c>
+      <c r="R53" t="n">
+        <v>68.53894288748768</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2391602.765864311</v>
+      </c>
+      <c r="T53" t="n">
+        <v>75.09786588460416</v>
+      </c>
+      <c r="U53" t="n">
+        <v>26.18196457326892</v>
+      </c>
+      <c r="V53" t="n">
+        <v>182.4396135265701</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" t="n">
+        <v>64.31696188942566</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1003643.317230274</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>68.0107353730542</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>25.61428571428572</v>
+      </c>
+      <c r="D54" t="n">
+        <v>187.1350649350649</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.206493506493507</v>
+      </c>
+      <c r="F54" t="n">
+        <v>73.09090909090909</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5204350.64935065</v>
+      </c>
+      <c r="H54" t="n">
+        <v>77.32987012987012</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>24.13351906856619</v>
+      </c>
+      <c r="P54" t="n">
+        <v>184.803806672453</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.131562492781169</v>
+      </c>
+      <c r="R54" t="n">
+        <v>70.74169880479262</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3987255.490691773</v>
+      </c>
+      <c r="T54" t="n">
+        <v>77.17005063794633</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>25.73888888888889</v>
+      </c>
+      <c r="D55" t="n">
+        <v>183.3111111111111</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.105555555555555</v>
+      </c>
+      <c r="F55" t="n">
+        <v>68.40555555555555</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1680231.481481481</v>
+      </c>
+      <c r="H55" t="n">
+        <v>72.52222222222223</v>
+      </c>
+      <c r="I55" t="n">
+        <v>24.1038961038961</v>
+      </c>
+      <c r="J55" t="n">
+        <v>184.6883116883117</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>70.97402597402598</v>
+      </c>
+      <c r="M55" t="n">
+        <v>4262337.662337663</v>
+      </c>
+      <c r="N55" t="n">
+        <v>76.32467532467533</v>
+      </c>
+      <c r="O55" t="n">
+        <v>24.0771164021164</v>
+      </c>
+      <c r="P55" t="n">
+        <v>184.4344907407408</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>64.64804894179895</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1181832.837301587</v>
+      </c>
+      <c r="T55" t="n">
+        <v>71.0891865079365</v>
+      </c>
+      <c r="U55" t="n">
+        <v>23.11903957556132</v>
+      </c>
+      <c r="V55" t="n">
+        <v>184.7916149872672</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>67.45391022021457</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2546674.661892053</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>74.78012225294833</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>26.76363636363637</v>
+      </c>
+      <c r="D56" t="n">
+        <v>181.659595959596</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>67.35757575757576</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1273585.858585858</v>
+      </c>
+      <c r="H56" t="n">
+        <v>70.34747474747475</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>25.82098354320577</v>
+      </c>
+      <c r="P56" t="n">
+        <v>179.4209816726483</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>66.02912285245618</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1158056.215389549</v>
+      </c>
+      <c r="T56" t="n">
+        <v>70.37074312518757</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>26.1969696969697</v>
+      </c>
+      <c r="J57" t="n">
+        <v>182.7878787878788</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>68.07575757575758</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1400757.575757576</v>
+      </c>
+      <c r="N57" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="O57" t="n">
+        <v>29</v>
+      </c>
+      <c r="P57" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="T57" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>24.05353276353277</v>
+      </c>
+      <c r="V57" t="n">
+        <v>182.0722317188984</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" t="n">
+        <v>66.81969610636277</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1479275.166191833</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>72.92555555555556</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>27.79040404040404</v>
+      </c>
+      <c r="D58" t="n">
+        <v>180.6546717171717</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>67.53737373737374</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="H58" t="n">
+        <v>69.83118686868687</v>
+      </c>
+      <c r="I58" t="n">
+        <v>25.61428571428572</v>
+      </c>
+      <c r="J58" t="n">
+        <v>187.1350649350649</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.206493506493507</v>
+      </c>
+      <c r="L58" t="n">
+        <v>73.09090909090909</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5204350.64935065</v>
+      </c>
+      <c r="N58" t="n">
+        <v>77.32987012987012</v>
+      </c>
+      <c r="O58" t="n">
+        <v>25.10873973852235</v>
+      </c>
+      <c r="P58" t="n">
+        <v>178.3820519154758</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>64.90591783216783</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1252055.211817168</v>
+      </c>
+      <c r="T58" t="n">
+        <v>69.53118881118883</v>
+      </c>
+      <c r="U58" t="n">
+        <v>24.13351906856619</v>
+      </c>
+      <c r="V58" t="n">
+        <v>184.803806672453</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.131562492781169</v>
+      </c>
+      <c r="X58" t="n">
+        <v>70.74169880479262</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>3987255.490691773</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>77.17005063794633</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="J59" t="n">
+        <v>183.4833333333333</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L59" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1041250</v>
+      </c>
+      <c r="N59" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="O59" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="P59" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="S59" t="n">
+        <v>775000</v>
+      </c>
+      <c r="T59" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="U59" t="n">
+        <v>25.29765554493816</v>
+      </c>
+      <c r="V59" t="n">
+        <v>185.003876089021</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.028537585602803</v>
+      </c>
+      <c r="X59" t="n">
+        <v>65.28115322680542</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1006235.443468233</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>68.66067815705496</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>183.6740740740741</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>66.58703703703704</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1224768.518518518</v>
+      </c>
+      <c r="H60" t="n">
+        <v>70.55185185185185</v>
+      </c>
+      <c r="I60" t="n">
+        <v>25.76666666666667</v>
+      </c>
+      <c r="J60" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>67.48333333333333</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1530416.666666667</v>
+      </c>
+      <c r="N60" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="O60" t="n">
+        <v>24.87493987493987</v>
+      </c>
+      <c r="P60" t="n">
+        <v>183.4552068302069</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>64.39673520923522</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1007061.988936989</v>
+      </c>
+      <c r="T60" t="n">
+        <v>69.19237012987013</v>
+      </c>
+      <c r="U60" t="n">
+        <v>26.51497712164379</v>
+      </c>
+      <c r="V60" t="n">
+        <v>181.952375032375</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.120953120953121</v>
+      </c>
+      <c r="X60" t="n">
+        <v>66.77504964171631</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1358160.191660192</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>70.61306138306138</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>26.95424242424243</v>
+      </c>
+      <c r="D61" t="n">
+        <v>185.3758585858586</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.083636363636364</v>
+      </c>
+      <c r="F61" t="n">
+        <v>69.25010101010102</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1925252.525252525</v>
+      </c>
+      <c r="H61" t="n">
+        <v>72.48222222222223</v>
+      </c>
+      <c r="I61" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="J61" t="n">
+        <v>183.4343434343435</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>70.31313131313131</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2490404.04040404</v>
+      </c>
+      <c r="N61" t="n">
+        <v>74.50505050505051</v>
+      </c>
+      <c r="O61" t="n">
+        <v>27.38291407867495</v>
+      </c>
+      <c r="P61" t="n">
+        <v>185.4870387728214</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.1271259175607</v>
+      </c>
+      <c r="R61" t="n">
+        <v>69.98390090344438</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2094229.387822323</v>
+      </c>
+      <c r="T61" t="n">
+        <v>73.07276736307172</v>
+      </c>
+      <c r="U61" t="n">
+        <v>25.71167953535103</v>
+      </c>
+      <c r="V61" t="n">
+        <v>181.7177680746521</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1</v>
+      </c>
+      <c r="X61" t="n">
+        <v>68.69204102839369</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2048259.5018374</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>73.30221795559959</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>24.1038961038961</v>
+      </c>
+      <c r="D62" t="n">
+        <v>184.6883116883117</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>70.97402597402598</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4262337.662337663</v>
+      </c>
+      <c r="H62" t="n">
+        <v>76.32467532467533</v>
+      </c>
+      <c r="I62" t="n">
+        <v>26.24242424242424</v>
+      </c>
+      <c r="J62" t="n">
+        <v>184.4090909090909</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>67.10606060606061</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1326515.151515152</v>
+      </c>
+      <c r="N62" t="n">
+        <v>70.63636363636364</v>
+      </c>
+      <c r="O62" t="n">
+        <v>23.11903957556132</v>
+      </c>
+      <c r="P62" t="n">
+        <v>184.7916149872672</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>67.45391022021457</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2546674.661892053</v>
+      </c>
+      <c r="T62" t="n">
+        <v>74.78012225294833</v>
+      </c>
+      <c r="U62" t="n">
+        <v>24.67607030650509</v>
+      </c>
+      <c r="V62" t="n">
+        <v>183.4741928763668</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>64.1912877782443</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1015003.267666311</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>69.38707508272725</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>26.01060606060606</v>
+      </c>
+      <c r="D63" t="n">
+        <v>184.1075757575757</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>65.63939393939394</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1166545.454545454</v>
+      </c>
+      <c r="H63" t="n">
+        <v>68.98333333333333</v>
+      </c>
+      <c r="I63" t="n">
+        <v>25.51038961038961</v>
+      </c>
+      <c r="J63" t="n">
+        <v>182.8454545454545</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>67.27142857142857</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1397662.337662338</v>
+      </c>
+      <c r="N63" t="n">
+        <v>71.24545454545455</v>
+      </c>
+      <c r="O63" t="n">
+        <v>26.18196457326892</v>
+      </c>
+      <c r="P63" t="n">
+        <v>182.4396135265701</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>64.31696188942566</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1003643.317230274</v>
+      </c>
+      <c r="T63" t="n">
+        <v>68.0107353730542</v>
+      </c>
+      <c r="U63" t="n">
+        <v>23.49163402992381</v>
+      </c>
+      <c r="V63" t="n">
+        <v>182.0213416251058</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="n">
+        <v>63.81737753572194</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1122069.114677355</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>70.9140947383451</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>25.81471861471862</v>
+      </c>
+      <c r="D64" t="n">
+        <v>185.3487734487734</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.33030303030303</v>
+      </c>
+      <c r="F64" t="n">
+        <v>71.23838383838384</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3140707.070707071</v>
+      </c>
+      <c r="H64" t="n">
+        <v>76.56637806637806</v>
+      </c>
+      <c r="I64" t="n">
+        <v>23.68961038961039</v>
+      </c>
+      <c r="J64" t="n">
+        <v>184.1142857142857</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.148051948051948</v>
+      </c>
+      <c r="L64" t="n">
+        <v>68.29870129870129</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2328506.493506494</v>
+      </c>
+      <c r="N64" t="n">
+        <v>75.29740259740258</v>
+      </c>
+      <c r="O64" t="n">
+        <v>24.74489655511328</v>
+      </c>
+      <c r="P64" t="n">
+        <v>183.581002014841</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.191335692171605</v>
+      </c>
+      <c r="R64" t="n">
+        <v>69.99214310285518</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3188339.623568725</v>
+      </c>
+      <c r="T64" t="n">
+        <v>75.9262460071748</v>
+      </c>
+      <c r="U64" t="n">
+        <v>24.62027326332751</v>
+      </c>
+      <c r="V64" t="n">
+        <v>183.9102464080158</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.162651656332309</v>
+      </c>
+      <c r="X64" t="n">
+        <v>68.53894288748768</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2391602.765864311</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>75.09786588460416</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:Z45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.75714285714286</v>
+        <v>26.10330578512397</v>
       </c>
       <c r="D2" t="n">
-        <v>184.5428571428571</v>
+        <v>184.1545454545455</v>
       </c>
       <c r="E2" t="n">
-        <v>1.214285714285714</v>
+        <v>1.179338842975207</v>
       </c>
       <c r="F2" t="n">
-        <v>72.94285714285715</v>
+        <v>73.0900826446281</v>
       </c>
       <c r="G2" t="n">
-        <v>6193214.285714285</v>
+        <v>6146074.38016529</v>
       </c>
       <c r="H2" t="n">
-        <v>77.7</v>
+        <v>77.47685950413224</v>
       </c>
       <c r="I2" t="n">
-        <v>27.84285714285715</v>
+        <v>28.00818181818182</v>
       </c>
       <c r="J2" t="n">
-        <v>183.264935064935</v>
+        <v>182.9309090909091</v>
       </c>
       <c r="K2" t="n">
-        <v>2.344155844155844</v>
+        <v>2.413636363636364</v>
       </c>
       <c r="L2" t="n">
-        <v>82.57532467532469</v>
+        <v>82.88454545454546</v>
       </c>
       <c r="M2" t="n">
-        <v>38316883.11688311</v>
+        <v>40085454.54545455</v>
       </c>
       <c r="N2" t="n">
-        <v>84.55974025974025</v>
+        <v>84.66454545454545</v>
       </c>
       <c r="O2" t="n">
-        <v>26.54104041616646</v>
+        <v>26.53778329513624</v>
       </c>
       <c r="P2" t="n">
-        <v>184.7348299319728</v>
+        <v>184.9579220779221</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.335388155262105</v>
+        <v>1.40827731092437</v>
       </c>
       <c r="R2" t="n">
-        <v>70.03281512605042</v>
+        <v>70.29345811051694</v>
       </c>
       <c r="S2" t="n">
-        <v>3335327.781112445</v>
+        <v>3627757.830404889</v>
       </c>
       <c r="T2" t="n">
-        <v>73.8702581032413</v>
+        <v>74.07986121721416</v>
       </c>
       <c r="U2" t="n">
-        <v>27.46499447642305</v>
+        <v>27.10158309001788</v>
       </c>
       <c r="V2" t="n">
-        <v>182.3110756439328</v>
+        <v>182.5357371404763</v>
       </c>
       <c r="W2" t="n">
-        <v>1.937458573172858</v>
+        <v>1.885667641537206</v>
       </c>
       <c r="X2" t="n">
-        <v>79.01235246235247</v>
+        <v>78.98572182246096</v>
       </c>
       <c r="Y2" t="n">
-        <v>23844299.66858539</v>
+        <v>24084349.68895838</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.30223268794695</v>
+        <v>81.47697790132572</v>
       </c>
     </row>
     <row r="3">
@@ -647,76 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24.73181818181818</v>
+        <v>24.68080808080808</v>
       </c>
       <c r="D3" t="n">
-        <v>185.019696969697</v>
+        <v>184.7545454545455</v>
       </c>
       <c r="E3" t="n">
-        <v>1.063636363636364</v>
+        <v>1.064646464646465</v>
       </c>
       <c r="F3" t="n">
-        <v>69.83636363636363</v>
+        <v>69.889898989899</v>
       </c>
       <c r="G3" t="n">
-        <v>2975833.333333333</v>
+        <v>3047020.202020202</v>
       </c>
       <c r="H3" t="n">
-        <v>75.5439393939394</v>
+        <v>75.58888888888889</v>
       </c>
       <c r="I3" t="n">
-        <v>26.16060606060606</v>
+        <v>26.26590909090909</v>
       </c>
       <c r="J3" t="n">
-        <v>183.3848484848485</v>
+        <v>183.5416666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>1.615151515151515</v>
+        <v>1.634848484848485</v>
       </c>
       <c r="L3" t="n">
-        <v>76.28282828282828</v>
+        <v>76.4189393939394</v>
       </c>
       <c r="M3" t="n">
-        <v>12461010.1010101</v>
+        <v>12592348.48484849</v>
       </c>
       <c r="N3" t="n">
-        <v>79.4969696969697</v>
+        <v>79.57878787878788</v>
       </c>
       <c r="O3" t="n">
-        <v>25.23322081836575</v>
+        <v>25.01872840882503</v>
       </c>
       <c r="P3" t="n">
-        <v>184.4230924067881</v>
+        <v>184.6624034848672</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.117838783599653</v>
+        <v>1.104200214707461</v>
       </c>
       <c r="R3" t="n">
-        <v>68.38258443783806</v>
+        <v>68.39180842864418</v>
       </c>
       <c r="S3" t="n">
-        <v>2260378.02190429</v>
+        <v>2332025.518876364</v>
       </c>
       <c r="T3" t="n">
-        <v>73.27418297617572</v>
+        <v>73.50330147129665</v>
       </c>
       <c r="U3" t="n">
-        <v>25.33106574985469</v>
+        <v>25.14070103428836</v>
       </c>
       <c r="V3" t="n">
-        <v>182.0266687108216</v>
+        <v>181.8332528326614</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59366858356197</v>
+        <v>1.562596304468099</v>
       </c>
       <c r="X3" t="n">
-        <v>74.74005921472855</v>
+        <v>74.70471546367799</v>
       </c>
       <c r="Y3" t="n">
-        <v>11493538.01718053</v>
+        <v>11574638.97422393</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.09131933693986</v>
+        <v>79.13637043187968</v>
       </c>
     </row>
     <row r="4">
@@ -729,76 +729,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.3008658008658</v>
+        <v>25.3460606060606</v>
       </c>
       <c r="D4" t="n">
-        <v>184.4738816738817</v>
+        <v>184.4126262626263</v>
       </c>
       <c r="E4" t="n">
-        <v>1.754978354978355</v>
+        <v>1.808484848484849</v>
       </c>
       <c r="F4" t="n">
-        <v>79.97301587301588</v>
+        <v>80.61474747474747</v>
       </c>
       <c r="G4" t="n">
-        <v>31599733.04473305</v>
+        <v>35162540.40404041</v>
       </c>
       <c r="H4" t="n">
-        <v>83.74733044733044</v>
+        <v>84.22222222222221</v>
       </c>
       <c r="I4" t="n">
-        <v>25.77922077922078</v>
+        <v>25.79545454545455</v>
       </c>
       <c r="J4" t="n">
-        <v>186.4</v>
+        <v>186.23</v>
       </c>
       <c r="K4" t="n">
-        <v>1.225974025974026</v>
+        <v>1.248181818181818</v>
       </c>
       <c r="L4" t="n">
-        <v>76.05454545454545</v>
+        <v>76.07818181818182</v>
       </c>
       <c r="M4" t="n">
-        <v>13493376.62337662</v>
+        <v>13460363.63636364</v>
       </c>
       <c r="N4" t="n">
-        <v>79.3987012987013</v>
+        <v>79.36909090909091</v>
       </c>
       <c r="O4" t="n">
-        <v>24.44167626024769</v>
+        <v>24.4168428978429</v>
       </c>
       <c r="P4" t="n">
-        <v>185.1718472004186</v>
+        <v>184.8154782254782</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.529103436246293</v>
+        <v>1.532947903947904</v>
       </c>
       <c r="R4" t="n">
-        <v>76.28516774231061</v>
+        <v>76.26987382987383</v>
       </c>
       <c r="S4" t="n">
-        <v>22503626.54805512</v>
+        <v>21156981.46113146</v>
       </c>
       <c r="T4" t="n">
-        <v>82.00816210244781</v>
+        <v>82.05887016687015</v>
       </c>
       <c r="U4" t="n">
-        <v>25.10075684978936</v>
+        <v>24.94636711542671</v>
       </c>
       <c r="V4" t="n">
-        <v>184.6815733071538</v>
+        <v>185.0591305860463</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22042159766618</v>
+        <v>1.193529568127091</v>
       </c>
       <c r="X4" t="n">
-        <v>72.04932010284178</v>
+        <v>72.03887250992901</v>
       </c>
       <c r="Y4" t="n">
-        <v>5788223.678626155</v>
+        <v>5762901.734058855</v>
       </c>
       <c r="Z4" t="n">
-        <v>75.75028893535087</v>
+        <v>76.01139701973294</v>
       </c>
     </row>
     <row r="5">
@@ -811,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.53246753246754</v>
+        <v>25.53636363636364</v>
       </c>
       <c r="D5" t="n">
-        <v>183.8571428571429</v>
+        <v>183.9090909090909</v>
       </c>
       <c r="E5" t="n">
-        <v>1.038961038961039</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="F5" t="n">
-        <v>72.37662337662339</v>
+        <v>72.48181818181817</v>
       </c>
       <c r="G5" t="n">
-        <v>4474025.974025974</v>
+        <v>4577272.727272728</v>
       </c>
       <c r="H5" t="n">
-        <v>76.05194805194806</v>
+        <v>76.06363636363636</v>
       </c>
       <c r="I5" t="n">
-        <v>25.28961038961039</v>
+        <v>25.48760330578513</v>
       </c>
       <c r="J5" t="n">
-        <v>183.5194805194805</v>
+        <v>183.7950413223141</v>
       </c>
       <c r="K5" t="n">
-        <v>1.346753246753247</v>
+        <v>1.36198347107438</v>
       </c>
       <c r="L5" t="n">
-        <v>73.22077922077922</v>
+        <v>73.41983471074379</v>
       </c>
       <c r="M5" t="n">
-        <v>7368311.688311689</v>
+        <v>7316859.504132232</v>
       </c>
       <c r="N5" t="n">
-        <v>77.66493506493508</v>
+        <v>77.64545454545454</v>
       </c>
       <c r="O5" t="n">
-        <v>25.06424792139078</v>
+        <v>25.12013542013542</v>
       </c>
       <c r="P5" t="n">
-        <v>182.1354003139717</v>
+        <v>182.4552697302697</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.131577417291703</v>
+        <v>1.136639286639287</v>
       </c>
       <c r="R5" t="n">
-        <v>70.0292168149311</v>
+        <v>69.91116661116661</v>
       </c>
       <c r="S5" t="n">
-        <v>3060825.48403977</v>
+        <v>2937943.158693159</v>
       </c>
       <c r="T5" t="n">
-        <v>74.85582010582011</v>
+        <v>74.6719178969179</v>
       </c>
       <c r="U5" t="n">
-        <v>25.83945585815151</v>
+        <v>25.56330433656521</v>
       </c>
       <c r="V5" t="n">
-        <v>182.2817141795403</v>
+        <v>182.3016826571175</v>
       </c>
       <c r="W5" t="n">
-        <v>1.321755587407761</v>
+        <v>1.272028872898438</v>
       </c>
       <c r="X5" t="n">
-        <v>71.60149165649166</v>
+        <v>71.5465527065527</v>
       </c>
       <c r="Y5" t="n">
-        <v>4130323.399426661</v>
+        <v>4293361.070290417</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.81114455592716</v>
+        <v>76.73273949078296</v>
       </c>
     </row>
     <row r="6">
@@ -893,76 +893,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.45454545454546</v>
+        <v>24.55454545454545</v>
       </c>
       <c r="D6" t="n">
-        <v>185.5064935064935</v>
+        <v>185.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1.25974025974026</v>
+        <v>1.263636363636364</v>
       </c>
       <c r="F6" t="n">
-        <v>74.75324675324676</v>
+        <v>75.06363636363636</v>
       </c>
       <c r="G6" t="n">
-        <v>10753246.75324675</v>
+        <v>11195681.81818182</v>
       </c>
       <c r="H6" t="n">
-        <v>79.57142857142857</v>
+        <v>79.68181818181819</v>
       </c>
       <c r="I6" t="n">
-        <v>24.62337662337663</v>
+        <v>25.00826446280992</v>
       </c>
       <c r="J6" t="n">
-        <v>187.3766233766234</v>
+        <v>186.603305785124</v>
       </c>
       <c r="K6" t="n">
-        <v>1.038961038961039</v>
+        <v>1.049586776859504</v>
       </c>
       <c r="L6" t="n">
-        <v>73.16883116883118</v>
+        <v>73.33884297520662</v>
       </c>
       <c r="M6" t="n">
-        <v>5062337.662337663</v>
+        <v>5136363.636363637</v>
       </c>
       <c r="N6" t="n">
-        <v>77.32467532467533</v>
+        <v>77.11570247933884</v>
       </c>
       <c r="O6" t="n">
-        <v>23.04809054656345</v>
+        <v>22.96644480934136</v>
       </c>
       <c r="P6" t="n">
-        <v>184.8191109547267</v>
+        <v>184.7342242291553</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.212904058174994</v>
+        <v>1.202148148148148</v>
       </c>
       <c r="R6" t="n">
-        <v>71.26351395730707</v>
+        <v>71.23520780879402</v>
       </c>
       <c r="S6" t="n">
-        <v>7002015.012901713</v>
+        <v>7029183.269476374</v>
       </c>
       <c r="T6" t="n">
-        <v>78.05814684494487</v>
+        <v>78.16315307425653</v>
       </c>
       <c r="U6" t="n">
-        <v>25.29097394513361</v>
+        <v>25.33426193236354</v>
       </c>
       <c r="V6" t="n">
-        <v>183.0837984082522</v>
+        <v>183.2899213145737</v>
       </c>
       <c r="W6" t="n">
-        <v>1.083890889689209</v>
+        <v>1.072076857584879</v>
       </c>
       <c r="X6" t="n">
-        <v>70.58646147347828</v>
+        <v>70.90836288191903</v>
       </c>
       <c r="Y6" t="n">
-        <v>3076779.189453559</v>
+        <v>3268867.758751449</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.6091898981815</v>
+        <v>74.88350884013985</v>
       </c>
     </row>
     <row r="7">
@@ -975,76 +975,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>24.92207792207792</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>184.038961038961</v>
+        <v>184.0545454545455</v>
       </c>
       <c r="E7" t="n">
-        <v>1.116883116883117</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="F7" t="n">
-        <v>72.85714285714286</v>
+        <v>72.97272727272727</v>
       </c>
       <c r="G7" t="n">
-        <v>4697077.922077922</v>
+        <v>4746136.363636364</v>
       </c>
       <c r="H7" t="n">
-        <v>76.6103896103896</v>
+        <v>76.57272727272728</v>
       </c>
       <c r="I7" t="n">
-        <v>26.18441558441559</v>
+        <v>26.25909090909091</v>
       </c>
       <c r="J7" t="n">
-        <v>182.4324675324676</v>
+        <v>182.0827272727273</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="L7" t="n">
-        <v>80.58311688311689</v>
+        <v>80.78818181818183</v>
       </c>
       <c r="M7" t="n">
-        <v>35072207.79220779</v>
+        <v>35250545.45454545</v>
       </c>
       <c r="N7" t="n">
-        <v>82.4909090909091</v>
+        <v>82.58363636363637</v>
       </c>
       <c r="O7" t="n">
-        <v>24.05835368335368</v>
+        <v>24.15788461538461</v>
       </c>
       <c r="P7" t="n">
-        <v>182.74185999186</v>
+        <v>182.8098575498576</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.041761148904006</v>
+        <v>1.040343915343915</v>
       </c>
       <c r="R7" t="n">
-        <v>70.55081690795977</v>
+        <v>70.6698310948311</v>
       </c>
       <c r="S7" t="n">
-        <v>3384843.232164661</v>
+        <v>3462158.781033781</v>
       </c>
       <c r="T7" t="n">
-        <v>75.3547953369382</v>
+        <v>75.41835673585675</v>
       </c>
       <c r="U7" t="n">
-        <v>24.70533731834042</v>
+        <v>24.99373612283829</v>
       </c>
       <c r="V7" t="n">
-        <v>180.9094669233988</v>
+        <v>180.8991268463791</v>
       </c>
       <c r="W7" t="n">
-        <v>1.512483861168072</v>
+        <v>1.552191083770031</v>
       </c>
       <c r="X7" t="n">
-        <v>75.60444132464256</v>
+        <v>75.91953749867837</v>
       </c>
       <c r="Y7" t="n">
-        <v>15968914.05485639</v>
+        <v>15890858.88601852</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.08295471298568</v>
+        <v>79.21223496575664</v>
       </c>
     </row>
     <row r="8">
@@ -1057,76 +1057,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.16883116883117</v>
+        <v>25.43636363636364</v>
       </c>
       <c r="D8" t="n">
-        <v>184.1688311688311</v>
+        <v>184.3818181818181</v>
       </c>
       <c r="E8" t="n">
-        <v>1.194805194805195</v>
+        <v>1.209090909090909</v>
       </c>
       <c r="F8" t="n">
-        <v>72.1038961038961</v>
+        <v>72.18181818181817</v>
       </c>
       <c r="G8" t="n">
-        <v>3715584.415584415</v>
+        <v>3650000</v>
       </c>
       <c r="H8" t="n">
-        <v>76</v>
+        <v>75.73636363636363</v>
       </c>
       <c r="I8" t="n">
-        <v>26.14025974025974</v>
+        <v>26.37363636363636</v>
       </c>
       <c r="J8" t="n">
-        <v>182.4363636363637</v>
+        <v>182.5881818181818</v>
       </c>
       <c r="K8" t="n">
-        <v>2.096103896103896</v>
+        <v>2.149090909090909</v>
       </c>
       <c r="L8" t="n">
-        <v>78.55064935064934</v>
+        <v>78.66636363636363</v>
       </c>
       <c r="M8" t="n">
-        <v>21361298.7012987</v>
+        <v>21377272.72727273</v>
       </c>
       <c r="N8" t="n">
-        <v>80.65584415584415</v>
+        <v>80.59636363636363</v>
       </c>
       <c r="O8" t="n">
-        <v>26.03209458849853</v>
+        <v>25.81782430213465</v>
       </c>
       <c r="P8" t="n">
-        <v>183.2602555080387</v>
+        <v>183.1474308450171</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.165195149677908</v>
+        <v>1.136724137931035</v>
       </c>
       <c r="R8" t="n">
-        <v>70.11228188888286</v>
+        <v>70.13735063786788</v>
       </c>
       <c r="S8" t="n">
-        <v>2659948.519460835</v>
+        <v>2714007.06707086</v>
       </c>
       <c r="T8" t="n">
-        <v>74.10430628484816</v>
+        <v>74.33269609700645</v>
       </c>
       <c r="U8" t="n">
-        <v>25.39790946145626</v>
+        <v>25.29662779111055</v>
       </c>
       <c r="V8" t="n">
-        <v>183.0843898803259</v>
+        <v>182.86790482506</v>
       </c>
       <c r="W8" t="n">
-        <v>1.95192613443845</v>
+        <v>1.962929490688111</v>
       </c>
       <c r="X8" t="n">
-        <v>76.29772475745382</v>
+        <v>76.04017371198407</v>
       </c>
       <c r="Y8" t="n">
-        <v>17108203.40396695</v>
+        <v>16401725.28875977</v>
       </c>
       <c r="Z8" t="n">
-        <v>80.3989667101736</v>
+        <v>80.38639920424403</v>
       </c>
     </row>
     <row r="9">
@@ -1139,76 +1139,76 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.78863636363636</v>
+        <v>26.75723905723906</v>
       </c>
       <c r="D9" t="n">
-        <v>183.7431818181818</v>
+        <v>183.951936026936</v>
       </c>
       <c r="E9" t="n">
-        <v>1.723863636363636</v>
+        <v>1.738131313131313</v>
       </c>
       <c r="F9" t="n">
-        <v>77.53522727272727</v>
+        <v>77.496632996633</v>
       </c>
       <c r="G9" t="n">
-        <v>18098636.36363636</v>
+        <v>18198164.98316498</v>
       </c>
       <c r="H9" t="n">
-        <v>79.77954545454546</v>
+        <v>79.82340067340067</v>
       </c>
       <c r="I9" t="n">
-        <v>24.83636363636364</v>
+        <v>24.88111888111888</v>
       </c>
       <c r="J9" t="n">
-        <v>184.9181818181818</v>
+        <v>184.7482517482517</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>69.95454545454545</v>
+        <v>69.98601398601399</v>
       </c>
       <c r="M9" t="n">
-        <v>2783863.636363636</v>
+        <v>2770104.895104895</v>
       </c>
       <c r="N9" t="n">
-        <v>74.59999999999999</v>
+        <v>74.62937062937064</v>
       </c>
       <c r="O9" t="n">
-        <v>26.28077821777764</v>
+        <v>26.4445965457121</v>
       </c>
       <c r="P9" t="n">
-        <v>182.1002924182987</v>
+        <v>182.1903793987604</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.769360468859897</v>
+        <v>1.794692222981697</v>
       </c>
       <c r="R9" t="n">
-        <v>76.40745118725668</v>
+        <v>76.55374874934371</v>
       </c>
       <c r="S9" t="n">
-        <v>15846594.62019674</v>
+        <v>16200766.63744341</v>
       </c>
       <c r="T9" t="n">
-        <v>79.5338229466948</v>
+        <v>79.53111253099812</v>
       </c>
       <c r="U9" t="n">
-        <v>25.77338461538462</v>
+        <v>25.91443786982249</v>
       </c>
       <c r="V9" t="n">
-        <v>181.8730769230769</v>
+        <v>181.7165142549758</v>
       </c>
       <c r="W9" t="n">
-        <v>1.035076923076923</v>
+        <v>1.042313071543841</v>
       </c>
       <c r="X9" t="n">
-        <v>67.49861538461539</v>
+        <v>67.57424421732115</v>
       </c>
       <c r="Y9" t="n">
-        <v>1620358.461538462</v>
+        <v>1616877.407208177</v>
       </c>
       <c r="Z9" t="n">
-        <v>72.28969230769231</v>
+        <v>72.17388918773534</v>
       </c>
     </row>
     <row r="10">
@@ -1221,76 +1221,76 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>23.94805194805195</v>
+        <v>24.06363636363636</v>
       </c>
       <c r="D10" t="n">
-        <v>184.7662337662337</v>
+        <v>184.6545454545455</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>71.97402597402598</v>
+        <v>72.15454545454546</v>
       </c>
       <c r="G10" t="n">
-        <v>5398051.948051949</v>
+        <v>5452272.727272728</v>
       </c>
       <c r="H10" t="n">
-        <v>77.83116883116884</v>
+        <v>77.78181818181818</v>
       </c>
       <c r="I10" t="n">
-        <v>25.52090909090909</v>
+        <v>25.85384615384616</v>
       </c>
       <c r="J10" t="n">
-        <v>187.4727272727272</v>
+        <v>187.1951048951049</v>
       </c>
       <c r="K10" t="n">
-        <v>1.486363636363637</v>
+        <v>1.53986013986014</v>
       </c>
       <c r="L10" t="n">
-        <v>78.13363636363637</v>
+        <v>78.30699300699301</v>
       </c>
       <c r="M10" t="n">
-        <v>18975909.09090909</v>
+        <v>19034965.03496503</v>
       </c>
       <c r="N10" t="n">
-        <v>81.75272727272727</v>
+        <v>81.62307692307692</v>
       </c>
       <c r="O10" t="n">
-        <v>23.30908309082222</v>
+        <v>23.36307449072667</v>
       </c>
       <c r="P10" t="n">
-        <v>183.3037849107414</v>
+        <v>182.6972344177562</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.073890457368718</v>
+        <v>1.08224931590149</v>
       </c>
       <c r="R10" t="n">
-        <v>67.99492941840768</v>
+        <v>68.24991669200365</v>
       </c>
       <c r="S10" t="n">
-        <v>2511074.729618208</v>
+        <v>2627385.177865612</v>
       </c>
       <c r="T10" t="n">
-        <v>74.56220127698388</v>
+        <v>74.82169534813013</v>
       </c>
       <c r="U10" t="n">
-        <v>25.54789929635582</v>
+        <v>25.48735967179111</v>
       </c>
       <c r="V10" t="n">
-        <v>186.5524322296062</v>
+        <v>186.6171936263909</v>
       </c>
       <c r="W10" t="n">
-        <v>1.378456097043054</v>
+        <v>1.383031383951117</v>
       </c>
       <c r="X10" t="n">
-        <v>74.94643653689306</v>
+        <v>74.97006947777851</v>
       </c>
       <c r="Y10" t="n">
-        <v>13650326.75833828</v>
+        <v>13449298.17531038</v>
       </c>
       <c r="Z10" t="n">
-        <v>78.73000124271864</v>
+        <v>78.82860246714762</v>
       </c>
     </row>
     <row r="11">
@@ -1303,533 +1303,569 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25.62976992143659</v>
+        <v>25.72659285159285</v>
       </c>
       <c r="D11" t="n">
-        <v>186.3258978675645</v>
+        <v>186.3965617715618</v>
       </c>
       <c r="E11" t="n">
-        <v>1.77847923681257</v>
+        <v>1.786810411810412</v>
       </c>
       <c r="F11" t="n">
-        <v>80.13959034792367</v>
+        <v>80.37869075369075</v>
       </c>
       <c r="G11" t="n">
-        <v>29548007.85634119</v>
+        <v>30229817.4048174</v>
       </c>
       <c r="H11" t="n">
-        <v>83.84778338945006</v>
+        <v>83.96299533799535</v>
       </c>
       <c r="I11" t="n">
-        <v>25.95555555555556</v>
+        <v>25.67037037037037</v>
       </c>
       <c r="J11" t="n">
-        <v>181.0648148148148</v>
+        <v>181.4456790123457</v>
       </c>
       <c r="K11" t="n">
-        <v>1.051851851851852</v>
+        <v>1.045679012345679</v>
       </c>
       <c r="L11" t="n">
-        <v>71.02962962962964</v>
+        <v>70.95432098765433</v>
       </c>
       <c r="M11" t="n">
-        <v>3338935.185185185</v>
+        <v>3293703.703703704</v>
       </c>
       <c r="N11" t="n">
-        <v>73.29814814814814</v>
+        <v>73.51481481481481</v>
       </c>
       <c r="O11" t="n">
-        <v>25.06312241407207</v>
+        <v>24.8135679461652</v>
       </c>
       <c r="P11" t="n">
-        <v>184.076849219374</v>
+        <v>183.9314402861314</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.808753130080361</v>
+        <v>1.76277271165143</v>
       </c>
       <c r="R11" t="n">
-        <v>76.60997515197744</v>
+        <v>76.16277464335816</v>
       </c>
       <c r="S11" t="n">
-        <v>16744923.02698996</v>
+        <v>15622918.12363838</v>
       </c>
       <c r="T11" t="n">
-        <v>81.66740469788144</v>
+        <v>81.49824943807782</v>
       </c>
       <c r="U11" t="n">
-        <v>26.42016144349478</v>
+        <v>26.03937376990517</v>
       </c>
       <c r="V11" t="n">
-        <v>183.3278822412156</v>
+        <v>183.3066870363489</v>
       </c>
       <c r="W11" t="n">
-        <v>1.264577397910731</v>
+        <v>1.219601690133091</v>
       </c>
       <c r="X11" t="n">
-        <v>70.08405508072174</v>
+        <v>69.62724802840745</v>
       </c>
       <c r="Y11" t="n">
-        <v>2746374.45394112</v>
+        <v>2557524.612907222</v>
       </c>
       <c r="Z11" t="n">
-        <v>72.65479582146249</v>
+        <v>72.58290323024623</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.61428571428572</v>
+        <v>24.68080808080808</v>
       </c>
       <c r="D12" t="n">
-        <v>187.1350649350649</v>
+        <v>184.7545454545455</v>
       </c>
       <c r="E12" t="n">
-        <v>1.206493506493507</v>
+        <v>1.064646464646465</v>
       </c>
       <c r="F12" t="n">
-        <v>73.09090909090909</v>
+        <v>69.889898989899</v>
       </c>
       <c r="G12" t="n">
-        <v>5204350.64935065</v>
+        <v>3047020.202020202</v>
       </c>
       <c r="H12" t="n">
-        <v>77.32987012987012</v>
+        <v>75.58888888888889</v>
       </c>
       <c r="I12" t="n">
-        <v>25.2</v>
+        <v>25.3460606060606</v>
       </c>
       <c r="J12" t="n">
-        <v>183.6740740740741</v>
+        <v>184.4126262626263</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>1.808484848484849</v>
       </c>
       <c r="L12" t="n">
-        <v>66.58703703703704</v>
+        <v>80.61474747474747</v>
       </c>
       <c r="M12" t="n">
-        <v>1224768.518518518</v>
+        <v>35162540.40404041</v>
       </c>
       <c r="N12" t="n">
-        <v>70.55185185185185</v>
+        <v>84.22222222222221</v>
       </c>
       <c r="O12" t="n">
-        <v>24.13351906856619</v>
+        <v>25.01872840882503</v>
       </c>
       <c r="P12" t="n">
-        <v>184.803806672453</v>
+        <v>184.6624034848672</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.131562492781169</v>
+        <v>1.104200214707461</v>
       </c>
       <c r="R12" t="n">
-        <v>70.74169880479262</v>
+        <v>68.39180842864418</v>
       </c>
       <c r="S12" t="n">
-        <v>3987255.490691773</v>
+        <v>2332025.518876364</v>
       </c>
       <c r="T12" t="n">
-        <v>77.17005063794633</v>
+        <v>73.50330147129665</v>
       </c>
       <c r="U12" t="n">
-        <v>24.87493987493987</v>
+        <v>24.4168428978429</v>
       </c>
       <c r="V12" t="n">
-        <v>183.4552068302069</v>
+        <v>184.8154782254782</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.532947903947904</v>
       </c>
       <c r="X12" t="n">
-        <v>64.39673520923522</v>
+        <v>76.26987382987383</v>
       </c>
       <c r="Y12" t="n">
-        <v>1007061.988936989</v>
+        <v>21156981.46113146</v>
       </c>
       <c r="Z12" t="n">
-        <v>69.19237012987013</v>
+        <v>82.05887016687015</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>24.62337662337663</v>
+        <v>25.00826446280992</v>
       </c>
       <c r="D13" t="n">
-        <v>187.3766233766234</v>
+        <v>186.603305785124</v>
       </c>
       <c r="E13" t="n">
-        <v>1.038961038961039</v>
+        <v>1.049586776859504</v>
       </c>
       <c r="F13" t="n">
-        <v>73.16883116883118</v>
+        <v>73.33884297520662</v>
       </c>
       <c r="G13" t="n">
-        <v>5062337.662337663</v>
+        <v>5136363.636363637</v>
       </c>
       <c r="H13" t="n">
-        <v>77.32467532467533</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>77.11570247933884</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.75723905723906</v>
+      </c>
+      <c r="J13" t="n">
+        <v>183.951936026936</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.738131313131313</v>
+      </c>
+      <c r="L13" t="n">
+        <v>77.496632996633</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18198164.98316498</v>
+      </c>
+      <c r="N13" t="n">
+        <v>79.82340067340067</v>
+      </c>
       <c r="O13" t="n">
-        <v>25.29097394513361</v>
+        <v>25.33426193236354</v>
       </c>
       <c r="P13" t="n">
-        <v>183.0837984082522</v>
+        <v>183.2899213145737</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.083890889689209</v>
+        <v>1.072076857584879</v>
       </c>
       <c r="R13" t="n">
-        <v>70.58646147347828</v>
+        <v>70.90836288191903</v>
       </c>
       <c r="S13" t="n">
-        <v>3076779.189453559</v>
+        <v>3268867.758751449</v>
       </c>
       <c r="T13" t="n">
-        <v>74.6091898981815</v>
+        <v>74.88350884013985</v>
       </c>
       <c r="U13" t="n">
-        <v>27.5</v>
+        <v>26.4445965457121</v>
       </c>
       <c r="V13" t="n">
-        <v>182.8333333333333</v>
+        <v>182.1903793987604</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>1.794692222981697</v>
       </c>
       <c r="X13" t="n">
-        <v>67.16666666666667</v>
+        <v>76.55374874934371</v>
       </c>
       <c r="Y13" t="n">
-        <v>1137500</v>
+        <v>16200766.63744341</v>
       </c>
       <c r="Z13" t="n">
-        <v>69</v>
+        <v>79.53111253099812</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>25.75714285714286</v>
+        <v>28.00818181818182</v>
       </c>
       <c r="D14" t="n">
-        <v>184.5428571428571</v>
+        <v>182.9309090909091</v>
       </c>
       <c r="E14" t="n">
-        <v>1.214285714285714</v>
+        <v>2.413636363636364</v>
       </c>
       <c r="F14" t="n">
-        <v>72.94285714285715</v>
+        <v>82.88454545454546</v>
       </c>
       <c r="G14" t="n">
-        <v>6193214.285714285</v>
+        <v>40085454.54545455</v>
       </c>
       <c r="H14" t="n">
-        <v>77.7</v>
+        <v>84.66454545454545</v>
       </c>
       <c r="I14" t="n">
-        <v>26.01060606060606</v>
+        <v>24.06363636363636</v>
       </c>
       <c r="J14" t="n">
-        <v>184.1075757575757</v>
+        <v>184.6545454545455</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>65.63939393939394</v>
+        <v>72.15454545454546</v>
       </c>
       <c r="M14" t="n">
-        <v>1166545.454545454</v>
+        <v>5452272.727272728</v>
       </c>
       <c r="N14" t="n">
-        <v>68.98333333333333</v>
+        <v>77.78181818181818</v>
       </c>
       <c r="O14" t="n">
-        <v>26.54104041616646</v>
+        <v>27.10158309001788</v>
       </c>
       <c r="P14" t="n">
-        <v>184.7348299319728</v>
+        <v>182.5357371404763</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.335388155262105</v>
+        <v>1.885667641537206</v>
       </c>
       <c r="R14" t="n">
-        <v>70.03281512605042</v>
+        <v>78.98572182246096</v>
       </c>
       <c r="S14" t="n">
-        <v>3335327.781112445</v>
+        <v>24084349.68895838</v>
       </c>
       <c r="T14" t="n">
-        <v>73.8702581032413</v>
+        <v>81.47697790132572</v>
       </c>
       <c r="U14" t="n">
-        <v>26.18196457326892</v>
+        <v>23.36307449072667</v>
       </c>
       <c r="V14" t="n">
-        <v>182.4396135265701</v>
+        <v>182.6972344177562</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>1.08224931590149</v>
       </c>
       <c r="X14" t="n">
-        <v>64.31696188942566</v>
+        <v>68.24991669200365</v>
       </c>
       <c r="Y14" t="n">
-        <v>1003643.317230274</v>
+        <v>2627385.177865612</v>
       </c>
       <c r="Z14" t="n">
-        <v>68.0107353730542</v>
+        <v>74.82169534813013</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.28961038961039</v>
+        <v>25.48760330578513</v>
       </c>
       <c r="D15" t="n">
-        <v>183.5194805194805</v>
+        <v>183.7950413223141</v>
       </c>
       <c r="E15" t="n">
-        <v>1.346753246753247</v>
+        <v>1.36198347107438</v>
       </c>
       <c r="F15" t="n">
-        <v>73.22077922077922</v>
+        <v>73.41983471074379</v>
       </c>
       <c r="G15" t="n">
-        <v>7368311.688311689</v>
+        <v>7316859.504132232</v>
       </c>
       <c r="H15" t="n">
-        <v>77.66493506493508</v>
+        <v>77.64545454545454</v>
       </c>
       <c r="I15" t="n">
-        <v>28.75</v>
+        <v>26.10330578512397</v>
       </c>
       <c r="J15" t="n">
-        <v>183.4833333333333</v>
+        <v>184.1545454545455</v>
       </c>
       <c r="K15" t="n">
-        <v>1.15</v>
+        <v>1.179338842975207</v>
       </c>
       <c r="L15" t="n">
-        <v>67.7</v>
+        <v>73.0900826446281</v>
       </c>
       <c r="M15" t="n">
-        <v>1041250</v>
+        <v>6146074.38016529</v>
       </c>
       <c r="N15" t="n">
-        <v>69.95</v>
+        <v>77.47685950413224</v>
       </c>
       <c r="O15" t="n">
-        <v>25.83945585815151</v>
+        <v>25.56330433656521</v>
       </c>
       <c r="P15" t="n">
-        <v>182.2817141795403</v>
+        <v>182.3016826571175</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.321755587407761</v>
+        <v>1.272028872898438</v>
       </c>
       <c r="R15" t="n">
-        <v>71.60149165649166</v>
+        <v>71.5465527065527</v>
       </c>
       <c r="S15" t="n">
-        <v>4130323.399426661</v>
+        <v>4293361.070290417</v>
       </c>
       <c r="T15" t="n">
-        <v>76.81114455592716</v>
+        <v>76.73273949078296</v>
       </c>
       <c r="U15" t="n">
-        <v>25.29765554493816</v>
+        <v>26.53778329513624</v>
       </c>
       <c r="V15" t="n">
-        <v>185.003876089021</v>
+        <v>184.9579220779221</v>
       </c>
       <c r="W15" t="n">
-        <v>1.028537585602803</v>
+        <v>1.40827731092437</v>
       </c>
       <c r="X15" t="n">
-        <v>65.28115322680542</v>
+        <v>70.29345811051694</v>
       </c>
       <c r="Y15" t="n">
-        <v>1006235.443468233</v>
+        <v>3627757.830404889</v>
       </c>
       <c r="Z15" t="n">
-        <v>68.66067815705496</v>
+        <v>74.07986121721416</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>26.95424242424243</v>
+        <v>26.26590909090909</v>
       </c>
       <c r="D16" t="n">
-        <v>185.3758585858586</v>
+        <v>183.5416666666667</v>
       </c>
       <c r="E16" t="n">
-        <v>1.083636363636364</v>
+        <v>1.634848484848485</v>
       </c>
       <c r="F16" t="n">
-        <v>69.25010101010102</v>
+        <v>76.4189393939394</v>
       </c>
       <c r="G16" t="n">
-        <v>1925252.525252525</v>
+        <v>12592348.48484849</v>
       </c>
       <c r="H16" t="n">
-        <v>72.48222222222223</v>
+        <v>79.57878787878788</v>
       </c>
       <c r="I16" t="n">
-        <v>27.79040404040404</v>
+        <v>24.88111888111888</v>
       </c>
       <c r="J16" t="n">
-        <v>180.6546717171717</v>
+        <v>184.7482517482517</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>67.53737373737374</v>
+        <v>69.98601398601399</v>
       </c>
       <c r="M16" t="n">
-        <v>1260000</v>
+        <v>2770104.895104895</v>
       </c>
       <c r="N16" t="n">
-        <v>69.83118686868687</v>
+        <v>74.62937062937064</v>
       </c>
       <c r="O16" t="n">
-        <v>27.38291407867495</v>
+        <v>25.14070103428836</v>
       </c>
       <c r="P16" t="n">
-        <v>185.4870387728214</v>
+        <v>181.8332528326614</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.1271259175607</v>
+        <v>1.562596304468099</v>
       </c>
       <c r="R16" t="n">
-        <v>69.98390090344438</v>
+        <v>74.70471546367799</v>
       </c>
       <c r="S16" t="n">
-        <v>2094229.387822323</v>
+        <v>11574638.97422393</v>
       </c>
       <c r="T16" t="n">
-        <v>73.07276736307172</v>
+        <v>79.13637043187968</v>
       </c>
       <c r="U16" t="n">
-        <v>25.10873973852235</v>
+        <v>25.91443786982249</v>
       </c>
       <c r="V16" t="n">
-        <v>178.3820519154758</v>
+        <v>181.7165142549758</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.042313071543841</v>
       </c>
       <c r="X16" t="n">
-        <v>64.90591783216783</v>
+        <v>67.57424421732115</v>
       </c>
       <c r="Y16" t="n">
-        <v>1252055.211817168</v>
+        <v>1616877.407208177</v>
       </c>
       <c r="Z16" t="n">
-        <v>69.53118881118883</v>
+        <v>72.17388918773534</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>24.92207792207792</v>
+        <v>25.79545454545455</v>
       </c>
       <c r="D17" t="n">
-        <v>184.038961038961</v>
+        <v>186.23</v>
       </c>
       <c r="E17" t="n">
-        <v>1.116883116883117</v>
+        <v>1.248181818181818</v>
       </c>
       <c r="F17" t="n">
-        <v>72.85714285714286</v>
+        <v>76.07818181818182</v>
       </c>
       <c r="G17" t="n">
-        <v>4697077.922077922</v>
+        <v>13460363.63636364</v>
       </c>
       <c r="H17" t="n">
-        <v>76.6103896103896</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>79.36909090909091</v>
+      </c>
+      <c r="I17" t="n">
+        <v>25.85384615384616</v>
+      </c>
+      <c r="J17" t="n">
+        <v>187.1951048951049</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.53986013986014</v>
+      </c>
+      <c r="L17" t="n">
+        <v>78.30699300699301</v>
+      </c>
+      <c r="M17" t="n">
+        <v>19034965.03496503</v>
+      </c>
+      <c r="N17" t="n">
+        <v>81.62307692307692</v>
+      </c>
       <c r="O17" t="n">
-        <v>24.05835368335368</v>
+        <v>24.94636711542671</v>
       </c>
       <c r="P17" t="n">
-        <v>182.74185999186</v>
+        <v>185.0591305860463</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.041761148904006</v>
+        <v>1.193529568127091</v>
       </c>
       <c r="R17" t="n">
-        <v>70.55081690795977</v>
+        <v>72.03887250992901</v>
       </c>
       <c r="S17" t="n">
-        <v>3384843.232164661</v>
+        <v>5762901.734058855</v>
       </c>
       <c r="T17" t="n">
-        <v>75.3547953369382</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+        <v>76.01139701973294</v>
+      </c>
+      <c r="U17" t="n">
+        <v>25.48735967179111</v>
+      </c>
+      <c r="V17" t="n">
+        <v>186.6171936263909</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.383031383951117</v>
+      </c>
+      <c r="X17" t="n">
+        <v>74.97006947777851</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13449298.17531038</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>78.82860246714762</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1841,76 +1877,76 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.53246753246754</v>
+        <v>25.53636363636364</v>
       </c>
       <c r="D18" t="n">
-        <v>183.8571428571429</v>
+        <v>183.9090909090909</v>
       </c>
       <c r="E18" t="n">
-        <v>1.038961038961039</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="F18" t="n">
-        <v>72.37662337662339</v>
+        <v>72.48181818181817</v>
       </c>
       <c r="G18" t="n">
-        <v>4474025.974025974</v>
+        <v>4577272.727272728</v>
       </c>
       <c r="H18" t="n">
-        <v>76.05194805194806</v>
+        <v>76.06363636363636</v>
       </c>
       <c r="I18" t="n">
-        <v>26.76363636363637</v>
+        <v>26.95909090909091</v>
       </c>
       <c r="J18" t="n">
-        <v>181.659595959596</v>
+        <v>181.5780303030303</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>67.35757575757576</v>
+        <v>67.51060606060607</v>
       </c>
       <c r="M18" t="n">
-        <v>1273585.858585858</v>
+        <v>1287954.545454546</v>
       </c>
       <c r="N18" t="n">
-        <v>70.34747474747475</v>
+        <v>70.27575757575758</v>
       </c>
       <c r="O18" t="n">
-        <v>25.06424792139078</v>
+        <v>25.12013542013542</v>
       </c>
       <c r="P18" t="n">
-        <v>182.1354003139717</v>
+        <v>182.4552697302697</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.131577417291703</v>
+        <v>1.136639286639287</v>
       </c>
       <c r="R18" t="n">
-        <v>70.0292168149311</v>
+        <v>69.91116661116661</v>
       </c>
       <c r="S18" t="n">
-        <v>3060825.48403977</v>
+        <v>2937943.158693159</v>
       </c>
       <c r="T18" t="n">
-        <v>74.85582010582011</v>
+        <v>74.6719178969179</v>
       </c>
       <c r="U18" t="n">
-        <v>25.82098354320577</v>
+        <v>25.41676329842997</v>
       </c>
       <c r="V18" t="n">
-        <v>179.4209816726483</v>
+        <v>179.4409926647427</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>66.02912285245618</v>
+        <v>65.99645752395752</v>
       </c>
       <c r="Y18" t="n">
-        <v>1158056.215389549</v>
+        <v>1207054.982054982</v>
       </c>
       <c r="Z18" t="n">
-        <v>70.37074312518757</v>
+        <v>70.95946760030094</v>
       </c>
     </row>
     <row r="19">
@@ -1923,76 +1959,76 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>26.18441558441559</v>
+        <v>26.25909090909091</v>
       </c>
       <c r="D19" t="n">
-        <v>182.4324675324676</v>
+        <v>182.0827272727273</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="F19" t="n">
-        <v>80.58311688311689</v>
+        <v>80.78818181818183</v>
       </c>
       <c r="G19" t="n">
-        <v>35072207.79220779</v>
+        <v>35250545.45454545</v>
       </c>
       <c r="H19" t="n">
-        <v>82.4909090909091</v>
+        <v>82.58363636363637</v>
       </c>
       <c r="I19" t="n">
-        <v>26.24242424242424</v>
+        <v>26.23232323232323</v>
       </c>
       <c r="J19" t="n">
-        <v>184.4090909090909</v>
+        <v>184.4242424242424</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>67.10606060606061</v>
+        <v>67.01010101010101</v>
       </c>
       <c r="M19" t="n">
-        <v>1326515.151515152</v>
+        <v>1316919.191919192</v>
       </c>
       <c r="N19" t="n">
-        <v>70.63636363636364</v>
+        <v>70.52525252525253</v>
       </c>
       <c r="O19" t="n">
-        <v>24.70533731834042</v>
+        <v>24.99373612283829</v>
       </c>
       <c r="P19" t="n">
-        <v>180.9094669233988</v>
+        <v>180.8991268463791</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.512483861168072</v>
+        <v>1.552191083770031</v>
       </c>
       <c r="R19" t="n">
-        <v>75.60444132464256</v>
+        <v>75.91953749867837</v>
       </c>
       <c r="S19" t="n">
-        <v>15968914.05485639</v>
+        <v>15890858.88601852</v>
       </c>
       <c r="T19" t="n">
-        <v>79.08295471298568</v>
+        <v>79.21223496575664</v>
       </c>
       <c r="U19" t="n">
-        <v>24.67607030650509</v>
+        <v>24.87786770037978</v>
       </c>
       <c r="V19" t="n">
-        <v>183.4741928763668</v>
+        <v>183.4569136428073</v>
       </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>64.1912877782443</v>
+        <v>64.69145680942783</v>
       </c>
       <c r="Y19" t="n">
-        <v>1015003.267666311</v>
+        <v>1066359.031878839</v>
       </c>
       <c r="Z19" t="n">
-        <v>69.38707508272725</v>
+        <v>69.80983859582892</v>
       </c>
     </row>
     <row r="20">
@@ -2005,76 +2041,76 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.51038961038961</v>
+        <v>25.37727272727273</v>
       </c>
       <c r="D20" t="n">
-        <v>182.8454545454545</v>
+        <v>182.9618181818182</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>67.27142857142857</v>
+        <v>67.02000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1397662.337662338</v>
+        <v>1374063.636363636</v>
       </c>
       <c r="H20" t="n">
-        <v>71.24545454545455</v>
+        <v>71.12181818181818</v>
       </c>
       <c r="I20" t="n">
-        <v>24.83636363636364</v>
+        <v>24.88111888111888</v>
       </c>
       <c r="J20" t="n">
-        <v>184.9181818181818</v>
+        <v>184.7482517482517</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>69.95454545454545</v>
+        <v>69.98601398601399</v>
       </c>
       <c r="M20" t="n">
-        <v>2783863.636363636</v>
+        <v>2770104.895104895</v>
       </c>
       <c r="N20" t="n">
-        <v>74.59999999999999</v>
+        <v>74.62937062937064</v>
       </c>
       <c r="O20" t="n">
-        <v>23.49163402992381</v>
+        <v>23.76014382094667</v>
       </c>
       <c r="P20" t="n">
-        <v>182.0213416251058</v>
+        <v>182.3692724709074</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>63.81737753572194</v>
+        <v>64.16933094167203</v>
       </c>
       <c r="S20" t="n">
-        <v>1122069.114677355</v>
+        <v>1156315.046940815</v>
       </c>
       <c r="T20" t="n">
-        <v>70.9140947383451</v>
+        <v>71.03003298350824</v>
       </c>
       <c r="U20" t="n">
-        <v>25.77338461538462</v>
+        <v>25.91443786982249</v>
       </c>
       <c r="V20" t="n">
-        <v>181.8730769230769</v>
+        <v>181.7165142549758</v>
       </c>
       <c r="W20" t="n">
-        <v>1.035076923076923</v>
+        <v>1.042313071543841</v>
       </c>
       <c r="X20" t="n">
-        <v>67.49861538461539</v>
+        <v>67.57424421732115</v>
       </c>
       <c r="Y20" t="n">
-        <v>1620358.461538462</v>
+        <v>1616877.407208177</v>
       </c>
       <c r="Z20" t="n">
-        <v>72.28969230769231</v>
+        <v>72.17388918773534</v>
       </c>
     </row>
     <row r="21">
@@ -2087,76 +2123,76 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>24.73181818181818</v>
+        <v>24.68080808080808</v>
       </c>
       <c r="D21" t="n">
-        <v>185.019696969697</v>
+        <v>184.7545454545455</v>
       </c>
       <c r="E21" t="n">
-        <v>1.063636363636364</v>
+        <v>1.064646464646465</v>
       </c>
       <c r="F21" t="n">
-        <v>69.83636363636363</v>
+        <v>69.889898989899</v>
       </c>
       <c r="G21" t="n">
-        <v>2975833.333333333</v>
+        <v>3047020.202020202</v>
       </c>
       <c r="H21" t="n">
-        <v>75.5439393939394</v>
+        <v>75.58888888888889</v>
       </c>
       <c r="I21" t="n">
-        <v>26.11111111111111</v>
+        <v>26.21969696969697</v>
       </c>
       <c r="J21" t="n">
-        <v>183.4343434343435</v>
+        <v>183.0303030303031</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>70.31313131313131</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="M21" t="n">
-        <v>2490404.04040404</v>
+        <v>2521590.909090909</v>
       </c>
       <c r="N21" t="n">
-        <v>74.50505050505051</v>
+        <v>74.28030303030303</v>
       </c>
       <c r="O21" t="n">
-        <v>25.23322081836575</v>
+        <v>25.01872840882503</v>
       </c>
       <c r="P21" t="n">
-        <v>184.4230924067881</v>
+        <v>184.6624034848672</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.117838783599653</v>
+        <v>1.104200214707461</v>
       </c>
       <c r="R21" t="n">
-        <v>68.38258443783806</v>
+        <v>68.39180842864418</v>
       </c>
       <c r="S21" t="n">
-        <v>2260378.02190429</v>
+        <v>2332025.518876364</v>
       </c>
       <c r="T21" t="n">
-        <v>73.27418297617572</v>
+        <v>73.50330147129665</v>
       </c>
       <c r="U21" t="n">
-        <v>25.71167953535103</v>
+        <v>25.43375965151327</v>
       </c>
       <c r="V21" t="n">
-        <v>181.7177680746521</v>
+        <v>182.39419025352</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>68.69204102839369</v>
+        <v>68.43747212931994</v>
       </c>
       <c r="Y21" t="n">
-        <v>2048259.5018374</v>
+        <v>1973982.049217556</v>
       </c>
       <c r="Z21" t="n">
-        <v>73.30221795559959</v>
+        <v>73.31346902225526</v>
       </c>
     </row>
     <row r="22">
@@ -2169,76 +2205,76 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>23.68961038961039</v>
+        <v>23.65545454545454</v>
       </c>
       <c r="D22" t="n">
-        <v>184.1142857142857</v>
+        <v>184.2072727272727</v>
       </c>
       <c r="E22" t="n">
-        <v>1.148051948051948</v>
+        <v>1.149090909090909</v>
       </c>
       <c r="F22" t="n">
-        <v>68.29870129870129</v>
+        <v>68.15454545454546</v>
       </c>
       <c r="G22" t="n">
-        <v>2328506.493506494</v>
+        <v>2220181.818181818</v>
       </c>
       <c r="H22" t="n">
-        <v>75.29740259740258</v>
+        <v>75.17181818181817</v>
       </c>
       <c r="I22" t="n">
-        <v>25.95555555555556</v>
+        <v>25.67037037037037</v>
       </c>
       <c r="J22" t="n">
-        <v>181.0648148148148</v>
+        <v>181.4456790123457</v>
       </c>
       <c r="K22" t="n">
-        <v>1.051851851851852</v>
+        <v>1.045679012345679</v>
       </c>
       <c r="L22" t="n">
-        <v>71.02962962962964</v>
+        <v>70.95432098765433</v>
       </c>
       <c r="M22" t="n">
-        <v>3338935.185185185</v>
+        <v>3293703.703703704</v>
       </c>
       <c r="N22" t="n">
-        <v>73.29814814814814</v>
+        <v>73.51481481481481</v>
       </c>
       <c r="O22" t="n">
-        <v>24.62027326332751</v>
+        <v>24.85835795099592</v>
       </c>
       <c r="P22" t="n">
-        <v>183.9102464080158</v>
+        <v>183.359672485611</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.162651656332309</v>
+        <v>1.16718949276595</v>
       </c>
       <c r="R22" t="n">
-        <v>68.53894288748768</v>
+        <v>68.75142668790804</v>
       </c>
       <c r="S22" t="n">
-        <v>2391602.765864311</v>
+        <v>2496013.602771684</v>
       </c>
       <c r="T22" t="n">
-        <v>75.09786588460416</v>
+        <v>74.88350611922291</v>
       </c>
       <c r="U22" t="n">
-        <v>26.42016144349478</v>
+        <v>26.03937376990517</v>
       </c>
       <c r="V22" t="n">
-        <v>183.3278822412156</v>
+        <v>183.3066870363489</v>
       </c>
       <c r="W22" t="n">
-        <v>1.264577397910731</v>
+        <v>1.219601690133091</v>
       </c>
       <c r="X22" t="n">
-        <v>70.08405508072174</v>
+        <v>69.62724802840745</v>
       </c>
       <c r="Y22" t="n">
-        <v>2746374.45394112</v>
+        <v>2557524.612907222</v>
       </c>
       <c r="Z22" t="n">
-        <v>72.65479582146249</v>
+        <v>72.58290323024623</v>
       </c>
     </row>
     <row r="23">
@@ -2251,76 +2287,76 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>25.77922077922078</v>
+        <v>25.79545454545455</v>
       </c>
       <c r="D23" t="n">
-        <v>186.4</v>
+        <v>186.23</v>
       </c>
       <c r="E23" t="n">
-        <v>1.225974025974026</v>
+        <v>1.248181818181818</v>
       </c>
       <c r="F23" t="n">
-        <v>76.05454545454545</v>
+        <v>76.07818181818182</v>
       </c>
       <c r="G23" t="n">
-        <v>13493376.62337662</v>
+        <v>13460363.63636364</v>
       </c>
       <c r="H23" t="n">
-        <v>79.3987012987013</v>
+        <v>79.36909090909091</v>
       </c>
       <c r="I23" t="n">
-        <v>26.1969696969697</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="J23" t="n">
-        <v>182.7878787878788</v>
+        <v>182.0606060606061</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>68.07575757575758</v>
+        <v>67.94949494949496</v>
       </c>
       <c r="M23" t="n">
-        <v>1400757.575757576</v>
+        <v>1391161.616161616</v>
       </c>
       <c r="N23" t="n">
-        <v>71.33333333333333</v>
+        <v>71.27272727272728</v>
       </c>
       <c r="O23" t="n">
-        <v>25.10075684978936</v>
+        <v>24.94636711542671</v>
       </c>
       <c r="P23" t="n">
-        <v>184.6815733071538</v>
+        <v>185.0591305860463</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.22042159766618</v>
+        <v>1.193529568127091</v>
       </c>
       <c r="R23" t="n">
-        <v>72.04932010284178</v>
+        <v>72.03887250992901</v>
       </c>
       <c r="S23" t="n">
-        <v>5788223.678626155</v>
+        <v>5762901.734058855</v>
       </c>
       <c r="T23" t="n">
-        <v>75.75028893535087</v>
+        <v>76.01139701973294</v>
       </c>
       <c r="U23" t="n">
-        <v>24.05353276353277</v>
+        <v>24.32992719214942</v>
       </c>
       <c r="V23" t="n">
-        <v>182.0722317188984</v>
+        <v>182.1738271604938</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>66.81969610636277</v>
+        <v>66.95798670465336</v>
       </c>
       <c r="Y23" t="n">
-        <v>1479275.166191833</v>
+        <v>1478218.106995885</v>
       </c>
       <c r="Z23" t="n">
-        <v>72.92555555555556</v>
+        <v>72.8115606204495</v>
       </c>
     </row>
     <row r="24">
@@ -2333,76 +2369,76 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>24.1038961038961</v>
+        <v>24.04636363636363</v>
       </c>
       <c r="D24" t="n">
-        <v>184.6883116883117</v>
+        <v>184.7945454545455</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>70.97402597402598</v>
+        <v>71.14181818181819</v>
       </c>
       <c r="G24" t="n">
-        <v>4262337.662337663</v>
+        <v>4415181.818181818</v>
       </c>
       <c r="H24" t="n">
-        <v>76.32467532467533</v>
+        <v>76.64727272727274</v>
       </c>
       <c r="I24" t="n">
-        <v>25.76666666666667</v>
+        <v>25.81414141414142</v>
       </c>
       <c r="J24" t="n">
-        <v>181.4166666666667</v>
+        <v>182.3282828282828</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>1.02020202020202</v>
       </c>
       <c r="L24" t="n">
-        <v>67.48333333333333</v>
+        <v>67.42323232323233</v>
       </c>
       <c r="M24" t="n">
-        <v>1530416.666666667</v>
+        <v>1496035.353535354</v>
       </c>
       <c r="N24" t="n">
-        <v>71.95</v>
+        <v>71.88585858585857</v>
       </c>
       <c r="O24" t="n">
-        <v>23.11903957556132</v>
+        <v>23.17223981249468</v>
       </c>
       <c r="P24" t="n">
-        <v>184.7916149872672</v>
+        <v>184.6098602019891</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>67.45391022021457</v>
+        <v>67.55594103200924</v>
       </c>
       <c r="S24" t="n">
-        <v>2546674.661892053</v>
+        <v>2545997.034019897</v>
       </c>
       <c r="T24" t="n">
-        <v>74.78012225294833</v>
+        <v>74.75548996577857</v>
       </c>
       <c r="U24" t="n">
-        <v>26.51497712164379</v>
+        <v>26.59254885032663</v>
       </c>
       <c r="V24" t="n">
-        <v>181.952375032375</v>
+        <v>181.4586773720107</v>
       </c>
       <c r="W24" t="n">
-        <v>1.120953120953121</v>
+        <v>1.12371233704567</v>
       </c>
       <c r="X24" t="n">
-        <v>66.77504964171631</v>
+        <v>66.87789634234079</v>
       </c>
       <c r="Y24" t="n">
-        <v>1358160.191660192</v>
+        <v>1377551.238884572</v>
       </c>
       <c r="Z24" t="n">
-        <v>70.61306138306138</v>
+        <v>70.74887852887852</v>
       </c>
     </row>
     <row r="25">
@@ -2415,22 +2451,22 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>23.94805194805195</v>
+        <v>24.06363636363636</v>
       </c>
       <c r="D25" t="n">
-        <v>184.7662337662337</v>
+        <v>184.6545454545455</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>71.97402597402598</v>
+        <v>72.15454545454546</v>
       </c>
       <c r="G25" t="n">
-        <v>5398051.948051949</v>
+        <v>5452272.727272728</v>
       </c>
       <c r="H25" t="n">
-        <v>77.83116883116884</v>
+        <v>77.78181818181818</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -2439,22 +2475,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>23.30908309082222</v>
+        <v>23.36307449072667</v>
       </c>
       <c r="P25" t="n">
-        <v>183.3037849107414</v>
+        <v>182.6972344177562</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.073890457368718</v>
+        <v>1.08224931590149</v>
       </c>
       <c r="R25" t="n">
-        <v>67.99492941840768</v>
+        <v>68.24991669200365</v>
       </c>
       <c r="S25" t="n">
-        <v>2511074.729618208</v>
+        <v>2627385.177865612</v>
       </c>
       <c r="T25" t="n">
-        <v>74.56220127698388</v>
+        <v>74.82169534813013</v>
       </c>
       <c r="U25" t="n">
         <v>29</v>
@@ -2485,76 +2521,76 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>25.81471861471862</v>
+        <v>25.84030303030303</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3487734487734</v>
+        <v>184.9241414141414</v>
       </c>
       <c r="E26" t="n">
-        <v>1.33030303030303</v>
+        <v>1.321212121212121</v>
       </c>
       <c r="F26" t="n">
-        <v>71.23838383838384</v>
+        <v>71.34686868686867</v>
       </c>
       <c r="G26" t="n">
-        <v>3140707.070707071</v>
+        <v>3189494.94949495</v>
       </c>
       <c r="H26" t="n">
-        <v>76.56637806637806</v>
+        <v>76.55646464646466</v>
       </c>
       <c r="I26" t="n">
-        <v>25.73888888888889</v>
+        <v>26.05308641975309</v>
       </c>
       <c r="J26" t="n">
-        <v>183.3111111111111</v>
+        <v>183.1037037037037</v>
       </c>
       <c r="K26" t="n">
-        <v>1.105555555555555</v>
+        <v>1.104938271604938</v>
       </c>
       <c r="L26" t="n">
-        <v>68.40555555555555</v>
+        <v>68.59876543209877</v>
       </c>
       <c r="M26" t="n">
-        <v>1680231.481481481</v>
+        <v>1671203.703703704</v>
       </c>
       <c r="N26" t="n">
-        <v>72.52222222222223</v>
+        <v>72.31358024691357</v>
       </c>
       <c r="O26" t="n">
-        <v>24.74489655511328</v>
+        <v>24.9063176984694</v>
       </c>
       <c r="P26" t="n">
-        <v>183.581002014841</v>
+        <v>183.9865548902422</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.191335692171605</v>
+        <v>1.236407511992651</v>
       </c>
       <c r="R26" t="n">
-        <v>69.99214310285518</v>
+        <v>70.10686280936126</v>
       </c>
       <c r="S26" t="n">
-        <v>3188339.623568725</v>
+        <v>3172913.743824115</v>
       </c>
       <c r="T26" t="n">
-        <v>75.9262460071748</v>
+        <v>75.84113777278793</v>
       </c>
       <c r="U26" t="n">
-        <v>24.0771164021164</v>
+        <v>23.9060405643739</v>
       </c>
       <c r="V26" t="n">
-        <v>184.4344907407408</v>
+        <v>184.3540123456791</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>64.64804894179895</v>
+        <v>64.02879188712522</v>
       </c>
       <c r="Y26" t="n">
-        <v>1181832.837301587</v>
+        <v>1099708.002645503</v>
       </c>
       <c r="Z26" t="n">
-        <v>71.0891865079365</v>
+        <v>70.74927248677248</v>
       </c>
     </row>
     <row r="27">
@@ -2567,22 +2603,22 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>25.16883116883117</v>
+        <v>25.43636363636364</v>
       </c>
       <c r="D27" t="n">
-        <v>184.1688311688311</v>
+        <v>184.3818181818181</v>
       </c>
       <c r="E27" t="n">
-        <v>1.194805194805195</v>
+        <v>1.209090909090909</v>
       </c>
       <c r="F27" t="n">
-        <v>72.1038961038961</v>
+        <v>72.18181818181817</v>
       </c>
       <c r="G27" t="n">
-        <v>3715584.415584415</v>
+        <v>3650000</v>
       </c>
       <c r="H27" t="n">
-        <v>76</v>
+        <v>75.73636363636363</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2591,22 +2627,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>26.03209458849853</v>
+        <v>25.81782430213465</v>
       </c>
       <c r="P27" t="n">
-        <v>183.2602555080387</v>
+        <v>183.1474308450171</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.165195149677908</v>
+        <v>1.136724137931035</v>
       </c>
       <c r="R27" t="n">
-        <v>70.11228188888286</v>
+        <v>70.13735063786788</v>
       </c>
       <c r="S27" t="n">
-        <v>2659948.519460835</v>
+        <v>2714007.06707086</v>
       </c>
       <c r="T27" t="n">
-        <v>74.10430628484816</v>
+        <v>74.33269609700645</v>
       </c>
       <c r="U27" t="n">
         <v>21.4</v>
@@ -2637,76 +2673,76 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>25.51038961038961</v>
+        <v>25.37727272727273</v>
       </c>
       <c r="D28" t="n">
-        <v>182.8454545454545</v>
+        <v>182.9618181818182</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>67.27142857142857</v>
+        <v>67.02000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>1397662.337662338</v>
+        <v>1374063.636363636</v>
       </c>
       <c r="H28" t="n">
-        <v>71.24545454545455</v>
+        <v>71.12181818181818</v>
       </c>
       <c r="I28" t="n">
-        <v>26.11111111111111</v>
+        <v>26.21969696969697</v>
       </c>
       <c r="J28" t="n">
-        <v>183.4343434343435</v>
+        <v>183.0303030303031</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>70.31313131313131</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="M28" t="n">
-        <v>2490404.04040404</v>
+        <v>2521590.909090909</v>
       </c>
       <c r="N28" t="n">
-        <v>74.50505050505051</v>
+        <v>74.28030303030303</v>
       </c>
       <c r="O28" t="n">
-        <v>23.49163402992381</v>
+        <v>23.76014382094667</v>
       </c>
       <c r="P28" t="n">
-        <v>182.0213416251058</v>
+        <v>182.3692724709074</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>63.81737753572194</v>
+        <v>64.16933094167203</v>
       </c>
       <c r="S28" t="n">
-        <v>1122069.114677355</v>
+        <v>1156315.046940815</v>
       </c>
       <c r="T28" t="n">
-        <v>70.9140947383451</v>
+        <v>71.03003298350824</v>
       </c>
       <c r="U28" t="n">
-        <v>25.71167953535103</v>
+        <v>25.43375965151327</v>
       </c>
       <c r="V28" t="n">
-        <v>181.7177680746521</v>
+        <v>182.39419025352</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>68.69204102839369</v>
+        <v>68.43747212931994</v>
       </c>
       <c r="Y28" t="n">
-        <v>2048259.5018374</v>
+        <v>1973982.049217556</v>
       </c>
       <c r="Z28" t="n">
-        <v>73.30221795559959</v>
+        <v>73.31346902225526</v>
       </c>
     </row>
     <row r="29">
@@ -2719,22 +2755,22 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>27.79040404040404</v>
+        <v>27.94095500459137</v>
       </c>
       <c r="D29" t="n">
-        <v>180.6546717171717</v>
+        <v>181.1100091827365</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>67.53737373737374</v>
+        <v>67.58916437098256</v>
       </c>
       <c r="G29" t="n">
         <v>1260000</v>
       </c>
       <c r="H29" t="n">
-        <v>69.83118686868687</v>
+        <v>69.78053259871443</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2743,22 +2779,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>25.10873973852235</v>
+        <v>25.29041653998176</v>
       </c>
       <c r="P29" t="n">
-        <v>178.3820519154758</v>
+        <v>178.724201608668</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>64.90591783216783</v>
+        <v>65.12331932889245</v>
       </c>
       <c r="S29" t="n">
-        <v>1252055.211817168</v>
+        <v>1261750.334448161</v>
       </c>
       <c r="T29" t="n">
-        <v>69.53118881118883</v>
+        <v>69.63060946958181</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2777,76 +2813,76 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>25.76666666666667</v>
+        <v>25.81414141414142</v>
       </c>
       <c r="D30" t="n">
-        <v>181.4166666666667</v>
+        <v>182.3282828282828</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>1.02020202020202</v>
       </c>
       <c r="F30" t="n">
-        <v>67.48333333333333</v>
+        <v>67.42323232323233</v>
       </c>
       <c r="G30" t="n">
-        <v>1530416.666666667</v>
+        <v>1496035.353535354</v>
       </c>
       <c r="H30" t="n">
-        <v>71.95</v>
+        <v>71.88585858585857</v>
       </c>
       <c r="I30" t="n">
-        <v>25.73888888888889</v>
+        <v>26.05308641975309</v>
       </c>
       <c r="J30" t="n">
-        <v>183.3111111111111</v>
+        <v>183.1037037037037</v>
       </c>
       <c r="K30" t="n">
-        <v>1.105555555555555</v>
+        <v>1.104938271604938</v>
       </c>
       <c r="L30" t="n">
-        <v>68.40555555555555</v>
+        <v>68.59876543209877</v>
       </c>
       <c r="M30" t="n">
-        <v>1680231.481481481</v>
+        <v>1671203.703703704</v>
       </c>
       <c r="N30" t="n">
-        <v>72.52222222222223</v>
+        <v>72.31358024691357</v>
       </c>
       <c r="O30" t="n">
-        <v>26.51497712164379</v>
+        <v>26.59254885032663</v>
       </c>
       <c r="P30" t="n">
-        <v>181.952375032375</v>
+        <v>181.4586773720107</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.120953120953121</v>
+        <v>1.12371233704567</v>
       </c>
       <c r="R30" t="n">
-        <v>66.77504964171631</v>
+        <v>66.87789634234079</v>
       </c>
       <c r="S30" t="n">
-        <v>1358160.191660192</v>
+        <v>1377551.238884572</v>
       </c>
       <c r="T30" t="n">
-        <v>70.61306138306138</v>
+        <v>70.74887852887852</v>
       </c>
       <c r="U30" t="n">
-        <v>24.0771164021164</v>
+        <v>23.9060405643739</v>
       </c>
       <c r="V30" t="n">
-        <v>184.4344907407408</v>
+        <v>184.3540123456791</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>64.64804894179895</v>
+        <v>64.02879188712522</v>
       </c>
       <c r="Y30" t="n">
-        <v>1181832.837301587</v>
+        <v>1099708.002645503</v>
       </c>
       <c r="Z30" t="n">
-        <v>71.0891865079365</v>
+        <v>70.74927248677248</v>
       </c>
     </row>
     <row r="31">
@@ -2859,76 +2895,76 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>25.81471861471862</v>
+        <v>25.84030303030303</v>
       </c>
       <c r="D31" t="n">
-        <v>185.3487734487734</v>
+        <v>184.9241414141414</v>
       </c>
       <c r="E31" t="n">
-        <v>1.33030303030303</v>
+        <v>1.321212121212121</v>
       </c>
       <c r="F31" t="n">
-        <v>71.23838383838384</v>
+        <v>71.34686868686867</v>
       </c>
       <c r="G31" t="n">
-        <v>3140707.070707071</v>
+        <v>3189494.94949495</v>
       </c>
       <c r="H31" t="n">
-        <v>76.56637806637806</v>
+        <v>76.55646464646466</v>
       </c>
       <c r="I31" t="n">
-        <v>25.2</v>
+        <v>25.98888888888889</v>
       </c>
       <c r="J31" t="n">
-        <v>183.6740740740741</v>
+        <v>183.9160493827161</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>66.58703703703704</v>
+        <v>66.70246913580246</v>
       </c>
       <c r="M31" t="n">
-        <v>1224768.518518518</v>
+        <v>1163734.567901235</v>
       </c>
       <c r="N31" t="n">
-        <v>70.55185185185185</v>
+        <v>69.93456790123456</v>
       </c>
       <c r="O31" t="n">
-        <v>24.74489655511328</v>
+        <v>24.9063176984694</v>
       </c>
       <c r="P31" t="n">
-        <v>183.581002014841</v>
+        <v>183.9865548902422</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.191335692171605</v>
+        <v>1.236407511992651</v>
       </c>
       <c r="R31" t="n">
-        <v>69.99214310285518</v>
+        <v>70.10686280936126</v>
       </c>
       <c r="S31" t="n">
-        <v>3188339.623568725</v>
+        <v>3172913.743824115</v>
       </c>
       <c r="T31" t="n">
-        <v>75.9262460071748</v>
+        <v>75.84113777278793</v>
       </c>
       <c r="U31" t="n">
-        <v>24.87493987493987</v>
+        <v>24.9553835053835</v>
       </c>
       <c r="V31" t="n">
-        <v>183.4552068302069</v>
+        <v>183.5819352869353</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>64.39673520923522</v>
+        <v>64.83978238428239</v>
       </c>
       <c r="Y31" t="n">
-        <v>1007061.988936989</v>
+        <v>1063629.955599956</v>
       </c>
       <c r="Z31" t="n">
-        <v>69.19237012987013</v>
+        <v>69.44951998001997</v>
       </c>
     </row>
     <row r="32">
@@ -2941,76 +2977,76 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>28.75</v>
+        <v>29.05</v>
       </c>
       <c r="D32" t="n">
-        <v>183.4833333333333</v>
+        <v>183.48</v>
       </c>
       <c r="E32" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="F32" t="n">
-        <v>67.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>1041250</v>
+        <v>1046900</v>
       </c>
       <c r="H32" t="n">
-        <v>69.95</v>
+        <v>70.05</v>
       </c>
       <c r="I32" t="n">
-        <v>26.24242424242424</v>
+        <v>26.23232323232323</v>
       </c>
       <c r="J32" t="n">
-        <v>184.4090909090909</v>
+        <v>184.4242424242424</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>67.10606060606061</v>
+        <v>67.01010101010101</v>
       </c>
       <c r="M32" t="n">
-        <v>1326515.151515152</v>
+        <v>1316919.191919192</v>
       </c>
       <c r="N32" t="n">
-        <v>70.63636363636364</v>
+        <v>70.52525252525253</v>
       </c>
       <c r="O32" t="n">
-        <v>25.29765554493816</v>
+        <v>25.04514799646493</v>
       </c>
       <c r="P32" t="n">
-        <v>185.003876089021</v>
+        <v>184.9832177320941</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.028537585602803</v>
+        <v>1.028826255065386</v>
       </c>
       <c r="R32" t="n">
-        <v>65.28115322680542</v>
+        <v>65.20242186697106</v>
       </c>
       <c r="S32" t="n">
-        <v>1006235.443468233</v>
+        <v>1015413.10730015</v>
       </c>
       <c r="T32" t="n">
-        <v>68.66067815705496</v>
+        <v>68.91709411734125</v>
       </c>
       <c r="U32" t="n">
-        <v>24.67607030650509</v>
+        <v>24.87786770037978</v>
       </c>
       <c r="V32" t="n">
-        <v>183.4741928763668</v>
+        <v>183.4569136428073</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>64.1912877782443</v>
+        <v>64.69145680942783</v>
       </c>
       <c r="Y32" t="n">
-        <v>1015003.267666311</v>
+        <v>1066359.031878839</v>
       </c>
       <c r="Z32" t="n">
-        <v>69.38707508272725</v>
+        <v>69.80983859582892</v>
       </c>
     </row>
     <row r="33">
@@ -3023,76 +3059,76 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>26.76363636363637</v>
+        <v>26.95909090909091</v>
       </c>
       <c r="D33" t="n">
-        <v>181.659595959596</v>
+        <v>181.5780303030303</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>67.35757575757576</v>
+        <v>67.51060606060607</v>
       </c>
       <c r="G33" t="n">
-        <v>1273585.858585858</v>
+        <v>1287954.545454546</v>
       </c>
       <c r="H33" t="n">
-        <v>70.34747474747475</v>
+        <v>70.27575757575758</v>
       </c>
       <c r="I33" t="n">
-        <v>25.61428571428572</v>
+        <v>25.87107438016529</v>
       </c>
       <c r="J33" t="n">
-        <v>187.1350649350649</v>
+        <v>186.6884297520661</v>
       </c>
       <c r="K33" t="n">
-        <v>1.206493506493507</v>
+        <v>1.227272727272727</v>
       </c>
       <c r="L33" t="n">
-        <v>73.09090909090909</v>
+        <v>73.19669421487605</v>
       </c>
       <c r="M33" t="n">
-        <v>5204350.64935065</v>
+        <v>5316033.05785124</v>
       </c>
       <c r="N33" t="n">
-        <v>77.32987012987012</v>
+        <v>76.90082644628099</v>
       </c>
       <c r="O33" t="n">
-        <v>25.82098354320577</v>
+        <v>25.41676329842997</v>
       </c>
       <c r="P33" t="n">
-        <v>179.4209816726483</v>
+        <v>179.4409926647427</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>66.02912285245618</v>
+        <v>65.99645752395752</v>
       </c>
       <c r="S33" t="n">
-        <v>1158056.215389549</v>
+        <v>1207054.982054982</v>
       </c>
       <c r="T33" t="n">
-        <v>70.37074312518757</v>
+        <v>70.95946760030094</v>
       </c>
       <c r="U33" t="n">
-        <v>24.13351906856619</v>
+        <v>23.99010501991761</v>
       </c>
       <c r="V33" t="n">
-        <v>184.803806672453</v>
+        <v>184.8949125465017</v>
       </c>
       <c r="W33" t="n">
-        <v>1.131562492781169</v>
+        <v>1.126287715837941</v>
       </c>
       <c r="X33" t="n">
-        <v>70.74169880479262</v>
+        <v>70.65821696516599</v>
       </c>
       <c r="Y33" t="n">
-        <v>3987255.490691773</v>
+        <v>3979469.669205801</v>
       </c>
       <c r="Z33" t="n">
-        <v>77.17005063794633</v>
+        <v>77.3441520173979</v>
       </c>
     </row>
     <row r="34">
@@ -3151,76 +3187,76 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>26.1969696969697</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="D35" t="n">
-        <v>182.7878787878788</v>
+        <v>182.0606060606061</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>68.07575757575758</v>
+        <v>67.94949494949496</v>
       </c>
       <c r="G35" t="n">
-        <v>1400757.575757576</v>
+        <v>1391161.616161616</v>
       </c>
       <c r="H35" t="n">
-        <v>71.33333333333333</v>
+        <v>71.27272727272728</v>
       </c>
       <c r="I35" t="n">
-        <v>26.95424242424243</v>
+        <v>26.87179487179488</v>
       </c>
       <c r="J35" t="n">
-        <v>185.3758585858586</v>
+        <v>185.6597513597513</v>
       </c>
       <c r="K35" t="n">
-        <v>1.083636363636364</v>
+        <v>1.086713286713287</v>
       </c>
       <c r="L35" t="n">
-        <v>69.25010101010102</v>
+        <v>69.51756021756022</v>
       </c>
       <c r="M35" t="n">
-        <v>1925252.525252525</v>
+        <v>1987466.977466978</v>
       </c>
       <c r="N35" t="n">
-        <v>72.48222222222223</v>
+        <v>72.81709401709402</v>
       </c>
       <c r="O35" t="n">
-        <v>24.05353276353277</v>
+        <v>24.32992719214942</v>
       </c>
       <c r="P35" t="n">
-        <v>182.0722317188984</v>
+        <v>182.1738271604938</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>66.81969610636277</v>
+        <v>66.95798670465336</v>
       </c>
       <c r="S35" t="n">
-        <v>1479275.166191833</v>
+        <v>1478218.106995885</v>
       </c>
       <c r="T35" t="n">
-        <v>72.92555555555556</v>
+        <v>72.8115606204495</v>
       </c>
       <c r="U35" t="n">
-        <v>27.38291407867495</v>
+        <v>27.25943223443224</v>
       </c>
       <c r="V35" t="n">
-        <v>185.4870387728214</v>
+        <v>185.3515125454256</v>
       </c>
       <c r="W35" t="n">
-        <v>1.1271259175607</v>
+        <v>1.130397863006559</v>
       </c>
       <c r="X35" t="n">
-        <v>69.98390090344438</v>
+        <v>69.87794495359714</v>
       </c>
       <c r="Y35" t="n">
-        <v>2094229.387822323</v>
+        <v>2098139.105459758</v>
       </c>
       <c r="Z35" t="n">
-        <v>73.07276736307172</v>
+        <v>73.09123130492695</v>
       </c>
     </row>
     <row r="36">
@@ -3233,76 +3269,76 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>24.1038961038961</v>
+        <v>24.04636363636363</v>
       </c>
       <c r="D36" t="n">
-        <v>184.6883116883117</v>
+        <v>184.7945454545455</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>70.97402597402598</v>
+        <v>71.14181818181819</v>
       </c>
       <c r="G36" t="n">
-        <v>4262337.662337663</v>
+        <v>4415181.818181818</v>
       </c>
       <c r="H36" t="n">
-        <v>76.32467532467533</v>
+        <v>76.64727272727274</v>
       </c>
       <c r="I36" t="n">
-        <v>23.68961038961039</v>
+        <v>23.65545454545454</v>
       </c>
       <c r="J36" t="n">
-        <v>184.1142857142857</v>
+        <v>184.2072727272727</v>
       </c>
       <c r="K36" t="n">
-        <v>1.148051948051948</v>
+        <v>1.149090909090909</v>
       </c>
       <c r="L36" t="n">
-        <v>68.29870129870129</v>
+        <v>68.15454545454546</v>
       </c>
       <c r="M36" t="n">
-        <v>2328506.493506494</v>
+        <v>2220181.818181818</v>
       </c>
       <c r="N36" t="n">
-        <v>75.29740259740258</v>
+        <v>75.17181818181817</v>
       </c>
       <c r="O36" t="n">
-        <v>23.11903957556132</v>
+        <v>23.17223981249468</v>
       </c>
       <c r="P36" t="n">
-        <v>184.7916149872672</v>
+        <v>184.6098602019891</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>67.45391022021457</v>
+        <v>67.55594103200924</v>
       </c>
       <c r="S36" t="n">
-        <v>2546674.661892053</v>
+        <v>2545997.034019897</v>
       </c>
       <c r="T36" t="n">
-        <v>74.78012225294833</v>
+        <v>74.75548996577857</v>
       </c>
       <c r="U36" t="n">
-        <v>24.62027326332751</v>
+        <v>24.85835795099592</v>
       </c>
       <c r="V36" t="n">
-        <v>183.9102464080158</v>
+        <v>183.359672485611</v>
       </c>
       <c r="W36" t="n">
-        <v>1.162651656332309</v>
+        <v>1.16718949276595</v>
       </c>
       <c r="X36" t="n">
-        <v>68.53894288748768</v>
+        <v>68.75142668790804</v>
       </c>
       <c r="Y36" t="n">
-        <v>2391602.765864311</v>
+        <v>2496013.602771684</v>
       </c>
       <c r="Z36" t="n">
-        <v>75.09786588460416</v>
+        <v>74.88350611922291</v>
       </c>
     </row>
     <row r="37">
@@ -3315,22 +3351,22 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>26.01060606060606</v>
+        <v>26.02636363636363</v>
       </c>
       <c r="D37" t="n">
-        <v>184.1075757575757</v>
+        <v>184.4520454545454</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>65.63939393939394</v>
+        <v>65.35113636363636</v>
       </c>
       <c r="G37" t="n">
-        <v>1166545.454545454</v>
+        <v>1097702.272727273</v>
       </c>
       <c r="H37" t="n">
-        <v>68.98333333333333</v>
+        <v>68.89749999999999</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -3339,22 +3375,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>26.18196457326892</v>
+        <v>25.99042874396135</v>
       </c>
       <c r="P37" t="n">
-        <v>182.4396135265701</v>
+        <v>182.1929347826087</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>64.31696188942566</v>
+        <v>64.02976046698873</v>
       </c>
       <c r="S37" t="n">
-        <v>1003643.317230274</v>
+        <v>1002673.169825344</v>
       </c>
       <c r="T37" t="n">
-        <v>68.0107353730542</v>
+        <v>67.88176173665303</v>
       </c>
       <c r="U37" t="n">
         <v>29</v>
@@ -3385,76 +3421,614 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>26.24242424242424</v>
+        <v>26.23232323232323</v>
       </c>
       <c r="D38" t="n">
-        <v>184.4090909090909</v>
+        <v>184.4242424242424</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>67.10606060606061</v>
+        <v>67.01010101010101</v>
       </c>
       <c r="G38" t="n">
-        <v>1326515.151515152</v>
+        <v>1316919.191919192</v>
       </c>
       <c r="H38" t="n">
-        <v>70.63636363636364</v>
+        <v>70.52525252525253</v>
       </c>
       <c r="I38" t="n">
-        <v>27.79040404040404</v>
+        <v>27.94095500459137</v>
       </c>
       <c r="J38" t="n">
-        <v>180.6546717171717</v>
+        <v>181.1100091827365</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>67.53737373737374</v>
+        <v>67.58916437098256</v>
       </c>
       <c r="M38" t="n">
         <v>1260000</v>
       </c>
       <c r="N38" t="n">
-        <v>69.83118686868687</v>
+        <v>69.78053259871443</v>
       </c>
       <c r="O38" t="n">
-        <v>24.67607030650509</v>
+        <v>24.87786770037978</v>
       </c>
       <c r="P38" t="n">
-        <v>183.4741928763668</v>
+        <v>183.4569136428073</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>64.1912877782443</v>
+        <v>64.69145680942783</v>
       </c>
       <c r="S38" t="n">
-        <v>1015003.267666311</v>
+        <v>1066359.031878839</v>
       </c>
       <c r="T38" t="n">
-        <v>69.38707508272725</v>
+        <v>69.80983859582892</v>
       </c>
       <c r="U38" t="n">
-        <v>25.10873973852235</v>
+        <v>25.29041653998176</v>
       </c>
       <c r="V38" t="n">
-        <v>178.3820519154758</v>
+        <v>178.724201608668</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>64.90591783216783</v>
+        <v>65.12331932889245</v>
       </c>
       <c r="Y38" t="n">
-        <v>1252055.211817168</v>
+        <v>1261750.334448161</v>
       </c>
       <c r="Z38" t="n">
-        <v>69.53118881118883</v>
+        <v>69.63060946958181</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="D39" t="n">
+        <v>183.48</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F39" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1046900</v>
+      </c>
+      <c r="H39" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="I39" t="n">
+        <v>25.84030303030303</v>
+      </c>
+      <c r="J39" t="n">
+        <v>184.9241414141414</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.321212121212121</v>
+      </c>
+      <c r="L39" t="n">
+        <v>71.34686868686867</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3189494.94949495</v>
+      </c>
+      <c r="N39" t="n">
+        <v>76.55646464646466</v>
+      </c>
+      <c r="O39" t="n">
+        <v>25.04514799646493</v>
+      </c>
+      <c r="P39" t="n">
+        <v>184.9832177320941</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.028826255065386</v>
+      </c>
+      <c r="R39" t="n">
+        <v>65.20242186697106</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1015413.10730015</v>
+      </c>
+      <c r="T39" t="n">
+        <v>68.91709411734125</v>
+      </c>
+      <c r="U39" t="n">
+        <v>24.9063176984694</v>
+      </c>
+      <c r="V39" t="n">
+        <v>183.9865548902422</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.236407511992651</v>
+      </c>
+      <c r="X39" t="n">
+        <v>70.10686280936126</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>3172913.743824115</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>75.84113777278793</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>25.37727272727273</v>
+      </c>
+      <c r="D40" t="n">
+        <v>182.9618181818182</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>67.02000000000001</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1374063.636363636</v>
+      </c>
+      <c r="H40" t="n">
+        <v>71.12181818181818</v>
+      </c>
+      <c r="I40" t="n">
+        <v>25.98888888888889</v>
+      </c>
+      <c r="J40" t="n">
+        <v>183.9160493827161</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>66.70246913580246</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1163734.567901235</v>
+      </c>
+      <c r="N40" t="n">
+        <v>69.93456790123456</v>
+      </c>
+      <c r="O40" t="n">
+        <v>23.76014382094667</v>
+      </c>
+      <c r="P40" t="n">
+        <v>182.3692724709074</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>64.16933094167203</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1156315.046940815</v>
+      </c>
+      <c r="T40" t="n">
+        <v>71.03003298350824</v>
+      </c>
+      <c r="U40" t="n">
+        <v>24.9553835053835</v>
+      </c>
+      <c r="V40" t="n">
+        <v>183.5819352869353</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>64.83978238428239</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1063629.955599956</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>69.44951998001997</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>26.87179487179488</v>
+      </c>
+      <c r="D41" t="n">
+        <v>185.6597513597513</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.086713286713287</v>
+      </c>
+      <c r="F41" t="n">
+        <v>69.51756021756022</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1987466.977466978</v>
+      </c>
+      <c r="H41" t="n">
+        <v>72.81709401709402</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>27.25943223443224</v>
+      </c>
+      <c r="P41" t="n">
+        <v>185.3515125454256</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.130397863006559</v>
+      </c>
+      <c r="R41" t="n">
+        <v>69.87794495359714</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2098139.105459758</v>
+      </c>
+      <c r="T41" t="n">
+        <v>73.09123130492695</v>
+      </c>
+      <c r="U41" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>775000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>25.81414141414142</v>
+      </c>
+      <c r="D42" t="n">
+        <v>182.3282828282828</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.02020202020202</v>
+      </c>
+      <c r="F42" t="n">
+        <v>67.42323232323233</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1496035.353535354</v>
+      </c>
+      <c r="H42" t="n">
+        <v>71.88585858585857</v>
+      </c>
+      <c r="I42" t="n">
+        <v>26.21969696969697</v>
+      </c>
+      <c r="J42" t="n">
+        <v>183.0303030303031</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2521590.909090909</v>
+      </c>
+      <c r="N42" t="n">
+        <v>74.28030303030303</v>
+      </c>
+      <c r="O42" t="n">
+        <v>26.59254885032663</v>
+      </c>
+      <c r="P42" t="n">
+        <v>181.4586773720107</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.12371233704567</v>
+      </c>
+      <c r="R42" t="n">
+        <v>66.87789634234079</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1377551.238884572</v>
+      </c>
+      <c r="T42" t="n">
+        <v>70.74887852887852</v>
+      </c>
+      <c r="U42" t="n">
+        <v>25.43375965151327</v>
+      </c>
+      <c r="V42" t="n">
+        <v>182.39419025352</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>68.43747212931994</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1973982.049217556</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>73.31346902225526</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>23.65545454545454</v>
+      </c>
+      <c r="D43" t="n">
+        <v>184.2072727272727</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.149090909090909</v>
+      </c>
+      <c r="F43" t="n">
+        <v>68.15454545454546</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2220181.818181818</v>
+      </c>
+      <c r="H43" t="n">
+        <v>75.17181818181817</v>
+      </c>
+      <c r="I43" t="n">
+        <v>26.02636363636363</v>
+      </c>
+      <c r="J43" t="n">
+        <v>184.4520454545454</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>65.35113636363636</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1097702.272727273</v>
+      </c>
+      <c r="N43" t="n">
+        <v>68.89749999999999</v>
+      </c>
+      <c r="O43" t="n">
+        <v>24.85835795099592</v>
+      </c>
+      <c r="P43" t="n">
+        <v>183.359672485611</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.16718949276595</v>
+      </c>
+      <c r="R43" t="n">
+        <v>68.75142668790804</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2496013.602771684</v>
+      </c>
+      <c r="T43" t="n">
+        <v>74.88350611922291</v>
+      </c>
+      <c r="U43" t="n">
+        <v>25.99042874396135</v>
+      </c>
+      <c r="V43" t="n">
+        <v>182.1929347826087</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>64.02976046698873</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1002673.169825344</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>67.88176173665303</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>25.87107438016529</v>
+      </c>
+      <c r="D44" t="n">
+        <v>186.6884297520661</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.227272727272727</v>
+      </c>
+      <c r="F44" t="n">
+        <v>73.19669421487605</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5316033.05785124</v>
+      </c>
+      <c r="H44" t="n">
+        <v>76.90082644628099</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>23.99010501991761</v>
+      </c>
+      <c r="P44" t="n">
+        <v>184.8949125465017</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.126287715837941</v>
+      </c>
+      <c r="R44" t="n">
+        <v>70.65821696516599</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3979469.669205801</v>
+      </c>
+      <c r="T44" t="n">
+        <v>77.3441520173979</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>26.05308641975309</v>
+      </c>
+      <c r="D45" t="n">
+        <v>183.1037037037037</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.104938271604938</v>
+      </c>
+      <c r="F45" t="n">
+        <v>68.59876543209877</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1671203.703703704</v>
+      </c>
+      <c r="H45" t="n">
+        <v>72.31358024691357</v>
+      </c>
+      <c r="I45" t="n">
+        <v>24.04636363636363</v>
+      </c>
+      <c r="J45" t="n">
+        <v>184.7945454545455</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>71.14181818181819</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4415181.818181818</v>
+      </c>
+      <c r="N45" t="n">
+        <v>76.64727272727274</v>
+      </c>
+      <c r="O45" t="n">
+        <v>23.9060405643739</v>
+      </c>
+      <c r="P45" t="n">
+        <v>184.3540123456791</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>64.02879188712522</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1099708.002645503</v>
+      </c>
+      <c r="T45" t="n">
+        <v>70.74927248677248</v>
+      </c>
+      <c r="U45" t="n">
+        <v>23.17223981249468</v>
+      </c>
+      <c r="V45" t="n">
+        <v>184.6098602019891</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>67.55594103200924</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2545997.034019897</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>74.75548996577857</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:Z53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,2067 +558,2079 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.10330578512397</v>
+        <v>23.99090909090909</v>
       </c>
       <c r="D2" t="n">
-        <v>184.1545454545455</v>
+        <v>184.4034090909091</v>
       </c>
       <c r="E2" t="n">
-        <v>1.179338842975207</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>73.0900826446281</v>
+        <v>72.03295454545454</v>
       </c>
       <c r="G2" t="n">
-        <v>6146074.38016529</v>
+        <v>5426136.363636364</v>
       </c>
       <c r="H2" t="n">
-        <v>77.47685950413224</v>
+        <v>77.85113636363637</v>
       </c>
       <c r="I2" t="n">
-        <v>28.00818181818182</v>
+        <v>25.85384615384616</v>
       </c>
       <c r="J2" t="n">
-        <v>182.9309090909091</v>
+        <v>187.1951048951049</v>
       </c>
       <c r="K2" t="n">
-        <v>2.413636363636364</v>
+        <v>1.53986013986014</v>
       </c>
       <c r="L2" t="n">
-        <v>82.88454545454546</v>
+        <v>78.30699300699301</v>
       </c>
       <c r="M2" t="n">
-        <v>40085454.54545455</v>
+        <v>19034965.03496503</v>
       </c>
       <c r="N2" t="n">
-        <v>84.66454545454545</v>
+        <v>81.62307692307692</v>
       </c>
       <c r="O2" t="n">
-        <v>26.53778329513624</v>
+        <v>23.18731691496909</v>
       </c>
       <c r="P2" t="n">
-        <v>184.9579220779221</v>
+        <v>182.6795576500794</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.40827731092437</v>
+        <v>1.068612952265126</v>
       </c>
       <c r="R2" t="n">
-        <v>70.29345811051694</v>
+        <v>68.0595126515996</v>
       </c>
       <c r="S2" t="n">
-        <v>3627757.830404889</v>
+        <v>2617965.985946421</v>
       </c>
       <c r="T2" t="n">
-        <v>74.07986121721416</v>
+        <v>74.82927110570589</v>
       </c>
       <c r="U2" t="n">
-        <v>27.10158309001788</v>
+        <v>25.48735967179111</v>
       </c>
       <c r="V2" t="n">
-        <v>182.5357371404763</v>
+        <v>186.6171936263909</v>
       </c>
       <c r="W2" t="n">
-        <v>1.885667641537206</v>
+        <v>1.383031383951117</v>
       </c>
       <c r="X2" t="n">
-        <v>78.98572182246096</v>
+        <v>74.97006947777851</v>
       </c>
       <c r="Y2" t="n">
-        <v>24084349.68895838</v>
+        <v>13449298.17531038</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.47697790132572</v>
+        <v>78.82860246714762</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24.68080808080808</v>
+        <v>25.75936447811448</v>
       </c>
       <c r="D3" t="n">
-        <v>184.7545454545455</v>
+        <v>186.4296085858586</v>
       </c>
       <c r="E3" t="n">
-        <v>1.064646464646465</v>
+        <v>1.787563131313131</v>
       </c>
       <c r="F3" t="n">
-        <v>69.889898989899</v>
+        <v>80.33617424242424</v>
       </c>
       <c r="G3" t="n">
-        <v>3047020.202020202</v>
+        <v>30082302.18855219</v>
       </c>
       <c r="H3" t="n">
-        <v>75.58888888888889</v>
+        <v>83.87657828282829</v>
       </c>
       <c r="I3" t="n">
-        <v>26.26590909090909</v>
+        <v>25.71666666666667</v>
       </c>
       <c r="J3" t="n">
-        <v>183.5416666666667</v>
+        <v>181.3263888888889</v>
       </c>
       <c r="K3" t="n">
-        <v>1.634848484848485</v>
+        <v>1.038888888888889</v>
       </c>
       <c r="L3" t="n">
-        <v>76.4189393939394</v>
+        <v>71.03611111111113</v>
       </c>
       <c r="M3" t="n">
-        <v>12592348.48484849</v>
+        <v>3400729.166666667</v>
       </c>
       <c r="N3" t="n">
-        <v>79.57878787878788</v>
+        <v>73.52916666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>25.01872840882503</v>
+        <v>24.81977107211375</v>
       </c>
       <c r="P3" t="n">
-        <v>184.6624034848672</v>
+        <v>183.8750023389612</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.104200214707461</v>
+        <v>1.764742901390499</v>
       </c>
       <c r="R3" t="n">
-        <v>68.39180842864418</v>
+        <v>76.17271600856554</v>
       </c>
       <c r="S3" t="n">
-        <v>2332025.518876364</v>
+        <v>15638052.60495607</v>
       </c>
       <c r="T3" t="n">
-        <v>73.50330147129665</v>
+        <v>81.50353834052633</v>
       </c>
       <c r="U3" t="n">
-        <v>25.14070103428836</v>
+        <v>26.47920688365132</v>
       </c>
       <c r="V3" t="n">
-        <v>181.8332528326614</v>
+        <v>183.6007142651587</v>
       </c>
       <c r="W3" t="n">
-        <v>1.562596304468099</v>
+        <v>1.250343894788339</v>
       </c>
       <c r="X3" t="n">
-        <v>74.70471546367799</v>
+        <v>69.93445048778382</v>
       </c>
       <c r="Y3" t="n">
-        <v>11574638.97422393</v>
+        <v>2705492.333592333</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.13637043187968</v>
+        <v>72.48474776252553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.3460606060606</v>
+        <v>24.48717171717172</v>
       </c>
       <c r="D4" t="n">
-        <v>184.4126262626263</v>
+        <v>184.8768686868687</v>
       </c>
       <c r="E4" t="n">
-        <v>1.808484848484849</v>
+        <v>1.058181818181818</v>
       </c>
       <c r="F4" t="n">
-        <v>80.61474747474747</v>
+        <v>69.75646464646465</v>
       </c>
       <c r="G4" t="n">
-        <v>35162540.40404041</v>
+        <v>2982873.737373737</v>
       </c>
       <c r="H4" t="n">
-        <v>84.22222222222221</v>
+        <v>75.54333333333332</v>
       </c>
       <c r="I4" t="n">
-        <v>25.79545454545455</v>
+        <v>25.31878787878788</v>
       </c>
       <c r="J4" t="n">
-        <v>186.23</v>
+        <v>184.3144444444445</v>
       </c>
       <c r="K4" t="n">
-        <v>1.248181818181818</v>
+        <v>1.781212121212121</v>
       </c>
       <c r="L4" t="n">
-        <v>76.07818181818182</v>
+        <v>80.50020202020202</v>
       </c>
       <c r="M4" t="n">
-        <v>13460363.63636364</v>
+        <v>34390267.67676768</v>
       </c>
       <c r="N4" t="n">
-        <v>79.36909090909091</v>
+        <v>84.09676767676768</v>
       </c>
       <c r="O4" t="n">
-        <v>24.4168428978429</v>
+        <v>24.72831439896657</v>
       </c>
       <c r="P4" t="n">
-        <v>184.8154782254782</v>
+        <v>184.0096923607794</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.532947903947904</v>
+        <v>1.107739422413336</v>
       </c>
       <c r="R4" t="n">
-        <v>76.26987382987383</v>
+        <v>68.11976407248146</v>
       </c>
       <c r="S4" t="n">
-        <v>21156981.46113146</v>
+        <v>2367220.084364106</v>
       </c>
       <c r="T4" t="n">
-        <v>82.05887016687015</v>
+        <v>73.63034033197076</v>
       </c>
       <c r="U4" t="n">
-        <v>24.94636711542671</v>
+        <v>24.15642184521132</v>
       </c>
       <c r="V4" t="n">
-        <v>185.0591305860463</v>
+        <v>184.4817940149519</v>
       </c>
       <c r="W4" t="n">
-        <v>1.193529568127091</v>
+        <v>1.521579482895272</v>
       </c>
       <c r="X4" t="n">
-        <v>72.03887250992901</v>
+        <v>76.40987382987383</v>
       </c>
       <c r="Y4" t="n">
-        <v>5762901.734058855</v>
+        <v>22494439.3558683</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.01139701973294</v>
+        <v>82.2719227984491</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.53636363636364</v>
+        <v>24.94214876033058</v>
       </c>
       <c r="D5" t="n">
-        <v>183.9090909090909</v>
+        <v>186.5454545454545</v>
       </c>
       <c r="E5" t="n">
-        <v>1.045454545454545</v>
+        <v>1.041322314049587</v>
       </c>
       <c r="F5" t="n">
-        <v>72.48181818181817</v>
+        <v>73.32231404958678</v>
       </c>
       <c r="G5" t="n">
-        <v>4577272.727272728</v>
+        <v>5104958.67768595</v>
       </c>
       <c r="H5" t="n">
-        <v>76.06363636363636</v>
+        <v>77.13223140495869</v>
       </c>
       <c r="I5" t="n">
-        <v>25.48760330578513</v>
+        <v>26.67390572390572</v>
       </c>
       <c r="J5" t="n">
-        <v>183.7950413223141</v>
+        <v>183.8352693602693</v>
       </c>
       <c r="K5" t="n">
-        <v>1.36198347107438</v>
+        <v>1.721464646464646</v>
       </c>
       <c r="L5" t="n">
-        <v>73.41983471074379</v>
+        <v>77.52996632996633</v>
       </c>
       <c r="M5" t="n">
-        <v>7316859.504132232</v>
+        <v>18239831.64983165</v>
       </c>
       <c r="N5" t="n">
-        <v>77.64545454545454</v>
+        <v>79.89006734006735</v>
       </c>
       <c r="O5" t="n">
-        <v>25.12013542013542</v>
+        <v>25.4026541882558</v>
       </c>
       <c r="P5" t="n">
-        <v>182.4552697302697</v>
+        <v>183.0104600351125</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.136639286639287</v>
+        <v>1.07102466903269</v>
       </c>
       <c r="R5" t="n">
-        <v>69.91116661116661</v>
+        <v>70.91299251154867</v>
       </c>
       <c r="S5" t="n">
-        <v>2937943.158693159</v>
+        <v>3252643.011276701</v>
       </c>
       <c r="T5" t="n">
-        <v>74.6719178969179</v>
+        <v>74.80333207246309</v>
       </c>
       <c r="U5" t="n">
-        <v>25.56330433656521</v>
+        <v>26.29710258435945</v>
       </c>
       <c r="V5" t="n">
-        <v>182.3016826571175</v>
+        <v>182.2940931668764</v>
       </c>
       <c r="W5" t="n">
-        <v>1.272028872898438</v>
+        <v>1.760422899310199</v>
       </c>
       <c r="X5" t="n">
-        <v>71.5465527065527</v>
+        <v>76.40353739668672</v>
       </c>
       <c r="Y5" t="n">
-        <v>4293361.070290417</v>
+        <v>15881867.18092167</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.73273949078296</v>
+        <v>79.52748934259232</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.55454545454545</v>
+        <v>27.96272727272727</v>
       </c>
       <c r="D6" t="n">
-        <v>185.3</v>
+        <v>183.0218181818182</v>
       </c>
       <c r="E6" t="n">
-        <v>1.263636363636364</v>
+        <v>2.395454545454546</v>
       </c>
       <c r="F6" t="n">
-        <v>75.06363636363636</v>
+        <v>82.8209090909091</v>
       </c>
       <c r="G6" t="n">
-        <v>11195681.81818182</v>
+        <v>39894545.45454545</v>
       </c>
       <c r="H6" t="n">
-        <v>79.68181818181819</v>
+        <v>84.67363636363636</v>
       </c>
       <c r="I6" t="n">
-        <v>25.00826446280992</v>
+        <v>23.99090909090909</v>
       </c>
       <c r="J6" t="n">
-        <v>186.603305785124</v>
+        <v>184.4034090909091</v>
       </c>
       <c r="K6" t="n">
-        <v>1.049586776859504</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>73.33884297520662</v>
+        <v>72.03295454545454</v>
       </c>
       <c r="M6" t="n">
-        <v>5136363.636363637</v>
+        <v>5426136.363636364</v>
       </c>
       <c r="N6" t="n">
-        <v>77.11570247933884</v>
+        <v>77.85113636363637</v>
       </c>
       <c r="O6" t="n">
-        <v>22.96644480934136</v>
+        <v>27.13419178567005</v>
       </c>
       <c r="P6" t="n">
-        <v>184.7342242291553</v>
+        <v>182.4003616464051</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.202148148148148</v>
+        <v>1.886655783829697</v>
       </c>
       <c r="R6" t="n">
-        <v>71.23520780879402</v>
+        <v>79.00864672364672</v>
       </c>
       <c r="S6" t="n">
-        <v>7029183.269476374</v>
+        <v>24048401.07235759</v>
       </c>
       <c r="T6" t="n">
-        <v>78.16315307425653</v>
+        <v>81.47243244678027</v>
       </c>
       <c r="U6" t="n">
-        <v>25.33426193236354</v>
+        <v>23.18731691496909</v>
       </c>
       <c r="V6" t="n">
-        <v>183.2899213145737</v>
+        <v>182.6795576500794</v>
       </c>
       <c r="W6" t="n">
-        <v>1.072076857584879</v>
+        <v>1.068612952265126</v>
       </c>
       <c r="X6" t="n">
-        <v>70.90836288191903</v>
+        <v>68.0595126515996</v>
       </c>
       <c r="Y6" t="n">
-        <v>3268867.758751449</v>
+        <v>2617965.985946421</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.88350884013985</v>
+        <v>74.82927110570589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>25.54132231404959</v>
       </c>
       <c r="D7" t="n">
-        <v>184.0545454545455</v>
+        <v>183.7297520661157</v>
       </c>
       <c r="E7" t="n">
-        <v>1.136363636363636</v>
+        <v>1.37603305785124</v>
       </c>
       <c r="F7" t="n">
-        <v>72.97272727272727</v>
+        <v>73.23388429752066</v>
       </c>
       <c r="G7" t="n">
-        <v>4746136.363636364</v>
+        <v>6951404.958677686</v>
       </c>
       <c r="H7" t="n">
-        <v>76.57272727272728</v>
+        <v>77.45537190082645</v>
       </c>
       <c r="I7" t="n">
-        <v>26.25909090909091</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="J7" t="n">
-        <v>182.0827272727273</v>
+        <v>184.2363636363637</v>
       </c>
       <c r="K7" t="n">
-        <v>1.71</v>
+        <v>1.207438016528926</v>
       </c>
       <c r="L7" t="n">
-        <v>80.78818181818183</v>
+        <v>73.02892561983471</v>
       </c>
       <c r="M7" t="n">
-        <v>35250545.45454545</v>
+        <v>5968553.719008264</v>
       </c>
       <c r="N7" t="n">
-        <v>82.58363636363637</v>
+        <v>77.41239669421488</v>
       </c>
       <c r="O7" t="n">
-        <v>24.15788461538461</v>
+        <v>25.67393444719531</v>
       </c>
       <c r="P7" t="n">
-        <v>182.8098575498576</v>
+        <v>182.1304464858813</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.040343915343915</v>
+        <v>1.283091883961449</v>
       </c>
       <c r="R7" t="n">
-        <v>70.6698310948311</v>
+        <v>71.61341177341177</v>
       </c>
       <c r="S7" t="n">
-        <v>3462158.781033781</v>
+        <v>4347172.999102348</v>
       </c>
       <c r="T7" t="n">
-        <v>75.41835673585675</v>
+        <v>76.64134939939287</v>
       </c>
       <c r="U7" t="n">
-        <v>24.99373612283829</v>
+        <v>26.57286350903998</v>
       </c>
       <c r="V7" t="n">
-        <v>180.8991268463791</v>
+        <v>184.7808097784569</v>
       </c>
       <c r="W7" t="n">
-        <v>1.552191083770031</v>
+        <v>1.389453781512605</v>
       </c>
       <c r="X7" t="n">
-        <v>75.91953749867837</v>
+        <v>70.33046345811053</v>
       </c>
       <c r="Y7" t="n">
-        <v>15890858.88601852</v>
+        <v>3512656.226126814</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.21223496575664</v>
+        <v>73.98766870384519</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.43636363636364</v>
+        <v>26.22237762237762</v>
       </c>
       <c r="D8" t="n">
-        <v>184.3818181818181</v>
+        <v>183.7076923076923</v>
       </c>
       <c r="E8" t="n">
-        <v>1.209090909090909</v>
+        <v>1.616783216783217</v>
       </c>
       <c r="F8" t="n">
-        <v>72.18181818181817</v>
+        <v>76.3944055944056</v>
       </c>
       <c r="G8" t="n">
-        <v>3650000</v>
+        <v>12678321.67832168</v>
       </c>
       <c r="H8" t="n">
-        <v>75.73636363636363</v>
+        <v>79.63426573426574</v>
       </c>
       <c r="I8" t="n">
-        <v>26.37363636363636</v>
+        <v>25.13492063492064</v>
       </c>
       <c r="J8" t="n">
-        <v>182.5881818181818</v>
+        <v>184.6316738816739</v>
       </c>
       <c r="K8" t="n">
-        <v>2.149090909090909</v>
+        <v>1.015079365079365</v>
       </c>
       <c r="L8" t="n">
-        <v>78.66636363636363</v>
+        <v>69.93658008658008</v>
       </c>
       <c r="M8" t="n">
-        <v>21377272.72727273</v>
+        <v>2656121.933621933</v>
       </c>
       <c r="N8" t="n">
-        <v>80.59636363636363</v>
+        <v>74.38225108225109</v>
       </c>
       <c r="O8" t="n">
-        <v>25.81782430213465</v>
+        <v>24.95155619948295</v>
       </c>
       <c r="P8" t="n">
-        <v>183.1474308450171</v>
+        <v>181.7271984189602</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.136724137931035</v>
+        <v>1.550788197131392</v>
       </c>
       <c r="R8" t="n">
-        <v>70.13735063786788</v>
+        <v>74.58407301542303</v>
       </c>
       <c r="S8" t="n">
-        <v>2714007.06707086</v>
+        <v>11541974.43774517</v>
       </c>
       <c r="T8" t="n">
-        <v>74.33269609700645</v>
+        <v>79.26224403502179</v>
       </c>
       <c r="U8" t="n">
-        <v>25.29662779111055</v>
+        <v>25.54059544465559</v>
       </c>
       <c r="V8" t="n">
-        <v>182.86790482506</v>
+        <v>181.8841578221277</v>
       </c>
       <c r="W8" t="n">
-        <v>1.962929490688111</v>
+        <v>1.040302855039698</v>
       </c>
       <c r="X8" t="n">
-        <v>76.04017371198407</v>
+        <v>67.40725249687657</v>
       </c>
       <c r="Y8" t="n">
-        <v>16401725.28875977</v>
+        <v>1621063.413278451</v>
       </c>
       <c r="Z8" t="n">
-        <v>80.38639920424403</v>
+        <v>72.34852959071004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.75723905723906</v>
+        <v>25.94132231404959</v>
       </c>
       <c r="D9" t="n">
-        <v>183.951936026936</v>
+        <v>186.0181818181818</v>
       </c>
       <c r="E9" t="n">
-        <v>1.738131313131313</v>
+        <v>1.26198347107438</v>
       </c>
       <c r="F9" t="n">
-        <v>77.496632996633</v>
+        <v>76.08925619834712</v>
       </c>
       <c r="G9" t="n">
-        <v>18198164.98316498</v>
+        <v>13144876.03305785</v>
       </c>
       <c r="H9" t="n">
-        <v>79.82340067340067</v>
+        <v>79.13553719008264</v>
       </c>
       <c r="I9" t="n">
-        <v>24.88111888111888</v>
+        <v>25.85384615384616</v>
       </c>
       <c r="J9" t="n">
-        <v>184.7482517482517</v>
+        <v>187.1951048951049</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>1.53986013986014</v>
       </c>
       <c r="L9" t="n">
-        <v>69.98601398601399</v>
+        <v>78.30699300699301</v>
       </c>
       <c r="M9" t="n">
-        <v>2770104.895104895</v>
+        <v>19034965.03496503</v>
       </c>
       <c r="N9" t="n">
-        <v>74.62937062937064</v>
+        <v>81.62307692307692</v>
       </c>
       <c r="O9" t="n">
-        <v>26.4445965457121</v>
+        <v>24.82488354555974</v>
       </c>
       <c r="P9" t="n">
-        <v>182.1903793987604</v>
+        <v>184.9848120595201</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.794692222981697</v>
+        <v>1.17376111239044</v>
       </c>
       <c r="R9" t="n">
-        <v>76.55374874934371</v>
+        <v>71.84112376935695</v>
       </c>
       <c r="S9" t="n">
-        <v>16200766.63744341</v>
+        <v>5778426.326308399</v>
       </c>
       <c r="T9" t="n">
-        <v>79.53111253099812</v>
+        <v>76.07582417191902</v>
       </c>
       <c r="U9" t="n">
-        <v>25.91443786982249</v>
+        <v>25.48735967179111</v>
       </c>
       <c r="V9" t="n">
-        <v>181.7165142549758</v>
+        <v>186.6171936263909</v>
       </c>
       <c r="W9" t="n">
-        <v>1.042313071543841</v>
+        <v>1.383031383951117</v>
       </c>
       <c r="X9" t="n">
-        <v>67.57424421732115</v>
+        <v>74.97006947777851</v>
       </c>
       <c r="Y9" t="n">
-        <v>1616877.407208177</v>
+        <v>13449298.17531038</v>
       </c>
       <c r="Z9" t="n">
-        <v>72.17388918773534</v>
+        <v>78.82860246714762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.06363636363636</v>
+        <v>26.06681818181818</v>
       </c>
       <c r="D10" t="n">
-        <v>184.6545454545455</v>
+        <v>182.2870454545455</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2.087727272727273</v>
       </c>
       <c r="F10" t="n">
-        <v>72.15454545454546</v>
+        <v>78.55727272727272</v>
       </c>
       <c r="G10" t="n">
-        <v>5452272.727272728</v>
+        <v>21251022.72727273</v>
       </c>
       <c r="H10" t="n">
-        <v>77.78181818181818</v>
+        <v>80.70545454545454</v>
       </c>
       <c r="I10" t="n">
-        <v>25.85384615384616</v>
+        <v>25.22148760330579</v>
       </c>
       <c r="J10" t="n">
-        <v>187.1951048951049</v>
+        <v>184.1404958677686</v>
       </c>
       <c r="K10" t="n">
-        <v>1.53986013986014</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="L10" t="n">
-        <v>78.30699300699301</v>
+        <v>72.12975206611571</v>
       </c>
       <c r="M10" t="n">
-        <v>19034965.03496503</v>
+        <v>4288842.975206612</v>
       </c>
       <c r="N10" t="n">
-        <v>81.62307692307692</v>
+        <v>76.1107438016529</v>
       </c>
       <c r="O10" t="n">
-        <v>23.36307449072667</v>
+        <v>25.34594552990198</v>
       </c>
       <c r="P10" t="n">
-        <v>182.6972344177562</v>
+        <v>182.7396397178475</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.08224931590149</v>
+        <v>1.963514286009749</v>
       </c>
       <c r="R10" t="n">
-        <v>68.24991669200365</v>
+        <v>76.28715226948893</v>
       </c>
       <c r="S10" t="n">
-        <v>2627385.177865612</v>
+        <v>17566886.10747322</v>
       </c>
       <c r="T10" t="n">
-        <v>74.82169534813013</v>
+        <v>80.59263702100816</v>
       </c>
       <c r="U10" t="n">
-        <v>25.48735967179111</v>
+        <v>24.8531746031746</v>
       </c>
       <c r="V10" t="n">
-        <v>186.6171936263909</v>
+        <v>182.0717010262465</v>
       </c>
       <c r="W10" t="n">
-        <v>1.383031383951117</v>
+        <v>1.113728022818932</v>
       </c>
       <c r="X10" t="n">
-        <v>74.97006947777851</v>
+        <v>69.58585606312879</v>
       </c>
       <c r="Y10" t="n">
-        <v>13449298.17531038</v>
+        <v>2894139.097434552</v>
       </c>
       <c r="Z10" t="n">
-        <v>78.82860246714762</v>
+        <v>74.7756734006734</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25.72659285159285</v>
+        <v>26.4198347107438</v>
       </c>
       <c r="D11" t="n">
-        <v>186.3965617715618</v>
+        <v>182.2107438016529</v>
       </c>
       <c r="E11" t="n">
-        <v>1.786810411810412</v>
+        <v>1.729752066115703</v>
       </c>
       <c r="F11" t="n">
-        <v>80.37869075369075</v>
+        <v>80.77355371900826</v>
       </c>
       <c r="G11" t="n">
-        <v>30229817.4048174</v>
+        <v>34887851.23966942</v>
       </c>
       <c r="H11" t="n">
-        <v>83.96299533799535</v>
+        <v>82.47272727272728</v>
       </c>
       <c r="I11" t="n">
-        <v>25.67037037037037</v>
+        <v>24.68181818181818</v>
       </c>
       <c r="J11" t="n">
-        <v>181.4456790123457</v>
+        <v>185.5181818181818</v>
       </c>
       <c r="K11" t="n">
-        <v>1.045679012345679</v>
+        <v>1.281818181818182</v>
       </c>
       <c r="L11" t="n">
-        <v>70.95432098765433</v>
+        <v>75.12727272727273</v>
       </c>
       <c r="M11" t="n">
-        <v>3293703.703703704</v>
+        <v>11041818.18181818</v>
       </c>
       <c r="N11" t="n">
-        <v>73.51481481481481</v>
+        <v>79.58181818181819</v>
       </c>
       <c r="O11" t="n">
-        <v>24.8135679461652</v>
+        <v>24.90901144856957</v>
       </c>
       <c r="P11" t="n">
-        <v>183.9314402861314</v>
+        <v>181.1425217320025</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76277271165143</v>
+        <v>1.512801672793229</v>
       </c>
       <c r="R11" t="n">
-        <v>76.16277464335816</v>
+        <v>75.79453752744634</v>
       </c>
       <c r="S11" t="n">
-        <v>15622918.12363838</v>
+        <v>15219224.27376779</v>
       </c>
       <c r="T11" t="n">
-        <v>81.49824943807782</v>
+        <v>79.08278045015309</v>
       </c>
       <c r="U11" t="n">
-        <v>26.03937376990517</v>
+        <v>23.0821855500821</v>
       </c>
       <c r="V11" t="n">
-        <v>183.3066870363489</v>
+        <v>184.6805205254516</v>
       </c>
       <c r="W11" t="n">
-        <v>1.219601690133091</v>
+        <v>1.202333333333333</v>
       </c>
       <c r="X11" t="n">
-        <v>69.62724802840745</v>
+        <v>71.2915041050903</v>
       </c>
       <c r="Y11" t="n">
-        <v>2557524.612907222</v>
+        <v>6950567.528735632</v>
       </c>
       <c r="Z11" t="n">
-        <v>72.58290323024623</v>
+        <v>78.0733382594417</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>24.68080808080808</v>
+        <v>25.34710743801653</v>
       </c>
       <c r="D12" t="n">
-        <v>184.7545454545455</v>
+        <v>184.4380165289256</v>
       </c>
       <c r="E12" t="n">
-        <v>1.064646464646465</v>
+        <v>1.173553719008265</v>
       </c>
       <c r="F12" t="n">
-        <v>69.889898989899</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="G12" t="n">
-        <v>3047020.202020202</v>
+        <v>3835330.578512396</v>
       </c>
       <c r="H12" t="n">
-        <v>75.58888888888889</v>
+        <v>75.84297520661157</v>
       </c>
       <c r="I12" t="n">
-        <v>25.3460606060606</v>
+        <v>25.71666666666667</v>
       </c>
       <c r="J12" t="n">
-        <v>184.4126262626263</v>
+        <v>181.3263888888889</v>
       </c>
       <c r="K12" t="n">
-        <v>1.808484848484849</v>
+        <v>1.038888888888889</v>
       </c>
       <c r="L12" t="n">
-        <v>80.61474747474747</v>
+        <v>71.03611111111113</v>
       </c>
       <c r="M12" t="n">
-        <v>35162540.40404041</v>
+        <v>3400729.166666667</v>
       </c>
       <c r="N12" t="n">
-        <v>84.22222222222221</v>
+        <v>73.52916666666667</v>
       </c>
       <c r="O12" t="n">
-        <v>25.01872840882503</v>
+        <v>25.769700414528</v>
       </c>
       <c r="P12" t="n">
-        <v>184.6624034848672</v>
+        <v>183.2808811877777</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.104200214707461</v>
+        <v>1.178140824692549</v>
       </c>
       <c r="R12" t="n">
-        <v>68.39180842864418</v>
+        <v>69.9454935868729</v>
       </c>
       <c r="S12" t="n">
-        <v>2332025.518876364</v>
+        <v>2704018.662372111</v>
       </c>
       <c r="T12" t="n">
-        <v>73.50330147129665</v>
+        <v>74.26468875951636</v>
       </c>
       <c r="U12" t="n">
-        <v>24.4168428978429</v>
+        <v>26.47920688365132</v>
       </c>
       <c r="V12" t="n">
-        <v>184.8154782254782</v>
+        <v>183.6007142651587</v>
       </c>
       <c r="W12" t="n">
-        <v>1.532947903947904</v>
+        <v>1.250343894788339</v>
       </c>
       <c r="X12" t="n">
-        <v>76.26987382987383</v>
+        <v>69.93445048778382</v>
       </c>
       <c r="Y12" t="n">
-        <v>21156981.46113146</v>
+        <v>2705492.333592333</v>
       </c>
       <c r="Z12" t="n">
-        <v>82.05887016687015</v>
+        <v>72.48474776252553</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>25.00826446280992</v>
+        <v>25.0446510560147</v>
       </c>
       <c r="D13" t="n">
-        <v>186.603305785124</v>
+        <v>184.2012167125804</v>
       </c>
       <c r="E13" t="n">
-        <v>1.049586776859504</v>
+        <v>1.140266299357209</v>
       </c>
       <c r="F13" t="n">
-        <v>73.33884297520662</v>
+        <v>73.0121671258035</v>
       </c>
       <c r="G13" t="n">
-        <v>5136363.636363637</v>
+        <v>4763096.877869605</v>
       </c>
       <c r="H13" t="n">
-        <v>77.11570247933884</v>
+        <v>76.64267676767678</v>
       </c>
       <c r="I13" t="n">
-        <v>26.75723905723906</v>
+        <v>25.75936447811448</v>
       </c>
       <c r="J13" t="n">
-        <v>183.951936026936</v>
+        <v>186.4296085858586</v>
       </c>
       <c r="K13" t="n">
-        <v>1.738131313131313</v>
+        <v>1.787563131313131</v>
       </c>
       <c r="L13" t="n">
-        <v>77.496632996633</v>
+        <v>80.33617424242424</v>
       </c>
       <c r="M13" t="n">
-        <v>18198164.98316498</v>
+        <v>30082302.18855219</v>
       </c>
       <c r="N13" t="n">
-        <v>79.82340067340067</v>
+        <v>83.87657828282829</v>
       </c>
       <c r="O13" t="n">
-        <v>25.33426193236354</v>
+        <v>24.26546509046509</v>
       </c>
       <c r="P13" t="n">
-        <v>183.2899213145737</v>
+        <v>182.7177156177156</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.072076857584879</v>
+        <v>1.037638287638288</v>
       </c>
       <c r="R13" t="n">
-        <v>70.90836288191903</v>
+        <v>70.56276131276131</v>
       </c>
       <c r="S13" t="n">
-        <v>3268867.758751449</v>
+        <v>3403146.991896993</v>
       </c>
       <c r="T13" t="n">
-        <v>74.88350884013985</v>
+        <v>75.29687072187072</v>
       </c>
       <c r="U13" t="n">
-        <v>26.4445965457121</v>
+        <v>24.81977107211375</v>
       </c>
       <c r="V13" t="n">
-        <v>182.1903793987604</v>
+        <v>183.8750023389612</v>
       </c>
       <c r="W13" t="n">
-        <v>1.794692222981697</v>
+        <v>1.764742901390499</v>
       </c>
       <c r="X13" t="n">
-        <v>76.55374874934371</v>
+        <v>76.17271600856554</v>
       </c>
       <c r="Y13" t="n">
-        <v>16200766.63744341</v>
+        <v>15638052.60495607</v>
       </c>
       <c r="Z13" t="n">
-        <v>79.53111253099812</v>
+        <v>81.50353834052633</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>28.00818181818182</v>
+        <v>25.13492063492064</v>
       </c>
       <c r="D14" t="n">
-        <v>182.9309090909091</v>
+        <v>184.6316738816739</v>
       </c>
       <c r="E14" t="n">
-        <v>2.413636363636364</v>
+        <v>1.015079365079365</v>
       </c>
       <c r="F14" t="n">
-        <v>82.88454545454546</v>
+        <v>69.93658008658008</v>
       </c>
       <c r="G14" t="n">
-        <v>40085454.54545455</v>
+        <v>2656121.933621933</v>
       </c>
       <c r="H14" t="n">
-        <v>84.66454545454545</v>
+        <v>74.38225108225109</v>
       </c>
       <c r="I14" t="n">
-        <v>24.06363636363636</v>
+        <v>25.94132231404959</v>
       </c>
       <c r="J14" t="n">
-        <v>184.6545454545455</v>
+        <v>186.0181818181818</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.26198347107438</v>
       </c>
       <c r="L14" t="n">
-        <v>72.15454545454546</v>
+        <v>76.08925619834712</v>
       </c>
       <c r="M14" t="n">
-        <v>5452272.727272728</v>
+        <v>13144876.03305785</v>
       </c>
       <c r="N14" t="n">
-        <v>77.78181818181818</v>
+        <v>79.13553719008264</v>
       </c>
       <c r="O14" t="n">
-        <v>27.10158309001788</v>
+        <v>25.54059544465559</v>
       </c>
       <c r="P14" t="n">
-        <v>182.5357371404763</v>
+        <v>181.8841578221277</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.885667641537206</v>
+        <v>1.040302855039698</v>
       </c>
       <c r="R14" t="n">
-        <v>78.98572182246096</v>
+        <v>67.40725249687657</v>
       </c>
       <c r="S14" t="n">
-        <v>24084349.68895838</v>
+        <v>1621063.413278451</v>
       </c>
       <c r="T14" t="n">
-        <v>81.47697790132572</v>
+        <v>72.34852959071004</v>
       </c>
       <c r="U14" t="n">
-        <v>23.36307449072667</v>
+        <v>24.82488354555974</v>
       </c>
       <c r="V14" t="n">
-        <v>182.6972344177562</v>
+        <v>184.9848120595201</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08224931590149</v>
+        <v>1.17376111239044</v>
       </c>
       <c r="X14" t="n">
-        <v>68.24991669200365</v>
+        <v>71.84112376935695</v>
       </c>
       <c r="Y14" t="n">
-        <v>2627385.177865612</v>
+        <v>5778426.326308399</v>
       </c>
       <c r="Z14" t="n">
-        <v>74.82169534813013</v>
+        <v>76.07582417191902</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.48760330578513</v>
+        <v>27.96272727272727</v>
       </c>
       <c r="D15" t="n">
-        <v>183.7950413223141</v>
+        <v>183.0218181818182</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36198347107438</v>
+        <v>2.395454545454546</v>
       </c>
       <c r="F15" t="n">
-        <v>73.41983471074379</v>
+        <v>82.8209090909091</v>
       </c>
       <c r="G15" t="n">
-        <v>7316859.504132232</v>
+        <v>39894545.45454545</v>
       </c>
       <c r="H15" t="n">
-        <v>77.64545454545454</v>
+        <v>84.67363636363636</v>
       </c>
       <c r="I15" t="n">
-        <v>26.10330578512397</v>
+        <v>25.85384615384616</v>
       </c>
       <c r="J15" t="n">
-        <v>184.1545454545455</v>
+        <v>187.1951048951049</v>
       </c>
       <c r="K15" t="n">
-        <v>1.179338842975207</v>
+        <v>1.53986013986014</v>
       </c>
       <c r="L15" t="n">
-        <v>73.0900826446281</v>
+        <v>78.30699300699301</v>
       </c>
       <c r="M15" t="n">
-        <v>6146074.38016529</v>
+        <v>19034965.03496503</v>
       </c>
       <c r="N15" t="n">
-        <v>77.47685950413224</v>
+        <v>81.62307692307692</v>
       </c>
       <c r="O15" t="n">
-        <v>25.56330433656521</v>
+        <v>27.13419178567005</v>
       </c>
       <c r="P15" t="n">
-        <v>182.3016826571175</v>
+        <v>182.4003616464051</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.272028872898438</v>
+        <v>1.886655783829697</v>
       </c>
       <c r="R15" t="n">
-        <v>71.5465527065527</v>
+        <v>79.00864672364672</v>
       </c>
       <c r="S15" t="n">
-        <v>4293361.070290417</v>
+        <v>24048401.07235759</v>
       </c>
       <c r="T15" t="n">
-        <v>76.73273949078296</v>
+        <v>81.47243244678027</v>
       </c>
       <c r="U15" t="n">
-        <v>26.53778329513624</v>
+        <v>25.48735967179111</v>
       </c>
       <c r="V15" t="n">
-        <v>184.9579220779221</v>
+        <v>186.6171936263909</v>
       </c>
       <c r="W15" t="n">
-        <v>1.40827731092437</v>
+        <v>1.383031383951117</v>
       </c>
       <c r="X15" t="n">
-        <v>70.29345811051694</v>
+        <v>74.97006947777851</v>
       </c>
       <c r="Y15" t="n">
-        <v>3627757.830404889</v>
+        <v>13449298.17531038</v>
       </c>
       <c r="Z15" t="n">
-        <v>74.07986121721416</v>
+        <v>78.82860246714762</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>26.26590909090909</v>
+        <v>24.68181818181818</v>
       </c>
       <c r="D16" t="n">
-        <v>183.5416666666667</v>
+        <v>185.5181818181818</v>
       </c>
       <c r="E16" t="n">
-        <v>1.634848484848485</v>
+        <v>1.281818181818182</v>
       </c>
       <c r="F16" t="n">
-        <v>76.4189393939394</v>
+        <v>75.12727272727273</v>
       </c>
       <c r="G16" t="n">
-        <v>12592348.48484849</v>
+        <v>11041818.18181818</v>
       </c>
       <c r="H16" t="n">
-        <v>79.57878787878788</v>
+        <v>79.58181818181819</v>
       </c>
       <c r="I16" t="n">
-        <v>24.88111888111888</v>
+        <v>25.22148760330579</v>
       </c>
       <c r="J16" t="n">
-        <v>184.7482517482517</v>
+        <v>184.1404958677686</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="L16" t="n">
-        <v>69.98601398601399</v>
+        <v>72.12975206611571</v>
       </c>
       <c r="M16" t="n">
-        <v>2770104.895104895</v>
+        <v>4288842.975206612</v>
       </c>
       <c r="N16" t="n">
-        <v>74.62937062937064</v>
+        <v>76.1107438016529</v>
       </c>
       <c r="O16" t="n">
-        <v>25.14070103428836</v>
+        <v>23.0821855500821</v>
       </c>
       <c r="P16" t="n">
-        <v>181.8332528326614</v>
+        <v>184.6805205254516</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.562596304468099</v>
+        <v>1.202333333333333</v>
       </c>
       <c r="R16" t="n">
-        <v>74.70471546367799</v>
+        <v>71.2915041050903</v>
       </c>
       <c r="S16" t="n">
-        <v>11574638.97422393</v>
+        <v>6950567.528735632</v>
       </c>
       <c r="T16" t="n">
-        <v>79.13637043187968</v>
+        <v>78.0733382594417</v>
       </c>
       <c r="U16" t="n">
-        <v>25.91443786982249</v>
+        <v>24.8531746031746</v>
       </c>
       <c r="V16" t="n">
-        <v>181.7165142549758</v>
+        <v>182.0717010262465</v>
       </c>
       <c r="W16" t="n">
-        <v>1.042313071543841</v>
+        <v>1.113728022818932</v>
       </c>
       <c r="X16" t="n">
-        <v>67.57424421732115</v>
+        <v>69.58585606312879</v>
       </c>
       <c r="Y16" t="n">
-        <v>1616877.407208177</v>
+        <v>2894139.097434552</v>
       </c>
       <c r="Z16" t="n">
-        <v>72.17388918773534</v>
+        <v>74.7756734006734</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>25.79545454545455</v>
+        <v>23.99090909090909</v>
       </c>
       <c r="D17" t="n">
-        <v>186.23</v>
+        <v>184.4034090909091</v>
       </c>
       <c r="E17" t="n">
-        <v>1.248181818181818</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>76.07818181818182</v>
+        <v>72.03295454545454</v>
       </c>
       <c r="G17" t="n">
-        <v>13460363.63636364</v>
+        <v>5426136.363636364</v>
       </c>
       <c r="H17" t="n">
-        <v>79.36909090909091</v>
+        <v>77.85113636363637</v>
       </c>
       <c r="I17" t="n">
-        <v>25.85384615384616</v>
+        <v>25.34710743801653</v>
       </c>
       <c r="J17" t="n">
-        <v>187.1951048951049</v>
+        <v>184.4380165289256</v>
       </c>
       <c r="K17" t="n">
-        <v>1.53986013986014</v>
+        <v>1.173553719008265</v>
       </c>
       <c r="L17" t="n">
-        <v>78.30699300699301</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="M17" t="n">
-        <v>19034965.03496503</v>
+        <v>3835330.578512396</v>
       </c>
       <c r="N17" t="n">
-        <v>81.62307692307692</v>
+        <v>75.84297520661157</v>
       </c>
       <c r="O17" t="n">
-        <v>24.94636711542671</v>
+        <v>23.18731691496909</v>
       </c>
       <c r="P17" t="n">
-        <v>185.0591305860463</v>
+        <v>182.6795576500794</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.193529568127091</v>
+        <v>1.068612952265126</v>
       </c>
       <c r="R17" t="n">
-        <v>72.03887250992901</v>
+        <v>68.0595126515996</v>
       </c>
       <c r="S17" t="n">
-        <v>5762901.734058855</v>
+        <v>2617965.985946421</v>
       </c>
       <c r="T17" t="n">
-        <v>76.01139701973294</v>
+        <v>74.82927110570589</v>
       </c>
       <c r="U17" t="n">
-        <v>25.48735967179111</v>
+        <v>25.769700414528</v>
       </c>
       <c r="V17" t="n">
-        <v>186.6171936263909</v>
+        <v>183.2808811877777</v>
       </c>
       <c r="W17" t="n">
-        <v>1.383031383951117</v>
+        <v>1.178140824692549</v>
       </c>
       <c r="X17" t="n">
-        <v>74.97006947777851</v>
+        <v>69.9454935868729</v>
       </c>
       <c r="Y17" t="n">
-        <v>13449298.17531038</v>
+        <v>2704018.662372111</v>
       </c>
       <c r="Z17" t="n">
-        <v>78.82860246714762</v>
+        <v>74.26468875951636</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.53636363636364</v>
+        <v>26.67390572390572</v>
       </c>
       <c r="D18" t="n">
-        <v>183.9090909090909</v>
+        <v>183.8352693602693</v>
       </c>
       <c r="E18" t="n">
-        <v>1.045454545454545</v>
+        <v>1.721464646464646</v>
       </c>
       <c r="F18" t="n">
-        <v>72.48181818181817</v>
+        <v>77.52996632996633</v>
       </c>
       <c r="G18" t="n">
-        <v>4577272.727272728</v>
+        <v>18239831.64983165</v>
       </c>
       <c r="H18" t="n">
-        <v>76.06363636363636</v>
+        <v>79.89006734006735</v>
       </c>
       <c r="I18" t="n">
-        <v>26.95909090909091</v>
+        <v>25.31878787878788</v>
       </c>
       <c r="J18" t="n">
-        <v>181.5780303030303</v>
+        <v>184.3144444444445</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>1.781212121212121</v>
       </c>
       <c r="L18" t="n">
-        <v>67.51060606060607</v>
+        <v>80.50020202020202</v>
       </c>
       <c r="M18" t="n">
-        <v>1287954.545454546</v>
+        <v>34390267.67676768</v>
       </c>
       <c r="N18" t="n">
-        <v>70.27575757575758</v>
+        <v>84.09676767676768</v>
       </c>
       <c r="O18" t="n">
-        <v>25.12013542013542</v>
+        <v>26.29710258435945</v>
       </c>
       <c r="P18" t="n">
-        <v>182.4552697302697</v>
+        <v>182.2940931668764</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.136639286639287</v>
+        <v>1.760422899310199</v>
       </c>
       <c r="R18" t="n">
-        <v>69.91116661116661</v>
+        <v>76.40353739668672</v>
       </c>
       <c r="S18" t="n">
-        <v>2937943.158693159</v>
+        <v>15881867.18092167</v>
       </c>
       <c r="T18" t="n">
-        <v>74.6719178969179</v>
+        <v>79.52748934259232</v>
       </c>
       <c r="U18" t="n">
-        <v>25.41676329842997</v>
+        <v>24.15642184521132</v>
       </c>
       <c r="V18" t="n">
-        <v>179.4409926647427</v>
+        <v>184.4817940149519</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.521579482895272</v>
       </c>
       <c r="X18" t="n">
-        <v>65.99645752395752</v>
+        <v>76.40987382987383</v>
       </c>
       <c r="Y18" t="n">
-        <v>1207054.982054982</v>
+        <v>22494439.3558683</v>
       </c>
       <c r="Z18" t="n">
-        <v>70.95946760030094</v>
+        <v>82.2719227984491</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>26.25909090909091</v>
+        <v>26.4198347107438</v>
       </c>
       <c r="D19" t="n">
-        <v>182.0827272727273</v>
+        <v>182.2107438016529</v>
       </c>
       <c r="E19" t="n">
-        <v>1.71</v>
+        <v>1.729752066115703</v>
       </c>
       <c r="F19" t="n">
-        <v>80.78818181818183</v>
+        <v>80.77355371900826</v>
       </c>
       <c r="G19" t="n">
-        <v>35250545.45454545</v>
+        <v>34887851.23966942</v>
       </c>
       <c r="H19" t="n">
-        <v>82.58363636363637</v>
+        <v>82.47272727272728</v>
       </c>
       <c r="I19" t="n">
-        <v>26.23232323232323</v>
+        <v>24.48717171717172</v>
       </c>
       <c r="J19" t="n">
-        <v>184.4242424242424</v>
+        <v>184.8768686868687</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.058181818181818</v>
       </c>
       <c r="L19" t="n">
-        <v>67.01010101010101</v>
+        <v>69.75646464646465</v>
       </c>
       <c r="M19" t="n">
-        <v>1316919.191919192</v>
+        <v>2982873.737373737</v>
       </c>
       <c r="N19" t="n">
-        <v>70.52525252525253</v>
+        <v>75.54333333333332</v>
       </c>
       <c r="O19" t="n">
-        <v>24.99373612283829</v>
+        <v>24.90901144856957</v>
       </c>
       <c r="P19" t="n">
-        <v>180.8991268463791</v>
+        <v>181.1425217320025</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.552191083770031</v>
+        <v>1.512801672793229</v>
       </c>
       <c r="R19" t="n">
-        <v>75.91953749867837</v>
+        <v>75.79453752744634</v>
       </c>
       <c r="S19" t="n">
-        <v>15890858.88601852</v>
+        <v>15219224.27376779</v>
       </c>
       <c r="T19" t="n">
-        <v>79.21223496575664</v>
+        <v>79.08278045015309</v>
       </c>
       <c r="U19" t="n">
-        <v>24.87786770037978</v>
+        <v>24.72831439896657</v>
       </c>
       <c r="V19" t="n">
-        <v>183.4569136428073</v>
+        <v>184.0096923607794</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.107739422413336</v>
       </c>
       <c r="X19" t="n">
-        <v>64.69145680942783</v>
+        <v>68.11976407248146</v>
       </c>
       <c r="Y19" t="n">
-        <v>1066359.031878839</v>
+        <v>2367220.084364106</v>
       </c>
       <c r="Z19" t="n">
-        <v>69.80983859582892</v>
+        <v>73.63034033197076</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.37727272727273</v>
+        <v>26.22237762237762</v>
       </c>
       <c r="D20" t="n">
-        <v>182.9618181818182</v>
+        <v>183.7076923076923</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>1.616783216783217</v>
       </c>
       <c r="F20" t="n">
-        <v>67.02000000000001</v>
+        <v>76.3944055944056</v>
       </c>
       <c r="G20" t="n">
-        <v>1374063.636363636</v>
+        <v>12678321.67832168</v>
       </c>
       <c r="H20" t="n">
-        <v>71.12181818181818</v>
+        <v>79.63426573426574</v>
       </c>
       <c r="I20" t="n">
-        <v>24.88111888111888</v>
+        <v>25.54132231404959</v>
       </c>
       <c r="J20" t="n">
-        <v>184.7482517482517</v>
+        <v>183.7297520661157</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>1.37603305785124</v>
       </c>
       <c r="L20" t="n">
-        <v>69.98601398601399</v>
+        <v>73.23388429752066</v>
       </c>
       <c r="M20" t="n">
-        <v>2770104.895104895</v>
+        <v>6951404.958677686</v>
       </c>
       <c r="N20" t="n">
-        <v>74.62937062937064</v>
+        <v>77.45537190082645</v>
       </c>
       <c r="O20" t="n">
-        <v>23.76014382094667</v>
+        <v>24.95155619948295</v>
       </c>
       <c r="P20" t="n">
-        <v>182.3692724709074</v>
+        <v>181.7271984189602</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>1.550788197131392</v>
       </c>
       <c r="R20" t="n">
-        <v>64.16933094167203</v>
+        <v>74.58407301542303</v>
       </c>
       <c r="S20" t="n">
-        <v>1156315.046940815</v>
+        <v>11541974.43774517</v>
       </c>
       <c r="T20" t="n">
-        <v>71.03003298350824</v>
+        <v>79.26224403502179</v>
       </c>
       <c r="U20" t="n">
-        <v>25.91443786982249</v>
+        <v>25.67393444719531</v>
       </c>
       <c r="V20" t="n">
-        <v>181.7165142549758</v>
+        <v>182.1304464858813</v>
       </c>
       <c r="W20" t="n">
-        <v>1.042313071543841</v>
+        <v>1.283091883961449</v>
       </c>
       <c r="X20" t="n">
-        <v>67.57424421732115</v>
+        <v>71.61341177341177</v>
       </c>
       <c r="Y20" t="n">
-        <v>1616877.407208177</v>
+        <v>4347172.999102348</v>
       </c>
       <c r="Z20" t="n">
-        <v>72.17388918773534</v>
+        <v>76.64134939939287</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>24.68080808080808</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="D21" t="n">
-        <v>184.7545454545455</v>
+        <v>184.2363636363637</v>
       </c>
       <c r="E21" t="n">
-        <v>1.064646464646465</v>
+        <v>1.207438016528926</v>
       </c>
       <c r="F21" t="n">
-        <v>69.889898989899</v>
+        <v>73.02892561983471</v>
       </c>
       <c r="G21" t="n">
-        <v>3047020.202020202</v>
+        <v>5968553.719008264</v>
       </c>
       <c r="H21" t="n">
-        <v>75.58888888888889</v>
+        <v>77.41239669421488</v>
       </c>
       <c r="I21" t="n">
-        <v>26.21969696969697</v>
+        <v>25.0446510560147</v>
       </c>
       <c r="J21" t="n">
-        <v>183.0303030303031</v>
+        <v>184.2012167125804</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>1.140266299357209</v>
       </c>
       <c r="L21" t="n">
-        <v>70.45454545454545</v>
+        <v>73.0121671258035</v>
       </c>
       <c r="M21" t="n">
-        <v>2521590.909090909</v>
+        <v>4763096.877869605</v>
       </c>
       <c r="N21" t="n">
-        <v>74.28030303030303</v>
+        <v>76.64267676767678</v>
       </c>
       <c r="O21" t="n">
-        <v>25.01872840882503</v>
+        <v>26.57286350903998</v>
       </c>
       <c r="P21" t="n">
-        <v>184.6624034848672</v>
+        <v>184.7808097784569</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.104200214707461</v>
+        <v>1.389453781512605</v>
       </c>
       <c r="R21" t="n">
-        <v>68.39180842864418</v>
+        <v>70.33046345811053</v>
       </c>
       <c r="S21" t="n">
-        <v>2332025.518876364</v>
+        <v>3512656.226126814</v>
       </c>
       <c r="T21" t="n">
-        <v>73.50330147129665</v>
+        <v>73.98766870384519</v>
       </c>
       <c r="U21" t="n">
-        <v>25.43375965151327</v>
+        <v>24.26546509046509</v>
       </c>
       <c r="V21" t="n">
-        <v>182.39419025352</v>
+        <v>182.7177156177156</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.037638287638288</v>
       </c>
       <c r="X21" t="n">
-        <v>68.43747212931994</v>
+        <v>70.56276131276131</v>
       </c>
       <c r="Y21" t="n">
-        <v>1973982.049217556</v>
+        <v>3403146.991896993</v>
       </c>
       <c r="Z21" t="n">
-        <v>73.31346902225526</v>
+        <v>75.29687072187072</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>23.65545454545454</v>
+        <v>25.75936447811448</v>
       </c>
       <c r="D22" t="n">
-        <v>184.2072727272727</v>
+        <v>186.4296085858586</v>
       </c>
       <c r="E22" t="n">
-        <v>1.149090909090909</v>
+        <v>1.787563131313131</v>
       </c>
       <c r="F22" t="n">
-        <v>68.15454545454546</v>
+        <v>80.33617424242424</v>
       </c>
       <c r="G22" t="n">
-        <v>2220181.818181818</v>
+        <v>30082302.18855219</v>
       </c>
       <c r="H22" t="n">
-        <v>75.17181818181817</v>
+        <v>83.87657828282829</v>
       </c>
       <c r="I22" t="n">
-        <v>25.67037037037037</v>
+        <v>26.06681818181818</v>
       </c>
       <c r="J22" t="n">
-        <v>181.4456790123457</v>
+        <v>182.2870454545455</v>
       </c>
       <c r="K22" t="n">
-        <v>1.045679012345679</v>
+        <v>2.087727272727273</v>
       </c>
       <c r="L22" t="n">
-        <v>70.95432098765433</v>
+        <v>78.55727272727272</v>
       </c>
       <c r="M22" t="n">
-        <v>3293703.703703704</v>
+        <v>21251022.72727273</v>
       </c>
       <c r="N22" t="n">
-        <v>73.51481481481481</v>
+        <v>80.70545454545454</v>
       </c>
       <c r="O22" t="n">
-        <v>24.85835795099592</v>
+        <v>24.81977107211375</v>
       </c>
       <c r="P22" t="n">
-        <v>183.359672485611</v>
+        <v>183.8750023389612</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.16718949276595</v>
+        <v>1.764742901390499</v>
       </c>
       <c r="R22" t="n">
-        <v>68.75142668790804</v>
+        <v>76.17271600856554</v>
       </c>
       <c r="S22" t="n">
-        <v>2496013.602771684</v>
+        <v>15638052.60495607</v>
       </c>
       <c r="T22" t="n">
-        <v>74.88350611922291</v>
+        <v>81.50353834052633</v>
       </c>
       <c r="U22" t="n">
-        <v>26.03937376990517</v>
+        <v>25.34594552990198</v>
       </c>
       <c r="V22" t="n">
-        <v>183.3066870363489</v>
+        <v>182.7396397178475</v>
       </c>
       <c r="W22" t="n">
-        <v>1.219601690133091</v>
+        <v>1.963514286009749</v>
       </c>
       <c r="X22" t="n">
-        <v>69.62724802840745</v>
+        <v>76.28715226948893</v>
       </c>
       <c r="Y22" t="n">
-        <v>2557524.612907222</v>
+        <v>17566886.10747322</v>
       </c>
       <c r="Z22" t="n">
-        <v>72.58290323024623</v>
+        <v>80.59263702100816</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>25.79545454545455</v>
+        <v>24.94214876033058</v>
       </c>
       <c r="D23" t="n">
-        <v>186.23</v>
+        <v>186.5454545454545</v>
       </c>
       <c r="E23" t="n">
-        <v>1.248181818181818</v>
+        <v>1.041322314049587</v>
       </c>
       <c r="F23" t="n">
-        <v>76.07818181818182</v>
+        <v>73.32231404958678</v>
       </c>
       <c r="G23" t="n">
-        <v>13460363.63636364</v>
+        <v>5104958.67768595</v>
       </c>
       <c r="H23" t="n">
-        <v>79.36909090909091</v>
+        <v>77.13223140495869</v>
       </c>
       <c r="I23" t="n">
-        <v>26.09090909090909</v>
+        <v>25.71666666666667</v>
       </c>
       <c r="J23" t="n">
-        <v>182.0606060606061</v>
+        <v>181.3263888888889</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>1.038888888888889</v>
       </c>
       <c r="L23" t="n">
-        <v>67.94949494949496</v>
+        <v>71.03611111111113</v>
       </c>
       <c r="M23" t="n">
-        <v>1391161.616161616</v>
+        <v>3400729.166666667</v>
       </c>
       <c r="N23" t="n">
-        <v>71.27272727272728</v>
+        <v>73.52916666666667</v>
       </c>
       <c r="O23" t="n">
-        <v>24.94636711542671</v>
+        <v>25.4026541882558</v>
       </c>
       <c r="P23" t="n">
-        <v>185.0591305860463</v>
+        <v>183.0104600351125</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.193529568127091</v>
+        <v>1.07102466903269</v>
       </c>
       <c r="R23" t="n">
-        <v>72.03887250992901</v>
+        <v>70.91299251154867</v>
       </c>
       <c r="S23" t="n">
-        <v>5762901.734058855</v>
+        <v>3252643.011276701</v>
       </c>
       <c r="T23" t="n">
-        <v>76.01139701973294</v>
+        <v>74.80333207246309</v>
       </c>
       <c r="U23" t="n">
-        <v>24.32992719214942</v>
+        <v>26.47920688365132</v>
       </c>
       <c r="V23" t="n">
-        <v>182.1738271604938</v>
+        <v>183.6007142651587</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.250343894788339</v>
       </c>
       <c r="X23" t="n">
-        <v>66.95798670465336</v>
+        <v>69.93445048778382</v>
       </c>
       <c r="Y23" t="n">
-        <v>1478218.106995885</v>
+        <v>2705492.333592333</v>
       </c>
       <c r="Z23" t="n">
-        <v>72.8115606204495</v>
+        <v>72.48474776252553</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>24.04636363636363</v>
+        <v>26.38727272727273</v>
       </c>
       <c r="D24" t="n">
-        <v>184.7945454545455</v>
+        <v>184.4963636363637</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>1.019090909090909</v>
       </c>
       <c r="F24" t="n">
-        <v>71.14181818181819</v>
+        <v>67.11636363636364</v>
       </c>
       <c r="G24" t="n">
-        <v>4415181.818181818</v>
+        <v>1309840.909090909</v>
       </c>
       <c r="H24" t="n">
-        <v>76.64727272727274</v>
+        <v>70.48818181818183</v>
       </c>
       <c r="I24" t="n">
-        <v>25.81414141414142</v>
+        <v>27.85143097643098</v>
       </c>
       <c r="J24" t="n">
-        <v>182.3282828282828</v>
+        <v>181.1434343434343</v>
       </c>
       <c r="K24" t="n">
-        <v>1.02020202020202</v>
+        <v>1.018518518518518</v>
       </c>
       <c r="L24" t="n">
-        <v>67.42323232323233</v>
+        <v>67.81784511784512</v>
       </c>
       <c r="M24" t="n">
-        <v>1496035.353535354</v>
+        <v>1447777.777777778</v>
       </c>
       <c r="N24" t="n">
-        <v>71.88585858585857</v>
+        <v>70.10159932659933</v>
       </c>
       <c r="O24" t="n">
-        <v>23.17223981249468</v>
+        <v>24.56836745862833</v>
       </c>
       <c r="P24" t="n">
-        <v>184.6098602019891</v>
+        <v>182.8497245170288</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>1.007692307692308</v>
       </c>
       <c r="R24" t="n">
-        <v>67.55594103200924</v>
+        <v>64.4695638757378</v>
       </c>
       <c r="S24" t="n">
-        <v>2545997.034019897</v>
+        <v>1056942.400160226</v>
       </c>
       <c r="T24" t="n">
-        <v>74.75548996577857</v>
+        <v>69.79114614853745</v>
       </c>
       <c r="U24" t="n">
-        <v>26.59254885032663</v>
+        <v>25.20616465659944</v>
       </c>
       <c r="V24" t="n">
-        <v>181.4586773720107</v>
+        <v>179.1507580402689</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12371233704567</v>
+        <v>1.006805555555556</v>
       </c>
       <c r="X24" t="n">
-        <v>66.87789634234079</v>
+        <v>64.93143918279787</v>
       </c>
       <c r="Y24" t="n">
-        <v>1377551.238884572</v>
+        <v>1193535.301003345</v>
       </c>
       <c r="Z24" t="n">
-        <v>70.74887852887852</v>
+        <v>69.48274302388432</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>24.06363636363636</v>
+        <v>29.11</v>
       </c>
       <c r="D25" t="n">
-        <v>184.6545454545455</v>
+        <v>183.32</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="F25" t="n">
-        <v>72.15454545454546</v>
+        <v>67.87</v>
       </c>
       <c r="G25" t="n">
-        <v>5452272.727272728</v>
+        <v>1037400</v>
       </c>
       <c r="H25" t="n">
-        <v>77.78181818181818</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+        <v>69.97999999999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25.52047750229569</v>
+      </c>
+      <c r="J25" t="n">
+        <v>184.7290174471993</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.264738292011019</v>
+      </c>
+      <c r="L25" t="n">
+        <v>70.86786042240588</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3244237.832874197</v>
+      </c>
+      <c r="N25" t="n">
+        <v>76.37658402203857</v>
+      </c>
       <c r="O25" t="n">
-        <v>23.36307449072667</v>
+        <v>24.89329614461308</v>
       </c>
       <c r="P25" t="n">
-        <v>182.6972344177562</v>
+        <v>185.0998843987608</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.08224931590149</v>
+        <v>1.030678106917237</v>
       </c>
       <c r="R25" t="n">
-        <v>68.24991669200365</v>
+        <v>65.26908853363773</v>
       </c>
       <c r="S25" t="n">
-        <v>2627385.177865612</v>
+        <v>1046866.811003853</v>
       </c>
       <c r="T25" t="n">
-        <v>74.82169534813013</v>
+        <v>69.2467237469709</v>
       </c>
       <c r="U25" t="n">
-        <v>29</v>
+        <v>24.6231770980997</v>
       </c>
       <c r="V25" t="n">
-        <v>181.6</v>
+        <v>183.205746338285</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.192188647266047</v>
       </c>
       <c r="X25" t="n">
-        <v>70.2</v>
+        <v>69.55463642652498</v>
       </c>
       <c r="Y25" t="n">
-        <v>1820000</v>
+        <v>2992488.039308473</v>
       </c>
       <c r="Z25" t="n">
-        <v>70.2</v>
+        <v>75.64575599151452</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>25.84030303030303</v>
+        <v>25.45206611570248</v>
       </c>
       <c r="D26" t="n">
-        <v>184.9241414141414</v>
+        <v>183.2471074380165</v>
       </c>
       <c r="E26" t="n">
-        <v>1.321212121212121</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>71.34686868686867</v>
+        <v>67.04545454545455</v>
       </c>
       <c r="G26" t="n">
-        <v>3189494.94949495</v>
+        <v>1360103.305785124</v>
       </c>
       <c r="H26" t="n">
-        <v>76.55646464646466</v>
+        <v>71.03801652892561</v>
       </c>
       <c r="I26" t="n">
-        <v>26.05308641975309</v>
+        <v>25.55277777777778</v>
       </c>
       <c r="J26" t="n">
-        <v>183.1037037037037</v>
+        <v>183.5716049382716</v>
       </c>
       <c r="K26" t="n">
-        <v>1.104938271604938</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>68.59876543209877</v>
+        <v>66.52746913580248</v>
       </c>
       <c r="M26" t="n">
-        <v>1671203.703703704</v>
+        <v>1187901.234567901</v>
       </c>
       <c r="N26" t="n">
-        <v>72.31358024691357</v>
+        <v>70.28456790123457</v>
       </c>
       <c r="O26" t="n">
-        <v>24.9063176984694</v>
+        <v>23.56668197286638</v>
       </c>
       <c r="P26" t="n">
-        <v>183.9865548902422</v>
+        <v>182.0834655940428</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.236407511992651</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>70.10686280936126</v>
+        <v>64.17281167857631</v>
       </c>
       <c r="S26" t="n">
-        <v>3172913.743824115</v>
+        <v>1159419.451042877</v>
       </c>
       <c r="T26" t="n">
-        <v>75.84113777278793</v>
+        <v>71.28115552613303</v>
       </c>
       <c r="U26" t="n">
-        <v>23.9060405643739</v>
+        <v>25.18190172400698</v>
       </c>
       <c r="V26" t="n">
-        <v>184.3540123456791</v>
+        <v>183.4440810359232</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>64.02879188712522</v>
+        <v>64.8128593073593</v>
       </c>
       <c r="Y26" t="n">
-        <v>1099708.002645503</v>
+        <v>1035885.016328701</v>
       </c>
       <c r="Z26" t="n">
-        <v>70.74927248677248</v>
+        <v>69.30842686261107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>25.43636363636364</v>
+        <v>26.68874458874459</v>
       </c>
       <c r="D27" t="n">
-        <v>184.3818181818181</v>
+        <v>185.6223665223665</v>
       </c>
       <c r="E27" t="n">
-        <v>1.209090909090909</v>
+        <v>1.073376623376623</v>
       </c>
       <c r="F27" t="n">
-        <v>72.18181818181817</v>
+        <v>69.49617604617605</v>
       </c>
       <c r="G27" t="n">
-        <v>3650000</v>
+        <v>1990764.790764791</v>
       </c>
       <c r="H27" t="n">
-        <v>75.73636363636363</v>
+        <v>72.82106782106781</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2627,1408 +2639,2004 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>25.81782430213465</v>
+        <v>26.94418811002662</v>
       </c>
       <c r="P27" t="n">
-        <v>183.1474308450171</v>
+        <v>185.0683817321395</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.136724137931035</v>
+        <v>1.118495738216235</v>
       </c>
       <c r="R27" t="n">
-        <v>70.13735063786788</v>
+        <v>69.80358863703584</v>
       </c>
       <c r="S27" t="n">
-        <v>2714007.06707086</v>
+        <v>2103228.030639133</v>
       </c>
       <c r="T27" t="n">
-        <v>74.33269609700645</v>
+        <v>73.18901084939905</v>
       </c>
       <c r="U27" t="n">
-        <v>21.4</v>
+        <v>22.3875</v>
       </c>
       <c r="V27" t="n">
-        <v>179.8</v>
+        <v>180.65</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>61.6</v>
+        <v>62.2375</v>
       </c>
       <c r="Y27" t="n">
-        <v>775000</v>
+        <v>823437.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>70.8</v>
+        <v>70.52500000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>25.37727272727273</v>
+        <v>25.72181818181819</v>
       </c>
       <c r="D28" t="n">
-        <v>182.9618181818182</v>
+        <v>182.7009090909091</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>67.02000000000001</v>
+        <v>67.68636363636364</v>
       </c>
       <c r="G28" t="n">
-        <v>1374063.636363636</v>
+        <v>1565022.727272727</v>
       </c>
       <c r="H28" t="n">
-        <v>71.12181818181818</v>
+        <v>72.04636363636364</v>
       </c>
       <c r="I28" t="n">
-        <v>26.21969696969697</v>
+        <v>26.05734265734266</v>
       </c>
       <c r="J28" t="n">
-        <v>183.0303030303031</v>
+        <v>182.8741258741259</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>70.45454545454545</v>
+        <v>70.44335664335664</v>
       </c>
       <c r="M28" t="n">
-        <v>2521590.909090909</v>
+        <v>2576153.846153846</v>
       </c>
       <c r="N28" t="n">
-        <v>74.28030303030303</v>
+        <v>74.4979020979021</v>
       </c>
       <c r="O28" t="n">
-        <v>23.76014382094667</v>
+        <v>25.83424634624635</v>
       </c>
       <c r="P28" t="n">
-        <v>182.3692724709074</v>
+        <v>182.0086191586192</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>1.103341103341103</v>
       </c>
       <c r="R28" t="n">
-        <v>64.16933094167203</v>
+        <v>66.47505908905909</v>
       </c>
       <c r="S28" t="n">
-        <v>1156315.046940815</v>
+        <v>1409329.448329448</v>
       </c>
       <c r="T28" t="n">
-        <v>71.03003298350824</v>
+        <v>70.94827639027639</v>
       </c>
       <c r="U28" t="n">
-        <v>25.43375965151327</v>
+        <v>25.44150277753957</v>
       </c>
       <c r="V28" t="n">
-        <v>182.39419025352</v>
+        <v>182.3927914987279</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.003205128205128</v>
       </c>
       <c r="X28" t="n">
-        <v>68.43747212931994</v>
+        <v>68.70878760159695</v>
       </c>
       <c r="Y28" t="n">
-        <v>1973982.049217556</v>
+        <v>2063652.202498356</v>
       </c>
       <c r="Z28" t="n">
-        <v>73.31346902225526</v>
+        <v>73.52096137171387</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>27.94095500459137</v>
+        <v>24.36721763085399</v>
       </c>
       <c r="D29" t="n">
-        <v>181.1100091827365</v>
+        <v>183.6962350780533</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>1.137373737373738</v>
       </c>
       <c r="F29" t="n">
-        <v>67.58916437098256</v>
+        <v>68.50413223140495</v>
       </c>
       <c r="G29" t="n">
-        <v>1260000</v>
+        <v>2162217.630853994</v>
       </c>
       <c r="H29" t="n">
-        <v>69.78053259871443</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>74.76501377410467</v>
+      </c>
+      <c r="I29" t="n">
+        <v>26.05636363636363</v>
+      </c>
+      <c r="J29" t="n">
+        <v>184.1720454545454</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>65.23113636363635</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1078602.272727273</v>
+      </c>
+      <c r="N29" t="n">
+        <v>68.8175</v>
+      </c>
       <c r="O29" t="n">
-        <v>25.29041653998176</v>
+        <v>24.87231675198764</v>
       </c>
       <c r="P29" t="n">
-        <v>178.724201608668</v>
+        <v>183.409117844062</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>1.150258846237443</v>
       </c>
       <c r="R29" t="n">
-        <v>65.12331932889245</v>
+        <v>68.62056105827138</v>
       </c>
       <c r="S29" t="n">
-        <v>1261750.334448161</v>
+        <v>2368801.868320579</v>
       </c>
       <c r="T29" t="n">
-        <v>69.63060946958181</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+        <v>74.57840383132817</v>
+      </c>
+      <c r="U29" t="n">
+        <v>25.99547260361047</v>
+      </c>
+      <c r="V29" t="n">
+        <v>182.1657418001526</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>64.08524292312907</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1016423.169825344</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>67.96443717524953</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>25.81414141414142</v>
+        <v>25.6297520661157</v>
       </c>
       <c r="D30" t="n">
-        <v>182.3282828282828</v>
+        <v>186.5504132231405</v>
       </c>
       <c r="E30" t="n">
-        <v>1.02020202020202</v>
+        <v>1.216528925619835</v>
       </c>
       <c r="F30" t="n">
-        <v>67.42323232323233</v>
+        <v>72.97520661157024</v>
       </c>
       <c r="G30" t="n">
-        <v>1496035.353535354</v>
+        <v>5321280.991735538</v>
       </c>
       <c r="H30" t="n">
-        <v>71.88585858585857</v>
-      </c>
-      <c r="I30" t="n">
-        <v>26.05308641975309</v>
-      </c>
-      <c r="J30" t="n">
-        <v>183.1037037037037</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.104938271604938</v>
-      </c>
-      <c r="L30" t="n">
-        <v>68.59876543209877</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1671203.703703704</v>
-      </c>
-      <c r="N30" t="n">
-        <v>72.31358024691357</v>
-      </c>
+        <v>76.81652892561983</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>26.59254885032663</v>
+        <v>23.81737774719034</v>
       </c>
       <c r="P30" t="n">
-        <v>181.4586773720107</v>
+        <v>184.6449125465017</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.12371233704567</v>
+        <v>1.128385617935843</v>
       </c>
       <c r="R30" t="n">
-        <v>66.87789634234079</v>
+        <v>70.3708043777534</v>
       </c>
       <c r="S30" t="n">
-        <v>1377551.238884572</v>
+        <v>3866672.466408598</v>
       </c>
       <c r="T30" t="n">
-        <v>70.74887852887852</v>
+        <v>77.24240376564966</v>
       </c>
       <c r="U30" t="n">
-        <v>23.9060405643739</v>
+        <v>23.96527777777778</v>
       </c>
       <c r="V30" t="n">
-        <v>184.3540123456791</v>
+        <v>182.6527777777778</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>64.02879188712522</v>
+        <v>68.25694444444444</v>
       </c>
       <c r="Y30" t="n">
-        <v>1099708.002645503</v>
+        <v>2353125</v>
       </c>
       <c r="Z30" t="n">
-        <v>70.74927248677248</v>
+        <v>73.375</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>25.84030303030303</v>
+        <v>25.69777777777778</v>
       </c>
       <c r="D31" t="n">
-        <v>184.9241414141414</v>
+        <v>183.7122222222222</v>
       </c>
       <c r="E31" t="n">
-        <v>1.321212121212121</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="F31" t="n">
-        <v>71.34686868686867</v>
+        <v>68.19666666666667</v>
       </c>
       <c r="G31" t="n">
-        <v>3189494.94949495</v>
+        <v>1628027.777777778</v>
       </c>
       <c r="H31" t="n">
-        <v>76.55646464646466</v>
+        <v>72.25444444444445</v>
       </c>
       <c r="I31" t="n">
-        <v>25.98888888888889</v>
+        <v>23.66689623507806</v>
       </c>
       <c r="J31" t="n">
-        <v>183.9160493827161</v>
+        <v>184.9233241505969</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>66.70246913580246</v>
+        <v>70.11099632690542</v>
       </c>
       <c r="M31" t="n">
-        <v>1163734.567901235</v>
+        <v>3865992.309458219</v>
       </c>
       <c r="N31" t="n">
-        <v>69.93456790123456</v>
+        <v>76.18893480257115</v>
       </c>
       <c r="O31" t="n">
-        <v>24.9063176984694</v>
+        <v>23.96159663865546</v>
       </c>
       <c r="P31" t="n">
-        <v>183.9865548902422</v>
+        <v>184.4987990196078</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.236407511992651</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>70.10686280936126</v>
+        <v>64.48167250233428</v>
       </c>
       <c r="S31" t="n">
-        <v>3172913.743824115</v>
+        <v>1170122.414799253</v>
       </c>
       <c r="T31" t="n">
-        <v>75.84113777278793</v>
+        <v>71.18651844070961</v>
       </c>
       <c r="U31" t="n">
-        <v>24.9553835053835</v>
+        <v>22.82705449210833</v>
       </c>
       <c r="V31" t="n">
-        <v>183.5819352869353</v>
+        <v>184.6810762486243</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>64.83978238428239</v>
+        <v>66.67392677628128</v>
       </c>
       <c r="Y31" t="n">
-        <v>1063629.955599956</v>
+        <v>2307231.237192734</v>
       </c>
       <c r="Z31" t="n">
-        <v>69.44951998001997</v>
+        <v>74.58773132593836</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>29.05</v>
+        <v>27.10209790209791</v>
       </c>
       <c r="D32" t="n">
-        <v>183.48</v>
+        <v>181.3921522921523</v>
       </c>
       <c r="E32" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>67.90000000000001</v>
+        <v>67.47521367521368</v>
       </c>
       <c r="G32" t="n">
-        <v>1046900</v>
+        <v>1250264.18026418</v>
       </c>
       <c r="H32" t="n">
-        <v>70.05</v>
-      </c>
-      <c r="I32" t="n">
-        <v>26.23232323232323</v>
-      </c>
-      <c r="J32" t="n">
-        <v>184.4242424242424</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>67.01010101010101</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1316919.191919192</v>
-      </c>
-      <c r="N32" t="n">
-        <v>70.52525252525253</v>
-      </c>
+        <v>70.13022533022534</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>25.04514799646493</v>
+        <v>25.37346197961583</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9832177320941</v>
+        <v>180.0884310988157</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.028826255065386</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>65.20242186697106</v>
+        <v>65.8332191739884</v>
       </c>
       <c r="S32" t="n">
-        <v>1015413.10730015</v>
+        <v>1166835.269431423</v>
       </c>
       <c r="T32" t="n">
-        <v>68.91709411734125</v>
-      </c>
-      <c r="U32" t="n">
-        <v>24.87786770037978</v>
-      </c>
-      <c r="V32" t="n">
-        <v>183.4569136428073</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>64.69145680942783</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1066359.031878839</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>69.80983859582892</v>
-      </c>
+        <v>70.57649080264466</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" t="n">
-        <v>26.95909090909091</v>
-      </c>
-      <c r="D33" t="n">
-        <v>181.5780303030303</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>67.51060606060607</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1287954.545454546</v>
-      </c>
-      <c r="H33" t="n">
-        <v>70.27575757575758</v>
-      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>25.87107438016529</v>
+        <v>25.88727272727273</v>
       </c>
       <c r="J33" t="n">
-        <v>186.6884297520661</v>
+        <v>182.7136363636363</v>
       </c>
       <c r="K33" t="n">
-        <v>1.227272727272727</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>73.19669421487605</v>
+        <v>67.59181818181818</v>
       </c>
       <c r="M33" t="n">
-        <v>5316033.05785124</v>
+        <v>1341204.545454545</v>
       </c>
       <c r="N33" t="n">
-        <v>76.90082644628099</v>
+        <v>71.26727272727274</v>
       </c>
       <c r="O33" t="n">
-        <v>25.41676329842997</v>
+        <v>29</v>
       </c>
       <c r="P33" t="n">
-        <v>179.4409926647427</v>
+        <v>181.6</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>65.99645752395752</v>
+        <v>70.2</v>
       </c>
       <c r="S33" t="n">
-        <v>1207054.982054982</v>
+        <v>1820000</v>
       </c>
       <c r="T33" t="n">
-        <v>70.95946760030094</v>
+        <v>70.2</v>
       </c>
       <c r="U33" t="n">
-        <v>23.99010501991761</v>
+        <v>23.8005059015059</v>
       </c>
       <c r="V33" t="n">
-        <v>184.8949125465017</v>
+        <v>181.7865268620268</v>
       </c>
       <c r="W33" t="n">
-        <v>1.126287715837941</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>70.65821696516599</v>
+        <v>66.41397374847375</v>
       </c>
       <c r="Y33" t="n">
-        <v>3979469.669205801</v>
+        <v>1434065.595746846</v>
       </c>
       <c r="Z33" t="n">
-        <v>77.3441520173979</v>
+        <v>72.67669576719577</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>27.85143097643098</v>
+      </c>
+      <c r="D34" t="n">
+        <v>181.1434343434343</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.018518518518518</v>
+      </c>
+      <c r="F34" t="n">
+        <v>67.81784511784512</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1447777.777777778</v>
+      </c>
+      <c r="H34" t="n">
+        <v>70.10159932659933</v>
+      </c>
+      <c r="I34" t="n">
+        <v>25.6297520661157</v>
+      </c>
+      <c r="J34" t="n">
+        <v>186.5504132231405</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.216528925619835</v>
+      </c>
+      <c r="L34" t="n">
+        <v>72.97520661157024</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5321280.991735538</v>
+      </c>
+      <c r="N34" t="n">
+        <v>76.81652892561983</v>
+      </c>
+      <c r="O34" t="n">
+        <v>25.20616465659944</v>
+      </c>
+      <c r="P34" t="n">
+        <v>179.1507580402689</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.006805555555556</v>
+      </c>
+      <c r="R34" t="n">
+        <v>64.93143918279787</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1193535.301003345</v>
+      </c>
+      <c r="T34" t="n">
+        <v>69.48274302388432</v>
+      </c>
       <c r="U34" t="n">
-        <v>21.4</v>
+        <v>23.81737774719034</v>
       </c>
       <c r="V34" t="n">
-        <v>179.8</v>
+        <v>184.6449125465017</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.128385617935843</v>
       </c>
       <c r="X34" t="n">
-        <v>61.6</v>
+        <v>70.3708043777534</v>
       </c>
       <c r="Y34" t="n">
-        <v>775000</v>
+        <v>3866672.466408598</v>
       </c>
       <c r="Z34" t="n">
-        <v>70.8</v>
+        <v>77.24240376564966</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" t="n">
-        <v>26.09090909090909</v>
-      </c>
-      <c r="D35" t="n">
-        <v>182.0606060606061</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="n">
-        <v>67.94949494949496</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1391161.616161616</v>
-      </c>
-      <c r="H35" t="n">
-        <v>71.27272727272728</v>
-      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>26.87179487179488</v>
+        <v>29.11</v>
       </c>
       <c r="J35" t="n">
-        <v>185.6597513597513</v>
+        <v>183.32</v>
       </c>
       <c r="K35" t="n">
-        <v>1.086713286713287</v>
+        <v>1.16</v>
       </c>
       <c r="L35" t="n">
-        <v>69.51756021756022</v>
+        <v>67.87</v>
       </c>
       <c r="M35" t="n">
-        <v>1987466.977466978</v>
+        <v>1037400</v>
       </c>
       <c r="N35" t="n">
-        <v>72.81709401709402</v>
+        <v>69.97999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>24.32992719214942</v>
+        <v>22.3875</v>
       </c>
       <c r="P35" t="n">
-        <v>182.1738271604938</v>
+        <v>180.65</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>66.95798670465336</v>
+        <v>62.2375</v>
       </c>
       <c r="S35" t="n">
-        <v>1478218.106995885</v>
+        <v>823437.5</v>
       </c>
       <c r="T35" t="n">
-        <v>72.8115606204495</v>
+        <v>70.52500000000001</v>
       </c>
       <c r="U35" t="n">
-        <v>27.25943223443224</v>
+        <v>24.89329614461308</v>
       </c>
       <c r="V35" t="n">
-        <v>185.3515125454256</v>
+        <v>185.0998843987608</v>
       </c>
       <c r="W35" t="n">
-        <v>1.130397863006559</v>
+        <v>1.030678106917237</v>
       </c>
       <c r="X35" t="n">
-        <v>69.87794495359714</v>
+        <v>65.26908853363773</v>
       </c>
       <c r="Y35" t="n">
-        <v>2098139.105459758</v>
+        <v>1046866.811003853</v>
       </c>
       <c r="Z35" t="n">
-        <v>73.09123130492695</v>
+        <v>69.2467237469709</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>24.04636363636363</v>
+        <v>25.55277777777778</v>
       </c>
       <c r="D36" t="n">
-        <v>184.7945454545455</v>
+        <v>183.5716049382716</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>71.14181818181819</v>
+        <v>66.52746913580248</v>
       </c>
       <c r="G36" t="n">
-        <v>4415181.818181818</v>
+        <v>1187901.234567901</v>
       </c>
       <c r="H36" t="n">
-        <v>76.64727272727274</v>
+        <v>70.28456790123457</v>
       </c>
       <c r="I36" t="n">
-        <v>23.65545454545454</v>
+        <v>25.72181818181819</v>
       </c>
       <c r="J36" t="n">
-        <v>184.2072727272727</v>
+        <v>182.7009090909091</v>
       </c>
       <c r="K36" t="n">
-        <v>1.149090909090909</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>68.15454545454546</v>
+        <v>67.68636363636364</v>
       </c>
       <c r="M36" t="n">
-        <v>2220181.818181818</v>
+        <v>1565022.727272727</v>
       </c>
       <c r="N36" t="n">
-        <v>75.17181818181817</v>
+        <v>72.04636363636364</v>
       </c>
       <c r="O36" t="n">
-        <v>23.17223981249468</v>
+        <v>25.18190172400698</v>
       </c>
       <c r="P36" t="n">
-        <v>184.6098602019891</v>
+        <v>183.4440810359232</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>67.55594103200924</v>
+        <v>64.8128593073593</v>
       </c>
       <c r="S36" t="n">
-        <v>2545997.034019897</v>
+        <v>1035885.016328701</v>
       </c>
       <c r="T36" t="n">
-        <v>74.75548996577857</v>
+        <v>69.30842686261107</v>
       </c>
       <c r="U36" t="n">
-        <v>24.85835795099592</v>
+        <v>25.83424634624635</v>
       </c>
       <c r="V36" t="n">
-        <v>183.359672485611</v>
+        <v>182.0086191586192</v>
       </c>
       <c r="W36" t="n">
-        <v>1.16718949276595</v>
+        <v>1.103341103341103</v>
       </c>
       <c r="X36" t="n">
-        <v>68.75142668790804</v>
+        <v>66.47505908905909</v>
       </c>
       <c r="Y36" t="n">
-        <v>2496013.602771684</v>
+        <v>1409329.448329448</v>
       </c>
       <c r="Z36" t="n">
-        <v>74.88350611922291</v>
+        <v>70.94827639027639</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>26.02636363636363</v>
+        <v>26.68874458874459</v>
       </c>
       <c r="D37" t="n">
-        <v>184.4520454545454</v>
+        <v>185.6223665223665</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>1.073376623376623</v>
       </c>
       <c r="F37" t="n">
-        <v>65.35113636363636</v>
+        <v>69.49617604617605</v>
       </c>
       <c r="G37" t="n">
-        <v>1097702.272727273</v>
+        <v>1990764.790764791</v>
       </c>
       <c r="H37" t="n">
-        <v>68.89749999999999</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+        <v>72.82106782106781</v>
+      </c>
+      <c r="I37" t="n">
+        <v>26.05734265734266</v>
+      </c>
+      <c r="J37" t="n">
+        <v>182.8741258741259</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>70.44335664335664</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2576153.846153846</v>
+      </c>
+      <c r="N37" t="n">
+        <v>74.4979020979021</v>
+      </c>
       <c r="O37" t="n">
-        <v>25.99042874396135</v>
+        <v>26.94418811002662</v>
       </c>
       <c r="P37" t="n">
-        <v>182.1929347826087</v>
+        <v>185.0683817321395</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>1.118495738216235</v>
       </c>
       <c r="R37" t="n">
-        <v>64.02976046698873</v>
+        <v>69.80358863703584</v>
       </c>
       <c r="S37" t="n">
-        <v>1002673.169825344</v>
+        <v>2103228.030639133</v>
       </c>
       <c r="T37" t="n">
-        <v>67.88176173665303</v>
+        <v>73.18901084939905</v>
       </c>
       <c r="U37" t="n">
-        <v>29</v>
+        <v>25.44150277753957</v>
       </c>
       <c r="V37" t="n">
-        <v>181.6</v>
+        <v>182.3927914987279</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>1.003205128205128</v>
       </c>
       <c r="X37" t="n">
-        <v>70.2</v>
+        <v>68.70878760159695</v>
       </c>
       <c r="Y37" t="n">
-        <v>1820000</v>
+        <v>2063652.202498356</v>
       </c>
       <c r="Z37" t="n">
-        <v>70.2</v>
+        <v>73.52096137171387</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>26.23232323232323</v>
+        <v>23.66689623507806</v>
       </c>
       <c r="D38" t="n">
-        <v>184.4242424242424</v>
+        <v>184.9233241505969</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>67.01010101010101</v>
+        <v>70.11099632690542</v>
       </c>
       <c r="G38" t="n">
-        <v>1316919.191919192</v>
+        <v>3865992.309458219</v>
       </c>
       <c r="H38" t="n">
-        <v>70.52525252525253</v>
+        <v>76.18893480257115</v>
       </c>
       <c r="I38" t="n">
-        <v>27.94095500459137</v>
+        <v>26.38727272727273</v>
       </c>
       <c r="J38" t="n">
-        <v>181.1100091827365</v>
+        <v>184.4963636363637</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.019090909090909</v>
       </c>
       <c r="L38" t="n">
-        <v>67.58916437098256</v>
+        <v>67.11636363636364</v>
       </c>
       <c r="M38" t="n">
-        <v>1260000</v>
+        <v>1309840.909090909</v>
       </c>
       <c r="N38" t="n">
-        <v>69.78053259871443</v>
+        <v>70.48818181818183</v>
       </c>
       <c r="O38" t="n">
-        <v>24.87786770037978</v>
+        <v>22.82705449210833</v>
       </c>
       <c r="P38" t="n">
-        <v>183.4569136428073</v>
+        <v>184.6810762486243</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>64.69145680942783</v>
+        <v>66.67392677628128</v>
       </c>
       <c r="S38" t="n">
-        <v>1066359.031878839</v>
+        <v>2307231.237192734</v>
       </c>
       <c r="T38" t="n">
-        <v>69.80983859582892</v>
+        <v>74.58773132593836</v>
       </c>
       <c r="U38" t="n">
-        <v>25.29041653998176</v>
+        <v>24.56836745862833</v>
       </c>
       <c r="V38" t="n">
-        <v>178.724201608668</v>
+        <v>182.8497245170288</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>1.007692307692308</v>
       </c>
       <c r="X38" t="n">
-        <v>65.12331932889245</v>
+        <v>64.4695638757378</v>
       </c>
       <c r="Y38" t="n">
-        <v>1261750.334448161</v>
+        <v>1056942.400160226</v>
       </c>
       <c r="Z38" t="n">
-        <v>69.63060946958181</v>
+        <v>69.79114614853745</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>29.05</v>
+        <v>26.05636363636363</v>
       </c>
       <c r="D39" t="n">
-        <v>183.48</v>
+        <v>184.1720454545454</v>
       </c>
       <c r="E39" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>67.90000000000001</v>
+        <v>65.23113636363635</v>
       </c>
       <c r="G39" t="n">
-        <v>1046900</v>
+        <v>1078602.272727273</v>
       </c>
       <c r="H39" t="n">
-        <v>70.05</v>
+        <v>68.8175</v>
       </c>
       <c r="I39" t="n">
-        <v>25.84030303030303</v>
+        <v>25.45206611570248</v>
       </c>
       <c r="J39" t="n">
-        <v>184.9241414141414</v>
+        <v>183.2471074380165</v>
       </c>
       <c r="K39" t="n">
-        <v>1.321212121212121</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>71.34686868686867</v>
+        <v>67.04545454545455</v>
       </c>
       <c r="M39" t="n">
-        <v>3189494.94949495</v>
+        <v>1360103.305785124</v>
       </c>
       <c r="N39" t="n">
-        <v>76.55646464646466</v>
+        <v>71.03801652892561</v>
       </c>
       <c r="O39" t="n">
-        <v>25.04514799646493</v>
+        <v>25.99547260361047</v>
       </c>
       <c r="P39" t="n">
-        <v>184.9832177320941</v>
+        <v>182.1657418001526</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.028826255065386</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>65.20242186697106</v>
+        <v>64.08524292312907</v>
       </c>
       <c r="S39" t="n">
-        <v>1015413.10730015</v>
+        <v>1016423.169825344</v>
       </c>
       <c r="T39" t="n">
-        <v>68.91709411734125</v>
+        <v>67.96443717524953</v>
       </c>
       <c r="U39" t="n">
-        <v>24.9063176984694</v>
+        <v>23.56668197286638</v>
       </c>
       <c r="V39" t="n">
-        <v>183.9865548902422</v>
+        <v>182.0834655940428</v>
       </c>
       <c r="W39" t="n">
-        <v>1.236407511992651</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>70.10686280936126</v>
+        <v>64.17281167857631</v>
       </c>
       <c r="Y39" t="n">
-        <v>3172913.743824115</v>
+        <v>1159419.451042877</v>
       </c>
       <c r="Z39" t="n">
-        <v>75.84113777278793</v>
+        <v>71.28115552613303</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>25.37727272727273</v>
+        <v>25.52047750229569</v>
       </c>
       <c r="D40" t="n">
-        <v>182.9618181818182</v>
+        <v>184.7290174471993</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>1.264738292011019</v>
       </c>
       <c r="F40" t="n">
-        <v>67.02000000000001</v>
+        <v>70.86786042240588</v>
       </c>
       <c r="G40" t="n">
-        <v>1374063.636363636</v>
+        <v>3244237.832874197</v>
       </c>
       <c r="H40" t="n">
-        <v>71.12181818181818</v>
+        <v>76.37658402203857</v>
       </c>
       <c r="I40" t="n">
-        <v>25.98888888888889</v>
+        <v>24.36721763085399</v>
       </c>
       <c r="J40" t="n">
-        <v>183.9160493827161</v>
+        <v>183.6962350780533</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>1.137373737373738</v>
       </c>
       <c r="L40" t="n">
-        <v>66.70246913580246</v>
+        <v>68.50413223140495</v>
       </c>
       <c r="M40" t="n">
-        <v>1163734.567901235</v>
+        <v>2162217.630853994</v>
       </c>
       <c r="N40" t="n">
-        <v>69.93456790123456</v>
+        <v>74.76501377410467</v>
       </c>
       <c r="O40" t="n">
-        <v>23.76014382094667</v>
+        <v>24.6231770980997</v>
       </c>
       <c r="P40" t="n">
-        <v>182.3692724709074</v>
+        <v>183.205746338285</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>1.192188647266047</v>
       </c>
       <c r="R40" t="n">
-        <v>64.16933094167203</v>
+        <v>69.55463642652498</v>
       </c>
       <c r="S40" t="n">
-        <v>1156315.046940815</v>
+        <v>2992488.039308473</v>
       </c>
       <c r="T40" t="n">
-        <v>71.03003298350824</v>
+        <v>75.64575599151452</v>
       </c>
       <c r="U40" t="n">
-        <v>24.9553835053835</v>
+        <v>24.87231675198764</v>
       </c>
       <c r="V40" t="n">
-        <v>183.5819352869353</v>
+        <v>183.409117844062</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>1.150258846237443</v>
       </c>
       <c r="X40" t="n">
-        <v>64.83978238428239</v>
+        <v>68.62056105827138</v>
       </c>
       <c r="Y40" t="n">
-        <v>1063629.955599956</v>
+        <v>2368801.868320579</v>
       </c>
       <c r="Z40" t="n">
-        <v>69.44951998001997</v>
+        <v>74.57840383132817</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" t="n">
-        <v>26.87179487179488</v>
-      </c>
-      <c r="D41" t="n">
-        <v>185.6597513597513</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.086713286713287</v>
-      </c>
-      <c r="F41" t="n">
-        <v>69.51756021756022</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1987466.977466978</v>
-      </c>
-      <c r="H41" t="n">
-        <v>72.81709401709402</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>27.10209790209791</v>
+      </c>
+      <c r="J41" t="n">
+        <v>181.3921522921523</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>67.47521367521368</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1250264.18026418</v>
+      </c>
+      <c r="N41" t="n">
+        <v>70.13022533022534</v>
+      </c>
       <c r="O41" t="n">
-        <v>27.25943223443224</v>
+        <v>23.96527777777778</v>
       </c>
       <c r="P41" t="n">
-        <v>185.3515125454256</v>
+        <v>182.6527777777778</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.130397863006559</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>69.87794495359714</v>
+        <v>68.25694444444444</v>
       </c>
       <c r="S41" t="n">
-        <v>2098139.105459758</v>
+        <v>2353125</v>
       </c>
       <c r="T41" t="n">
-        <v>73.09123130492695</v>
+        <v>73.375</v>
       </c>
       <c r="U41" t="n">
-        <v>21.4</v>
+        <v>25.37346197961583</v>
       </c>
       <c r="V41" t="n">
-        <v>179.8</v>
+        <v>180.0884310988157</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>61.6</v>
+        <v>65.8332191739884</v>
       </c>
       <c r="Y41" t="n">
-        <v>775000</v>
+        <v>1166835.269431423</v>
       </c>
       <c r="Z41" t="n">
-        <v>70.8</v>
+        <v>70.57649080264466</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>25.81414141414142</v>
+        <v>25.88727272727273</v>
       </c>
       <c r="D42" t="n">
-        <v>182.3282828282828</v>
+        <v>182.7136363636363</v>
       </c>
       <c r="E42" t="n">
-        <v>1.02020202020202</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>67.42323232323233</v>
+        <v>67.59181818181818</v>
       </c>
       <c r="G42" t="n">
-        <v>1496035.353535354</v>
+        <v>1341204.545454545</v>
       </c>
       <c r="H42" t="n">
-        <v>71.88585858585857</v>
+        <v>71.26727272727274</v>
       </c>
       <c r="I42" t="n">
-        <v>26.21969696969697</v>
+        <v>25.69777777777778</v>
       </c>
       <c r="J42" t="n">
-        <v>183.0303030303031</v>
+        <v>183.7122222222222</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="L42" t="n">
-        <v>70.45454545454545</v>
+        <v>68.19666666666667</v>
       </c>
       <c r="M42" t="n">
-        <v>2521590.909090909</v>
+        <v>1628027.777777778</v>
       </c>
       <c r="N42" t="n">
-        <v>74.28030303030303</v>
+        <v>72.25444444444445</v>
       </c>
       <c r="O42" t="n">
-        <v>26.59254885032663</v>
+        <v>23.8005059015059</v>
       </c>
       <c r="P42" t="n">
-        <v>181.4586773720107</v>
+        <v>181.7865268620268</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.12371233704567</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>66.87789634234079</v>
+        <v>66.41397374847375</v>
       </c>
       <c r="S42" t="n">
-        <v>1377551.238884572</v>
+        <v>1434065.595746846</v>
       </c>
       <c r="T42" t="n">
-        <v>70.74887852887852</v>
+        <v>72.67669576719577</v>
       </c>
       <c r="U42" t="n">
-        <v>25.43375965151327</v>
+        <v>23.96159663865546</v>
       </c>
       <c r="V42" t="n">
-        <v>182.39419025352</v>
+        <v>184.4987990196078</v>
       </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>68.43747212931994</v>
+        <v>64.48167250233428</v>
       </c>
       <c r="Y42" t="n">
-        <v>1973982.049217556</v>
+        <v>1170122.414799253</v>
       </c>
       <c r="Z42" t="n">
-        <v>73.31346902225526</v>
+        <v>71.18651844070961</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
-      <c r="C43" t="n">
-        <v>23.65545454545454</v>
-      </c>
-      <c r="D43" t="n">
-        <v>184.2072727272727</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1.149090909090909</v>
-      </c>
-      <c r="F43" t="n">
-        <v>68.15454545454546</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2220181.818181818</v>
-      </c>
-      <c r="H43" t="n">
-        <v>75.17181818181817</v>
-      </c>
-      <c r="I43" t="n">
-        <v>26.02636363636363</v>
-      </c>
-      <c r="J43" t="n">
-        <v>184.4520454545454</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>65.35113636363636</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1097702.272727273</v>
-      </c>
-      <c r="N43" t="n">
-        <v>68.89749999999999</v>
-      </c>
-      <c r="O43" t="n">
-        <v>24.85835795099592</v>
-      </c>
-      <c r="P43" t="n">
-        <v>183.359672485611</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.16718949276595</v>
-      </c>
-      <c r="R43" t="n">
-        <v>68.75142668790804</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2496013.602771684</v>
-      </c>
-      <c r="T43" t="n">
-        <v>74.88350611922291</v>
-      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="n">
-        <v>25.99042874396135</v>
+        <v>29</v>
       </c>
       <c r="V43" t="n">
-        <v>182.1929347826087</v>
+        <v>181.6</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>64.02976046698873</v>
+        <v>70.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1002673.169825344</v>
+        <v>1820000</v>
       </c>
       <c r="Z43" t="n">
-        <v>67.88176173665303</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>25.87107438016529</v>
+        <v>24.36721763085399</v>
       </c>
       <c r="D44" t="n">
-        <v>186.6884297520661</v>
+        <v>183.6962350780533</v>
       </c>
       <c r="E44" t="n">
-        <v>1.227272727272727</v>
+        <v>1.137373737373738</v>
       </c>
       <c r="F44" t="n">
-        <v>73.19669421487605</v>
+        <v>68.50413223140495</v>
       </c>
       <c r="G44" t="n">
-        <v>5316033.05785124</v>
+        <v>2162217.630853994</v>
       </c>
       <c r="H44" t="n">
-        <v>76.90082644628099</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+        <v>74.76501377410467</v>
+      </c>
+      <c r="I44" t="n">
+        <v>27.85143097643098</v>
+      </c>
+      <c r="J44" t="n">
+        <v>181.1434343434343</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.018518518518518</v>
+      </c>
+      <c r="L44" t="n">
+        <v>67.81784511784512</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1447777.777777778</v>
+      </c>
+      <c r="N44" t="n">
+        <v>70.10159932659933</v>
+      </c>
       <c r="O44" t="n">
-        <v>23.99010501991761</v>
+        <v>24.87231675198764</v>
       </c>
       <c r="P44" t="n">
-        <v>184.8949125465017</v>
+        <v>183.409117844062</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.126287715837941</v>
+        <v>1.150258846237443</v>
       </c>
       <c r="R44" t="n">
-        <v>70.65821696516599</v>
+        <v>68.62056105827138</v>
       </c>
       <c r="S44" t="n">
-        <v>3979469.669205801</v>
+        <v>2368801.868320579</v>
       </c>
       <c r="T44" t="n">
-        <v>77.3441520173979</v>
-      </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+        <v>74.57840383132817</v>
+      </c>
+      <c r="U44" t="n">
+        <v>25.20616465659944</v>
+      </c>
+      <c r="V44" t="n">
+        <v>179.1507580402689</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.006805555555556</v>
+      </c>
+      <c r="X44" t="n">
+        <v>64.93143918279787</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1193535.301003345</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>69.48274302388432</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>26.05308641975309</v>
+        <v>26.38727272727273</v>
       </c>
       <c r="D45" t="n">
-        <v>183.1037037037037</v>
+        <v>184.4963636363637</v>
       </c>
       <c r="E45" t="n">
-        <v>1.104938271604938</v>
+        <v>1.019090909090909</v>
       </c>
       <c r="F45" t="n">
-        <v>68.59876543209877</v>
+        <v>67.11636363636364</v>
       </c>
       <c r="G45" t="n">
-        <v>1671203.703703704</v>
+        <v>1309840.909090909</v>
       </c>
       <c r="H45" t="n">
-        <v>72.31358024691357</v>
+        <v>70.48818181818183</v>
       </c>
       <c r="I45" t="n">
-        <v>24.04636363636363</v>
+        <v>25.55277777777778</v>
       </c>
       <c r="J45" t="n">
-        <v>184.7945454545455</v>
+        <v>183.5716049382716</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>71.14181818181819</v>
+        <v>66.52746913580248</v>
       </c>
       <c r="M45" t="n">
-        <v>4415181.818181818</v>
+        <v>1187901.234567901</v>
       </c>
       <c r="N45" t="n">
-        <v>76.64727272727274</v>
+        <v>70.28456790123457</v>
       </c>
       <c r="O45" t="n">
-        <v>23.9060405643739</v>
+        <v>24.56836745862833</v>
       </c>
       <c r="P45" t="n">
-        <v>184.3540123456791</v>
+        <v>182.8497245170288</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>1.007692307692308</v>
       </c>
       <c r="R45" t="n">
-        <v>64.02879188712522</v>
+        <v>64.4695638757378</v>
       </c>
       <c r="S45" t="n">
-        <v>1099708.002645503</v>
+        <v>1056942.400160226</v>
       </c>
       <c r="T45" t="n">
-        <v>70.74927248677248</v>
+        <v>69.79114614853745</v>
       </c>
       <c r="U45" t="n">
-        <v>23.17223981249468</v>
+        <v>25.18190172400698</v>
       </c>
       <c r="V45" t="n">
-        <v>184.6098602019891</v>
+        <v>183.4440810359232</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>67.55594103200924</v>
+        <v>64.8128593073593</v>
       </c>
       <c r="Y45" t="n">
-        <v>2545997.034019897</v>
+        <v>1035885.016328701</v>
       </c>
       <c r="Z45" t="n">
-        <v>74.75548996577857</v>
+        <v>69.30842686261107</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>25.72181818181819</v>
+      </c>
+      <c r="D46" t="n">
+        <v>182.7009090909091</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>67.68636363636364</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1565022.727272727</v>
+      </c>
+      <c r="H46" t="n">
+        <v>72.04636363636364</v>
+      </c>
+      <c r="I46" t="n">
+        <v>26.05636363636363</v>
+      </c>
+      <c r="J46" t="n">
+        <v>184.1720454545454</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>65.23113636363635</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1078602.272727273</v>
+      </c>
+      <c r="N46" t="n">
+        <v>68.8175</v>
+      </c>
+      <c r="O46" t="n">
+        <v>25.83424634624635</v>
+      </c>
+      <c r="P46" t="n">
+        <v>182.0086191586192</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.103341103341103</v>
+      </c>
+      <c r="R46" t="n">
+        <v>66.47505908905909</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1409329.448329448</v>
+      </c>
+      <c r="T46" t="n">
+        <v>70.94827639027639</v>
+      </c>
+      <c r="U46" t="n">
+        <v>25.99547260361047</v>
+      </c>
+      <c r="V46" t="n">
+        <v>182.1657418001526</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>64.08524292312907</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1016423.169825344</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>67.96443717524953</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>25.6297520661157</v>
+      </c>
+      <c r="D47" t="n">
+        <v>186.5504132231405</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.216528925619835</v>
+      </c>
+      <c r="F47" t="n">
+        <v>72.97520661157024</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5321280.991735538</v>
+      </c>
+      <c r="H47" t="n">
+        <v>76.81652892561983</v>
+      </c>
+      <c r="I47" t="n">
+        <v>26.68874458874459</v>
+      </c>
+      <c r="J47" t="n">
+        <v>185.6223665223665</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.073376623376623</v>
+      </c>
+      <c r="L47" t="n">
+        <v>69.49617604617605</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1990764.790764791</v>
+      </c>
+      <c r="N47" t="n">
+        <v>72.82106782106781</v>
+      </c>
+      <c r="O47" t="n">
+        <v>23.81737774719034</v>
+      </c>
+      <c r="P47" t="n">
+        <v>184.6449125465017</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.128385617935843</v>
+      </c>
+      <c r="R47" t="n">
+        <v>70.3708043777534</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3866672.466408598</v>
+      </c>
+      <c r="T47" t="n">
+        <v>77.24240376564966</v>
+      </c>
+      <c r="U47" t="n">
+        <v>26.94418811002662</v>
+      </c>
+      <c r="V47" t="n">
+        <v>185.0683817321395</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.118495738216235</v>
+      </c>
+      <c r="X47" t="n">
+        <v>69.80358863703584</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2103228.030639133</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>73.18901084939905</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="D48" t="n">
+        <v>183.32</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F48" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1037400</v>
+      </c>
+      <c r="H48" t="n">
+        <v>69.97999999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>25.45206611570248</v>
+      </c>
+      <c r="J48" t="n">
+        <v>183.2471074380165</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>67.04545454545455</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1360103.305785124</v>
+      </c>
+      <c r="N48" t="n">
+        <v>71.03801652892561</v>
+      </c>
+      <c r="O48" t="n">
+        <v>24.89329614461308</v>
+      </c>
+      <c r="P48" t="n">
+        <v>185.0998843987608</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.030678106917237</v>
+      </c>
+      <c r="R48" t="n">
+        <v>65.26908853363773</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1046866.811003853</v>
+      </c>
+      <c r="T48" t="n">
+        <v>69.2467237469709</v>
+      </c>
+      <c r="U48" t="n">
+        <v>23.56668197286638</v>
+      </c>
+      <c r="V48" t="n">
+        <v>182.0834655940428</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>64.17281167857631</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1159419.451042877</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>71.28115552613303</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>27.10209790209791</v>
+      </c>
+      <c r="D49" t="n">
+        <v>181.3921522921523</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>67.47521367521368</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1250264.18026418</v>
+      </c>
+      <c r="H49" t="n">
+        <v>70.13022533022534</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>25.37346197961583</v>
+      </c>
+      <c r="P49" t="n">
+        <v>180.0884310988157</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>65.8332191739884</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1166835.269431423</v>
+      </c>
+      <c r="T49" t="n">
+        <v>70.57649080264466</v>
+      </c>
+      <c r="U49" t="n">
+        <v>22.3875</v>
+      </c>
+      <c r="V49" t="n">
+        <v>180.65</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>62.2375</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>823437.5</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>70.52500000000001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>23.66689623507806</v>
+      </c>
+      <c r="D50" t="n">
+        <v>184.9233241505969</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>70.11099632690542</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3865992.309458219</v>
+      </c>
+      <c r="H50" t="n">
+        <v>76.18893480257115</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>22.82705449210833</v>
+      </c>
+      <c r="P50" t="n">
+        <v>184.6810762486243</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>66.67392677628128</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2307231.237192734</v>
+      </c>
+      <c r="T50" t="n">
+        <v>74.58773132593836</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>25.52047750229569</v>
+      </c>
+      <c r="J51" t="n">
+        <v>184.7290174471993</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.264738292011019</v>
+      </c>
+      <c r="L51" t="n">
+        <v>70.86786042240588</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3244237.832874197</v>
+      </c>
+      <c r="N51" t="n">
+        <v>76.37658402203857</v>
+      </c>
+      <c r="O51" t="n">
+        <v>29</v>
+      </c>
+      <c r="P51" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="T51" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>24.6231770980997</v>
+      </c>
+      <c r="V51" t="n">
+        <v>183.205746338285</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.192188647266047</v>
+      </c>
+      <c r="X51" t="n">
+        <v>69.55463642652498</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>2992488.039308473</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>75.64575599151452</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>26.05734265734266</v>
+      </c>
+      <c r="D52" t="n">
+        <v>182.8741258741259</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>70.44335664335664</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2576153.846153846</v>
+      </c>
+      <c r="H52" t="n">
+        <v>74.4979020979021</v>
+      </c>
+      <c r="I52" t="n">
+        <v>25.88727272727273</v>
+      </c>
+      <c r="J52" t="n">
+        <v>182.7136363636363</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>67.59181818181818</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1341204.545454545</v>
+      </c>
+      <c r="N52" t="n">
+        <v>71.26727272727274</v>
+      </c>
+      <c r="O52" t="n">
+        <v>25.44150277753957</v>
+      </c>
+      <c r="P52" t="n">
+        <v>182.3927914987279</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.003205128205128</v>
+      </c>
+      <c r="R52" t="n">
+        <v>68.70878760159695</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2063652.202498356</v>
+      </c>
+      <c r="T52" t="n">
+        <v>73.52096137171387</v>
+      </c>
+      <c r="U52" t="n">
+        <v>23.8005059015059</v>
+      </c>
+      <c r="V52" t="n">
+        <v>181.7865268620268</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="X52" t="n">
+        <v>66.41397374847375</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1434065.595746846</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>72.67669576719577</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>25.69777777777778</v>
+      </c>
+      <c r="D53" t="n">
+        <v>183.7122222222222</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="F53" t="n">
+        <v>68.19666666666667</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1628027.777777778</v>
+      </c>
+      <c r="H53" t="n">
+        <v>72.25444444444445</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>23.96159663865546</v>
+      </c>
+      <c r="P53" t="n">
+        <v>184.4987990196078</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>64.48167250233428</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1170122.414799253</v>
+      </c>
+      <c r="T53" t="n">
+        <v>71.18651844070961</v>
+      </c>
+      <c r="U53" t="n">
+        <v>23.96527777777778</v>
+      </c>
+      <c r="V53" t="n">
+        <v>182.6527777777778</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" t="n">
+        <v>68.25694444444444</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2353125</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>73.375</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:Z51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1915 +558,1915 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.10330578512397</v>
+        <v>24.48717171717172</v>
       </c>
       <c r="D2" t="n">
-        <v>184.1545454545455</v>
+        <v>184.8768686868687</v>
       </c>
       <c r="E2" t="n">
-        <v>1.179338842975207</v>
+        <v>1.058181818181818</v>
       </c>
       <c r="F2" t="n">
-        <v>73.0900826446281</v>
+        <v>69.75646464646465</v>
       </c>
       <c r="G2" t="n">
-        <v>6146074.38016529</v>
+        <v>2982873.737373737</v>
       </c>
       <c r="H2" t="n">
-        <v>77.47685950413224</v>
+        <v>75.54333333333332</v>
       </c>
       <c r="I2" t="n">
-        <v>28.00818181818182</v>
+        <v>25.31878787878788</v>
       </c>
       <c r="J2" t="n">
-        <v>182.9309090909091</v>
+        <v>184.3144444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>2.413636363636364</v>
+        <v>1.781212121212121</v>
       </c>
       <c r="L2" t="n">
-        <v>82.88454545454546</v>
+        <v>80.50020202020202</v>
       </c>
       <c r="M2" t="n">
-        <v>40085454.54545455</v>
+        <v>34390267.67676768</v>
       </c>
       <c r="N2" t="n">
-        <v>84.66454545454545</v>
+        <v>84.09676767676768</v>
       </c>
       <c r="O2" t="n">
-        <v>26.53778329513624</v>
+        <v>24.72831439896657</v>
       </c>
       <c r="P2" t="n">
-        <v>184.9579220779221</v>
+        <v>184.0096923607794</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.40827731092437</v>
+        <v>1.107739422413336</v>
       </c>
       <c r="R2" t="n">
-        <v>70.29345811051694</v>
+        <v>68.11976407248146</v>
       </c>
       <c r="S2" t="n">
-        <v>3627757.830404889</v>
+        <v>2367220.084364106</v>
       </c>
       <c r="T2" t="n">
-        <v>74.07986121721416</v>
+        <v>73.63034033197076</v>
       </c>
       <c r="U2" t="n">
-        <v>27.10158309001788</v>
+        <v>24.15642184521132</v>
       </c>
       <c r="V2" t="n">
-        <v>182.5357371404763</v>
+        <v>184.4817940149519</v>
       </c>
       <c r="W2" t="n">
-        <v>1.885667641537206</v>
+        <v>1.521579482895272</v>
       </c>
       <c r="X2" t="n">
-        <v>78.98572182246096</v>
+        <v>76.40987382987383</v>
       </c>
       <c r="Y2" t="n">
-        <v>24084349.68895838</v>
+        <v>22494439.3558683</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.47697790132572</v>
+        <v>82.2719227984491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24.68080808080808</v>
+        <v>24.94214876033058</v>
       </c>
       <c r="D3" t="n">
-        <v>184.7545454545455</v>
+        <v>186.5454545454545</v>
       </c>
       <c r="E3" t="n">
-        <v>1.064646464646465</v>
+        <v>1.041322314049587</v>
       </c>
       <c r="F3" t="n">
-        <v>69.889898989899</v>
+        <v>73.32231404958678</v>
       </c>
       <c r="G3" t="n">
-        <v>3047020.202020202</v>
+        <v>5104958.67768595</v>
       </c>
       <c r="H3" t="n">
-        <v>75.58888888888889</v>
+        <v>77.13223140495869</v>
       </c>
       <c r="I3" t="n">
-        <v>26.26590909090909</v>
+        <v>26.67390572390572</v>
       </c>
       <c r="J3" t="n">
-        <v>183.5416666666667</v>
+        <v>183.8352693602693</v>
       </c>
       <c r="K3" t="n">
-        <v>1.634848484848485</v>
+        <v>1.721464646464646</v>
       </c>
       <c r="L3" t="n">
-        <v>76.4189393939394</v>
+        <v>77.52996632996633</v>
       </c>
       <c r="M3" t="n">
-        <v>12592348.48484849</v>
+        <v>18239831.64983165</v>
       </c>
       <c r="N3" t="n">
-        <v>79.57878787878788</v>
+        <v>79.89006734006735</v>
       </c>
       <c r="O3" t="n">
-        <v>25.01872840882503</v>
+        <v>25.4026541882558</v>
       </c>
       <c r="P3" t="n">
-        <v>184.6624034848672</v>
+        <v>183.0104600351125</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.104200214707461</v>
+        <v>1.07102466903269</v>
       </c>
       <c r="R3" t="n">
-        <v>68.39180842864418</v>
+        <v>70.91299251154867</v>
       </c>
       <c r="S3" t="n">
-        <v>2332025.518876364</v>
+        <v>3252643.011276701</v>
       </c>
       <c r="T3" t="n">
-        <v>73.50330147129665</v>
+        <v>74.80333207246309</v>
       </c>
       <c r="U3" t="n">
-        <v>25.14070103428836</v>
+        <v>26.29710258435945</v>
       </c>
       <c r="V3" t="n">
-        <v>181.8332528326614</v>
+        <v>182.2940931668764</v>
       </c>
       <c r="W3" t="n">
-        <v>1.562596304468099</v>
+        <v>1.760422899310199</v>
       </c>
       <c r="X3" t="n">
-        <v>74.70471546367799</v>
+        <v>76.40353739668672</v>
       </c>
       <c r="Y3" t="n">
-        <v>11574638.97422393</v>
+        <v>15881867.18092167</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.13637043187968</v>
+        <v>79.52748934259232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.3460606060606</v>
+        <v>27.96272727272727</v>
       </c>
       <c r="D4" t="n">
-        <v>184.4126262626263</v>
+        <v>183.0218181818182</v>
       </c>
       <c r="E4" t="n">
-        <v>1.808484848484849</v>
+        <v>2.395454545454546</v>
       </c>
       <c r="F4" t="n">
-        <v>80.61474747474747</v>
+        <v>82.8209090909091</v>
       </c>
       <c r="G4" t="n">
-        <v>35162540.40404041</v>
+        <v>39894545.45454545</v>
       </c>
       <c r="H4" t="n">
-        <v>84.22222222222221</v>
+        <v>84.67363636363636</v>
       </c>
       <c r="I4" t="n">
-        <v>25.79545454545455</v>
+        <v>23.99173553719008</v>
       </c>
       <c r="J4" t="n">
-        <v>186.23</v>
+        <v>184.2871900826446</v>
       </c>
       <c r="K4" t="n">
-        <v>1.248181818181818</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>76.07818181818182</v>
+        <v>72.01859504132231</v>
       </c>
       <c r="M4" t="n">
-        <v>13460363.63636364</v>
+        <v>5430578.512396694</v>
       </c>
       <c r="N4" t="n">
-        <v>79.36909090909091</v>
+        <v>77.85330578512398</v>
       </c>
       <c r="O4" t="n">
-        <v>24.4168428978429</v>
+        <v>27.13419178567005</v>
       </c>
       <c r="P4" t="n">
-        <v>184.8154782254782</v>
+        <v>182.4003616464051</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.532947903947904</v>
+        <v>1.886655783829697</v>
       </c>
       <c r="R4" t="n">
-        <v>76.26987382987383</v>
+        <v>79.00864672364672</v>
       </c>
       <c r="S4" t="n">
-        <v>21156981.46113146</v>
+        <v>24048401.07235759</v>
       </c>
       <c r="T4" t="n">
-        <v>82.05887016687015</v>
+        <v>81.47243244678027</v>
       </c>
       <c r="U4" t="n">
-        <v>24.94636711542671</v>
+        <v>23.14157997054606</v>
       </c>
       <c r="V4" t="n">
-        <v>185.0591305860463</v>
+        <v>182.5890715479191</v>
       </c>
       <c r="W4" t="n">
-        <v>1.193529568127091</v>
+        <v>1.062375411150115</v>
       </c>
       <c r="X4" t="n">
-        <v>72.03887250992901</v>
+        <v>68.02060958757859</v>
       </c>
       <c r="Y4" t="n">
-        <v>5762901.734058855</v>
+        <v>2648390.130764688</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.01139701973294</v>
+        <v>74.87350004824938</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.53636363636364</v>
+        <v>25.54132231404959</v>
       </c>
       <c r="D5" t="n">
-        <v>183.9090909090909</v>
+        <v>183.7297520661157</v>
       </c>
       <c r="E5" t="n">
-        <v>1.045454545454545</v>
+        <v>1.37603305785124</v>
       </c>
       <c r="F5" t="n">
-        <v>72.48181818181817</v>
+        <v>73.23388429752066</v>
       </c>
       <c r="G5" t="n">
-        <v>4577272.727272728</v>
+        <v>6951404.958677686</v>
       </c>
       <c r="H5" t="n">
-        <v>76.06363636363636</v>
+        <v>77.45537190082645</v>
       </c>
       <c r="I5" t="n">
-        <v>25.48760330578513</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="J5" t="n">
-        <v>183.7950413223141</v>
+        <v>184.2363636363637</v>
       </c>
       <c r="K5" t="n">
-        <v>1.36198347107438</v>
+        <v>1.207438016528926</v>
       </c>
       <c r="L5" t="n">
-        <v>73.41983471074379</v>
+        <v>73.02892561983471</v>
       </c>
       <c r="M5" t="n">
-        <v>7316859.504132232</v>
+        <v>5968553.719008264</v>
       </c>
       <c r="N5" t="n">
-        <v>77.64545454545454</v>
+        <v>77.41239669421488</v>
       </c>
       <c r="O5" t="n">
-        <v>25.12013542013542</v>
+        <v>25.67393444719531</v>
       </c>
       <c r="P5" t="n">
-        <v>182.4552697302697</v>
+        <v>182.1304464858813</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.136639286639287</v>
+        <v>1.283091883961449</v>
       </c>
       <c r="R5" t="n">
-        <v>69.91116661116661</v>
+        <v>71.61341177341177</v>
       </c>
       <c r="S5" t="n">
-        <v>2937943.158693159</v>
+        <v>4347172.999102348</v>
       </c>
       <c r="T5" t="n">
-        <v>74.6719178969179</v>
+        <v>76.64134939939287</v>
       </c>
       <c r="U5" t="n">
-        <v>25.56330433656521</v>
+        <v>26.57286350903998</v>
       </c>
       <c r="V5" t="n">
-        <v>182.3016826571175</v>
+        <v>184.7808097784569</v>
       </c>
       <c r="W5" t="n">
-        <v>1.272028872898438</v>
+        <v>1.389453781512605</v>
       </c>
       <c r="X5" t="n">
-        <v>71.5465527065527</v>
+        <v>70.33046345811053</v>
       </c>
       <c r="Y5" t="n">
-        <v>4293361.070290417</v>
+        <v>3512656.226126814</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.73273949078296</v>
+        <v>73.98766870384519</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.55454545454545</v>
+        <v>26.22237762237762</v>
       </c>
       <c r="D6" t="n">
-        <v>185.3</v>
+        <v>183.7076923076923</v>
       </c>
       <c r="E6" t="n">
-        <v>1.263636363636364</v>
+        <v>1.616783216783217</v>
       </c>
       <c r="F6" t="n">
-        <v>75.06363636363636</v>
+        <v>76.3944055944056</v>
       </c>
       <c r="G6" t="n">
-        <v>11195681.81818182</v>
+        <v>12678321.67832168</v>
       </c>
       <c r="H6" t="n">
-        <v>79.68181818181819</v>
+        <v>79.63426573426574</v>
       </c>
       <c r="I6" t="n">
-        <v>25.00826446280992</v>
+        <v>25.13492063492064</v>
       </c>
       <c r="J6" t="n">
-        <v>186.603305785124</v>
+        <v>184.6316738816739</v>
       </c>
       <c r="K6" t="n">
-        <v>1.049586776859504</v>
+        <v>1.015079365079365</v>
       </c>
       <c r="L6" t="n">
-        <v>73.33884297520662</v>
+        <v>69.93658008658008</v>
       </c>
       <c r="M6" t="n">
-        <v>5136363.636363637</v>
+        <v>2656121.933621933</v>
       </c>
       <c r="N6" t="n">
-        <v>77.11570247933884</v>
+        <v>74.38225108225109</v>
       </c>
       <c r="O6" t="n">
-        <v>22.96644480934136</v>
+        <v>24.95155619948295</v>
       </c>
       <c r="P6" t="n">
-        <v>184.7342242291553</v>
+        <v>181.7271984189602</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.202148148148148</v>
+        <v>1.550788197131392</v>
       </c>
       <c r="R6" t="n">
-        <v>71.23520780879402</v>
+        <v>74.58407301542303</v>
       </c>
       <c r="S6" t="n">
-        <v>7029183.269476374</v>
+        <v>11541974.43774517</v>
       </c>
       <c r="T6" t="n">
-        <v>78.16315307425653</v>
+        <v>79.26224403502179</v>
       </c>
       <c r="U6" t="n">
-        <v>25.33426193236354</v>
+        <v>25.54059544465559</v>
       </c>
       <c r="V6" t="n">
-        <v>183.2899213145737</v>
+        <v>181.8841578221277</v>
       </c>
       <c r="W6" t="n">
-        <v>1.072076857584879</v>
+        <v>1.040302855039698</v>
       </c>
       <c r="X6" t="n">
-        <v>70.90836288191903</v>
+        <v>67.40725249687657</v>
       </c>
       <c r="Y6" t="n">
-        <v>3268867.758751449</v>
+        <v>1621063.413278451</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.88350884013985</v>
+        <v>72.34852959071004</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>25.94132231404959</v>
       </c>
       <c r="D7" t="n">
-        <v>184.0545454545455</v>
+        <v>186.0181818181818</v>
       </c>
       <c r="E7" t="n">
-        <v>1.136363636363636</v>
+        <v>1.26198347107438</v>
       </c>
       <c r="F7" t="n">
-        <v>72.97272727272727</v>
+        <v>76.08925619834712</v>
       </c>
       <c r="G7" t="n">
-        <v>4746136.363636364</v>
+        <v>13144876.03305785</v>
       </c>
       <c r="H7" t="n">
-        <v>76.57272727272728</v>
+        <v>79.13553719008264</v>
       </c>
       <c r="I7" t="n">
-        <v>26.25909090909091</v>
+        <v>25.88571428571428</v>
       </c>
       <c r="J7" t="n">
-        <v>182.0827272727273</v>
+        <v>187.2525974025974</v>
       </c>
       <c r="K7" t="n">
-        <v>1.71</v>
+        <v>1.52987012987013</v>
       </c>
       <c r="L7" t="n">
-        <v>80.78818181818183</v>
+        <v>78.20649350649352</v>
       </c>
       <c r="M7" t="n">
-        <v>35250545.45454545</v>
+        <v>18650324.67532467</v>
       </c>
       <c r="N7" t="n">
-        <v>82.58363636363637</v>
+        <v>81.52142857142857</v>
       </c>
       <c r="O7" t="n">
-        <v>24.15788461538461</v>
+        <v>24.82488354555974</v>
       </c>
       <c r="P7" t="n">
-        <v>182.8098575498576</v>
+        <v>184.9848120595201</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.040343915343915</v>
+        <v>1.17376111239044</v>
       </c>
       <c r="R7" t="n">
-        <v>70.6698310948311</v>
+        <v>71.84112376935695</v>
       </c>
       <c r="S7" t="n">
-        <v>3462158.781033781</v>
+        <v>5778426.326308399</v>
       </c>
       <c r="T7" t="n">
-        <v>75.41835673585675</v>
+        <v>76.07582417191902</v>
       </c>
       <c r="U7" t="n">
-        <v>24.99373612283829</v>
+        <v>25.38111969523461</v>
       </c>
       <c r="V7" t="n">
-        <v>180.8991268463791</v>
+        <v>186.5566248508795</v>
       </c>
       <c r="W7" t="n">
-        <v>1.552191083770031</v>
+        <v>1.366661010372191</v>
       </c>
       <c r="X7" t="n">
-        <v>75.91953749867837</v>
+        <v>74.84583374584928</v>
       </c>
       <c r="Y7" t="n">
-        <v>15890858.88601852</v>
+        <v>13202699.953997</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.21223496575664</v>
+        <v>78.82436163158214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.43636363636364</v>
+        <v>26.06681818181818</v>
       </c>
       <c r="D8" t="n">
-        <v>184.3818181818181</v>
+        <v>182.2870454545455</v>
       </c>
       <c r="E8" t="n">
-        <v>1.209090909090909</v>
+        <v>2.087727272727273</v>
       </c>
       <c r="F8" t="n">
-        <v>72.18181818181817</v>
+        <v>78.55727272727272</v>
       </c>
       <c r="G8" t="n">
-        <v>3650000</v>
+        <v>21251022.72727273</v>
       </c>
       <c r="H8" t="n">
-        <v>75.73636363636363</v>
+        <v>80.70545454545454</v>
       </c>
       <c r="I8" t="n">
-        <v>26.37363636363636</v>
+        <v>25.22148760330579</v>
       </c>
       <c r="J8" t="n">
-        <v>182.5881818181818</v>
+        <v>184.1404958677686</v>
       </c>
       <c r="K8" t="n">
-        <v>2.149090909090909</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="L8" t="n">
-        <v>78.66636363636363</v>
+        <v>72.12975206611571</v>
       </c>
       <c r="M8" t="n">
-        <v>21377272.72727273</v>
+        <v>4288842.975206612</v>
       </c>
       <c r="N8" t="n">
-        <v>80.59636363636363</v>
+        <v>76.1107438016529</v>
       </c>
       <c r="O8" t="n">
-        <v>25.81782430213465</v>
+        <v>25.34594552990198</v>
       </c>
       <c r="P8" t="n">
-        <v>183.1474308450171</v>
+        <v>182.7396397178475</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.136724137931035</v>
+        <v>1.963514286009749</v>
       </c>
       <c r="R8" t="n">
-        <v>70.13735063786788</v>
+        <v>76.28715226948893</v>
       </c>
       <c r="S8" t="n">
-        <v>2714007.06707086</v>
+        <v>17566886.10747322</v>
       </c>
       <c r="T8" t="n">
-        <v>74.33269609700645</v>
+        <v>80.59263702100816</v>
       </c>
       <c r="U8" t="n">
-        <v>25.29662779111055</v>
+        <v>24.8531746031746</v>
       </c>
       <c r="V8" t="n">
-        <v>182.86790482506</v>
+        <v>182.0717010262465</v>
       </c>
       <c r="W8" t="n">
-        <v>1.962929490688111</v>
+        <v>1.113728022818932</v>
       </c>
       <c r="X8" t="n">
-        <v>76.04017371198407</v>
+        <v>69.58585606312879</v>
       </c>
       <c r="Y8" t="n">
-        <v>16401725.28875977</v>
+        <v>2894139.097434552</v>
       </c>
       <c r="Z8" t="n">
-        <v>80.38639920424403</v>
+        <v>74.7756734006734</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.75723905723906</v>
+        <v>26.4198347107438</v>
       </c>
       <c r="D9" t="n">
-        <v>183.951936026936</v>
+        <v>182.2107438016529</v>
       </c>
       <c r="E9" t="n">
-        <v>1.738131313131313</v>
+        <v>1.729752066115703</v>
       </c>
       <c r="F9" t="n">
-        <v>77.496632996633</v>
+        <v>80.77355371900826</v>
       </c>
       <c r="G9" t="n">
-        <v>18198164.98316498</v>
+        <v>34887851.23966942</v>
       </c>
       <c r="H9" t="n">
-        <v>79.82340067340067</v>
+        <v>82.47272727272728</v>
       </c>
       <c r="I9" t="n">
-        <v>24.88111888111888</v>
+        <v>24.68181818181818</v>
       </c>
       <c r="J9" t="n">
-        <v>184.7482517482517</v>
+        <v>185.5181818181818</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>1.281818181818182</v>
       </c>
       <c r="L9" t="n">
-        <v>69.98601398601399</v>
+        <v>75.12727272727273</v>
       </c>
       <c r="M9" t="n">
-        <v>2770104.895104895</v>
+        <v>11041818.18181818</v>
       </c>
       <c r="N9" t="n">
-        <v>74.62937062937064</v>
+        <v>79.58181818181819</v>
       </c>
       <c r="O9" t="n">
-        <v>26.4445965457121</v>
+        <v>24.90901144856957</v>
       </c>
       <c r="P9" t="n">
-        <v>182.1903793987604</v>
+        <v>181.1425217320025</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.794692222981697</v>
+        <v>1.512801672793229</v>
       </c>
       <c r="R9" t="n">
-        <v>76.55374874934371</v>
+        <v>75.79453752744634</v>
       </c>
       <c r="S9" t="n">
-        <v>16200766.63744341</v>
+        <v>15219224.27376779</v>
       </c>
       <c r="T9" t="n">
-        <v>79.53111253099812</v>
+        <v>79.08278045015309</v>
       </c>
       <c r="U9" t="n">
-        <v>25.91443786982249</v>
+        <v>23.0821855500821</v>
       </c>
       <c r="V9" t="n">
-        <v>181.7165142549758</v>
+        <v>184.6805205254516</v>
       </c>
       <c r="W9" t="n">
-        <v>1.042313071543841</v>
+        <v>1.202333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>67.57424421732115</v>
+        <v>71.2915041050903</v>
       </c>
       <c r="Y9" t="n">
-        <v>1616877.407208177</v>
+        <v>6950567.528735632</v>
       </c>
       <c r="Z9" t="n">
-        <v>72.17388918773534</v>
+        <v>78.0733382594417</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.06363636363636</v>
+        <v>25.34710743801653</v>
       </c>
       <c r="D10" t="n">
-        <v>184.6545454545455</v>
+        <v>184.4380165289256</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>1.173553719008265</v>
       </c>
       <c r="F10" t="n">
-        <v>72.15454545454546</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="G10" t="n">
-        <v>5452272.727272728</v>
+        <v>3835330.578512396</v>
       </c>
       <c r="H10" t="n">
-        <v>77.78181818181818</v>
+        <v>75.84297520661157</v>
       </c>
       <c r="I10" t="n">
-        <v>25.85384615384616</v>
+        <v>25.8037037037037</v>
       </c>
       <c r="J10" t="n">
-        <v>187.1951048951049</v>
+        <v>181.1512345679012</v>
       </c>
       <c r="K10" t="n">
-        <v>1.53986013986014</v>
+        <v>1.076234567901234</v>
       </c>
       <c r="L10" t="n">
-        <v>78.30699300699301</v>
+        <v>71.1848765432099</v>
       </c>
       <c r="M10" t="n">
-        <v>19034965.03496503</v>
+        <v>3585370.370370371</v>
       </c>
       <c r="N10" t="n">
-        <v>81.62307692307692</v>
+        <v>73.63703703703703</v>
       </c>
       <c r="O10" t="n">
-        <v>23.36307449072667</v>
+        <v>25.769700414528</v>
       </c>
       <c r="P10" t="n">
-        <v>182.6972344177562</v>
+        <v>183.2808811877777</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.08224931590149</v>
+        <v>1.178140824692549</v>
       </c>
       <c r="R10" t="n">
-        <v>68.24991669200365</v>
+        <v>69.9454935868729</v>
       </c>
       <c r="S10" t="n">
-        <v>2627385.177865612</v>
+        <v>2704018.66237211</v>
       </c>
       <c r="T10" t="n">
-        <v>74.82169534813013</v>
+        <v>74.26468875951636</v>
       </c>
       <c r="U10" t="n">
-        <v>25.48735967179111</v>
+        <v>26.54628619528619</v>
       </c>
       <c r="V10" t="n">
-        <v>186.6171936263909</v>
+        <v>183.7406428386428</v>
       </c>
       <c r="W10" t="n">
-        <v>1.383031383951117</v>
+        <v>1.255309505309505</v>
       </c>
       <c r="X10" t="n">
-        <v>74.97006947777851</v>
+        <v>70.05600543900543</v>
       </c>
       <c r="Y10" t="n">
-        <v>13449298.17531038</v>
+        <v>2813568.1002331</v>
       </c>
       <c r="Z10" t="n">
-        <v>78.82860246714762</v>
+        <v>72.48127298627298</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25.72659285159285</v>
+        <v>25.0446510560147</v>
       </c>
       <c r="D11" t="n">
-        <v>186.3965617715618</v>
+        <v>184.2012167125804</v>
       </c>
       <c r="E11" t="n">
-        <v>1.786810411810412</v>
+        <v>1.140266299357209</v>
       </c>
       <c r="F11" t="n">
-        <v>80.37869075369075</v>
+        <v>73.0121671258035</v>
       </c>
       <c r="G11" t="n">
-        <v>30229817.4048174</v>
+        <v>4763096.877869605</v>
       </c>
       <c r="H11" t="n">
-        <v>83.96299533799535</v>
+        <v>76.64267676767678</v>
       </c>
       <c r="I11" t="n">
-        <v>25.67037037037037</v>
+        <v>25.62402874902875</v>
       </c>
       <c r="J11" t="n">
-        <v>181.4456790123457</v>
+        <v>186.4061771561772</v>
       </c>
       <c r="K11" t="n">
-        <v>1.045679012345679</v>
+        <v>1.755827505827506</v>
       </c>
       <c r="L11" t="n">
-        <v>70.95432098765433</v>
+        <v>80.21416083916083</v>
       </c>
       <c r="M11" t="n">
-        <v>3293703.703703704</v>
+        <v>29955778.94327894</v>
       </c>
       <c r="N11" t="n">
-        <v>73.51481481481481</v>
+        <v>83.81876456876458</v>
       </c>
       <c r="O11" t="n">
-        <v>24.8135679461652</v>
+        <v>24.26546509046509</v>
       </c>
       <c r="P11" t="n">
-        <v>183.9314402861314</v>
+        <v>182.7177156177156</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76277271165143</v>
+        <v>1.037638287638288</v>
       </c>
       <c r="R11" t="n">
-        <v>76.16277464335816</v>
+        <v>70.56276131276131</v>
       </c>
       <c r="S11" t="n">
-        <v>15622918.12363838</v>
+        <v>3403146.991896993</v>
       </c>
       <c r="T11" t="n">
-        <v>81.49824943807782</v>
+        <v>75.29687072187072</v>
       </c>
       <c r="U11" t="n">
-        <v>26.03937376990517</v>
+        <v>24.8432502204127</v>
       </c>
       <c r="V11" t="n">
-        <v>183.3066870363489</v>
+        <v>183.798079082118</v>
       </c>
       <c r="W11" t="n">
-        <v>1.219601690133091</v>
+        <v>1.744378062821999</v>
       </c>
       <c r="X11" t="n">
-        <v>69.62724802840745</v>
+        <v>76.23635323867589</v>
       </c>
       <c r="Y11" t="n">
-        <v>2557524.612907222</v>
+        <v>15836567.78919022</v>
       </c>
       <c r="Z11" t="n">
-        <v>72.58290323024623</v>
+        <v>81.52249692971661</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>24.68080808080808</v>
+        <v>25.13492063492064</v>
       </c>
       <c r="D12" t="n">
-        <v>184.7545454545455</v>
+        <v>184.6316738816739</v>
       </c>
       <c r="E12" t="n">
-        <v>1.064646464646465</v>
+        <v>1.015079365079365</v>
       </c>
       <c r="F12" t="n">
-        <v>69.889898989899</v>
+        <v>69.93658008658008</v>
       </c>
       <c r="G12" t="n">
-        <v>3047020.202020202</v>
+        <v>2656121.933621933</v>
       </c>
       <c r="H12" t="n">
-        <v>75.58888888888889</v>
+        <v>74.38225108225109</v>
       </c>
       <c r="I12" t="n">
-        <v>25.3460606060606</v>
+        <v>25.94132231404959</v>
       </c>
       <c r="J12" t="n">
-        <v>184.4126262626263</v>
+        <v>186.0181818181818</v>
       </c>
       <c r="K12" t="n">
-        <v>1.808484848484849</v>
+        <v>1.26198347107438</v>
       </c>
       <c r="L12" t="n">
-        <v>80.61474747474747</v>
+        <v>76.08925619834712</v>
       </c>
       <c r="M12" t="n">
-        <v>35162540.40404041</v>
+        <v>13144876.03305785</v>
       </c>
       <c r="N12" t="n">
-        <v>84.22222222222221</v>
+        <v>79.13553719008264</v>
       </c>
       <c r="O12" t="n">
-        <v>25.01872840882503</v>
+        <v>25.54059544465559</v>
       </c>
       <c r="P12" t="n">
-        <v>184.6624034848672</v>
+        <v>181.8841578221277</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.104200214707461</v>
+        <v>1.040302855039698</v>
       </c>
       <c r="R12" t="n">
-        <v>68.39180842864418</v>
+        <v>67.40725249687657</v>
       </c>
       <c r="S12" t="n">
-        <v>2332025.518876364</v>
+        <v>1621063.413278451</v>
       </c>
       <c r="T12" t="n">
-        <v>73.50330147129665</v>
+        <v>72.34852959071004</v>
       </c>
       <c r="U12" t="n">
-        <v>24.4168428978429</v>
+        <v>24.82488354555974</v>
       </c>
       <c r="V12" t="n">
-        <v>184.8154782254782</v>
+        <v>184.9848120595201</v>
       </c>
       <c r="W12" t="n">
-        <v>1.532947903947904</v>
+        <v>1.17376111239044</v>
       </c>
       <c r="X12" t="n">
-        <v>76.26987382987383</v>
+        <v>71.84112376935695</v>
       </c>
       <c r="Y12" t="n">
-        <v>21156981.46113146</v>
+        <v>5778426.326308399</v>
       </c>
       <c r="Z12" t="n">
-        <v>82.05887016687015</v>
+        <v>76.07582417191902</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>25.00826446280992</v>
+        <v>27.96272727272727</v>
       </c>
       <c r="D13" t="n">
-        <v>186.603305785124</v>
+        <v>183.0218181818182</v>
       </c>
       <c r="E13" t="n">
-        <v>1.049586776859504</v>
+        <v>2.395454545454546</v>
       </c>
       <c r="F13" t="n">
-        <v>73.33884297520662</v>
+        <v>82.8209090909091</v>
       </c>
       <c r="G13" t="n">
-        <v>5136363.636363637</v>
+        <v>39894545.45454545</v>
       </c>
       <c r="H13" t="n">
-        <v>77.11570247933884</v>
+        <v>84.67363636363636</v>
       </c>
       <c r="I13" t="n">
-        <v>26.75723905723906</v>
+        <v>25.88571428571428</v>
       </c>
       <c r="J13" t="n">
-        <v>183.951936026936</v>
+        <v>187.2525974025974</v>
       </c>
       <c r="K13" t="n">
-        <v>1.738131313131313</v>
+        <v>1.52987012987013</v>
       </c>
       <c r="L13" t="n">
-        <v>77.496632996633</v>
+        <v>78.20649350649352</v>
       </c>
       <c r="M13" t="n">
-        <v>18198164.98316498</v>
+        <v>18650324.67532467</v>
       </c>
       <c r="N13" t="n">
-        <v>79.82340067340067</v>
+        <v>81.52142857142857</v>
       </c>
       <c r="O13" t="n">
-        <v>25.33426193236354</v>
+        <v>27.13419178567005</v>
       </c>
       <c r="P13" t="n">
-        <v>183.2899213145737</v>
+        <v>182.4003616464051</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.072076857584879</v>
+        <v>1.886655783829697</v>
       </c>
       <c r="R13" t="n">
-        <v>70.90836288191903</v>
+        <v>79.00864672364672</v>
       </c>
       <c r="S13" t="n">
-        <v>3268867.758751449</v>
+        <v>24048401.07235759</v>
       </c>
       <c r="T13" t="n">
-        <v>74.88350884013985</v>
+        <v>81.47243244678027</v>
       </c>
       <c r="U13" t="n">
-        <v>26.4445965457121</v>
+        <v>25.38111969523461</v>
       </c>
       <c r="V13" t="n">
-        <v>182.1903793987604</v>
+        <v>186.5566248508795</v>
       </c>
       <c r="W13" t="n">
-        <v>1.794692222981697</v>
+        <v>1.366661010372191</v>
       </c>
       <c r="X13" t="n">
-        <v>76.55374874934371</v>
+        <v>74.84583374584928</v>
       </c>
       <c r="Y13" t="n">
-        <v>16200766.63744341</v>
+        <v>13202699.953997</v>
       </c>
       <c r="Z13" t="n">
-        <v>79.53111253099812</v>
+        <v>78.82436163158214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>28.00818181818182</v>
+        <v>24.68181818181818</v>
       </c>
       <c r="D14" t="n">
-        <v>182.9309090909091</v>
+        <v>185.5181818181818</v>
       </c>
       <c r="E14" t="n">
-        <v>2.413636363636364</v>
+        <v>1.281818181818182</v>
       </c>
       <c r="F14" t="n">
-        <v>82.88454545454546</v>
+        <v>75.12727272727273</v>
       </c>
       <c r="G14" t="n">
-        <v>40085454.54545455</v>
+        <v>11041818.18181818</v>
       </c>
       <c r="H14" t="n">
-        <v>84.66454545454545</v>
+        <v>79.58181818181819</v>
       </c>
       <c r="I14" t="n">
-        <v>24.06363636363636</v>
+        <v>25.22148760330579</v>
       </c>
       <c r="J14" t="n">
-        <v>184.6545454545455</v>
+        <v>184.1404958677686</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="L14" t="n">
-        <v>72.15454545454546</v>
+        <v>72.12975206611571</v>
       </c>
       <c r="M14" t="n">
-        <v>5452272.727272728</v>
+        <v>4288842.975206612</v>
       </c>
       <c r="N14" t="n">
-        <v>77.78181818181818</v>
+        <v>76.1107438016529</v>
       </c>
       <c r="O14" t="n">
-        <v>27.10158309001788</v>
+        <v>23.0821855500821</v>
       </c>
       <c r="P14" t="n">
-        <v>182.5357371404763</v>
+        <v>184.6805205254516</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.885667641537206</v>
+        <v>1.202333333333333</v>
       </c>
       <c r="R14" t="n">
-        <v>78.98572182246096</v>
+        <v>71.2915041050903</v>
       </c>
       <c r="S14" t="n">
-        <v>24084349.68895838</v>
+        <v>6950567.528735632</v>
       </c>
       <c r="T14" t="n">
-        <v>81.47697790132572</v>
+        <v>78.0733382594417</v>
       </c>
       <c r="U14" t="n">
-        <v>23.36307449072667</v>
+        <v>24.8531746031746</v>
       </c>
       <c r="V14" t="n">
-        <v>182.6972344177562</v>
+        <v>182.0717010262465</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08224931590149</v>
+        <v>1.113728022818932</v>
       </c>
       <c r="X14" t="n">
-        <v>68.24991669200365</v>
+        <v>69.58585606312879</v>
       </c>
       <c r="Y14" t="n">
-        <v>2627385.177865612</v>
+        <v>2894139.097434552</v>
       </c>
       <c r="Z14" t="n">
-        <v>74.82169534813013</v>
+        <v>74.7756734006734</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.48760330578513</v>
+        <v>23.99173553719008</v>
       </c>
       <c r="D15" t="n">
-        <v>183.7950413223141</v>
+        <v>184.2871900826446</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36198347107438</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>73.41983471074379</v>
+        <v>72.01859504132231</v>
       </c>
       <c r="G15" t="n">
-        <v>7316859.504132232</v>
+        <v>5430578.512396694</v>
       </c>
       <c r="H15" t="n">
-        <v>77.64545454545454</v>
+        <v>77.85330578512398</v>
       </c>
       <c r="I15" t="n">
-        <v>26.10330578512397</v>
+        <v>25.34710743801653</v>
       </c>
       <c r="J15" t="n">
-        <v>184.1545454545455</v>
+        <v>184.4380165289256</v>
       </c>
       <c r="K15" t="n">
-        <v>1.179338842975207</v>
+        <v>1.173553719008265</v>
       </c>
       <c r="L15" t="n">
-        <v>73.0900826446281</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="M15" t="n">
-        <v>6146074.38016529</v>
+        <v>3835330.578512396</v>
       </c>
       <c r="N15" t="n">
-        <v>77.47685950413224</v>
+        <v>75.84297520661157</v>
       </c>
       <c r="O15" t="n">
-        <v>25.56330433656521</v>
+        <v>23.14157997054606</v>
       </c>
       <c r="P15" t="n">
-        <v>182.3016826571175</v>
+        <v>182.5890715479191</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.272028872898438</v>
+        <v>1.062375411150115</v>
       </c>
       <c r="R15" t="n">
-        <v>71.5465527065527</v>
+        <v>68.02060958757859</v>
       </c>
       <c r="S15" t="n">
-        <v>4293361.070290417</v>
+        <v>2648390.130764688</v>
       </c>
       <c r="T15" t="n">
-        <v>76.73273949078296</v>
+        <v>74.87350004824938</v>
       </c>
       <c r="U15" t="n">
-        <v>26.53778329513624</v>
+        <v>25.769700414528</v>
       </c>
       <c r="V15" t="n">
-        <v>184.9579220779221</v>
+        <v>183.2808811877777</v>
       </c>
       <c r="W15" t="n">
-        <v>1.40827731092437</v>
+        <v>1.178140824692549</v>
       </c>
       <c r="X15" t="n">
-        <v>70.29345811051694</v>
+        <v>69.9454935868729</v>
       </c>
       <c r="Y15" t="n">
-        <v>3627757.830404889</v>
+        <v>2704018.66237211</v>
       </c>
       <c r="Z15" t="n">
-        <v>74.07986121721416</v>
+        <v>74.26468875951636</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>26.26590909090909</v>
+        <v>26.67390572390572</v>
       </c>
       <c r="D16" t="n">
-        <v>183.5416666666667</v>
+        <v>183.8352693602693</v>
       </c>
       <c r="E16" t="n">
-        <v>1.634848484848485</v>
+        <v>1.721464646464646</v>
       </c>
       <c r="F16" t="n">
-        <v>76.4189393939394</v>
+        <v>77.52996632996633</v>
       </c>
       <c r="G16" t="n">
-        <v>12592348.48484849</v>
+        <v>18239831.64983165</v>
       </c>
       <c r="H16" t="n">
-        <v>79.57878787878788</v>
+        <v>79.89006734006735</v>
       </c>
       <c r="I16" t="n">
-        <v>24.88111888111888</v>
+        <v>25.31878787878788</v>
       </c>
       <c r="J16" t="n">
-        <v>184.7482517482517</v>
+        <v>184.3144444444445</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>1.781212121212121</v>
       </c>
       <c r="L16" t="n">
-        <v>69.98601398601399</v>
+        <v>80.50020202020202</v>
       </c>
       <c r="M16" t="n">
-        <v>2770104.895104895</v>
+        <v>34390267.67676768</v>
       </c>
       <c r="N16" t="n">
-        <v>74.62937062937064</v>
+        <v>84.09676767676768</v>
       </c>
       <c r="O16" t="n">
-        <v>25.14070103428836</v>
+        <v>26.29710258435945</v>
       </c>
       <c r="P16" t="n">
-        <v>181.8332528326614</v>
+        <v>182.2940931668764</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.562596304468099</v>
+        <v>1.760422899310199</v>
       </c>
       <c r="R16" t="n">
-        <v>74.70471546367799</v>
+        <v>76.40353739668672</v>
       </c>
       <c r="S16" t="n">
-        <v>11574638.97422393</v>
+        <v>15881867.18092167</v>
       </c>
       <c r="T16" t="n">
-        <v>79.13637043187968</v>
+        <v>79.52748934259232</v>
       </c>
       <c r="U16" t="n">
-        <v>25.91443786982249</v>
+        <v>24.15642184521132</v>
       </c>
       <c r="V16" t="n">
-        <v>181.7165142549758</v>
+        <v>184.4817940149519</v>
       </c>
       <c r="W16" t="n">
-        <v>1.042313071543841</v>
+        <v>1.521579482895272</v>
       </c>
       <c r="X16" t="n">
-        <v>67.57424421732115</v>
+        <v>76.40987382987383</v>
       </c>
       <c r="Y16" t="n">
-        <v>1616877.407208177</v>
+        <v>22494439.3558683</v>
       </c>
       <c r="Z16" t="n">
-        <v>72.17388918773534</v>
+        <v>82.2719227984491</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>25.79545454545455</v>
+        <v>26.4198347107438</v>
       </c>
       <c r="D17" t="n">
-        <v>186.23</v>
+        <v>182.2107438016529</v>
       </c>
       <c r="E17" t="n">
-        <v>1.248181818181818</v>
+        <v>1.729752066115703</v>
       </c>
       <c r="F17" t="n">
-        <v>76.07818181818182</v>
+        <v>80.77355371900826</v>
       </c>
       <c r="G17" t="n">
-        <v>13460363.63636364</v>
+        <v>34887851.23966942</v>
       </c>
       <c r="H17" t="n">
-        <v>79.36909090909091</v>
+        <v>82.47272727272728</v>
       </c>
       <c r="I17" t="n">
-        <v>25.85384615384616</v>
+        <v>24.48717171717172</v>
       </c>
       <c r="J17" t="n">
-        <v>187.1951048951049</v>
+        <v>184.8768686868687</v>
       </c>
       <c r="K17" t="n">
-        <v>1.53986013986014</v>
+        <v>1.058181818181818</v>
       </c>
       <c r="L17" t="n">
-        <v>78.30699300699301</v>
+        <v>69.75646464646465</v>
       </c>
       <c r="M17" t="n">
-        <v>19034965.03496503</v>
+        <v>2982873.737373737</v>
       </c>
       <c r="N17" t="n">
-        <v>81.62307692307692</v>
+        <v>75.54333333333332</v>
       </c>
       <c r="O17" t="n">
-        <v>24.94636711542671</v>
+        <v>24.90901144856957</v>
       </c>
       <c r="P17" t="n">
-        <v>185.0591305860463</v>
+        <v>181.1425217320025</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.193529568127091</v>
+        <v>1.512801672793229</v>
       </c>
       <c r="R17" t="n">
-        <v>72.03887250992901</v>
+        <v>75.79453752744634</v>
       </c>
       <c r="S17" t="n">
-        <v>5762901.734058855</v>
+        <v>15219224.27376779</v>
       </c>
       <c r="T17" t="n">
-        <v>76.01139701973294</v>
+        <v>79.08278045015309</v>
       </c>
       <c r="U17" t="n">
-        <v>25.48735967179111</v>
+        <v>24.72831439896657</v>
       </c>
       <c r="V17" t="n">
-        <v>186.6171936263909</v>
+        <v>184.0096923607794</v>
       </c>
       <c r="W17" t="n">
-        <v>1.383031383951117</v>
+        <v>1.107739422413336</v>
       </c>
       <c r="X17" t="n">
-        <v>74.97006947777851</v>
+        <v>68.11976407248146</v>
       </c>
       <c r="Y17" t="n">
-        <v>13449298.17531038</v>
+        <v>2367220.084364106</v>
       </c>
       <c r="Z17" t="n">
-        <v>78.82860246714762</v>
+        <v>73.63034033197076</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.53636363636364</v>
+        <v>26.22237762237762</v>
       </c>
       <c r="D18" t="n">
-        <v>183.9090909090909</v>
+        <v>183.7076923076923</v>
       </c>
       <c r="E18" t="n">
-        <v>1.045454545454545</v>
+        <v>1.616783216783217</v>
       </c>
       <c r="F18" t="n">
-        <v>72.48181818181817</v>
+        <v>76.3944055944056</v>
       </c>
       <c r="G18" t="n">
-        <v>4577272.727272728</v>
+        <v>12678321.67832168</v>
       </c>
       <c r="H18" t="n">
-        <v>76.06363636363636</v>
+        <v>79.63426573426574</v>
       </c>
       <c r="I18" t="n">
-        <v>26.95909090909091</v>
+        <v>25.54132231404959</v>
       </c>
       <c r="J18" t="n">
-        <v>181.5780303030303</v>
+        <v>183.7297520661157</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>1.37603305785124</v>
       </c>
       <c r="L18" t="n">
-        <v>67.51060606060607</v>
+        <v>73.23388429752066</v>
       </c>
       <c r="M18" t="n">
-        <v>1287954.545454546</v>
+        <v>6951404.958677686</v>
       </c>
       <c r="N18" t="n">
-        <v>70.27575757575758</v>
+        <v>77.45537190082645</v>
       </c>
       <c r="O18" t="n">
-        <v>25.12013542013542</v>
+        <v>24.95155619948295</v>
       </c>
       <c r="P18" t="n">
-        <v>182.4552697302697</v>
+        <v>181.7271984189602</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.136639286639287</v>
+        <v>1.550788197131392</v>
       </c>
       <c r="R18" t="n">
-        <v>69.91116661116661</v>
+        <v>74.58407301542303</v>
       </c>
       <c r="S18" t="n">
-        <v>2937943.158693159</v>
+        <v>11541974.43774517</v>
       </c>
       <c r="T18" t="n">
-        <v>74.6719178969179</v>
+        <v>79.26224403502179</v>
       </c>
       <c r="U18" t="n">
-        <v>25.41676329842997</v>
+        <v>25.67393444719531</v>
       </c>
       <c r="V18" t="n">
-        <v>179.4409926647427</v>
+        <v>182.1304464858813</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.283091883961449</v>
       </c>
       <c r="X18" t="n">
-        <v>65.99645752395752</v>
+        <v>71.61341177341177</v>
       </c>
       <c r="Y18" t="n">
-        <v>1207054.982054982</v>
+        <v>4347172.999102348</v>
       </c>
       <c r="Z18" t="n">
-        <v>70.95946760030094</v>
+        <v>76.64134939939287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>26.25909090909091</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="D19" t="n">
-        <v>182.0827272727273</v>
+        <v>184.2363636363637</v>
       </c>
       <c r="E19" t="n">
-        <v>1.71</v>
+        <v>1.207438016528926</v>
       </c>
       <c r="F19" t="n">
-        <v>80.78818181818183</v>
+        <v>73.02892561983471</v>
       </c>
       <c r="G19" t="n">
-        <v>35250545.45454545</v>
+        <v>5968553.719008264</v>
       </c>
       <c r="H19" t="n">
-        <v>82.58363636363637</v>
+        <v>77.41239669421488</v>
       </c>
       <c r="I19" t="n">
-        <v>26.23232323232323</v>
+        <v>25.0446510560147</v>
       </c>
       <c r="J19" t="n">
-        <v>184.4242424242424</v>
+        <v>184.2012167125804</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.140266299357209</v>
       </c>
       <c r="L19" t="n">
-        <v>67.01010101010101</v>
+        <v>73.0121671258035</v>
       </c>
       <c r="M19" t="n">
-        <v>1316919.191919192</v>
+        <v>4763096.877869605</v>
       </c>
       <c r="N19" t="n">
-        <v>70.52525252525253</v>
+        <v>76.64267676767678</v>
       </c>
       <c r="O19" t="n">
-        <v>24.99373612283829</v>
+        <v>26.57286350903998</v>
       </c>
       <c r="P19" t="n">
-        <v>180.8991268463791</v>
+        <v>184.7808097784569</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.552191083770031</v>
+        <v>1.389453781512605</v>
       </c>
       <c r="R19" t="n">
-        <v>75.91953749867837</v>
+        <v>70.33046345811053</v>
       </c>
       <c r="S19" t="n">
-        <v>15890858.88601852</v>
+        <v>3512656.226126814</v>
       </c>
       <c r="T19" t="n">
-        <v>79.21223496575664</v>
+        <v>73.98766870384519</v>
       </c>
       <c r="U19" t="n">
-        <v>24.87786770037978</v>
+        <v>24.26546509046509</v>
       </c>
       <c r="V19" t="n">
-        <v>183.4569136428073</v>
+        <v>182.7177156177156</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.037638287638288</v>
       </c>
       <c r="X19" t="n">
-        <v>64.69145680942783</v>
+        <v>70.56276131276131</v>
       </c>
       <c r="Y19" t="n">
-        <v>1066359.031878839</v>
+        <v>3403146.991896993</v>
       </c>
       <c r="Z19" t="n">
-        <v>69.80983859582892</v>
+        <v>75.29687072187072</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.37727272727273</v>
+        <v>25.62402874902875</v>
       </c>
       <c r="D20" t="n">
-        <v>182.9618181818182</v>
+        <v>186.4061771561772</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>1.755827505827506</v>
       </c>
       <c r="F20" t="n">
-        <v>67.02000000000001</v>
+        <v>80.21416083916083</v>
       </c>
       <c r="G20" t="n">
-        <v>1374063.636363636</v>
+        <v>29955778.94327894</v>
       </c>
       <c r="H20" t="n">
-        <v>71.12181818181818</v>
+        <v>83.81876456876458</v>
       </c>
       <c r="I20" t="n">
-        <v>24.88111888111888</v>
+        <v>26.06681818181818</v>
       </c>
       <c r="J20" t="n">
-        <v>184.7482517482517</v>
+        <v>182.2870454545455</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2.087727272727273</v>
       </c>
       <c r="L20" t="n">
-        <v>69.98601398601399</v>
+        <v>78.55727272727272</v>
       </c>
       <c r="M20" t="n">
-        <v>2770104.895104895</v>
+        <v>21251022.72727273</v>
       </c>
       <c r="N20" t="n">
-        <v>74.62937062937064</v>
+        <v>80.70545454545454</v>
       </c>
       <c r="O20" t="n">
-        <v>23.76014382094667</v>
+        <v>24.8432502204127</v>
       </c>
       <c r="P20" t="n">
-        <v>182.3692724709074</v>
+        <v>183.798079082118</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>1.744378062821999</v>
       </c>
       <c r="R20" t="n">
-        <v>64.16933094167203</v>
+        <v>76.23635323867589</v>
       </c>
       <c r="S20" t="n">
-        <v>1156315.046940815</v>
+        <v>15836567.78919022</v>
       </c>
       <c r="T20" t="n">
-        <v>71.03003298350824</v>
+        <v>81.52249692971661</v>
       </c>
       <c r="U20" t="n">
-        <v>25.91443786982249</v>
+        <v>25.34594552990198</v>
       </c>
       <c r="V20" t="n">
-        <v>181.7165142549758</v>
+        <v>182.7396397178475</v>
       </c>
       <c r="W20" t="n">
-        <v>1.042313071543841</v>
+        <v>1.963514286009749</v>
       </c>
       <c r="X20" t="n">
-        <v>67.57424421732115</v>
+        <v>76.28715226948893</v>
       </c>
       <c r="Y20" t="n">
-        <v>1616877.407208177</v>
+        <v>17566886.10747322</v>
       </c>
       <c r="Z20" t="n">
-        <v>72.17388918773534</v>
+        <v>80.59263702100816</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>24.68080808080808</v>
+        <v>24.94214876033058</v>
       </c>
       <c r="D21" t="n">
-        <v>184.7545454545455</v>
+        <v>186.5454545454545</v>
       </c>
       <c r="E21" t="n">
-        <v>1.064646464646465</v>
+        <v>1.041322314049587</v>
       </c>
       <c r="F21" t="n">
-        <v>69.889898989899</v>
+        <v>73.32231404958678</v>
       </c>
       <c r="G21" t="n">
-        <v>3047020.202020202</v>
+        <v>5104958.67768595</v>
       </c>
       <c r="H21" t="n">
-        <v>75.58888888888889</v>
+        <v>77.13223140495869</v>
       </c>
       <c r="I21" t="n">
-        <v>26.21969696969697</v>
+        <v>25.8037037037037</v>
       </c>
       <c r="J21" t="n">
-        <v>183.0303030303031</v>
+        <v>181.1512345679012</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>1.076234567901234</v>
       </c>
       <c r="L21" t="n">
-        <v>70.45454545454545</v>
+        <v>71.1848765432099</v>
       </c>
       <c r="M21" t="n">
-        <v>2521590.909090909</v>
+        <v>3585370.370370371</v>
       </c>
       <c r="N21" t="n">
-        <v>74.28030303030303</v>
+        <v>73.63703703703703</v>
       </c>
       <c r="O21" t="n">
-        <v>25.01872840882503</v>
+        <v>25.4026541882558</v>
       </c>
       <c r="P21" t="n">
-        <v>184.6624034848672</v>
+        <v>183.0104600351125</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.104200214707461</v>
+        <v>1.07102466903269</v>
       </c>
       <c r="R21" t="n">
-        <v>68.39180842864418</v>
+        <v>70.91299251154867</v>
       </c>
       <c r="S21" t="n">
-        <v>2332025.518876364</v>
+        <v>3252643.011276701</v>
       </c>
       <c r="T21" t="n">
-        <v>73.50330147129665</v>
+        <v>74.80333207246309</v>
       </c>
       <c r="U21" t="n">
-        <v>25.43375965151327</v>
+        <v>26.54628619528619</v>
       </c>
       <c r="V21" t="n">
-        <v>182.39419025352</v>
+        <v>183.7406428386428</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.255309505309505</v>
       </c>
       <c r="X21" t="n">
-        <v>68.43747212931994</v>
+        <v>70.05600543900543</v>
       </c>
       <c r="Y21" t="n">
-        <v>1973982.049217556</v>
+        <v>2813568.1002331</v>
       </c>
       <c r="Z21" t="n">
-        <v>73.31346902225526</v>
+        <v>72.48127298627298</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>23.65545454545454</v>
+        <v>26.38727272727273</v>
       </c>
       <c r="D22" t="n">
-        <v>184.2072727272727</v>
+        <v>184.4963636363637</v>
       </c>
       <c r="E22" t="n">
-        <v>1.149090909090909</v>
+        <v>1.019090909090909</v>
       </c>
       <c r="F22" t="n">
-        <v>68.15454545454546</v>
+        <v>67.11636363636364</v>
       </c>
       <c r="G22" t="n">
-        <v>2220181.818181818</v>
+        <v>1309840.909090909</v>
       </c>
       <c r="H22" t="n">
-        <v>75.17181818181817</v>
+        <v>70.48818181818183</v>
       </c>
       <c r="I22" t="n">
-        <v>25.67037037037037</v>
+        <v>27.85143097643098</v>
       </c>
       <c r="J22" t="n">
-        <v>181.4456790123457</v>
+        <v>181.1434343434343</v>
       </c>
       <c r="K22" t="n">
-        <v>1.045679012345679</v>
+        <v>1.018518518518518</v>
       </c>
       <c r="L22" t="n">
-        <v>70.95432098765433</v>
+        <v>67.81784511784512</v>
       </c>
       <c r="M22" t="n">
-        <v>3293703.703703704</v>
+        <v>1447777.777777778</v>
       </c>
       <c r="N22" t="n">
-        <v>73.51481481481481</v>
+        <v>70.10159932659933</v>
       </c>
       <c r="O22" t="n">
-        <v>24.85835795099592</v>
+        <v>24.56836745862832</v>
       </c>
       <c r="P22" t="n">
-        <v>183.359672485611</v>
+        <v>182.8497245170288</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.16718949276595</v>
+        <v>1.007692307692308</v>
       </c>
       <c r="R22" t="n">
-        <v>68.75142668790804</v>
+        <v>64.4695638757378</v>
       </c>
       <c r="S22" t="n">
-        <v>2496013.602771684</v>
+        <v>1056942.400160226</v>
       </c>
       <c r="T22" t="n">
-        <v>74.88350611922291</v>
+        <v>69.79114614853745</v>
       </c>
       <c r="U22" t="n">
-        <v>26.03937376990517</v>
+        <v>25.20616465659944</v>
       </c>
       <c r="V22" t="n">
-        <v>183.3066870363489</v>
+        <v>179.1507580402689</v>
       </c>
       <c r="W22" t="n">
-        <v>1.219601690133091</v>
+        <v>1.006805555555556</v>
       </c>
       <c r="X22" t="n">
-        <v>69.62724802840745</v>
+        <v>64.93143918279787</v>
       </c>
       <c r="Y22" t="n">
-        <v>2557524.612907222</v>
+        <v>1193535.301003345</v>
       </c>
       <c r="Z22" t="n">
-        <v>72.58290323024623</v>
+        <v>69.48274302388432</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>25.79545454545455</v>
+        <v>29.11</v>
       </c>
       <c r="D23" t="n">
-        <v>186.23</v>
+        <v>183.32</v>
       </c>
       <c r="E23" t="n">
-        <v>1.248181818181818</v>
+        <v>1.16</v>
       </c>
       <c r="F23" t="n">
-        <v>76.07818181818182</v>
+        <v>67.87</v>
       </c>
       <c r="G23" t="n">
-        <v>13460363.63636364</v>
+        <v>1037400</v>
       </c>
       <c r="H23" t="n">
-        <v>79.36909090909091</v>
+        <v>69.97999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>26.09090909090909</v>
+        <v>25.52047750229569</v>
       </c>
       <c r="J23" t="n">
-        <v>182.0606060606061</v>
+        <v>184.7290174471993</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>1.264738292011019</v>
       </c>
       <c r="L23" t="n">
-        <v>67.94949494949496</v>
+        <v>70.86786042240588</v>
       </c>
       <c r="M23" t="n">
-        <v>1391161.616161616</v>
+        <v>3244237.832874197</v>
       </c>
       <c r="N23" t="n">
-        <v>71.27272727272728</v>
+        <v>76.37658402203857</v>
       </c>
       <c r="O23" t="n">
-        <v>24.94636711542671</v>
+        <v>24.89329614461308</v>
       </c>
       <c r="P23" t="n">
-        <v>185.0591305860463</v>
+        <v>185.0998843987608</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.193529568127091</v>
+        <v>1.030678106917237</v>
       </c>
       <c r="R23" t="n">
-        <v>72.03887250992901</v>
+        <v>65.26908853363773</v>
       </c>
       <c r="S23" t="n">
-        <v>5762901.734058855</v>
+        <v>1046866.811003853</v>
       </c>
       <c r="T23" t="n">
-        <v>76.01139701973294</v>
+        <v>69.2467237469709</v>
       </c>
       <c r="U23" t="n">
-        <v>24.32992719214942</v>
+        <v>24.6231770980997</v>
       </c>
       <c r="V23" t="n">
-        <v>182.1738271604938</v>
+        <v>183.205746338285</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.192188647266047</v>
       </c>
       <c r="X23" t="n">
-        <v>66.95798670465336</v>
+        <v>69.55463642652498</v>
       </c>
       <c r="Y23" t="n">
-        <v>1478218.106995885</v>
+        <v>2992488.039308473</v>
       </c>
       <c r="Z23" t="n">
-        <v>72.8115606204495</v>
+        <v>75.64575599151452</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>24.04636363636363</v>
+        <v>25.45206611570248</v>
       </c>
       <c r="D24" t="n">
-        <v>184.7945454545455</v>
+        <v>183.2471074380165</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>71.14181818181819</v>
+        <v>67.04545454545455</v>
       </c>
       <c r="G24" t="n">
-        <v>4415181.818181818</v>
+        <v>1360103.305785124</v>
       </c>
       <c r="H24" t="n">
-        <v>76.64727272727274</v>
+        <v>71.03801652892561</v>
       </c>
       <c r="I24" t="n">
-        <v>25.81414141414142</v>
+        <v>25.55277777777778</v>
       </c>
       <c r="J24" t="n">
-        <v>182.3282828282828</v>
+        <v>183.5716049382716</v>
       </c>
       <c r="K24" t="n">
-        <v>1.02020202020202</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>67.42323232323233</v>
+        <v>66.52746913580248</v>
       </c>
       <c r="M24" t="n">
-        <v>1496035.353535354</v>
+        <v>1187901.234567901</v>
       </c>
       <c r="N24" t="n">
-        <v>71.88585858585857</v>
+        <v>70.28456790123457</v>
       </c>
       <c r="O24" t="n">
-        <v>23.17223981249468</v>
+        <v>23.56668197286638</v>
       </c>
       <c r="P24" t="n">
-        <v>184.6098602019891</v>
+        <v>182.0834655940428</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>67.55594103200924</v>
+        <v>64.17281167857631</v>
       </c>
       <c r="S24" t="n">
-        <v>2545997.034019897</v>
+        <v>1159419.451042877</v>
       </c>
       <c r="T24" t="n">
-        <v>74.75548996577857</v>
+        <v>71.28115552613303</v>
       </c>
       <c r="U24" t="n">
-        <v>26.59254885032663</v>
+        <v>25.18190172400698</v>
       </c>
       <c r="V24" t="n">
-        <v>181.4586773720107</v>
+        <v>183.4440810359232</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12371233704567</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>66.87789634234079</v>
+        <v>64.8128593073593</v>
       </c>
       <c r="Y24" t="n">
-        <v>1377551.238884572</v>
+        <v>1035885.016328701</v>
       </c>
       <c r="Z24" t="n">
-        <v>70.74887852887852</v>
+        <v>69.30842686261107</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>24.06363636363636</v>
+        <v>26.68874458874459</v>
       </c>
       <c r="D25" t="n">
-        <v>184.6545454545455</v>
+        <v>185.6223665223665</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>1.073376623376623</v>
       </c>
       <c r="F25" t="n">
-        <v>72.15454545454546</v>
+        <v>69.49617604617605</v>
       </c>
       <c r="G25" t="n">
-        <v>5452272.727272728</v>
+        <v>1990764.79076479</v>
       </c>
       <c r="H25" t="n">
-        <v>77.78181818181818</v>
+        <v>72.82106782106781</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -2475,1560 +2475,2004 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>23.36307449072667</v>
+        <v>26.94418811002662</v>
       </c>
       <c r="P25" t="n">
-        <v>182.6972344177562</v>
+        <v>185.0683817321395</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.08224931590149</v>
+        <v>1.118495738216235</v>
       </c>
       <c r="R25" t="n">
-        <v>68.24991669200365</v>
+        <v>69.80358863703584</v>
       </c>
       <c r="S25" t="n">
-        <v>2627385.177865612</v>
+        <v>2103228.030639133</v>
       </c>
       <c r="T25" t="n">
-        <v>74.82169534813013</v>
+        <v>73.18901084939905</v>
       </c>
       <c r="U25" t="n">
-        <v>29</v>
+        <v>22.3875</v>
       </c>
       <c r="V25" t="n">
-        <v>181.6</v>
+        <v>180.65</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>70.2</v>
+        <v>62.2375</v>
       </c>
       <c r="Y25" t="n">
-        <v>1820000</v>
+        <v>823437.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>70.2</v>
+        <v>70.52500000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>25.84030303030303</v>
+        <v>25.72181818181819</v>
       </c>
       <c r="D26" t="n">
-        <v>184.9241414141414</v>
+        <v>182.7009090909091</v>
       </c>
       <c r="E26" t="n">
-        <v>1.321212121212121</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>71.34686868686867</v>
+        <v>67.68636363636364</v>
       </c>
       <c r="G26" t="n">
-        <v>3189494.94949495</v>
+        <v>1565022.727272727</v>
       </c>
       <c r="H26" t="n">
-        <v>76.55646464646466</v>
+        <v>72.04636363636364</v>
       </c>
       <c r="I26" t="n">
-        <v>26.05308641975309</v>
+        <v>26.05734265734266</v>
       </c>
       <c r="J26" t="n">
-        <v>183.1037037037037</v>
+        <v>182.8741258741259</v>
       </c>
       <c r="K26" t="n">
-        <v>1.104938271604938</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>68.59876543209877</v>
+        <v>70.44335664335664</v>
       </c>
       <c r="M26" t="n">
-        <v>1671203.703703704</v>
+        <v>2576153.846153846</v>
       </c>
       <c r="N26" t="n">
-        <v>72.31358024691357</v>
+        <v>74.4979020979021</v>
       </c>
       <c r="O26" t="n">
-        <v>24.9063176984694</v>
+        <v>25.83424634624635</v>
       </c>
       <c r="P26" t="n">
-        <v>183.9865548902422</v>
+        <v>182.0086191586192</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.236407511992651</v>
+        <v>1.103341103341103</v>
       </c>
       <c r="R26" t="n">
-        <v>70.10686280936126</v>
+        <v>66.47505908905909</v>
       </c>
       <c r="S26" t="n">
-        <v>3172913.743824115</v>
+        <v>1409329.448329448</v>
       </c>
       <c r="T26" t="n">
-        <v>75.84113777278793</v>
+        <v>70.94827639027639</v>
       </c>
       <c r="U26" t="n">
-        <v>23.9060405643739</v>
+        <v>25.44150277753957</v>
       </c>
       <c r="V26" t="n">
-        <v>184.3540123456791</v>
+        <v>182.3927914987279</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.003205128205128</v>
       </c>
       <c r="X26" t="n">
-        <v>64.02879188712522</v>
+        <v>68.70878760159695</v>
       </c>
       <c r="Y26" t="n">
-        <v>1099708.002645503</v>
+        <v>2063652.202498356</v>
       </c>
       <c r="Z26" t="n">
-        <v>70.74927248677248</v>
+        <v>73.52096137171387</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>25.43636363636364</v>
+        <v>24.36721763085399</v>
       </c>
       <c r="D27" t="n">
-        <v>184.3818181818181</v>
+        <v>183.6962350780533</v>
       </c>
       <c r="E27" t="n">
-        <v>1.209090909090909</v>
+        <v>1.137373737373737</v>
       </c>
       <c r="F27" t="n">
-        <v>72.18181818181817</v>
+        <v>68.50413223140495</v>
       </c>
       <c r="G27" t="n">
-        <v>3650000</v>
+        <v>2162217.630853994</v>
       </c>
       <c r="H27" t="n">
-        <v>75.73636363636363</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>74.76501377410467</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26.05636363636363</v>
+      </c>
+      <c r="J27" t="n">
+        <v>184.1720454545454</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>65.23113636363635</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1078602.272727273</v>
+      </c>
+      <c r="N27" t="n">
+        <v>68.8175</v>
+      </c>
       <c r="O27" t="n">
-        <v>25.81782430213465</v>
+        <v>24.87231675198764</v>
       </c>
       <c r="P27" t="n">
-        <v>183.1474308450171</v>
+        <v>183.409117844062</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.136724137931035</v>
+        <v>1.150258846237443</v>
       </c>
       <c r="R27" t="n">
-        <v>70.13735063786788</v>
+        <v>68.62056105827138</v>
       </c>
       <c r="S27" t="n">
-        <v>2714007.06707086</v>
+        <v>2368801.868320579</v>
       </c>
       <c r="T27" t="n">
-        <v>74.33269609700645</v>
+        <v>74.57840383132817</v>
       </c>
       <c r="U27" t="n">
-        <v>21.4</v>
+        <v>25.99547260361047</v>
       </c>
       <c r="V27" t="n">
-        <v>179.8</v>
+        <v>182.1657418001526</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>61.6</v>
+        <v>64.08524292312907</v>
       </c>
       <c r="Y27" t="n">
-        <v>775000</v>
+        <v>1016423.169825344</v>
       </c>
       <c r="Z27" t="n">
-        <v>70.8</v>
+        <v>67.96443717524953</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>25.37727272727273</v>
+        <v>25.6297520661157</v>
       </c>
       <c r="D28" t="n">
-        <v>182.9618181818182</v>
+        <v>186.5504132231405</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>1.216528925619835</v>
       </c>
       <c r="F28" t="n">
-        <v>67.02000000000001</v>
+        <v>72.97520661157024</v>
       </c>
       <c r="G28" t="n">
-        <v>1374063.636363636</v>
+        <v>5321280.991735538</v>
       </c>
       <c r="H28" t="n">
-        <v>71.12181818181818</v>
-      </c>
-      <c r="I28" t="n">
-        <v>26.21969696969697</v>
-      </c>
-      <c r="J28" t="n">
-        <v>183.0303030303031</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>70.45454545454545</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2521590.909090909</v>
-      </c>
-      <c r="N28" t="n">
-        <v>74.28030303030303</v>
-      </c>
+        <v>76.81652892561983</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>23.76014382094667</v>
+        <v>23.81737774719034</v>
       </c>
       <c r="P28" t="n">
-        <v>182.3692724709074</v>
+        <v>184.6449125465017</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>1.128385617935843</v>
       </c>
       <c r="R28" t="n">
-        <v>64.16933094167203</v>
+        <v>70.3708043777534</v>
       </c>
       <c r="S28" t="n">
-        <v>1156315.046940815</v>
+        <v>3866672.466408598</v>
       </c>
       <c r="T28" t="n">
-        <v>71.03003298350824</v>
+        <v>77.24240376564966</v>
       </c>
       <c r="U28" t="n">
-        <v>25.43375965151327</v>
+        <v>23.96527777777778</v>
       </c>
       <c r="V28" t="n">
-        <v>182.39419025352</v>
+        <v>182.6527777777777</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>68.43747212931994</v>
+        <v>68.25694444444444</v>
       </c>
       <c r="Y28" t="n">
-        <v>1973982.049217556</v>
+        <v>2353125</v>
       </c>
       <c r="Z28" t="n">
-        <v>73.31346902225526</v>
+        <v>73.375</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>27.94095500459137</v>
+        <v>25.69777777777778</v>
       </c>
       <c r="D29" t="n">
-        <v>181.1100091827365</v>
+        <v>183.7122222222222</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>67.58916437098256</v>
+        <v>68.19666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>1260000</v>
+        <v>1628027.777777778</v>
       </c>
       <c r="H29" t="n">
-        <v>69.78053259871443</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>72.25444444444445</v>
+      </c>
+      <c r="I29" t="n">
+        <v>23.66689623507806</v>
+      </c>
+      <c r="J29" t="n">
+        <v>184.9233241505969</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>70.11099632690542</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3865992.309458219</v>
+      </c>
+      <c r="N29" t="n">
+        <v>76.18893480257115</v>
+      </c>
       <c r="O29" t="n">
-        <v>25.29041653998176</v>
+        <v>23.96159663865546</v>
       </c>
       <c r="P29" t="n">
-        <v>178.724201608668</v>
+        <v>184.4987990196078</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>65.12331932889245</v>
+        <v>64.48167250233428</v>
       </c>
       <c r="S29" t="n">
-        <v>1261750.334448161</v>
+        <v>1170122.414799253</v>
       </c>
       <c r="T29" t="n">
-        <v>69.63060946958181</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+        <v>71.18651844070961</v>
+      </c>
+      <c r="U29" t="n">
+        <v>22.82705449210833</v>
+      </c>
+      <c r="V29" t="n">
+        <v>184.6810762486243</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>66.67392677628128</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2307231.237192734</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>74.58773132593836</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>25.81414141414142</v>
+        <v>27.10209790209791</v>
       </c>
       <c r="D30" t="n">
-        <v>182.3282828282828</v>
+        <v>181.3921522921523</v>
       </c>
       <c r="E30" t="n">
-        <v>1.02020202020202</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>67.42323232323233</v>
+        <v>67.47521367521368</v>
       </c>
       <c r="G30" t="n">
-        <v>1496035.353535354</v>
+        <v>1250264.18026418</v>
       </c>
       <c r="H30" t="n">
-        <v>71.88585858585857</v>
-      </c>
-      <c r="I30" t="n">
-        <v>26.05308641975309</v>
-      </c>
-      <c r="J30" t="n">
-        <v>183.1037037037037</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.104938271604938</v>
-      </c>
-      <c r="L30" t="n">
-        <v>68.59876543209877</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1671203.703703704</v>
-      </c>
-      <c r="N30" t="n">
-        <v>72.31358024691357</v>
-      </c>
+        <v>70.13022533022534</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>26.59254885032663</v>
+        <v>25.37346197961583</v>
       </c>
       <c r="P30" t="n">
-        <v>181.4586773720107</v>
+        <v>180.0884310988157</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.12371233704567</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>66.87789634234079</v>
+        <v>65.8332191739884</v>
       </c>
       <c r="S30" t="n">
-        <v>1377551.238884572</v>
+        <v>1166835.269431423</v>
       </c>
       <c r="T30" t="n">
-        <v>70.74887852887852</v>
-      </c>
-      <c r="U30" t="n">
-        <v>23.9060405643739</v>
-      </c>
-      <c r="V30" t="n">
-        <v>184.3540123456791</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>64.02879188712522</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1099708.002645503</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>70.74927248677248</v>
-      </c>
+        <v>70.57649080264466</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" t="n">
-        <v>25.84030303030303</v>
-      </c>
-      <c r="D31" t="n">
-        <v>184.9241414141414</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.321212121212121</v>
-      </c>
-      <c r="F31" t="n">
-        <v>71.34686868686867</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3189494.94949495</v>
-      </c>
-      <c r="H31" t="n">
-        <v>76.55646464646466</v>
-      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>25.98888888888889</v>
+        <v>25.88727272727273</v>
       </c>
       <c r="J31" t="n">
-        <v>183.9160493827161</v>
+        <v>182.7136363636363</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>66.70246913580246</v>
+        <v>67.59181818181818</v>
       </c>
       <c r="M31" t="n">
-        <v>1163734.567901235</v>
+        <v>1341204.545454545</v>
       </c>
       <c r="N31" t="n">
-        <v>69.93456790123456</v>
+        <v>71.26727272727274</v>
       </c>
       <c r="O31" t="n">
-        <v>24.9063176984694</v>
+        <v>29</v>
       </c>
       <c r="P31" t="n">
-        <v>183.9865548902422</v>
+        <v>181.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.236407511992651</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>70.10686280936126</v>
+        <v>70.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3172913.743824115</v>
+        <v>1820000</v>
       </c>
       <c r="T31" t="n">
-        <v>75.84113777278793</v>
+        <v>70.2</v>
       </c>
       <c r="U31" t="n">
-        <v>24.9553835053835</v>
+        <v>23.8005059015059</v>
       </c>
       <c r="V31" t="n">
-        <v>183.5819352869353</v>
+        <v>181.7865268620268</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>64.83978238428239</v>
+        <v>66.41397374847375</v>
       </c>
       <c r="Y31" t="n">
-        <v>1063629.955599956</v>
+        <v>1434065.595746846</v>
       </c>
       <c r="Z31" t="n">
-        <v>69.44951998001997</v>
+        <v>72.67669576719577</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>29.05</v>
+        <v>27.85143097643098</v>
       </c>
       <c r="D32" t="n">
-        <v>183.48</v>
+        <v>181.1434343434343</v>
       </c>
       <c r="E32" t="n">
-        <v>1.16</v>
+        <v>1.018518518518518</v>
       </c>
       <c r="F32" t="n">
-        <v>67.90000000000001</v>
+        <v>67.81784511784512</v>
       </c>
       <c r="G32" t="n">
-        <v>1046900</v>
+        <v>1447777.777777778</v>
       </c>
       <c r="H32" t="n">
-        <v>70.05</v>
+        <v>70.10159932659933</v>
       </c>
       <c r="I32" t="n">
-        <v>26.23232323232323</v>
+        <v>25.6297520661157</v>
       </c>
       <c r="J32" t="n">
-        <v>184.4242424242424</v>
+        <v>186.5504132231405</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>1.216528925619835</v>
       </c>
       <c r="L32" t="n">
-        <v>67.01010101010101</v>
+        <v>72.97520661157024</v>
       </c>
       <c r="M32" t="n">
-        <v>1316919.191919192</v>
+        <v>5321280.991735538</v>
       </c>
       <c r="N32" t="n">
-        <v>70.52525252525253</v>
+        <v>76.81652892561983</v>
       </c>
       <c r="O32" t="n">
-        <v>25.04514799646493</v>
+        <v>25.20616465659944</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9832177320941</v>
+        <v>179.1507580402689</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.028826255065386</v>
+        <v>1.006805555555556</v>
       </c>
       <c r="R32" t="n">
-        <v>65.20242186697106</v>
+        <v>64.93143918279787</v>
       </c>
       <c r="S32" t="n">
-        <v>1015413.10730015</v>
+        <v>1193535.301003345</v>
       </c>
       <c r="T32" t="n">
-        <v>68.91709411734125</v>
+        <v>69.48274302388432</v>
       </c>
       <c r="U32" t="n">
-        <v>24.87786770037978</v>
+        <v>23.81737774719034</v>
       </c>
       <c r="V32" t="n">
-        <v>183.4569136428073</v>
+        <v>184.6449125465017</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.128385617935843</v>
       </c>
       <c r="X32" t="n">
-        <v>64.69145680942783</v>
+        <v>70.3708043777534</v>
       </c>
       <c r="Y32" t="n">
-        <v>1066359.031878839</v>
+        <v>3866672.466408598</v>
       </c>
       <c r="Z32" t="n">
-        <v>69.80983859582892</v>
+        <v>77.24240376564966</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" t="n">
-        <v>26.95909090909091</v>
-      </c>
-      <c r="D33" t="n">
-        <v>181.5780303030303</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>67.51060606060607</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1287954.545454546</v>
-      </c>
-      <c r="H33" t="n">
-        <v>70.27575757575758</v>
-      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>25.87107438016529</v>
+        <v>29.11</v>
       </c>
       <c r="J33" t="n">
-        <v>186.6884297520661</v>
+        <v>183.32</v>
       </c>
       <c r="K33" t="n">
-        <v>1.227272727272727</v>
+        <v>1.16</v>
       </c>
       <c r="L33" t="n">
-        <v>73.19669421487605</v>
+        <v>67.87</v>
       </c>
       <c r="M33" t="n">
-        <v>5316033.05785124</v>
+        <v>1037400</v>
       </c>
       <c r="N33" t="n">
-        <v>76.90082644628099</v>
+        <v>69.97999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>25.41676329842997</v>
+        <v>22.3875</v>
       </c>
       <c r="P33" t="n">
-        <v>179.4409926647427</v>
+        <v>180.65</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>65.99645752395752</v>
+        <v>62.2375</v>
       </c>
       <c r="S33" t="n">
-        <v>1207054.982054982</v>
+        <v>823437.5</v>
       </c>
       <c r="T33" t="n">
-        <v>70.95946760030094</v>
+        <v>70.52500000000001</v>
       </c>
       <c r="U33" t="n">
-        <v>23.99010501991761</v>
+        <v>24.89329614461308</v>
       </c>
       <c r="V33" t="n">
-        <v>184.8949125465017</v>
+        <v>185.0998843987608</v>
       </c>
       <c r="W33" t="n">
-        <v>1.126287715837941</v>
+        <v>1.030678106917237</v>
       </c>
       <c r="X33" t="n">
-        <v>70.65821696516599</v>
+        <v>65.26908853363773</v>
       </c>
       <c r="Y33" t="n">
-        <v>3979469.669205801</v>
+        <v>1046866.811003853</v>
       </c>
       <c r="Z33" t="n">
-        <v>77.3441520173979</v>
+        <v>69.2467237469709</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>25.55277777777778</v>
+      </c>
+      <c r="D34" t="n">
+        <v>183.5716049382716</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>66.52746913580248</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1187901.234567901</v>
+      </c>
+      <c r="H34" t="n">
+        <v>70.28456790123457</v>
+      </c>
+      <c r="I34" t="n">
+        <v>25.72181818181819</v>
+      </c>
+      <c r="J34" t="n">
+        <v>182.7009090909091</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>67.68636363636364</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1565022.727272727</v>
+      </c>
+      <c r="N34" t="n">
+        <v>72.04636363636364</v>
+      </c>
+      <c r="O34" t="n">
+        <v>25.18190172400698</v>
+      </c>
+      <c r="P34" t="n">
+        <v>183.4440810359232</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>64.8128593073593</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1035885.016328701</v>
+      </c>
+      <c r="T34" t="n">
+        <v>69.30842686261107</v>
+      </c>
       <c r="U34" t="n">
-        <v>21.4</v>
+        <v>25.83424634624635</v>
       </c>
       <c r="V34" t="n">
-        <v>179.8</v>
+        <v>182.0086191586192</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.103341103341103</v>
       </c>
       <c r="X34" t="n">
-        <v>61.6</v>
+        <v>66.47505908905909</v>
       </c>
       <c r="Y34" t="n">
-        <v>775000</v>
+        <v>1409329.448329448</v>
       </c>
       <c r="Z34" t="n">
-        <v>70.8</v>
+        <v>70.94827639027639</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>26.09090909090909</v>
+        <v>26.68874458874459</v>
       </c>
       <c r="D35" t="n">
-        <v>182.0606060606061</v>
+        <v>185.6223665223665</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>1.073376623376623</v>
       </c>
       <c r="F35" t="n">
-        <v>67.94949494949496</v>
+        <v>69.49617604617605</v>
       </c>
       <c r="G35" t="n">
-        <v>1391161.616161616</v>
+        <v>1990764.79076479</v>
       </c>
       <c r="H35" t="n">
-        <v>71.27272727272728</v>
+        <v>72.82106782106781</v>
       </c>
       <c r="I35" t="n">
-        <v>26.87179487179488</v>
+        <v>26.05734265734266</v>
       </c>
       <c r="J35" t="n">
-        <v>185.6597513597513</v>
+        <v>182.8741258741259</v>
       </c>
       <c r="K35" t="n">
-        <v>1.086713286713287</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>69.51756021756022</v>
+        <v>70.44335664335664</v>
       </c>
       <c r="M35" t="n">
-        <v>1987466.977466978</v>
+        <v>2576153.846153846</v>
       </c>
       <c r="N35" t="n">
-        <v>72.81709401709402</v>
+        <v>74.4979020979021</v>
       </c>
       <c r="O35" t="n">
-        <v>24.32992719214942</v>
+        <v>26.94418811002662</v>
       </c>
       <c r="P35" t="n">
-        <v>182.1738271604938</v>
+        <v>185.0683817321395</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>1.118495738216235</v>
       </c>
       <c r="R35" t="n">
-        <v>66.95798670465336</v>
+        <v>69.80358863703584</v>
       </c>
       <c r="S35" t="n">
-        <v>1478218.106995885</v>
+        <v>2103228.030639133</v>
       </c>
       <c r="T35" t="n">
-        <v>72.8115606204495</v>
+        <v>73.18901084939905</v>
       </c>
       <c r="U35" t="n">
-        <v>27.25943223443224</v>
+        <v>25.44150277753957</v>
       </c>
       <c r="V35" t="n">
-        <v>185.3515125454256</v>
+        <v>182.3927914987279</v>
       </c>
       <c r="W35" t="n">
-        <v>1.130397863006559</v>
+        <v>1.003205128205128</v>
       </c>
       <c r="X35" t="n">
-        <v>69.87794495359714</v>
+        <v>68.70878760159695</v>
       </c>
       <c r="Y35" t="n">
-        <v>2098139.105459758</v>
+        <v>2063652.202498356</v>
       </c>
       <c r="Z35" t="n">
-        <v>73.09123130492695</v>
+        <v>73.52096137171387</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>24.04636363636363</v>
+        <v>23.66689623507806</v>
       </c>
       <c r="D36" t="n">
-        <v>184.7945454545455</v>
+        <v>184.9233241505969</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>71.14181818181819</v>
+        <v>70.11099632690542</v>
       </c>
       <c r="G36" t="n">
-        <v>4415181.818181818</v>
+        <v>3865992.309458219</v>
       </c>
       <c r="H36" t="n">
-        <v>76.64727272727274</v>
+        <v>76.18893480257115</v>
       </c>
       <c r="I36" t="n">
-        <v>23.65545454545454</v>
+        <v>26.38727272727273</v>
       </c>
       <c r="J36" t="n">
-        <v>184.2072727272727</v>
+        <v>184.4963636363637</v>
       </c>
       <c r="K36" t="n">
-        <v>1.149090909090909</v>
+        <v>1.019090909090909</v>
       </c>
       <c r="L36" t="n">
-        <v>68.15454545454546</v>
+        <v>67.11636363636364</v>
       </c>
       <c r="M36" t="n">
-        <v>2220181.818181818</v>
+        <v>1309840.909090909</v>
       </c>
       <c r="N36" t="n">
-        <v>75.17181818181817</v>
+        <v>70.48818181818183</v>
       </c>
       <c r="O36" t="n">
-        <v>23.17223981249468</v>
+        <v>22.82705449210833</v>
       </c>
       <c r="P36" t="n">
-        <v>184.6098602019891</v>
+        <v>184.6810762486243</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>67.55594103200924</v>
+        <v>66.67392677628128</v>
       </c>
       <c r="S36" t="n">
-        <v>2545997.034019897</v>
+        <v>2307231.237192734</v>
       </c>
       <c r="T36" t="n">
-        <v>74.75548996577857</v>
+        <v>74.58773132593836</v>
       </c>
       <c r="U36" t="n">
-        <v>24.85835795099592</v>
+        <v>24.56836745862832</v>
       </c>
       <c r="V36" t="n">
-        <v>183.359672485611</v>
+        <v>182.8497245170288</v>
       </c>
       <c r="W36" t="n">
-        <v>1.16718949276595</v>
+        <v>1.007692307692308</v>
       </c>
       <c r="X36" t="n">
-        <v>68.75142668790804</v>
+        <v>64.4695638757378</v>
       </c>
       <c r="Y36" t="n">
-        <v>2496013.602771684</v>
+        <v>1056942.400160226</v>
       </c>
       <c r="Z36" t="n">
-        <v>74.88350611922291</v>
+        <v>69.79114614853745</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>26.02636363636363</v>
+        <v>26.05636363636363</v>
       </c>
       <c r="D37" t="n">
-        <v>184.4520454545454</v>
+        <v>184.1720454545454</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>65.35113636363636</v>
+        <v>65.23113636363635</v>
       </c>
       <c r="G37" t="n">
-        <v>1097702.272727273</v>
+        <v>1078602.272727273</v>
       </c>
       <c r="H37" t="n">
-        <v>68.89749999999999</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+        <v>68.8175</v>
+      </c>
+      <c r="I37" t="n">
+        <v>25.45206611570248</v>
+      </c>
+      <c r="J37" t="n">
+        <v>183.2471074380165</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>67.04545454545455</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1360103.305785124</v>
+      </c>
+      <c r="N37" t="n">
+        <v>71.03801652892561</v>
+      </c>
       <c r="O37" t="n">
-        <v>25.99042874396135</v>
+        <v>25.99547260361047</v>
       </c>
       <c r="P37" t="n">
-        <v>182.1929347826087</v>
+        <v>182.1657418001526</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>64.02976046698873</v>
+        <v>64.08524292312907</v>
       </c>
       <c r="S37" t="n">
-        <v>1002673.169825344</v>
+        <v>1016423.169825344</v>
       </c>
       <c r="T37" t="n">
-        <v>67.88176173665303</v>
+        <v>67.96443717524953</v>
       </c>
       <c r="U37" t="n">
-        <v>29</v>
+        <v>23.56668197286638</v>
       </c>
       <c r="V37" t="n">
-        <v>181.6</v>
+        <v>182.0834655940428</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>70.2</v>
+        <v>64.17281167857631</v>
       </c>
       <c r="Y37" t="n">
-        <v>1820000</v>
+        <v>1159419.451042877</v>
       </c>
       <c r="Z37" t="n">
-        <v>70.2</v>
+        <v>71.28115552613303</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>26.23232323232323</v>
+        <v>25.52047750229569</v>
       </c>
       <c r="D38" t="n">
-        <v>184.4242424242424</v>
+        <v>184.7290174471993</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>1.264738292011019</v>
       </c>
       <c r="F38" t="n">
-        <v>67.01010101010101</v>
+        <v>70.86786042240588</v>
       </c>
       <c r="G38" t="n">
-        <v>1316919.191919192</v>
+        <v>3244237.832874197</v>
       </c>
       <c r="H38" t="n">
-        <v>70.52525252525253</v>
+        <v>76.37658402203857</v>
       </c>
       <c r="I38" t="n">
-        <v>27.94095500459137</v>
+        <v>24.36721763085399</v>
       </c>
       <c r="J38" t="n">
-        <v>181.1100091827365</v>
+        <v>183.6962350780533</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.137373737373737</v>
       </c>
       <c r="L38" t="n">
-        <v>67.58916437098256</v>
+        <v>68.50413223140495</v>
       </c>
       <c r="M38" t="n">
-        <v>1260000</v>
+        <v>2162217.630853994</v>
       </c>
       <c r="N38" t="n">
-        <v>69.78053259871443</v>
+        <v>74.76501377410467</v>
       </c>
       <c r="O38" t="n">
-        <v>24.87786770037978</v>
+        <v>24.6231770980997</v>
       </c>
       <c r="P38" t="n">
-        <v>183.4569136428073</v>
+        <v>183.205746338285</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>1.192188647266047</v>
       </c>
       <c r="R38" t="n">
-        <v>64.69145680942783</v>
+        <v>69.55463642652498</v>
       </c>
       <c r="S38" t="n">
-        <v>1066359.031878839</v>
+        <v>2992488.039308473</v>
       </c>
       <c r="T38" t="n">
-        <v>69.80983859582892</v>
+        <v>75.64575599151452</v>
       </c>
       <c r="U38" t="n">
-        <v>25.29041653998176</v>
+        <v>24.87231675198764</v>
       </c>
       <c r="V38" t="n">
-        <v>178.724201608668</v>
+        <v>183.409117844062</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>1.150258846237443</v>
       </c>
       <c r="X38" t="n">
-        <v>65.12331932889245</v>
+        <v>68.62056105827138</v>
       </c>
       <c r="Y38" t="n">
-        <v>1261750.334448161</v>
+        <v>2368801.868320579</v>
       </c>
       <c r="Z38" t="n">
-        <v>69.63060946958181</v>
+        <v>74.57840383132817</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
-      <c r="C39" t="n">
-        <v>29.05</v>
-      </c>
-      <c r="D39" t="n">
-        <v>183.48</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="F39" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1046900</v>
-      </c>
-      <c r="H39" t="n">
-        <v>70.05</v>
-      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>25.84030303030303</v>
+        <v>27.10209790209791</v>
       </c>
       <c r="J39" t="n">
-        <v>184.9241414141414</v>
+        <v>181.3921522921523</v>
       </c>
       <c r="K39" t="n">
-        <v>1.321212121212121</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>71.34686868686867</v>
+        <v>67.47521367521368</v>
       </c>
       <c r="M39" t="n">
-        <v>3189494.94949495</v>
+        <v>1250264.18026418</v>
       </c>
       <c r="N39" t="n">
-        <v>76.55646464646466</v>
+        <v>70.13022533022534</v>
       </c>
       <c r="O39" t="n">
-        <v>25.04514799646493</v>
+        <v>23.96527777777778</v>
       </c>
       <c r="P39" t="n">
-        <v>184.9832177320941</v>
+        <v>182.6527777777777</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.028826255065386</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>65.20242186697106</v>
+        <v>68.25694444444444</v>
       </c>
       <c r="S39" t="n">
-        <v>1015413.10730015</v>
+        <v>2353125</v>
       </c>
       <c r="T39" t="n">
-        <v>68.91709411734125</v>
+        <v>73.375</v>
       </c>
       <c r="U39" t="n">
-        <v>24.9063176984694</v>
+        <v>25.37346197961583</v>
       </c>
       <c r="V39" t="n">
-        <v>183.9865548902422</v>
+        <v>180.0884310988157</v>
       </c>
       <c r="W39" t="n">
-        <v>1.236407511992651</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>70.10686280936126</v>
+        <v>65.8332191739884</v>
       </c>
       <c r="Y39" t="n">
-        <v>3172913.743824115</v>
+        <v>1166835.269431423</v>
       </c>
       <c r="Z39" t="n">
-        <v>75.84113777278793</v>
+        <v>70.57649080264466</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>25.37727272727273</v>
+        <v>25.88727272727273</v>
       </c>
       <c r="D40" t="n">
-        <v>182.9618181818182</v>
+        <v>182.7136363636363</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>67.02000000000001</v>
+        <v>67.59181818181818</v>
       </c>
       <c r="G40" t="n">
-        <v>1374063.636363636</v>
+        <v>1341204.545454545</v>
       </c>
       <c r="H40" t="n">
-        <v>71.12181818181818</v>
+        <v>71.26727272727274</v>
       </c>
       <c r="I40" t="n">
-        <v>25.98888888888889</v>
+        <v>25.69777777777778</v>
       </c>
       <c r="J40" t="n">
-        <v>183.9160493827161</v>
+        <v>183.7122222222222</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="L40" t="n">
-        <v>66.70246913580246</v>
+        <v>68.19666666666667</v>
       </c>
       <c r="M40" t="n">
-        <v>1163734.567901235</v>
+        <v>1628027.777777778</v>
       </c>
       <c r="N40" t="n">
-        <v>69.93456790123456</v>
+        <v>72.25444444444445</v>
       </c>
       <c r="O40" t="n">
-        <v>23.76014382094667</v>
+        <v>23.8005059015059</v>
       </c>
       <c r="P40" t="n">
-        <v>182.3692724709074</v>
+        <v>181.7865268620268</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>64.16933094167203</v>
+        <v>66.41397374847375</v>
       </c>
       <c r="S40" t="n">
-        <v>1156315.046940815</v>
+        <v>1434065.595746846</v>
       </c>
       <c r="T40" t="n">
-        <v>71.03003298350824</v>
+        <v>72.67669576719577</v>
       </c>
       <c r="U40" t="n">
-        <v>24.9553835053835</v>
+        <v>23.96159663865546</v>
       </c>
       <c r="V40" t="n">
-        <v>183.5819352869353</v>
+        <v>184.4987990196078</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>64.83978238428239</v>
+        <v>64.48167250233428</v>
       </c>
       <c r="Y40" t="n">
-        <v>1063629.955599956</v>
+        <v>1170122.414799253</v>
       </c>
       <c r="Z40" t="n">
-        <v>69.44951998001997</v>
+        <v>71.18651844070961</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" t="n">
-        <v>26.87179487179488</v>
-      </c>
-      <c r="D41" t="n">
-        <v>185.6597513597513</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.086713286713287</v>
-      </c>
-      <c r="F41" t="n">
-        <v>69.51756021756022</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1987466.977466978</v>
-      </c>
-      <c r="H41" t="n">
-        <v>72.81709401709402</v>
-      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>27.25943223443224</v>
-      </c>
-      <c r="P41" t="n">
-        <v>185.3515125454256</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.130397863006559</v>
-      </c>
-      <c r="R41" t="n">
-        <v>69.87794495359714</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2098139.105459758</v>
-      </c>
-      <c r="T41" t="n">
-        <v>73.09123130492695</v>
-      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
-        <v>21.4</v>
+        <v>29</v>
       </c>
       <c r="V41" t="n">
-        <v>179.8</v>
+        <v>181.6</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>61.6</v>
+        <v>70.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>775000</v>
+        <v>1820000</v>
       </c>
       <c r="Z41" t="n">
-        <v>70.8</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>25.81414141414142</v>
+        <v>24.36721763085399</v>
       </c>
       <c r="D42" t="n">
-        <v>182.3282828282828</v>
+        <v>183.6962350780533</v>
       </c>
       <c r="E42" t="n">
-        <v>1.02020202020202</v>
+        <v>1.137373737373737</v>
       </c>
       <c r="F42" t="n">
-        <v>67.42323232323233</v>
+        <v>68.50413223140495</v>
       </c>
       <c r="G42" t="n">
-        <v>1496035.353535354</v>
+        <v>2162217.630853994</v>
       </c>
       <c r="H42" t="n">
-        <v>71.88585858585857</v>
+        <v>74.76501377410467</v>
       </c>
       <c r="I42" t="n">
-        <v>26.21969696969697</v>
+        <v>27.85143097643098</v>
       </c>
       <c r="J42" t="n">
-        <v>183.0303030303031</v>
+        <v>181.1434343434343</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>1.018518518518518</v>
       </c>
       <c r="L42" t="n">
-        <v>70.45454545454545</v>
+        <v>67.81784511784512</v>
       </c>
       <c r="M42" t="n">
-        <v>2521590.909090909</v>
+        <v>1447777.777777778</v>
       </c>
       <c r="N42" t="n">
-        <v>74.28030303030303</v>
+        <v>70.10159932659933</v>
       </c>
       <c r="O42" t="n">
-        <v>26.59254885032663</v>
+        <v>24.87231675198764</v>
       </c>
       <c r="P42" t="n">
-        <v>181.4586773720107</v>
+        <v>183.409117844062</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.12371233704567</v>
+        <v>1.150258846237443</v>
       </c>
       <c r="R42" t="n">
-        <v>66.87789634234079</v>
+        <v>68.62056105827138</v>
       </c>
       <c r="S42" t="n">
-        <v>1377551.238884572</v>
+        <v>2368801.868320579</v>
       </c>
       <c r="T42" t="n">
-        <v>70.74887852887852</v>
+        <v>74.57840383132817</v>
       </c>
       <c r="U42" t="n">
-        <v>25.43375965151327</v>
+        <v>25.20616465659944</v>
       </c>
       <c r="V42" t="n">
-        <v>182.39419025352</v>
+        <v>179.1507580402689</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>1.006805555555556</v>
       </c>
       <c r="X42" t="n">
-        <v>68.43747212931994</v>
+        <v>64.93143918279787</v>
       </c>
       <c r="Y42" t="n">
-        <v>1973982.049217556</v>
+        <v>1193535.301003345</v>
       </c>
       <c r="Z42" t="n">
-        <v>73.31346902225526</v>
+        <v>69.48274302388432</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>23.65545454545454</v>
+        <v>26.38727272727273</v>
       </c>
       <c r="D43" t="n">
-        <v>184.2072727272727</v>
+        <v>184.4963636363637</v>
       </c>
       <c r="E43" t="n">
-        <v>1.149090909090909</v>
+        <v>1.019090909090909</v>
       </c>
       <c r="F43" t="n">
-        <v>68.15454545454546</v>
+        <v>67.11636363636364</v>
       </c>
       <c r="G43" t="n">
-        <v>2220181.818181818</v>
+        <v>1309840.909090909</v>
       </c>
       <c r="H43" t="n">
-        <v>75.17181818181817</v>
+        <v>70.48818181818183</v>
       </c>
       <c r="I43" t="n">
-        <v>26.02636363636363</v>
+        <v>25.55277777777778</v>
       </c>
       <c r="J43" t="n">
-        <v>184.4520454545454</v>
+        <v>183.5716049382716</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>65.35113636363636</v>
+        <v>66.52746913580248</v>
       </c>
       <c r="M43" t="n">
-        <v>1097702.272727273</v>
+        <v>1187901.234567901</v>
       </c>
       <c r="N43" t="n">
-        <v>68.89749999999999</v>
+        <v>70.28456790123457</v>
       </c>
       <c r="O43" t="n">
-        <v>24.85835795099592</v>
+        <v>24.56836745862832</v>
       </c>
       <c r="P43" t="n">
-        <v>183.359672485611</v>
+        <v>182.8497245170288</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.16718949276595</v>
+        <v>1.007692307692308</v>
       </c>
       <c r="R43" t="n">
-        <v>68.75142668790804</v>
+        <v>64.4695638757378</v>
       </c>
       <c r="S43" t="n">
-        <v>2496013.602771684</v>
+        <v>1056942.400160226</v>
       </c>
       <c r="T43" t="n">
-        <v>74.88350611922291</v>
+        <v>69.79114614853745</v>
       </c>
       <c r="U43" t="n">
-        <v>25.99042874396135</v>
+        <v>25.18190172400698</v>
       </c>
       <c r="V43" t="n">
-        <v>182.1929347826087</v>
+        <v>183.4440810359232</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>64.02976046698873</v>
+        <v>64.8128593073593</v>
       </c>
       <c r="Y43" t="n">
-        <v>1002673.169825344</v>
+        <v>1035885.016328701</v>
       </c>
       <c r="Z43" t="n">
-        <v>67.88176173665303</v>
+        <v>69.30842686261107</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>25.87107438016529</v>
+        <v>25.72181818181819</v>
       </c>
       <c r="D44" t="n">
-        <v>186.6884297520661</v>
+        <v>182.7009090909091</v>
       </c>
       <c r="E44" t="n">
-        <v>1.227272727272727</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>73.19669421487605</v>
+        <v>67.68636363636364</v>
       </c>
       <c r="G44" t="n">
-        <v>5316033.05785124</v>
+        <v>1565022.727272727</v>
       </c>
       <c r="H44" t="n">
-        <v>76.90082644628099</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+        <v>72.04636363636364</v>
+      </c>
+      <c r="I44" t="n">
+        <v>26.05636363636363</v>
+      </c>
+      <c r="J44" t="n">
+        <v>184.1720454545454</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>65.23113636363635</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1078602.272727273</v>
+      </c>
+      <c r="N44" t="n">
+        <v>68.8175</v>
+      </c>
       <c r="O44" t="n">
-        <v>23.99010501991761</v>
+        <v>25.83424634624635</v>
       </c>
       <c r="P44" t="n">
-        <v>184.8949125465017</v>
+        <v>182.0086191586192</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.126287715837941</v>
+        <v>1.103341103341103</v>
       </c>
       <c r="R44" t="n">
-        <v>70.65821696516599</v>
+        <v>66.47505908905909</v>
       </c>
       <c r="S44" t="n">
-        <v>3979469.669205801</v>
+        <v>1409329.448329448</v>
       </c>
       <c r="T44" t="n">
-        <v>77.3441520173979</v>
-      </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+        <v>70.94827639027639</v>
+      </c>
+      <c r="U44" t="n">
+        <v>25.99547260361047</v>
+      </c>
+      <c r="V44" t="n">
+        <v>182.1657418001526</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>64.08524292312907</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1016423.169825344</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>67.96443717524953</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>26.05308641975309</v>
+        <v>25.6297520661157</v>
       </c>
       <c r="D45" t="n">
-        <v>183.1037037037037</v>
+        <v>186.5504132231405</v>
       </c>
       <c r="E45" t="n">
-        <v>1.104938271604938</v>
+        <v>1.216528925619835</v>
       </c>
       <c r="F45" t="n">
-        <v>68.59876543209877</v>
+        <v>72.97520661157024</v>
       </c>
       <c r="G45" t="n">
-        <v>1671203.703703704</v>
+        <v>5321280.991735538</v>
       </c>
       <c r="H45" t="n">
-        <v>72.31358024691357</v>
+        <v>76.81652892561983</v>
       </c>
       <c r="I45" t="n">
-        <v>24.04636363636363</v>
+        <v>26.68874458874459</v>
       </c>
       <c r="J45" t="n">
-        <v>184.7945454545455</v>
+        <v>185.6223665223665</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>1.073376623376623</v>
       </c>
       <c r="L45" t="n">
-        <v>71.14181818181819</v>
+        <v>69.49617604617605</v>
       </c>
       <c r="M45" t="n">
-        <v>4415181.818181818</v>
+        <v>1990764.79076479</v>
       </c>
       <c r="N45" t="n">
-        <v>76.64727272727274</v>
+        <v>72.82106782106781</v>
       </c>
       <c r="O45" t="n">
-        <v>23.9060405643739</v>
+        <v>23.81737774719034</v>
       </c>
       <c r="P45" t="n">
-        <v>184.3540123456791</v>
+        <v>184.6449125465017</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>1.128385617935843</v>
       </c>
       <c r="R45" t="n">
-        <v>64.02879188712522</v>
+        <v>70.3708043777534</v>
       </c>
       <c r="S45" t="n">
-        <v>1099708.002645503</v>
+        <v>3866672.466408598</v>
       </c>
       <c r="T45" t="n">
-        <v>70.74927248677248</v>
+        <v>77.24240376564966</v>
       </c>
       <c r="U45" t="n">
-        <v>23.17223981249468</v>
+        <v>26.94418811002662</v>
       </c>
       <c r="V45" t="n">
-        <v>184.6098602019891</v>
+        <v>185.0683817321395</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>1.118495738216235</v>
       </c>
       <c r="X45" t="n">
-        <v>67.55594103200924</v>
+        <v>69.80358863703584</v>
       </c>
       <c r="Y45" t="n">
-        <v>2545997.034019897</v>
+        <v>2103228.030639133</v>
       </c>
       <c r="Z45" t="n">
-        <v>74.75548996577857</v>
+        <v>73.18901084939905</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="D46" t="n">
+        <v>183.32</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F46" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1037400</v>
+      </c>
+      <c r="H46" t="n">
+        <v>69.97999999999999</v>
+      </c>
+      <c r="I46" t="n">
+        <v>25.45206611570248</v>
+      </c>
+      <c r="J46" t="n">
+        <v>183.2471074380165</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>67.04545454545455</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1360103.305785124</v>
+      </c>
+      <c r="N46" t="n">
+        <v>71.03801652892561</v>
+      </c>
+      <c r="O46" t="n">
+        <v>24.89329614461308</v>
+      </c>
+      <c r="P46" t="n">
+        <v>185.0998843987608</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.030678106917237</v>
+      </c>
+      <c r="R46" t="n">
+        <v>65.26908853363773</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1046866.811003853</v>
+      </c>
+      <c r="T46" t="n">
+        <v>69.2467237469709</v>
+      </c>
+      <c r="U46" t="n">
+        <v>23.56668197286638</v>
+      </c>
+      <c r="V46" t="n">
+        <v>182.0834655940428</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>64.17281167857631</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1159419.451042877</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>71.28115552613303</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>27.10209790209791</v>
+      </c>
+      <c r="D47" t="n">
+        <v>181.3921522921523</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>67.47521367521368</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1250264.18026418</v>
+      </c>
+      <c r="H47" t="n">
+        <v>70.13022533022534</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>25.37346197961583</v>
+      </c>
+      <c r="P47" t="n">
+        <v>180.0884310988157</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>65.8332191739884</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1166835.269431423</v>
+      </c>
+      <c r="T47" t="n">
+        <v>70.57649080264466</v>
+      </c>
+      <c r="U47" t="n">
+        <v>22.3875</v>
+      </c>
+      <c r="V47" t="n">
+        <v>180.65</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>62.2375</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>823437.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>70.52500000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>23.66689623507806</v>
+      </c>
+      <c r="D48" t="n">
+        <v>184.9233241505969</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>70.11099632690542</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3865992.309458219</v>
+      </c>
+      <c r="H48" t="n">
+        <v>76.18893480257115</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>22.82705449210833</v>
+      </c>
+      <c r="P48" t="n">
+        <v>184.6810762486243</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>66.67392677628128</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2307231.237192734</v>
+      </c>
+      <c r="T48" t="n">
+        <v>74.58773132593836</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>25.52047750229569</v>
+      </c>
+      <c r="J49" t="n">
+        <v>184.7290174471993</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.264738292011019</v>
+      </c>
+      <c r="L49" t="n">
+        <v>70.86786042240588</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3244237.832874197</v>
+      </c>
+      <c r="N49" t="n">
+        <v>76.37658402203857</v>
+      </c>
+      <c r="O49" t="n">
+        <v>29</v>
+      </c>
+      <c r="P49" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="T49" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>24.6231770980997</v>
+      </c>
+      <c r="V49" t="n">
+        <v>183.205746338285</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.192188647266047</v>
+      </c>
+      <c r="X49" t="n">
+        <v>69.55463642652498</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2992488.039308473</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>75.64575599151452</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>26.05734265734266</v>
+      </c>
+      <c r="D50" t="n">
+        <v>182.8741258741259</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>70.44335664335664</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2576153.846153846</v>
+      </c>
+      <c r="H50" t="n">
+        <v>74.4979020979021</v>
+      </c>
+      <c r="I50" t="n">
+        <v>25.88727272727273</v>
+      </c>
+      <c r="J50" t="n">
+        <v>182.7136363636363</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>67.59181818181818</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1341204.545454545</v>
+      </c>
+      <c r="N50" t="n">
+        <v>71.26727272727274</v>
+      </c>
+      <c r="O50" t="n">
+        <v>25.44150277753957</v>
+      </c>
+      <c r="P50" t="n">
+        <v>182.3927914987279</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.003205128205128</v>
+      </c>
+      <c r="R50" t="n">
+        <v>68.70878760159695</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2063652.202498356</v>
+      </c>
+      <c r="T50" t="n">
+        <v>73.52096137171387</v>
+      </c>
+      <c r="U50" t="n">
+        <v>23.8005059015059</v>
+      </c>
+      <c r="V50" t="n">
+        <v>181.7865268620268</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>66.41397374847375</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1434065.595746846</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>72.67669576719577</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>25.69777777777778</v>
+      </c>
+      <c r="D51" t="n">
+        <v>183.7122222222222</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="F51" t="n">
+        <v>68.19666666666667</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1628027.777777778</v>
+      </c>
+      <c r="H51" t="n">
+        <v>72.25444444444445</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>23.96159663865546</v>
+      </c>
+      <c r="P51" t="n">
+        <v>184.4987990196078</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>64.48167250233428</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1170122.414799253</v>
+      </c>
+      <c r="T51" t="n">
+        <v>71.18651844070961</v>
+      </c>
+      <c r="U51" t="n">
+        <v>23.96527777777778</v>
+      </c>
+      <c r="V51" t="n">
+        <v>182.6527777777777</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>68.25694444444444</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>2353125</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>73.375</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,329 +558,1313 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.48717171717172</v>
+        <v>26.22237762237762</v>
       </c>
       <c r="D2" t="n">
-        <v>184.8768686868687</v>
+        <v>183.7076923076923</v>
       </c>
       <c r="E2" t="n">
-        <v>1.058181818181818</v>
+        <v>1.616783216783217</v>
       </c>
       <c r="F2" t="n">
-        <v>69.75646464646465</v>
+        <v>76.3944055944056</v>
       </c>
       <c r="G2" t="n">
-        <v>2982873.737373737</v>
+        <v>12678321.67832168</v>
       </c>
       <c r="H2" t="n">
-        <v>75.54333333333332</v>
+        <v>79.63426573426574</v>
       </c>
       <c r="I2" t="n">
-        <v>25.31878787878788</v>
+        <v>25.13492063492064</v>
       </c>
       <c r="J2" t="n">
-        <v>184.3144444444445</v>
+        <v>184.6316738816739</v>
       </c>
       <c r="K2" t="n">
-        <v>1.781212121212121</v>
+        <v>1.015079365079365</v>
       </c>
       <c r="L2" t="n">
-        <v>80.50020202020202</v>
+        <v>69.93658008658008</v>
       </c>
       <c r="M2" t="n">
-        <v>34390267.67676768</v>
+        <v>2656121.933621933</v>
       </c>
       <c r="N2" t="n">
-        <v>84.09676767676768</v>
+        <v>74.38225108225109</v>
       </c>
       <c r="O2" t="n">
-        <v>24.72831439896657</v>
+        <v>24.95155619948295</v>
       </c>
       <c r="P2" t="n">
-        <v>184.0096923607794</v>
+        <v>181.7271984189602</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.107739422413336</v>
+        <v>1.550788197131392</v>
       </c>
       <c r="R2" t="n">
-        <v>68.11976407248146</v>
+        <v>74.58407301542303</v>
       </c>
       <c r="S2" t="n">
-        <v>2367220.084364106</v>
+        <v>11541974.43774517</v>
       </c>
       <c r="T2" t="n">
-        <v>73.63034033197076</v>
+        <v>79.26224403502179</v>
       </c>
       <c r="U2" t="n">
-        <v>24.15642184521132</v>
+        <v>25.54059544465559</v>
       </c>
       <c r="V2" t="n">
-        <v>184.4817940149519</v>
+        <v>181.8841578221277</v>
       </c>
       <c r="W2" t="n">
-        <v>1.521579482895272</v>
+        <v>1.040302855039698</v>
       </c>
       <c r="X2" t="n">
-        <v>76.40987382987383</v>
+        <v>67.40725249687657</v>
       </c>
       <c r="Y2" t="n">
-        <v>22494439.3558683</v>
+        <v>1621063.413278451</v>
       </c>
       <c r="Z2" t="n">
-        <v>82.2719227984491</v>
+        <v>72.34852959071004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24.94214876033058</v>
+        <v>25.94132231404959</v>
       </c>
       <c r="D3" t="n">
-        <v>186.5454545454545</v>
+        <v>186.0181818181818</v>
       </c>
       <c r="E3" t="n">
-        <v>1.041322314049587</v>
+        <v>1.26198347107438</v>
       </c>
       <c r="F3" t="n">
-        <v>73.32231404958678</v>
+        <v>76.08925619834712</v>
       </c>
       <c r="G3" t="n">
-        <v>5104958.67768595</v>
+        <v>13144876.03305785</v>
       </c>
       <c r="H3" t="n">
-        <v>77.13223140495869</v>
+        <v>79.13553719008264</v>
       </c>
       <c r="I3" t="n">
-        <v>26.67390572390572</v>
+        <v>25.88571428571428</v>
       </c>
       <c r="J3" t="n">
-        <v>183.8352693602693</v>
+        <v>187.2525974025974</v>
       </c>
       <c r="K3" t="n">
-        <v>1.721464646464646</v>
+        <v>1.52987012987013</v>
       </c>
       <c r="L3" t="n">
-        <v>77.52996632996633</v>
+        <v>78.20649350649352</v>
       </c>
       <c r="M3" t="n">
-        <v>18239831.64983165</v>
+        <v>18650324.67532467</v>
       </c>
       <c r="N3" t="n">
-        <v>79.89006734006735</v>
+        <v>81.52142857142857</v>
       </c>
       <c r="O3" t="n">
-        <v>25.4026541882558</v>
+        <v>24.82488354555974</v>
       </c>
       <c r="P3" t="n">
-        <v>183.0104600351125</v>
+        <v>184.9848120595201</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.07102466903269</v>
+        <v>1.17376111239044</v>
       </c>
       <c r="R3" t="n">
-        <v>70.91299251154867</v>
+        <v>71.84112376935695</v>
       </c>
       <c r="S3" t="n">
-        <v>3252643.011276701</v>
+        <v>5778426.326308399</v>
       </c>
       <c r="T3" t="n">
-        <v>74.80333207246309</v>
+        <v>76.07582417191902</v>
       </c>
       <c r="U3" t="n">
-        <v>26.29710258435945</v>
+        <v>25.38111969523461</v>
       </c>
       <c r="V3" t="n">
-        <v>182.2940931668764</v>
+        <v>186.5566248508795</v>
       </c>
       <c r="W3" t="n">
-        <v>1.760422899310199</v>
+        <v>1.366661010372191</v>
       </c>
       <c r="X3" t="n">
-        <v>76.40353739668672</v>
+        <v>74.84583374584928</v>
       </c>
       <c r="Y3" t="n">
-        <v>15881867.18092167</v>
+        <v>13202699.953997</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.52748934259232</v>
+        <v>78.82436163158214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.96272727272727</v>
+        <v>26.06681818181818</v>
       </c>
       <c r="D4" t="n">
-        <v>183.0218181818182</v>
+        <v>182.2870454545455</v>
       </c>
       <c r="E4" t="n">
-        <v>2.395454545454546</v>
+        <v>2.087727272727273</v>
       </c>
       <c r="F4" t="n">
-        <v>82.8209090909091</v>
+        <v>78.55727272727272</v>
       </c>
       <c r="G4" t="n">
-        <v>39894545.45454545</v>
+        <v>21251022.72727273</v>
       </c>
       <c r="H4" t="n">
-        <v>84.67363636363636</v>
+        <v>80.70545454545454</v>
       </c>
       <c r="I4" t="n">
-        <v>23.99173553719008</v>
+        <v>25.22148760330579</v>
       </c>
       <c r="J4" t="n">
-        <v>184.2871900826446</v>
+        <v>184.1404958677686</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="L4" t="n">
-        <v>72.01859504132231</v>
+        <v>72.12975206611571</v>
       </c>
       <c r="M4" t="n">
-        <v>5430578.512396694</v>
+        <v>4288842.975206612</v>
       </c>
       <c r="N4" t="n">
-        <v>77.85330578512398</v>
+        <v>76.1107438016529</v>
       </c>
       <c r="O4" t="n">
-        <v>27.13419178567005</v>
+        <v>25.34594552990198</v>
       </c>
       <c r="P4" t="n">
-        <v>182.4003616464051</v>
+        <v>182.7396397178475</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.886655783829697</v>
+        <v>1.963514286009749</v>
       </c>
       <c r="R4" t="n">
-        <v>79.00864672364672</v>
+        <v>76.28715226948893</v>
       </c>
       <c r="S4" t="n">
-        <v>24048401.07235759</v>
+        <v>17566886.10747322</v>
       </c>
       <c r="T4" t="n">
-        <v>81.47243244678027</v>
+        <v>80.59263702100816</v>
       </c>
       <c r="U4" t="n">
-        <v>23.14157997054606</v>
+        <v>24.8531746031746</v>
       </c>
       <c r="V4" t="n">
-        <v>182.5890715479191</v>
+        <v>182.0717010262465</v>
       </c>
       <c r="W4" t="n">
-        <v>1.062375411150115</v>
+        <v>1.113728022818932</v>
       </c>
       <c r="X4" t="n">
-        <v>68.02060958757859</v>
+        <v>69.58585606312879</v>
       </c>
       <c r="Y4" t="n">
-        <v>2648390.130764688</v>
+        <v>2894139.097434552</v>
       </c>
       <c r="Z4" t="n">
-        <v>74.87350004824938</v>
+        <v>74.7756734006734</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
+        <v>26.4198347107438</v>
+      </c>
+      <c r="D5" t="n">
+        <v>182.2107438016529</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.729752066115703</v>
+      </c>
+      <c r="F5" t="n">
+        <v>80.77355371900826</v>
+      </c>
+      <c r="G5" t="n">
+        <v>34887851.23966942</v>
+      </c>
+      <c r="H5" t="n">
+        <v>82.47272727272728</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24.68181818181818</v>
+      </c>
+      <c r="J5" t="n">
+        <v>185.5181818181818</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.281818181818182</v>
+      </c>
+      <c r="L5" t="n">
+        <v>75.12727272727273</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11041818.18181818</v>
+      </c>
+      <c r="N5" t="n">
+        <v>79.58181818181819</v>
+      </c>
+      <c r="O5" t="n">
+        <v>24.90901144856957</v>
+      </c>
+      <c r="P5" t="n">
+        <v>181.1425217320025</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.512801672793229</v>
+      </c>
+      <c r="R5" t="n">
+        <v>75.79453752744634</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15219224.27376779</v>
+      </c>
+      <c r="T5" t="n">
+        <v>79.08278045015309</v>
+      </c>
+      <c r="U5" t="n">
+        <v>23.0821855500821</v>
+      </c>
+      <c r="V5" t="n">
+        <v>184.6805205254516</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.202333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>71.2915041050903</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6950567.528735632</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>78.0733382594417</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>25.34710743801653</v>
+      </c>
+      <c r="D6" t="n">
+        <v>184.4380165289256</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.173553719008265</v>
+      </c>
+      <c r="F6" t="n">
+        <v>72.18181818181819</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3835330.578512396</v>
+      </c>
+      <c r="H6" t="n">
+        <v>75.84297520661157</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.8037037037037</v>
+      </c>
+      <c r="J6" t="n">
+        <v>181.1512345679012</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.076234567901234</v>
+      </c>
+      <c r="L6" t="n">
+        <v>71.1848765432099</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3585370.370370371</v>
+      </c>
+      <c r="N6" t="n">
+        <v>73.63703703703703</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25.769700414528</v>
+      </c>
+      <c r="P6" t="n">
+        <v>183.2808811877777</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.178140824692549</v>
+      </c>
+      <c r="R6" t="n">
+        <v>69.9454935868729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2704018.66237211</v>
+      </c>
+      <c r="T6" t="n">
+        <v>74.26468875951636</v>
+      </c>
+      <c r="U6" t="n">
+        <v>26.54628619528619</v>
+      </c>
+      <c r="V6" t="n">
+        <v>183.7406428386428</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.255309505309505</v>
+      </c>
+      <c r="X6" t="n">
+        <v>70.05600543900543</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2813568.1002331</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>72.48127298627298</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25.0446510560147</v>
+      </c>
+      <c r="D7" t="n">
+        <v>184.2012167125804</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.140266299357209</v>
+      </c>
+      <c r="F7" t="n">
+        <v>73.0121671258035</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4763096.877869605</v>
+      </c>
+      <c r="H7" t="n">
+        <v>76.64267676767678</v>
+      </c>
+      <c r="I7" t="n">
+        <v>25.62402874902875</v>
+      </c>
+      <c r="J7" t="n">
+        <v>186.4061771561772</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.755827505827506</v>
+      </c>
+      <c r="L7" t="n">
+        <v>80.21416083916083</v>
+      </c>
+      <c r="M7" t="n">
+        <v>29955778.94327894</v>
+      </c>
+      <c r="N7" t="n">
+        <v>83.81876456876458</v>
+      </c>
+      <c r="O7" t="n">
+        <v>24.26546509046509</v>
+      </c>
+      <c r="P7" t="n">
+        <v>182.7177156177156</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.037638287638288</v>
+      </c>
+      <c r="R7" t="n">
+        <v>70.56276131276131</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3403146.991896993</v>
+      </c>
+      <c r="T7" t="n">
+        <v>75.29687072187072</v>
+      </c>
+      <c r="U7" t="n">
+        <v>24.8432502204127</v>
+      </c>
+      <c r="V7" t="n">
+        <v>183.798079082118</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.744378062821999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>76.23635323867589</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>15836567.78919022</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>81.52249692971661</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25.13492063492064</v>
+      </c>
+      <c r="D8" t="n">
+        <v>184.6316738816739</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.015079365079365</v>
+      </c>
+      <c r="F8" t="n">
+        <v>69.93658008658008</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2656121.933621933</v>
+      </c>
+      <c r="H8" t="n">
+        <v>74.38225108225109</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25.94132231404959</v>
+      </c>
+      <c r="J8" t="n">
+        <v>186.0181818181818</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.26198347107438</v>
+      </c>
+      <c r="L8" t="n">
+        <v>76.08925619834712</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13144876.03305785</v>
+      </c>
+      <c r="N8" t="n">
+        <v>79.13553719008264</v>
+      </c>
+      <c r="O8" t="n">
+        <v>25.54059544465559</v>
+      </c>
+      <c r="P8" t="n">
+        <v>181.8841578221277</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.040302855039698</v>
+      </c>
+      <c r="R8" t="n">
+        <v>67.40725249687657</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1621063.413278451</v>
+      </c>
+      <c r="T8" t="n">
+        <v>72.34852959071004</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24.82488354555974</v>
+      </c>
+      <c r="V8" t="n">
+        <v>184.9848120595201</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.17376111239044</v>
+      </c>
+      <c r="X8" t="n">
+        <v>71.84112376935695</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5778426.326308399</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>76.07582417191902</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>27.96272727272727</v>
+      </c>
+      <c r="D9" t="n">
+        <v>183.0218181818182</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.395454545454546</v>
+      </c>
+      <c r="F9" t="n">
+        <v>82.8209090909091</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39894545.45454545</v>
+      </c>
+      <c r="H9" t="n">
+        <v>84.67363636363636</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.88571428571428</v>
+      </c>
+      <c r="J9" t="n">
+        <v>187.2525974025974</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.52987012987013</v>
+      </c>
+      <c r="L9" t="n">
+        <v>78.20649350649352</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18650324.67532467</v>
+      </c>
+      <c r="N9" t="n">
+        <v>81.52142857142857</v>
+      </c>
+      <c r="O9" t="n">
+        <v>27.13419178567005</v>
+      </c>
+      <c r="P9" t="n">
+        <v>182.4003616464051</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.886655783829697</v>
+      </c>
+      <c r="R9" t="n">
+        <v>79.00864672364672</v>
+      </c>
+      <c r="S9" t="n">
+        <v>24048401.07235759</v>
+      </c>
+      <c r="T9" t="n">
+        <v>81.47243244678027</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.38111969523461</v>
+      </c>
+      <c r="V9" t="n">
+        <v>186.5566248508795</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.366661010372191</v>
+      </c>
+      <c r="X9" t="n">
+        <v>74.84583374584928</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>13202699.953997</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>78.82436163158214</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24.68181818181818</v>
+      </c>
+      <c r="D10" t="n">
+        <v>185.5181818181818</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.281818181818182</v>
+      </c>
+      <c r="F10" t="n">
+        <v>75.12727272727273</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11041818.18181818</v>
+      </c>
+      <c r="H10" t="n">
+        <v>79.58181818181819</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.22148760330579</v>
+      </c>
+      <c r="J10" t="n">
+        <v>184.1404958677686</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.033057851239669</v>
+      </c>
+      <c r="L10" t="n">
+        <v>72.12975206611571</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4288842.975206612</v>
+      </c>
+      <c r="N10" t="n">
+        <v>76.1107438016529</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23.0821855500821</v>
+      </c>
+      <c r="P10" t="n">
+        <v>184.6805205254516</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.202333333333333</v>
+      </c>
+      <c r="R10" t="n">
+        <v>71.2915041050903</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6950567.528735632</v>
+      </c>
+      <c r="T10" t="n">
+        <v>78.0733382594417</v>
+      </c>
+      <c r="U10" t="n">
+        <v>24.8531746031746</v>
+      </c>
+      <c r="V10" t="n">
+        <v>182.0717010262465</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.113728022818932</v>
+      </c>
+      <c r="X10" t="n">
+        <v>69.58585606312879</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2894139.097434552</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>74.7756734006734</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>23.99173553719008</v>
+      </c>
+      <c r="D11" t="n">
+        <v>184.2871900826446</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>72.01859504132231</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5430578.512396694</v>
+      </c>
+      <c r="H11" t="n">
+        <v>77.85330578512398</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25.34710743801653</v>
+      </c>
+      <c r="J11" t="n">
+        <v>184.4380165289256</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.173553719008265</v>
+      </c>
+      <c r="L11" t="n">
+        <v>72.18181818181819</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3835330.578512396</v>
+      </c>
+      <c r="N11" t="n">
+        <v>75.84297520661157</v>
+      </c>
+      <c r="O11" t="n">
+        <v>23.14157997054606</v>
+      </c>
+      <c r="P11" t="n">
+        <v>182.5890715479191</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.062375411150115</v>
+      </c>
+      <c r="R11" t="n">
+        <v>68.02060958757859</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2648390.130764688</v>
+      </c>
+      <c r="T11" t="n">
+        <v>74.87350004824938</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.769700414528</v>
+      </c>
+      <c r="V11" t="n">
+        <v>183.2808811877777</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.178140824692549</v>
+      </c>
+      <c r="X11" t="n">
+        <v>69.9454935868729</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2704018.66237211</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>74.26468875951636</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>26.70668220668221</v>
+      </c>
+      <c r="D12" t="n">
+        <v>183.7864024864025</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.71981351981352</v>
+      </c>
+      <c r="F12" t="n">
+        <v>77.64304584304584</v>
+      </c>
+      <c r="G12" t="n">
+        <v>18319075.36907537</v>
+      </c>
+      <c r="H12" t="n">
+        <v>79.95236985236986</v>
+      </c>
+      <c r="I12" t="n">
+        <v>25.24435261707988</v>
+      </c>
+      <c r="J12" t="n">
+        <v>184.2949494949495</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.792011019283746</v>
+      </c>
+      <c r="L12" t="n">
+        <v>80.60927456382002</v>
+      </c>
+      <c r="M12" t="n">
+        <v>35322970.61524335</v>
+      </c>
+      <c r="N12" t="n">
+        <v>84.21524334251608</v>
+      </c>
+      <c r="O12" t="n">
+        <v>26.20053059069077</v>
+      </c>
+      <c r="P12" t="n">
+        <v>182.2746757437833</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.721159599363261</v>
+      </c>
+      <c r="R12" t="n">
+        <v>76.26031657130055</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15511947.91059436</v>
+      </c>
+      <c r="T12" t="n">
+        <v>79.4644773418801</v>
+      </c>
+      <c r="U12" t="n">
+        <v>24.09977743504059</v>
+      </c>
+      <c r="V12" t="n">
+        <v>184.0198127408653</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.498405590510854</v>
+      </c>
+      <c r="X12" t="n">
+        <v>76.56655196655197</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22507672.14169845</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>82.3017479985901</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.4198347107438</v>
+      </c>
+      <c r="D13" t="n">
+        <v>182.2107438016529</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.729752066115703</v>
+      </c>
+      <c r="F13" t="n">
+        <v>80.77355371900826</v>
+      </c>
+      <c r="G13" t="n">
+        <v>34887851.23966942</v>
+      </c>
+      <c r="H13" t="n">
+        <v>82.47272727272728</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24.30146923783288</v>
+      </c>
+      <c r="J13" t="n">
+        <v>184.8678604224059</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.052892561983471</v>
+      </c>
+      <c r="L13" t="n">
+        <v>69.73820018365473</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3034935.720844812</v>
+      </c>
+      <c r="N13" t="n">
+        <v>75.7060606060606</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24.90901144856957</v>
+      </c>
+      <c r="P13" t="n">
+        <v>181.1425217320025</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.512801672793229</v>
+      </c>
+      <c r="R13" t="n">
+        <v>75.79453752744634</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15219224.27376779</v>
+      </c>
+      <c r="T13" t="n">
+        <v>79.08278045015309</v>
+      </c>
+      <c r="U13" t="n">
+        <v>24.61664945360597</v>
+      </c>
+      <c r="V13" t="n">
+        <v>183.7360839643449</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.111581293103032</v>
+      </c>
+      <c r="X13" t="n">
+        <v>68.18160370225587</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2439245.531240096</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>73.75940030179162</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.22237762237762</v>
+      </c>
+      <c r="D14" t="n">
+        <v>183.7076923076923</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.616783216783217</v>
+      </c>
+      <c r="F14" t="n">
+        <v>76.3944055944056</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12678321.67832168</v>
+      </c>
+      <c r="H14" t="n">
+        <v>79.63426573426574</v>
+      </c>
+      <c r="I14" t="n">
         <v>25.54132231404959</v>
       </c>
-      <c r="D5" t="n">
+      <c r="J14" t="n">
         <v>183.7297520661157</v>
       </c>
-      <c r="E5" t="n">
+      <c r="K14" t="n">
         <v>1.37603305785124</v>
       </c>
-      <c r="F5" t="n">
+      <c r="L14" t="n">
         <v>73.23388429752066</v>
       </c>
-      <c r="G5" t="n">
+      <c r="M14" t="n">
         <v>6951404.958677686</v>
       </c>
-      <c r="H5" t="n">
+      <c r="N14" t="n">
         <v>77.45537190082645</v>
       </c>
-      <c r="I5" t="n">
+      <c r="O14" t="n">
+        <v>24.95155619948295</v>
+      </c>
+      <c r="P14" t="n">
+        <v>181.7271984189602</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.550788197131392</v>
+      </c>
+      <c r="R14" t="n">
+        <v>74.58407301542303</v>
+      </c>
+      <c r="S14" t="n">
+        <v>11541974.43774517</v>
+      </c>
+      <c r="T14" t="n">
+        <v>79.26224403502179</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25.67393444719531</v>
+      </c>
+      <c r="V14" t="n">
+        <v>182.1304464858813</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.283091883961449</v>
+      </c>
+      <c r="X14" t="n">
+        <v>71.61341177341177</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4347172.999102348</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>76.64134939939287</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
         <v>26.18181818181818</v>
       </c>
-      <c r="J5" t="n">
+      <c r="D15" t="n">
         <v>184.2363636363637</v>
       </c>
-      <c r="K5" t="n">
+      <c r="E15" t="n">
         <v>1.207438016528926</v>
       </c>
-      <c r="L5" t="n">
+      <c r="F15" t="n">
         <v>73.02892561983471</v>
       </c>
-      <c r="M5" t="n">
+      <c r="G15" t="n">
         <v>5968553.719008264</v>
       </c>
-      <c r="N5" t="n">
+      <c r="H15" t="n">
         <v>77.41239669421488</v>
       </c>
-      <c r="O5" t="n">
-        <v>25.67393444719531</v>
-      </c>
-      <c r="P5" t="n">
-        <v>182.1304464858813</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.283091883961449</v>
-      </c>
-      <c r="R5" t="n">
-        <v>71.61341177341177</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4347172.999102348</v>
-      </c>
-      <c r="T5" t="n">
-        <v>76.64134939939287</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="I15" t="n">
+        <v>25.0446510560147</v>
+      </c>
+      <c r="J15" t="n">
+        <v>184.2012167125804</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.140266299357209</v>
+      </c>
+      <c r="L15" t="n">
+        <v>73.0121671258035</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4763096.877869605</v>
+      </c>
+      <c r="N15" t="n">
+        <v>76.64267676767678</v>
+      </c>
+      <c r="O15" t="n">
         <v>26.57286350903998</v>
       </c>
-      <c r="V5" t="n">
+      <c r="P15" t="n">
         <v>184.7808097784569</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Q15" t="n">
         <v>1.389453781512605</v>
       </c>
-      <c r="X5" t="n">
+      <c r="R15" t="n">
         <v>70.33046345811053</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="S15" t="n">
         <v>3512656.226126814</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="T15" t="n">
         <v>73.98766870384519</v>
+      </c>
+      <c r="U15" t="n">
+        <v>24.26546509046509</v>
+      </c>
+      <c r="V15" t="n">
+        <v>182.7177156177156</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.037638287638288</v>
+      </c>
+      <c r="X15" t="n">
+        <v>70.56276131276131</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3403146.991896993</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>75.29687072187072</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.62402874902875</v>
+      </c>
+      <c r="D16" t="n">
+        <v>186.4061771561772</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.755827505827506</v>
+      </c>
+      <c r="F16" t="n">
+        <v>80.21416083916083</v>
+      </c>
+      <c r="G16" t="n">
+        <v>29955778.94327894</v>
+      </c>
+      <c r="H16" t="n">
+        <v>83.81876456876458</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26.06681818181818</v>
+      </c>
+      <c r="J16" t="n">
+        <v>182.2870454545455</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.087727272727273</v>
+      </c>
+      <c r="L16" t="n">
+        <v>78.55727272727272</v>
+      </c>
+      <c r="M16" t="n">
+        <v>21251022.72727273</v>
+      </c>
+      <c r="N16" t="n">
+        <v>80.70545454545454</v>
+      </c>
+      <c r="O16" t="n">
+        <v>24.8432502204127</v>
+      </c>
+      <c r="P16" t="n">
+        <v>183.798079082118</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.744378062821999</v>
+      </c>
+      <c r="R16" t="n">
+        <v>76.23635323867589</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15836567.78919022</v>
+      </c>
+      <c r="T16" t="n">
+        <v>81.52249692971661</v>
+      </c>
+      <c r="U16" t="n">
+        <v>25.34594552990198</v>
+      </c>
+      <c r="V16" t="n">
+        <v>182.7396397178475</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.963514286009749</v>
+      </c>
+      <c r="X16" t="n">
+        <v>76.28715226948893</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17566886.10747322</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>80.59263702100816</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>24.98863636363636</v>
+      </c>
+      <c r="D17" t="n">
+        <v>186.4416666666666</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.037878787878788</v>
+      </c>
+      <c r="F17" t="n">
+        <v>73.32045454545455</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5048712.121212121</v>
+      </c>
+      <c r="H17" t="n">
+        <v>77.05454545454546</v>
+      </c>
+      <c r="I17" t="n">
+        <v>25.8037037037037</v>
+      </c>
+      <c r="J17" t="n">
+        <v>181.1512345679012</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.076234567901234</v>
+      </c>
+      <c r="L17" t="n">
+        <v>71.1848765432099</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3585370.370370371</v>
+      </c>
+      <c r="N17" t="n">
+        <v>73.63703703703703</v>
+      </c>
+      <c r="O17" t="n">
+        <v>25.45243300590115</v>
+      </c>
+      <c r="P17" t="n">
+        <v>183.0929216988531</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.068729135019097</v>
+      </c>
+      <c r="R17" t="n">
+        <v>70.98908371529642</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3280140.151641324</v>
+      </c>
+      <c r="T17" t="n">
+        <v>74.8233442548303</v>
+      </c>
+      <c r="U17" t="n">
+        <v>26.54628619528619</v>
+      </c>
+      <c r="V17" t="n">
+        <v>183.7406428386428</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.255309505309505</v>
+      </c>
+      <c r="X17" t="n">
+        <v>70.05600543900543</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2813568.1002331</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>72.48127298627298</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1312 +558,984 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.22237762237762</v>
+        <v>25.34710743801653</v>
       </c>
       <c r="D2" t="n">
-        <v>183.7076923076923</v>
+        <v>184.4380165289256</v>
       </c>
       <c r="E2" t="n">
-        <v>1.616783216783217</v>
+        <v>1.173553719008265</v>
       </c>
       <c r="F2" t="n">
-        <v>76.3944055944056</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="G2" t="n">
-        <v>12678321.67832168</v>
+        <v>3835330.578512396</v>
       </c>
       <c r="H2" t="n">
-        <v>79.63426573426574</v>
+        <v>75.84297520661157</v>
       </c>
       <c r="I2" t="n">
-        <v>25.13492063492064</v>
+        <v>25.8037037037037</v>
       </c>
       <c r="J2" t="n">
-        <v>184.6316738816739</v>
+        <v>181.1512345679012</v>
       </c>
       <c r="K2" t="n">
-        <v>1.015079365079365</v>
+        <v>1.076234567901234</v>
       </c>
       <c r="L2" t="n">
-        <v>69.93658008658008</v>
+        <v>71.1848765432099</v>
       </c>
       <c r="M2" t="n">
-        <v>2656121.933621933</v>
+        <v>3585370.370370371</v>
       </c>
       <c r="N2" t="n">
-        <v>74.38225108225109</v>
+        <v>73.63703703703703</v>
       </c>
       <c r="O2" t="n">
-        <v>24.95155619948295</v>
+        <v>25.769700414528</v>
       </c>
       <c r="P2" t="n">
-        <v>181.7271984189602</v>
+        <v>183.2808811877777</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.550788197131392</v>
+        <v>1.178140824692549</v>
       </c>
       <c r="R2" t="n">
-        <v>74.58407301542303</v>
+        <v>69.9454935868729</v>
       </c>
       <c r="S2" t="n">
-        <v>11541974.43774517</v>
+        <v>2704018.66237211</v>
       </c>
       <c r="T2" t="n">
-        <v>79.26224403502179</v>
+        <v>74.26468875951636</v>
       </c>
       <c r="U2" t="n">
-        <v>25.54059544465559</v>
+        <v>26.54628619528619</v>
       </c>
       <c r="V2" t="n">
-        <v>181.8841578221277</v>
+        <v>183.7406428386428</v>
       </c>
       <c r="W2" t="n">
-        <v>1.040302855039698</v>
+        <v>1.255309505309505</v>
       </c>
       <c r="X2" t="n">
-        <v>67.40725249687657</v>
+        <v>70.05600543900543</v>
       </c>
       <c r="Y2" t="n">
-        <v>1621063.413278451</v>
+        <v>2813568.1002331</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.34852959071004</v>
+        <v>72.48127298627298</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.94132231404959</v>
+        <v>25.0446510560147</v>
       </c>
       <c r="D3" t="n">
-        <v>186.0181818181818</v>
+        <v>184.2012167125804</v>
       </c>
       <c r="E3" t="n">
-        <v>1.26198347107438</v>
+        <v>1.140266299357209</v>
       </c>
       <c r="F3" t="n">
-        <v>76.08925619834712</v>
+        <v>73.0121671258035</v>
       </c>
       <c r="G3" t="n">
-        <v>13144876.03305785</v>
+        <v>4763096.877869605</v>
       </c>
       <c r="H3" t="n">
-        <v>79.13553719008264</v>
+        <v>76.64267676767678</v>
       </c>
       <c r="I3" t="n">
-        <v>25.88571428571428</v>
+        <v>25.62402874902875</v>
       </c>
       <c r="J3" t="n">
-        <v>187.2525974025974</v>
+        <v>186.4061771561772</v>
       </c>
       <c r="K3" t="n">
-        <v>1.52987012987013</v>
+        <v>1.755827505827506</v>
       </c>
       <c r="L3" t="n">
-        <v>78.20649350649352</v>
+        <v>80.21416083916083</v>
       </c>
       <c r="M3" t="n">
-        <v>18650324.67532467</v>
+        <v>29955778.94327894</v>
       </c>
       <c r="N3" t="n">
-        <v>81.52142857142857</v>
+        <v>83.81876456876458</v>
       </c>
       <c r="O3" t="n">
-        <v>24.82488354555974</v>
+        <v>24.26546509046509</v>
       </c>
       <c r="P3" t="n">
-        <v>184.9848120595201</v>
+        <v>182.7177156177156</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.17376111239044</v>
+        <v>1.037638287638288</v>
       </c>
       <c r="R3" t="n">
-        <v>71.84112376935695</v>
+        <v>70.56276131276131</v>
       </c>
       <c r="S3" t="n">
-        <v>5778426.326308399</v>
+        <v>3403146.991896993</v>
       </c>
       <c r="T3" t="n">
-        <v>76.07582417191902</v>
+        <v>75.29687072187072</v>
       </c>
       <c r="U3" t="n">
-        <v>25.38111969523461</v>
+        <v>24.8432502204127</v>
       </c>
       <c r="V3" t="n">
-        <v>186.5566248508795</v>
+        <v>183.798079082118</v>
       </c>
       <c r="W3" t="n">
-        <v>1.366661010372191</v>
+        <v>1.744378062821999</v>
       </c>
       <c r="X3" t="n">
-        <v>74.84583374584928</v>
+        <v>76.23635323867589</v>
       </c>
       <c r="Y3" t="n">
-        <v>13202699.953997</v>
+        <v>15836567.78919022</v>
       </c>
       <c r="Z3" t="n">
-        <v>78.82436163158214</v>
+        <v>81.52249692971661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.06681818181818</v>
+        <v>25.16835016835017</v>
       </c>
       <c r="D4" t="n">
-        <v>182.2870454545455</v>
+        <v>184.5289562289562</v>
       </c>
       <c r="E4" t="n">
-        <v>2.087727272727273</v>
+        <v>1.02013468013468</v>
       </c>
       <c r="F4" t="n">
-        <v>78.55727272727272</v>
+        <v>69.94080808080807</v>
       </c>
       <c r="G4" t="n">
-        <v>21251022.72727273</v>
+        <v>2632380.471380471</v>
       </c>
       <c r="H4" t="n">
-        <v>80.70545454545454</v>
+        <v>74.39919191919192</v>
       </c>
       <c r="I4" t="n">
-        <v>25.22148760330579</v>
+        <v>26.0202861952862</v>
       </c>
       <c r="J4" t="n">
-        <v>184.1404958677686</v>
+        <v>185.9981481481481</v>
       </c>
       <c r="K4" t="n">
-        <v>1.033057851239669</v>
+        <v>1.267929292929293</v>
       </c>
       <c r="L4" t="n">
-        <v>72.12975206611571</v>
+        <v>76.03552188552187</v>
       </c>
       <c r="M4" t="n">
-        <v>4288842.975206612</v>
+        <v>12942062.28956229</v>
       </c>
       <c r="N4" t="n">
-        <v>76.1107438016529</v>
+        <v>79.01313131313132</v>
       </c>
       <c r="O4" t="n">
-        <v>25.34594552990198</v>
+        <v>25.40600502370754</v>
       </c>
       <c r="P4" t="n">
-        <v>182.7396397178475</v>
+        <v>182.0339096194931</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.963514286009749</v>
+        <v>1.037615998037051</v>
       </c>
       <c r="R4" t="n">
-        <v>76.28715226948893</v>
+        <v>67.34531972172248</v>
       </c>
       <c r="S4" t="n">
-        <v>17566886.10747322</v>
+        <v>1621746.142248293</v>
       </c>
       <c r="T4" t="n">
-        <v>80.59263702100816</v>
+        <v>72.43543921219893</v>
       </c>
       <c r="U4" t="n">
-        <v>24.8531746031746</v>
+        <v>24.69731972068466</v>
       </c>
       <c r="V4" t="n">
-        <v>182.0717010262465</v>
+        <v>184.9027443878934</v>
       </c>
       <c r="W4" t="n">
-        <v>1.113728022818932</v>
+        <v>1.159281019691236</v>
       </c>
       <c r="X4" t="n">
-        <v>69.58585606312879</v>
+        <v>71.72201051406739</v>
       </c>
       <c r="Y4" t="n">
-        <v>2894139.097434552</v>
+        <v>5747993.740292502</v>
       </c>
       <c r="Z4" t="n">
-        <v>74.7756734006734</v>
+        <v>76.08911333406303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.4198347107438</v>
+        <v>28.07520661157025</v>
       </c>
       <c r="D5" t="n">
-        <v>182.2107438016529</v>
+        <v>182.9925619834711</v>
       </c>
       <c r="E5" t="n">
-        <v>1.729752066115703</v>
+        <v>2.414049586776859</v>
       </c>
       <c r="F5" t="n">
-        <v>80.77355371900826</v>
+        <v>82.89173553719007</v>
       </c>
       <c r="G5" t="n">
-        <v>34887851.23966942</v>
+        <v>39731404.95867768</v>
       </c>
       <c r="H5" t="n">
-        <v>82.47272727272728</v>
+        <v>84.68512396694214</v>
       </c>
       <c r="I5" t="n">
-        <v>24.68181818181818</v>
+        <v>25.87333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>185.5181818181818</v>
+        <v>187.3024242424243</v>
       </c>
       <c r="K5" t="n">
-        <v>1.281818181818182</v>
+        <v>1.521212121212121</v>
       </c>
       <c r="L5" t="n">
-        <v>75.12727272727273</v>
+        <v>78.13272727272728</v>
       </c>
       <c r="M5" t="n">
-        <v>11041818.18181818</v>
+        <v>18446969.6969697</v>
       </c>
       <c r="N5" t="n">
-        <v>79.58181818181819</v>
+        <v>81.48</v>
       </c>
       <c r="O5" t="n">
-        <v>24.90901144856957</v>
+        <v>27.03807644851123</v>
       </c>
       <c r="P5" t="n">
-        <v>181.1425217320025</v>
+        <v>182.5702588393893</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.512801672793229</v>
+        <v>1.879477285999025</v>
       </c>
       <c r="R5" t="n">
-        <v>75.79453752744634</v>
+        <v>78.98688163688163</v>
       </c>
       <c r="S5" t="n">
-        <v>15219224.27376779</v>
+        <v>24015329.64619921</v>
       </c>
       <c r="T5" t="n">
-        <v>79.08278045015309</v>
+        <v>81.5064071194506</v>
       </c>
       <c r="U5" t="n">
-        <v>23.0821855500821</v>
+        <v>25.29645245629304</v>
       </c>
       <c r="V5" t="n">
-        <v>184.6805205254516</v>
+        <v>186.6602572682283</v>
       </c>
       <c r="W5" t="n">
-        <v>1.202333333333333</v>
+        <v>1.342216943014045</v>
       </c>
       <c r="X5" t="n">
-        <v>71.2915041050903</v>
+        <v>74.75240779242228</v>
       </c>
       <c r="Y5" t="n">
-        <v>6950567.528735632</v>
+        <v>13042223.66076757</v>
       </c>
       <c r="Z5" t="n">
-        <v>78.0733382594417</v>
+        <v>78.84347826355072</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.34710743801653</v>
+        <v>24.68181818181818</v>
       </c>
       <c r="D6" t="n">
-        <v>184.4380165289256</v>
+        <v>185.5181818181818</v>
       </c>
       <c r="E6" t="n">
-        <v>1.173553719008265</v>
+        <v>1.281818181818182</v>
       </c>
       <c r="F6" t="n">
-        <v>72.18181818181819</v>
+        <v>75.12727272727273</v>
       </c>
       <c r="G6" t="n">
-        <v>3835330.578512396</v>
+        <v>11041818.18181818</v>
       </c>
       <c r="H6" t="n">
-        <v>75.84297520661157</v>
+        <v>79.58181818181819</v>
       </c>
       <c r="I6" t="n">
-        <v>25.8037037037037</v>
+        <v>25.22148760330579</v>
       </c>
       <c r="J6" t="n">
-        <v>181.1512345679012</v>
+        <v>184.1404958677686</v>
       </c>
       <c r="K6" t="n">
-        <v>1.076234567901234</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="L6" t="n">
-        <v>71.1848765432099</v>
+        <v>72.12975206611571</v>
       </c>
       <c r="M6" t="n">
-        <v>3585370.370370371</v>
+        <v>4288842.975206612</v>
       </c>
       <c r="N6" t="n">
-        <v>73.63703703703703</v>
+        <v>76.1107438016529</v>
       </c>
       <c r="O6" t="n">
-        <v>25.769700414528</v>
+        <v>23.0821855500821</v>
       </c>
       <c r="P6" t="n">
-        <v>183.2808811877777</v>
+        <v>184.6805205254516</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.178140824692549</v>
+        <v>1.202333333333333</v>
       </c>
       <c r="R6" t="n">
-        <v>69.9454935868729</v>
+        <v>71.2915041050903</v>
       </c>
       <c r="S6" t="n">
-        <v>2704018.66237211</v>
+        <v>6950567.528735632</v>
       </c>
       <c r="T6" t="n">
-        <v>74.26468875951636</v>
+        <v>78.0733382594417</v>
       </c>
       <c r="U6" t="n">
-        <v>26.54628619528619</v>
+        <v>24.8531746031746</v>
       </c>
       <c r="V6" t="n">
-        <v>183.7406428386428</v>
+        <v>182.0717010262465</v>
       </c>
       <c r="W6" t="n">
-        <v>1.255309505309505</v>
+        <v>1.113728022818932</v>
       </c>
       <c r="X6" t="n">
-        <v>70.05600543900543</v>
+        <v>69.58585606312879</v>
       </c>
       <c r="Y6" t="n">
-        <v>2813568.1002331</v>
+        <v>2894139.097434552</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.48127298627298</v>
+        <v>74.7756734006734</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.0446510560147</v>
+        <v>23.97390572390573</v>
       </c>
       <c r="D7" t="n">
-        <v>184.2012167125804</v>
+        <v>183.994739057239</v>
       </c>
       <c r="E7" t="n">
-        <v>1.140266299357209</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>73.0121671258035</v>
+        <v>72.00778619528619</v>
       </c>
       <c r="G7" t="n">
-        <v>4763096.877869605</v>
+        <v>5434511.784511785</v>
       </c>
       <c r="H7" t="n">
-        <v>76.64267676767678</v>
+        <v>77.87478956228956</v>
       </c>
       <c r="I7" t="n">
-        <v>25.62402874902875</v>
+        <v>25.34710743801653</v>
       </c>
       <c r="J7" t="n">
-        <v>186.4061771561772</v>
+        <v>184.4380165289256</v>
       </c>
       <c r="K7" t="n">
-        <v>1.755827505827506</v>
+        <v>1.173553719008265</v>
       </c>
       <c r="L7" t="n">
-        <v>80.21416083916083</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="M7" t="n">
-        <v>29955778.94327894</v>
+        <v>3835330.578512396</v>
       </c>
       <c r="N7" t="n">
-        <v>83.81876456876458</v>
+        <v>75.84297520661157</v>
       </c>
       <c r="O7" t="n">
-        <v>24.26546509046509</v>
+        <v>23.08811497300056</v>
       </c>
       <c r="P7" t="n">
-        <v>182.7177156177156</v>
+        <v>182.7014405855925</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.037638287638288</v>
+        <v>1.057177460220939</v>
       </c>
       <c r="R7" t="n">
-        <v>70.56276131276131</v>
+        <v>67.93035045528038</v>
       </c>
       <c r="S7" t="n">
-        <v>3403146.991896993</v>
+        <v>2654253.453200964</v>
       </c>
       <c r="T7" t="n">
-        <v>75.29687072187072</v>
+        <v>74.88404171089526</v>
       </c>
       <c r="U7" t="n">
-        <v>24.8432502204127</v>
+        <v>25.769700414528</v>
       </c>
       <c r="V7" t="n">
-        <v>183.798079082118</v>
+        <v>183.2808811877777</v>
       </c>
       <c r="W7" t="n">
-        <v>1.744378062821999</v>
+        <v>1.178140824692549</v>
       </c>
       <c r="X7" t="n">
-        <v>76.23635323867589</v>
+        <v>69.9454935868729</v>
       </c>
       <c r="Y7" t="n">
-        <v>15836567.78919022</v>
+        <v>2704018.66237211</v>
       </c>
       <c r="Z7" t="n">
-        <v>81.52249692971661</v>
+        <v>74.26468875951636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.13492063492064</v>
+        <v>26.70668220668221</v>
       </c>
       <c r="D8" t="n">
-        <v>184.6316738816739</v>
+        <v>183.7864024864025</v>
       </c>
       <c r="E8" t="n">
-        <v>1.015079365079365</v>
+        <v>1.71981351981352</v>
       </c>
       <c r="F8" t="n">
-        <v>69.93658008658008</v>
+        <v>77.64304584304584</v>
       </c>
       <c r="G8" t="n">
-        <v>2656121.933621933</v>
+        <v>18319075.36907537</v>
       </c>
       <c r="H8" t="n">
-        <v>74.38225108225109</v>
+        <v>79.95236985236986</v>
       </c>
       <c r="I8" t="n">
-        <v>25.94132231404959</v>
+        <v>25.24435261707988</v>
       </c>
       <c r="J8" t="n">
-        <v>186.0181818181818</v>
+        <v>184.2949494949495</v>
       </c>
       <c r="K8" t="n">
-        <v>1.26198347107438</v>
+        <v>1.792011019283746</v>
       </c>
       <c r="L8" t="n">
-        <v>76.08925619834712</v>
+        <v>80.60927456382002</v>
       </c>
       <c r="M8" t="n">
-        <v>13144876.03305785</v>
+        <v>35322970.61524335</v>
       </c>
       <c r="N8" t="n">
-        <v>79.13553719008264</v>
+        <v>84.21524334251608</v>
       </c>
       <c r="O8" t="n">
-        <v>25.54059544465559</v>
+        <v>26.20053059069077</v>
       </c>
       <c r="P8" t="n">
-        <v>181.8841578221277</v>
+        <v>182.2746757437833</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.040302855039698</v>
+        <v>1.721159599363261</v>
       </c>
       <c r="R8" t="n">
-        <v>67.40725249687657</v>
+        <v>76.26031657130055</v>
       </c>
       <c r="S8" t="n">
-        <v>1621063.413278451</v>
+        <v>15511947.91059436</v>
       </c>
       <c r="T8" t="n">
-        <v>72.34852959071004</v>
+        <v>79.4644773418801</v>
       </c>
       <c r="U8" t="n">
-        <v>24.82488354555974</v>
+        <v>24.09977743504059</v>
       </c>
       <c r="V8" t="n">
-        <v>184.9848120595201</v>
+        <v>184.0198127408653</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17376111239044</v>
+        <v>1.498405590510854</v>
       </c>
       <c r="X8" t="n">
-        <v>71.84112376935695</v>
+        <v>76.56655196655197</v>
       </c>
       <c r="Y8" t="n">
-        <v>5778426.326308399</v>
+        <v>22507672.14169845</v>
       </c>
       <c r="Z8" t="n">
-        <v>76.07582417191902</v>
+        <v>82.3017479985901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.96272727272727</v>
+        <v>26.4198347107438</v>
       </c>
       <c r="D9" t="n">
-        <v>183.0218181818182</v>
+        <v>182.2107438016529</v>
       </c>
       <c r="E9" t="n">
-        <v>2.395454545454546</v>
+        <v>1.729752066115703</v>
       </c>
       <c r="F9" t="n">
-        <v>82.8209090909091</v>
+        <v>80.77355371900826</v>
       </c>
       <c r="G9" t="n">
-        <v>39894545.45454545</v>
+        <v>34887851.23966942</v>
       </c>
       <c r="H9" t="n">
-        <v>84.67363636363636</v>
+        <v>82.47272727272728</v>
       </c>
       <c r="I9" t="n">
-        <v>25.88571428571428</v>
+        <v>24.30146923783288</v>
       </c>
       <c r="J9" t="n">
-        <v>187.2525974025974</v>
+        <v>184.8678604224059</v>
       </c>
       <c r="K9" t="n">
-        <v>1.52987012987013</v>
+        <v>1.052892561983471</v>
       </c>
       <c r="L9" t="n">
-        <v>78.20649350649352</v>
+        <v>69.73820018365473</v>
       </c>
       <c r="M9" t="n">
-        <v>18650324.67532467</v>
+        <v>3034935.720844812</v>
       </c>
       <c r="N9" t="n">
-        <v>81.52142857142857</v>
+        <v>75.7060606060606</v>
       </c>
       <c r="O9" t="n">
-        <v>27.13419178567005</v>
+        <v>24.90901144856957</v>
       </c>
       <c r="P9" t="n">
-        <v>182.4003616464051</v>
+        <v>181.1425217320025</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.886655783829697</v>
+        <v>1.512801672793229</v>
       </c>
       <c r="R9" t="n">
-        <v>79.00864672364672</v>
+        <v>75.79453752744634</v>
       </c>
       <c r="S9" t="n">
-        <v>24048401.07235759</v>
+        <v>15219224.27376779</v>
       </c>
       <c r="T9" t="n">
-        <v>81.47243244678027</v>
+        <v>79.08278045015309</v>
       </c>
       <c r="U9" t="n">
-        <v>25.38111969523461</v>
+        <v>24.61664945360597</v>
       </c>
       <c r="V9" t="n">
-        <v>186.5566248508795</v>
+        <v>183.7360839643449</v>
       </c>
       <c r="W9" t="n">
-        <v>1.366661010372191</v>
+        <v>1.111581293103032</v>
       </c>
       <c r="X9" t="n">
-        <v>74.84583374584928</v>
+        <v>68.18160370225587</v>
       </c>
       <c r="Y9" t="n">
-        <v>13202699.953997</v>
+        <v>2439245.531240096</v>
       </c>
       <c r="Z9" t="n">
-        <v>78.82436163158214</v>
+        <v>73.75940030179162</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.68181818181818</v>
+        <v>26.16681096681097</v>
       </c>
       <c r="D10" t="n">
-        <v>185.5181818181818</v>
+        <v>183.831746031746</v>
       </c>
       <c r="E10" t="n">
-        <v>1.281818181818182</v>
+        <v>1.588600288600288</v>
       </c>
       <c r="F10" t="n">
-        <v>75.12727272727273</v>
+        <v>76.34242424242424</v>
       </c>
       <c r="G10" t="n">
-        <v>11041818.18181818</v>
+        <v>12767171.71717172</v>
       </c>
       <c r="H10" t="n">
-        <v>79.58181818181819</v>
+        <v>79.68419913419913</v>
       </c>
       <c r="I10" t="n">
-        <v>25.22148760330579</v>
+        <v>25.54924242424243</v>
       </c>
       <c r="J10" t="n">
-        <v>184.1404958677686</v>
+        <v>183.7446969696969</v>
       </c>
       <c r="K10" t="n">
-        <v>1.033057851239669</v>
+        <v>1.382575757575758</v>
       </c>
       <c r="L10" t="n">
-        <v>72.12975206611571</v>
+        <v>73.15378787878787</v>
       </c>
       <c r="M10" t="n">
-        <v>4288842.975206612</v>
+        <v>6766060.606060606</v>
       </c>
       <c r="N10" t="n">
-        <v>76.1107438016529</v>
+        <v>77.37954545454545</v>
       </c>
       <c r="O10" t="n">
-        <v>23.0821855500821</v>
+        <v>24.85563758896088</v>
       </c>
       <c r="P10" t="n">
-        <v>184.6805205254516</v>
+        <v>181.7528954263015</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.202333333333333</v>
+        <v>1.536290903547473</v>
       </c>
       <c r="R10" t="n">
-        <v>71.2915041050903</v>
+        <v>74.55788146463195</v>
       </c>
       <c r="S10" t="n">
-        <v>6950567.528735632</v>
+        <v>11567237.13318573</v>
       </c>
       <c r="T10" t="n">
-        <v>78.0733382594417</v>
+        <v>79.35531356047056</v>
       </c>
       <c r="U10" t="n">
-        <v>24.8531746031746</v>
+        <v>25.70110657659571</v>
       </c>
       <c r="V10" t="n">
-        <v>182.0717010262465</v>
+        <v>182.0741213999366</v>
       </c>
       <c r="W10" t="n">
-        <v>1.113728022818932</v>
+        <v>1.293591802722238</v>
       </c>
       <c r="X10" t="n">
-        <v>69.58585606312879</v>
+        <v>71.6797183680517</v>
       </c>
       <c r="Y10" t="n">
-        <v>2894139.097434552</v>
+        <v>4335666.158268061</v>
       </c>
       <c r="Z10" t="n">
-        <v>74.7756734006734</v>
+        <v>76.64850967671619</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>23.99173553719008</v>
+        <v>26.225</v>
       </c>
       <c r="D11" t="n">
-        <v>184.2871900826446</v>
+        <v>184.2416666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>1.206818181818182</v>
       </c>
       <c r="F11" t="n">
-        <v>72.01859504132231</v>
+        <v>73.06818181818183</v>
       </c>
       <c r="G11" t="n">
-        <v>5430578.512396694</v>
+        <v>5907007.575757575</v>
       </c>
       <c r="H11" t="n">
-        <v>77.85330578512398</v>
+        <v>77.42803030303031</v>
       </c>
       <c r="I11" t="n">
-        <v>25.34710743801653</v>
+        <v>25.0446510560147</v>
       </c>
       <c r="J11" t="n">
-        <v>184.4380165289256</v>
+        <v>184.2012167125804</v>
       </c>
       <c r="K11" t="n">
-        <v>1.173553719008265</v>
+        <v>1.140266299357209</v>
       </c>
       <c r="L11" t="n">
-        <v>72.18181818181819</v>
+        <v>73.0121671258035</v>
       </c>
       <c r="M11" t="n">
-        <v>3835330.578512396</v>
+        <v>4763096.877869605</v>
       </c>
       <c r="N11" t="n">
-        <v>75.84297520661157</v>
+        <v>76.64267676767678</v>
       </c>
       <c r="O11" t="n">
-        <v>23.14157997054606</v>
+        <v>26.55179154995331</v>
       </c>
       <c r="P11" t="n">
-        <v>182.5890715479191</v>
+        <v>184.8090756302521</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.062375411150115</v>
+        <v>1.390332633053221</v>
       </c>
       <c r="R11" t="n">
-        <v>68.02060958757859</v>
+        <v>70.36959150326798</v>
       </c>
       <c r="S11" t="n">
-        <v>2648390.130764688</v>
+        <v>3520184.87394958</v>
       </c>
       <c r="T11" t="n">
-        <v>74.87350004824938</v>
+        <v>73.98869631185808</v>
       </c>
       <c r="U11" t="n">
-        <v>25.769700414528</v>
+        <v>24.26546509046509</v>
       </c>
       <c r="V11" t="n">
-        <v>183.2808811877777</v>
+        <v>182.7177156177156</v>
       </c>
       <c r="W11" t="n">
-        <v>1.178140824692549</v>
+        <v>1.037638287638288</v>
       </c>
       <c r="X11" t="n">
-        <v>69.9454935868729</v>
+        <v>70.56276131276131</v>
       </c>
       <c r="Y11" t="n">
-        <v>2704018.66237211</v>
+        <v>3403146.991896993</v>
       </c>
       <c r="Z11" t="n">
-        <v>74.26468875951636</v>
+        <v>75.29687072187072</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>26.70668220668221</v>
+        <v>25.62402874902875</v>
       </c>
       <c r="D12" t="n">
-        <v>183.7864024864025</v>
+        <v>186.4061771561772</v>
       </c>
       <c r="E12" t="n">
-        <v>1.71981351981352</v>
+        <v>1.755827505827506</v>
       </c>
       <c r="F12" t="n">
-        <v>77.64304584304584</v>
+        <v>80.21416083916083</v>
       </c>
       <c r="G12" t="n">
-        <v>18319075.36907537</v>
+        <v>29955778.94327894</v>
       </c>
       <c r="H12" t="n">
-        <v>79.95236985236986</v>
+        <v>83.81876456876458</v>
       </c>
       <c r="I12" t="n">
-        <v>25.24435261707988</v>
+        <v>26.06681818181818</v>
       </c>
       <c r="J12" t="n">
-        <v>184.2949494949495</v>
+        <v>182.2870454545455</v>
       </c>
       <c r="K12" t="n">
-        <v>1.792011019283746</v>
+        <v>2.087727272727273</v>
       </c>
       <c r="L12" t="n">
-        <v>80.60927456382002</v>
+        <v>78.55727272727272</v>
       </c>
       <c r="M12" t="n">
-        <v>35322970.61524335</v>
+        <v>21251022.72727273</v>
       </c>
       <c r="N12" t="n">
-        <v>84.21524334251608</v>
+        <v>80.70545454545454</v>
       </c>
       <c r="O12" t="n">
-        <v>26.20053059069077</v>
+        <v>24.8432502204127</v>
       </c>
       <c r="P12" t="n">
-        <v>182.2746757437833</v>
+        <v>183.798079082118</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.721159599363261</v>
+        <v>1.744378062821999</v>
       </c>
       <c r="R12" t="n">
-        <v>76.26031657130055</v>
+        <v>76.23635323867589</v>
       </c>
       <c r="S12" t="n">
-        <v>15511947.91059436</v>
+        <v>15836567.78919022</v>
       </c>
       <c r="T12" t="n">
-        <v>79.4644773418801</v>
+        <v>81.52249692971661</v>
       </c>
       <c r="U12" t="n">
-        <v>24.09977743504059</v>
+        <v>25.34594552990198</v>
       </c>
       <c r="V12" t="n">
-        <v>184.0198127408653</v>
+        <v>182.7396397178475</v>
       </c>
       <c r="W12" t="n">
-        <v>1.498405590510854</v>
+        <v>1.963514286009749</v>
       </c>
       <c r="X12" t="n">
-        <v>76.56655196655197</v>
+        <v>76.28715226948893</v>
       </c>
       <c r="Y12" t="n">
-        <v>22507672.14169845</v>
+        <v>17566886.10747322</v>
       </c>
       <c r="Z12" t="n">
-        <v>82.3017479985901</v>
+        <v>80.59263702100816</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.4198347107438</v>
+        <v>24.98863636363636</v>
       </c>
       <c r="D13" t="n">
-        <v>182.2107438016529</v>
+        <v>186.4416666666666</v>
       </c>
       <c r="E13" t="n">
-        <v>1.729752066115703</v>
+        <v>1.037878787878788</v>
       </c>
       <c r="F13" t="n">
-        <v>80.77355371900826</v>
+        <v>73.32045454545455</v>
       </c>
       <c r="G13" t="n">
-        <v>34887851.23966942</v>
+        <v>5048712.121212121</v>
       </c>
       <c r="H13" t="n">
-        <v>82.47272727272728</v>
+        <v>77.05454545454546</v>
       </c>
       <c r="I13" t="n">
-        <v>24.30146923783288</v>
+        <v>25.8037037037037</v>
       </c>
       <c r="J13" t="n">
-        <v>184.8678604224059</v>
+        <v>181.1512345679012</v>
       </c>
       <c r="K13" t="n">
-        <v>1.052892561983471</v>
+        <v>1.076234567901234</v>
       </c>
       <c r="L13" t="n">
-        <v>69.73820018365473</v>
+        <v>71.1848765432099</v>
       </c>
       <c r="M13" t="n">
-        <v>3034935.720844812</v>
+        <v>3585370.370370371</v>
       </c>
       <c r="N13" t="n">
-        <v>75.7060606060606</v>
+        <v>73.63703703703703</v>
       </c>
       <c r="O13" t="n">
-        <v>24.90901144856957</v>
+        <v>25.45243300590115</v>
       </c>
       <c r="P13" t="n">
-        <v>181.1425217320025</v>
+        <v>183.0929216988531</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.512801672793229</v>
+        <v>1.068729135019097</v>
       </c>
       <c r="R13" t="n">
-        <v>75.79453752744634</v>
+        <v>70.98908371529642</v>
       </c>
       <c r="S13" t="n">
-        <v>15219224.27376779</v>
+        <v>3280140.151641324</v>
       </c>
       <c r="T13" t="n">
-        <v>79.08278045015309</v>
+        <v>74.8233442548303</v>
       </c>
       <c r="U13" t="n">
-        <v>24.61664945360597</v>
+        <v>26.54628619528619</v>
       </c>
       <c r="V13" t="n">
-        <v>183.7360839643449</v>
+        <v>183.7406428386428</v>
       </c>
       <c r="W13" t="n">
-        <v>1.111581293103032</v>
+        <v>1.255309505309505</v>
       </c>
       <c r="X13" t="n">
-        <v>68.18160370225587</v>
+        <v>70.05600543900543</v>
       </c>
       <c r="Y13" t="n">
-        <v>2439245.531240096</v>
+        <v>2813568.1002331</v>
       </c>
       <c r="Z13" t="n">
-        <v>73.75940030179162</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>26.22237762237762</v>
-      </c>
-      <c r="D14" t="n">
-        <v>183.7076923076923</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.616783216783217</v>
-      </c>
-      <c r="F14" t="n">
-        <v>76.3944055944056</v>
-      </c>
-      <c r="G14" t="n">
-        <v>12678321.67832168</v>
-      </c>
-      <c r="H14" t="n">
-        <v>79.63426573426574</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25.54132231404959</v>
-      </c>
-      <c r="J14" t="n">
-        <v>183.7297520661157</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.37603305785124</v>
-      </c>
-      <c r="L14" t="n">
-        <v>73.23388429752066</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6951404.958677686</v>
-      </c>
-      <c r="N14" t="n">
-        <v>77.45537190082645</v>
-      </c>
-      <c r="O14" t="n">
-        <v>24.95155619948295</v>
-      </c>
-      <c r="P14" t="n">
-        <v>181.7271984189602</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.550788197131392</v>
-      </c>
-      <c r="R14" t="n">
-        <v>74.58407301542303</v>
-      </c>
-      <c r="S14" t="n">
-        <v>11541974.43774517</v>
-      </c>
-      <c r="T14" t="n">
-        <v>79.26224403502179</v>
-      </c>
-      <c r="U14" t="n">
-        <v>25.67393444719531</v>
-      </c>
-      <c r="V14" t="n">
-        <v>182.1304464858813</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.283091883961449</v>
-      </c>
-      <c r="X14" t="n">
-        <v>71.61341177341177</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>4347172.999102348</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>76.64134939939287</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>26.18181818181818</v>
-      </c>
-      <c r="D15" t="n">
-        <v>184.2363636363637</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.207438016528926</v>
-      </c>
-      <c r="F15" t="n">
-        <v>73.02892561983471</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5968553.719008264</v>
-      </c>
-      <c r="H15" t="n">
-        <v>77.41239669421488</v>
-      </c>
-      <c r="I15" t="n">
-        <v>25.0446510560147</v>
-      </c>
-      <c r="J15" t="n">
-        <v>184.2012167125804</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.140266299357209</v>
-      </c>
-      <c r="L15" t="n">
-        <v>73.0121671258035</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4763096.877869605</v>
-      </c>
-      <c r="N15" t="n">
-        <v>76.64267676767678</v>
-      </c>
-      <c r="O15" t="n">
-        <v>26.57286350903998</v>
-      </c>
-      <c r="P15" t="n">
-        <v>184.7808097784569</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.389453781512605</v>
-      </c>
-      <c r="R15" t="n">
-        <v>70.33046345811053</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3512656.226126814</v>
-      </c>
-      <c r="T15" t="n">
-        <v>73.98766870384519</v>
-      </c>
-      <c r="U15" t="n">
-        <v>24.26546509046509</v>
-      </c>
-      <c r="V15" t="n">
-        <v>182.7177156177156</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.037638287638288</v>
-      </c>
-      <c r="X15" t="n">
-        <v>70.56276131276131</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>3403146.991896993</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>75.29687072187072</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>25.62402874902875</v>
-      </c>
-      <c r="D16" t="n">
-        <v>186.4061771561772</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.755827505827506</v>
-      </c>
-      <c r="F16" t="n">
-        <v>80.21416083916083</v>
-      </c>
-      <c r="G16" t="n">
-        <v>29955778.94327894</v>
-      </c>
-      <c r="H16" t="n">
-        <v>83.81876456876458</v>
-      </c>
-      <c r="I16" t="n">
-        <v>26.06681818181818</v>
-      </c>
-      <c r="J16" t="n">
-        <v>182.2870454545455</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.087727272727273</v>
-      </c>
-      <c r="L16" t="n">
-        <v>78.55727272727272</v>
-      </c>
-      <c r="M16" t="n">
-        <v>21251022.72727273</v>
-      </c>
-      <c r="N16" t="n">
-        <v>80.70545454545454</v>
-      </c>
-      <c r="O16" t="n">
-        <v>24.8432502204127</v>
-      </c>
-      <c r="P16" t="n">
-        <v>183.798079082118</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.744378062821999</v>
-      </c>
-      <c r="R16" t="n">
-        <v>76.23635323867589</v>
-      </c>
-      <c r="S16" t="n">
-        <v>15836567.78919022</v>
-      </c>
-      <c r="T16" t="n">
-        <v>81.52249692971661</v>
-      </c>
-      <c r="U16" t="n">
-        <v>25.34594552990198</v>
-      </c>
-      <c r="V16" t="n">
-        <v>182.7396397178475</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.963514286009749</v>
-      </c>
-      <c r="X16" t="n">
-        <v>76.28715226948893</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>17566886.10747322</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>80.59263702100816</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>24.98863636363636</v>
-      </c>
-      <c r="D17" t="n">
-        <v>186.4416666666666</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.037878787878788</v>
-      </c>
-      <c r="F17" t="n">
-        <v>73.32045454545455</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5048712.121212121</v>
-      </c>
-      <c r="H17" t="n">
-        <v>77.05454545454546</v>
-      </c>
-      <c r="I17" t="n">
-        <v>25.8037037037037</v>
-      </c>
-      <c r="J17" t="n">
-        <v>181.1512345679012</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.076234567901234</v>
-      </c>
-      <c r="L17" t="n">
-        <v>71.1848765432099</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3585370.370370371</v>
-      </c>
-      <c r="N17" t="n">
-        <v>73.63703703703703</v>
-      </c>
-      <c r="O17" t="n">
-        <v>25.45243300590115</v>
-      </c>
-      <c r="P17" t="n">
-        <v>183.0929216988531</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.068729135019097</v>
-      </c>
-      <c r="R17" t="n">
-        <v>70.98908371529642</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3280140.151641324</v>
-      </c>
-      <c r="T17" t="n">
-        <v>74.8233442548303</v>
-      </c>
-      <c r="U17" t="n">
-        <v>26.54628619528619</v>
-      </c>
-      <c r="V17" t="n">
-        <v>183.7406428386428</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.255309505309505</v>
-      </c>
-      <c r="X17" t="n">
-        <v>70.05600543900543</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2813568.1002331</v>
-      </c>
-      <c r="Z17" t="n">
         <v>72.48127298627298</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,985 +558,821 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.34710743801653</v>
+        <v>25.16835016835017</v>
       </c>
       <c r="D2" t="n">
-        <v>184.4380165289256</v>
+        <v>184.5289562289562</v>
       </c>
       <c r="E2" t="n">
-        <v>1.173553719008265</v>
+        <v>1.02013468013468</v>
       </c>
       <c r="F2" t="n">
-        <v>72.18181818181819</v>
+        <v>69.94080808080807</v>
       </c>
       <c r="G2" t="n">
-        <v>3835330.578512396</v>
+        <v>2632380.471380471</v>
       </c>
       <c r="H2" t="n">
-        <v>75.84297520661157</v>
+        <v>74.39919191919192</v>
       </c>
       <c r="I2" t="n">
-        <v>25.8037037037037</v>
+        <v>26.02213039485767</v>
       </c>
       <c r="J2" t="n">
-        <v>181.1512345679012</v>
+        <v>186.1161616161616</v>
       </c>
       <c r="K2" t="n">
-        <v>1.076234567901234</v>
+        <v>1.255922865013774</v>
       </c>
       <c r="L2" t="n">
-        <v>71.1848765432099</v>
+        <v>75.9932966023875</v>
       </c>
       <c r="M2" t="n">
-        <v>3585370.370370371</v>
+        <v>12909522.49770432</v>
       </c>
       <c r="N2" t="n">
-        <v>73.63703703703703</v>
+        <v>78.9961432506887</v>
       </c>
       <c r="O2" t="n">
-        <v>25.769700414528</v>
+        <v>25.40600502370754</v>
       </c>
       <c r="P2" t="n">
-        <v>183.2808811877777</v>
+        <v>182.0339096194931</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.178140824692549</v>
+        <v>1.037615998037051</v>
       </c>
       <c r="R2" t="n">
-        <v>69.9454935868729</v>
+        <v>67.34531972172248</v>
       </c>
       <c r="S2" t="n">
-        <v>2704018.66237211</v>
+        <v>1621746.142248293</v>
       </c>
       <c r="T2" t="n">
-        <v>74.26468875951636</v>
+        <v>72.43543921219893</v>
       </c>
       <c r="U2" t="n">
-        <v>26.54628619528619</v>
+        <v>24.66980333165599</v>
       </c>
       <c r="V2" t="n">
-        <v>183.7406428386428</v>
+        <v>184.749517941873</v>
       </c>
       <c r="W2" t="n">
-        <v>1.255309505309505</v>
+        <v>1.17376111239044</v>
       </c>
       <c r="X2" t="n">
-        <v>70.05600543900543</v>
+        <v>71.68604355545321</v>
       </c>
       <c r="Y2" t="n">
-        <v>2813568.1002331</v>
+        <v>5757704.401174708</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.48127298627298</v>
+        <v>76.0490862040046</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.0446510560147</v>
+        <v>28.07520661157025</v>
       </c>
       <c r="D3" t="n">
-        <v>184.2012167125804</v>
+        <v>182.9925619834711</v>
       </c>
       <c r="E3" t="n">
-        <v>1.140266299357209</v>
+        <v>2.414049586776859</v>
       </c>
       <c r="F3" t="n">
-        <v>73.0121671258035</v>
+        <v>82.89173553719007</v>
       </c>
       <c r="G3" t="n">
-        <v>4763096.877869605</v>
+        <v>39731404.95867768</v>
       </c>
       <c r="H3" t="n">
-        <v>76.64267676767678</v>
+        <v>84.68512396694214</v>
       </c>
       <c r="I3" t="n">
-        <v>25.62402874902875</v>
+        <v>25.81428571428571</v>
       </c>
       <c r="J3" t="n">
-        <v>186.4061771561772</v>
+        <v>187.2811688311688</v>
       </c>
       <c r="K3" t="n">
-        <v>1.755827505827506</v>
+        <v>1.501298701298701</v>
       </c>
       <c r="L3" t="n">
-        <v>80.21416083916083</v>
+        <v>78.09220779220779</v>
       </c>
       <c r="M3" t="n">
-        <v>29955778.94327894</v>
+        <v>18464610.38961039</v>
       </c>
       <c r="N3" t="n">
-        <v>83.81876456876458</v>
+        <v>81.49285714285715</v>
       </c>
       <c r="O3" t="n">
-        <v>24.26546509046509</v>
+        <v>27.03807644851123</v>
       </c>
       <c r="P3" t="n">
-        <v>182.7177156177156</v>
+        <v>182.5702588393893</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.037638287638288</v>
+        <v>1.879477285999025</v>
       </c>
       <c r="R3" t="n">
-        <v>70.56276131276131</v>
+        <v>78.98688163688163</v>
       </c>
       <c r="S3" t="n">
-        <v>3403146.991896993</v>
+        <v>24015329.64619921</v>
       </c>
       <c r="T3" t="n">
-        <v>75.29687072187072</v>
+        <v>81.5064071194506</v>
       </c>
       <c r="U3" t="n">
-        <v>24.8432502204127</v>
+        <v>25.22238953650444</v>
       </c>
       <c r="V3" t="n">
-        <v>183.798079082118</v>
+        <v>186.7153550096097</v>
       </c>
       <c r="W3" t="n">
-        <v>1.744378062821999</v>
+        <v>1.337560481271662</v>
       </c>
       <c r="X3" t="n">
-        <v>76.23635323867589</v>
+        <v>74.62096602098154</v>
       </c>
       <c r="Y3" t="n">
-        <v>15836567.78919022</v>
+        <v>12820676.14447319</v>
       </c>
       <c r="Z3" t="n">
-        <v>81.52249692971661</v>
+        <v>78.77938808660859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.16835016835017</v>
+        <v>24.78512396694215</v>
       </c>
       <c r="D4" t="n">
-        <v>184.5289562289562</v>
+        <v>185.5537190082645</v>
       </c>
       <c r="E4" t="n">
-        <v>1.02013468013468</v>
+        <v>1.289256198347108</v>
       </c>
       <c r="F4" t="n">
-        <v>69.94080808080807</v>
+        <v>75.16528925619834</v>
       </c>
       <c r="G4" t="n">
-        <v>2632380.471380471</v>
+        <v>10808264.46280992</v>
       </c>
       <c r="H4" t="n">
-        <v>74.39919191919192</v>
+        <v>79.47933884297521</v>
       </c>
       <c r="I4" t="n">
-        <v>26.0202861952862</v>
+        <v>25.12727272727273</v>
       </c>
       <c r="J4" t="n">
-        <v>185.9981481481481</v>
+        <v>184.1969696969697</v>
       </c>
       <c r="K4" t="n">
-        <v>1.267929292929293</v>
+        <v>1.03030303030303</v>
       </c>
       <c r="L4" t="n">
-        <v>76.03552188552187</v>
+        <v>72.05075757575757</v>
       </c>
       <c r="M4" t="n">
-        <v>12942062.28956229</v>
+        <v>4208712.121212122</v>
       </c>
       <c r="N4" t="n">
-        <v>79.01313131313132</v>
+        <v>76.16212121212122</v>
       </c>
       <c r="O4" t="n">
-        <v>25.40600502370754</v>
+        <v>23.11471413643827</v>
       </c>
       <c r="P4" t="n">
-        <v>182.0339096194931</v>
+        <v>184.7713822958651</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.037615998037051</v>
+        <v>1.202121212121212</v>
       </c>
       <c r="R4" t="n">
-        <v>67.34531972172248</v>
+        <v>71.34136736826393</v>
       </c>
       <c r="S4" t="n">
-        <v>1621746.142248293</v>
+        <v>6841788.662486938</v>
       </c>
       <c r="T4" t="n">
-        <v>72.43543921219893</v>
+        <v>78.07394387221974</v>
       </c>
       <c r="U4" t="n">
-        <v>24.69731972068466</v>
+        <v>24.67096560846561</v>
       </c>
       <c r="V4" t="n">
-        <v>184.9027443878934</v>
+        <v>182.0622537185037</v>
       </c>
       <c r="W4" t="n">
-        <v>1.159281019691236</v>
+        <v>1.104250687584021</v>
       </c>
       <c r="X4" t="n">
-        <v>71.72201051406739</v>
+        <v>69.45370139120139</v>
       </c>
       <c r="Y4" t="n">
-        <v>5747993.740292502</v>
+        <v>2883915.700426117</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.08911333406303</v>
+        <v>74.79783950617285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>28.07520661157025</v>
+        <v>23.97390572390573</v>
       </c>
       <c r="D5" t="n">
-        <v>182.9925619834711</v>
+        <v>183.994739057239</v>
       </c>
       <c r="E5" t="n">
-        <v>2.414049586776859</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>82.89173553719007</v>
+        <v>72.00778619528619</v>
       </c>
       <c r="G5" t="n">
-        <v>39731404.95867768</v>
+        <v>5434511.784511785</v>
       </c>
       <c r="H5" t="n">
-        <v>84.68512396694214</v>
+        <v>77.87478956228956</v>
       </c>
       <c r="I5" t="n">
-        <v>25.87333333333333</v>
+        <v>25.32575757575757</v>
       </c>
       <c r="J5" t="n">
-        <v>187.3024242424243</v>
+        <v>184.5454545454545</v>
       </c>
       <c r="K5" t="n">
-        <v>1.521212121212121</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>78.13272727272728</v>
+        <v>72.22727272727273</v>
       </c>
       <c r="M5" t="n">
-        <v>18446969.6969697</v>
+        <v>3931628.787878788</v>
       </c>
       <c r="N5" t="n">
-        <v>81.48</v>
+        <v>75.88636363636363</v>
       </c>
       <c r="O5" t="n">
-        <v>27.03807644851123</v>
+        <v>23.08811497300056</v>
       </c>
       <c r="P5" t="n">
-        <v>182.5702588393893</v>
+        <v>182.7014405855925</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.879477285999025</v>
+        <v>1.057177460220939</v>
       </c>
       <c r="R5" t="n">
-        <v>78.98688163688163</v>
+        <v>67.93035045528038</v>
       </c>
       <c r="S5" t="n">
-        <v>24015329.64619921</v>
+        <v>2654253.453200964</v>
       </c>
       <c r="T5" t="n">
-        <v>81.5064071194506</v>
+        <v>74.88404171089526</v>
       </c>
       <c r="U5" t="n">
-        <v>25.29645245629304</v>
+        <v>25.86296612072475</v>
       </c>
       <c r="V5" t="n">
-        <v>186.6602572682283</v>
+        <v>183.3932768912654</v>
       </c>
       <c r="W5" t="n">
-        <v>1.342216943014045</v>
+        <v>1.200332793005207</v>
       </c>
       <c r="X5" t="n">
-        <v>74.75240779242228</v>
+        <v>69.93769010895447</v>
       </c>
       <c r="Y5" t="n">
-        <v>13042223.66076757</v>
+        <v>2676137.477544806</v>
       </c>
       <c r="Z5" t="n">
-        <v>78.84347826355072</v>
+        <v>74.22719926412456</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.68181818181818</v>
+        <v>26.78409090909091</v>
       </c>
       <c r="D6" t="n">
-        <v>185.5181818181818</v>
+        <v>183.7871212121212</v>
       </c>
       <c r="E6" t="n">
-        <v>1.281818181818182</v>
+        <v>1.724242424242424</v>
       </c>
       <c r="F6" t="n">
-        <v>75.12727272727273</v>
+        <v>77.7151515151515</v>
       </c>
       <c r="G6" t="n">
-        <v>11041818.18181818</v>
+        <v>18346590.90909091</v>
       </c>
       <c r="H6" t="n">
-        <v>79.58181818181819</v>
+        <v>79.99469696969697</v>
       </c>
       <c r="I6" t="n">
-        <v>25.22148760330579</v>
+        <v>25.24435261707988</v>
       </c>
       <c r="J6" t="n">
-        <v>184.1404958677686</v>
+        <v>184.2949494949495</v>
       </c>
       <c r="K6" t="n">
-        <v>1.033057851239669</v>
+        <v>1.792011019283746</v>
       </c>
       <c r="L6" t="n">
-        <v>72.12975206611571</v>
+        <v>80.60927456382002</v>
       </c>
       <c r="M6" t="n">
-        <v>4288842.975206612</v>
+        <v>35322970.61524335</v>
       </c>
       <c r="N6" t="n">
-        <v>76.1107438016529</v>
+        <v>84.21524334251608</v>
       </c>
       <c r="O6" t="n">
-        <v>23.0821855500821</v>
+        <v>26.08680669063964</v>
       </c>
       <c r="P6" t="n">
-        <v>184.6805205254516</v>
+        <v>182.1924929253305</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.202333333333333</v>
+        <v>1.697922899310199</v>
       </c>
       <c r="R6" t="n">
-        <v>71.2915041050903</v>
+        <v>76.12983570586546</v>
       </c>
       <c r="S6" t="n">
-        <v>6950567.528735632</v>
+        <v>15204392.84517288</v>
       </c>
       <c r="T6" t="n">
-        <v>78.0733382594417</v>
+        <v>79.39811132326865</v>
       </c>
       <c r="U6" t="n">
-        <v>24.8531746031746</v>
+        <v>24.09977743504059</v>
       </c>
       <c r="V6" t="n">
-        <v>182.0717010262465</v>
+        <v>184.0198127408653</v>
       </c>
       <c r="W6" t="n">
-        <v>1.113728022818932</v>
+        <v>1.498405590510854</v>
       </c>
       <c r="X6" t="n">
-        <v>69.58585606312879</v>
+        <v>76.56655196655197</v>
       </c>
       <c r="Y6" t="n">
-        <v>2894139.097434552</v>
+        <v>22507672.14169845</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.7756734006734</v>
+        <v>82.3017479985901</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>23.97390572390573</v>
+        <v>26.35371900826446</v>
       </c>
       <c r="D7" t="n">
-        <v>183.994739057239</v>
+        <v>182.4115702479339</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.706611570247934</v>
       </c>
       <c r="F7" t="n">
-        <v>72.00778619528619</v>
+        <v>80.69669421487603</v>
       </c>
       <c r="G7" t="n">
-        <v>5434511.784511785</v>
+        <v>34783305.78512397</v>
       </c>
       <c r="H7" t="n">
-        <v>77.87478956228956</v>
+        <v>82.44380165289257</v>
       </c>
       <c r="I7" t="n">
-        <v>25.34710743801653</v>
+        <v>24.30146923783288</v>
       </c>
       <c r="J7" t="n">
-        <v>184.4380165289256</v>
+        <v>184.8678604224059</v>
       </c>
       <c r="K7" t="n">
-        <v>1.173553719008265</v>
+        <v>1.052892561983471</v>
       </c>
       <c r="L7" t="n">
-        <v>72.18181818181819</v>
+        <v>69.73820018365473</v>
       </c>
       <c r="M7" t="n">
-        <v>3835330.578512396</v>
+        <v>3034935.720844812</v>
       </c>
       <c r="N7" t="n">
-        <v>75.84297520661157</v>
+        <v>75.7060606060606</v>
       </c>
       <c r="O7" t="n">
-        <v>23.08811497300056</v>
+        <v>24.97643569099381</v>
       </c>
       <c r="P7" t="n">
-        <v>182.7014405855925</v>
+        <v>181.1455520350328</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.057177460220939</v>
+        <v>1.518862278853835</v>
       </c>
       <c r="R7" t="n">
-        <v>67.93035045528038</v>
+        <v>75.73165873956755</v>
       </c>
       <c r="S7" t="n">
-        <v>2654253.453200964</v>
+        <v>15054205.33437385</v>
       </c>
       <c r="T7" t="n">
-        <v>74.88404171089526</v>
+        <v>78.97217438954704</v>
       </c>
       <c r="U7" t="n">
-        <v>25.769700414528</v>
+        <v>24.61664945360597</v>
       </c>
       <c r="V7" t="n">
-        <v>183.2808811877777</v>
+        <v>183.7360839643449</v>
       </c>
       <c r="W7" t="n">
-        <v>1.178140824692549</v>
+        <v>1.111581293103032</v>
       </c>
       <c r="X7" t="n">
-        <v>69.9454935868729</v>
+        <v>68.18160370225587</v>
       </c>
       <c r="Y7" t="n">
-        <v>2704018.66237211</v>
+        <v>2439245.531240096</v>
       </c>
       <c r="Z7" t="n">
-        <v>74.26468875951636</v>
+        <v>73.75940030179162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.70668220668221</v>
+        <v>26.16681096681097</v>
       </c>
       <c r="D8" t="n">
-        <v>183.7864024864025</v>
+        <v>183.831746031746</v>
       </c>
       <c r="E8" t="n">
-        <v>1.71981351981352</v>
+        <v>1.588600288600288</v>
       </c>
       <c r="F8" t="n">
-        <v>77.64304584304584</v>
+        <v>76.34242424242424</v>
       </c>
       <c r="G8" t="n">
-        <v>18319075.36907537</v>
+        <v>12767171.71717172</v>
       </c>
       <c r="H8" t="n">
-        <v>79.95236985236986</v>
+        <v>79.68419913419913</v>
       </c>
       <c r="I8" t="n">
-        <v>25.24435261707988</v>
+        <v>25.50826446280992</v>
       </c>
       <c r="J8" t="n">
-        <v>184.2949494949495</v>
+        <v>183.6123966942149</v>
       </c>
       <c r="K8" t="n">
-        <v>1.792011019283746</v>
+        <v>1.38099173553719</v>
       </c>
       <c r="L8" t="n">
-        <v>80.60927456382002</v>
+        <v>73.02231404958678</v>
       </c>
       <c r="M8" t="n">
-        <v>35322970.61524335</v>
+        <v>6606611.570247934</v>
       </c>
       <c r="N8" t="n">
-        <v>84.21524334251608</v>
+        <v>77.30495867768595</v>
       </c>
       <c r="O8" t="n">
-        <v>26.20053059069077</v>
+        <v>24.85563758896088</v>
       </c>
       <c r="P8" t="n">
-        <v>182.2746757437833</v>
+        <v>181.7528954263015</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.721159599363261</v>
+        <v>1.536290903547473</v>
       </c>
       <c r="R8" t="n">
-        <v>76.26031657130055</v>
+        <v>74.55788146463195</v>
       </c>
       <c r="S8" t="n">
-        <v>15511947.91059436</v>
+        <v>11567237.13318573</v>
       </c>
       <c r="T8" t="n">
-        <v>79.4644773418801</v>
+        <v>79.35531356047056</v>
       </c>
       <c r="U8" t="n">
-        <v>24.09977743504059</v>
+        <v>25.76834004160091</v>
       </c>
       <c r="V8" t="n">
-        <v>184.0198127408653</v>
+        <v>181.9899506181127</v>
       </c>
       <c r="W8" t="n">
-        <v>1.498405590510854</v>
+        <v>1.306295952620063</v>
       </c>
       <c r="X8" t="n">
-        <v>76.56655196655197</v>
+        <v>71.69955290500747</v>
       </c>
       <c r="Y8" t="n">
-        <v>22507672.14169845</v>
+        <v>4339345.599229493</v>
       </c>
       <c r="Z8" t="n">
-        <v>82.3017479985901</v>
+        <v>76.63753503194215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.4198347107438</v>
+        <v>26.19586776859504</v>
       </c>
       <c r="D9" t="n">
-        <v>182.2107438016529</v>
+        <v>184.3214876033058</v>
       </c>
       <c r="E9" t="n">
-        <v>1.729752066115703</v>
+        <v>1.217355371900826</v>
       </c>
       <c r="F9" t="n">
-        <v>80.77355371900826</v>
+        <v>72.9917355371901</v>
       </c>
       <c r="G9" t="n">
-        <v>34887851.23966942</v>
+        <v>5805165.289256198</v>
       </c>
       <c r="H9" t="n">
-        <v>82.47272727272728</v>
+        <v>77.42561983471074</v>
       </c>
       <c r="I9" t="n">
-        <v>24.30146923783288</v>
+        <v>25.02241161616162</v>
       </c>
       <c r="J9" t="n">
-        <v>184.8678604224059</v>
+        <v>184.1566708754209</v>
       </c>
       <c r="K9" t="n">
-        <v>1.052892561983471</v>
+        <v>1.1378367003367</v>
       </c>
       <c r="L9" t="n">
-        <v>69.73820018365473</v>
+        <v>72.98337542087542</v>
       </c>
       <c r="M9" t="n">
-        <v>3034935.720844812</v>
+        <v>4779135.101010102</v>
       </c>
       <c r="N9" t="n">
-        <v>75.7060606060606</v>
+        <v>76.70023148148148</v>
       </c>
       <c r="O9" t="n">
-        <v>24.90901144856957</v>
+        <v>26.45422714540361</v>
       </c>
       <c r="P9" t="n">
-        <v>181.1425217320025</v>
+        <v>184.822021899669</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.512801672793229</v>
+        <v>1.357635599694423</v>
       </c>
       <c r="R9" t="n">
-        <v>75.79453752744634</v>
+        <v>70.33122103386809</v>
       </c>
       <c r="S9" t="n">
-        <v>15219224.27376779</v>
+        <v>3497872.135217723</v>
       </c>
       <c r="T9" t="n">
-        <v>79.08278045015309</v>
+        <v>74.02554749172397</v>
       </c>
       <c r="U9" t="n">
-        <v>24.61664945360597</v>
+        <v>24.37355133292633</v>
       </c>
       <c r="V9" t="n">
-        <v>183.7360839643449</v>
+        <v>182.7568643162393</v>
       </c>
       <c r="W9" t="n">
-        <v>1.111581293103032</v>
+        <v>1.039710097001764</v>
       </c>
       <c r="X9" t="n">
-        <v>68.18160370225587</v>
+        <v>70.54190620336455</v>
       </c>
       <c r="Y9" t="n">
-        <v>2439245.531240096</v>
+        <v>3360567.034238909</v>
       </c>
       <c r="Z9" t="n">
-        <v>73.75940030179162</v>
+        <v>75.20963149504816</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>26.16681096681097</v>
+        <v>25.4520202020202</v>
       </c>
       <c r="D10" t="n">
-        <v>183.831746031746</v>
+        <v>186.3260489510489</v>
       </c>
       <c r="E10" t="n">
-        <v>1.588600288600288</v>
+        <v>1.715229215229215</v>
       </c>
       <c r="F10" t="n">
-        <v>76.34242424242424</v>
+        <v>80.16394716394717</v>
       </c>
       <c r="G10" t="n">
-        <v>12767171.71717172</v>
+        <v>30315287.49028749</v>
       </c>
       <c r="H10" t="n">
-        <v>79.68419913419913</v>
+        <v>83.8529526029526</v>
       </c>
       <c r="I10" t="n">
-        <v>25.54924242424243</v>
+        <v>26.07084481175391</v>
       </c>
       <c r="J10" t="n">
-        <v>183.7446969696969</v>
+        <v>182.2306473829201</v>
       </c>
       <c r="K10" t="n">
-        <v>1.382575757575758</v>
+        <v>2.089853076216713</v>
       </c>
       <c r="L10" t="n">
-        <v>73.15378787878787</v>
+        <v>78.61772268135904</v>
       </c>
       <c r="M10" t="n">
-        <v>6766060.606060606</v>
+        <v>21569616.62075299</v>
       </c>
       <c r="N10" t="n">
-        <v>77.37954545454545</v>
+        <v>80.74233241505968</v>
       </c>
       <c r="O10" t="n">
-        <v>24.85563758896088</v>
+        <v>25.07951395667643</v>
       </c>
       <c r="P10" t="n">
-        <v>181.7528954263015</v>
+        <v>184.0361743202132</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.536290903547473</v>
+        <v>1.737052055495992</v>
       </c>
       <c r="R10" t="n">
-        <v>74.55788146463195</v>
+        <v>76.45796496028763</v>
       </c>
       <c r="S10" t="n">
-        <v>11567237.13318573</v>
+        <v>16026402.95402538</v>
       </c>
       <c r="T10" t="n">
-        <v>79.35531356047056</v>
+        <v>81.43824784546753</v>
       </c>
       <c r="U10" t="n">
-        <v>25.70110657659571</v>
+        <v>25.21880215637021</v>
       </c>
       <c r="V10" t="n">
-        <v>182.0741213999366</v>
+        <v>182.5240743846461</v>
       </c>
       <c r="W10" t="n">
-        <v>1.293591802722238</v>
+        <v>1.918984279147619</v>
       </c>
       <c r="X10" t="n">
-        <v>71.6797183680517</v>
+        <v>76.14621498183205</v>
       </c>
       <c r="Y10" t="n">
-        <v>4335666.158268061</v>
+        <v>17144298.37521489</v>
       </c>
       <c r="Z10" t="n">
-        <v>76.64850967671619</v>
+        <v>80.57225375115576</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.225</v>
+        <v>24.98863636363636</v>
       </c>
       <c r="D11" t="n">
-        <v>184.2416666666667</v>
+        <v>186.4416666666666</v>
       </c>
       <c r="E11" t="n">
-        <v>1.206818181818182</v>
+        <v>1.037878787878788</v>
       </c>
       <c r="F11" t="n">
-        <v>73.06818181818183</v>
+        <v>73.32045454545455</v>
       </c>
       <c r="G11" t="n">
-        <v>5907007.575757575</v>
+        <v>5048712.121212121</v>
       </c>
       <c r="H11" t="n">
-        <v>77.42803030303031</v>
+        <v>77.05454545454546</v>
       </c>
       <c r="I11" t="n">
-        <v>25.0446510560147</v>
+        <v>25.76083333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>184.2012167125804</v>
+        <v>181.1611111111111</v>
       </c>
       <c r="K11" t="n">
-        <v>1.140266299357209</v>
+        <v>1.093611111111111</v>
       </c>
       <c r="L11" t="n">
-        <v>73.0121671258035</v>
+        <v>71.37888888888889</v>
       </c>
       <c r="M11" t="n">
-        <v>4763096.877869605</v>
+        <v>3791833.333333333</v>
       </c>
       <c r="N11" t="n">
-        <v>76.64267676767678</v>
+        <v>73.86083333333333</v>
       </c>
       <c r="O11" t="n">
-        <v>26.55179154995331</v>
+        <v>25.45243300590115</v>
       </c>
       <c r="P11" t="n">
-        <v>184.8090756302521</v>
+        <v>183.0929216988531</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.390332633053221</v>
+        <v>1.068729135019097</v>
       </c>
       <c r="R11" t="n">
-        <v>70.36959150326798</v>
+        <v>70.98908371529642</v>
       </c>
       <c r="S11" t="n">
-        <v>3520184.87394958</v>
+        <v>3280140.151641324</v>
       </c>
       <c r="T11" t="n">
-        <v>73.98869631185808</v>
+        <v>74.8233442548303</v>
       </c>
       <c r="U11" t="n">
-        <v>24.26546509046509</v>
+        <v>26.58753290480563</v>
       </c>
       <c r="V11" t="n">
-        <v>182.7177156177156</v>
+        <v>184.0239610221429</v>
       </c>
       <c r="W11" t="n">
-        <v>1.037638287638288</v>
+        <v>1.245086563268382</v>
       </c>
       <c r="X11" t="n">
-        <v>70.56276131276131</v>
+        <v>70.11584910039454</v>
       </c>
       <c r="Y11" t="n">
-        <v>3403146.991896993</v>
+        <v>2914704.766445676</v>
       </c>
       <c r="Z11" t="n">
-        <v>75.29687072187072</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>25.62402874902875</v>
-      </c>
-      <c r="D12" t="n">
-        <v>186.4061771561772</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.755827505827506</v>
-      </c>
-      <c r="F12" t="n">
-        <v>80.21416083916083</v>
-      </c>
-      <c r="G12" t="n">
-        <v>29955778.94327894</v>
-      </c>
-      <c r="H12" t="n">
-        <v>83.81876456876458</v>
-      </c>
-      <c r="I12" t="n">
-        <v>26.06681818181818</v>
-      </c>
-      <c r="J12" t="n">
-        <v>182.2870454545455</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.087727272727273</v>
-      </c>
-      <c r="L12" t="n">
-        <v>78.55727272727272</v>
-      </c>
-      <c r="M12" t="n">
-        <v>21251022.72727273</v>
-      </c>
-      <c r="N12" t="n">
-        <v>80.70545454545454</v>
-      </c>
-      <c r="O12" t="n">
-        <v>24.8432502204127</v>
-      </c>
-      <c r="P12" t="n">
-        <v>183.798079082118</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.744378062821999</v>
-      </c>
-      <c r="R12" t="n">
-        <v>76.23635323867589</v>
-      </c>
-      <c r="S12" t="n">
-        <v>15836567.78919022</v>
-      </c>
-      <c r="T12" t="n">
-        <v>81.52249692971661</v>
-      </c>
-      <c r="U12" t="n">
-        <v>25.34594552990198</v>
-      </c>
-      <c r="V12" t="n">
-        <v>182.7396397178475</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.963514286009749</v>
-      </c>
-      <c r="X12" t="n">
-        <v>76.28715226948893</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>17566886.10747322</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>80.59263702100816</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24.98863636363636</v>
-      </c>
-      <c r="D13" t="n">
-        <v>186.4416666666666</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.037878787878788</v>
-      </c>
-      <c r="F13" t="n">
-        <v>73.32045454545455</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5048712.121212121</v>
-      </c>
-      <c r="H13" t="n">
-        <v>77.05454545454546</v>
-      </c>
-      <c r="I13" t="n">
-        <v>25.8037037037037</v>
-      </c>
-      <c r="J13" t="n">
-        <v>181.1512345679012</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.076234567901234</v>
-      </c>
-      <c r="L13" t="n">
-        <v>71.1848765432099</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3585370.370370371</v>
-      </c>
-      <c r="N13" t="n">
-        <v>73.63703703703703</v>
-      </c>
-      <c r="O13" t="n">
-        <v>25.45243300590115</v>
-      </c>
-      <c r="P13" t="n">
-        <v>183.0929216988531</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.068729135019097</v>
-      </c>
-      <c r="R13" t="n">
-        <v>70.98908371529642</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3280140.151641324</v>
-      </c>
-      <c r="T13" t="n">
-        <v>74.8233442548303</v>
-      </c>
-      <c r="U13" t="n">
-        <v>26.54628619528619</v>
-      </c>
-      <c r="V13" t="n">
-        <v>183.7406428386428</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.255309505309505</v>
-      </c>
-      <c r="X13" t="n">
-        <v>70.05600543900543</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2813568.1002331</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>72.48127298627298</v>
+        <v>72.46349492258584</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,821 +558,657 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.16835016835017</v>
+        <v>24.73636363636363</v>
       </c>
       <c r="D2" t="n">
-        <v>184.5289562289562</v>
+        <v>185.5545454545455</v>
       </c>
       <c r="E2" t="n">
-        <v>1.02013468013468</v>
+        <v>1.290909090909091</v>
       </c>
       <c r="F2" t="n">
-        <v>69.94080808080807</v>
+        <v>75.11818181818182</v>
       </c>
       <c r="G2" t="n">
-        <v>2632380.471380471</v>
+        <v>10735454.54545455</v>
       </c>
       <c r="H2" t="n">
-        <v>74.39919191919192</v>
+        <v>79.52727272727273</v>
       </c>
       <c r="I2" t="n">
-        <v>26.02213039485767</v>
+        <v>25.08099173553719</v>
       </c>
       <c r="J2" t="n">
-        <v>186.1161616161616</v>
+        <v>184.2231404958678</v>
       </c>
       <c r="K2" t="n">
-        <v>1.255922865013774</v>
+        <v>1.024793388429752</v>
       </c>
       <c r="L2" t="n">
-        <v>75.9932966023875</v>
+        <v>71.98099173553719</v>
       </c>
       <c r="M2" t="n">
-        <v>12909522.49770432</v>
+        <v>4153305.785123967</v>
       </c>
       <c r="N2" t="n">
-        <v>78.9961432506887</v>
+        <v>76.16859504132232</v>
       </c>
       <c r="O2" t="n">
-        <v>25.40600502370754</v>
+        <v>23.08480623973727</v>
       </c>
       <c r="P2" t="n">
-        <v>182.0339096194931</v>
+        <v>184.7485205254516</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.037615998037051</v>
+        <v>1.194747126436782</v>
       </c>
       <c r="R2" t="n">
-        <v>67.34531972172248</v>
+        <v>71.29274548440065</v>
       </c>
       <c r="S2" t="n">
-        <v>1621746.142248293</v>
+        <v>6617864.080459771</v>
       </c>
       <c r="T2" t="n">
-        <v>72.43543921219893</v>
+        <v>77.99513136288999</v>
       </c>
       <c r="U2" t="n">
-        <v>24.66980333165599</v>
+        <v>24.6699790108881</v>
       </c>
       <c r="V2" t="n">
-        <v>184.749517941873</v>
+        <v>182.0059296763842</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17376111239044</v>
+        <v>1.097199097199097</v>
       </c>
       <c r="X2" t="n">
-        <v>71.68604355545321</v>
+        <v>69.48668250940977</v>
       </c>
       <c r="Y2" t="n">
-        <v>5757704.401174708</v>
+        <v>2904705.557489648</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.0490862040046</v>
+        <v>74.79599020508111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>28.07520661157025</v>
+        <v>23.97153351698806</v>
       </c>
       <c r="D3" t="n">
-        <v>182.9925619834711</v>
+        <v>183.928145087236</v>
       </c>
       <c r="E3" t="n">
-        <v>2.414049586776859</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>82.89173553719007</v>
+        <v>71.96717171717172</v>
       </c>
       <c r="G3" t="n">
-        <v>39731404.95867768</v>
+        <v>5414508.723599633</v>
       </c>
       <c r="H3" t="n">
-        <v>84.68512396694214</v>
+        <v>77.84687786960514</v>
       </c>
       <c r="I3" t="n">
-        <v>25.81428571428571</v>
+        <v>25.23140495867769</v>
       </c>
       <c r="J3" t="n">
-        <v>187.2811688311688</v>
+        <v>184.5206611570248</v>
       </c>
       <c r="K3" t="n">
-        <v>1.501298701298701</v>
+        <v>1.15702479338843</v>
       </c>
       <c r="L3" t="n">
-        <v>78.09220779220779</v>
+        <v>72.19008264462809</v>
       </c>
       <c r="M3" t="n">
-        <v>18464610.38961039</v>
+        <v>3950206.611570248</v>
       </c>
       <c r="N3" t="n">
-        <v>81.49285714285715</v>
+        <v>75.95867768595041</v>
       </c>
       <c r="O3" t="n">
-        <v>27.03807644851123</v>
+        <v>22.98150091916267</v>
       </c>
       <c r="P3" t="n">
-        <v>182.5702588393893</v>
+        <v>183.0023620617531</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.879477285999025</v>
+        <v>1.050517703640234</v>
       </c>
       <c r="R3" t="n">
-        <v>78.98688163688163</v>
+        <v>67.79753646504895</v>
       </c>
       <c r="S3" t="n">
-        <v>24015329.64619921</v>
+        <v>2636458.31258287</v>
       </c>
       <c r="T3" t="n">
-        <v>81.5064071194506</v>
+        <v>74.90512060160906</v>
       </c>
       <c r="U3" t="n">
-        <v>25.22238953650444</v>
+        <v>25.94768717872166</v>
       </c>
       <c r="V3" t="n">
-        <v>186.7153550096097</v>
+        <v>183.4509729095936</v>
       </c>
       <c r="W3" t="n">
-        <v>1.337560481271662</v>
+        <v>1.2122752726201</v>
       </c>
       <c r="X3" t="n">
-        <v>74.62096602098154</v>
+        <v>69.87873403735472</v>
       </c>
       <c r="Y3" t="n">
-        <v>12820676.14447319</v>
+        <v>2641820.821898408</v>
       </c>
       <c r="Z3" t="n">
-        <v>78.77938808660859</v>
+        <v>74.08170954205438</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>24.78512396694215</v>
+        <v>26.700826446281</v>
       </c>
       <c r="D4" t="n">
-        <v>185.5537190082645</v>
+        <v>183.7223140495868</v>
       </c>
       <c r="E4" t="n">
-        <v>1.289256198347108</v>
+        <v>1.717355371900826</v>
       </c>
       <c r="F4" t="n">
-        <v>75.16528925619834</v>
+        <v>77.72561983471074</v>
       </c>
       <c r="G4" t="n">
-        <v>10808264.46280992</v>
+        <v>18315371.90082645</v>
       </c>
       <c r="H4" t="n">
-        <v>79.47933884297521</v>
+        <v>80.0305785123967</v>
       </c>
       <c r="I4" t="n">
-        <v>25.12727272727273</v>
+        <v>25.17878787878788</v>
       </c>
       <c r="J4" t="n">
-        <v>184.1969696969697</v>
+        <v>184.2144444444445</v>
       </c>
       <c r="K4" t="n">
-        <v>1.03030303030303</v>
+        <v>1.791212121212121</v>
       </c>
       <c r="L4" t="n">
-        <v>72.05075757575757</v>
+        <v>80.46020202020202</v>
       </c>
       <c r="M4" t="n">
-        <v>4208712.121212122</v>
+        <v>34730267.67676768</v>
       </c>
       <c r="N4" t="n">
-        <v>76.16212121212122</v>
+        <v>84.12676767676768</v>
       </c>
       <c r="O4" t="n">
-        <v>23.11471413643827</v>
+        <v>26.09469820797052</v>
       </c>
       <c r="P4" t="n">
-        <v>184.7713822958651</v>
+        <v>182.1190831912696</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.202121212121212</v>
+        <v>1.694176759721798</v>
       </c>
       <c r="R4" t="n">
-        <v>71.34136736826393</v>
+        <v>76.10211326015362</v>
       </c>
       <c r="S4" t="n">
-        <v>6841788.662486938</v>
+        <v>15077282.31331113</v>
       </c>
       <c r="T4" t="n">
-        <v>78.07394387221974</v>
+        <v>79.39477757004801</v>
       </c>
       <c r="U4" t="n">
-        <v>24.67096560846561</v>
+        <v>24.21716258595206</v>
       </c>
       <c r="V4" t="n">
-        <v>182.0622537185037</v>
+        <v>184.0366088297667</v>
       </c>
       <c r="W4" t="n">
-        <v>1.104250687584021</v>
+        <v>1.511209112524902</v>
       </c>
       <c r="X4" t="n">
-        <v>69.45370139120139</v>
+        <v>76.68987382987385</v>
       </c>
       <c r="Y4" t="n">
-        <v>2883915.700426117</v>
+        <v>22840754.17068312</v>
       </c>
       <c r="Z4" t="n">
-        <v>74.79783950617285</v>
+        <v>82.30599687252318</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>23.97390572390573</v>
+        <v>26.35371900826446</v>
       </c>
       <c r="D5" t="n">
-        <v>183.994739057239</v>
+        <v>182.4115702479339</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>1.706611570247934</v>
       </c>
       <c r="F5" t="n">
-        <v>72.00778619528619</v>
+        <v>80.69669421487603</v>
       </c>
       <c r="G5" t="n">
-        <v>5434511.784511785</v>
+        <v>34783305.78512397</v>
       </c>
       <c r="H5" t="n">
-        <v>77.87478956228956</v>
+        <v>82.44380165289257</v>
       </c>
       <c r="I5" t="n">
-        <v>25.32575757575757</v>
+        <v>24.2679797979798</v>
       </c>
       <c r="J5" t="n">
-        <v>184.5454545454545</v>
+        <v>184.8273737373738</v>
       </c>
       <c r="K5" t="n">
-        <v>1.166666666666667</v>
+        <v>1.058181818181818</v>
       </c>
       <c r="L5" t="n">
-        <v>72.22727272727273</v>
+        <v>69.6029292929293</v>
       </c>
       <c r="M5" t="n">
-        <v>3931628.787878788</v>
+        <v>2971611.111111111</v>
       </c>
       <c r="N5" t="n">
-        <v>75.88636363636363</v>
+        <v>75.6130303030303</v>
       </c>
       <c r="O5" t="n">
-        <v>23.08811497300056</v>
+        <v>24.97643569099381</v>
       </c>
       <c r="P5" t="n">
-        <v>182.7014405855925</v>
+        <v>181.1455520350328</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.057177460220939</v>
+        <v>1.518862278853835</v>
       </c>
       <c r="R5" t="n">
-        <v>67.93035045528038</v>
+        <v>75.73165873956755</v>
       </c>
       <c r="S5" t="n">
-        <v>2654253.453200964</v>
+        <v>15054205.33437385</v>
       </c>
       <c r="T5" t="n">
-        <v>74.88404171089526</v>
+        <v>78.97217438954704</v>
       </c>
       <c r="U5" t="n">
-        <v>25.86296612072475</v>
+        <v>24.57062209127426</v>
       </c>
       <c r="V5" t="n">
-        <v>183.3932768912654</v>
+        <v>183.6866154377024</v>
       </c>
       <c r="W5" t="n">
-        <v>1.200332793005207</v>
+        <v>1.10735480702872</v>
       </c>
       <c r="X5" t="n">
-        <v>69.93769010895447</v>
+        <v>68.22668714940454</v>
       </c>
       <c r="Y5" t="n">
-        <v>2676137.477544806</v>
+        <v>2482304.699748721</v>
       </c>
       <c r="Z5" t="n">
-        <v>74.22719926412456</v>
+        <v>73.81995571658615</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.78409090909091</v>
+        <v>26.08733488733488</v>
       </c>
       <c r="D6" t="n">
-        <v>183.7871212121212</v>
+        <v>183.8649572649573</v>
       </c>
       <c r="E6" t="n">
-        <v>1.724242424242424</v>
+        <v>1.564646464646465</v>
       </c>
       <c r="F6" t="n">
-        <v>77.7151515151515</v>
+        <v>76.26876456876457</v>
       </c>
       <c r="G6" t="n">
-        <v>18346590.90909091</v>
+        <v>12791569.54156954</v>
       </c>
       <c r="H6" t="n">
-        <v>79.99469696969697</v>
+        <v>79.72144522144524</v>
       </c>
       <c r="I6" t="n">
-        <v>25.24435261707988</v>
+        <v>25.50826446280992</v>
       </c>
       <c r="J6" t="n">
-        <v>184.2949494949495</v>
+        <v>183.6123966942149</v>
       </c>
       <c r="K6" t="n">
-        <v>1.792011019283746</v>
+        <v>1.38099173553719</v>
       </c>
       <c r="L6" t="n">
-        <v>80.60927456382002</v>
+        <v>73.02231404958678</v>
       </c>
       <c r="M6" t="n">
-        <v>35322970.61524335</v>
+        <v>6606611.570247934</v>
       </c>
       <c r="N6" t="n">
-        <v>84.21524334251608</v>
+        <v>77.30495867768595</v>
       </c>
       <c r="O6" t="n">
-        <v>26.08680669063964</v>
+        <v>24.9271538707328</v>
       </c>
       <c r="P6" t="n">
-        <v>182.1924929253305</v>
+        <v>181.7110953593789</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.697922899310199</v>
+        <v>1.554752027182179</v>
       </c>
       <c r="R6" t="n">
-        <v>76.12983570586546</v>
+        <v>74.57515439780876</v>
       </c>
       <c r="S6" t="n">
-        <v>15204392.84517288</v>
+        <v>11470984.71892936</v>
       </c>
       <c r="T6" t="n">
-        <v>79.39811132326865</v>
+        <v>79.31711830728737</v>
       </c>
       <c r="U6" t="n">
-        <v>24.09977743504059</v>
+        <v>25.76834004160091</v>
       </c>
       <c r="V6" t="n">
-        <v>184.0198127408653</v>
+        <v>181.9899506181127</v>
       </c>
       <c r="W6" t="n">
-        <v>1.498405590510854</v>
+        <v>1.306295952620063</v>
       </c>
       <c r="X6" t="n">
-        <v>76.56655196655197</v>
+        <v>71.69955290500747</v>
       </c>
       <c r="Y6" t="n">
-        <v>22507672.14169845</v>
+        <v>4339345.599229493</v>
       </c>
       <c r="Z6" t="n">
-        <v>82.3017479985901</v>
+        <v>76.63753503194215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>26.35371900826446</v>
+        <v>26.19586776859504</v>
       </c>
       <c r="D7" t="n">
-        <v>182.4115702479339</v>
+        <v>184.3214876033058</v>
       </c>
       <c r="E7" t="n">
-        <v>1.706611570247934</v>
+        <v>1.217355371900826</v>
       </c>
       <c r="F7" t="n">
-        <v>80.69669421487603</v>
+        <v>72.9917355371901</v>
       </c>
       <c r="G7" t="n">
-        <v>34783305.78512397</v>
+        <v>5805165.289256198</v>
       </c>
       <c r="H7" t="n">
-        <v>82.44380165289257</v>
+        <v>77.42561983471074</v>
       </c>
       <c r="I7" t="n">
-        <v>24.30146923783288</v>
+        <v>25.03271349862259</v>
       </c>
       <c r="J7" t="n">
-        <v>184.8678604224059</v>
+        <v>184.0882690541782</v>
       </c>
       <c r="K7" t="n">
-        <v>1.052892561983471</v>
+        <v>1.133838383838384</v>
       </c>
       <c r="L7" t="n">
-        <v>69.73820018365473</v>
+        <v>72.96533516988062</v>
       </c>
       <c r="M7" t="n">
-        <v>3034935.720844812</v>
+        <v>4769800.275482094</v>
       </c>
       <c r="N7" t="n">
-        <v>75.7060606060606</v>
+        <v>76.71430211202939</v>
       </c>
       <c r="O7" t="n">
-        <v>24.97643569099381</v>
+        <v>26.45422714540361</v>
       </c>
       <c r="P7" t="n">
-        <v>181.1455520350328</v>
+        <v>184.822021899669</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.518862278853835</v>
+        <v>1.357635599694423</v>
       </c>
       <c r="R7" t="n">
-        <v>75.73165873956755</v>
+        <v>70.33122103386809</v>
       </c>
       <c r="S7" t="n">
-        <v>15054205.33437385</v>
+        <v>3497872.135217723</v>
       </c>
       <c r="T7" t="n">
-        <v>78.97217438954704</v>
+        <v>74.02554749172397</v>
       </c>
       <c r="U7" t="n">
-        <v>24.61664945360597</v>
+        <v>24.33478327228327</v>
       </c>
       <c r="V7" t="n">
-        <v>183.7360839643449</v>
+        <v>182.793851981352</v>
       </c>
       <c r="W7" t="n">
-        <v>1.111581293103032</v>
+        <v>1.043320105820106</v>
       </c>
       <c r="X7" t="n">
-        <v>68.18160370225587</v>
+        <v>70.47753404003406</v>
       </c>
       <c r="Y7" t="n">
-        <v>2439245.531240096</v>
+        <v>3325845.855533355</v>
       </c>
       <c r="Z7" t="n">
-        <v>73.75940030179162</v>
+        <v>75.16505254005254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.16681096681097</v>
+        <v>25.40635521885522</v>
       </c>
       <c r="D8" t="n">
-        <v>183.831746031746</v>
+        <v>186.3254419191919</v>
       </c>
       <c r="E8" t="n">
-        <v>1.588600288600288</v>
+        <v>1.710016835016835</v>
       </c>
       <c r="F8" t="n">
-        <v>76.34242424242424</v>
+        <v>80.08501683501683</v>
       </c>
       <c r="G8" t="n">
-        <v>12767171.71717172</v>
+        <v>30008228.11447811</v>
       </c>
       <c r="H8" t="n">
-        <v>79.68419913419913</v>
+        <v>83.85921717171718</v>
       </c>
       <c r="I8" t="n">
-        <v>25.50826446280992</v>
+        <v>26.14792929292929</v>
       </c>
       <c r="J8" t="n">
-        <v>183.6123966942149</v>
+        <v>182.3437121212121</v>
       </c>
       <c r="K8" t="n">
-        <v>1.38099173553719</v>
+        <v>2.098838383838384</v>
       </c>
       <c r="L8" t="n">
-        <v>73.02231404958678</v>
+        <v>78.68949494949496</v>
       </c>
       <c r="M8" t="n">
-        <v>6606611.570247934</v>
+        <v>21848578.28282828</v>
       </c>
       <c r="N8" t="n">
-        <v>77.30495867768595</v>
+        <v>80.70656565656566</v>
       </c>
       <c r="O8" t="n">
-        <v>24.85563758896088</v>
+        <v>25.07164736610961</v>
       </c>
       <c r="P8" t="n">
-        <v>181.7528954263015</v>
+        <v>184.1152758034194</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.536290903547473</v>
+        <v>1.726009292004716</v>
       </c>
       <c r="R8" t="n">
-        <v>74.55788146463195</v>
+        <v>76.48525914176086</v>
       </c>
       <c r="S8" t="n">
-        <v>11567237.13318573</v>
+        <v>16207407.54802025</v>
       </c>
       <c r="T8" t="n">
-        <v>79.35531356047056</v>
+        <v>81.4602757456333</v>
       </c>
       <c r="U8" t="n">
-        <v>25.76834004160091</v>
+        <v>25.22914391046877</v>
       </c>
       <c r="V8" t="n">
-        <v>181.9899506181127</v>
+        <v>182.6380202846491</v>
       </c>
       <c r="W8" t="n">
-        <v>1.306295952620063</v>
+        <v>1.91088270706238</v>
       </c>
       <c r="X8" t="n">
-        <v>71.69955290500747</v>
+        <v>76.24160571078448</v>
       </c>
       <c r="Y8" t="n">
-        <v>4339345.599229493</v>
+        <v>17261708.98196715</v>
       </c>
       <c r="Z8" t="n">
-        <v>76.63753503194215</v>
+        <v>80.60255604934824</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.19586776859504</v>
+        <v>24.95454545454545</v>
       </c>
       <c r="D9" t="n">
-        <v>184.3214876033058</v>
+        <v>186.5231404958678</v>
       </c>
       <c r="E9" t="n">
-        <v>1.217355371900826</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="F9" t="n">
-        <v>72.9917355371901</v>
+        <v>73.27520661157024</v>
       </c>
       <c r="G9" t="n">
-        <v>5805165.289256198</v>
+        <v>4970495.867768595</v>
       </c>
       <c r="H9" t="n">
-        <v>77.42561983471074</v>
+        <v>77.02644628099173</v>
       </c>
       <c r="I9" t="n">
-        <v>25.02241161616162</v>
+        <v>25.84537037037037</v>
       </c>
       <c r="J9" t="n">
-        <v>184.1566708754209</v>
+        <v>181.1049382716049</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1378367003367</v>
+        <v>1.104012345679012</v>
       </c>
       <c r="L9" t="n">
-        <v>72.98337542087542</v>
+        <v>71.420987654321</v>
       </c>
       <c r="M9" t="n">
-        <v>4779135.101010102</v>
+        <v>3818395.061728395</v>
       </c>
       <c r="N9" t="n">
-        <v>76.70023148148148</v>
+        <v>73.83302469135803</v>
       </c>
       <c r="O9" t="n">
-        <v>26.45422714540361</v>
+        <v>25.38100916661077</v>
       </c>
       <c r="P9" t="n">
-        <v>184.822021899669</v>
+        <v>182.9325379571904</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.357635599694423</v>
+        <v>1.070648233873646</v>
       </c>
       <c r="R9" t="n">
-        <v>70.33122103386809</v>
+        <v>70.93614327382987</v>
       </c>
       <c r="S9" t="n">
-        <v>3497872.135217723</v>
+        <v>3289590.122136855</v>
       </c>
       <c r="T9" t="n">
-        <v>74.02554749172397</v>
+        <v>74.8505746849231</v>
       </c>
       <c r="U9" t="n">
-        <v>24.37355133292633</v>
+        <v>26.63090157990158</v>
       </c>
       <c r="V9" t="n">
-        <v>182.7568643162393</v>
+        <v>183.972510970511</v>
       </c>
       <c r="W9" t="n">
-        <v>1.039710097001764</v>
+        <v>1.254210604210604</v>
       </c>
       <c r="X9" t="n">
-        <v>70.54190620336455</v>
+        <v>70.177434010434</v>
       </c>
       <c r="Y9" t="n">
-        <v>3360567.034238909</v>
+        <v>2955636.781551782</v>
       </c>
       <c r="Z9" t="n">
-        <v>75.20963149504816</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>25.4520202020202</v>
-      </c>
-      <c r="D10" t="n">
-        <v>186.3260489510489</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.715229215229215</v>
-      </c>
-      <c r="F10" t="n">
-        <v>80.16394716394717</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30315287.49028749</v>
-      </c>
-      <c r="H10" t="n">
-        <v>83.8529526029526</v>
-      </c>
-      <c r="I10" t="n">
-        <v>26.07084481175391</v>
-      </c>
-      <c r="J10" t="n">
-        <v>182.2306473829201</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.089853076216713</v>
-      </c>
-      <c r="L10" t="n">
-        <v>78.61772268135904</v>
-      </c>
-      <c r="M10" t="n">
-        <v>21569616.62075299</v>
-      </c>
-      <c r="N10" t="n">
-        <v>80.74233241505968</v>
-      </c>
-      <c r="O10" t="n">
-        <v>25.07951395667643</v>
-      </c>
-      <c r="P10" t="n">
-        <v>184.0361743202132</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.737052055495992</v>
-      </c>
-      <c r="R10" t="n">
-        <v>76.45796496028763</v>
-      </c>
-      <c r="S10" t="n">
-        <v>16026402.95402538</v>
-      </c>
-      <c r="T10" t="n">
-        <v>81.43824784546753</v>
-      </c>
-      <c r="U10" t="n">
-        <v>25.21880215637021</v>
-      </c>
-      <c r="V10" t="n">
-        <v>182.5240743846461</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.918984279147619</v>
-      </c>
-      <c r="X10" t="n">
-        <v>76.14621498183205</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>17144298.37521489</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>80.57225375115576</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>24.98863636363636</v>
-      </c>
-      <c r="D11" t="n">
-        <v>186.4416666666666</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.037878787878788</v>
-      </c>
-      <c r="F11" t="n">
-        <v>73.32045454545455</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5048712.121212121</v>
-      </c>
-      <c r="H11" t="n">
-        <v>77.05454545454546</v>
-      </c>
-      <c r="I11" t="n">
-        <v>25.76083333333333</v>
-      </c>
-      <c r="J11" t="n">
-        <v>181.1611111111111</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.093611111111111</v>
-      </c>
-      <c r="L11" t="n">
-        <v>71.37888888888889</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3791833.333333333</v>
-      </c>
-      <c r="N11" t="n">
-        <v>73.86083333333333</v>
-      </c>
-      <c r="O11" t="n">
-        <v>25.45243300590115</v>
-      </c>
-      <c r="P11" t="n">
-        <v>183.0929216988531</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.068729135019097</v>
-      </c>
-      <c r="R11" t="n">
-        <v>70.98908371529642</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3280140.151641324</v>
-      </c>
-      <c r="T11" t="n">
-        <v>74.8233442548303</v>
-      </c>
-      <c r="U11" t="n">
-        <v>26.58753290480563</v>
-      </c>
-      <c r="V11" t="n">
-        <v>184.0239610221429</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.245086563268382</v>
-      </c>
-      <c r="X11" t="n">
-        <v>70.11584910039454</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2914704.766445676</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>72.46349492258584</v>
+        <v>72.47907518407519</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,656 +558,328 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.73636363636363</v>
+        <v>26.12491582491582</v>
       </c>
       <c r="D2" t="n">
-        <v>185.5545454545455</v>
+        <v>183.906734006734</v>
       </c>
       <c r="E2" t="n">
-        <v>1.290909090909091</v>
+        <v>1.566245791245791</v>
       </c>
       <c r="F2" t="n">
-        <v>75.11818181818182</v>
+        <v>76.26085858585859</v>
       </c>
       <c r="G2" t="n">
-        <v>10735454.54545455</v>
+        <v>12730260.94276094</v>
       </c>
       <c r="H2" t="n">
-        <v>79.52727272727273</v>
+        <v>79.64520202020202</v>
       </c>
       <c r="I2" t="n">
-        <v>25.08099173553719</v>
+        <v>25.50826446280992</v>
       </c>
       <c r="J2" t="n">
-        <v>184.2231404958678</v>
+        <v>183.6123966942149</v>
       </c>
       <c r="K2" t="n">
-        <v>1.024793388429752</v>
+        <v>1.38099173553719</v>
       </c>
       <c r="L2" t="n">
-        <v>71.98099173553719</v>
+        <v>73.02231404958678</v>
       </c>
       <c r="M2" t="n">
-        <v>4153305.785123967</v>
+        <v>6606611.570247934</v>
       </c>
       <c r="N2" t="n">
-        <v>76.16859504132232</v>
+        <v>77.30495867768595</v>
       </c>
       <c r="O2" t="n">
-        <v>23.08480623973727</v>
+        <v>24.90792546522369</v>
       </c>
       <c r="P2" t="n">
-        <v>184.7485205254516</v>
+        <v>181.8185989200288</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.194747126436782</v>
+        <v>1.539577854008764</v>
       </c>
       <c r="R2" t="n">
-        <v>71.29274548440065</v>
+        <v>74.58799621166125</v>
       </c>
       <c r="S2" t="n">
-        <v>6617864.080459771</v>
+        <v>11511110.63848926</v>
       </c>
       <c r="T2" t="n">
-        <v>77.99513136288999</v>
+        <v>79.39179044692975</v>
       </c>
       <c r="U2" t="n">
-        <v>24.6699790108881</v>
+        <v>25.76834004160091</v>
       </c>
       <c r="V2" t="n">
-        <v>182.0059296763842</v>
+        <v>181.9899506181127</v>
       </c>
       <c r="W2" t="n">
-        <v>1.097199097199097</v>
+        <v>1.306295952620063</v>
       </c>
       <c r="X2" t="n">
-        <v>69.48668250940977</v>
+        <v>71.69955290500747</v>
       </c>
       <c r="Y2" t="n">
-        <v>2904705.557489648</v>
+        <v>4339345.599229493</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.79599020508111</v>
+        <v>76.63753503194215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>23.97153351698806</v>
+        <v>26.19586776859504</v>
       </c>
       <c r="D3" t="n">
-        <v>183.928145087236</v>
+        <v>184.3214876033058</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>1.217355371900826</v>
       </c>
       <c r="F3" t="n">
-        <v>71.96717171717172</v>
+        <v>72.9917355371901</v>
       </c>
       <c r="G3" t="n">
-        <v>5414508.723599633</v>
+        <v>5805165.289256198</v>
       </c>
       <c r="H3" t="n">
-        <v>77.84687786960514</v>
+        <v>77.42561983471074</v>
       </c>
       <c r="I3" t="n">
-        <v>25.23140495867769</v>
+        <v>25.03271349862259</v>
       </c>
       <c r="J3" t="n">
-        <v>184.5206611570248</v>
+        <v>184.0882690541782</v>
       </c>
       <c r="K3" t="n">
-        <v>1.15702479338843</v>
+        <v>1.133838383838384</v>
       </c>
       <c r="L3" t="n">
-        <v>72.19008264462809</v>
+        <v>72.96533516988062</v>
       </c>
       <c r="M3" t="n">
-        <v>3950206.611570248</v>
+        <v>4769800.275482094</v>
       </c>
       <c r="N3" t="n">
-        <v>75.95867768595041</v>
+        <v>76.71430211202939</v>
       </c>
       <c r="O3" t="n">
-        <v>22.98150091916267</v>
+        <v>26.45422714540361</v>
       </c>
       <c r="P3" t="n">
-        <v>183.0023620617531</v>
+        <v>184.822021899669</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.050517703640234</v>
+        <v>1.357635599694423</v>
       </c>
       <c r="R3" t="n">
-        <v>67.79753646504895</v>
+        <v>70.33122103386809</v>
       </c>
       <c r="S3" t="n">
-        <v>2636458.31258287</v>
+        <v>3497872.135217723</v>
       </c>
       <c r="T3" t="n">
-        <v>74.90512060160906</v>
+        <v>74.02554749172397</v>
       </c>
       <c r="U3" t="n">
-        <v>25.94768717872166</v>
+        <v>24.33478327228327</v>
       </c>
       <c r="V3" t="n">
-        <v>183.4509729095936</v>
+        <v>182.793851981352</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2122752726201</v>
+        <v>1.043320105820106</v>
       </c>
       <c r="X3" t="n">
-        <v>69.87873403735472</v>
+        <v>70.47753404003406</v>
       </c>
       <c r="Y3" t="n">
-        <v>2641820.821898408</v>
+        <v>3325845.855533355</v>
       </c>
       <c r="Z3" t="n">
-        <v>74.08170954205438</v>
+        <v>75.16505254005254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.700826446281</v>
+        <v>25.40635521885522</v>
       </c>
       <c r="D4" t="n">
-        <v>183.7223140495868</v>
+        <v>186.3254419191919</v>
       </c>
       <c r="E4" t="n">
-        <v>1.717355371900826</v>
+        <v>1.710016835016835</v>
       </c>
       <c r="F4" t="n">
-        <v>77.72561983471074</v>
+        <v>80.08501683501683</v>
       </c>
       <c r="G4" t="n">
-        <v>18315371.90082645</v>
+        <v>30008228.11447811</v>
       </c>
       <c r="H4" t="n">
-        <v>80.0305785123967</v>
+        <v>83.85921717171718</v>
       </c>
       <c r="I4" t="n">
-        <v>25.17878787878788</v>
+        <v>26.14792929292929</v>
       </c>
       <c r="J4" t="n">
-        <v>184.2144444444445</v>
+        <v>182.3437121212121</v>
       </c>
       <c r="K4" t="n">
-        <v>1.791212121212121</v>
+        <v>2.098838383838384</v>
       </c>
       <c r="L4" t="n">
-        <v>80.46020202020202</v>
+        <v>78.68949494949496</v>
       </c>
       <c r="M4" t="n">
-        <v>34730267.67676768</v>
+        <v>21848578.28282828</v>
       </c>
       <c r="N4" t="n">
-        <v>84.12676767676768</v>
+        <v>80.70656565656566</v>
       </c>
       <c r="O4" t="n">
-        <v>26.09469820797052</v>
+        <v>25.07164736610961</v>
       </c>
       <c r="P4" t="n">
-        <v>182.1190831912696</v>
+        <v>184.1152758034194</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.694176759721798</v>
+        <v>1.726009292004716</v>
       </c>
       <c r="R4" t="n">
-        <v>76.10211326015362</v>
+        <v>76.48525914176086</v>
       </c>
       <c r="S4" t="n">
-        <v>15077282.31331113</v>
+        <v>16207407.54802025</v>
       </c>
       <c r="T4" t="n">
-        <v>79.39477757004801</v>
+        <v>81.4602757456333</v>
       </c>
       <c r="U4" t="n">
-        <v>24.21716258595206</v>
+        <v>25.22914391046877</v>
       </c>
       <c r="V4" t="n">
-        <v>184.0366088297667</v>
+        <v>182.6380202846491</v>
       </c>
       <c r="W4" t="n">
-        <v>1.511209112524902</v>
+        <v>1.91088270706238</v>
       </c>
       <c r="X4" t="n">
-        <v>76.68987382987385</v>
+        <v>76.24160571078448</v>
       </c>
       <c r="Y4" t="n">
-        <v>22840754.17068312</v>
+        <v>17261708.98196715</v>
       </c>
       <c r="Z4" t="n">
-        <v>82.30599687252318</v>
+        <v>80.60255604934824</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.35371900826446</v>
+        <v>24.95454545454545</v>
       </c>
       <c r="D5" t="n">
-        <v>182.4115702479339</v>
+        <v>186.5231404958678</v>
       </c>
       <c r="E5" t="n">
-        <v>1.706611570247934</v>
+        <v>1.033057851239669</v>
       </c>
       <c r="F5" t="n">
-        <v>80.69669421487603</v>
+        <v>73.27520661157024</v>
       </c>
       <c r="G5" t="n">
-        <v>34783305.78512397</v>
+        <v>4970495.867768595</v>
       </c>
       <c r="H5" t="n">
-        <v>82.44380165289257</v>
+        <v>77.02644628099173</v>
       </c>
       <c r="I5" t="n">
-        <v>24.2679797979798</v>
+        <v>25.84537037037037</v>
       </c>
       <c r="J5" t="n">
-        <v>184.8273737373738</v>
+        <v>181.1049382716049</v>
       </c>
       <c r="K5" t="n">
-        <v>1.058181818181818</v>
+        <v>1.104012345679012</v>
       </c>
       <c r="L5" t="n">
-        <v>69.6029292929293</v>
+        <v>71.420987654321</v>
       </c>
       <c r="M5" t="n">
-        <v>2971611.111111111</v>
+        <v>3818395.061728395</v>
       </c>
       <c r="N5" t="n">
-        <v>75.6130303030303</v>
+        <v>73.83302469135803</v>
       </c>
       <c r="O5" t="n">
-        <v>24.97643569099381</v>
+        <v>25.38100916661077</v>
       </c>
       <c r="P5" t="n">
-        <v>181.1455520350328</v>
+        <v>182.9325379571904</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.518862278853835</v>
+        <v>1.070648233873646</v>
       </c>
       <c r="R5" t="n">
-        <v>75.73165873956755</v>
+        <v>70.93614327382987</v>
       </c>
       <c r="S5" t="n">
-        <v>15054205.33437385</v>
+        <v>3289590.122136855</v>
       </c>
       <c r="T5" t="n">
-        <v>78.97217438954704</v>
+        <v>74.8505746849231</v>
       </c>
       <c r="U5" t="n">
-        <v>24.57062209127426</v>
+        <v>26.63090157990158</v>
       </c>
       <c r="V5" t="n">
-        <v>183.6866154377024</v>
+        <v>183.972510970511</v>
       </c>
       <c r="W5" t="n">
-        <v>1.10735480702872</v>
+        <v>1.254210604210604</v>
       </c>
       <c r="X5" t="n">
-        <v>68.22668714940454</v>
+        <v>70.177434010434</v>
       </c>
       <c r="Y5" t="n">
-        <v>2482304.699748721</v>
+        <v>2955636.781551782</v>
       </c>
       <c r="Z5" t="n">
-        <v>73.81995571658615</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26.08733488733488</v>
-      </c>
-      <c r="D6" t="n">
-        <v>183.8649572649573</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.564646464646465</v>
-      </c>
-      <c r="F6" t="n">
-        <v>76.26876456876457</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12791569.54156954</v>
-      </c>
-      <c r="H6" t="n">
-        <v>79.72144522144524</v>
-      </c>
-      <c r="I6" t="n">
-        <v>25.50826446280992</v>
-      </c>
-      <c r="J6" t="n">
-        <v>183.6123966942149</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.38099173553719</v>
-      </c>
-      <c r="L6" t="n">
-        <v>73.02231404958678</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6606611.570247934</v>
-      </c>
-      <c r="N6" t="n">
-        <v>77.30495867768595</v>
-      </c>
-      <c r="O6" t="n">
-        <v>24.9271538707328</v>
-      </c>
-      <c r="P6" t="n">
-        <v>181.7110953593789</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.554752027182179</v>
-      </c>
-      <c r="R6" t="n">
-        <v>74.57515439780876</v>
-      </c>
-      <c r="S6" t="n">
-        <v>11470984.71892936</v>
-      </c>
-      <c r="T6" t="n">
-        <v>79.31711830728737</v>
-      </c>
-      <c r="U6" t="n">
-        <v>25.76834004160091</v>
-      </c>
-      <c r="V6" t="n">
-        <v>181.9899506181127</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.306295952620063</v>
-      </c>
-      <c r="X6" t="n">
-        <v>71.69955290500747</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>4339345.599229493</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>76.63753503194215</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26.19586776859504</v>
-      </c>
-      <c r="D7" t="n">
-        <v>184.3214876033058</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.217355371900826</v>
-      </c>
-      <c r="F7" t="n">
-        <v>72.9917355371901</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5805165.289256198</v>
-      </c>
-      <c r="H7" t="n">
-        <v>77.42561983471074</v>
-      </c>
-      <c r="I7" t="n">
-        <v>25.03271349862259</v>
-      </c>
-      <c r="J7" t="n">
-        <v>184.0882690541782</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.133838383838384</v>
-      </c>
-      <c r="L7" t="n">
-        <v>72.96533516988062</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4769800.275482094</v>
-      </c>
-      <c r="N7" t="n">
-        <v>76.71430211202939</v>
-      </c>
-      <c r="O7" t="n">
-        <v>26.45422714540361</v>
-      </c>
-      <c r="P7" t="n">
-        <v>184.822021899669</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.357635599694423</v>
-      </c>
-      <c r="R7" t="n">
-        <v>70.33122103386809</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3497872.135217723</v>
-      </c>
-      <c r="T7" t="n">
-        <v>74.02554749172397</v>
-      </c>
-      <c r="U7" t="n">
-        <v>24.33478327228327</v>
-      </c>
-      <c r="V7" t="n">
-        <v>182.793851981352</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.043320105820106</v>
-      </c>
-      <c r="X7" t="n">
-        <v>70.47753404003406</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3325845.855533355</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>75.16505254005254</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>25.40635521885522</v>
-      </c>
-      <c r="D8" t="n">
-        <v>186.3254419191919</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.710016835016835</v>
-      </c>
-      <c r="F8" t="n">
-        <v>80.08501683501683</v>
-      </c>
-      <c r="G8" t="n">
-        <v>30008228.11447811</v>
-      </c>
-      <c r="H8" t="n">
-        <v>83.85921717171718</v>
-      </c>
-      <c r="I8" t="n">
-        <v>26.14792929292929</v>
-      </c>
-      <c r="J8" t="n">
-        <v>182.3437121212121</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.098838383838384</v>
-      </c>
-      <c r="L8" t="n">
-        <v>78.68949494949496</v>
-      </c>
-      <c r="M8" t="n">
-        <v>21848578.28282828</v>
-      </c>
-      <c r="N8" t="n">
-        <v>80.70656565656566</v>
-      </c>
-      <c r="O8" t="n">
-        <v>25.07164736610961</v>
-      </c>
-      <c r="P8" t="n">
-        <v>184.1152758034194</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.726009292004716</v>
-      </c>
-      <c r="R8" t="n">
-        <v>76.48525914176086</v>
-      </c>
-      <c r="S8" t="n">
-        <v>16207407.54802025</v>
-      </c>
-      <c r="T8" t="n">
-        <v>81.4602757456333</v>
-      </c>
-      <c r="U8" t="n">
-        <v>25.22914391046877</v>
-      </c>
-      <c r="V8" t="n">
-        <v>182.6380202846491</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.91088270706238</v>
-      </c>
-      <c r="X8" t="n">
-        <v>76.24160571078448</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>17261708.98196715</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>80.60255604934824</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>24.95454545454545</v>
-      </c>
-      <c r="D9" t="n">
-        <v>186.5231404958678</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.033057851239669</v>
-      </c>
-      <c r="F9" t="n">
-        <v>73.27520661157024</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4970495.867768595</v>
-      </c>
-      <c r="H9" t="n">
-        <v>77.02644628099173</v>
-      </c>
-      <c r="I9" t="n">
-        <v>25.84537037037037</v>
-      </c>
-      <c r="J9" t="n">
-        <v>181.1049382716049</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.104012345679012</v>
-      </c>
-      <c r="L9" t="n">
-        <v>71.420987654321</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3818395.061728395</v>
-      </c>
-      <c r="N9" t="n">
-        <v>73.83302469135803</v>
-      </c>
-      <c r="O9" t="n">
-        <v>25.38100916661077</v>
-      </c>
-      <c r="P9" t="n">
-        <v>182.9325379571904</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.070648233873646</v>
-      </c>
-      <c r="R9" t="n">
-        <v>70.93614327382987</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3289590.122136855</v>
-      </c>
-      <c r="T9" t="n">
-        <v>74.8505746849231</v>
-      </c>
-      <c r="U9" t="n">
-        <v>26.63090157990158</v>
-      </c>
-      <c r="V9" t="n">
-        <v>183.972510970511</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.254210604210604</v>
-      </c>
-      <c r="X9" t="n">
-        <v>70.177434010434</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2955636.781551782</v>
-      </c>
-      <c r="Z9" t="n">
         <v>72.47907518407519</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,329 +558,821 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.12491582491582</v>
+        <v>25.9375</v>
       </c>
       <c r="D2" t="n">
-        <v>183.906734006734</v>
+        <v>180.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.566245791245791</v>
+        <v>1.3125</v>
       </c>
       <c r="F2" t="n">
-        <v>76.26085858585859</v>
+        <v>72.75</v>
       </c>
       <c r="G2" t="n">
-        <v>12730260.94276094</v>
+        <v>5356250</v>
       </c>
       <c r="H2" t="n">
-        <v>79.64520202020202</v>
+        <v>75.1875</v>
       </c>
       <c r="I2" t="n">
-        <v>25.50826446280992</v>
+        <v>25.39696969696969</v>
       </c>
       <c r="J2" t="n">
-        <v>183.6123966942149</v>
+        <v>185.5969696969697</v>
       </c>
       <c r="K2" t="n">
-        <v>1.38099173553719</v>
+        <v>1.409090909090909</v>
       </c>
       <c r="L2" t="n">
-        <v>73.02231404958678</v>
+        <v>75.5060606060606</v>
       </c>
       <c r="M2" t="n">
-        <v>6606611.570247934</v>
+        <v>8751515.15151515</v>
       </c>
       <c r="N2" t="n">
-        <v>77.30495867768595</v>
+        <v>79.11515151515151</v>
       </c>
       <c r="O2" t="n">
-        <v>24.90792546522369</v>
+        <v>27.2155303030303</v>
       </c>
       <c r="P2" t="n">
-        <v>181.8185989200288</v>
+        <v>184.3468614718615</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.539577854008764</v>
+        <v>1.243290043290044</v>
       </c>
       <c r="R2" t="n">
-        <v>74.58799621166125</v>
+        <v>70.94713203463203</v>
       </c>
       <c r="S2" t="n">
-        <v>11511110.63848926</v>
+        <v>4028014.06926407</v>
       </c>
       <c r="T2" t="n">
-        <v>79.39179044692975</v>
+        <v>72.31271645021646</v>
       </c>
       <c r="U2" t="n">
-        <v>25.76834004160091</v>
+        <v>23.77</v>
       </c>
       <c r="V2" t="n">
-        <v>181.9899506181127</v>
+        <v>184.7266666666667</v>
       </c>
       <c r="W2" t="n">
-        <v>1.306295952620063</v>
+        <v>1.183333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>71.69955290500747</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>4339345.599229493</v>
+        <v>5189083.333333333</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.63753503194215</v>
+        <v>77.45666666666666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.19586776859504</v>
+        <v>23.92727272727273</v>
       </c>
       <c r="D3" t="n">
-        <v>184.3214876033058</v>
+        <v>184.8636363636364</v>
       </c>
       <c r="E3" t="n">
-        <v>1.217355371900826</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>72.9917355371901</v>
+        <v>70.56136363636364</v>
       </c>
       <c r="G3" t="n">
-        <v>5805165.289256198</v>
+        <v>3141818.181818182</v>
       </c>
       <c r="H3" t="n">
-        <v>77.42561983471074</v>
+        <v>76.1909090909091</v>
       </c>
       <c r="I3" t="n">
-        <v>25.03271349862259</v>
+        <v>23.91666666666667</v>
       </c>
       <c r="J3" t="n">
-        <v>184.0882690541782</v>
+        <v>185.7916666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>1.133838383838384</v>
+        <v>1.291666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>72.96533516988062</v>
+        <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>4769800.275482094</v>
+        <v>29854166.66666667</v>
       </c>
       <c r="N3" t="n">
-        <v>76.71430211202939</v>
+        <v>83.70833333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>26.45422714540361</v>
+        <v>23.65110342555995</v>
       </c>
       <c r="P3" t="n">
-        <v>184.822021899669</v>
+        <v>182.2576169301713</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.357635599694423</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>70.33122103386809</v>
+        <v>68.4949769433465</v>
       </c>
       <c r="S3" t="n">
-        <v>3497872.135217723</v>
+        <v>2698818.552371542</v>
       </c>
       <c r="T3" t="n">
-        <v>74.02554749172397</v>
+        <v>74.83621541501977</v>
       </c>
       <c r="U3" t="n">
-        <v>24.33478327228327</v>
+        <v>25.475</v>
       </c>
       <c r="V3" t="n">
-        <v>182.793851981352</v>
+        <v>184.2916666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>1.043320105820106</v>
+        <v>1.544444444444444</v>
       </c>
       <c r="X3" t="n">
-        <v>70.47753404003406</v>
+        <v>77.34444444444443</v>
       </c>
       <c r="Y3" t="n">
-        <v>3325845.855533355</v>
+        <v>18836805.55555555</v>
       </c>
       <c r="Z3" t="n">
-        <v>75.16505254005254</v>
+        <v>80.67222222222222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.40635521885522</v>
+        <v>24.49242424242425</v>
       </c>
       <c r="D4" t="n">
-        <v>186.3254419191919</v>
+        <v>183.4310606060606</v>
       </c>
       <c r="E4" t="n">
-        <v>1.710016835016835</v>
+        <v>1.750757575757576</v>
       </c>
       <c r="F4" t="n">
-        <v>80.08501683501683</v>
+        <v>81.13484848484848</v>
       </c>
       <c r="G4" t="n">
-        <v>30008228.11447811</v>
+        <v>40359090.90909091</v>
       </c>
       <c r="H4" t="n">
-        <v>83.85921717171718</v>
+        <v>84.89848484848484</v>
       </c>
       <c r="I4" t="n">
-        <v>26.14792929292929</v>
+        <v>25.9040404040404</v>
       </c>
       <c r="J4" t="n">
-        <v>182.3437121212121</v>
+        <v>183.8472222222222</v>
       </c>
       <c r="K4" t="n">
-        <v>2.098838383838384</v>
+        <v>1.098232323232323</v>
       </c>
       <c r="L4" t="n">
-        <v>78.68949494949496</v>
+        <v>69.91439393939393</v>
       </c>
       <c r="M4" t="n">
-        <v>21848578.28282828</v>
+        <v>2284494.94949495</v>
       </c>
       <c r="N4" t="n">
-        <v>80.70656565656566</v>
+        <v>74.04242424242425</v>
       </c>
       <c r="O4" t="n">
-        <v>25.07164736610961</v>
+        <v>23.28304093567251</v>
       </c>
       <c r="P4" t="n">
-        <v>184.1152758034194</v>
+        <v>181.9578947368421</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.726009292004716</v>
+        <v>1.492397660818713</v>
       </c>
       <c r="R4" t="n">
-        <v>76.48525914176086</v>
+        <v>78.64093567251462</v>
       </c>
       <c r="S4" t="n">
-        <v>16207407.54802025</v>
+        <v>29987017.54385965</v>
       </c>
       <c r="T4" t="n">
-        <v>81.4602757456333</v>
+        <v>83.63859649122807</v>
       </c>
       <c r="U4" t="n">
-        <v>25.22914391046877</v>
+        <v>24.17053503323526</v>
       </c>
       <c r="V4" t="n">
-        <v>182.6380202846491</v>
+        <v>183.6046638334967</v>
       </c>
       <c r="W4" t="n">
-        <v>1.91088270706238</v>
+        <v>1.013157894736842</v>
       </c>
       <c r="X4" t="n">
-        <v>76.24160571078448</v>
+        <v>66.96104391413316</v>
       </c>
       <c r="Y4" t="n">
-        <v>17261708.98196715</v>
+        <v>1707149.395227198</v>
       </c>
       <c r="Z4" t="n">
-        <v>80.60255604934824</v>
+        <v>73.34913370382478</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>24.95454545454545</v>
+        <v>26.65</v>
       </c>
       <c r="D5" t="n">
-        <v>186.5231404958678</v>
+        <v>184.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1.033057851239669</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
-        <v>73.27520661157024</v>
+        <v>73.175</v>
       </c>
       <c r="G5" t="n">
-        <v>4970495.867768595</v>
+        <v>5088125</v>
       </c>
       <c r="H5" t="n">
-        <v>77.02644628099173</v>
+        <v>77.42500000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>25.84537037037037</v>
+        <v>25.06481481481481</v>
       </c>
       <c r="J5" t="n">
-        <v>181.1049382716049</v>
+        <v>181.7638888888889</v>
       </c>
       <c r="K5" t="n">
-        <v>1.104012345679012</v>
+        <v>1.842592592592593</v>
       </c>
       <c r="L5" t="n">
-        <v>71.420987654321</v>
+        <v>77.85185185185185</v>
       </c>
       <c r="M5" t="n">
-        <v>3818395.061728395</v>
+        <v>20594907.40740741</v>
       </c>
       <c r="N5" t="n">
-        <v>73.83302469135803</v>
+        <v>80.88888888888889</v>
       </c>
       <c r="O5" t="n">
-        <v>25.38100916661077</v>
+        <v>26.74506707946337</v>
       </c>
       <c r="P5" t="n">
-        <v>182.9325379571904</v>
+        <v>184.2811867905057</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.070648233873646</v>
+        <v>1.453147574819401</v>
       </c>
       <c r="R5" t="n">
-        <v>70.93614327382987</v>
+        <v>71.17843137254901</v>
       </c>
       <c r="S5" t="n">
-        <v>3289590.122136855</v>
+        <v>4001124.097007224</v>
       </c>
       <c r="T5" t="n">
-        <v>74.8505746849231</v>
+        <v>74.14664602683179</v>
       </c>
       <c r="U5" t="n">
-        <v>26.63090157990158</v>
+        <v>24.46228070175438</v>
       </c>
       <c r="V5" t="n">
-        <v>183.972510970511</v>
+        <v>180.0631578947369</v>
       </c>
       <c r="W5" t="n">
-        <v>1.254210604210604</v>
+        <v>1.67280701754386</v>
       </c>
       <c r="X5" t="n">
-        <v>70.177434010434</v>
+        <v>76.11578947368422</v>
       </c>
       <c r="Y5" t="n">
-        <v>2955636.781551782</v>
+        <v>19728991.22807018</v>
       </c>
       <c r="Z5" t="n">
-        <v>72.47907518407519</v>
+        <v>81.34298245614035</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="D6" t="n">
+        <v>187.6333333333333</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>76.83333333333333</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14300000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.56666666666666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.58148148148148</v>
+      </c>
+      <c r="J6" t="n">
+        <v>184.9481481481481</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75.75555555555556</v>
+      </c>
+      <c r="M6" t="n">
+        <v>13270740.74074074</v>
+      </c>
+      <c r="N6" t="n">
+        <v>80.1111111111111</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25.37037037037037</v>
+      </c>
+      <c r="P6" t="n">
+        <v>186.7037037037037</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.256410256410256</v>
+      </c>
+      <c r="R6" t="n">
+        <v>74.53276353276352</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11404159.54415955</v>
+      </c>
+      <c r="T6" t="n">
+        <v>79.13960113960114</v>
+      </c>
+      <c r="U6" t="n">
+        <v>23.21683794466403</v>
+      </c>
+      <c r="V6" t="n">
+        <v>181.4338339920949</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.39897233201581</v>
+      </c>
+      <c r="X6" t="n">
+        <v>73.93125164690382</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11369884.05797101</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>80.6059815546772</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>26.52847222222222</v>
+      </c>
+      <c r="D7" t="n">
+        <v>185.9069444444444</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.327083333333333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>75.5048611111111</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11132152.77777778</v>
+      </c>
+      <c r="H7" t="n">
+        <v>77.93541666666667</v>
+      </c>
+      <c r="I7" t="n">
+        <v>23.97569444444444</v>
+      </c>
+      <c r="J7" t="n">
+        <v>182.2256944444445</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>72.00347222222223</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5494444.444444444</v>
+      </c>
+      <c r="N7" t="n">
+        <v>77.93402777777777</v>
+      </c>
+      <c r="O7" t="n">
+        <v>23.72766475011057</v>
+      </c>
+      <c r="P7" t="n">
+        <v>184.4310776942356</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.051378446115288</v>
+      </c>
+      <c r="R7" t="n">
+        <v>70.92436974789916</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6049267.470145953</v>
+      </c>
+      <c r="T7" t="n">
+        <v>76.64090372991302</v>
+      </c>
+      <c r="U7" t="n">
+        <v>22.593671679198</v>
+      </c>
+      <c r="V7" t="n">
+        <v>182.6355863617377</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>67.42599989557226</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2853063.648705096</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>75.12061403508773</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25.34090909090909</v>
+      </c>
+      <c r="D8" t="n">
+        <v>185.4318181818182</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.068181818181818</v>
+      </c>
+      <c r="F8" t="n">
+        <v>72.43181818181819</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4644886.363636363</v>
+      </c>
+      <c r="H8" t="n">
+        <v>75.88636363636364</v>
+      </c>
+      <c r="I8" t="n">
+        <v>26.66818181818181</v>
+      </c>
+      <c r="J8" t="n">
+        <v>182.0272727272727</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.654545454545454</v>
+      </c>
+      <c r="L8" t="n">
+        <v>80.5840909090909</v>
+      </c>
+      <c r="M8" t="n">
+        <v>31827727.27272727</v>
+      </c>
+      <c r="N8" t="n">
+        <v>82.05681818181819</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26.14049145299145</v>
+      </c>
+      <c r="P8" t="n">
+        <v>183.9685337810338</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.358089133089133</v>
+      </c>
+      <c r="R8" t="n">
+        <v>69.33301790801789</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2453350.122100122</v>
+      </c>
+      <c r="T8" t="n">
+        <v>73.8993080993081</v>
+      </c>
+      <c r="U8" t="n">
+        <v>25.70514705882353</v>
+      </c>
+      <c r="V8" t="n">
+        <v>182.5997549019608</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.667892156862745</v>
+      </c>
+      <c r="X8" t="n">
+        <v>76.08235294117647</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13471096.81372549</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>78.60122549019607</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25.34090909090909</v>
+      </c>
+      <c r="D9" t="n">
+        <v>183.725</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.440909090909091</v>
+      </c>
+      <c r="F9" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4821136.363636364</v>
+      </c>
+      <c r="H9" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28.79393939393939</v>
+      </c>
+      <c r="J9" t="n">
+        <v>182.4757575757576</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.563636363636364</v>
+      </c>
+      <c r="L9" t="n">
+        <v>83.65454545454544</v>
+      </c>
+      <c r="M9" t="n">
+        <v>42184848.48484849</v>
+      </c>
+      <c r="N9" t="n">
+        <v>85.14545454545454</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26.51805124223603</v>
+      </c>
+      <c r="P9" t="n">
+        <v>181.8292807735743</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.40131517033691</v>
+      </c>
+      <c r="R9" t="n">
+        <v>72.39206309994353</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4602072.157914549</v>
+      </c>
+      <c r="T9" t="n">
+        <v>75.96707956898175</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.99544778892605</v>
+      </c>
+      <c r="V9" t="n">
+        <v>183.8228353771832</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.807878112225938</v>
+      </c>
+      <c r="X9" t="n">
+        <v>79.10302861389818</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>26613048.12337421</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>82.18482905982906</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22.96597222222222</v>
+      </c>
+      <c r="D10" t="n">
+        <v>185.0263888888889</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="F10" t="n">
+        <v>69.52152777777778</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3301527.777777778</v>
+      </c>
+      <c r="H10" t="n">
+        <v>76.74791666666667</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.57727272727272</v>
+      </c>
+      <c r="J10" t="n">
+        <v>185.2090909090909</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>73.22727272727272</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4416818.181818182</v>
+      </c>
+      <c r="N10" t="n">
+        <v>76.06136363636362</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23.09787784679089</v>
+      </c>
+      <c r="P10" t="n">
+        <v>182.0580538302277</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.092013457556936</v>
+      </c>
+      <c r="R10" t="n">
+        <v>67.66668737060041</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2727383.17805383</v>
+      </c>
+      <c r="T10" t="n">
+        <v>74.77438405797102</v>
+      </c>
+      <c r="U10" t="n">
+        <v>25.53109217171717</v>
+      </c>
+      <c r="V10" t="n">
+        <v>183.9381313131313</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.051747090469916</v>
+      </c>
+      <c r="X10" t="n">
+        <v>71.45620608256478</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3530705.835529205</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>75.26765618137901</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="D11" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20210000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>81.16666666666667</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25.02430555555556</v>
+      </c>
+      <c r="J11" t="n">
+        <v>183.9548611111111</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.145833333333333</v>
+      </c>
+      <c r="L11" t="n">
+        <v>72.96527777777779</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4894791.666666667</v>
+      </c>
+      <c r="N11" t="n">
+        <v>77.12847222222223</v>
+      </c>
+      <c r="O11" t="n">
+        <v>25.06666666666667</v>
+      </c>
+      <c r="P11" t="n">
+        <v>182.0555555555556</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.419444444444444</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10823888.88888889</v>
+      </c>
+      <c r="T11" t="n">
+        <v>78.71944444444443</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.07514880952381</v>
+      </c>
+      <c r="V11" t="n">
+        <v>182.9417162698412</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.039434523809524</v>
+      </c>
+      <c r="X11" t="n">
+        <v>70.56225198412699</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3222501.240079365</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>74.87400793650794</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.9375</v>
+        <v>27.36111111111111</v>
       </c>
       <c r="D2" t="n">
-        <v>180.5</v>
+        <v>181.8333333333334</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3125</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="F2" t="n">
-        <v>72.75</v>
+        <v>73.63888888888889</v>
       </c>
       <c r="G2" t="n">
-        <v>5356250</v>
+        <v>5755555.555555556</v>
       </c>
       <c r="H2" t="n">
-        <v>75.1875</v>
+        <v>75.91666666666667</v>
       </c>
       <c r="I2" t="n">
-        <v>25.39696969696969</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="J2" t="n">
-        <v>185.5969696969697</v>
+        <v>185.2727272727273</v>
       </c>
       <c r="K2" t="n">
-        <v>1.409090909090909</v>
+        <v>1.393939393939394</v>
       </c>
       <c r="L2" t="n">
-        <v>75.5060606060606</v>
+        <v>74.93939393939394</v>
       </c>
       <c r="M2" t="n">
-        <v>8751515.15151515</v>
+        <v>8666666.666666668</v>
       </c>
       <c r="N2" t="n">
-        <v>79.11515151515151</v>
+        <v>78.87878787878789</v>
       </c>
       <c r="O2" t="n">
-        <v>27.2155303030303</v>
+        <v>26.724280129672</v>
       </c>
       <c r="P2" t="n">
-        <v>184.3468614718615</v>
+        <v>183.8461507028441</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.243290043290044</v>
+        <v>1.369885311103846</v>
       </c>
       <c r="R2" t="n">
-        <v>70.94713203463203</v>
+        <v>71.56991323417239</v>
       </c>
       <c r="S2" t="n">
-        <v>4028014.06926407</v>
+        <v>4955758.026179579</v>
       </c>
       <c r="T2" t="n">
-        <v>72.31271645021646</v>
+        <v>73.75415781301079</v>
       </c>
       <c r="U2" t="n">
-        <v>23.77</v>
+        <v>23.56640773020083</v>
       </c>
       <c r="V2" t="n">
-        <v>184.7266666666667</v>
+        <v>185.1763609953265</v>
       </c>
       <c r="W2" t="n">
-        <v>1.183333333333333</v>
+        <v>1.155456612353164</v>
       </c>
       <c r="X2" t="n">
-        <v>71.40000000000001</v>
+        <v>72.10016420361249</v>
       </c>
       <c r="Y2" t="n">
-        <v>5189083.333333333</v>
+        <v>6930055.576607301</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.45666666666666</v>
+        <v>78.4581912340533</v>
       </c>
     </row>
     <row r="3">
@@ -656,37 +656,37 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>70.56136363636364</v>
+        <v>70.74772727272727</v>
       </c>
       <c r="G3" t="n">
-        <v>3141818.181818182</v>
+        <v>3216363.636363636</v>
       </c>
       <c r="H3" t="n">
-        <v>76.1909090909091</v>
+        <v>76.56363636363636</v>
       </c>
       <c r="I3" t="n">
-        <v>23.91666666666667</v>
+        <v>23.84259259259259</v>
       </c>
       <c r="J3" t="n">
-        <v>185.7916666666667</v>
+        <v>186.0092592592593</v>
       </c>
       <c r="K3" t="n">
-        <v>1.291666666666667</v>
+        <v>1.314814814814815</v>
       </c>
       <c r="L3" t="n">
-        <v>79</v>
+        <v>78.97222222222223</v>
       </c>
       <c r="M3" t="n">
-        <v>29854166.66666667</v>
+        <v>29597222.22222222</v>
       </c>
       <c r="N3" t="n">
-        <v>83.70833333333333</v>
+        <v>83.70370370370371</v>
       </c>
       <c r="O3" t="n">
         <v>23.65110342555995</v>
       </c>
       <c r="P3" t="n">
-        <v>182.2576169301713</v>
+        <v>182.2250082345191</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -701,22 +701,22 @@
         <v>74.83621541501977</v>
       </c>
       <c r="U3" t="n">
-        <v>25.475</v>
+        <v>25.24074074074074</v>
       </c>
       <c r="V3" t="n">
-        <v>184.2916666666667</v>
+        <v>182.7314814814814</v>
       </c>
       <c r="W3" t="n">
-        <v>1.544444444444444</v>
+        <v>1.685185185185185</v>
       </c>
       <c r="X3" t="n">
-        <v>77.34444444444443</v>
+        <v>78.62962962962963</v>
       </c>
       <c r="Y3" t="n">
-        <v>18836805.55555555</v>
+        <v>24131944.44444444</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.67222222222222</v>
+        <v>81.62037037037038</v>
       </c>
     </row>
     <row r="4">
@@ -729,22 +729,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>24.49242424242425</v>
+        <v>24.51851851851852</v>
       </c>
       <c r="D4" t="n">
-        <v>183.4310606060606</v>
+        <v>183.0222222222222</v>
       </c>
       <c r="E4" t="n">
-        <v>1.750757575757576</v>
+        <v>1.762962962962963</v>
       </c>
       <c r="F4" t="n">
-        <v>81.13484848484848</v>
+        <v>80.70740740740742</v>
       </c>
       <c r="G4" t="n">
-        <v>40359090.90909091</v>
+        <v>35779259.25925926</v>
       </c>
       <c r="H4" t="n">
-        <v>84.89848484848484</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>25.9040404040404</v>
@@ -765,40 +765,40 @@
         <v>74.04242424242425</v>
       </c>
       <c r="O4" t="n">
-        <v>23.28304093567251</v>
+        <v>23.59209744503862</v>
       </c>
       <c r="P4" t="n">
-        <v>181.9578947368421</v>
+        <v>182.4797555385791</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.492397660818713</v>
+        <v>1.616840675664205</v>
       </c>
       <c r="R4" t="n">
-        <v>78.64093567251462</v>
+        <v>78.4438927085986</v>
       </c>
       <c r="S4" t="n">
-        <v>29987017.54385965</v>
+        <v>26493722.94372295</v>
       </c>
       <c r="T4" t="n">
-        <v>83.63859649122807</v>
+        <v>83.1362363127069</v>
       </c>
       <c r="U4" t="n">
-        <v>24.17053503323526</v>
+        <v>24.17711398060368</v>
       </c>
       <c r="V4" t="n">
-        <v>183.6046638334967</v>
+        <v>183.5513743598126</v>
       </c>
       <c r="W4" t="n">
-        <v>1.013157894736842</v>
+        <v>1.0125</v>
       </c>
       <c r="X4" t="n">
-        <v>66.96104391413316</v>
+        <v>66.92617549308054</v>
       </c>
       <c r="Y4" t="n">
-        <v>1707149.395227198</v>
+        <v>1696856.632069304</v>
       </c>
       <c r="Z4" t="n">
-        <v>73.34913370382478</v>
+        <v>73.30637054593004</v>
       </c>
     </row>
     <row r="5">
@@ -811,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.65</v>
+        <v>26.59090909090909</v>
       </c>
       <c r="D5" t="n">
-        <v>184.3</v>
+        <v>183.7272727272727</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>1.227272727272728</v>
       </c>
       <c r="F5" t="n">
-        <v>73.175</v>
+        <v>73.36363636363636</v>
       </c>
       <c r="G5" t="n">
-        <v>5088125</v>
+        <v>5443750</v>
       </c>
       <c r="H5" t="n">
-        <v>77.42500000000001</v>
+        <v>77.40909090909091</v>
       </c>
       <c r="I5" t="n">
-        <v>25.06481481481481</v>
+        <v>25.1</v>
       </c>
       <c r="J5" t="n">
-        <v>181.7638888888889</v>
+        <v>182.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1.842592592592593</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>77.85185185185185</v>
+        <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>20594907.40740741</v>
+        <v>21150833.33333333</v>
       </c>
       <c r="N5" t="n">
-        <v>80.88888888888889</v>
+        <v>81.13333333333333</v>
       </c>
       <c r="O5" t="n">
         <v>26.74506707946337</v>
       </c>
       <c r="P5" t="n">
-        <v>184.2811867905057</v>
+        <v>184.1422394220846</v>
       </c>
       <c r="Q5" t="n">
         <v>1.453147574819401</v>
       </c>
       <c r="R5" t="n">
-        <v>71.17843137254901</v>
+        <v>71.35243550051599</v>
       </c>
       <c r="S5" t="n">
-        <v>4001124.097007224</v>
+        <v>4677228.328173375</v>
       </c>
       <c r="T5" t="n">
-        <v>74.14664602683179</v>
+        <v>74.36047471620226</v>
       </c>
       <c r="U5" t="n">
-        <v>24.46228070175438</v>
+        <v>24.31836219336219</v>
       </c>
       <c r="V5" t="n">
-        <v>180.0631578947369</v>
+        <v>179.9677128427128</v>
       </c>
       <c r="W5" t="n">
-        <v>1.67280701754386</v>
+        <v>1.68975468975469</v>
       </c>
       <c r="X5" t="n">
-        <v>76.11578947368422</v>
+        <v>76.26388888888889</v>
       </c>
       <c r="Y5" t="n">
-        <v>19728991.22807018</v>
+        <v>19615647.54689755</v>
       </c>
       <c r="Z5" t="n">
-        <v>81.34298245614035</v>
+        <v>81.58639971139972</v>
       </c>
     </row>
     <row r="6">
@@ -896,7 +896,7 @@
         <v>25.83333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>187.6333333333333</v>
+        <v>187.7333333333333</v>
       </c>
       <c r="E6" t="n">
         <v>1.4</v>
@@ -911,58 +911,58 @@
         <v>80.56666666666666</v>
       </c>
       <c r="I6" t="n">
-        <v>25.58148148148148</v>
+        <v>25.43333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>184.9481481481481</v>
+        <v>185</v>
       </c>
       <c r="K6" t="n">
-        <v>1.407407407407407</v>
+        <v>1.4</v>
       </c>
       <c r="L6" t="n">
-        <v>75.75555555555556</v>
+        <v>75.60000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>13270740.74074074</v>
+        <v>12740000</v>
       </c>
       <c r="N6" t="n">
-        <v>80.1111111111111</v>
+        <v>80.10000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>25.37037037037037</v>
+        <v>25.29876373626373</v>
       </c>
       <c r="P6" t="n">
-        <v>186.7037037037037</v>
+        <v>186.5364010989011</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.256410256410256</v>
+        <v>1.421016483516484</v>
       </c>
       <c r="R6" t="n">
-        <v>74.53276353276352</v>
+        <v>74.95283882783883</v>
       </c>
       <c r="S6" t="n">
-        <v>11404159.54415955</v>
+        <v>11532605.31135531</v>
       </c>
       <c r="T6" t="n">
-        <v>79.13960113960114</v>
+        <v>78.87087912087912</v>
       </c>
       <c r="U6" t="n">
-        <v>23.21683794466403</v>
+        <v>23.12597547380156</v>
       </c>
       <c r="V6" t="n">
-        <v>181.4338339920949</v>
+        <v>181.9108602749907</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39897233201581</v>
+        <v>1.382571534745448</v>
       </c>
       <c r="X6" t="n">
-        <v>73.93125164690382</v>
+        <v>73.89390561129692</v>
       </c>
       <c r="Y6" t="n">
-        <v>11369884.05797101</v>
+        <v>11189641.39725009</v>
       </c>
       <c r="Z6" t="n">
-        <v>80.6059815546772</v>
+        <v>80.6631828316611</v>
       </c>
     </row>
     <row r="7">
@@ -975,76 +975,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>26.52847222222222</v>
+        <v>26.45</v>
       </c>
       <c r="D7" t="n">
-        <v>185.9069444444444</v>
+        <v>185.375</v>
       </c>
       <c r="E7" t="n">
-        <v>1.327083333333333</v>
+        <v>1.325</v>
       </c>
       <c r="F7" t="n">
-        <v>75.5048611111111</v>
+        <v>75.5</v>
       </c>
       <c r="G7" t="n">
-        <v>11132152.77777778</v>
+        <v>10977500</v>
       </c>
       <c r="H7" t="n">
-        <v>77.93541666666667</v>
+        <v>77.875</v>
       </c>
       <c r="I7" t="n">
-        <v>23.97569444444444</v>
+        <v>23.96944444444444</v>
       </c>
       <c r="J7" t="n">
-        <v>182.2256944444445</v>
+        <v>182.5472222222223</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>1.025</v>
       </c>
       <c r="L7" t="n">
-        <v>72.00347222222223</v>
+        <v>71.43611111111112</v>
       </c>
       <c r="M7" t="n">
-        <v>5494444.444444444</v>
+        <v>5074722.222222222</v>
       </c>
       <c r="N7" t="n">
-        <v>77.93402777777777</v>
+        <v>77.36666666666667</v>
       </c>
       <c r="O7" t="n">
-        <v>23.72766475011057</v>
+        <v>24.00461133069829</v>
       </c>
       <c r="P7" t="n">
-        <v>184.4310776942356</v>
+        <v>183.7020750988142</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.051378446115288</v>
+        <v>1.091544325239977</v>
       </c>
       <c r="R7" t="n">
-        <v>70.92436974789916</v>
+        <v>71.54512516469038</v>
       </c>
       <c r="S7" t="n">
-        <v>6049267.470145953</v>
+        <v>6402520.351025786</v>
       </c>
       <c r="T7" t="n">
-        <v>76.64090372991302</v>
+        <v>76.35269621682664</v>
       </c>
       <c r="U7" t="n">
-        <v>22.593671679198</v>
+        <v>22.66614452798663</v>
       </c>
       <c r="V7" t="n">
-        <v>182.6355863617377</v>
+        <v>182.9700605680869</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.0125</v>
       </c>
       <c r="X7" t="n">
-        <v>67.42599989557226</v>
+        <v>67.55596282372599</v>
       </c>
       <c r="Y7" t="n">
-        <v>2853063.648705096</v>
+        <v>2813447.68170426</v>
       </c>
       <c r="Z7" t="n">
-        <v>75.12061403508773</v>
+        <v>75.07852965747703</v>
       </c>
     </row>
     <row r="8">
@@ -1066,19 +1066,19 @@
         <v>1.068181818181818</v>
       </c>
       <c r="F8" t="n">
-        <v>72.43181818181819</v>
+        <v>72.47727272727273</v>
       </c>
       <c r="G8" t="n">
-        <v>4644886.363636363</v>
+        <v>4672159.090909091</v>
       </c>
       <c r="H8" t="n">
-        <v>75.88636363636364</v>
+        <v>75.93181818181819</v>
       </c>
       <c r="I8" t="n">
         <v>26.66818181818181</v>
       </c>
       <c r="J8" t="n">
-        <v>182.0272727272727</v>
+        <v>181.9772727272727</v>
       </c>
       <c r="K8" t="n">
         <v>1.654545454545454</v>
@@ -1102,31 +1102,31 @@
         <v>1.358089133089133</v>
       </c>
       <c r="R8" t="n">
-        <v>69.33301790801789</v>
+        <v>69.34227716727716</v>
       </c>
       <c r="S8" t="n">
-        <v>2453350.122100122</v>
+        <v>2458905.677655678</v>
       </c>
       <c r="T8" t="n">
-        <v>73.8993080993081</v>
+        <v>73.90856735856735</v>
       </c>
       <c r="U8" t="n">
-        <v>25.70514705882353</v>
+        <v>25.44295634920635</v>
       </c>
       <c r="V8" t="n">
-        <v>182.5997549019608</v>
+        <v>182.4575892857143</v>
       </c>
       <c r="W8" t="n">
-        <v>1.667892156862745</v>
+        <v>1.630208333333333</v>
       </c>
       <c r="X8" t="n">
-        <v>76.08235294117647</v>
+        <v>75.80034722222223</v>
       </c>
       <c r="Y8" t="n">
-        <v>13471096.81372549</v>
+        <v>12938684.27579365</v>
       </c>
       <c r="Z8" t="n">
-        <v>78.60122549019607</v>
+        <v>78.78918650793651</v>
       </c>
     </row>
     <row r="9">
@@ -1142,7 +1142,7 @@
         <v>25.34090909090909</v>
       </c>
       <c r="D9" t="n">
-        <v>183.725</v>
+        <v>183.9295454545455</v>
       </c>
       <c r="E9" t="n">
         <v>1.440909090909091</v>
@@ -1160,7 +1160,7 @@
         <v>28.79393939393939</v>
       </c>
       <c r="J9" t="n">
-        <v>182.4757575757576</v>
+        <v>182.1272727272727</v>
       </c>
       <c r="K9" t="n">
         <v>2.563636363636364</v>
@@ -1175,40 +1175,40 @@
         <v>85.14545454545454</v>
       </c>
       <c r="O9" t="n">
-        <v>26.51805124223603</v>
+        <v>26.33417443064182</v>
       </c>
       <c r="P9" t="n">
-        <v>181.8292807735743</v>
+        <v>181.8533255693582</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.40131517033691</v>
+        <v>1.390980848861284</v>
       </c>
       <c r="R9" t="n">
-        <v>72.39206309994353</v>
+        <v>72.14939182194618</v>
       </c>
       <c r="S9" t="n">
-        <v>4602072.157914549</v>
+        <v>4534797.166149069</v>
       </c>
       <c r="T9" t="n">
-        <v>75.96707956898175</v>
+        <v>76.00219979296067</v>
       </c>
       <c r="U9" t="n">
         <v>25.99544778892605</v>
       </c>
       <c r="V9" t="n">
-        <v>183.8228353771832</v>
+        <v>183.6713117800074</v>
       </c>
       <c r="W9" t="n">
         <v>1.807878112225938</v>
       </c>
       <c r="X9" t="n">
-        <v>79.10302861389818</v>
+        <v>79.02062430323299</v>
       </c>
       <c r="Y9" t="n">
-        <v>26613048.12337421</v>
+        <v>26407037.34671126</v>
       </c>
       <c r="Z9" t="n">
-        <v>82.18482905982906</v>
+        <v>82.10242474916389</v>
       </c>
     </row>
     <row r="10">
@@ -1224,7 +1224,7 @@
         <v>22.96597222222222</v>
       </c>
       <c r="D10" t="n">
-        <v>185.0263888888889</v>
+        <v>184.8395833333334</v>
       </c>
       <c r="E10" t="n">
         <v>1.025</v>
@@ -1242,7 +1242,7 @@
         <v>25.57727272727272</v>
       </c>
       <c r="J10" t="n">
-        <v>185.2090909090909</v>
+        <v>185.0431818181818</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1251,16 +1251,16 @@
         <v>73.22727272727272</v>
       </c>
       <c r="M10" t="n">
-        <v>4416818.181818182</v>
+        <v>4566590.909090909</v>
       </c>
       <c r="N10" t="n">
-        <v>76.06136363636362</v>
+        <v>76.39318181818182</v>
       </c>
       <c r="O10" t="n">
         <v>23.09787784679089</v>
       </c>
       <c r="P10" t="n">
-        <v>182.0580538302277</v>
+        <v>181.9251708074534</v>
       </c>
       <c r="Q10" t="n">
         <v>1.092013457556936</v>
@@ -1275,22 +1275,22 @@
         <v>74.77438405797102</v>
       </c>
       <c r="U10" t="n">
-        <v>25.53109217171717</v>
+        <v>25.00843380830593</v>
       </c>
       <c r="V10" t="n">
-        <v>183.9381313131313</v>
+        <v>183.8752321580806</v>
       </c>
       <c r="W10" t="n">
-        <v>1.051747090469916</v>
+        <v>1.047896876141761</v>
       </c>
       <c r="X10" t="n">
-        <v>71.45620608256478</v>
+        <v>71.0867700341006</v>
       </c>
       <c r="Y10" t="n">
-        <v>3530705.835529205</v>
+        <v>3516493.118986725</v>
       </c>
       <c r="Z10" t="n">
-        <v>75.26765618137901</v>
+        <v>76.1680748386311</v>
       </c>
     </row>
     <row r="11">
@@ -1303,76 +1303,896 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.33333333333333</v>
+        <v>26.24848484848485</v>
       </c>
       <c r="D11" t="n">
-        <v>182.3333333333333</v>
+        <v>182.3818181818181</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>1.584848484848485</v>
       </c>
       <c r="F11" t="n">
-        <v>78.8</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>20210000</v>
+        <v>19795151.51515152</v>
       </c>
       <c r="H11" t="n">
-        <v>81.16666666666667</v>
+        <v>81.03636363636365</v>
       </c>
       <c r="I11" t="n">
-        <v>25.02430555555556</v>
+        <v>24.90208333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>183.9548611111111</v>
+        <v>184.0770833333334</v>
       </c>
       <c r="K11" t="n">
-        <v>1.145833333333333</v>
+        <v>1.143055555555555</v>
       </c>
       <c r="L11" t="n">
-        <v>72.96527777777779</v>
+        <v>72.74375000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>4894791.666666667</v>
+        <v>4893263.888888889</v>
       </c>
       <c r="N11" t="n">
-        <v>77.12847222222223</v>
+        <v>77.42777777777778</v>
       </c>
       <c r="O11" t="n">
-        <v>25.06666666666667</v>
+        <v>24.97777777777778</v>
       </c>
       <c r="P11" t="n">
-        <v>182.0555555555556</v>
+        <v>182.0965079365079</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.419444444444444</v>
+        <v>1.401269841269841</v>
       </c>
       <c r="R11" t="n">
-        <v>74.5</v>
+        <v>74.42539682539683</v>
       </c>
       <c r="S11" t="n">
-        <v>10823888.88888889</v>
+        <v>10627079.36507937</v>
       </c>
       <c r="T11" t="n">
-        <v>78.71944444444443</v>
+        <v>78.54031746031747</v>
       </c>
       <c r="U11" t="n">
-        <v>25.07514880952381</v>
+        <v>24.58331339712919</v>
       </c>
       <c r="V11" t="n">
-        <v>182.9417162698412</v>
+        <v>183.4052731259968</v>
       </c>
       <c r="W11" t="n">
-        <v>1.039434523809524</v>
+        <v>1.034280303030303</v>
       </c>
       <c r="X11" t="n">
-        <v>70.56225198412699</v>
+        <v>70.12245813397129</v>
       </c>
       <c r="Y11" t="n">
-        <v>3222501.240079365</v>
+        <v>3163558.861642743</v>
       </c>
       <c r="Z11" t="n">
-        <v>74.87400793650794</v>
+        <v>75.4396331738437</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.34090909090909</v>
+      </c>
+      <c r="D12" t="n">
+        <v>185.4318181818182</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.068181818181818</v>
+      </c>
+      <c r="F12" t="n">
+        <v>72.47727272727273</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4672159.090909091</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75.93181818181819</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.92727272727273</v>
+      </c>
+      <c r="J12" t="n">
+        <v>184.8636363636364</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>70.74772727272727</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3216363.636363636</v>
+      </c>
+      <c r="N12" t="n">
+        <v>76.56363636363636</v>
+      </c>
+      <c r="O12" t="n">
+        <v>26.14049145299145</v>
+      </c>
+      <c r="P12" t="n">
+        <v>183.9685337810338</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.358089133089133</v>
+      </c>
+      <c r="R12" t="n">
+        <v>69.34227716727716</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2458905.677655678</v>
+      </c>
+      <c r="T12" t="n">
+        <v>73.90856735856735</v>
+      </c>
+      <c r="U12" t="n">
+        <v>23.65110342555995</v>
+      </c>
+      <c r="V12" t="n">
+        <v>182.2250082345191</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>68.4949769433465</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2698818.552371542</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>74.83621541501977</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24.90208333333333</v>
+      </c>
+      <c r="D13" t="n">
+        <v>184.0770833333334</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.143055555555555</v>
+      </c>
+      <c r="F13" t="n">
+        <v>72.74375000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4893263.888888889</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77.42777777777778</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="J13" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="L13" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10977500</v>
+      </c>
+      <c r="N13" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24.58331339712919</v>
+      </c>
+      <c r="P13" t="n">
+        <v>183.4052731259968</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.034280303030303</v>
+      </c>
+      <c r="R13" t="n">
+        <v>70.12245813397129</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3163558.861642743</v>
+      </c>
+      <c r="T13" t="n">
+        <v>75.4396331738437</v>
+      </c>
+      <c r="U13" t="n">
+        <v>24.00461133069829</v>
+      </c>
+      <c r="V13" t="n">
+        <v>183.7020750988142</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.091544325239977</v>
+      </c>
+      <c r="X13" t="n">
+        <v>71.54512516469038</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6402520.351025786</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>76.35269621682664</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>25.9040404040404</v>
+      </c>
+      <c r="D14" t="n">
+        <v>183.8472222222222</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.098232323232323</v>
+      </c>
+      <c r="F14" t="n">
+        <v>69.91439393939393</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2284494.94949495</v>
+      </c>
+      <c r="H14" t="n">
+        <v>74.04242424242425</v>
+      </c>
+      <c r="I14" t="n">
+        <v>26.59090909090909</v>
+      </c>
+      <c r="J14" t="n">
+        <v>183.7272727272727</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.227272727272728</v>
+      </c>
+      <c r="L14" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5443750</v>
+      </c>
+      <c r="N14" t="n">
+        <v>77.40909090909091</v>
+      </c>
+      <c r="O14" t="n">
+        <v>24.17711398060368</v>
+      </c>
+      <c r="P14" t="n">
+        <v>183.5513743598126</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="R14" t="n">
+        <v>66.92617549308054</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1696856.632069304</v>
+      </c>
+      <c r="T14" t="n">
+        <v>73.30637054593004</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26.74506707946337</v>
+      </c>
+      <c r="V14" t="n">
+        <v>184.1422394220846</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.453147574819401</v>
+      </c>
+      <c r="X14" t="n">
+        <v>71.35243550051599</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4677228.328173375</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>74.36047471620226</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>23.84259259259259</v>
+      </c>
+      <c r="D15" t="n">
+        <v>186.0092592592593</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.314814814814815</v>
+      </c>
+      <c r="F15" t="n">
+        <v>78.97222222222223</v>
+      </c>
+      <c r="G15" t="n">
+        <v>29597222.22222222</v>
+      </c>
+      <c r="H15" t="n">
+        <v>83.70370370370371</v>
+      </c>
+      <c r="I15" t="n">
+        <v>26.66818181818181</v>
+      </c>
+      <c r="J15" t="n">
+        <v>181.9772727272727</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.654545454545454</v>
+      </c>
+      <c r="L15" t="n">
+        <v>80.5840909090909</v>
+      </c>
+      <c r="M15" t="n">
+        <v>31827727.27272727</v>
+      </c>
+      <c r="N15" t="n">
+        <v>82.05681818181819</v>
+      </c>
+      <c r="O15" t="n">
+        <v>25.24074074074074</v>
+      </c>
+      <c r="P15" t="n">
+        <v>182.7314814814814</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.685185185185185</v>
+      </c>
+      <c r="R15" t="n">
+        <v>78.62962962962963</v>
+      </c>
+      <c r="S15" t="n">
+        <v>24131944.44444444</v>
+      </c>
+      <c r="T15" t="n">
+        <v>81.62037037037038</v>
+      </c>
+      <c r="U15" t="n">
+        <v>25.44295634920635</v>
+      </c>
+      <c r="V15" t="n">
+        <v>182.4575892857143</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.630208333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>75.80034722222223</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12938684.27579365</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>78.78918650793651</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23.96944444444444</v>
+      </c>
+      <c r="D16" t="n">
+        <v>182.5472222222223</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="F16" t="n">
+        <v>71.43611111111112</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5074722.222222222</v>
+      </c>
+      <c r="H16" t="n">
+        <v>77.36666666666667</v>
+      </c>
+      <c r="I16" t="n">
+        <v>22.96597222222222</v>
+      </c>
+      <c r="J16" t="n">
+        <v>184.8395833333334</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L16" t="n">
+        <v>69.52152777777778</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3301527.777777778</v>
+      </c>
+      <c r="N16" t="n">
+        <v>76.74791666666667</v>
+      </c>
+      <c r="O16" t="n">
+        <v>22.66614452798663</v>
+      </c>
+      <c r="P16" t="n">
+        <v>182.9700605680869</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="R16" t="n">
+        <v>67.55596282372599</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2813447.68170426</v>
+      </c>
+      <c r="T16" t="n">
+        <v>75.07852965747703</v>
+      </c>
+      <c r="U16" t="n">
+        <v>23.09787784679089</v>
+      </c>
+      <c r="V16" t="n">
+        <v>181.9251708074534</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.092013457556936</v>
+      </c>
+      <c r="X16" t="n">
+        <v>67.66668737060041</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2727383.17805383</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>74.77438405797102</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25.43333333333333</v>
+      </c>
+      <c r="D17" t="n">
+        <v>185</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>75.60000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12740000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>80.10000000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>26.24848484848485</v>
+      </c>
+      <c r="J17" t="n">
+        <v>182.3818181818181</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.584848484848485</v>
+      </c>
+      <c r="L17" t="n">
+        <v>78.66666666666667</v>
+      </c>
+      <c r="M17" t="n">
+        <v>19795151.51515152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>81.03636363636365</v>
+      </c>
+      <c r="O17" t="n">
+        <v>23.12597547380156</v>
+      </c>
+      <c r="P17" t="n">
+        <v>181.9108602749907</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.382571534745448</v>
+      </c>
+      <c r="R17" t="n">
+        <v>73.89390561129692</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11189641.39725009</v>
+      </c>
+      <c r="T17" t="n">
+        <v>80.6631828316611</v>
+      </c>
+      <c r="U17" t="n">
+        <v>24.97777777777778</v>
+      </c>
+      <c r="V17" t="n">
+        <v>182.0965079365079</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.401269841269841</v>
+      </c>
+      <c r="X17" t="n">
+        <v>74.42539682539683</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10627079.36507937</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>78.54031746031747</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25.34090909090909</v>
+      </c>
+      <c r="D18" t="n">
+        <v>183.9295454545455</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.440909090909091</v>
+      </c>
+      <c r="F18" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4821136.363636364</v>
+      </c>
+      <c r="H18" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="J18" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.393939393939394</v>
+      </c>
+      <c r="L18" t="n">
+        <v>74.93939393939394</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8666666.666666668</v>
+      </c>
+      <c r="N18" t="n">
+        <v>78.87878787878789</v>
+      </c>
+      <c r="O18" t="n">
+        <v>26.33417443064182</v>
+      </c>
+      <c r="P18" t="n">
+        <v>181.8533255693582</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.390980848861284</v>
+      </c>
+      <c r="R18" t="n">
+        <v>72.14939182194618</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4534797.166149069</v>
+      </c>
+      <c r="T18" t="n">
+        <v>76.00219979296067</v>
+      </c>
+      <c r="U18" t="n">
+        <v>23.56640773020083</v>
+      </c>
+      <c r="V18" t="n">
+        <v>185.1763609953265</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.155456612353164</v>
+      </c>
+      <c r="X18" t="n">
+        <v>72.10016420361249</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6930055.576607301</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>78.4581912340533</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>78</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21150833.33333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>81.13333333333333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>25.57727272727272</v>
+      </c>
+      <c r="J19" t="n">
+        <v>185.0431818181818</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>73.22727272727272</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4566590.909090909</v>
+      </c>
+      <c r="N19" t="n">
+        <v>76.39318181818182</v>
+      </c>
+      <c r="O19" t="n">
+        <v>24.31836219336219</v>
+      </c>
+      <c r="P19" t="n">
+        <v>179.9677128427128</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.68975468975469</v>
+      </c>
+      <c r="R19" t="n">
+        <v>76.26388888888889</v>
+      </c>
+      <c r="S19" t="n">
+        <v>19615647.54689755</v>
+      </c>
+      <c r="T19" t="n">
+        <v>81.58639971139972</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25.00843380830593</v>
+      </c>
+      <c r="V19" t="n">
+        <v>183.8752321580806</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.047896876141761</v>
+      </c>
+      <c r="X19" t="n">
+        <v>71.0867700341006</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3516493.118986725</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>76.1680748386311</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>28.79393939393939</v>
+      </c>
+      <c r="D20" t="n">
+        <v>182.1272727272727</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.563636363636364</v>
+      </c>
+      <c r="F20" t="n">
+        <v>83.65454545454544</v>
+      </c>
+      <c r="G20" t="n">
+        <v>42184848.48484849</v>
+      </c>
+      <c r="H20" t="n">
+        <v>85.14545454545454</v>
+      </c>
+      <c r="I20" t="n">
+        <v>24.51851851851852</v>
+      </c>
+      <c r="J20" t="n">
+        <v>183.0222222222222</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.762962962962963</v>
+      </c>
+      <c r="L20" t="n">
+        <v>80.70740740740742</v>
+      </c>
+      <c r="M20" t="n">
+        <v>35779259.25925926</v>
+      </c>
+      <c r="N20" t="n">
+        <v>84.39999999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25.99544778892605</v>
+      </c>
+      <c r="P20" t="n">
+        <v>183.6713117800074</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.807878112225938</v>
+      </c>
+      <c r="R20" t="n">
+        <v>79.02062430323299</v>
+      </c>
+      <c r="S20" t="n">
+        <v>26407037.34671126</v>
+      </c>
+      <c r="T20" t="n">
+        <v>82.10242474916389</v>
+      </c>
+      <c r="U20" t="n">
+        <v>23.59209744503862</v>
+      </c>
+      <c r="V20" t="n">
+        <v>182.4797555385791</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.616840675664205</v>
+      </c>
+      <c r="X20" t="n">
+        <v>78.4438927085986</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>26493722.94372295</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>83.1362363127069</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>187.7333333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>76.83333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14300000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>80.56666666666666</v>
+      </c>
+      <c r="I21" t="n">
+        <v>27.36111111111111</v>
+      </c>
+      <c r="J21" t="n">
+        <v>181.8333333333334</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="L21" t="n">
+        <v>73.63888888888889</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5755555.555555556</v>
+      </c>
+      <c r="N21" t="n">
+        <v>75.91666666666667</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25.29876373626373</v>
+      </c>
+      <c r="P21" t="n">
+        <v>186.5364010989011</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.421016483516484</v>
+      </c>
+      <c r="R21" t="n">
+        <v>74.95283882783883</v>
+      </c>
+      <c r="S21" t="n">
+        <v>11532605.31135531</v>
+      </c>
+      <c r="T21" t="n">
+        <v>78.87087912087912</v>
+      </c>
+      <c r="U21" t="n">
+        <v>26.724280129672</v>
+      </c>
+      <c r="V21" t="n">
+        <v>183.8461507028441</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.369885311103846</v>
+      </c>
+      <c r="X21" t="n">
+        <v>71.56991323417239</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4955758.026179579</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>73.75415781301079</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,575 +558,1641 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.59090909090909</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="D2" t="n">
-        <v>183.7272727272727</v>
+        <v>185.3090909090909</v>
       </c>
       <c r="E2" t="n">
-        <v>1.227272727272728</v>
+        <v>1.072727272727273</v>
       </c>
       <c r="F2" t="n">
-        <v>73.36363636363636</v>
+        <v>72.50909090909093</v>
       </c>
       <c r="G2" t="n">
-        <v>5443750</v>
+        <v>4694090.909090908</v>
       </c>
       <c r="H2" t="n">
-        <v>77.40909090909091</v>
+        <v>75.90909090909091</v>
       </c>
       <c r="I2" t="n">
-        <v>25.1</v>
+        <v>23.96</v>
       </c>
       <c r="J2" t="n">
-        <v>182.6</v>
+        <v>184.8363636363636</v>
       </c>
       <c r="K2" t="n">
-        <v>1.766666666666667</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>78</v>
+        <v>70.56181818181818</v>
       </c>
       <c r="M2" t="n">
-        <v>21150833.33333333</v>
+        <v>3156545.454545454</v>
       </c>
       <c r="N2" t="n">
-        <v>81.13333333333333</v>
+        <v>76.21454545454546</v>
       </c>
       <c r="O2" t="n">
-        <v>26.74506707946337</v>
+        <v>26.04572649572649</v>
       </c>
       <c r="P2" t="n">
-        <v>184.1422394220846</v>
+        <v>183.8637159137159</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.453147574819401</v>
+        <v>1.330915750915751</v>
       </c>
       <c r="R2" t="n">
-        <v>71.35243550051599</v>
+        <v>69.10345136345136</v>
       </c>
       <c r="S2" t="n">
-        <v>4677228.328173375</v>
+        <v>2391754.171754172</v>
       </c>
       <c r="T2" t="n">
-        <v>74.36047471620226</v>
+        <v>73.6305575905576</v>
       </c>
       <c r="U2" t="n">
-        <v>24.31836219336219</v>
+        <v>23.62676509338913</v>
       </c>
       <c r="V2" t="n">
-        <v>179.9677128427128</v>
+        <v>182.5094183523211</v>
       </c>
       <c r="W2" t="n">
-        <v>1.68975468975469</v>
+        <v>1.011764705882353</v>
       </c>
       <c r="X2" t="n">
-        <v>76.26388888888889</v>
+        <v>68.52539331938308</v>
       </c>
       <c r="Y2" t="n">
-        <v>19615647.54689755</v>
+        <v>2769937.19483841</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.58639971139972</v>
+        <v>74.72779586142758</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.83333333333333</v>
+        <v>24.76166666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7333333333333</v>
+        <v>184.0016666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4</v>
+        <v>1.114444444444444</v>
       </c>
       <c r="F3" t="n">
-        <v>76.83333333333333</v>
+        <v>72.55499999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>14300000</v>
+        <v>4724611.111111111</v>
       </c>
       <c r="H3" t="n">
-        <v>80.56666666666666</v>
+        <v>77.36222222222223</v>
       </c>
       <c r="I3" t="n">
-        <v>25.43333333333333</v>
+        <v>26.4</v>
       </c>
       <c r="J3" t="n">
-        <v>185</v>
+        <v>185.32</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="L3" t="n">
-        <v>75.60000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>12740000</v>
+        <v>10762000</v>
       </c>
       <c r="N3" t="n">
-        <v>80.10000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="O3" t="n">
-        <v>25.29876373626373</v>
+        <v>24.5211961722488</v>
       </c>
       <c r="P3" t="n">
-        <v>186.5364010989011</v>
+        <v>183.5242185007975</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.421016483516484</v>
+        <v>1.027424242424242</v>
       </c>
       <c r="R3" t="n">
-        <v>74.95283882783883</v>
+        <v>70.04342105263159</v>
       </c>
       <c r="S3" t="n">
-        <v>11532605.31135531</v>
+        <v>3126983.452950558</v>
       </c>
       <c r="T3" t="n">
-        <v>78.87087912087912</v>
+        <v>75.56988835725677</v>
       </c>
       <c r="U3" t="n">
-        <v>23.12597547380156</v>
+        <v>24.09968906455863</v>
       </c>
       <c r="V3" t="n">
-        <v>181.9108602749907</v>
+        <v>184.0256600790514</v>
       </c>
       <c r="W3" t="n">
-        <v>1.382571534745448</v>
+        <v>1.121235460191982</v>
       </c>
       <c r="X3" t="n">
-        <v>73.89390561129692</v>
+        <v>71.66010013175232</v>
       </c>
       <c r="Y3" t="n">
-        <v>11189641.39725009</v>
+        <v>6563816.280820629</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.6631828316611</v>
+        <v>76.53815697346133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.45</v>
+        <v>25.74323232323233</v>
       </c>
       <c r="D4" t="n">
-        <v>185.375</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="E4" t="n">
-        <v>1.325</v>
+        <v>1.098585858585859</v>
       </c>
       <c r="F4" t="n">
-        <v>75.5</v>
+        <v>70.15151515151516</v>
       </c>
       <c r="G4" t="n">
-        <v>10977500</v>
+        <v>2499595.95959596</v>
       </c>
       <c r="H4" t="n">
-        <v>77.875</v>
+        <v>74.39393939393939</v>
       </c>
       <c r="I4" t="n">
-        <v>23.96944444444444</v>
+        <v>26.52727272727272</v>
       </c>
       <c r="J4" t="n">
-        <v>182.5472222222223</v>
+        <v>183.9090909090909</v>
       </c>
       <c r="K4" t="n">
-        <v>1.025</v>
+        <v>1.236363636363637</v>
       </c>
       <c r="L4" t="n">
-        <v>71.43611111111112</v>
+        <v>73.16363636363636</v>
       </c>
       <c r="M4" t="n">
-        <v>5074722.222222222</v>
+        <v>5176818.181818182</v>
       </c>
       <c r="N4" t="n">
-        <v>77.36666666666667</v>
+        <v>77.21818181818182</v>
       </c>
       <c r="O4" t="n">
-        <v>24.00461133069829</v>
+        <v>24.07169118448294</v>
       </c>
       <c r="P4" t="n">
-        <v>183.7020750988142</v>
+        <v>182.91109948785</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.091544325239977</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
-        <v>71.54512516469038</v>
+        <v>67.00094039446442</v>
       </c>
       <c r="S4" t="n">
-        <v>6402520.351025786</v>
+        <v>1799935.305655443</v>
       </c>
       <c r="T4" t="n">
-        <v>76.35269621682664</v>
+        <v>73.64509643674404</v>
       </c>
       <c r="U4" t="n">
-        <v>22.66614452798663</v>
+        <v>26.51827588579291</v>
       </c>
       <c r="V4" t="n">
-        <v>182.9700605680869</v>
+        <v>184.1915693154455</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0125</v>
+        <v>1.45140694874441</v>
       </c>
       <c r="X4" t="n">
-        <v>67.55596282372599</v>
+        <v>71.2819484004128</v>
       </c>
       <c r="Y4" t="n">
-        <v>2813447.68170426</v>
+        <v>4824838.218094255</v>
       </c>
       <c r="Z4" t="n">
-        <v>75.07852965747703</v>
+        <v>74.49949088407291</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.34090909090909</v>
+        <v>24.1875</v>
       </c>
       <c r="D5" t="n">
-        <v>185.4318181818182</v>
+        <v>185.6180555555556</v>
       </c>
       <c r="E5" t="n">
-        <v>1.068181818181818</v>
+        <v>1.402777777777778</v>
       </c>
       <c r="F5" t="n">
-        <v>72.47727272727273</v>
+        <v>79.50694444444446</v>
       </c>
       <c r="G5" t="n">
-        <v>4672159.090909091</v>
+        <v>31031250</v>
       </c>
       <c r="H5" t="n">
-        <v>75.93181818181819</v>
+        <v>83.80555555555556</v>
       </c>
       <c r="I5" t="n">
-        <v>26.66818181818181</v>
+        <v>26.80727272727272</v>
       </c>
       <c r="J5" t="n">
-        <v>181.9772727272727</v>
+        <v>182.3454545454545</v>
       </c>
       <c r="K5" t="n">
-        <v>1.654545454545454</v>
+        <v>1.705454545454545</v>
       </c>
       <c r="L5" t="n">
-        <v>80.5840909090909</v>
+        <v>80.72181818181818</v>
       </c>
       <c r="M5" t="n">
-        <v>31827727.27272727</v>
+        <v>32284000</v>
       </c>
       <c r="N5" t="n">
-        <v>82.05681818181819</v>
+        <v>82.13636363636364</v>
       </c>
       <c r="O5" t="n">
-        <v>26.14049145299145</v>
+        <v>24.86805555555556</v>
       </c>
       <c r="P5" t="n">
-        <v>183.9685337810338</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.358089133089133</v>
+        <v>1.670138888888889</v>
       </c>
       <c r="R5" t="n">
-        <v>69.34227716727716</v>
+        <v>78.22222222222223</v>
       </c>
       <c r="S5" t="n">
-        <v>2458905.677655678</v>
+        <v>22821614.58333333</v>
       </c>
       <c r="T5" t="n">
-        <v>73.90856735856735</v>
+        <v>81.62152777777779</v>
       </c>
       <c r="U5" t="n">
-        <v>25.44295634920635</v>
+        <v>25.37936507936508</v>
       </c>
       <c r="V5" t="n">
-        <v>182.4575892857143</v>
+        <v>182.3244047619048</v>
       </c>
       <c r="W5" t="n">
-        <v>1.630208333333333</v>
+        <v>1.629166666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>75.80034722222223</v>
+        <v>75.98194444444444</v>
       </c>
       <c r="Y5" t="n">
-        <v>12938684.27579365</v>
+        <v>13752822.42063492</v>
       </c>
       <c r="Z5" t="n">
-        <v>78.78918650793651</v>
+        <v>78.94801587301588</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.34090909090909</v>
+        <v>24.10055555555556</v>
       </c>
       <c r="D6" t="n">
-        <v>183.9295454545455</v>
+        <v>183.1127777777778</v>
       </c>
       <c r="E6" t="n">
-        <v>1.440909090909091</v>
+        <v>1.045</v>
       </c>
       <c r="F6" t="n">
-        <v>72.15000000000001</v>
+        <v>71.4238888888889</v>
       </c>
       <c r="G6" t="n">
-        <v>4821136.363636364</v>
+        <v>5105402.777777778</v>
       </c>
       <c r="H6" t="n">
-        <v>76.875</v>
+        <v>77.21833333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>28.79393939393939</v>
+        <v>22.91277777777777</v>
       </c>
       <c r="J6" t="n">
-        <v>182.1272727272727</v>
+        <v>184.7916666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>2.563636363636364</v>
+        <v>1.02</v>
       </c>
       <c r="L6" t="n">
-        <v>83.65454545454544</v>
+        <v>69.63722222222222</v>
       </c>
       <c r="M6" t="n">
-        <v>42184848.48484849</v>
+        <v>3416222.222222222</v>
       </c>
       <c r="N6" t="n">
-        <v>85.14545454545454</v>
+        <v>77.07833333333333</v>
       </c>
       <c r="O6" t="n">
-        <v>26.33417443064182</v>
+        <v>22.88028404344194</v>
       </c>
       <c r="P6" t="n">
-        <v>181.8533255693582</v>
+        <v>183.3234168755221</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.390980848861284</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>72.14939182194618</v>
+        <v>67.6447702589808</v>
       </c>
       <c r="S6" t="n">
-        <v>4534797.166149069</v>
+        <v>2711284.461152882</v>
       </c>
       <c r="T6" t="n">
-        <v>76.00219979296067</v>
+        <v>74.75756056808689</v>
       </c>
       <c r="U6" t="n">
-        <v>25.99544778892605</v>
+        <v>23.08739318652362</v>
       </c>
       <c r="V6" t="n">
-        <v>183.6713117800074</v>
+        <v>182.0855911914173</v>
       </c>
       <c r="W6" t="n">
-        <v>1.807878112225938</v>
+        <v>1.073610766045549</v>
       </c>
       <c r="X6" t="n">
-        <v>79.02062430323299</v>
+        <v>67.36971353284397</v>
       </c>
       <c r="Y6" t="n">
-        <v>26407037.34671126</v>
+        <v>2668861.087897609</v>
       </c>
       <c r="Z6" t="n">
-        <v>82.10242474916389</v>
+        <v>74.51950724637682</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>22.96597222222222</v>
+        <v>25.49166666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>184.8395833333334</v>
+        <v>184.3611111111111</v>
       </c>
       <c r="E7" t="n">
-        <v>1.025</v>
+        <v>1.494444444444444</v>
       </c>
       <c r="F7" t="n">
-        <v>69.52152777777778</v>
+        <v>75.89444444444445</v>
       </c>
       <c r="G7" t="n">
-        <v>3301527.777777778</v>
+        <v>12907777.77777778</v>
       </c>
       <c r="H7" t="n">
-        <v>76.74791666666667</v>
+        <v>80.10277777777779</v>
       </c>
       <c r="I7" t="n">
-        <v>25.57727272727272</v>
+        <v>25.95909090909091</v>
       </c>
       <c r="J7" t="n">
-        <v>185.0431818181818</v>
+        <v>182.15</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>1.552272727272727</v>
       </c>
       <c r="L7" t="n">
-        <v>73.22727272727272</v>
+        <v>78.45454545454545</v>
       </c>
       <c r="M7" t="n">
-        <v>4566590.909090909</v>
+        <v>19748636.36363637</v>
       </c>
       <c r="N7" t="n">
-        <v>76.39318181818182</v>
+        <v>81.02727272727273</v>
       </c>
       <c r="O7" t="n">
-        <v>23.09787784679089</v>
+        <v>23.11300012386969</v>
       </c>
       <c r="P7" t="n">
-        <v>181.9251708074534</v>
+        <v>182.5905526136504</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.092013457556936</v>
+        <v>1.36100272513316</v>
       </c>
       <c r="R7" t="n">
-        <v>67.66668737060041</v>
+        <v>73.80931809736157</v>
       </c>
       <c r="S7" t="n">
-        <v>2727383.17805383</v>
+        <v>10753573.64053016</v>
       </c>
       <c r="T7" t="n">
-        <v>74.77438405797102</v>
+        <v>80.55294267930138</v>
       </c>
       <c r="U7" t="n">
-        <v>25.00843380830593</v>
+        <v>25.09333333333333</v>
       </c>
       <c r="V7" t="n">
-        <v>183.8752321580806</v>
+        <v>182.232380952381</v>
       </c>
       <c r="W7" t="n">
-        <v>1.047896876141761</v>
+        <v>1.430952380952381</v>
       </c>
       <c r="X7" t="n">
-        <v>71.0867700341006</v>
+        <v>74.43904761904763</v>
       </c>
       <c r="Y7" t="n">
-        <v>3516493.118986725</v>
+        <v>10638809.52380952</v>
       </c>
       <c r="Z7" t="n">
-        <v>76.1680748386311</v>
+        <v>78.49523809523809</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.24848484848485</v>
+        <v>25.27272727272727</v>
       </c>
       <c r="D8" t="n">
-        <v>182.3818181818181</v>
+        <v>183.9236363636364</v>
       </c>
       <c r="E8" t="n">
-        <v>1.584848484848485</v>
+        <v>1.432727272727273</v>
       </c>
       <c r="F8" t="n">
-        <v>78.66666666666667</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>19795151.51515152</v>
+        <v>4942909.090909092</v>
       </c>
       <c r="H8" t="n">
-        <v>81.03636363636365</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>24.90208333333333</v>
+        <v>25.40909090909091</v>
       </c>
       <c r="J8" t="n">
-        <v>184.0770833333334</v>
+        <v>185.6363636363636</v>
       </c>
       <c r="K8" t="n">
-        <v>1.143055555555555</v>
+        <v>1.386363636363637</v>
       </c>
       <c r="L8" t="n">
-        <v>72.74375000000001</v>
+        <v>75.34090909090909</v>
       </c>
       <c r="M8" t="n">
-        <v>4893263.888888889</v>
+        <v>9402272.727272728</v>
       </c>
       <c r="N8" t="n">
-        <v>77.42777777777778</v>
+        <v>79.04545454545455</v>
       </c>
       <c r="O8" t="n">
-        <v>24.97777777777778</v>
+        <v>26.32887800605192</v>
       </c>
       <c r="P8" t="n">
-        <v>182.0965079365079</v>
+        <v>181.8518912247173</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.401269841269841</v>
+        <v>1.374323140627488</v>
       </c>
       <c r="R8" t="n">
-        <v>74.42539682539683</v>
+        <v>72.13489807294157</v>
       </c>
       <c r="S8" t="n">
-        <v>10627079.36507937</v>
+        <v>4515914.655996177</v>
       </c>
       <c r="T8" t="n">
-        <v>78.54031746031747</v>
+        <v>75.94022137283007</v>
       </c>
       <c r="U8" t="n">
-        <v>24.58331339712919</v>
+        <v>23.29980579765063</v>
       </c>
       <c r="V8" t="n">
-        <v>183.4052731259968</v>
+        <v>184.9072707464949</v>
       </c>
       <c r="W8" t="n">
-        <v>1.034280303030303</v>
+        <v>1.141592459264873</v>
       </c>
       <c r="X8" t="n">
-        <v>70.12245813397129</v>
+        <v>72.09178981937603</v>
       </c>
       <c r="Y8" t="n">
-        <v>3163558.861642743</v>
+        <v>6709625.015788808</v>
       </c>
       <c r="Z8" t="n">
-        <v>75.4396331738437</v>
+        <v>78.82697675887331</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>182.55</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>77.825</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21598750</v>
+      </c>
+      <c r="H9" t="n">
+        <v>81.125</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.56181818181818</v>
+      </c>
+      <c r="J9" t="n">
+        <v>185.4345454545455</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>73.18181818181817</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4525272.727272728</v>
+      </c>
+      <c r="N9" t="n">
+        <v>76.41454545454545</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.72790207980425</v>
+      </c>
+      <c r="P9" t="n">
+        <v>180.4214368059476</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.669489930359495</v>
+      </c>
+      <c r="R9" t="n">
+        <v>76.65443840579709</v>
+      </c>
+      <c r="S9" t="n">
+        <v>19878311.74712968</v>
+      </c>
+      <c r="T9" t="n">
+        <v>81.38545195746283</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.07631226403605</v>
+      </c>
+      <c r="V9" t="n">
+        <v>183.7610552916819</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.047013153087322</v>
+      </c>
+      <c r="X9" t="n">
+        <v>71.07811167945438</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3452324.929971989</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>76.03011204481793</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28.45909090909091</v>
+      </c>
+      <c r="D10" t="n">
+        <v>181.9363636363636</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.468181818181818</v>
+      </c>
+      <c r="F10" t="n">
+        <v>83.19545454545454</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39809090.90909091</v>
+      </c>
+      <c r="H10" t="n">
+        <v>84.88181818181818</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24.58333333333334</v>
+      </c>
+      <c r="J10" t="n">
+        <v>183.7944444444445</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.822222222222222</v>
+      </c>
+      <c r="L10" t="n">
+        <v>80.72499999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>35737222.22222222</v>
+      </c>
+      <c r="N10" t="n">
+        <v>84.27222222222221</v>
+      </c>
+      <c r="O10" t="n">
+        <v>26.51658584169454</v>
+      </c>
+      <c r="P10" t="n">
+        <v>184.2434838350055</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.915908584169454</v>
+      </c>
+      <c r="R10" t="n">
+        <v>79.10546822742475</v>
+      </c>
+      <c r="S10" t="n">
+        <v>26325278.01003344</v>
+      </c>
+      <c r="T10" t="n">
+        <v>81.88681856187291</v>
+      </c>
+      <c r="U10" t="n">
+        <v>23.44407308377897</v>
+      </c>
+      <c r="V10" t="n">
+        <v>182.6967731756734</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.582195724139458</v>
+      </c>
+      <c r="X10" t="n">
+        <v>77.94161518362286</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>25518118.29474873</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>83.12391636496496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>187.475</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F11" t="n">
+        <v>77.125</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15125000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>80.875</v>
+      </c>
+      <c r="I11" t="n">
+        <v>27.36111111111111</v>
+      </c>
+      <c r="J11" t="n">
+        <v>181.8333333333334</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="L11" t="n">
+        <v>73.63888888888889</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5755555.555555556</v>
+      </c>
+      <c r="N11" t="n">
+        <v>75.91666666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>25.57933596009254</v>
+      </c>
+      <c r="P11" t="n">
+        <v>186.5733534557548</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.460499204742626</v>
+      </c>
+      <c r="R11" t="n">
+        <v>75.01726069982649</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11554190.82562175</v>
+      </c>
+      <c r="T11" t="n">
+        <v>78.83736986697514</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26.6794241037376</v>
+      </c>
+      <c r="V11" t="n">
+        <v>183.4538436391984</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.388215941190769</v>
+      </c>
+      <c r="X11" t="n">
+        <v>71.71746904887638</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4919991.036328278</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>73.95717240425479</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.58333333333334</v>
+      </c>
+      <c r="D12" t="n">
+        <v>183.7944444444445</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.822222222222222</v>
+      </c>
+      <c r="F12" t="n">
+        <v>80.72499999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35737222.22222222</v>
+      </c>
+      <c r="H12" t="n">
+        <v>84.27222222222221</v>
+      </c>
+      <c r="I12" t="n">
+        <v>24.10055555555556</v>
+      </c>
+      <c r="J12" t="n">
+        <v>183.1127777777778</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="L12" t="n">
+        <v>71.4238888888889</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5105402.777777778</v>
+      </c>
+      <c r="N12" t="n">
+        <v>77.21833333333333</v>
+      </c>
+      <c r="O12" t="n">
+        <v>23.44407308377897</v>
+      </c>
+      <c r="P12" t="n">
+        <v>182.6967731756734</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.582195724139458</v>
+      </c>
+      <c r="R12" t="n">
+        <v>77.94161518362286</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25518118.29474873</v>
+      </c>
+      <c r="T12" t="n">
+        <v>83.12391636496496</v>
+      </c>
+      <c r="U12" t="n">
+        <v>22.88028404344194</v>
+      </c>
+      <c r="V12" t="n">
+        <v>183.3234168755221</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>67.6447702589808</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2711284.461152882</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>74.75756056808689</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>25.56181818181818</v>
+      </c>
+      <c r="D13" t="n">
+        <v>185.4345454545455</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>73.18181818181817</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4525272.727272728</v>
+      </c>
+      <c r="H13" t="n">
+        <v>76.41454545454545</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28.45909090909091</v>
+      </c>
+      <c r="J13" t="n">
+        <v>181.9363636363636</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.468181818181818</v>
+      </c>
+      <c r="L13" t="n">
+        <v>83.19545454545454</v>
+      </c>
+      <c r="M13" t="n">
+        <v>39809090.90909091</v>
+      </c>
+      <c r="N13" t="n">
+        <v>84.88181818181818</v>
+      </c>
+      <c r="O13" t="n">
+        <v>25.07631226403605</v>
+      </c>
+      <c r="P13" t="n">
+        <v>183.7610552916819</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.047013153087322</v>
+      </c>
+      <c r="R13" t="n">
+        <v>71.07811167945438</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3452324.929971989</v>
+      </c>
+      <c r="T13" t="n">
+        <v>76.03011204481793</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.51658584169454</v>
+      </c>
+      <c r="V13" t="n">
+        <v>184.2434838350055</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.915908584169454</v>
+      </c>
+      <c r="X13" t="n">
+        <v>79.10546822742475</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>26325278.01003344</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>81.88681856187291</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.52727272727272</v>
+      </c>
+      <c r="D14" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.236363636363637</v>
+      </c>
+      <c r="F14" t="n">
+        <v>73.16363636363636</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5176818.181818182</v>
+      </c>
+      <c r="H14" t="n">
+        <v>77.21818181818182</v>
+      </c>
+      <c r="I14" t="n">
+        <v>24.1875</v>
+      </c>
+      <c r="J14" t="n">
+        <v>185.6180555555556</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.402777777777778</v>
+      </c>
+      <c r="L14" t="n">
+        <v>79.50694444444446</v>
+      </c>
+      <c r="M14" t="n">
+        <v>31031250</v>
+      </c>
+      <c r="N14" t="n">
+        <v>83.80555555555556</v>
+      </c>
+      <c r="O14" t="n">
+        <v>26.51827588579291</v>
+      </c>
+      <c r="P14" t="n">
+        <v>184.1915693154455</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.45140694874441</v>
+      </c>
+      <c r="R14" t="n">
+        <v>71.2819484004128</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4824838.218094255</v>
+      </c>
+      <c r="T14" t="n">
+        <v>74.49949088407291</v>
+      </c>
+      <c r="U14" t="n">
+        <v>24.86805555555556</v>
+      </c>
+      <c r="V14" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.670138888888889</v>
+      </c>
+      <c r="X14" t="n">
+        <v>78.22222222222223</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>22821614.58333333</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>81.62152777777779</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.40909090909091</v>
+      </c>
+      <c r="D15" t="n">
+        <v>185.6363636363636</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.386363636363637</v>
+      </c>
+      <c r="F15" t="n">
+        <v>75.34090909090909</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9402272.727272728</v>
+      </c>
+      <c r="H15" t="n">
+        <v>79.04545454545455</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>187.475</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="L15" t="n">
+        <v>77.125</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15125000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>80.875</v>
+      </c>
+      <c r="O15" t="n">
+        <v>23.29980579765063</v>
+      </c>
+      <c r="P15" t="n">
+        <v>184.9072707464949</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.141592459264873</v>
+      </c>
+      <c r="R15" t="n">
+        <v>72.09178981937603</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6709625.015788808</v>
+      </c>
+      <c r="T15" t="n">
+        <v>78.82697675887331</v>
+      </c>
+      <c r="U15" t="n">
+        <v>25.57933596009254</v>
+      </c>
+      <c r="V15" t="n">
+        <v>186.5733534557548</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.460499204742626</v>
+      </c>
+      <c r="X15" t="n">
+        <v>75.01726069982649</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11554190.82562175</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>78.83736986697514</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>185.32</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F16" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10762000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>25.95909090909091</v>
+      </c>
+      <c r="J16" t="n">
+        <v>182.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.552272727272727</v>
+      </c>
+      <c r="L16" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="M16" t="n">
+        <v>19748636.36363637</v>
+      </c>
+      <c r="N16" t="n">
+        <v>81.02727272727273</v>
+      </c>
+      <c r="O16" t="n">
+        <v>24.09968906455863</v>
+      </c>
+      <c r="P16" t="n">
+        <v>184.0256600790514</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.121235460191982</v>
+      </c>
+      <c r="R16" t="n">
+        <v>71.66010013175232</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6563816.280820629</v>
+      </c>
+      <c r="T16" t="n">
+        <v>76.53815697346133</v>
+      </c>
+      <c r="U16" t="n">
+        <v>25.09333333333333</v>
+      </c>
+      <c r="V16" t="n">
+        <v>182.232380952381</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.430952380952381</v>
+      </c>
+      <c r="X16" t="n">
+        <v>74.43904761904763</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10638809.52380952</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>78.49523809523809</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>182.55</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>77.825</v>
+      </c>
+      <c r="G17" t="n">
+        <v>21598750</v>
+      </c>
+      <c r="H17" t="n">
+        <v>81.125</v>
+      </c>
+      <c r="I17" t="n">
+        <v>25.74323232323233</v>
+      </c>
+      <c r="J17" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.098585858585859</v>
+      </c>
+      <c r="L17" t="n">
+        <v>70.15151515151516</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2499595.95959596</v>
+      </c>
+      <c r="N17" t="n">
+        <v>74.39393939393939</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24.72790207980425</v>
+      </c>
+      <c r="P17" t="n">
+        <v>180.4214368059476</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.669489930359495</v>
+      </c>
+      <c r="R17" t="n">
+        <v>76.65443840579709</v>
+      </c>
+      <c r="S17" t="n">
+        <v>19878311.74712968</v>
+      </c>
+      <c r="T17" t="n">
+        <v>81.38545195746283</v>
+      </c>
+      <c r="U17" t="n">
+        <v>24.07169118448294</v>
+      </c>
+      <c r="V17" t="n">
+        <v>182.91109948785</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>67.00094039446442</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1799935.305655443</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>73.64509643674404</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>27.36111111111111</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181.8333333333334</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="F18" t="n">
+        <v>73.63888888888889</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5755555.555555556</v>
+      </c>
+      <c r="H18" t="n">
+        <v>75.91666666666667</v>
+      </c>
+      <c r="I18" t="n">
+        <v>24.76166666666667</v>
+      </c>
+      <c r="J18" t="n">
+        <v>184.0016666666667</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.114444444444444</v>
+      </c>
+      <c r="L18" t="n">
+        <v>72.55499999999999</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4724611.111111111</v>
+      </c>
+      <c r="N18" t="n">
+        <v>77.36222222222223</v>
+      </c>
+      <c r="O18" t="n">
+        <v>26.6794241037376</v>
+      </c>
+      <c r="P18" t="n">
+        <v>183.4538436391984</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.388215941190769</v>
+      </c>
+      <c r="R18" t="n">
+        <v>71.71746904887638</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4919991.036328278</v>
+      </c>
+      <c r="T18" t="n">
+        <v>73.95717240425479</v>
+      </c>
+      <c r="U18" t="n">
+        <v>24.5211961722488</v>
+      </c>
+      <c r="V18" t="n">
+        <v>183.5242185007975</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.027424242424242</v>
+      </c>
+      <c r="X18" t="n">
+        <v>70.04342105263159</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3126983.452950558</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>75.56988835725677</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="D19" t="n">
+        <v>184.8363636363636</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>70.56181818181818</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3156545.454545454</v>
+      </c>
+      <c r="H19" t="n">
+        <v>76.21454545454546</v>
+      </c>
+      <c r="I19" t="n">
+        <v>25.49166666666667</v>
+      </c>
+      <c r="J19" t="n">
+        <v>184.3611111111111</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.494444444444444</v>
+      </c>
+      <c r="L19" t="n">
+        <v>75.89444444444445</v>
+      </c>
+      <c r="M19" t="n">
+        <v>12907777.77777778</v>
+      </c>
+      <c r="N19" t="n">
+        <v>80.10277777777779</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23.62676509338913</v>
+      </c>
+      <c r="P19" t="n">
+        <v>182.5094183523211</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.011764705882353</v>
+      </c>
+      <c r="R19" t="n">
+        <v>68.52539331938308</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2769937.19483841</v>
+      </c>
+      <c r="T19" t="n">
+        <v>74.72779586142758</v>
+      </c>
+      <c r="U19" t="n">
+        <v>23.11300012386969</v>
+      </c>
+      <c r="V19" t="n">
+        <v>182.5905526136504</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.36100272513316</v>
+      </c>
+      <c r="X19" t="n">
+        <v>73.80931809736157</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10753573.64053016</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>80.55294267930138</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.80727272727272</v>
+      </c>
+      <c r="D20" t="n">
+        <v>182.3454545454545</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.705454545454545</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80.72181818181818</v>
+      </c>
+      <c r="G20" t="n">
+        <v>32284000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>82.13636363636364</v>
+      </c>
+      <c r="I20" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="J20" t="n">
+        <v>183.9236363636364</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.432727272727273</v>
+      </c>
+      <c r="L20" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4942909.090909092</v>
+      </c>
+      <c r="N20" t="n">
+        <v>77</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25.37936507936508</v>
+      </c>
+      <c r="P20" t="n">
+        <v>182.3244047619048</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.629166666666667</v>
+      </c>
+      <c r="R20" t="n">
+        <v>75.98194444444444</v>
+      </c>
+      <c r="S20" t="n">
+        <v>13752822.42063492</v>
+      </c>
+      <c r="T20" t="n">
+        <v>78.94801587301588</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.32887800605192</v>
+      </c>
+      <c r="V20" t="n">
+        <v>181.8518912247173</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.374323140627488</v>
+      </c>
+      <c r="X20" t="n">
+        <v>72.13489807294157</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4515914.655996177</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>75.94022137283007</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22.91277777777777</v>
+      </c>
+      <c r="D21" t="n">
+        <v>184.7916666666667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>69.63722222222222</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3416222.222222222</v>
+      </c>
+      <c r="H21" t="n">
+        <v>77.07833333333333</v>
+      </c>
+      <c r="I21" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="J21" t="n">
+        <v>185.3090909090909</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.072727272727273</v>
+      </c>
+      <c r="L21" t="n">
+        <v>72.50909090909093</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4694090.909090908</v>
+      </c>
+      <c r="N21" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="O21" t="n">
+        <v>23.08739318652362</v>
+      </c>
+      <c r="P21" t="n">
+        <v>182.0855911914173</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.073610766045549</v>
+      </c>
+      <c r="R21" t="n">
+        <v>67.36971353284397</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2668861.087897609</v>
+      </c>
+      <c r="T21" t="n">
+        <v>74.51950724637682</v>
+      </c>
+      <c r="U21" t="n">
+        <v>26.04572649572649</v>
+      </c>
+      <c r="V21" t="n">
+        <v>183.8637159137159</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.330915750915751</v>
+      </c>
+      <c r="X21" t="n">
+        <v>69.10345136345136</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2391754.171754172</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>73.6305575905576</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,687 +446,1283 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.59090909090909</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="D2" t="n">
-        <v>183.7272727272727</v>
+        <v>187.0681818181818</v>
       </c>
       <c r="E2" t="n">
-        <v>1.227272727272728</v>
+        <v>77.29545454545455</v>
       </c>
       <c r="F2" t="n">
-        <v>73.36363636363636</v>
+        <v>38250</v>
       </c>
       <c r="G2" t="n">
-        <v>5443750</v>
+        <v>27.97569444444444</v>
       </c>
       <c r="H2" t="n">
-        <v>77.40909090909091</v>
+        <v>182.5486111111111</v>
       </c>
       <c r="I2" t="n">
-        <v>25.1</v>
+        <v>74.16319444444444</v>
       </c>
       <c r="J2" t="n">
-        <v>182.6</v>
+        <v>21687.5</v>
       </c>
       <c r="K2" t="n">
-        <v>1.766666666666667</v>
+        <v>25.56285244360902</v>
       </c>
       <c r="L2" t="n">
-        <v>78</v>
+        <v>186.4813204887218</v>
       </c>
       <c r="M2" t="n">
-        <v>21150833.33333333</v>
+        <v>75.09281015037594</v>
       </c>
       <c r="N2" t="n">
-        <v>81.13333333333333</v>
+        <v>32082.7067669173</v>
       </c>
       <c r="O2" t="n">
-        <v>26.74506707946337</v>
+        <v>26.80305536568695</v>
       </c>
       <c r="P2" t="n">
-        <v>184.1422394220846</v>
+        <v>184.5339895192527</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.453147574819401</v>
+        <v>72.600674413306</v>
       </c>
       <c r="R2" t="n">
-        <v>71.35243550051599</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4677228.328173375</v>
-      </c>
-      <c r="T2" t="n">
-        <v>74.36047471620226</v>
-      </c>
-      <c r="U2" t="n">
-        <v>24.31836219336219</v>
-      </c>
-      <c r="V2" t="n">
-        <v>179.9677128427128</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.68975468975469</v>
-      </c>
-      <c r="X2" t="n">
-        <v>76.26388888888889</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>19615647.54689755</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>81.58639971139972</v>
+        <v>29754.54545454546</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.83333333333333</v>
+        <v>24.68666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7333333333333</v>
+        <v>184.1955555555556</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4</v>
+        <v>80.86</v>
       </c>
       <c r="F3" t="n">
-        <v>76.83333333333333</v>
+        <v>67737.77777777778</v>
       </c>
       <c r="G3" t="n">
-        <v>14300000</v>
+        <v>24.25046296296297</v>
       </c>
       <c r="H3" t="n">
-        <v>80.56666666666666</v>
+        <v>183.1981481481482</v>
       </c>
       <c r="I3" t="n">
-        <v>25.43333333333333</v>
+        <v>71.68657407407407</v>
       </c>
       <c r="J3" t="n">
-        <v>185</v>
+        <v>10831.48148148148</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4</v>
+        <v>23.45525846702318</v>
       </c>
       <c r="L3" t="n">
-        <v>75.60000000000001</v>
+        <v>182.7796407627609</v>
       </c>
       <c r="M3" t="n">
-        <v>12740000</v>
+        <v>77.77551436912051</v>
       </c>
       <c r="N3" t="n">
-        <v>80.10000000000001</v>
+        <v>57646.70514670515</v>
       </c>
       <c r="O3" t="n">
-        <v>25.29876373626373</v>
+        <v>22.93646858692625</v>
       </c>
       <c r="P3" t="n">
-        <v>186.5364010989011</v>
+        <v>183.0013981209061</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.421016483516484</v>
-      </c>
-      <c r="R3" t="n">
-        <v>74.95283882783883</v>
-      </c>
-      <c r="S3" t="n">
-        <v>11532605.31135531</v>
-      </c>
-      <c r="T3" t="n">
-        <v>78.87087912087912</v>
-      </c>
-      <c r="U3" t="n">
-        <v>23.12597547380156</v>
-      </c>
-      <c r="V3" t="n">
-        <v>181.9108602749907</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.382571534745448</v>
-      </c>
-      <c r="X3" t="n">
-        <v>73.89390561129692</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>11189641.39725009</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>80.6631828316611</v>
-      </c>
+        <v>67.76194623031007</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.45</v>
+        <v>25.59781144781145</v>
       </c>
       <c r="D4" t="n">
-        <v>185.375</v>
+        <v>185.7510101010101</v>
       </c>
       <c r="E4" t="n">
-        <v>1.325</v>
+        <v>73.04040404040403</v>
       </c>
       <c r="F4" t="n">
-        <v>75.5</v>
+        <v>12916.49831649832</v>
       </c>
       <c r="G4" t="n">
-        <v>10977500</v>
+        <v>28.42181818181819</v>
       </c>
       <c r="H4" t="n">
-        <v>77.875</v>
+        <v>181.9672727272727</v>
       </c>
       <c r="I4" t="n">
-        <v>23.96944444444444</v>
+        <v>83.35636363636362</v>
       </c>
       <c r="J4" t="n">
-        <v>182.5472222222223</v>
+        <v>97885.45454545456</v>
       </c>
       <c r="K4" t="n">
-        <v>1.025</v>
+        <v>24.94238143215125</v>
       </c>
       <c r="L4" t="n">
-        <v>71.43611111111112</v>
+        <v>183.5736066824622</v>
       </c>
       <c r="M4" t="n">
-        <v>5074722.222222222</v>
+        <v>70.95903246015138</v>
       </c>
       <c r="N4" t="n">
-        <v>77.36666666666667</v>
+        <v>15097.61042097999</v>
       </c>
       <c r="O4" t="n">
-        <v>24.00461133069829</v>
+        <v>26.41880849746067</v>
       </c>
       <c r="P4" t="n">
-        <v>183.7020750988142</v>
+        <v>183.8280889384368</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.091544325239977</v>
+        <v>78.79606627028366</v>
       </c>
       <c r="R4" t="n">
-        <v>71.54512516469038</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6402520.351025786</v>
-      </c>
-      <c r="T4" t="n">
-        <v>76.35269621682664</v>
-      </c>
-      <c r="U4" t="n">
-        <v>22.66614452798663</v>
-      </c>
-      <c r="V4" t="n">
-        <v>182.9700605680869</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.0125</v>
-      </c>
-      <c r="X4" t="n">
-        <v>67.55596282372599</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2813447.68170426</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>75.07852965747703</v>
+        <v>61997.76650563608</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.34090909090909</v>
+        <v>26.59090909090909</v>
       </c>
       <c r="D5" t="n">
-        <v>185.4318181818182</v>
+        <v>183.7878787878788</v>
       </c>
       <c r="E5" t="n">
-        <v>1.068181818181818</v>
+        <v>73.18181818181819</v>
       </c>
       <c r="F5" t="n">
-        <v>72.47727272727273</v>
+        <v>21696.9696969697</v>
       </c>
       <c r="G5" t="n">
-        <v>4672159.090909091</v>
+        <v>24.25</v>
       </c>
       <c r="H5" t="n">
-        <v>75.93181818181819</v>
+        <v>185.4694444444445</v>
       </c>
       <c r="I5" t="n">
-        <v>26.66818181818181</v>
+        <v>79.80555555555557</v>
       </c>
       <c r="J5" t="n">
-        <v>181.9772727272727</v>
+        <v>84227.77777777778</v>
       </c>
       <c r="K5" t="n">
-        <v>1.654545454545454</v>
+        <v>26.64907931771743</v>
       </c>
       <c r="L5" t="n">
-        <v>80.5840909090909</v>
+        <v>184.4289486325931</v>
       </c>
       <c r="M5" t="n">
-        <v>31827727.27272727</v>
+        <v>72.08972127498343</v>
       </c>
       <c r="N5" t="n">
-        <v>82.05681818181819</v>
+        <v>21153.73601131274</v>
       </c>
       <c r="O5" t="n">
-        <v>26.14049145299145</v>
+        <v>24.73730158730158</v>
       </c>
       <c r="P5" t="n">
-        <v>183.9685337810338</v>
+        <v>183.7460317460317</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.358089133089133</v>
+        <v>77.96349206349207</v>
       </c>
       <c r="R5" t="n">
-        <v>69.34227716727716</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2458905.677655678</v>
-      </c>
-      <c r="T5" t="n">
-        <v>73.90856735856735</v>
-      </c>
-      <c r="U5" t="n">
-        <v>25.44295634920635</v>
-      </c>
-      <c r="V5" t="n">
-        <v>182.4575892857143</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.630208333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>75.80034722222223</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12938684.27579365</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>78.78918650793651</v>
+        <v>69607.73809523809</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.34090909090909</v>
+        <v>25.34545454545455</v>
       </c>
       <c r="D6" t="n">
-        <v>183.9295454545455</v>
+        <v>185.5454545454546</v>
       </c>
       <c r="E6" t="n">
-        <v>1.440909090909091</v>
+        <v>74.69090909090909</v>
       </c>
       <c r="F6" t="n">
-        <v>72.15000000000001</v>
+        <v>26181.81818181818</v>
       </c>
       <c r="G6" t="n">
-        <v>4821136.363636364</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="H6" t="n">
-        <v>76.875</v>
+        <v>187.0681818181818</v>
       </c>
       <c r="I6" t="n">
-        <v>28.79393939393939</v>
+        <v>77.29545454545455</v>
       </c>
       <c r="J6" t="n">
-        <v>182.1272727272727</v>
+        <v>38250</v>
       </c>
       <c r="K6" t="n">
-        <v>2.563636363636364</v>
+        <v>23.35522925350512</v>
       </c>
       <c r="L6" t="n">
-        <v>83.65454545454544</v>
+        <v>184.9719704433498</v>
       </c>
       <c r="M6" t="n">
-        <v>42184848.48484849</v>
+        <v>72.36573954780852</v>
       </c>
       <c r="N6" t="n">
-        <v>85.14545454545454</v>
+        <v>19163.85246936971</v>
       </c>
       <c r="O6" t="n">
-        <v>26.33417443064182</v>
+        <v>25.56285244360902</v>
       </c>
       <c r="P6" t="n">
-        <v>181.8533255693582</v>
+        <v>186.4813204887218</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.390980848861284</v>
+        <v>75.09281015037594</v>
       </c>
       <c r="R6" t="n">
-        <v>72.14939182194618</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4534797.166149069</v>
-      </c>
-      <c r="T6" t="n">
-        <v>76.00219979296067</v>
-      </c>
-      <c r="U6" t="n">
-        <v>25.99544778892605</v>
-      </c>
-      <c r="V6" t="n">
-        <v>183.6713117800074</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.807878112225938</v>
-      </c>
-      <c r="X6" t="n">
-        <v>79.02062430323299</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>26407037.34671126</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>82.10242474916389</v>
+        <v>32082.7067669173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>22.96597222222222</v>
+        <v>26.35740740740741</v>
       </c>
       <c r="D7" t="n">
-        <v>184.8395833333334</v>
+        <v>185.8611111111111</v>
       </c>
       <c r="E7" t="n">
-        <v>1.025</v>
+        <v>75.37777777777778</v>
       </c>
       <c r="F7" t="n">
-        <v>69.52152777777778</v>
+        <v>32659.25925925926</v>
       </c>
       <c r="G7" t="n">
-        <v>3301527.777777778</v>
+        <v>25.89454545454546</v>
       </c>
       <c r="H7" t="n">
-        <v>76.74791666666667</v>
+        <v>182.1381818181818</v>
       </c>
       <c r="I7" t="n">
-        <v>25.57727272727272</v>
+        <v>78.09090909090909</v>
       </c>
       <c r="J7" t="n">
-        <v>185.0431818181818</v>
+        <v>47969.09090909092</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>23.77242063492064</v>
       </c>
       <c r="L7" t="n">
-        <v>73.22727272727272</v>
+        <v>184.0406746031746</v>
       </c>
       <c r="M7" t="n">
-        <v>4566590.909090909</v>
+        <v>70.92757936507935</v>
       </c>
       <c r="N7" t="n">
-        <v>76.39318181818182</v>
+        <v>22598.01587301587</v>
       </c>
       <c r="O7" t="n">
-        <v>23.09787784679089</v>
+        <v>24.94133333333333</v>
       </c>
       <c r="P7" t="n">
-        <v>181.9251708074534</v>
+        <v>182.2414603174603</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.092013457556936</v>
+        <v>74.41790476190477</v>
       </c>
       <c r="R7" t="n">
-        <v>67.66668737060041</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2727383.17805383</v>
-      </c>
-      <c r="T7" t="n">
-        <v>74.77438405797102</v>
-      </c>
-      <c r="U7" t="n">
-        <v>25.00843380830593</v>
-      </c>
-      <c r="V7" t="n">
-        <v>183.8752321580806</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.047896876141761</v>
-      </c>
-      <c r="X7" t="n">
-        <v>71.0867700341006</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3516493.118986725</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>76.1680748386311</v>
+        <v>36968.8253968254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.24848484848485</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>182.3818181818181</v>
+        <v>181.8222222222222</v>
       </c>
       <c r="E8" t="n">
-        <v>1.584848484848485</v>
+        <v>77.24444444444444</v>
       </c>
       <c r="F8" t="n">
-        <v>78.66666666666667</v>
+        <v>53800</v>
       </c>
       <c r="G8" t="n">
-        <v>19795151.51515152</v>
+        <v>27.3</v>
       </c>
       <c r="H8" t="n">
-        <v>81.03636363636365</v>
+        <v>183.4361111111111</v>
       </c>
       <c r="I8" t="n">
-        <v>24.90208333333333</v>
+        <v>71.75555555555556</v>
       </c>
       <c r="J8" t="n">
-        <v>184.0770833333334</v>
+        <v>13730.55555555556</v>
       </c>
       <c r="K8" t="n">
-        <v>1.143055555555555</v>
+        <v>24.79141257293431</v>
       </c>
       <c r="L8" t="n">
-        <v>72.74375000000001</v>
+        <v>180.3189676265763</v>
       </c>
       <c r="M8" t="n">
-        <v>4893263.888888889</v>
+        <v>76.85991436100132</v>
       </c>
       <c r="N8" t="n">
-        <v>77.42777777777778</v>
+        <v>54269.83342744212</v>
       </c>
       <c r="O8" t="n">
-        <v>24.97777777777778</v>
+        <v>24.84546568627451</v>
       </c>
       <c r="P8" t="n">
-        <v>182.0965079365079</v>
+        <v>183.5364923747277</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.401269841269841</v>
+        <v>67.81975762527233</v>
       </c>
       <c r="R8" t="n">
-        <v>74.42539682539683</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10627079.36507937</v>
-      </c>
-      <c r="T8" t="n">
-        <v>78.54031746031747</v>
-      </c>
-      <c r="U8" t="n">
-        <v>24.58331339712919</v>
-      </c>
-      <c r="V8" t="n">
-        <v>183.4052731259968</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.034280303030303</v>
-      </c>
-      <c r="X8" t="n">
-        <v>70.12245813397129</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3163558.861642743</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>75.4396331738437</v>
+        <v>7453.159041394335</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>27.97569444444444</v>
+      </c>
+      <c r="D9" t="n">
+        <v>182.5486111111111</v>
+      </c>
+      <c r="E9" t="n">
+        <v>74.16319444444444</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21687.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24.70138888888889</v>
+      </c>
+      <c r="H9" t="n">
+        <v>184.1013888888889</v>
+      </c>
+      <c r="I9" t="n">
+        <v>72.42916666666666</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16237.03703703704</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26.80305536568695</v>
+      </c>
+      <c r="L9" t="n">
+        <v>184.5339895192527</v>
+      </c>
+      <c r="M9" t="n">
+        <v>72.600674413306</v>
+      </c>
+      <c r="N9" t="n">
+        <v>29754.54545454546</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.45453307180996</v>
+      </c>
+      <c r="P9" t="n">
+        <v>183.3007563310094</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>70.03658371561184</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14127.78215786696</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>23.98333333333333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>184.9469696969697</v>
+      </c>
+      <c r="E10" t="n">
+        <v>70.40151515151514</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14339.39393939394</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25.27090909090909</v>
+      </c>
+      <c r="H10" t="n">
+        <v>182.1618181818182</v>
+      </c>
+      <c r="I10" t="n">
+        <v>75.86727272727273</v>
+      </c>
+      <c r="J10" t="n">
+        <v>43029.0909090909</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23.88706207120529</v>
+      </c>
+      <c r="L10" t="n">
+        <v>182.6613282994357</v>
+      </c>
+      <c r="M10" t="n">
+        <v>69.06919579425973</v>
+      </c>
+      <c r="N10" t="n">
+        <v>17048.67454228068</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23.26880032206119</v>
+      </c>
+      <c r="P10" t="n">
+        <v>182.5171314595228</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>73.94441150636803</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>26.87878787878788</v>
+      </c>
+      <c r="D11" t="n">
+        <v>182.8030303030303</v>
+      </c>
+      <c r="E11" t="n">
+        <v>80.74242424242424</v>
+      </c>
+      <c r="F11" t="n">
+        <v>65257.57575757577</v>
+      </c>
+      <c r="G11" t="n">
+        <v>25.48703703703704</v>
+      </c>
+      <c r="H11" t="n">
+        <v>183.9185185185185</v>
+      </c>
+      <c r="I11" t="n">
+        <v>72.74074074074075</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28892.59259259259</v>
+      </c>
+      <c r="K11" t="n">
+        <v>25.61076672295712</v>
+      </c>
+      <c r="L11" t="n">
+        <v>182.2354998123651</v>
+      </c>
+      <c r="M11" t="n">
+        <v>75.9591253088157</v>
+      </c>
+      <c r="N11" t="n">
+        <v>49591.3813053132</v>
+      </c>
+      <c r="O11" t="n">
+        <v>26.34899068322981</v>
+      </c>
+      <c r="P11" t="n">
+        <v>181.5406228433402</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>71.88135783298827</v>
+      </c>
+      <c r="R11" t="n">
+        <v>32174.8878536922</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="D12" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="E12" t="n">
+        <v>69</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2777.777777777778</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>185.2121212121212</v>
+      </c>
+      <c r="I12" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>16530.30303030303</v>
+      </c>
+      <c r="K12" t="n">
+        <v>24.53214285714285</v>
+      </c>
+      <c r="L12" t="n">
+        <v>182.9440476190476</v>
+      </c>
+      <c r="M12" t="n">
+        <v>70.9265873015873</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9424.603174603173</v>
+      </c>
+      <c r="O12" t="n">
+        <v>26.55433198380567</v>
+      </c>
+      <c r="P12" t="n">
+        <v>183.8641160593792</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>69.56318488529014</v>
+      </c>
+      <c r="R12" t="n">
+        <v>15607.27395411606</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.87878787878788</v>
+      </c>
+      <c r="D13" t="n">
+        <v>182.8030303030303</v>
+      </c>
+      <c r="E13" t="n">
+        <v>80.74242424242424</v>
+      </c>
+      <c r="F13" t="n">
+        <v>65257.57575757577</v>
+      </c>
+      <c r="G13" t="n">
+        <v>27.97569444444444</v>
+      </c>
+      <c r="H13" t="n">
+        <v>182.5486111111111</v>
+      </c>
+      <c r="I13" t="n">
+        <v>74.16319444444444</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21687.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>25.61076672295712</v>
+      </c>
+      <c r="L13" t="n">
+        <v>182.2354998123651</v>
+      </c>
+      <c r="M13" t="n">
+        <v>75.9591253088157</v>
+      </c>
+      <c r="N13" t="n">
+        <v>49591.3813053132</v>
+      </c>
+      <c r="O13" t="n">
+        <v>26.80305536568695</v>
+      </c>
+      <c r="P13" t="n">
+        <v>184.5339895192527</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>72.600674413306</v>
+      </c>
+      <c r="R13" t="n">
+        <v>29754.54545454546</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24.70138888888889</v>
+      </c>
+      <c r="D14" t="n">
+        <v>184.1013888888889</v>
+      </c>
+      <c r="E14" t="n">
+        <v>72.42916666666666</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16237.03703703704</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>183.4361111111111</v>
+      </c>
+      <c r="I14" t="n">
+        <v>71.75555555555556</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13730.55555555556</v>
+      </c>
+      <c r="K14" t="n">
+        <v>24.45453307180996</v>
+      </c>
+      <c r="L14" t="n">
+        <v>183.3007563310094</v>
+      </c>
+      <c r="M14" t="n">
+        <v>70.03658371561184</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14127.78215786696</v>
+      </c>
+      <c r="O14" t="n">
+        <v>24.84546568627451</v>
+      </c>
+      <c r="P14" t="n">
+        <v>183.5364923747277</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>67.81975762527233</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7453.159041394335</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.59781144781145</v>
+      </c>
+      <c r="D15" t="n">
+        <v>185.7510101010101</v>
+      </c>
+      <c r="E15" t="n">
+        <v>73.04040404040403</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12916.49831649832</v>
+      </c>
+      <c r="G15" t="n">
+        <v>24.25046296296297</v>
+      </c>
+      <c r="H15" t="n">
+        <v>183.1981481481482</v>
+      </c>
+      <c r="I15" t="n">
+        <v>71.68657407407407</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10831.48148148148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>24.94238143215125</v>
+      </c>
+      <c r="L15" t="n">
+        <v>183.5736066824622</v>
+      </c>
+      <c r="M15" t="n">
+        <v>70.95903246015138</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15097.61042097999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>22.93646858692625</v>
+      </c>
+      <c r="P15" t="n">
+        <v>183.0013981209061</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>67.76194623031007</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="D16" t="n">
+        <v>187.0681818181818</v>
+      </c>
+      <c r="E16" t="n">
+        <v>77.29545454545455</v>
+      </c>
+      <c r="F16" t="n">
+        <v>38250</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26.59090909090909</v>
+      </c>
+      <c r="H16" t="n">
+        <v>183.7878787878788</v>
+      </c>
+      <c r="I16" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21696.9696969697</v>
+      </c>
+      <c r="K16" t="n">
+        <v>25.56285244360902</v>
+      </c>
+      <c r="L16" t="n">
+        <v>186.4813204887218</v>
+      </c>
+      <c r="M16" t="n">
+        <v>75.09281015037594</v>
+      </c>
+      <c r="N16" t="n">
+        <v>32082.7067669173</v>
+      </c>
+      <c r="O16" t="n">
+        <v>26.64907931771743</v>
+      </c>
+      <c r="P16" t="n">
+        <v>184.4289486325931</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>72.08972127498343</v>
+      </c>
+      <c r="R16" t="n">
+        <v>21153.73601131274</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>28.42181818181819</v>
+      </c>
+      <c r="D17" t="n">
+        <v>181.9672727272727</v>
+      </c>
+      <c r="E17" t="n">
+        <v>83.35636363636362</v>
+      </c>
+      <c r="F17" t="n">
+        <v>97885.45454545456</v>
+      </c>
+      <c r="G17" t="n">
+        <v>26.35740740740741</v>
+      </c>
+      <c r="H17" t="n">
+        <v>185.8611111111111</v>
+      </c>
+      <c r="I17" t="n">
+        <v>75.37777777777778</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32659.25925925926</v>
+      </c>
+      <c r="K17" t="n">
+        <v>26.41880849746067</v>
+      </c>
+      <c r="L17" t="n">
+        <v>183.8280889384368</v>
+      </c>
+      <c r="M17" t="n">
+        <v>78.79606627028366</v>
+      </c>
+      <c r="N17" t="n">
+        <v>61997.76650563608</v>
+      </c>
+      <c r="O17" t="n">
+        <v>23.77242063492064</v>
+      </c>
+      <c r="P17" t="n">
+        <v>184.0406746031746</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>70.92757936507935</v>
+      </c>
+      <c r="R17" t="n">
+        <v>22598.01587301587</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>185.4694444444445</v>
+      </c>
+      <c r="E18" t="n">
+        <v>79.80555555555557</v>
+      </c>
+      <c r="F18" t="n">
+        <v>84227.77777777778</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>185.2121212121212</v>
+      </c>
+      <c r="I18" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>16530.30303030303</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24.73730158730158</v>
+      </c>
+      <c r="L18" t="n">
+        <v>183.7460317460317</v>
+      </c>
+      <c r="M18" t="n">
+        <v>77.96349206349207</v>
+      </c>
+      <c r="N18" t="n">
+        <v>69607.73809523809</v>
+      </c>
+      <c r="O18" t="n">
+        <v>26.55433198380567</v>
+      </c>
+      <c r="P18" t="n">
+        <v>183.8641160593792</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>69.56318488529014</v>
+      </c>
+      <c r="R18" t="n">
+        <v>15607.27395411606</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25.34545454545455</v>
+      </c>
+      <c r="D19" t="n">
+        <v>185.5454545454546</v>
+      </c>
+      <c r="E19" t="n">
+        <v>74.69090909090909</v>
+      </c>
+      <c r="F19" t="n">
+        <v>26181.81818181818</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="H19" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="I19" t="n">
+        <v>69</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2777.777777777778</v>
+      </c>
+      <c r="K19" t="n">
+        <v>23.35522925350512</v>
+      </c>
+      <c r="L19" t="n">
+        <v>184.9719704433498</v>
+      </c>
+      <c r="M19" t="n">
+        <v>72.36573954780852</v>
+      </c>
+      <c r="N19" t="n">
+        <v>19163.85246936971</v>
+      </c>
+      <c r="O19" t="n">
+        <v>24.53214285714285</v>
+      </c>
+      <c r="P19" t="n">
+        <v>182.9440476190476</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>70.9265873015873</v>
+      </c>
+      <c r="R19" t="n">
+        <v>9424.603174603173</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>25.89454545454546</v>
+      </c>
+      <c r="D20" t="n">
+        <v>182.1381818181818</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78.09090909090909</v>
+      </c>
+      <c r="F20" t="n">
+        <v>47969.09090909092</v>
+      </c>
+      <c r="G20" t="n">
+        <v>23.98333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>184.9469696969697</v>
+      </c>
+      <c r="I20" t="n">
+        <v>70.40151515151514</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14339.39393939394</v>
+      </c>
+      <c r="K20" t="n">
+        <v>24.94133333333333</v>
+      </c>
+      <c r="L20" t="n">
+        <v>182.2414603174603</v>
+      </c>
+      <c r="M20" t="n">
+        <v>74.41790476190477</v>
+      </c>
+      <c r="N20" t="n">
+        <v>36968.8253968254</v>
+      </c>
+      <c r="O20" t="n">
+        <v>23.88706207120529</v>
+      </c>
+      <c r="P20" t="n">
+        <v>182.6613282994357</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>69.06919579425973</v>
+      </c>
+      <c r="R20" t="n">
+        <v>17048.67454228068</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>25.48703703703704</v>
+      </c>
+      <c r="D21" t="n">
+        <v>183.9185185185185</v>
+      </c>
+      <c r="E21" t="n">
+        <v>72.74074074074075</v>
+      </c>
+      <c r="F21" t="n">
+        <v>28892.59259259259</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25.13333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>181.8222222222222</v>
+      </c>
+      <c r="I21" t="n">
+        <v>77.24444444444444</v>
+      </c>
+      <c r="J21" t="n">
+        <v>53800</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26.34899068322981</v>
+      </c>
+      <c r="L21" t="n">
+        <v>181.5406228433402</v>
+      </c>
+      <c r="M21" t="n">
+        <v>71.88135783298827</v>
+      </c>
+      <c r="N21" t="n">
+        <v>32174.8878536922</v>
+      </c>
+      <c r="O21" t="n">
+        <v>24.79141257293431</v>
+      </c>
+      <c r="P21" t="n">
+        <v>180.3189676265763</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>76.85991436100132</v>
+      </c>
+      <c r="R21" t="n">
+        <v>54269.83342744212</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25.27090909090909</v>
+      </c>
+      <c r="D22" t="n">
+        <v>182.1618181818182</v>
+      </c>
+      <c r="E22" t="n">
+        <v>75.86727272727273</v>
+      </c>
+      <c r="F22" t="n">
+        <v>43029.0909090909</v>
+      </c>
+      <c r="G22" t="n">
+        <v>24.68666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>184.1955555555556</v>
+      </c>
+      <c r="I22" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="J22" t="n">
+        <v>67737.77777777778</v>
+      </c>
+      <c r="K22" t="n">
+        <v>23.26880032206119</v>
+      </c>
+      <c r="L22" t="n">
+        <v>182.5171314595228</v>
+      </c>
+      <c r="M22" t="n">
+        <v>73.94441150636803</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>23.45525846702318</v>
+      </c>
+      <c r="P22" t="n">
+        <v>182.7796407627609</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>77.77551436912051</v>
+      </c>
+      <c r="R22" t="n">
+        <v>57646.70514670515</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,519 +518,347 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.68666666666667</v>
+        <v>26.22063492063492</v>
       </c>
       <c r="D2" t="n">
-        <v>184.1955555555556</v>
+        <v>185.7809523809524</v>
       </c>
       <c r="E2" t="n">
-        <v>80.86</v>
+        <v>75.0095238095238</v>
       </c>
       <c r="F2" t="n">
-        <v>67737.77777777778</v>
+        <v>31807.93650793651</v>
       </c>
       <c r="G2" t="n">
-        <v>24.10357142857143</v>
+        <v>25.89454545454546</v>
       </c>
       <c r="H2" t="n">
-        <v>182.8206349206349</v>
+        <v>182.1381818181818</v>
       </c>
       <c r="I2" t="n">
-        <v>71.33452380952382</v>
+        <v>78.09090909090909</v>
       </c>
       <c r="J2" t="n">
-        <v>10347.61904761905</v>
+        <v>47969.09090909092</v>
       </c>
       <c r="K2" t="n">
-        <v>23.45525846702318</v>
+        <v>23.83894557823129</v>
       </c>
       <c r="L2" t="n">
-        <v>182.7796407627609</v>
+        <v>184.2525510204082</v>
       </c>
       <c r="M2" t="n">
-        <v>77.77551436912051</v>
+        <v>71.15561224489795</v>
       </c>
       <c r="N2" t="n">
-        <v>57646.70514670515</v>
+        <v>23043.19727891156</v>
       </c>
       <c r="O2" t="n">
-        <v>22.95506831260345</v>
+        <v>24.94133333333333</v>
       </c>
       <c r="P2" t="n">
-        <v>183.0202460083958</v>
+        <v>182.2414603174603</v>
       </c>
       <c r="Q2" t="n">
-        <v>68.02452534026578</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>74.41790476190477</v>
+      </c>
+      <c r="R2" t="n">
+        <v>36968.8253968254</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.13740981240981</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>185.3758658008658</v>
+        <v>181.8222222222222</v>
       </c>
       <c r="E3" t="n">
-        <v>72.65963203463203</v>
+        <v>77.24444444444444</v>
       </c>
       <c r="F3" t="n">
-        <v>12517.71284271284</v>
+        <v>53800</v>
       </c>
       <c r="G3" t="n">
-        <v>28.42181818181819</v>
+        <v>27.3</v>
       </c>
       <c r="H3" t="n">
-        <v>181.9672727272727</v>
+        <v>183.4361111111111</v>
       </c>
       <c r="I3" t="n">
-        <v>83.35636363636362</v>
+        <v>71.75555555555556</v>
       </c>
       <c r="J3" t="n">
-        <v>97885.45454545456</v>
+        <v>13730.55555555556</v>
       </c>
       <c r="K3" t="n">
-        <v>24.91301867116724</v>
+        <v>24.79141257293431</v>
       </c>
       <c r="L3" t="n">
-        <v>184.1157230210578</v>
+        <v>180.3189676265763</v>
       </c>
       <c r="M3" t="n">
-        <v>70.82954661997938</v>
+        <v>76.85991436100132</v>
       </c>
       <c r="N3" t="n">
-        <v>15053.59088715578</v>
+        <v>54269.83342744212</v>
       </c>
       <c r="O3" t="n">
-        <v>26.41880849746067</v>
+        <v>24.84546568627451</v>
       </c>
       <c r="P3" t="n">
-        <v>183.8280889384368</v>
+        <v>183.5364923747277</v>
       </c>
       <c r="Q3" t="n">
-        <v>78.79606627028366</v>
+        <v>67.81975762527233</v>
       </c>
       <c r="R3" t="n">
-        <v>61997.76650563608</v>
+        <v>7453.159041394335</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.5974025974026</v>
+        <v>27.40555555555556</v>
       </c>
       <c r="D4" t="n">
-        <v>183.7662337662337</v>
+        <v>182.7138888888889</v>
       </c>
       <c r="E4" t="n">
-        <v>73.09090909090909</v>
+        <v>74.18055555555556</v>
       </c>
       <c r="F4" t="n">
-        <v>21142.85714285714</v>
+        <v>23150</v>
       </c>
       <c r="G4" t="n">
-        <v>24.25</v>
+        <v>24.70138888888889</v>
       </c>
       <c r="H4" t="n">
-        <v>185.4694444444445</v>
+        <v>184.1013888888889</v>
       </c>
       <c r="I4" t="n">
-        <v>79.80555555555557</v>
+        <v>72.42916666666666</v>
       </c>
       <c r="J4" t="n">
-        <v>84227.77777777778</v>
+        <v>16237.03703703704</v>
       </c>
       <c r="K4" t="n">
-        <v>26.09051519158388</v>
+        <v>26.81627162826853</v>
       </c>
       <c r="L4" t="n">
-        <v>184.7092851633407</v>
+        <v>184.2391089131027</v>
       </c>
       <c r="M4" t="n">
-        <v>71.76013376365039</v>
+        <v>72.53977769736285</v>
       </c>
       <c r="N4" t="n">
-        <v>20815.00353764694</v>
+        <v>25699.10873440285</v>
       </c>
       <c r="O4" t="n">
-        <v>24.73730158730158</v>
+        <v>24.45453307180996</v>
       </c>
       <c r="P4" t="n">
-        <v>183.7460317460317</v>
+        <v>183.3007563310094</v>
       </c>
       <c r="Q4" t="n">
-        <v>77.96349206349207</v>
+        <v>70.03658371561184</v>
       </c>
       <c r="R4" t="n">
-        <v>69607.73809523809</v>
+        <v>14127.78215786696</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.34545454545455</v>
+        <v>23.98333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>185.5454545454546</v>
+        <v>184.9469696969697</v>
       </c>
       <c r="E5" t="n">
-        <v>74.69090909090909</v>
+        <v>70.40151515151514</v>
       </c>
       <c r="F5" t="n">
-        <v>26181.81818181818</v>
+        <v>14339.39393939394</v>
       </c>
       <c r="G5" t="n">
-        <v>25.6</v>
+        <v>25.27090909090909</v>
       </c>
       <c r="H5" t="n">
-        <v>187.1090909090909</v>
+        <v>182.1618181818182</v>
       </c>
       <c r="I5" t="n">
-        <v>77.58181818181818</v>
+        <v>75.86727272727273</v>
       </c>
       <c r="J5" t="n">
-        <v>39400</v>
+        <v>43029.0909090909</v>
       </c>
       <c r="K5" t="n">
-        <v>23.35522925350512</v>
+        <v>23.90319606103311</v>
       </c>
       <c r="L5" t="n">
-        <v>184.9719704433498</v>
+        <v>183.0733463345813</v>
       </c>
       <c r="M5" t="n">
-        <v>72.36573954780852</v>
+        <v>69.20866133014472</v>
       </c>
       <c r="N5" t="n">
-        <v>19163.85246936971</v>
+        <v>17048.67454228068</v>
       </c>
       <c r="O5" t="n">
-        <v>25.61549934619156</v>
+        <v>23.26880032206119</v>
       </c>
       <c r="P5" t="n">
-        <v>186.0111433474992</v>
+        <v>182.5171314595228</v>
       </c>
       <c r="Q5" t="n">
-        <v>75.17859594638772</v>
-      </c>
-      <c r="R5" t="n">
-        <v>32457.46976135992</v>
-      </c>
+        <v>73.94441150636803</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.22063492063492</v>
+        <v>26.66753246753247</v>
       </c>
       <c r="D6" t="n">
-        <v>185.7809523809524</v>
+        <v>182.3597402597402</v>
       </c>
       <c r="E6" t="n">
-        <v>75.0095238095238</v>
+        <v>80.03636363636363</v>
       </c>
       <c r="F6" t="n">
-        <v>31807.93650793651</v>
+        <v>62477.92207792209</v>
       </c>
       <c r="G6" t="n">
-        <v>25.89454545454546</v>
+        <v>25.73492063492063</v>
       </c>
       <c r="H6" t="n">
-        <v>182.1381818181818</v>
+        <v>183.7555555555555</v>
       </c>
       <c r="I6" t="n">
-        <v>78.09090909090909</v>
+        <v>72.63492063492063</v>
       </c>
       <c r="J6" t="n">
-        <v>47969.09090909092</v>
+        <v>28971.42857142857</v>
       </c>
       <c r="K6" t="n">
-        <v>23.83894557823129</v>
+        <v>25.67208576253468</v>
       </c>
       <c r="L6" t="n">
-        <v>184.2525510204082</v>
+        <v>182.5389998391701</v>
       </c>
       <c r="M6" t="n">
-        <v>71.15561224489795</v>
+        <v>76.42782169327062</v>
       </c>
       <c r="N6" t="n">
-        <v>23043.19727891156</v>
+        <v>52918.3268331256</v>
       </c>
       <c r="O6" t="n">
-        <v>24.94133333333333</v>
+        <v>26.30665366833232</v>
       </c>
       <c r="P6" t="n">
-        <v>182.2414603174603</v>
+        <v>181.9821880010585</v>
       </c>
       <c r="Q6" t="n">
-        <v>74.41790476190477</v>
+        <v>71.91334430797491</v>
       </c>
       <c r="R6" t="n">
-        <v>36968.8253968254</v>
+        <v>31480.73094226249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.13333333333333</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="D7" t="n">
-        <v>181.8222222222222</v>
+        <v>185.1111111111111</v>
       </c>
       <c r="E7" t="n">
-        <v>77.24444444444444</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>53800</v>
+        <v>2777.777777777778</v>
       </c>
       <c r="G7" t="n">
-        <v>27.3</v>
+        <v>25.42857142857143</v>
       </c>
       <c r="H7" t="n">
-        <v>183.4361111111111</v>
+        <v>184.9754689754689</v>
       </c>
       <c r="I7" t="n">
-        <v>71.75555555555556</v>
+        <v>72.19047619047619</v>
       </c>
       <c r="J7" t="n">
-        <v>13730.55555555556</v>
+        <v>16597.4025974026</v>
       </c>
       <c r="K7" t="n">
-        <v>24.79141257293431</v>
+        <v>24.53214285714285</v>
       </c>
       <c r="L7" t="n">
-        <v>180.3189676265763</v>
+        <v>182.9440476190476</v>
       </c>
       <c r="M7" t="n">
-        <v>76.85991436100132</v>
+        <v>70.9265873015873</v>
       </c>
       <c r="N7" t="n">
-        <v>54269.83342744212</v>
+        <v>9424.603174603173</v>
       </c>
       <c r="O7" t="n">
-        <v>24.84546568627451</v>
+        <v>26.4068187190384</v>
       </c>
       <c r="P7" t="n">
-        <v>183.5364923747277</v>
+        <v>183.5419131440642</v>
       </c>
       <c r="Q7" t="n">
-        <v>67.81975762527233</v>
+        <v>69.68769884577664</v>
       </c>
       <c r="R7" t="n">
-        <v>7453.159041394335</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>27.40555555555556</v>
-      </c>
-      <c r="D8" t="n">
-        <v>182.7138888888889</v>
-      </c>
-      <c r="E8" t="n">
-        <v>74.18055555555556</v>
-      </c>
-      <c r="F8" t="n">
-        <v>23150</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24.70138888888889</v>
-      </c>
-      <c r="H8" t="n">
-        <v>184.1013888888889</v>
-      </c>
-      <c r="I8" t="n">
-        <v>72.42916666666666</v>
-      </c>
-      <c r="J8" t="n">
-        <v>16237.03703703704</v>
-      </c>
-      <c r="K8" t="n">
-        <v>26.81627162826853</v>
-      </c>
-      <c r="L8" t="n">
-        <v>184.2391089131027</v>
-      </c>
-      <c r="M8" t="n">
-        <v>72.53977769736285</v>
-      </c>
-      <c r="N8" t="n">
-        <v>25699.10873440285</v>
-      </c>
-      <c r="O8" t="n">
-        <v>24.45453307180996</v>
-      </c>
-      <c r="P8" t="n">
-        <v>183.3007563310094</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>70.03658371561184</v>
-      </c>
-      <c r="R8" t="n">
-        <v>14127.78215786696</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>23.98333333333333</v>
-      </c>
-      <c r="D9" t="n">
-        <v>184.9469696969697</v>
-      </c>
-      <c r="E9" t="n">
-        <v>70.40151515151514</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14339.39393939394</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.27090909090909</v>
-      </c>
-      <c r="H9" t="n">
-        <v>182.1618181818182</v>
-      </c>
-      <c r="I9" t="n">
-        <v>75.86727272727273</v>
-      </c>
-      <c r="J9" t="n">
-        <v>43029.0909090909</v>
-      </c>
-      <c r="K9" t="n">
-        <v>23.90319606103311</v>
-      </c>
-      <c r="L9" t="n">
-        <v>183.0733463345813</v>
-      </c>
-      <c r="M9" t="n">
-        <v>69.20866133014472</v>
-      </c>
-      <c r="N9" t="n">
-        <v>17048.67454228068</v>
-      </c>
-      <c r="O9" t="n">
-        <v>23.26880032206119</v>
-      </c>
-      <c r="P9" t="n">
-        <v>182.5171314595228</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>73.94441150636803</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>26.66753246753247</v>
-      </c>
-      <c r="D10" t="n">
-        <v>182.3597402597402</v>
-      </c>
-      <c r="E10" t="n">
-        <v>80.03636363636363</v>
-      </c>
-      <c r="F10" t="n">
-        <v>62477.92207792209</v>
-      </c>
-      <c r="G10" t="n">
-        <v>25.73492063492063</v>
-      </c>
-      <c r="H10" t="n">
-        <v>183.7555555555555</v>
-      </c>
-      <c r="I10" t="n">
-        <v>72.63492063492063</v>
-      </c>
-      <c r="J10" t="n">
-        <v>28971.42857142857</v>
-      </c>
-      <c r="K10" t="n">
-        <v>25.67208576253468</v>
-      </c>
-      <c r="L10" t="n">
-        <v>182.5389998391701</v>
-      </c>
-      <c r="M10" t="n">
-        <v>76.42782169327062</v>
-      </c>
-      <c r="N10" t="n">
-        <v>52918.3268331256</v>
-      </c>
-      <c r="O10" t="n">
-        <v>26.30665366833232</v>
-      </c>
-      <c r="P10" t="n">
-        <v>181.9821880010585</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>71.91334430797491</v>
-      </c>
-      <c r="R10" t="n">
-        <v>31480.73094226249</v>
+        <v>15756.54537681997</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,409 +456,1251 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.22063492063492</v>
+        <v>27.76619318181818</v>
       </c>
       <c r="D2" t="n">
-        <v>185.7809523809524</v>
+        <v>182.5727272727273</v>
       </c>
       <c r="E2" t="n">
-        <v>75.0095238095238</v>
+        <v>79.51676136363636</v>
       </c>
       <c r="F2" t="n">
-        <v>31807.93650793651</v>
+        <v>101457.6704545454</v>
       </c>
       <c r="G2" t="n">
-        <v>25.89454545454546</v>
+        <v>23779545.45454545</v>
       </c>
       <c r="H2" t="n">
-        <v>182.1381818181818</v>
+        <v>81.07670454545455</v>
       </c>
       <c r="I2" t="n">
-        <v>78.09090909090909</v>
+        <v>1.991477272727273</v>
       </c>
       <c r="J2" t="n">
-        <v>47969.09090909092</v>
+        <v>28.45833333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>23.83894557823129</v>
+        <v>180.8981481481481</v>
       </c>
       <c r="L2" t="n">
-        <v>184.2525510204082</v>
+        <v>74.20370370370371</v>
       </c>
       <c r="M2" t="n">
-        <v>71.15561224489795</v>
+        <v>23550.92592592593</v>
       </c>
       <c r="N2" t="n">
-        <v>23043.19727891156</v>
+        <v>5474652.777777777</v>
       </c>
       <c r="O2" t="n">
-        <v>24.94133333333333</v>
+        <v>76.24074074074075</v>
       </c>
       <c r="P2" t="n">
-        <v>182.2414603174603</v>
+        <v>1.462962962962963</v>
       </c>
       <c r="Q2" t="n">
-        <v>74.41790476190477</v>
+        <v>27.04278499278499</v>
       </c>
       <c r="R2" t="n">
-        <v>36968.8253968254</v>
+        <v>182.5969629329004</v>
+      </c>
+      <c r="S2" t="n">
+        <v>76.32545319264069</v>
+      </c>
+      <c r="T2" t="n">
+        <v>82879.37184343433</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14376740.78959235</v>
+      </c>
+      <c r="V2" t="n">
+        <v>78.50383748196248</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.699447601010101</v>
+      </c>
+      <c r="X2" t="n">
+        <v>28.32939958592133</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>183.044833032027</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>72.46471972188083</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>23365.4995595076</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4539269.478542405</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>73.75890166343217</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.211936157862354</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.13333333333333</v>
+        <v>25.70238095238095</v>
       </c>
       <c r="D3" t="n">
-        <v>181.8222222222222</v>
+        <v>183.9384920634921</v>
       </c>
       <c r="E3" t="n">
-        <v>77.24444444444444</v>
+        <v>73.20039682539682</v>
       </c>
       <c r="F3" t="n">
-        <v>53800</v>
+        <v>12843.25396825397</v>
       </c>
       <c r="G3" t="n">
-        <v>27.3</v>
+        <v>4930952.380952382</v>
       </c>
       <c r="H3" t="n">
-        <v>183.4361111111111</v>
+        <v>77.19444444444444</v>
       </c>
       <c r="I3" t="n">
-        <v>71.75555555555556</v>
+        <v>1.017857142857143</v>
       </c>
       <c r="J3" t="n">
-        <v>13730.55555555556</v>
+        <v>26.46594516594516</v>
       </c>
       <c r="K3" t="n">
-        <v>24.79141257293431</v>
+        <v>183.5294372294372</v>
       </c>
       <c r="L3" t="n">
-        <v>180.3189676265763</v>
+        <v>70.44805194805194</v>
       </c>
       <c r="M3" t="n">
-        <v>76.85991436100132</v>
+        <v>10141.70274170274</v>
       </c>
       <c r="N3" t="n">
-        <v>54269.83342744212</v>
+        <v>2567608.225108225</v>
       </c>
       <c r="O3" t="n">
-        <v>24.84546568627451</v>
+        <v>74.47417027417028</v>
       </c>
       <c r="P3" t="n">
-        <v>183.5364923747277</v>
+        <v>1.07041847041847</v>
       </c>
       <c r="Q3" t="n">
-        <v>67.81975762527233</v>
+        <v>25.79817563388992</v>
       </c>
       <c r="R3" t="n">
-        <v>7453.159041394335</v>
+        <v>183.3705627705628</v>
+      </c>
+      <c r="S3" t="n">
+        <v>70.5935064935065</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10669.5423623995</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3385377.241805813</v>
+      </c>
+      <c r="V3" t="n">
+        <v>75.15785405071119</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.006493506493506</v>
+      </c>
+      <c r="X3" t="n">
+        <v>25.41556531079251</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>183.6258685014814</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>68.13688206022302</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>13295.44876684465</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2065128.154236523</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>73.6813436282217</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.015037593984962</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.40555555555556</v>
+        <v>26.25688131313132</v>
       </c>
       <c r="D4" t="n">
-        <v>182.7138888888889</v>
+        <v>185.6121843434344</v>
       </c>
       <c r="E4" t="n">
-        <v>74.18055555555556</v>
+        <v>72.06253156565657</v>
       </c>
       <c r="F4" t="n">
-        <v>23150</v>
+        <v>15401.95707070707</v>
       </c>
       <c r="G4" t="n">
-        <v>24.70138888888889</v>
+        <v>3526219.223484848</v>
       </c>
       <c r="H4" t="n">
-        <v>184.1013888888889</v>
+        <v>75.3809659090909</v>
       </c>
       <c r="I4" t="n">
-        <v>72.42916666666666</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>16237.03703703704</v>
+        <v>25.29861111111111</v>
       </c>
       <c r="K4" t="n">
-        <v>26.81627162826853</v>
+        <v>182.9837962962963</v>
       </c>
       <c r="L4" t="n">
-        <v>184.2391089131027</v>
+        <v>72.82638888888889</v>
       </c>
       <c r="M4" t="n">
-        <v>72.53977769736285</v>
+        <v>11641.2037037037</v>
       </c>
       <c r="N4" t="n">
-        <v>25699.10873440285</v>
+        <v>6007638.888888888</v>
       </c>
       <c r="O4" t="n">
-        <v>24.45453307180996</v>
+        <v>77.83101851851852</v>
       </c>
       <c r="P4" t="n">
-        <v>183.3007563310094</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>70.03658371561184</v>
+        <v>26.33530342655056</v>
       </c>
       <c r="R4" t="n">
-        <v>14127.78215786696</v>
+        <v>184.3974923103212</v>
+      </c>
+      <c r="S4" t="n">
+        <v>70.61344017467087</v>
+      </c>
+      <c r="T4" t="n">
+        <v>14483.10615657226</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2647538.014224049</v>
+      </c>
+      <c r="V4" t="n">
+        <v>74.46330291204791</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>24.16154755761954</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>181.9994458419333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>68.4623285388717</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>10102.69769091847</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2930645.196400929</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>74.90740669074647</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>23.98333333333333</v>
+        <v>26.57121212121212</v>
       </c>
       <c r="D5" t="n">
-        <v>184.9469696969697</v>
+        <v>186.8166666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>70.40151515151514</v>
+        <v>77.78030303030302</v>
       </c>
       <c r="F5" t="n">
-        <v>14339.39393939394</v>
+        <v>52871.21212121212</v>
       </c>
       <c r="G5" t="n">
-        <v>25.27090909090909</v>
+        <v>17205757.57575757</v>
       </c>
       <c r="H5" t="n">
-        <v>182.1618181818182</v>
+        <v>81.31666666666666</v>
       </c>
       <c r="I5" t="n">
-        <v>75.86727272727273</v>
+        <v>1.643939393939394</v>
       </c>
       <c r="J5" t="n">
-        <v>43029.0909090909</v>
+        <v>27.34772727272727</v>
       </c>
       <c r="K5" t="n">
-        <v>23.90319606103311</v>
+        <v>184.0409090909091</v>
       </c>
       <c r="L5" t="n">
-        <v>183.0733463345813</v>
+        <v>72.96136363636364</v>
       </c>
       <c r="M5" t="n">
-        <v>69.20866133014472</v>
+        <v>31439.77272727273</v>
       </c>
       <c r="N5" t="n">
-        <v>17048.67454228068</v>
+        <v>4340284.090909091</v>
       </c>
       <c r="O5" t="n">
-        <v>23.26880032206119</v>
+        <v>75.86363636363637</v>
       </c>
       <c r="P5" t="n">
-        <v>182.5171314595228</v>
+        <v>1.114772727272727</v>
       </c>
       <c r="Q5" t="n">
-        <v>73.94441150636803</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>24.98929188722566</v>
+      </c>
+      <c r="R5" t="n">
+        <v>185.4702892990011</v>
+      </c>
+      <c r="S5" t="n">
+        <v>71.84523134294302</v>
+      </c>
+      <c r="T5" t="n">
+        <v>38914.19818920155</v>
+      </c>
+      <c r="U5" t="n">
+        <v>11071991.31454886</v>
+      </c>
+      <c r="V5" t="n">
+        <v>77.83554573034988</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.489679507313106</v>
+      </c>
+      <c r="X5" t="n">
+        <v>26.11926312539799</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>184.1890445391597</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>69.56278237478895</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>30850.8014536633</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3113364.333583083</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>73.81229576162141</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.18789189794124</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.66753246753247</v>
+        <v>29.36666666666666</v>
       </c>
       <c r="D6" t="n">
-        <v>182.3597402597402</v>
+        <v>182.480303030303</v>
       </c>
       <c r="E6" t="n">
-        <v>80.03636363636363</v>
+        <v>84.25151515151515</v>
       </c>
       <c r="F6" t="n">
-        <v>62477.92207792209</v>
+        <v>113145.4545454545</v>
       </c>
       <c r="G6" t="n">
-        <v>25.73492063492063</v>
+        <v>42198484.84848485</v>
       </c>
       <c r="H6" t="n">
-        <v>183.7555555555555</v>
+        <v>85.10606060606061</v>
       </c>
       <c r="I6" t="n">
-        <v>72.63492063492063</v>
+        <v>3.33939393939394</v>
       </c>
       <c r="J6" t="n">
-        <v>28971.42857142857</v>
+        <v>27.25902777777778</v>
       </c>
       <c r="K6" t="n">
-        <v>25.67208576253468</v>
+        <v>185.7902777777778</v>
       </c>
       <c r="L6" t="n">
-        <v>182.5389998391701</v>
+        <v>75.21319444444444</v>
       </c>
       <c r="M6" t="n">
-        <v>76.42782169327062</v>
+        <v>39669.44444444445</v>
       </c>
       <c r="N6" t="n">
-        <v>52918.3268331256</v>
+        <v>10381006.94444444</v>
       </c>
       <c r="O6" t="n">
-        <v>26.30665366833232</v>
+        <v>77.90069444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>181.9821880010585</v>
+        <v>1.195833333333333</v>
       </c>
       <c r="Q6" t="n">
-        <v>71.91334430797491</v>
+        <v>27.71460423634337</v>
       </c>
       <c r="R6" t="n">
-        <v>31480.73094226249</v>
+        <v>184.1878251579339</v>
+      </c>
+      <c r="S6" t="n">
+        <v>79.75401802303976</v>
+      </c>
+      <c r="T6" t="n">
+        <v>87085.84169453736</v>
+      </c>
+      <c r="U6" t="n">
+        <v>26746848.29059829</v>
+      </c>
+      <c r="V6" t="n">
+        <v>81.75524897807507</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.364269788182832</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24.55559221480274</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>184.9365510585905</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>69.91505895420369</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>29163.08603677024</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5222671.306215715</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>76.08152253448306</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.060768398268398</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.22222222222222</v>
+        <v>25.3</v>
       </c>
       <c r="D7" t="n">
-        <v>185.1111111111111</v>
+        <v>185.45</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>80.325</v>
       </c>
       <c r="F7" t="n">
-        <v>2777.777777777778</v>
+        <v>101650</v>
       </c>
       <c r="G7" t="n">
-        <v>25.42857142857143</v>
+        <v>34250000</v>
       </c>
       <c r="H7" t="n">
-        <v>184.9754689754689</v>
+        <v>84.3</v>
       </c>
       <c r="I7" t="n">
-        <v>72.19047619047619</v>
+        <v>2.125</v>
       </c>
       <c r="J7" t="n">
-        <v>16597.4025974026</v>
+        <v>26.26818181818182</v>
       </c>
       <c r="K7" t="n">
-        <v>24.53214285714285</v>
+        <v>184.9931818181818</v>
       </c>
       <c r="L7" t="n">
-        <v>182.9440476190476</v>
+        <v>72.1693181818182</v>
       </c>
       <c r="M7" t="n">
-        <v>70.9265873015873</v>
+        <v>17737.5</v>
       </c>
       <c r="N7" t="n">
-        <v>9424.603174603173</v>
+        <v>4074829.545454545</v>
       </c>
       <c r="O7" t="n">
-        <v>26.4068187190384</v>
+        <v>75.5625</v>
       </c>
       <c r="P7" t="n">
-        <v>183.5419131440642</v>
+        <v>1.056818181818182</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.68769884577664</v>
+        <v>26.01805555555556</v>
       </c>
       <c r="R7" t="n">
-        <v>15756.54537681997</v>
+        <v>184.2569444444445</v>
+      </c>
+      <c r="S7" t="n">
+        <v>77.13333333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>76113.88888888889</v>
+      </c>
+      <c r="U7" t="n">
+        <v>16960833.33333333</v>
+      </c>
+      <c r="V7" t="n">
+        <v>80.9375</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.658333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>26.86646939427112</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>183.6026088263588</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>70.44480610704748</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>17858.54049526463</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2645283.098327279</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>74.59226012174288</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.0251924001924</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26.49646464646465</v>
+      </c>
+      <c r="D8" t="n">
+        <v>185.820202020202</v>
+      </c>
+      <c r="E8" t="n">
+        <v>76.36161616161615</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47356.56565656565</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10709974.74747475</v>
+      </c>
+      <c r="H8" t="n">
+        <v>79.23215488215489</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.530808080808081</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.11230158730158</v>
+      </c>
+      <c r="K8" t="n">
+        <v>184.7674603174603</v>
+      </c>
+      <c r="L8" t="n">
+        <v>72.5845238095238</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25705.15873015873</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5144404.761904762</v>
+      </c>
+      <c r="O8" t="n">
+        <v>77.88095238095238</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>24.45707039337474</v>
+      </c>
+      <c r="R8" t="n">
+        <v>185.1181884057971</v>
+      </c>
+      <c r="S8" t="n">
+        <v>73.2718115942029</v>
+      </c>
+      <c r="T8" t="n">
+        <v>39196.14906832299</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7165957.81573499</v>
+      </c>
+      <c r="V8" t="n">
+        <v>78.47772256728778</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.166915113871636</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23.8899561721922</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>182.2570694522869</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>69.04026538678713</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>22340.65983705736</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3069865.182436611</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>74.9608773628028</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>26.91666666666667</v>
+      </c>
+      <c r="D9" t="n">
+        <v>181.9333333333333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>79.33333333333333</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49416.66666666666</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21821666.66666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>82.03333333333335</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.92467532467532</v>
+      </c>
+      <c r="K9" t="n">
+        <v>184.9142857142857</v>
+      </c>
+      <c r="L9" t="n">
+        <v>70.13766233766235</v>
+      </c>
+      <c r="M9" t="n">
+        <v>22077.92207792207</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3036753.246753247</v>
+      </c>
+      <c r="O9" t="n">
+        <v>74.83896103896105</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>26.7264594356261</v>
+      </c>
+      <c r="R9" t="n">
+        <v>182.6929497354497</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75.4953130511464</v>
+      </c>
+      <c r="T9" t="n">
+        <v>38591.65784832452</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11053073.74338624</v>
+      </c>
+      <c r="V9" t="n">
+        <v>79.53869047619048</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.588236331569665</v>
+      </c>
+      <c r="X9" t="n">
+        <v>24.49716911108216</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>183.4193794792164</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>68.59531562036997</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>20783.3313511885</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2687006.795288045</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>73.78556135893092</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.02994227994228</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.29823232323232</v>
+      </c>
+      <c r="D10" t="n">
+        <v>183.8569444444444</v>
+      </c>
+      <c r="E10" t="n">
+        <v>72.68169191919191</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23374.74747474748</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5741313.131313131</v>
+      </c>
+      <c r="H10" t="n">
+        <v>76.84671717171719</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.209848484848485</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.44907407407408</v>
+      </c>
+      <c r="K10" t="n">
+        <v>181.7592592592593</v>
+      </c>
+      <c r="L10" t="n">
+        <v>78.27777777777779</v>
+      </c>
+      <c r="M10" t="n">
+        <v>40560.18518518519</v>
+      </c>
+      <c r="N10" t="n">
+        <v>21134259.25925926</v>
+      </c>
+      <c r="O10" t="n">
+        <v>81.06018518518518</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.331018518518519</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>26.83575514874142</v>
+      </c>
+      <c r="R10" t="n">
+        <v>182.623048050586</v>
+      </c>
+      <c r="S10" t="n">
+        <v>71.66593418452257</v>
+      </c>
+      <c r="T10" t="n">
+        <v>31049.71538901602</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5851826.04036648</v>
+      </c>
+      <c r="V10" t="n">
+        <v>75.77641659732335</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.258972201997088</v>
+      </c>
+      <c r="X10" t="n">
+        <v>25.40398913951546</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>179.7061821219716</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>76.50849345586188</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>37094.85519353941</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>19655859.26622111</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>81.13363965469229</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.874401280980228</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>183.5851851851852</v>
+      </c>
+      <c r="E11" t="n">
+        <v>76.21296296296298</v>
+      </c>
+      <c r="F11" t="n">
+        <v>39390.74074074074</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12332037.03703704</v>
+      </c>
+      <c r="H11" t="n">
+        <v>80.21666666666665</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.537037037037037</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25.79945286195286</v>
+      </c>
+      <c r="K11" t="n">
+        <v>185.1044191919192</v>
+      </c>
+      <c r="L11" t="n">
+        <v>82.14402356902357</v>
+      </c>
+      <c r="M11" t="n">
+        <v>139582.1127946128</v>
+      </c>
+      <c r="N11" t="n">
+        <v>44540888.04713805</v>
+      </c>
+      <c r="O11" t="n">
+        <v>84.93573232323232</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.756439393939394</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24.52535395763656</v>
+      </c>
+      <c r="R11" t="n">
+        <v>181.72211352657</v>
+      </c>
+      <c r="S11" t="n">
+        <v>74.96061408398366</v>
+      </c>
+      <c r="T11" t="n">
+        <v>41001.35358602749</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11011912.78799703</v>
+      </c>
+      <c r="V11" t="n">
+        <v>80.01813823857303</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.387885544407284</v>
+      </c>
+      <c r="X11" t="n">
+        <v>24.31593625037561</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>182.9521115040566</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>78.08323509696507</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>112111.6554561635</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>28708764.47541779</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>83.15208838961699</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.803249890206412</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>28.45833333333333</v>
+      </c>
+      <c r="D12" t="n">
+        <v>180.8981481481481</v>
+      </c>
+      <c r="E12" t="n">
+        <v>74.20370370370371</v>
+      </c>
+      <c r="F12" t="n">
+        <v>23550.92592592593</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5474652.777777777</v>
+      </c>
+      <c r="H12" t="n">
+        <v>76.24074074074075</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.462962962962963</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24.11230158730158</v>
+      </c>
+      <c r="K12" t="n">
+        <v>184.7674603174603</v>
+      </c>
+      <c r="L12" t="n">
+        <v>72.5845238095238</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25705.15873015873</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5144404.761904762</v>
+      </c>
+      <c r="O12" t="n">
+        <v>77.88095238095238</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>28.32939958592133</v>
+      </c>
+      <c r="R12" t="n">
+        <v>183.044833032027</v>
+      </c>
+      <c r="S12" t="n">
+        <v>72.46471972188083</v>
+      </c>
+      <c r="T12" t="n">
+        <v>23365.4995595076</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4539269.478542405</v>
+      </c>
+      <c r="V12" t="n">
+        <v>73.75890166343217</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.211936157862354</v>
+      </c>
+      <c r="X12" t="n">
+        <v>23.8899561721922</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>182.2570694522869</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>69.04026538678713</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>22340.65983705736</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3069865.182436611</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>74.9608773628028</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>27.34772727272727</v>
+      </c>
+      <c r="D13" t="n">
+        <v>184.0409090909091</v>
+      </c>
+      <c r="E13" t="n">
+        <v>72.96136363636364</v>
+      </c>
+      <c r="F13" t="n">
+        <v>31439.77272727273</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4340284.090909091</v>
+      </c>
+      <c r="H13" t="n">
+        <v>75.86363636363637</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.114772727272727</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.49646464646465</v>
+      </c>
+      <c r="K13" t="n">
+        <v>185.820202020202</v>
+      </c>
+      <c r="L13" t="n">
+        <v>76.36161616161615</v>
+      </c>
+      <c r="M13" t="n">
+        <v>47356.56565656565</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10709974.74747475</v>
+      </c>
+      <c r="O13" t="n">
+        <v>79.23215488215489</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.530808080808081</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26.11926312539799</v>
+      </c>
+      <c r="R13" t="n">
+        <v>184.1890445391597</v>
+      </c>
+      <c r="S13" t="n">
+        <v>69.56278237478895</v>
+      </c>
+      <c r="T13" t="n">
+        <v>30850.8014536633</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3113364.333583083</v>
+      </c>
+      <c r="V13" t="n">
+        <v>73.81229576162141</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.18789189794124</v>
+      </c>
+      <c r="X13" t="n">
+        <v>24.45707039337474</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>185.1181884057971</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>73.2718115942029</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>39196.14906832299</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7165957.81573499</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>78.47772256728778</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.166915113871636</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,1129 +578,1317 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.76619318181818</v>
+        <v>25.3</v>
       </c>
       <c r="D2" t="n">
-        <v>182.5727272727273</v>
+        <v>185.45</v>
       </c>
       <c r="E2" t="n">
-        <v>79.51676136363636</v>
+        <v>80.325</v>
       </c>
       <c r="F2" t="n">
-        <v>101457.6704545454</v>
+        <v>101650</v>
       </c>
       <c r="G2" t="n">
-        <v>23779545.45454545</v>
+        <v>34250000</v>
       </c>
       <c r="H2" t="n">
-        <v>81.07670454545455</v>
+        <v>84.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.991477272727273</v>
+        <v>2.125</v>
       </c>
       <c r="J2" t="n">
-        <v>28.45833333333333</v>
+        <v>26.26818181818182</v>
       </c>
       <c r="K2" t="n">
-        <v>180.8981481481481</v>
+        <v>184.9931818181818</v>
       </c>
       <c r="L2" t="n">
-        <v>74.20370370370371</v>
+        <v>72.1693181818182</v>
       </c>
       <c r="M2" t="n">
-        <v>23550.92592592593</v>
+        <v>17737.5</v>
       </c>
       <c r="N2" t="n">
-        <v>5474652.777777777</v>
+        <v>4074829.545454545</v>
       </c>
       <c r="O2" t="n">
-        <v>76.24074074074075</v>
+        <v>75.5625</v>
       </c>
       <c r="P2" t="n">
-        <v>1.462962962962963</v>
+        <v>1.056818181818182</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.04278499278499</v>
+        <v>26.01805555555556</v>
       </c>
       <c r="R2" t="n">
-        <v>182.5969629329004</v>
+        <v>184.2569444444445</v>
       </c>
       <c r="S2" t="n">
-        <v>76.32545319264069</v>
+        <v>77.13333333333333</v>
       </c>
       <c r="T2" t="n">
-        <v>82879.37184343433</v>
+        <v>76113.88888888889</v>
       </c>
       <c r="U2" t="n">
-        <v>14376740.78959235</v>
+        <v>16960833.33333333</v>
       </c>
       <c r="V2" t="n">
-        <v>78.50383748196248</v>
+        <v>80.9375</v>
       </c>
       <c r="W2" t="n">
-        <v>1.699447601010101</v>
+        <v>1.658333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>28.32939958592133</v>
+        <v>26.86646939427112</v>
       </c>
       <c r="Y2" t="n">
-        <v>183.044833032027</v>
+        <v>183.6026088263588</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.46471972188083</v>
+        <v>70.44480610704748</v>
       </c>
       <c r="AA2" t="n">
-        <v>23365.4995595076</v>
+        <v>17858.54049526463</v>
       </c>
       <c r="AB2" t="n">
-        <v>4539269.478542405</v>
+        <v>2645283.098327279</v>
       </c>
       <c r="AC2" t="n">
-        <v>73.75890166343217</v>
+        <v>74.59226012174288</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.211936157862354</v>
+        <v>1.0251924001924</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.70238095238095</v>
+        <v>26.49646464646465</v>
       </c>
       <c r="D3" t="n">
-        <v>183.9384920634921</v>
+        <v>185.820202020202</v>
       </c>
       <c r="E3" t="n">
-        <v>73.20039682539682</v>
+        <v>76.36161616161615</v>
       </c>
       <c r="F3" t="n">
-        <v>12843.25396825397</v>
+        <v>47356.56565656565</v>
       </c>
       <c r="G3" t="n">
-        <v>4930952.380952382</v>
+        <v>10709974.74747475</v>
       </c>
       <c r="H3" t="n">
-        <v>77.19444444444444</v>
+        <v>79.23215488215489</v>
       </c>
       <c r="I3" t="n">
-        <v>1.017857142857143</v>
+        <v>1.530808080808081</v>
       </c>
       <c r="J3" t="n">
-        <v>26.46594516594516</v>
+        <v>24.11230158730158</v>
       </c>
       <c r="K3" t="n">
-        <v>183.5294372294372</v>
+        <v>184.7674603174603</v>
       </c>
       <c r="L3" t="n">
-        <v>70.44805194805194</v>
+        <v>72.5845238095238</v>
       </c>
       <c r="M3" t="n">
-        <v>10141.70274170274</v>
+        <v>25705.15873015873</v>
       </c>
       <c r="N3" t="n">
-        <v>2567608.225108225</v>
+        <v>5144404.761904762</v>
       </c>
       <c r="O3" t="n">
-        <v>74.47417027417028</v>
+        <v>77.88095238095238</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07041847041847</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.79817563388992</v>
+        <v>24.45707039337474</v>
       </c>
       <c r="R3" t="n">
-        <v>183.3705627705628</v>
+        <v>185.1181884057971</v>
       </c>
       <c r="S3" t="n">
-        <v>70.5935064935065</v>
+        <v>73.2718115942029</v>
       </c>
       <c r="T3" t="n">
-        <v>10669.5423623995</v>
+        <v>39196.14906832299</v>
       </c>
       <c r="U3" t="n">
-        <v>3385377.241805813</v>
+        <v>7165957.81573499</v>
       </c>
       <c r="V3" t="n">
-        <v>75.15785405071119</v>
+        <v>78.47772256728778</v>
       </c>
       <c r="W3" t="n">
-        <v>1.006493506493506</v>
+        <v>1.166915113871636</v>
       </c>
       <c r="X3" t="n">
-        <v>25.41556531079251</v>
+        <v>23.8899561721922</v>
       </c>
       <c r="Y3" t="n">
-        <v>183.6258685014814</v>
+        <v>182.2570694522869</v>
       </c>
       <c r="Z3" t="n">
-        <v>68.13688206022302</v>
+        <v>69.04026538678713</v>
       </c>
       <c r="AA3" t="n">
-        <v>13295.44876684465</v>
+        <v>22340.65983705736</v>
       </c>
       <c r="AB3" t="n">
-        <v>2065128.154236523</v>
+        <v>3069865.182436611</v>
       </c>
       <c r="AC3" t="n">
-        <v>73.6813436282217</v>
+        <v>74.9608773628028</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.015037593984962</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.25688131313132</v>
+        <v>26.91666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>185.6121843434344</v>
+        <v>181.9333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>72.06253156565657</v>
+        <v>79.33333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>15401.95707070707</v>
+        <v>49416.66666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>3526219.223484848</v>
+        <v>21821666.66666667</v>
       </c>
       <c r="H4" t="n">
-        <v>75.3809659090909</v>
+        <v>82.03333333333335</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>25.29861111111111</v>
+        <v>24.92467532467532</v>
       </c>
       <c r="K4" t="n">
-        <v>182.9837962962963</v>
+        <v>184.9142857142857</v>
       </c>
       <c r="L4" t="n">
-        <v>72.82638888888889</v>
+        <v>70.13766233766235</v>
       </c>
       <c r="M4" t="n">
-        <v>11641.2037037037</v>
+        <v>22077.92207792207</v>
       </c>
       <c r="N4" t="n">
-        <v>6007638.888888888</v>
+        <v>3036753.246753247</v>
       </c>
       <c r="O4" t="n">
-        <v>77.83101851851852</v>
+        <v>74.83896103896105</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.33530342655056</v>
+        <v>26.7264594356261</v>
       </c>
       <c r="R4" t="n">
-        <v>184.3974923103212</v>
+        <v>182.6929497354497</v>
       </c>
       <c r="S4" t="n">
-        <v>70.61344017467087</v>
+        <v>75.4953130511464</v>
       </c>
       <c r="T4" t="n">
-        <v>14483.10615657226</v>
+        <v>38591.65784832452</v>
       </c>
       <c r="U4" t="n">
-        <v>2647538.014224049</v>
+        <v>11053073.74338624</v>
       </c>
       <c r="V4" t="n">
-        <v>74.46330291204791</v>
+        <v>79.53869047619048</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>1.588236331569665</v>
       </c>
       <c r="X4" t="n">
-        <v>24.16154755761954</v>
+        <v>24.49716911108216</v>
       </c>
       <c r="Y4" t="n">
-        <v>181.9994458419333</v>
+        <v>183.4193794792164</v>
       </c>
       <c r="Z4" t="n">
-        <v>68.4623285388717</v>
+        <v>68.59531562036997</v>
       </c>
       <c r="AA4" t="n">
-        <v>10102.69769091847</v>
+        <v>20783.3313511885</v>
       </c>
       <c r="AB4" t="n">
-        <v>2930645.196400929</v>
+        <v>2687006.795288045</v>
       </c>
       <c r="AC4" t="n">
-        <v>74.90740669074647</v>
+        <v>73.78556135893092</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>1.02994227994228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.57121212121212</v>
+        <v>26.29823232323232</v>
       </c>
       <c r="D5" t="n">
-        <v>186.8166666666667</v>
+        <v>183.8569444444444</v>
       </c>
       <c r="E5" t="n">
-        <v>77.78030303030302</v>
+        <v>72.68169191919191</v>
       </c>
       <c r="F5" t="n">
-        <v>52871.21212121212</v>
+        <v>23374.74747474748</v>
       </c>
       <c r="G5" t="n">
-        <v>17205757.57575757</v>
+        <v>5741313.131313131</v>
       </c>
       <c r="H5" t="n">
-        <v>81.31666666666666</v>
+        <v>76.84671717171719</v>
       </c>
       <c r="I5" t="n">
-        <v>1.643939393939394</v>
+        <v>1.209848484848485</v>
       </c>
       <c r="J5" t="n">
-        <v>27.34772727272727</v>
+        <v>26.44907407407408</v>
       </c>
       <c r="K5" t="n">
-        <v>184.0409090909091</v>
+        <v>181.7592592592593</v>
       </c>
       <c r="L5" t="n">
-        <v>72.96136363636364</v>
+        <v>78.27777777777779</v>
       </c>
       <c r="M5" t="n">
-        <v>31439.77272727273</v>
+        <v>40560.18518518519</v>
       </c>
       <c r="N5" t="n">
-        <v>4340284.090909091</v>
+        <v>21134259.25925926</v>
       </c>
       <c r="O5" t="n">
-        <v>75.86363636363637</v>
+        <v>81.06018518518518</v>
       </c>
       <c r="P5" t="n">
-        <v>1.114772727272727</v>
+        <v>2.331018518518519</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.98929188722566</v>
+        <v>26.83575514874142</v>
       </c>
       <c r="R5" t="n">
-        <v>185.4702892990011</v>
+        <v>182.623048050586</v>
       </c>
       <c r="S5" t="n">
-        <v>71.84523134294302</v>
+        <v>71.66593418452257</v>
       </c>
       <c r="T5" t="n">
-        <v>38914.19818920155</v>
+        <v>31049.71538901602</v>
       </c>
       <c r="U5" t="n">
-        <v>11071991.31454886</v>
+        <v>5851826.04036648</v>
       </c>
       <c r="V5" t="n">
-        <v>77.83554573034988</v>
+        <v>75.77641659732335</v>
       </c>
       <c r="W5" t="n">
-        <v>1.489679507313106</v>
+        <v>1.258972201997088</v>
       </c>
       <c r="X5" t="n">
-        <v>26.11926312539799</v>
+        <v>25.40398913951546</v>
       </c>
       <c r="Y5" t="n">
-        <v>184.1890445391597</v>
+        <v>179.7061821219716</v>
       </c>
       <c r="Z5" t="n">
-        <v>69.56278237478895</v>
+        <v>76.50849345586188</v>
       </c>
       <c r="AA5" t="n">
-        <v>30850.8014536633</v>
+        <v>37094.85519353941</v>
       </c>
       <c r="AB5" t="n">
-        <v>3113364.333583083</v>
+        <v>19655859.26622111</v>
       </c>
       <c r="AC5" t="n">
-        <v>73.81229576162141</v>
+        <v>81.13363965469229</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18789189794124</v>
+        <v>1.874401280980228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>29.36666666666666</v>
+        <v>26.2</v>
       </c>
       <c r="D6" t="n">
-        <v>182.480303030303</v>
+        <v>183.5851851851852</v>
       </c>
       <c r="E6" t="n">
-        <v>84.25151515151515</v>
+        <v>76.21296296296298</v>
       </c>
       <c r="F6" t="n">
-        <v>113145.4545454545</v>
+        <v>39390.74074074074</v>
       </c>
       <c r="G6" t="n">
-        <v>42198484.84848485</v>
+        <v>12332037.03703704</v>
       </c>
       <c r="H6" t="n">
-        <v>85.10606060606061</v>
+        <v>80.21666666666665</v>
       </c>
       <c r="I6" t="n">
-        <v>3.33939393939394</v>
+        <v>1.537037037037037</v>
       </c>
       <c r="J6" t="n">
-        <v>27.25902777777778</v>
+        <v>25.79945286195286</v>
       </c>
       <c r="K6" t="n">
-        <v>185.7902777777778</v>
+        <v>185.1044191919192</v>
       </c>
       <c r="L6" t="n">
-        <v>75.21319444444444</v>
+        <v>82.14402356902357</v>
       </c>
       <c r="M6" t="n">
-        <v>39669.44444444445</v>
+        <v>139582.1127946128</v>
       </c>
       <c r="N6" t="n">
-        <v>10381006.94444444</v>
+        <v>44540888.04713805</v>
       </c>
       <c r="O6" t="n">
-        <v>77.90069444444444</v>
+        <v>84.93573232323232</v>
       </c>
       <c r="P6" t="n">
-        <v>1.195833333333333</v>
+        <v>2.756439393939394</v>
       </c>
       <c r="Q6" t="n">
-        <v>27.71460423634337</v>
+        <v>24.52535395763656</v>
       </c>
       <c r="R6" t="n">
-        <v>184.1878251579339</v>
+        <v>181.72211352657</v>
       </c>
       <c r="S6" t="n">
-        <v>79.75401802303976</v>
+        <v>74.96061408398366</v>
       </c>
       <c r="T6" t="n">
-        <v>87085.84169453736</v>
+        <v>41001.35358602749</v>
       </c>
       <c r="U6" t="n">
-        <v>26746848.29059829</v>
+        <v>11011912.78799703</v>
       </c>
       <c r="V6" t="n">
-        <v>81.75524897807507</v>
+        <v>80.01813823857303</v>
       </c>
       <c r="W6" t="n">
-        <v>2.364269788182832</v>
+        <v>1.387885544407284</v>
       </c>
       <c r="X6" t="n">
-        <v>24.55559221480274</v>
+        <v>24.31593625037561</v>
       </c>
       <c r="Y6" t="n">
-        <v>184.9365510585905</v>
+        <v>182.9521115040566</v>
       </c>
       <c r="Z6" t="n">
-        <v>69.91505895420369</v>
+        <v>78.08323509696507</v>
       </c>
       <c r="AA6" t="n">
-        <v>29163.08603677024</v>
+        <v>112111.6554561635</v>
       </c>
       <c r="AB6" t="n">
-        <v>5222671.306215715</v>
+        <v>28708764.47541779</v>
       </c>
       <c r="AC6" t="n">
-        <v>76.08152253448306</v>
+        <v>83.15208838961699</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.060768398268398</v>
+        <v>1.803249890206412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.3</v>
+        <v>28.45833333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>185.45</v>
+        <v>180.8981481481481</v>
       </c>
       <c r="E7" t="n">
-        <v>80.325</v>
+        <v>74.20370370370371</v>
       </c>
       <c r="F7" t="n">
-        <v>101650</v>
+        <v>23550.92592592593</v>
       </c>
       <c r="G7" t="n">
-        <v>34250000</v>
+        <v>5474652.777777777</v>
       </c>
       <c r="H7" t="n">
-        <v>84.3</v>
+        <v>76.24074074074075</v>
       </c>
       <c r="I7" t="n">
-        <v>2.125</v>
+        <v>1.462962962962963</v>
       </c>
       <c r="J7" t="n">
-        <v>26.26818181818182</v>
+        <v>24.11230158730158</v>
       </c>
       <c r="K7" t="n">
-        <v>184.9931818181818</v>
+        <v>184.7674603174603</v>
       </c>
       <c r="L7" t="n">
-        <v>72.1693181818182</v>
+        <v>72.5845238095238</v>
       </c>
       <c r="M7" t="n">
-        <v>17737.5</v>
+        <v>25705.15873015873</v>
       </c>
       <c r="N7" t="n">
-        <v>4074829.545454545</v>
+        <v>5144404.761904762</v>
       </c>
       <c r="O7" t="n">
-        <v>75.5625</v>
+        <v>77.88095238095238</v>
       </c>
       <c r="P7" t="n">
-        <v>1.056818181818182</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.01805555555556</v>
+        <v>28.45734228473999</v>
       </c>
       <c r="R7" t="n">
-        <v>184.2569444444445</v>
+        <v>182.5539347853766</v>
       </c>
       <c r="S7" t="n">
-        <v>77.13333333333333</v>
+        <v>72.61986505076338</v>
       </c>
       <c r="T7" t="n">
-        <v>76113.88888888889</v>
+        <v>23628.63564398091</v>
       </c>
       <c r="U7" t="n">
-        <v>16960833.33333333</v>
+        <v>4658074.029018722</v>
       </c>
       <c r="V7" t="n">
-        <v>80.9375</v>
+        <v>73.86992130844433</v>
       </c>
       <c r="W7" t="n">
-        <v>1.658333333333333</v>
+        <v>1.244267667541325</v>
       </c>
       <c r="X7" t="n">
-        <v>26.86646939427112</v>
+        <v>23.8899561721922</v>
       </c>
       <c r="Y7" t="n">
-        <v>183.6026088263588</v>
+        <v>182.2570694522869</v>
       </c>
       <c r="Z7" t="n">
-        <v>70.44480610704748</v>
+        <v>69.04026538678713</v>
       </c>
       <c r="AA7" t="n">
-        <v>17858.54049526463</v>
+        <v>22340.65983705736</v>
       </c>
       <c r="AB7" t="n">
-        <v>2645283.098327279</v>
+        <v>3069865.182436611</v>
       </c>
       <c r="AC7" t="n">
-        <v>74.59226012174288</v>
+        <v>74.9608773628028</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.0251924001924</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
+        <v>27.11717171717172</v>
+      </c>
+      <c r="D8" t="n">
+        <v>184.2787878787879</v>
+      </c>
+      <c r="E8" t="n">
+        <v>72.94545454545454</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31683.83838383839</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4352979.797979798</v>
+      </c>
+      <c r="H8" t="n">
+        <v>75.96969696969697</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.112121212121212</v>
+      </c>
+      <c r="J8" t="n">
         <v>26.49646464646465</v>
       </c>
-      <c r="D8" t="n">
+      <c r="K8" t="n">
         <v>185.820202020202</v>
       </c>
-      <c r="E8" t="n">
+      <c r="L8" t="n">
         <v>76.36161616161615</v>
       </c>
-      <c r="F8" t="n">
+      <c r="M8" t="n">
         <v>47356.56565656565</v>
       </c>
-      <c r="G8" t="n">
+      <c r="N8" t="n">
         <v>10709974.74747475</v>
       </c>
-      <c r="H8" t="n">
+      <c r="O8" t="n">
         <v>79.23215488215489</v>
       </c>
-      <c r="I8" t="n">
+      <c r="P8" t="n">
         <v>1.530808080808081</v>
       </c>
-      <c r="J8" t="n">
-        <v>24.11230158730158</v>
-      </c>
-      <c r="K8" t="n">
-        <v>184.7674603174603</v>
-      </c>
-      <c r="L8" t="n">
-        <v>72.5845238095238</v>
-      </c>
-      <c r="M8" t="n">
-        <v>25705.15873015873</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5144404.761904762</v>
-      </c>
-      <c r="O8" t="n">
-        <v>77.88095238095238</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
       <c r="Q8" t="n">
+        <v>25.93669949770827</v>
+      </c>
+      <c r="R8" t="n">
+        <v>184.2579866803112</v>
+      </c>
+      <c r="S8" t="n">
+        <v>69.17749967706108</v>
+      </c>
+      <c r="T8" t="n">
+        <v>30216.58541912928</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2968360.889110889</v>
+      </c>
+      <c r="V8" t="n">
+        <v>73.56331051826666</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.167015020392213</v>
+      </c>
+      <c r="X8" t="n">
         <v>24.45707039337474</v>
       </c>
-      <c r="R8" t="n">
+      <c r="Y8" t="n">
         <v>185.1181884057971</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Z8" t="n">
         <v>73.2718115942029</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AA8" t="n">
         <v>39196.14906832299</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AB8" t="n">
         <v>7165957.81573499</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AC8" t="n">
         <v>78.47772256728778</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AD8" t="n">
         <v>1.166915113871636</v>
-      </c>
-      <c r="X8" t="n">
-        <v>23.8899561721922</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>182.2570694522869</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>69.04026538678713</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>22340.65983705736</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3069865.182436611</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>74.9608773628028</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.91666666666667</v>
+        <v>25.79945286195286</v>
       </c>
       <c r="D9" t="n">
-        <v>181.9333333333333</v>
+        <v>185.1044191919192</v>
       </c>
       <c r="E9" t="n">
-        <v>79.33333333333333</v>
+        <v>82.14402356902357</v>
       </c>
       <c r="F9" t="n">
-        <v>49416.66666666666</v>
+        <v>139582.1127946128</v>
       </c>
       <c r="G9" t="n">
-        <v>21821666.66666667</v>
+        <v>44540888.04713805</v>
       </c>
       <c r="H9" t="n">
-        <v>82.03333333333335</v>
+        <v>84.93573232323232</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>2.756439393939394</v>
       </c>
       <c r="J9" t="n">
-        <v>24.92467532467532</v>
+        <v>26.21445005611672</v>
       </c>
       <c r="K9" t="n">
-        <v>184.9142857142857</v>
+        <v>185.6552749719417</v>
       </c>
       <c r="L9" t="n">
-        <v>70.13766233766235</v>
+        <v>72.02780583613918</v>
       </c>
       <c r="M9" t="n">
-        <v>22077.92207792207</v>
+        <v>15343.40628507295</v>
       </c>
       <c r="N9" t="n">
-        <v>3036753.246753247</v>
+        <v>3512194.865319865</v>
       </c>
       <c r="O9" t="n">
-        <v>74.83896103896105</v>
+        <v>75.39419191919191</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.7264594356261</v>
+        <v>24.31593625037561</v>
       </c>
       <c r="R9" t="n">
-        <v>182.6929497354497</v>
+        <v>182.9521115040566</v>
       </c>
       <c r="S9" t="n">
-        <v>75.4953130511464</v>
+        <v>78.08323509696507</v>
       </c>
       <c r="T9" t="n">
-        <v>38591.65784832452</v>
+        <v>112111.6554561635</v>
       </c>
       <c r="U9" t="n">
-        <v>11053073.74338624</v>
+        <v>28708764.47541779</v>
       </c>
       <c r="V9" t="n">
-        <v>79.53869047619048</v>
+        <v>83.15208838961699</v>
       </c>
       <c r="W9" t="n">
-        <v>1.588236331569665</v>
+        <v>1.803249890206412</v>
       </c>
       <c r="X9" t="n">
-        <v>24.49716911108216</v>
+        <v>26.29804749026717</v>
       </c>
       <c r="Y9" t="n">
-        <v>183.4193794792164</v>
+        <v>184.1928326709028</v>
       </c>
       <c r="Z9" t="n">
-        <v>68.59531562036997</v>
+        <v>70.4094776861272</v>
       </c>
       <c r="AA9" t="n">
-        <v>20783.3313511885</v>
+        <v>14435.60053423707</v>
       </c>
       <c r="AB9" t="n">
-        <v>2687006.795288045</v>
+        <v>2582842.432396685</v>
       </c>
       <c r="AC9" t="n">
-        <v>73.78556135893092</v>
+        <v>74.31305937861049</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.02994227994228</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>26.29823232323232</v>
+        <v>25.3</v>
       </c>
       <c r="D10" t="n">
-        <v>183.8569444444444</v>
+        <v>185.45</v>
       </c>
       <c r="E10" t="n">
-        <v>72.68169191919191</v>
+        <v>80.325</v>
       </c>
       <c r="F10" t="n">
-        <v>23374.74747474748</v>
+        <v>101650</v>
       </c>
       <c r="G10" t="n">
-        <v>5741313.131313131</v>
+        <v>34250000</v>
       </c>
       <c r="H10" t="n">
-        <v>76.84671717171719</v>
+        <v>84.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.209848484848485</v>
+        <v>2.125</v>
       </c>
       <c r="J10" t="n">
-        <v>26.44907407407408</v>
+        <v>26.91666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>181.7592592592593</v>
+        <v>181.9333333333333</v>
       </c>
       <c r="L10" t="n">
-        <v>78.27777777777779</v>
+        <v>79.33333333333333</v>
       </c>
       <c r="M10" t="n">
-        <v>40560.18518518519</v>
+        <v>49416.66666666666</v>
       </c>
       <c r="N10" t="n">
-        <v>21134259.25925926</v>
+        <v>21821666.66666667</v>
       </c>
       <c r="O10" t="n">
-        <v>81.06018518518518</v>
+        <v>82.03333333333335</v>
       </c>
       <c r="P10" t="n">
-        <v>2.331018518518519</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.83575514874142</v>
+        <v>26.01805555555556</v>
       </c>
       <c r="R10" t="n">
-        <v>182.623048050586</v>
+        <v>184.2569444444445</v>
       </c>
       <c r="S10" t="n">
-        <v>71.66593418452257</v>
+        <v>77.13333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>31049.71538901602</v>
+        <v>76113.88888888889</v>
       </c>
       <c r="U10" t="n">
-        <v>5851826.04036648</v>
+        <v>16960833.33333333</v>
       </c>
       <c r="V10" t="n">
-        <v>75.77641659732335</v>
+        <v>80.9375</v>
       </c>
       <c r="W10" t="n">
-        <v>1.258972201997088</v>
+        <v>1.658333333333333</v>
       </c>
       <c r="X10" t="n">
-        <v>25.40398913951546</v>
+        <v>26.7264594356261</v>
       </c>
       <c r="Y10" t="n">
-        <v>179.7061821219716</v>
+        <v>182.6929497354497</v>
       </c>
       <c r="Z10" t="n">
-        <v>76.50849345586188</v>
+        <v>75.4953130511464</v>
       </c>
       <c r="AA10" t="n">
-        <v>37094.85519353941</v>
+        <v>38591.65784832452</v>
       </c>
       <c r="AB10" t="n">
-        <v>19655859.26622111</v>
+        <v>11053073.74338624</v>
       </c>
       <c r="AC10" t="n">
-        <v>81.13363965469229</v>
+        <v>79.53869047619048</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.874401280980228</v>
+        <v>1.588236331569665</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.2</v>
+        <v>24.92467532467532</v>
       </c>
       <c r="D11" t="n">
-        <v>183.5851851851852</v>
+        <v>184.9142857142857</v>
       </c>
       <c r="E11" t="n">
-        <v>76.21296296296298</v>
+        <v>70.13766233766235</v>
       </c>
       <c r="F11" t="n">
-        <v>39390.74074074074</v>
+        <v>22077.92207792207</v>
       </c>
       <c r="G11" t="n">
-        <v>12332037.03703704</v>
+        <v>3036753.246753247</v>
       </c>
       <c r="H11" t="n">
-        <v>80.21666666666665</v>
+        <v>74.83896103896105</v>
       </c>
       <c r="I11" t="n">
-        <v>1.537037037037037</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>25.79945286195286</v>
+        <v>27.72550505050505</v>
       </c>
       <c r="K11" t="n">
-        <v>185.1044191919192</v>
+        <v>182.720202020202</v>
       </c>
       <c r="L11" t="n">
-        <v>82.14402356902357</v>
+        <v>79.59267676767678</v>
       </c>
       <c r="M11" t="n">
-        <v>139582.1127946128</v>
+        <v>102062.3737373737</v>
       </c>
       <c r="N11" t="n">
-        <v>44540888.04713805</v>
+        <v>24076262.62626263</v>
       </c>
       <c r="O11" t="n">
-        <v>84.93573232323232</v>
+        <v>81.21262626262626</v>
       </c>
       <c r="P11" t="n">
-        <v>2.756439393939394</v>
+        <v>1.981313131313131</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.52535395763656</v>
+        <v>24.49716911108216</v>
       </c>
       <c r="R11" t="n">
-        <v>181.72211352657</v>
+        <v>183.4193794792164</v>
       </c>
       <c r="S11" t="n">
-        <v>74.96061408398366</v>
+        <v>68.59531562036997</v>
       </c>
       <c r="T11" t="n">
-        <v>41001.35358602749</v>
+        <v>20783.3313511885</v>
       </c>
       <c r="U11" t="n">
-        <v>11011912.78799703</v>
+        <v>2687006.795288045</v>
       </c>
       <c r="V11" t="n">
-        <v>80.01813823857303</v>
+        <v>73.78556135893092</v>
       </c>
       <c r="W11" t="n">
-        <v>1.387885544407284</v>
+        <v>1.02994227994228</v>
       </c>
       <c r="X11" t="n">
-        <v>24.31593625037561</v>
+        <v>27.14914221580888</v>
       </c>
       <c r="Y11" t="n">
-        <v>182.9521115040566</v>
+        <v>182.4917448292448</v>
       </c>
       <c r="Z11" t="n">
-        <v>78.08323509696507</v>
+        <v>76.33929172679171</v>
       </c>
       <c r="AA11" t="n">
-        <v>112111.6554561635</v>
+        <v>83609.44163860829</v>
       </c>
       <c r="AB11" t="n">
-        <v>28708764.47541779</v>
+        <v>14386408.47963765</v>
       </c>
       <c r="AC11" t="n">
-        <v>83.15208838961699</v>
+        <v>78.40341109507777</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.803249890206412</v>
+        <v>1.716175645342312</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>28.45833333333333</v>
+        <v>25.41666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>180.8981481481481</v>
+        <v>183.2003968253968</v>
       </c>
       <c r="E12" t="n">
-        <v>74.20370370370371</v>
+        <v>72.92261904761905</v>
       </c>
       <c r="F12" t="n">
-        <v>23550.92592592593</v>
+        <v>11728.1746031746</v>
       </c>
       <c r="G12" t="n">
-        <v>5474652.777777777</v>
+        <v>6035119.047619047</v>
       </c>
       <c r="H12" t="n">
-        <v>76.24074074074075</v>
+        <v>77.8015873015873</v>
       </c>
       <c r="I12" t="n">
-        <v>1.462962962962963</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>24.11230158730158</v>
+        <v>26.2</v>
       </c>
       <c r="K12" t="n">
-        <v>184.7674603174603</v>
+        <v>183.5851851851852</v>
       </c>
       <c r="L12" t="n">
-        <v>72.5845238095238</v>
+        <v>76.21296296296298</v>
       </c>
       <c r="M12" t="n">
-        <v>25705.15873015873</v>
+        <v>39390.74074074074</v>
       </c>
       <c r="N12" t="n">
-        <v>5144404.761904762</v>
+        <v>12332037.03703704</v>
       </c>
       <c r="O12" t="n">
-        <v>77.88095238095238</v>
+        <v>80.21666666666665</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>1.537037037037037</v>
       </c>
       <c r="Q12" t="n">
-        <v>28.32939958592133</v>
+        <v>24.26211634751367</v>
       </c>
       <c r="R12" t="n">
-        <v>183.044833032027</v>
+        <v>182.0958037113481</v>
       </c>
       <c r="S12" t="n">
-        <v>72.46471972188083</v>
+        <v>68.41095870121929</v>
       </c>
       <c r="T12" t="n">
-        <v>23365.4995595076</v>
+        <v>10113.5090585942</v>
       </c>
       <c r="U12" t="n">
-        <v>4539269.478542405</v>
+        <v>2837240.174578603</v>
       </c>
       <c r="V12" t="n">
-        <v>73.75890166343217</v>
+        <v>74.68065779918204</v>
       </c>
       <c r="W12" t="n">
-        <v>1.211936157862354</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>23.8899561721922</v>
+        <v>24.52535395763656</v>
       </c>
       <c r="Y12" t="n">
-        <v>182.2570694522869</v>
+        <v>181.72211352657</v>
       </c>
       <c r="Z12" t="n">
-        <v>69.04026538678713</v>
+        <v>74.96061408398366</v>
       </c>
       <c r="AA12" t="n">
-        <v>22340.65983705736</v>
+        <v>41001.35358602749</v>
       </c>
       <c r="AB12" t="n">
-        <v>3069865.182436611</v>
+        <v>11011912.78799703</v>
       </c>
       <c r="AC12" t="n">
-        <v>74.9608773628028</v>
+        <v>80.01813823857303</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>1.387885544407284</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>27.34772727272727</v>
+        <v>26.37020202020202</v>
       </c>
       <c r="D13" t="n">
-        <v>184.0409090909091</v>
+        <v>183.6257575757576</v>
       </c>
       <c r="E13" t="n">
-        <v>72.96136363636364</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="F13" t="n">
-        <v>31439.77272727273</v>
+        <v>10123.9898989899</v>
       </c>
       <c r="G13" t="n">
-        <v>4340284.090909091</v>
+        <v>2617907.196969697</v>
       </c>
       <c r="H13" t="n">
-        <v>75.86363636363637</v>
+        <v>74.53989898989899</v>
       </c>
       <c r="I13" t="n">
-        <v>1.114772727272727</v>
+        <v>1.061616161616162</v>
       </c>
       <c r="J13" t="n">
-        <v>26.49646464646465</v>
+        <v>26.61948051948052</v>
       </c>
       <c r="K13" t="n">
-        <v>185.820202020202</v>
+        <v>186.6610389610389</v>
       </c>
       <c r="L13" t="n">
-        <v>76.36161616161615</v>
+        <v>77.96753246753246</v>
       </c>
       <c r="M13" t="n">
-        <v>47356.56565656565</v>
+        <v>54019.48051948052</v>
       </c>
       <c r="N13" t="n">
-        <v>10709974.74747475</v>
+        <v>17721818.18181818</v>
       </c>
       <c r="O13" t="n">
-        <v>79.23215488215489</v>
+        <v>81.41428571428571</v>
       </c>
       <c r="P13" t="n">
-        <v>1.530808080808081</v>
+        <v>1.681818181818182</v>
       </c>
       <c r="Q13" t="n">
-        <v>26.11926312539799</v>
+        <v>25.51702873785253</v>
       </c>
       <c r="R13" t="n">
-        <v>184.1890445391597</v>
+        <v>183.5135440297053</v>
       </c>
       <c r="S13" t="n">
-        <v>69.56278237478895</v>
+        <v>68.20499907542241</v>
       </c>
       <c r="T13" t="n">
-        <v>30850.8014536633</v>
+        <v>13400.56312553452</v>
       </c>
       <c r="U13" t="n">
-        <v>3113364.333583083</v>
+        <v>2064685.998593321</v>
       </c>
       <c r="V13" t="n">
-        <v>73.81229576162141</v>
+        <v>73.73253931105761</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18789189794124</v>
+        <v>1.013157894736842</v>
       </c>
       <c r="X13" t="n">
-        <v>24.45707039337474</v>
+        <v>24.79533289581748</v>
       </c>
       <c r="Y13" t="n">
-        <v>185.1181884057971</v>
+        <v>185.4031051134295</v>
       </c>
       <c r="Z13" t="n">
-        <v>73.2718115942029</v>
+        <v>71.8372659631241</v>
       </c>
       <c r="AA13" t="n">
-        <v>39196.14906832299</v>
+        <v>38633.22250803742</v>
       </c>
       <c r="AB13" t="n">
-        <v>7165957.81573499</v>
+        <v>11225391.0515682</v>
       </c>
       <c r="AC13" t="n">
-        <v>78.47772256728778</v>
+        <v>77.97182115232997</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.166915113871636</v>
+        <v>1.47235687093003</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.26818181818182</v>
+      </c>
+      <c r="D14" t="n">
+        <v>184.9931818181818</v>
+      </c>
+      <c r="E14" t="n">
+        <v>72.1693181818182</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17737.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4074829.545454545</v>
+      </c>
+      <c r="H14" t="n">
+        <v>75.5625</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.056818181818182</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27.25902777777778</v>
+      </c>
+      <c r="K14" t="n">
+        <v>185.7902777777778</v>
+      </c>
+      <c r="L14" t="n">
+        <v>75.21319444444444</v>
+      </c>
+      <c r="M14" t="n">
+        <v>39669.44444444445</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10381006.94444444</v>
+      </c>
+      <c r="O14" t="n">
+        <v>77.90069444444444</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.195833333333333</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>26.86646939427112</v>
+      </c>
+      <c r="R14" t="n">
+        <v>183.6026088263588</v>
+      </c>
+      <c r="S14" t="n">
+        <v>70.44480610704748</v>
+      </c>
+      <c r="T14" t="n">
+        <v>17858.54049526463</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2645283.098327279</v>
+      </c>
+      <c r="V14" t="n">
+        <v>74.59226012174288</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.0251924001924</v>
+      </c>
+      <c r="X14" t="n">
+        <v>24.55559221480274</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>184.9365510585905</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>69.91505895420369</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>29163.08603677024</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5222671.306215715</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>76.08152253448306</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.060768398268398</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>26.44907407407408</v>
+      </c>
+      <c r="D15" t="n">
+        <v>181.7592592592593</v>
+      </c>
+      <c r="E15" t="n">
+        <v>78.27777777777779</v>
+      </c>
+      <c r="F15" t="n">
+        <v>40560.18518518519</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21134259.25925926</v>
+      </c>
+      <c r="H15" t="n">
+        <v>81.06018518518518</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.331018518518519</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29.36666666666666</v>
+      </c>
+      <c r="K15" t="n">
+        <v>182.480303030303</v>
+      </c>
+      <c r="L15" t="n">
+        <v>84.25151515151515</v>
+      </c>
+      <c r="M15" t="n">
+        <v>113145.4545454545</v>
+      </c>
+      <c r="N15" t="n">
+        <v>42198484.84848485</v>
+      </c>
+      <c r="O15" t="n">
+        <v>85.10606060606061</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.33939393939394</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>25.40398913951546</v>
+      </c>
+      <c r="R15" t="n">
+        <v>179.7061821219716</v>
+      </c>
+      <c r="S15" t="n">
+        <v>76.50849345586188</v>
+      </c>
+      <c r="T15" t="n">
+        <v>37094.85519353941</v>
+      </c>
+      <c r="U15" t="n">
+        <v>19655859.26622111</v>
+      </c>
+      <c r="V15" t="n">
+        <v>81.13363965469229</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.874401280980228</v>
+      </c>
+      <c r="X15" t="n">
+        <v>27.71460423634337</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>184.1878251579339</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>79.75401802303976</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>87085.84169453736</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>26746848.29059829</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>81.75524897807507</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.364269788182832</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,1317 +578,2163 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.3</v>
+        <v>28.5</v>
       </c>
       <c r="D2" t="n">
-        <v>185.45</v>
+        <v>181.2222222222222</v>
       </c>
       <c r="E2" t="n">
-        <v>80.325</v>
+        <v>74.05555555555556</v>
       </c>
       <c r="F2" t="n">
-        <v>101650</v>
+        <v>23388.88888888889</v>
       </c>
       <c r="G2" t="n">
-        <v>34250000</v>
+        <v>5341666.666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>84.3</v>
+        <v>76.11111111111111</v>
       </c>
       <c r="I2" t="n">
-        <v>2.125</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="J2" t="n">
-        <v>26.26818181818182</v>
+        <v>23.78373015873016</v>
       </c>
       <c r="K2" t="n">
-        <v>184.9931818181818</v>
+        <v>184.6817460317461</v>
       </c>
       <c r="L2" t="n">
-        <v>72.1693181818182</v>
+        <v>72.74166666666666</v>
       </c>
       <c r="M2" t="n">
-        <v>17737.5</v>
+        <v>25919.44444444445</v>
       </c>
       <c r="N2" t="n">
-        <v>4074829.545454545</v>
+        <v>5530119.047619048</v>
       </c>
       <c r="O2" t="n">
-        <v>75.5625</v>
+        <v>78.38095238095239</v>
       </c>
       <c r="P2" t="n">
-        <v>1.056818181818182</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>26.01805555555556</v>
+        <v>28.37981975398856</v>
       </c>
       <c r="R2" t="n">
-        <v>184.2569444444445</v>
+        <v>182.3668345599109</v>
       </c>
       <c r="S2" t="n">
-        <v>77.13333333333333</v>
+        <v>72.79283278528803</v>
       </c>
       <c r="T2" t="n">
-        <v>76113.88888888889</v>
+        <v>23880.77839831585</v>
       </c>
       <c r="U2" t="n">
-        <v>16960833.33333333</v>
+        <v>4812961.227969448</v>
       </c>
       <c r="V2" t="n">
-        <v>80.9375</v>
+        <v>74.09159837848183</v>
       </c>
       <c r="W2" t="n">
-        <v>1.658333333333333</v>
+        <v>1.266176035631644</v>
       </c>
       <c r="X2" t="n">
-        <v>26.86646939427112</v>
+        <v>23.89675889328063</v>
       </c>
       <c r="Y2" t="n">
-        <v>183.6026088263588</v>
+        <v>182.2310954263128</v>
       </c>
       <c r="Z2" t="n">
-        <v>70.44480610704748</v>
+        <v>68.76753811405986</v>
       </c>
       <c r="AA2" t="n">
-        <v>17858.54049526463</v>
+        <v>22130.08469791078</v>
       </c>
       <c r="AB2" t="n">
-        <v>2645283.098327279</v>
+        <v>2924766.233766234</v>
       </c>
       <c r="AC2" t="n">
-        <v>74.59226012174288</v>
+        <v>74.73669678147938</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.0251924001924</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.49646464646465</v>
+        <v>26.99545454545454</v>
       </c>
       <c r="D3" t="n">
-        <v>185.820202020202</v>
+        <v>184.3931818181818</v>
       </c>
       <c r="E3" t="n">
-        <v>76.36161616161615</v>
+        <v>73.04090909090908</v>
       </c>
       <c r="F3" t="n">
-        <v>47356.56565656565</v>
+        <v>31746.59090909091</v>
       </c>
       <c r="G3" t="n">
-        <v>10709974.74747475</v>
+        <v>4460738.636363637</v>
       </c>
       <c r="H3" t="n">
-        <v>79.23215488215489</v>
+        <v>76.14772727272728</v>
       </c>
       <c r="I3" t="n">
-        <v>1.530808080808081</v>
+        <v>1.126136363636364</v>
       </c>
       <c r="J3" t="n">
-        <v>24.11230158730158</v>
+        <v>26.38658008658009</v>
       </c>
       <c r="K3" t="n">
-        <v>184.7674603174603</v>
+        <v>185.8978354978355</v>
       </c>
       <c r="L3" t="n">
-        <v>72.5845238095238</v>
+        <v>76.19307359307358</v>
       </c>
       <c r="M3" t="n">
-        <v>25705.15873015873</v>
+        <v>46877.05627705628</v>
       </c>
       <c r="N3" t="n">
-        <v>5144404.761904762</v>
+        <v>10503354.97835498</v>
       </c>
       <c r="O3" t="n">
-        <v>77.88095238095238</v>
+        <v>79.13405483405484</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>1.506926406926407</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.45707039337474</v>
+        <v>25.7959744349218</v>
       </c>
       <c r="R3" t="n">
-        <v>185.1181884057971</v>
+        <v>184.3917975153501</v>
       </c>
       <c r="S3" t="n">
-        <v>73.2718115942029</v>
+        <v>68.93406213669371</v>
       </c>
       <c r="T3" t="n">
-        <v>39196.14906832299</v>
+        <v>29446.78359652044</v>
       </c>
       <c r="U3" t="n">
-        <v>7165957.81573499</v>
+        <v>2801124.75024975</v>
       </c>
       <c r="V3" t="n">
-        <v>78.47772256728778</v>
+        <v>73.36028683305</v>
       </c>
       <c r="W3" t="n">
-        <v>1.166915113871636</v>
+        <v>1.13320439794124</v>
       </c>
       <c r="X3" t="n">
-        <v>23.8899561721922</v>
+        <v>24.38582224194025</v>
       </c>
       <c r="Y3" t="n">
-        <v>182.2570694522869</v>
+        <v>184.9048757763975</v>
       </c>
       <c r="Z3" t="n">
-        <v>69.04026538678713</v>
+        <v>73.2984575569358</v>
       </c>
       <c r="AA3" t="n">
-        <v>22340.65983705736</v>
+        <v>39281.2230109435</v>
       </c>
       <c r="AB3" t="n">
-        <v>3069865.182436611</v>
+        <v>7256237.651582373</v>
       </c>
       <c r="AC3" t="n">
-        <v>74.9608773628028</v>
+        <v>78.62376220053238</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>1.184736764270926</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.91666666666667</v>
+        <v>25.85984848484848</v>
       </c>
       <c r="D4" t="n">
-        <v>181.9333333333333</v>
+        <v>185.3275974025974</v>
       </c>
       <c r="E4" t="n">
-        <v>79.33333333333333</v>
+        <v>82.2504329004329</v>
       </c>
       <c r="F4" t="n">
-        <v>49416.66666666666</v>
+        <v>140371.9696969697</v>
       </c>
       <c r="G4" t="n">
-        <v>21821666.66666667</v>
+        <v>45146158.00865801</v>
       </c>
       <c r="H4" t="n">
-        <v>82.03333333333335</v>
+        <v>84.99253246753246</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>2.791233766233766</v>
       </c>
       <c r="J4" t="n">
-        <v>24.92467532467532</v>
+        <v>26.19580176767677</v>
       </c>
       <c r="K4" t="n">
-        <v>184.9142857142857</v>
+        <v>185.7599116161616</v>
       </c>
       <c r="L4" t="n">
-        <v>70.13766233766235</v>
+        <v>71.92900883838385</v>
       </c>
       <c r="M4" t="n">
-        <v>22077.92207792207</v>
+        <v>15295.42297979798</v>
       </c>
       <c r="N4" t="n">
-        <v>3036753.246753247</v>
+        <v>3460310.132575757</v>
       </c>
       <c r="O4" t="n">
-        <v>74.83896103896105</v>
+        <v>75.36392045454545</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.7264594356261</v>
+        <v>24.12794535746481</v>
       </c>
       <c r="R4" t="n">
-        <v>182.6929497354497</v>
+        <v>182.6073043661144</v>
       </c>
       <c r="S4" t="n">
-        <v>75.4953130511464</v>
+        <v>77.88453118201402</v>
       </c>
       <c r="T4" t="n">
-        <v>38591.65784832452</v>
+        <v>110722.0783030852</v>
       </c>
       <c r="U4" t="n">
-        <v>11053073.74338624</v>
+        <v>28448171.74816031</v>
       </c>
       <c r="V4" t="n">
-        <v>79.53869047619048</v>
+        <v>83.21827356472666</v>
       </c>
       <c r="W4" t="n">
-        <v>1.588236331569665</v>
+        <v>1.743444960836265</v>
       </c>
       <c r="X4" t="n">
-        <v>24.49716911108216</v>
+        <v>26.29553069927784</v>
       </c>
       <c r="Y4" t="n">
-        <v>183.4193794792164</v>
+        <v>184.2339822093111</v>
       </c>
       <c r="Z4" t="n">
-        <v>68.59531562036997</v>
+        <v>70.28452603325672</v>
       </c>
       <c r="AA4" t="n">
-        <v>20783.3313511885</v>
+        <v>14416.18696465307</v>
       </c>
       <c r="AB4" t="n">
-        <v>2687006.795288045</v>
+        <v>2415782.963718998</v>
       </c>
       <c r="AC4" t="n">
-        <v>73.78556135893092</v>
+        <v>74.16469180093679</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.02994227994228</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.29823232323232</v>
+        <v>25.3</v>
       </c>
       <c r="D5" t="n">
-        <v>183.8569444444444</v>
+        <v>185.45</v>
       </c>
       <c r="E5" t="n">
-        <v>72.68169191919191</v>
+        <v>80.325</v>
       </c>
       <c r="F5" t="n">
-        <v>23374.74747474748</v>
+        <v>101650</v>
       </c>
       <c r="G5" t="n">
-        <v>5741313.131313131</v>
+        <v>34250000</v>
       </c>
       <c r="H5" t="n">
-        <v>76.84671717171719</v>
+        <v>84.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.209848484848485</v>
+        <v>2.125</v>
       </c>
       <c r="J5" t="n">
-        <v>26.44907407407408</v>
+        <v>26.82857142857143</v>
       </c>
       <c r="K5" t="n">
-        <v>181.7592592592593</v>
+        <v>181.8428571428572</v>
       </c>
       <c r="L5" t="n">
-        <v>78.27777777777779</v>
+        <v>79.37142857142855</v>
       </c>
       <c r="M5" t="n">
-        <v>40560.18518518519</v>
+        <v>49471.42857142857</v>
       </c>
       <c r="N5" t="n">
-        <v>21134259.25925926</v>
+        <v>22147142.85714286</v>
       </c>
       <c r="O5" t="n">
-        <v>81.06018518518518</v>
+        <v>82.15714285714286</v>
       </c>
       <c r="P5" t="n">
-        <v>2.331018518518519</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.83575514874142</v>
+        <v>25.98950216450217</v>
       </c>
       <c r="R5" t="n">
-        <v>182.623048050586</v>
+        <v>184.0384199134199</v>
       </c>
       <c r="S5" t="n">
-        <v>71.66593418452257</v>
+        <v>77.19220779220778</v>
       </c>
       <c r="T5" t="n">
-        <v>31049.71538901602</v>
+        <v>77253.46320346321</v>
       </c>
       <c r="U5" t="n">
-        <v>5851826.04036648</v>
+        <v>17140454.54545454</v>
       </c>
       <c r="V5" t="n">
-        <v>75.77641659732335</v>
+        <v>81.01136363636364</v>
       </c>
       <c r="W5" t="n">
-        <v>1.258972201997088</v>
+        <v>1.668181818181818</v>
       </c>
       <c r="X5" t="n">
-        <v>25.40398913951546</v>
+        <v>26.84007082059877</v>
       </c>
       <c r="Y5" t="n">
-        <v>179.7061821219716</v>
+        <v>182.7243916987084</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.50849345586188</v>
+        <v>75.53635528607579</v>
       </c>
       <c r="AA5" t="n">
-        <v>37094.85519353941</v>
+        <v>38823.90548489927</v>
       </c>
       <c r="AB5" t="n">
-        <v>19655859.26622111</v>
+        <v>10868628.42600809</v>
       </c>
       <c r="AC5" t="n">
-        <v>81.13363965469229</v>
+        <v>79.43688997338066</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.874401280980228</v>
+        <v>1.59737027178021</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.2</v>
+        <v>24.98571428571429</v>
       </c>
       <c r="D6" t="n">
-        <v>183.5851851851852</v>
+        <v>184.9831168831169</v>
       </c>
       <c r="E6" t="n">
-        <v>76.21296296296298</v>
+        <v>70.11948051948052</v>
       </c>
       <c r="F6" t="n">
-        <v>39390.74074074074</v>
+        <v>21584.41558441558</v>
       </c>
       <c r="G6" t="n">
-        <v>12332037.03703704</v>
+        <v>2973409.09090909</v>
       </c>
       <c r="H6" t="n">
-        <v>80.21666666666665</v>
+        <v>74.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1.537037037037037</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>25.79945286195286</v>
+        <v>27.72528409090909</v>
       </c>
       <c r="K6" t="n">
-        <v>185.1044191919192</v>
+        <v>182.7988636363636</v>
       </c>
       <c r="L6" t="n">
-        <v>82.14402356902357</v>
+        <v>79.55312499999999</v>
       </c>
       <c r="M6" t="n">
-        <v>139582.1127946128</v>
+        <v>101933.8068181818</v>
       </c>
       <c r="N6" t="n">
-        <v>44540888.04713805</v>
+        <v>23893750</v>
       </c>
       <c r="O6" t="n">
-        <v>84.93573232323232</v>
+        <v>81.18238636363637</v>
       </c>
       <c r="P6" t="n">
-        <v>2.756439393939394</v>
+        <v>1.967613636363636</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.52535395763656</v>
+        <v>24.37216911108216</v>
       </c>
       <c r="R6" t="n">
-        <v>181.72211352657</v>
+        <v>183.6204664357382</v>
       </c>
       <c r="S6" t="n">
-        <v>74.96061408398366</v>
+        <v>68.92140257689171</v>
       </c>
       <c r="T6" t="n">
-        <v>41001.35358602749</v>
+        <v>21870.19754098558</v>
       </c>
       <c r="U6" t="n">
-        <v>11011912.78799703</v>
+        <v>2886463.317027176</v>
       </c>
       <c r="V6" t="n">
-        <v>80.01813823857303</v>
+        <v>74.12251788067006</v>
       </c>
       <c r="W6" t="n">
-        <v>1.387885544407284</v>
+        <v>1.046246627768367</v>
       </c>
       <c r="X6" t="n">
-        <v>24.31593625037561</v>
+        <v>27.25707070707071</v>
       </c>
       <c r="Y6" t="n">
-        <v>182.9521115040566</v>
+        <v>182.4460700757576</v>
       </c>
       <c r="Z6" t="n">
-        <v>78.08323509696507</v>
+        <v>76.60194128787879</v>
       </c>
       <c r="AA6" t="n">
-        <v>112111.6554561635</v>
+        <v>85810.62184343433</v>
       </c>
       <c r="AB6" t="n">
-        <v>28708764.47541779</v>
+        <v>15169233.34911616</v>
       </c>
       <c r="AC6" t="n">
-        <v>83.15208838961699</v>
+        <v>78.61455176767677</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.803249890206412</v>
+        <v>1.764030934343434</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>28.45833333333333</v>
+        <v>25.50694444444445</v>
       </c>
       <c r="D7" t="n">
-        <v>180.8981481481481</v>
+        <v>183.212962962963</v>
       </c>
       <c r="E7" t="n">
-        <v>74.20370370370371</v>
+        <v>73.01388888888889</v>
       </c>
       <c r="F7" t="n">
-        <v>23550.92592592593</v>
+        <v>11807.87037037037</v>
       </c>
       <c r="G7" t="n">
-        <v>5474652.777777777</v>
+        <v>6051388.888888888</v>
       </c>
       <c r="H7" t="n">
-        <v>76.24074074074075</v>
+        <v>77.78935185185185</v>
       </c>
       <c r="I7" t="n">
-        <v>1.462962962962963</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>24.11230158730158</v>
+        <v>25.9968253968254</v>
       </c>
       <c r="K7" t="n">
-        <v>184.7674603174603</v>
+        <v>183.3746031746032</v>
       </c>
       <c r="L7" t="n">
-        <v>72.5845238095238</v>
+        <v>76.15079365079364</v>
       </c>
       <c r="M7" t="n">
-        <v>25705.15873015873</v>
+        <v>39747.61904761905</v>
       </c>
       <c r="N7" t="n">
-        <v>5144404.761904762</v>
+        <v>12571904.76190476</v>
       </c>
       <c r="O7" t="n">
-        <v>77.88095238095238</v>
+        <v>80.2968253968254</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.523809523809524</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.45734228473999</v>
+        <v>24.44071422428621</v>
       </c>
       <c r="R7" t="n">
-        <v>182.5539347853766</v>
+        <v>182.1980569530444</v>
       </c>
       <c r="S7" t="n">
-        <v>72.61986505076338</v>
+        <v>68.56649520553836</v>
       </c>
       <c r="T7" t="n">
-        <v>23628.63564398091</v>
+        <v>10211.03102425181</v>
       </c>
       <c r="U7" t="n">
-        <v>4658074.029018722</v>
+        <v>2868110.474178706</v>
       </c>
       <c r="V7" t="n">
-        <v>73.86992130844433</v>
+        <v>74.56435113519092</v>
       </c>
       <c r="W7" t="n">
-        <v>1.244267667541325</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>23.8899561721922</v>
+        <v>24.65744624940277</v>
       </c>
       <c r="Y7" t="n">
-        <v>182.2570694522869</v>
+        <v>181.8760973084886</v>
       </c>
       <c r="Z7" t="n">
-        <v>69.04026538678713</v>
+        <v>75.06624064341456</v>
       </c>
       <c r="AA7" t="n">
-        <v>22340.65983705736</v>
+        <v>41072.58878802357</v>
       </c>
       <c r="AB7" t="n">
-        <v>3069865.182436611</v>
+        <v>10982175.24685459</v>
       </c>
       <c r="AC7" t="n">
-        <v>74.9608773628028</v>
+        <v>80.00840420449117</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>1.382473323777672</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>27.11717171717172</v>
+        <v>26.15324675324675</v>
       </c>
       <c r="D8" t="n">
-        <v>184.2787878787879</v>
+        <v>183.5246753246753</v>
       </c>
       <c r="E8" t="n">
-        <v>72.94545454545454</v>
+        <v>70.51948051948052</v>
       </c>
       <c r="F8" t="n">
-        <v>31683.83838383839</v>
+        <v>10205.1948051948</v>
       </c>
       <c r="G8" t="n">
-        <v>4352979.797979798</v>
+        <v>2728798.701298702</v>
       </c>
       <c r="H8" t="n">
-        <v>75.96969696969697</v>
+        <v>74.82337662337662</v>
       </c>
       <c r="I8" t="n">
-        <v>1.112121212121212</v>
+        <v>1.054545454545454</v>
       </c>
       <c r="J8" t="n">
-        <v>26.49646464646465</v>
+        <v>26.61948051948052</v>
       </c>
       <c r="K8" t="n">
-        <v>185.820202020202</v>
+        <v>186.6610389610389</v>
       </c>
       <c r="L8" t="n">
-        <v>76.36161616161615</v>
+        <v>77.96753246753246</v>
       </c>
       <c r="M8" t="n">
-        <v>47356.56565656565</v>
+        <v>54019.48051948052</v>
       </c>
       <c r="N8" t="n">
-        <v>10709974.74747475</v>
+        <v>17721818.18181818</v>
       </c>
       <c r="O8" t="n">
-        <v>79.23215488215489</v>
+        <v>81.41428571428571</v>
       </c>
       <c r="P8" t="n">
-        <v>1.530808080808081</v>
+        <v>1.681818181818182</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.93669949770827</v>
+        <v>25.666077956042</v>
       </c>
       <c r="R8" t="n">
-        <v>184.2579866803112</v>
+        <v>183.3087119737986</v>
       </c>
       <c r="S8" t="n">
-        <v>69.17749967706108</v>
+        <v>68.25684104860305</v>
       </c>
       <c r="T8" t="n">
-        <v>30216.58541912928</v>
+        <v>13532.97439910712</v>
       </c>
       <c r="U8" t="n">
-        <v>2968360.889110889</v>
+        <v>2064490.76530966</v>
       </c>
       <c r="V8" t="n">
-        <v>73.56331051826666</v>
+        <v>73.72440582917862</v>
       </c>
       <c r="W8" t="n">
-        <v>1.167015020392213</v>
+        <v>1.007518796992481</v>
       </c>
       <c r="X8" t="n">
-        <v>24.45707039337474</v>
+        <v>24.79533289581748</v>
       </c>
       <c r="Y8" t="n">
-        <v>185.1181884057971</v>
+        <v>185.4031051134295</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.2718115942029</v>
+        <v>71.8372659631241</v>
       </c>
       <c r="AA8" t="n">
-        <v>39196.14906832299</v>
+        <v>38633.22250803742</v>
       </c>
       <c r="AB8" t="n">
-        <v>7165957.81573499</v>
+        <v>11225391.0515682</v>
       </c>
       <c r="AC8" t="n">
-        <v>78.47772256728778</v>
+        <v>77.97182115232997</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.166915113871636</v>
+        <v>1.47235687093003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.79945286195286</v>
+        <v>26.13181818181818</v>
       </c>
       <c r="D9" t="n">
-        <v>185.1044191919192</v>
+        <v>185.0954545454545</v>
       </c>
       <c r="E9" t="n">
-        <v>82.14402356902357</v>
+        <v>72.16931818181818</v>
       </c>
       <c r="F9" t="n">
-        <v>139582.1127946128</v>
+        <v>17896.59090909091</v>
       </c>
       <c r="G9" t="n">
-        <v>44540888.04713805</v>
+        <v>4075113.636363637</v>
       </c>
       <c r="H9" t="n">
-        <v>84.93573232323232</v>
+        <v>75.69886363636364</v>
       </c>
       <c r="I9" t="n">
-        <v>2.756439393939394</v>
+        <v>1.068181818181818</v>
       </c>
       <c r="J9" t="n">
-        <v>26.21445005611672</v>
+        <v>27.06527777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>185.6552749719417</v>
+        <v>185.8309027777778</v>
       </c>
       <c r="L9" t="n">
-        <v>72.02780583613918</v>
+        <v>75.00069444444443</v>
       </c>
       <c r="M9" t="n">
-        <v>15343.40628507295</v>
+        <v>38775.69444444445</v>
       </c>
       <c r="N9" t="n">
-        <v>3512194.865319865</v>
+        <v>10118194.44444444</v>
       </c>
       <c r="O9" t="n">
-        <v>75.39419191919191</v>
+        <v>77.98506944444443</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>1.202083333333333</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.31593625037561</v>
+        <v>26.95739532019704</v>
       </c>
       <c r="R9" t="n">
-        <v>182.9521115040566</v>
+        <v>183.1566829004329</v>
       </c>
       <c r="S9" t="n">
-        <v>78.08323509696507</v>
+        <v>70.56110240334378</v>
       </c>
       <c r="T9" t="n">
-        <v>112111.6554561635</v>
+        <v>18437.61456933871</v>
       </c>
       <c r="U9" t="n">
-        <v>28708764.47541779</v>
+        <v>2708801.616845798</v>
       </c>
       <c r="V9" t="n">
-        <v>83.15208838961699</v>
+        <v>74.55040826989102</v>
       </c>
       <c r="W9" t="n">
-        <v>1.803249890206412</v>
+        <v>1.02056277056277</v>
       </c>
       <c r="X9" t="n">
-        <v>26.29804749026717</v>
+        <v>24.9163876693482</v>
       </c>
       <c r="Y9" t="n">
-        <v>184.1928326709028</v>
+        <v>185.0751874222269</v>
       </c>
       <c r="Z9" t="n">
-        <v>70.4094776861272</v>
+        <v>70.4053998632946</v>
       </c>
       <c r="AA9" t="n">
-        <v>14435.60053423707</v>
+        <v>30148.8814913157</v>
       </c>
       <c r="AB9" t="n">
-        <v>2582842.432396685</v>
+        <v>5685966.76076117</v>
       </c>
       <c r="AC9" t="n">
-        <v>74.31305937861049</v>
+        <v>76.10822707993759</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>1.073268398268398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.3</v>
+        <v>26.50992063492064</v>
       </c>
       <c r="D10" t="n">
-        <v>185.45</v>
+        <v>181.7936507936508</v>
       </c>
       <c r="E10" t="n">
-        <v>80.325</v>
+        <v>78.32738095238096</v>
       </c>
       <c r="F10" t="n">
-        <v>101650</v>
+        <v>40069.44444444445</v>
       </c>
       <c r="G10" t="n">
-        <v>34250000</v>
+        <v>20811507.93650794</v>
       </c>
       <c r="H10" t="n">
-        <v>84.3</v>
+        <v>81.01587301587301</v>
       </c>
       <c r="I10" t="n">
-        <v>2.125</v>
+        <v>2.337301587301587</v>
       </c>
       <c r="J10" t="n">
-        <v>26.91666666666667</v>
+        <v>29.32727272727273</v>
       </c>
       <c r="K10" t="n">
-        <v>181.9333333333333</v>
+        <v>182.6064935064935</v>
       </c>
       <c r="L10" t="n">
-        <v>79.33333333333333</v>
+        <v>84.18961038961038</v>
       </c>
       <c r="M10" t="n">
-        <v>49416.66666666666</v>
+        <v>112436.3636363636</v>
       </c>
       <c r="N10" t="n">
-        <v>21821666.66666667</v>
+        <v>41988311.68831169</v>
       </c>
       <c r="O10" t="n">
-        <v>82.03333333333335</v>
+        <v>85.12987012987013</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>3.32987012987013</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.01805555555556</v>
+        <v>25.24310180212436</v>
       </c>
       <c r="R10" t="n">
-        <v>184.2569444444445</v>
+        <v>179.5576799140709</v>
       </c>
       <c r="S10" t="n">
-        <v>77.13333333333333</v>
+        <v>76.20569280343716</v>
       </c>
       <c r="T10" t="n">
-        <v>76113.88888888889</v>
+        <v>35859.08222938298</v>
       </c>
       <c r="U10" t="n">
-        <v>16960833.33333333</v>
+        <v>18635974.6091419</v>
       </c>
       <c r="V10" t="n">
-        <v>80.9375</v>
+        <v>80.99550065640291</v>
       </c>
       <c r="W10" t="n">
-        <v>1.658333333333333</v>
+        <v>1.820915383697339</v>
       </c>
       <c r="X10" t="n">
-        <v>26.7264594356261</v>
+        <v>27.87959866220736</v>
       </c>
       <c r="Y10" t="n">
-        <v>182.6929497354497</v>
+        <v>184.5150302595955</v>
       </c>
       <c r="Z10" t="n">
-        <v>75.4953130511464</v>
+        <v>79.87611482720179</v>
       </c>
       <c r="AA10" t="n">
-        <v>38591.65784832452</v>
+        <v>87769.23076923077</v>
       </c>
       <c r="AB10" t="n">
-        <v>11053073.74338624</v>
+        <v>26452578.03790412</v>
       </c>
       <c r="AC10" t="n">
-        <v>79.53869047619048</v>
+        <v>81.74673514890905</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.588236331569665</v>
+        <v>2.386765408504539</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>24.92467532467532</v>
+        <v>25.64880952380952</v>
       </c>
       <c r="D11" t="n">
-        <v>184.9142857142857</v>
+        <v>183.7420634920635</v>
       </c>
       <c r="E11" t="n">
-        <v>70.13766233766235</v>
+        <v>72.96825396825396</v>
       </c>
       <c r="F11" t="n">
-        <v>22077.92207792207</v>
+        <v>12521.8253968254</v>
       </c>
       <c r="G11" t="n">
-        <v>3036753.246753247</v>
+        <v>4750595.238095238</v>
       </c>
       <c r="H11" t="n">
-        <v>74.83896103896105</v>
+        <v>77.01587301587301</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>1.017857142857143</v>
       </c>
       <c r="J11" t="n">
-        <v>27.72550505050505</v>
+        <v>26.10618686868687</v>
       </c>
       <c r="K11" t="n">
-        <v>182.720202020202</v>
+        <v>183.8183080808081</v>
       </c>
       <c r="L11" t="n">
-        <v>79.59267676767678</v>
+        <v>72.47941919191919</v>
       </c>
       <c r="M11" t="n">
-        <v>102062.3737373737</v>
+        <v>23147.47474747475</v>
       </c>
       <c r="N11" t="n">
-        <v>24076262.62626263</v>
+        <v>5648926.767676767</v>
       </c>
       <c r="O11" t="n">
-        <v>81.21262626262626</v>
+        <v>76.8433080808081</v>
       </c>
       <c r="P11" t="n">
-        <v>1.981313131313131</v>
+        <v>1.212121212121212</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.49716911108216</v>
+        <v>25.62062461348176</v>
       </c>
       <c r="R11" t="n">
-        <v>183.4193794792164</v>
+        <v>183.5919913419914</v>
       </c>
       <c r="S11" t="n">
-        <v>68.59531562036997</v>
+        <v>70.59554730983302</v>
       </c>
       <c r="T11" t="n">
-        <v>20783.3313511885</v>
+        <v>10433.82807668522</v>
       </c>
       <c r="U11" t="n">
-        <v>2687006.795288045</v>
+        <v>3466234.384662956</v>
       </c>
       <c r="V11" t="n">
-        <v>73.78556135893092</v>
+        <v>75.3017316017316</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02994227994228</v>
+        <v>1.006493506493506</v>
       </c>
       <c r="X11" t="n">
-        <v>27.14914221580888</v>
+        <v>26.96104926638848</v>
       </c>
       <c r="Y11" t="n">
-        <v>182.4917448292448</v>
+        <v>182.6580480505859</v>
       </c>
       <c r="Z11" t="n">
-        <v>76.33929172679171</v>
+        <v>71.96593418452258</v>
       </c>
       <c r="AA11" t="n">
-        <v>83609.44163860829</v>
+        <v>33263.24480078073</v>
       </c>
       <c r="AB11" t="n">
-        <v>14386408.47963765</v>
+        <v>6169855.452131186</v>
       </c>
       <c r="AC11" t="n">
-        <v>78.40341109507777</v>
+        <v>76.02200483261747</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.716175645342312</v>
+        <v>1.288089849055911</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.41666666666667</v>
+        <v>26.19580176767677</v>
       </c>
       <c r="D12" t="n">
-        <v>183.2003968253968</v>
+        <v>185.7599116161616</v>
       </c>
       <c r="E12" t="n">
-        <v>72.92261904761905</v>
+        <v>71.92900883838385</v>
       </c>
       <c r="F12" t="n">
-        <v>11728.1746031746</v>
+        <v>15295.42297979798</v>
       </c>
       <c r="G12" t="n">
-        <v>6035119.047619047</v>
+        <v>3460310.132575757</v>
       </c>
       <c r="H12" t="n">
-        <v>77.8015873015873</v>
+        <v>75.36392045454545</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>26.2</v>
+        <v>26.13181818181818</v>
       </c>
       <c r="K12" t="n">
-        <v>183.5851851851852</v>
+        <v>185.0954545454545</v>
       </c>
       <c r="L12" t="n">
-        <v>76.21296296296298</v>
+        <v>72.16931818181818</v>
       </c>
       <c r="M12" t="n">
-        <v>39390.74074074074</v>
+        <v>17896.59090909091</v>
       </c>
       <c r="N12" t="n">
-        <v>12332037.03703704</v>
+        <v>4075113.636363637</v>
       </c>
       <c r="O12" t="n">
-        <v>80.21666666666665</v>
+        <v>75.69886363636364</v>
       </c>
       <c r="P12" t="n">
-        <v>1.537037037037037</v>
+        <v>1.068181818181818</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.26211634751367</v>
+        <v>26.29553069927784</v>
       </c>
       <c r="R12" t="n">
-        <v>182.0958037113481</v>
+        <v>184.2339822093111</v>
       </c>
       <c r="S12" t="n">
-        <v>68.41095870121929</v>
+        <v>70.28452603325672</v>
       </c>
       <c r="T12" t="n">
-        <v>10113.5090585942</v>
+        <v>14416.18696465307</v>
       </c>
       <c r="U12" t="n">
-        <v>2837240.174578603</v>
+        <v>2415782.963718998</v>
       </c>
       <c r="V12" t="n">
-        <v>74.68065779918204</v>
+        <v>74.16469180093679</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>24.52535395763656</v>
+        <v>26.95739532019704</v>
       </c>
       <c r="Y12" t="n">
-        <v>181.72211352657</v>
+        <v>183.1566829004329</v>
       </c>
       <c r="Z12" t="n">
-        <v>74.96061408398366</v>
+        <v>70.56110240334378</v>
       </c>
       <c r="AA12" t="n">
-        <v>41001.35358602749</v>
+        <v>18437.61456933871</v>
       </c>
       <c r="AB12" t="n">
-        <v>11011912.78799703</v>
+        <v>2708801.616845798</v>
       </c>
       <c r="AC12" t="n">
-        <v>80.01813823857303</v>
+        <v>74.55040826989102</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.387885544407284</v>
+        <v>1.02056277056277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.37020202020202</v>
+        <v>27.06527777777778</v>
       </c>
       <c r="D13" t="n">
-        <v>183.6257575757576</v>
+        <v>185.8309027777778</v>
       </c>
       <c r="E13" t="n">
-        <v>70.45454545454545</v>
+        <v>75.00069444444443</v>
       </c>
       <c r="F13" t="n">
-        <v>10123.9898989899</v>
+        <v>38775.69444444445</v>
       </c>
       <c r="G13" t="n">
-        <v>2617907.196969697</v>
+        <v>10118194.44444444</v>
       </c>
       <c r="H13" t="n">
-        <v>74.53989898989899</v>
+        <v>77.98506944444443</v>
       </c>
       <c r="I13" t="n">
-        <v>1.061616161616162</v>
+        <v>1.202083333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>26.61948051948052</v>
+        <v>28.5</v>
       </c>
       <c r="K13" t="n">
-        <v>186.6610389610389</v>
+        <v>181.2222222222222</v>
       </c>
       <c r="L13" t="n">
-        <v>77.96753246753246</v>
+        <v>74.05555555555556</v>
       </c>
       <c r="M13" t="n">
-        <v>54019.48051948052</v>
+        <v>23388.88888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>17721818.18181818</v>
+        <v>5341666.666666666</v>
       </c>
       <c r="O13" t="n">
-        <v>81.41428571428571</v>
+        <v>76.11111111111111</v>
       </c>
       <c r="P13" t="n">
-        <v>1.681818181818182</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="Q13" t="n">
-        <v>25.51702873785253</v>
+        <v>24.9163876693482</v>
       </c>
       <c r="R13" t="n">
-        <v>183.5135440297053</v>
+        <v>185.0751874222269</v>
       </c>
       <c r="S13" t="n">
-        <v>68.20499907542241</v>
+        <v>70.4053998632946</v>
       </c>
       <c r="T13" t="n">
-        <v>13400.56312553452</v>
+        <v>30148.8814913157</v>
       </c>
       <c r="U13" t="n">
-        <v>2064685.998593321</v>
+        <v>5685966.76076117</v>
       </c>
       <c r="V13" t="n">
-        <v>73.73253931105761</v>
+        <v>76.10822707993759</v>
       </c>
       <c r="W13" t="n">
-        <v>1.013157894736842</v>
+        <v>1.073268398268398</v>
       </c>
       <c r="X13" t="n">
-        <v>24.79533289581748</v>
+        <v>28.37981975398856</v>
       </c>
       <c r="Y13" t="n">
-        <v>185.4031051134295</v>
+        <v>182.3668345599109</v>
       </c>
       <c r="Z13" t="n">
-        <v>71.8372659631241</v>
+        <v>72.79283278528803</v>
       </c>
       <c r="AA13" t="n">
-        <v>38633.22250803742</v>
+        <v>23880.77839831585</v>
       </c>
       <c r="AB13" t="n">
-        <v>11225391.0515682</v>
+        <v>4812961.227969448</v>
       </c>
       <c r="AC13" t="n">
-        <v>77.97182115232997</v>
+        <v>74.09159837848183</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47235687093003</v>
+        <v>1.266176035631644</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>26.26818181818182</v>
+        <v>27.72528409090909</v>
       </c>
       <c r="D14" t="n">
-        <v>184.9931818181818</v>
+        <v>182.7988636363636</v>
       </c>
       <c r="E14" t="n">
-        <v>72.1693181818182</v>
+        <v>79.55312499999999</v>
       </c>
       <c r="F14" t="n">
-        <v>17737.5</v>
+        <v>101933.8068181818</v>
       </c>
       <c r="G14" t="n">
-        <v>4074829.545454545</v>
+        <v>23893750</v>
       </c>
       <c r="H14" t="n">
-        <v>75.5625</v>
+        <v>81.18238636363637</v>
       </c>
       <c r="I14" t="n">
-        <v>1.056818181818182</v>
+        <v>1.967613636363636</v>
       </c>
       <c r="J14" t="n">
-        <v>27.25902777777778</v>
+        <v>25.50694444444445</v>
       </c>
       <c r="K14" t="n">
-        <v>185.7902777777778</v>
+        <v>183.212962962963</v>
       </c>
       <c r="L14" t="n">
-        <v>75.21319444444444</v>
+        <v>73.01388888888889</v>
       </c>
       <c r="M14" t="n">
-        <v>39669.44444444445</v>
+        <v>11807.87037037037</v>
       </c>
       <c r="N14" t="n">
-        <v>10381006.94444444</v>
+        <v>6051388.888888888</v>
       </c>
       <c r="O14" t="n">
-        <v>77.90069444444444</v>
+        <v>77.78935185185185</v>
       </c>
       <c r="P14" t="n">
-        <v>1.195833333333333</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.86646939427112</v>
+        <v>27.25707070707071</v>
       </c>
       <c r="R14" t="n">
-        <v>183.6026088263588</v>
+        <v>182.4460700757576</v>
       </c>
       <c r="S14" t="n">
-        <v>70.44480610704748</v>
+        <v>76.60194128787879</v>
       </c>
       <c r="T14" t="n">
-        <v>17858.54049526463</v>
+        <v>85810.62184343433</v>
       </c>
       <c r="U14" t="n">
-        <v>2645283.098327279</v>
+        <v>15169233.34911616</v>
       </c>
       <c r="V14" t="n">
-        <v>74.59226012174288</v>
+        <v>78.61455176767677</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0251924001924</v>
+        <v>1.764030934343434</v>
       </c>
       <c r="X14" t="n">
-        <v>24.55559221480274</v>
+        <v>24.44071422428621</v>
       </c>
       <c r="Y14" t="n">
-        <v>184.9365510585905</v>
+        <v>182.1980569530444</v>
       </c>
       <c r="Z14" t="n">
-        <v>69.91505895420369</v>
+        <v>68.56649520553836</v>
       </c>
       <c r="AA14" t="n">
-        <v>29163.08603677024</v>
+        <v>10211.03102425181</v>
       </c>
       <c r="AB14" t="n">
-        <v>5222671.306215715</v>
+        <v>2868110.474178706</v>
       </c>
       <c r="AC14" t="n">
-        <v>76.08152253448306</v>
+        <v>74.56435113519092</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.060768398268398</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>26.44907407407408</v>
+        <v>26.38658008658009</v>
       </c>
       <c r="D15" t="n">
-        <v>181.7592592592593</v>
+        <v>185.8978354978355</v>
       </c>
       <c r="E15" t="n">
-        <v>78.27777777777779</v>
+        <v>76.19307359307358</v>
       </c>
       <c r="F15" t="n">
-        <v>40560.18518518519</v>
+        <v>46877.05627705628</v>
       </c>
       <c r="G15" t="n">
-        <v>21134259.25925926</v>
+        <v>10503354.97835498</v>
       </c>
       <c r="H15" t="n">
-        <v>81.06018518518518</v>
+        <v>79.13405483405484</v>
       </c>
       <c r="I15" t="n">
-        <v>2.331018518518519</v>
+        <v>1.506926406926407</v>
       </c>
       <c r="J15" t="n">
-        <v>29.36666666666666</v>
+        <v>25.85984848484848</v>
       </c>
       <c r="K15" t="n">
-        <v>182.480303030303</v>
+        <v>185.3275974025974</v>
       </c>
       <c r="L15" t="n">
-        <v>84.25151515151515</v>
+        <v>82.2504329004329</v>
       </c>
       <c r="M15" t="n">
-        <v>113145.4545454545</v>
+        <v>140371.9696969697</v>
       </c>
       <c r="N15" t="n">
-        <v>42198484.84848485</v>
+        <v>45146158.00865801</v>
       </c>
       <c r="O15" t="n">
-        <v>85.10606060606061</v>
+        <v>84.99253246753246</v>
       </c>
       <c r="P15" t="n">
-        <v>3.33939393939394</v>
+        <v>2.791233766233766</v>
       </c>
       <c r="Q15" t="n">
-        <v>25.40398913951546</v>
+        <v>24.38582224194025</v>
       </c>
       <c r="R15" t="n">
-        <v>179.7061821219716</v>
+        <v>184.9048757763975</v>
       </c>
       <c r="S15" t="n">
-        <v>76.50849345586188</v>
+        <v>73.2984575569358</v>
       </c>
       <c r="T15" t="n">
-        <v>37094.85519353941</v>
+        <v>39281.2230109435</v>
       </c>
       <c r="U15" t="n">
-        <v>19655859.26622111</v>
+        <v>7256237.651582373</v>
       </c>
       <c r="V15" t="n">
-        <v>81.13363965469229</v>
+        <v>78.62376220053238</v>
       </c>
       <c r="W15" t="n">
-        <v>1.874401280980228</v>
+        <v>1.184736764270926</v>
       </c>
       <c r="X15" t="n">
-        <v>27.71460423634337</v>
+        <v>24.12794535746481</v>
       </c>
       <c r="Y15" t="n">
-        <v>184.1878251579339</v>
+        <v>182.6073043661144</v>
       </c>
       <c r="Z15" t="n">
-        <v>79.75401802303976</v>
+        <v>77.88453118201402</v>
       </c>
       <c r="AA15" t="n">
-        <v>87085.84169453736</v>
+        <v>110722.0783030852</v>
       </c>
       <c r="AB15" t="n">
-        <v>26746848.29059829</v>
+        <v>28448171.74816031</v>
       </c>
       <c r="AC15" t="n">
-        <v>81.75524897807507</v>
+        <v>83.21827356472666</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.364269788182832</v>
+        <v>1.743444960836265</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26.61948051948052</v>
+      </c>
+      <c r="D16" t="n">
+        <v>186.6610389610389</v>
+      </c>
+      <c r="E16" t="n">
+        <v>77.96753246753246</v>
+      </c>
+      <c r="F16" t="n">
+        <v>54019.48051948052</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17721818.18181818</v>
+      </c>
+      <c r="H16" t="n">
+        <v>81.41428571428571</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25.64880952380952</v>
+      </c>
+      <c r="K16" t="n">
+        <v>183.7420634920635</v>
+      </c>
+      <c r="L16" t="n">
+        <v>72.96825396825396</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12521.8253968254</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4750595.238095238</v>
+      </c>
+      <c r="O16" t="n">
+        <v>77.01587301587301</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.017857142857143</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>24.79533289581748</v>
+      </c>
+      <c r="R16" t="n">
+        <v>185.4031051134295</v>
+      </c>
+      <c r="S16" t="n">
+        <v>71.8372659631241</v>
+      </c>
+      <c r="T16" t="n">
+        <v>38633.22250803742</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11225391.0515682</v>
+      </c>
+      <c r="V16" t="n">
+        <v>77.97182115232997</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.47235687093003</v>
+      </c>
+      <c r="X16" t="n">
+        <v>25.62062461348176</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>183.5919913419914</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>70.59554730983302</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>10433.82807668522</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3466234.384662956</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>75.3017316017316</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.006493506493506</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>23.78373015873016</v>
+      </c>
+      <c r="D17" t="n">
+        <v>184.6817460317461</v>
+      </c>
+      <c r="E17" t="n">
+        <v>72.74166666666666</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25919.44444444445</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5530119.047619048</v>
+      </c>
+      <c r="H17" t="n">
+        <v>78.38095238095239</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.98571428571429</v>
+      </c>
+      <c r="K17" t="n">
+        <v>184.9831168831169</v>
+      </c>
+      <c r="L17" t="n">
+        <v>70.11948051948052</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21584.41558441558</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2973409.09090909</v>
+      </c>
+      <c r="O17" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23.89675889328063</v>
+      </c>
+      <c r="R17" t="n">
+        <v>182.2310954263128</v>
+      </c>
+      <c r="S17" t="n">
+        <v>68.76753811405986</v>
+      </c>
+      <c r="T17" t="n">
+        <v>22130.08469791078</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2924766.233766234</v>
+      </c>
+      <c r="V17" t="n">
+        <v>74.73669678147938</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>24.37216911108216</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>183.6204664357382</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>68.92140257689171</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>21870.19754098558</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2886463.317027176</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>74.12251788067006</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.046246627768367</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>26.82857142857143</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181.8428571428572</v>
+      </c>
+      <c r="E18" t="n">
+        <v>79.37142857142855</v>
+      </c>
+      <c r="F18" t="n">
+        <v>49471.42857142857</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22147142.85714286</v>
+      </c>
+      <c r="H18" t="n">
+        <v>82.15714285714286</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>26.99545454545454</v>
+      </c>
+      <c r="K18" t="n">
+        <v>184.3931818181818</v>
+      </c>
+      <c r="L18" t="n">
+        <v>73.04090909090908</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31746.59090909091</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4460738.636363637</v>
+      </c>
+      <c r="O18" t="n">
+        <v>76.14772727272728</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.126136363636364</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>26.84007082059877</v>
+      </c>
+      <c r="R18" t="n">
+        <v>182.7243916987084</v>
+      </c>
+      <c r="S18" t="n">
+        <v>75.53635528607579</v>
+      </c>
+      <c r="T18" t="n">
+        <v>38823.90548489927</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10868628.42600809</v>
+      </c>
+      <c r="V18" t="n">
+        <v>79.43688997338066</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.59737027178021</v>
+      </c>
+      <c r="X18" t="n">
+        <v>25.7959744349218</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>184.3917975153501</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>68.93406213669371</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>29446.78359652044</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2801124.75024975</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>73.36028683305</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.13320439794124</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>26.10618686868687</v>
+      </c>
+      <c r="D19" t="n">
+        <v>183.8183080808081</v>
+      </c>
+      <c r="E19" t="n">
+        <v>72.47941919191919</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23147.47474747475</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5648926.767676767</v>
+      </c>
+      <c r="H19" t="n">
+        <v>76.8433080808081</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.212121212121212</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26.15324675324675</v>
+      </c>
+      <c r="K19" t="n">
+        <v>183.5246753246753</v>
+      </c>
+      <c r="L19" t="n">
+        <v>70.51948051948052</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10205.1948051948</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2728798.701298702</v>
+      </c>
+      <c r="O19" t="n">
+        <v>74.82337662337662</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.054545454545454</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>26.96104926638848</v>
+      </c>
+      <c r="R19" t="n">
+        <v>182.6580480505859</v>
+      </c>
+      <c r="S19" t="n">
+        <v>71.96593418452258</v>
+      </c>
+      <c r="T19" t="n">
+        <v>33263.24480078073</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6169855.452131186</v>
+      </c>
+      <c r="V19" t="n">
+        <v>76.02200483261747</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.288089849055911</v>
+      </c>
+      <c r="X19" t="n">
+        <v>25.666077956042</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>183.3087119737986</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>68.25684104860305</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>13532.97439910712</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2064490.76530966</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>73.72440582917862</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.007518796992481</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>29.32727272727273</v>
+      </c>
+      <c r="D20" t="n">
+        <v>182.6064935064935</v>
+      </c>
+      <c r="E20" t="n">
+        <v>84.18961038961038</v>
+      </c>
+      <c r="F20" t="n">
+        <v>112436.3636363636</v>
+      </c>
+      <c r="G20" t="n">
+        <v>41988311.68831169</v>
+      </c>
+      <c r="H20" t="n">
+        <v>85.12987012987013</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.32987012987013</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="L20" t="n">
+        <v>80.325</v>
+      </c>
+      <c r="M20" t="n">
+        <v>101650</v>
+      </c>
+      <c r="N20" t="n">
+        <v>34250000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>27.87959866220736</v>
+      </c>
+      <c r="R20" t="n">
+        <v>184.5150302595955</v>
+      </c>
+      <c r="S20" t="n">
+        <v>79.87611482720179</v>
+      </c>
+      <c r="T20" t="n">
+        <v>87769.23076923077</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26452578.03790412</v>
+      </c>
+      <c r="V20" t="n">
+        <v>81.74673514890905</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.386765408504539</v>
+      </c>
+      <c r="X20" t="n">
+        <v>25.98950216450217</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>184.0384199134199</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>77.19220779220778</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>77253.46320346321</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>17140454.54545454</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>81.01136363636364</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.668181818181818</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>25.9968253968254</v>
+      </c>
+      <c r="D21" t="n">
+        <v>183.3746031746032</v>
+      </c>
+      <c r="E21" t="n">
+        <v>76.15079365079364</v>
+      </c>
+      <c r="F21" t="n">
+        <v>39747.61904761905</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12571904.76190476</v>
+      </c>
+      <c r="H21" t="n">
+        <v>80.2968253968254</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.523809523809524</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.50992063492064</v>
+      </c>
+      <c r="K21" t="n">
+        <v>181.7936507936508</v>
+      </c>
+      <c r="L21" t="n">
+        <v>78.32738095238096</v>
+      </c>
+      <c r="M21" t="n">
+        <v>40069.44444444445</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20811507.93650794</v>
+      </c>
+      <c r="O21" t="n">
+        <v>81.01587301587301</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.337301587301587</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>24.65744624940277</v>
+      </c>
+      <c r="R21" t="n">
+        <v>181.8760973084886</v>
+      </c>
+      <c r="S21" t="n">
+        <v>75.06624064341456</v>
+      </c>
+      <c r="T21" t="n">
+        <v>41072.58878802357</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10982175.24685459</v>
+      </c>
+      <c r="V21" t="n">
+        <v>80.00840420449117</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.382473323777672</v>
+      </c>
+      <c r="X21" t="n">
+        <v>25.24310180212436</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>179.5576799140709</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>76.20569280343716</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>35859.08222938298</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>18635974.6091419</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>80.99550065640291</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.820915383697339</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.13181818181818</v>
+      </c>
+      <c r="D22" t="n">
+        <v>185.0954545454545</v>
+      </c>
+      <c r="E22" t="n">
+        <v>72.16931818181818</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17896.59090909091</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4075113.636363637</v>
+      </c>
+      <c r="H22" t="n">
+        <v>75.69886363636364</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.068181818181818</v>
+      </c>
+      <c r="J22" t="n">
+        <v>26.38658008658009</v>
+      </c>
+      <c r="K22" t="n">
+        <v>185.8978354978355</v>
+      </c>
+      <c r="L22" t="n">
+        <v>76.19307359307358</v>
+      </c>
+      <c r="M22" t="n">
+        <v>46877.05627705628</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10503354.97835498</v>
+      </c>
+      <c r="O22" t="n">
+        <v>79.13405483405484</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.506926406926407</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>26.95739532019704</v>
+      </c>
+      <c r="R22" t="n">
+        <v>183.1566829004329</v>
+      </c>
+      <c r="S22" t="n">
+        <v>70.56110240334378</v>
+      </c>
+      <c r="T22" t="n">
+        <v>18437.61456933871</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2708801.616845798</v>
+      </c>
+      <c r="V22" t="n">
+        <v>74.55040826989102</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.02056277056277</v>
+      </c>
+      <c r="X22" t="n">
+        <v>24.38582224194025</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>184.9048757763975</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>73.2984575569358</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>39281.2230109435</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7256237.651582373</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>78.62376220053238</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.184736764270926</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25.50694444444445</v>
+      </c>
+      <c r="D23" t="n">
+        <v>183.212962962963</v>
+      </c>
+      <c r="E23" t="n">
+        <v>73.01388888888889</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11807.87037037037</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6051388.888888888</v>
+      </c>
+      <c r="H23" t="n">
+        <v>77.78935185185185</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>25.64880952380952</v>
+      </c>
+      <c r="K23" t="n">
+        <v>183.7420634920635</v>
+      </c>
+      <c r="L23" t="n">
+        <v>72.96825396825396</v>
+      </c>
+      <c r="M23" t="n">
+        <v>12521.8253968254</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4750595.238095238</v>
+      </c>
+      <c r="O23" t="n">
+        <v>77.01587301587301</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.017857142857143</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>24.44071422428621</v>
+      </c>
+      <c r="R23" t="n">
+        <v>182.1980569530444</v>
+      </c>
+      <c r="S23" t="n">
+        <v>68.56649520553836</v>
+      </c>
+      <c r="T23" t="n">
+        <v>10211.03102425181</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2868110.474178706</v>
+      </c>
+      <c r="V23" t="n">
+        <v>74.56435113519092</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>25.62062461348176</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>183.5919913419914</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>70.59554730983302</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>10433.82807668522</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3466234.384662956</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>75.3017316017316</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.006493506493506</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25.85984848484848</v>
+      </c>
+      <c r="D24" t="n">
+        <v>185.3275974025974</v>
+      </c>
+      <c r="E24" t="n">
+        <v>82.2504329004329</v>
+      </c>
+      <c r="F24" t="n">
+        <v>140371.9696969697</v>
+      </c>
+      <c r="G24" t="n">
+        <v>45146158.00865801</v>
+      </c>
+      <c r="H24" t="n">
+        <v>84.99253246753246</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.791233766233766</v>
+      </c>
+      <c r="J24" t="n">
+        <v>27.72528409090909</v>
+      </c>
+      <c r="K24" t="n">
+        <v>182.7988636363636</v>
+      </c>
+      <c r="L24" t="n">
+        <v>79.55312499999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>101933.8068181818</v>
+      </c>
+      <c r="N24" t="n">
+        <v>23893750</v>
+      </c>
+      <c r="O24" t="n">
+        <v>81.18238636363637</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.967613636363636</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>24.12794535746481</v>
+      </c>
+      <c r="R24" t="n">
+        <v>182.6073043661144</v>
+      </c>
+      <c r="S24" t="n">
+        <v>77.88453118201402</v>
+      </c>
+      <c r="T24" t="n">
+        <v>110722.0783030852</v>
+      </c>
+      <c r="U24" t="n">
+        <v>28448171.74816031</v>
+      </c>
+      <c r="V24" t="n">
+        <v>83.21827356472666</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.743444960836265</v>
+      </c>
+      <c r="X24" t="n">
+        <v>27.25707070707071</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>182.4460700757576</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>76.60194128787879</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>85810.62184343433</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>15169233.34911616</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>78.61455176767677</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.764030934343434</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AT29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,6 +574,86 @@
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -606,22 +686,22 @@
         <v>1.444444444444444</v>
       </c>
       <c r="J2" t="n">
-        <v>23.78373015873016</v>
+        <v>23.84027777777778</v>
       </c>
       <c r="K2" t="n">
-        <v>184.6817460317461</v>
+        <v>184.6657407407407</v>
       </c>
       <c r="L2" t="n">
-        <v>72.74166666666666</v>
+        <v>72.77268518518518</v>
       </c>
       <c r="M2" t="n">
-        <v>25919.44444444445</v>
+        <v>25998.61111111111</v>
       </c>
       <c r="N2" t="n">
-        <v>5530119.047619048</v>
+        <v>5588842.592592593</v>
       </c>
       <c r="O2" t="n">
-        <v>78.38095238095239</v>
+        <v>78.4074074074074</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -648,26 +728,58 @@
         <v>1.266176035631644</v>
       </c>
       <c r="X2" t="n">
-        <v>23.89675889328063</v>
+        <v>23.9230303030303</v>
       </c>
       <c r="Y2" t="n">
-        <v>182.2310954263128</v>
+        <v>182.5377272727273</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.76753811405986</v>
+        <v>68.77227272727272</v>
       </c>
       <c r="AA2" t="n">
-        <v>22130.08469791078</v>
+        <v>22137.27272727272</v>
       </c>
       <c r="AB2" t="n">
-        <v>2924766.233766234</v>
+        <v>2903893.939393939</v>
       </c>
       <c r="AC2" t="n">
-        <v>74.73669678147938</v>
+        <v>74.7580303030303</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
+      <c r="AE2" t="n">
+        <v>29.83333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>94.66666666666667</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>29333.33333333333</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2666666.666666667</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>94.83333333333333</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -679,25 +791,25 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.99545454545454</v>
+        <v>26.92987012987013</v>
       </c>
       <c r="D3" t="n">
-        <v>184.3931818181818</v>
+        <v>184.4103896103896</v>
       </c>
       <c r="E3" t="n">
-        <v>73.04090909090908</v>
+        <v>72.98181818181818</v>
       </c>
       <c r="F3" t="n">
-        <v>31746.59090909091</v>
+        <v>31190.90909090909</v>
       </c>
       <c r="G3" t="n">
-        <v>4460738.636363637</v>
+        <v>4401233.766233766</v>
       </c>
       <c r="H3" t="n">
-        <v>76.14772727272728</v>
+        <v>76.05194805194806</v>
       </c>
       <c r="I3" t="n">
-        <v>1.126136363636364</v>
+        <v>1.105194805194805</v>
       </c>
       <c r="J3" t="n">
         <v>26.38658008658009</v>
@@ -721,25 +833,25 @@
         <v>1.506926406926407</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.7959744349218</v>
+        <v>25.58428824308524</v>
       </c>
       <c r="R3" t="n">
-        <v>184.3917975153501</v>
+        <v>184.5033241445271</v>
       </c>
       <c r="S3" t="n">
-        <v>68.93406213669371</v>
+        <v>68.81353133082457</v>
       </c>
       <c r="T3" t="n">
-        <v>29446.78359652044</v>
+        <v>29312.19712618209</v>
       </c>
       <c r="U3" t="n">
-        <v>2801124.75024975</v>
+        <v>2826285.428856857</v>
       </c>
       <c r="V3" t="n">
-        <v>73.36028683305</v>
+        <v>73.4435024123746</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13320439794124</v>
+        <v>1.136360581774116</v>
       </c>
       <c r="X3" t="n">
         <v>24.38582224194025</v>
@@ -762,6 +874,22 @@
       <c r="AD3" t="n">
         <v>1.184736764270926</v>
       </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -773,25 +901,25 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.85984848484848</v>
+        <v>25.88194444444444</v>
       </c>
       <c r="D4" t="n">
-        <v>185.3275974025974</v>
+        <v>185.7458333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>82.2504329004329</v>
+        <v>82.35277777777777</v>
       </c>
       <c r="F4" t="n">
-        <v>140371.9696969697</v>
+        <v>140843.0555555556</v>
       </c>
       <c r="G4" t="n">
-        <v>45146158.00865801</v>
+        <v>46132638.8888889</v>
       </c>
       <c r="H4" t="n">
-        <v>84.99253246753246</v>
+        <v>85.1125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.791233766233766</v>
+        <v>2.8625</v>
       </c>
       <c r="J4" t="n">
         <v>26.19580176767677</v>
@@ -815,25 +943,25 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.12794535746481</v>
+        <v>23.94472412916349</v>
       </c>
       <c r="R4" t="n">
-        <v>182.6073043661144</v>
+        <v>182.6327641847093</v>
       </c>
       <c r="S4" t="n">
-        <v>77.88453118201402</v>
+        <v>77.47134698507695</v>
       </c>
       <c r="T4" t="n">
-        <v>110722.0783030852</v>
+        <v>107410.6065051145</v>
       </c>
       <c r="U4" t="n">
-        <v>28448171.74816031</v>
+        <v>27244836.73649005</v>
       </c>
       <c r="V4" t="n">
-        <v>83.21827356472666</v>
+        <v>83.02737976490836</v>
       </c>
       <c r="W4" t="n">
-        <v>1.743444960836265</v>
+        <v>1.670382757339279</v>
       </c>
       <c r="X4" t="n">
         <v>26.29553069927784</v>
@@ -856,6 +984,22 @@
       <c r="AD4" t="n">
         <v>1</v>
       </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -950,6 +1094,38 @@
       <c r="AD5" t="n">
         <v>1.59737027178021</v>
       </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>74250</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21250000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>124</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -961,22 +1137,22 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.98571428571429</v>
+        <v>25.02878787878788</v>
       </c>
       <c r="D6" t="n">
-        <v>184.9831168831169</v>
+        <v>185.0560606060606</v>
       </c>
       <c r="E6" t="n">
-        <v>70.11948051948052</v>
+        <v>69.98787878787878</v>
       </c>
       <c r="F6" t="n">
-        <v>21584.41558441558</v>
+        <v>21287.87878787879</v>
       </c>
       <c r="G6" t="n">
-        <v>2973409.09090909</v>
+        <v>2915946.969696969</v>
       </c>
       <c r="H6" t="n">
-        <v>74.7</v>
+        <v>74.48333333333333</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1003,25 +1179,25 @@
         <v>1.967613636363636</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.37216911108216</v>
+        <v>24.30995151156642</v>
       </c>
       <c r="R6" t="n">
-        <v>183.6204664357382</v>
+        <v>183.8025110913931</v>
       </c>
       <c r="S6" t="n">
-        <v>68.92140257689171</v>
+        <v>69.03654799996416</v>
       </c>
       <c r="T6" t="n">
-        <v>21870.19754098558</v>
+        <v>23043.96202486265</v>
       </c>
       <c r="U6" t="n">
-        <v>2886463.317027176</v>
+        <v>2965710.823855234</v>
       </c>
       <c r="V6" t="n">
-        <v>74.12251788067006</v>
+        <v>74.21144900648007</v>
       </c>
       <c r="W6" t="n">
-        <v>1.046246627768367</v>
+        <v>1.052853288878134</v>
       </c>
       <c r="X6" t="n">
         <v>27.25707070707071</v>
@@ -1043,6 +1219,54 @@
       </c>
       <c r="AD6" t="n">
         <v>1.764030934343434</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>25.38888888888889</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>188.0111111111111</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>366.1666666666667</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>62666.66666666666</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14816666.66666667</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>384.3333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>134500</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20750000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -1076,25 +1300,25 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>25.9968253968254</v>
+        <v>25.8962962962963</v>
       </c>
       <c r="K7" t="n">
-        <v>183.3746031746032</v>
+        <v>182.987037037037</v>
       </c>
       <c r="L7" t="n">
-        <v>76.15079365079364</v>
+        <v>76.10925925925926</v>
       </c>
       <c r="M7" t="n">
-        <v>39747.61904761905</v>
+        <v>39538.8888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>12571904.76190476</v>
+        <v>12615555.55555556</v>
       </c>
       <c r="O7" t="n">
-        <v>80.2968253968254</v>
+        <v>80.29629629629629</v>
       </c>
       <c r="P7" t="n">
-        <v>1.523809523809524</v>
+        <v>1.544444444444444</v>
       </c>
       <c r="Q7" t="n">
         <v>24.44071422428621</v>
@@ -1118,25 +1342,73 @@
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>24.65744624940277</v>
+        <v>24.88702062430323</v>
       </c>
       <c r="Y7" t="n">
-        <v>181.8760973084886</v>
+        <v>182.26211352657</v>
       </c>
       <c r="Z7" t="n">
-        <v>75.06624064341456</v>
+        <v>75.37728075065031</v>
       </c>
       <c r="AA7" t="n">
-        <v>41072.58878802357</v>
+        <v>42211.35358602749</v>
       </c>
       <c r="AB7" t="n">
-        <v>10982175.24685459</v>
+        <v>11322704.45466369</v>
       </c>
       <c r="AC7" t="n">
-        <v>80.00840420449117</v>
+        <v>80.06980490523968</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.382473323777672</v>
+        <v>1.386218877740617</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>24.48571428571428</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>279.8571428571428</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>41142.85714285714</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>12807142.85714286</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>309.5714285714286</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>68000</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
@@ -1232,6 +1504,54 @@
       <c r="AD8" t="n">
         <v>1.47235687093003</v>
       </c>
+      <c r="AE8" t="n">
+        <v>25.54761904761904</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>180.5238095238095</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>208.5714285714286</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>28428.57142857143</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>8350000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>222.4285714285714</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>23.98095238095238</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>192.1285714285714</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>266.8571428571428</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>180428.5714285714</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>72114285.71428572</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>285.4285714285714</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.142857142857143</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1264,25 +1584,25 @@
         <v>1.068181818181818</v>
       </c>
       <c r="J9" t="n">
-        <v>27.06527777777778</v>
+        <v>27.03174603174603</v>
       </c>
       <c r="K9" t="n">
-        <v>185.8309027777778</v>
+        <v>185.8353174603174</v>
       </c>
       <c r="L9" t="n">
-        <v>75.00069444444443</v>
+        <v>74.90079365079364</v>
       </c>
       <c r="M9" t="n">
-        <v>38775.69444444445</v>
+        <v>38329.36507936508</v>
       </c>
       <c r="N9" t="n">
-        <v>10118194.44444444</v>
+        <v>9957936.507936507</v>
       </c>
       <c r="O9" t="n">
-        <v>77.98506944444443</v>
+        <v>77.95436507936508</v>
       </c>
       <c r="P9" t="n">
-        <v>1.202083333333333</v>
+        <v>1.202380952380953</v>
       </c>
       <c r="Q9" t="n">
         <v>26.95739532019704</v>
@@ -1306,25 +1626,73 @@
         <v>1.02056277056277</v>
       </c>
       <c r="X9" t="n">
-        <v>24.9163876693482</v>
+        <v>24.95886481939113</v>
       </c>
       <c r="Y9" t="n">
-        <v>185.0751874222269</v>
+        <v>184.9158604553341</v>
       </c>
       <c r="Z9" t="n">
-        <v>70.4053998632946</v>
+        <v>70.38168147641832</v>
       </c>
       <c r="AA9" t="n">
-        <v>30148.8814913157</v>
+        <v>29898.04143225195</v>
       </c>
       <c r="AB9" t="n">
-        <v>5685966.76076117</v>
+        <v>5682091.263999159</v>
       </c>
       <c r="AC9" t="n">
-        <v>76.10822707993759</v>
+        <v>76.09647720700352</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.073268398268398</v>
+        <v>1.07012987012987</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>35333.33333333334</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>6858333.333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>25966666.66666667</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>188.3333333333333</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1358,25 +1726,25 @@
         <v>2.337301587301587</v>
       </c>
       <c r="J10" t="n">
-        <v>29.32727272727273</v>
+        <v>29.32121212121212</v>
       </c>
       <c r="K10" t="n">
-        <v>182.6064935064935</v>
+        <v>182.5712121212121</v>
       </c>
       <c r="L10" t="n">
-        <v>84.18961038961038</v>
+        <v>84.16060606060606</v>
       </c>
       <c r="M10" t="n">
-        <v>112436.3636363636</v>
+        <v>112024.2424242424</v>
       </c>
       <c r="N10" t="n">
-        <v>41988311.68831169</v>
+        <v>41471212.12121212</v>
       </c>
       <c r="O10" t="n">
-        <v>85.12987012987013</v>
+        <v>85.07575757575758</v>
       </c>
       <c r="P10" t="n">
-        <v>3.32987012987013</v>
+        <v>3.324242424242424</v>
       </c>
       <c r="Q10" t="n">
         <v>25.24310180212436</v>
@@ -1400,25 +1768,73 @@
         <v>1.820915383697339</v>
       </c>
       <c r="X10" t="n">
-        <v>27.87959866220736</v>
+        <v>28.0551839464883</v>
       </c>
       <c r="Y10" t="n">
-        <v>184.5150302595955</v>
+        <v>184.811013563731</v>
       </c>
       <c r="Z10" t="n">
-        <v>79.87611482720179</v>
+        <v>79.97140932738758</v>
       </c>
       <c r="AA10" t="n">
-        <v>87769.23076923077</v>
+        <v>88390.18952062431</v>
       </c>
       <c r="AB10" t="n">
-        <v>26452578.03790412</v>
+        <v>26566413.5079896</v>
       </c>
       <c r="AC10" t="n">
-        <v>81.74673514890905</v>
+        <v>81.7117707172055</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.386765408504539</v>
+        <v>2.407748049052397</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>179.625</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>104500</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>35750000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>181</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>131.6666666666667</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>158333.3333333333</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>56666666.66666666</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>133.6666666666667</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -1452,25 +1868,25 @@
         <v>1.017857142857143</v>
       </c>
       <c r="J11" t="n">
-        <v>26.10618686868687</v>
+        <v>26.10836940836941</v>
       </c>
       <c r="K11" t="n">
-        <v>183.8183080808081</v>
+        <v>183.9092352092352</v>
       </c>
       <c r="L11" t="n">
-        <v>72.47941919191919</v>
+        <v>72.65180375180375</v>
       </c>
       <c r="M11" t="n">
-        <v>23147.47474747475</v>
+        <v>23415.29581529581</v>
       </c>
       <c r="N11" t="n">
-        <v>5648926.767676767</v>
+        <v>5805266.955266954</v>
       </c>
       <c r="O11" t="n">
-        <v>76.8433080808081</v>
+        <v>76.91183261183262</v>
       </c>
       <c r="P11" t="n">
-        <v>1.212121212121212</v>
+        <v>1.216450216450216</v>
       </c>
       <c r="Q11" t="n">
         <v>25.62062461348176</v>
@@ -1494,25 +1910,73 @@
         <v>1.006493506493506</v>
       </c>
       <c r="X11" t="n">
-        <v>26.96104926638848</v>
+        <v>26.95548487587255</v>
       </c>
       <c r="Y11" t="n">
-        <v>182.6580480505859</v>
+        <v>182.6416653045657</v>
       </c>
       <c r="Z11" t="n">
-        <v>71.96593418452258</v>
+        <v>71.94158711997385</v>
       </c>
       <c r="AA11" t="n">
-        <v>33263.24480078073</v>
+        <v>34157.99405803512</v>
       </c>
       <c r="AB11" t="n">
-        <v>6169855.452131186</v>
+        <v>6114575.0621759</v>
       </c>
       <c r="AC11" t="n">
-        <v>76.02200483261747</v>
+        <v>76.04462889961476</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.288089849055911</v>
+        <v>1.290284502817145</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>25.45714285714286</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>184.3214285714286</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>215.8571428571429</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>46285.71428571428</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>17400000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>225.5714285714286</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>27.725</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>179.9722222222222</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>291.8333333333333</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>89833.33333333333</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>22183333.33333333</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>302.3333333333333</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="12">
@@ -1608,6 +2072,54 @@
       <c r="AD12" t="n">
         <v>1.02056277056277</v>
       </c>
+      <c r="AE12" t="n">
+        <v>27.64285714285714</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>180.0833333333333</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>161.1428571428571</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>42571.42857142857</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>21071428.57142857</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>166.1428571428571</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>35333.33333333334</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6858333.333333333</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.666666666666667</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1619,25 +2131,25 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>27.06527777777778</v>
+        <v>27.03174603174603</v>
       </c>
       <c r="D13" t="n">
-        <v>185.8309027777778</v>
+        <v>185.8353174603174</v>
       </c>
       <c r="E13" t="n">
-        <v>75.00069444444443</v>
+        <v>74.90079365079364</v>
       </c>
       <c r="F13" t="n">
-        <v>38775.69444444445</v>
+        <v>38329.36507936508</v>
       </c>
       <c r="G13" t="n">
-        <v>10118194.44444444</v>
+        <v>9957936.507936507</v>
       </c>
       <c r="H13" t="n">
-        <v>77.98506944444443</v>
+        <v>77.95436507936508</v>
       </c>
       <c r="I13" t="n">
-        <v>1.202083333333333</v>
+        <v>1.202380952380953</v>
       </c>
       <c r="J13" t="n">
         <v>28.5</v>
@@ -1661,25 +2173,25 @@
         <v>1.444444444444444</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.9163876693482</v>
+        <v>24.95886481939113</v>
       </c>
       <c r="R13" t="n">
-        <v>185.0751874222269</v>
+        <v>184.9158604553341</v>
       </c>
       <c r="S13" t="n">
-        <v>70.4053998632946</v>
+        <v>70.38168147641832</v>
       </c>
       <c r="T13" t="n">
-        <v>30148.8814913157</v>
+        <v>29898.04143225195</v>
       </c>
       <c r="U13" t="n">
-        <v>5685966.76076117</v>
+        <v>5682091.263999159</v>
       </c>
       <c r="V13" t="n">
-        <v>76.10822707993759</v>
+        <v>76.09647720700352</v>
       </c>
       <c r="W13" t="n">
-        <v>1.073268398268398</v>
+        <v>1.07012987012987</v>
       </c>
       <c r="X13" t="n">
         <v>28.37981975398856</v>
@@ -1701,6 +2213,54 @@
       </c>
       <c r="AD13" t="n">
         <v>1.266176035631644</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>25966666.66666667</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>188.3333333333333</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>29.83333333333333</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>94.66666666666667</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>29333.33333333333</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2666666.666666667</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>94.83333333333333</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -1796,6 +2356,54 @@
       <c r="AD14" t="n">
         <v>1</v>
       </c>
+      <c r="AE14" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>134500</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>20750000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>24.48571428571428</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>279.8571428571428</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>41142.85714285714</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12807142.85714286</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>309.5714285714286</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1828,25 +2436,25 @@
         <v>1.506926406926407</v>
       </c>
       <c r="J15" t="n">
-        <v>25.85984848484848</v>
+        <v>25.88194444444444</v>
       </c>
       <c r="K15" t="n">
-        <v>185.3275974025974</v>
+        <v>185.7458333333334</v>
       </c>
       <c r="L15" t="n">
-        <v>82.2504329004329</v>
+        <v>82.35277777777777</v>
       </c>
       <c r="M15" t="n">
-        <v>140371.9696969697</v>
+        <v>140843.0555555556</v>
       </c>
       <c r="N15" t="n">
-        <v>45146158.00865801</v>
+        <v>46132638.8888889</v>
       </c>
       <c r="O15" t="n">
-        <v>84.99253246753246</v>
+        <v>85.1125</v>
       </c>
       <c r="P15" t="n">
-        <v>2.791233766233766</v>
+        <v>2.8625</v>
       </c>
       <c r="Q15" t="n">
         <v>24.38582224194025</v>
@@ -1870,25 +2478,73 @@
         <v>1.184736764270926</v>
       </c>
       <c r="X15" t="n">
-        <v>24.12794535746481</v>
+        <v>23.94472412916349</v>
       </c>
       <c r="Y15" t="n">
-        <v>182.6073043661144</v>
+        <v>182.6327641847093</v>
       </c>
       <c r="Z15" t="n">
-        <v>77.88453118201402</v>
+        <v>77.47134698507695</v>
       </c>
       <c r="AA15" t="n">
-        <v>110722.0783030852</v>
+        <v>107410.6065051145</v>
       </c>
       <c r="AB15" t="n">
-        <v>28448171.74816031</v>
+        <v>27244836.73649005</v>
       </c>
       <c r="AC15" t="n">
-        <v>83.21827356472666</v>
+        <v>83.02737976490836</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.743444960836265</v>
+        <v>1.670382757339279</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>23.57619047619048</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>183.0428571428571</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>318.5714285714286</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>188428.5714285714</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>43328571.42857143</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>339.4285714285714</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>27.90555555555556</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>185.1805555555555</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>303.1666666666667</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>424166.6666666667</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>87495833.33333333</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>313</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.166666666666666</v>
       </c>
     </row>
     <row r="16">
@@ -1984,6 +2640,54 @@
       <c r="AD16" t="n">
         <v>1.006493506493506</v>
       </c>
+      <c r="AE16" t="n">
+        <v>23.98095238095238</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>192.1285714285714</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>266.8571428571428</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>180428.5714285714</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>72114285.71428572</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>285.4285714285714</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6.142857142857143</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>25.45714285714286</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>184.3214285714286</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>215.8571428571429</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>46285.71428571428</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>17400000</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>225.5714285714286</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.857142857142857</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1995,88 +2699,136 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>23.78373015873016</v>
+        <v>23.84027777777778</v>
       </c>
       <c r="D17" t="n">
-        <v>184.6817460317461</v>
+        <v>184.6657407407407</v>
       </c>
       <c r="E17" t="n">
-        <v>72.74166666666666</v>
+        <v>72.77268518518518</v>
       </c>
       <c r="F17" t="n">
-        <v>25919.44444444445</v>
+        <v>25998.61111111111</v>
       </c>
       <c r="G17" t="n">
-        <v>5530119.047619048</v>
+        <v>5588842.592592593</v>
       </c>
       <c r="H17" t="n">
-        <v>78.38095238095239</v>
+        <v>78.4074074074074</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>24.98571428571429</v>
+        <v>25.02878787878788</v>
       </c>
       <c r="K17" t="n">
-        <v>184.9831168831169</v>
+        <v>185.0560606060606</v>
       </c>
       <c r="L17" t="n">
-        <v>70.11948051948052</v>
+        <v>69.98787878787878</v>
       </c>
       <c r="M17" t="n">
-        <v>21584.41558441558</v>
+        <v>21287.87878787879</v>
       </c>
       <c r="N17" t="n">
-        <v>2973409.09090909</v>
+        <v>2915946.969696969</v>
       </c>
       <c r="O17" t="n">
-        <v>74.7</v>
+        <v>74.48333333333333</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.89675889328063</v>
+        <v>23.9230303030303</v>
       </c>
       <c r="R17" t="n">
-        <v>182.2310954263128</v>
+        <v>182.5377272727273</v>
       </c>
       <c r="S17" t="n">
-        <v>68.76753811405986</v>
+        <v>68.77227272727272</v>
       </c>
       <c r="T17" t="n">
-        <v>22130.08469791078</v>
+        <v>22137.27272727272</v>
       </c>
       <c r="U17" t="n">
-        <v>2924766.233766234</v>
+        <v>2903893.939393939</v>
       </c>
       <c r="V17" t="n">
-        <v>74.73669678147938</v>
+        <v>74.7580303030303</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>24.37216911108216</v>
+        <v>24.30995151156642</v>
       </c>
       <c r="Y17" t="n">
-        <v>183.6204664357382</v>
+        <v>183.8025110913931</v>
       </c>
       <c r="Z17" t="n">
-        <v>68.92140257689171</v>
+        <v>69.03654799996416</v>
       </c>
       <c r="AA17" t="n">
-        <v>21870.19754098558</v>
+        <v>23043.96202486265</v>
       </c>
       <c r="AB17" t="n">
-        <v>2886463.317027176</v>
+        <v>2965710.823855234</v>
       </c>
       <c r="AC17" t="n">
-        <v>74.12251788067006</v>
+        <v>74.21144900648007</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.046246627768367</v>
+        <v>1.052853288878134</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>25.225</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>186.5222222222222</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>252.3333333333333</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>90500</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13400000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>266.6666666666667</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>25.38888888888889</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>188.0111111111111</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>366.1666666666667</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>62666.66666666666</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>14816666.66666667</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>384.3333333333333</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -2110,25 +2862,25 @@
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>26.99545454545454</v>
+        <v>26.92987012987013</v>
       </c>
       <c r="K18" t="n">
-        <v>184.3931818181818</v>
+        <v>184.4103896103896</v>
       </c>
       <c r="L18" t="n">
-        <v>73.04090909090908</v>
+        <v>72.98181818181818</v>
       </c>
       <c r="M18" t="n">
-        <v>31746.59090909091</v>
+        <v>31190.90909090909</v>
       </c>
       <c r="N18" t="n">
-        <v>4460738.636363637</v>
+        <v>4401233.766233766</v>
       </c>
       <c r="O18" t="n">
-        <v>76.14772727272728</v>
+        <v>76.05194805194806</v>
       </c>
       <c r="P18" t="n">
-        <v>1.126136363636364</v>
+        <v>1.105194805194805</v>
       </c>
       <c r="Q18" t="n">
         <v>26.84007082059877</v>
@@ -2152,25 +2904,73 @@
         <v>1.59737027178021</v>
       </c>
       <c r="X18" t="n">
-        <v>25.7959744349218</v>
+        <v>25.58428824308524</v>
       </c>
       <c r="Y18" t="n">
-        <v>184.3917975153501</v>
+        <v>184.5033241445271</v>
       </c>
       <c r="Z18" t="n">
-        <v>68.93406213669371</v>
+        <v>68.81353133082457</v>
       </c>
       <c r="AA18" t="n">
-        <v>29446.78359652044</v>
+        <v>29312.19712618209</v>
       </c>
       <c r="AB18" t="n">
-        <v>2801124.75024975</v>
+        <v>2826285.428856857</v>
       </c>
       <c r="AC18" t="n">
-        <v>73.36028683305</v>
+        <v>73.4435024123746</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13320439794124</v>
+        <v>1.136360581774116</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>74250</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>21250000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>124</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>25.75555555555556</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>184.4833333333333</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>258.6666666666667</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>136666.6666666667</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13758333.33333333</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>275.6666666666667</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.333333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -2183,25 +2983,25 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>26.10618686868687</v>
+        <v>26.10836940836941</v>
       </c>
       <c r="D19" t="n">
-        <v>183.8183080808081</v>
+        <v>183.9092352092352</v>
       </c>
       <c r="E19" t="n">
-        <v>72.47941919191919</v>
+        <v>72.65180375180375</v>
       </c>
       <c r="F19" t="n">
-        <v>23147.47474747475</v>
+        <v>23415.29581529581</v>
       </c>
       <c r="G19" t="n">
-        <v>5648926.767676767</v>
+        <v>5805266.955266954</v>
       </c>
       <c r="H19" t="n">
-        <v>76.8433080808081</v>
+        <v>76.91183261183262</v>
       </c>
       <c r="I19" t="n">
-        <v>1.212121212121212</v>
+        <v>1.216450216450216</v>
       </c>
       <c r="J19" t="n">
         <v>26.15324675324675</v>
@@ -2225,25 +3025,25 @@
         <v>1.054545454545454</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.96104926638848</v>
+        <v>26.95548487587255</v>
       </c>
       <c r="R19" t="n">
-        <v>182.6580480505859</v>
+        <v>182.6416653045657</v>
       </c>
       <c r="S19" t="n">
-        <v>71.96593418452258</v>
+        <v>71.94158711997385</v>
       </c>
       <c r="T19" t="n">
-        <v>33263.24480078073</v>
+        <v>34157.99405803512</v>
       </c>
       <c r="U19" t="n">
-        <v>6169855.452131186</v>
+        <v>6114575.0621759</v>
       </c>
       <c r="V19" t="n">
-        <v>76.02200483261747</v>
+        <v>76.04462889961476</v>
       </c>
       <c r="W19" t="n">
-        <v>1.288089849055911</v>
+        <v>1.290284502817145</v>
       </c>
       <c r="X19" t="n">
         <v>25.666077956042</v>
@@ -2265,6 +3065,54 @@
       </c>
       <c r="AD19" t="n">
         <v>1.007518796992481</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>27.725</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>179.9722222222222</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>291.8333333333333</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>89833.33333333333</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>22183333.33333333</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>302.3333333333333</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>25.54761904761904</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>180.5238095238095</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>208.5714285714286</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>28428.57142857143</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8350000</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>222.4285714285714</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.285714285714286</v>
       </c>
     </row>
     <row r="20">
@@ -2277,25 +3125,25 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29.32727272727273</v>
+        <v>29.32121212121212</v>
       </c>
       <c r="D20" t="n">
-        <v>182.6064935064935</v>
+        <v>182.5712121212121</v>
       </c>
       <c r="E20" t="n">
-        <v>84.18961038961038</v>
+        <v>84.16060606060606</v>
       </c>
       <c r="F20" t="n">
-        <v>112436.3636363636</v>
+        <v>112024.2424242424</v>
       </c>
       <c r="G20" t="n">
-        <v>41988311.68831169</v>
+        <v>41471212.12121212</v>
       </c>
       <c r="H20" t="n">
-        <v>85.12987012987013</v>
+        <v>85.07575757575758</v>
       </c>
       <c r="I20" t="n">
-        <v>3.32987012987013</v>
+        <v>3.324242424242424</v>
       </c>
       <c r="J20" t="n">
         <v>25.3</v>
@@ -2319,25 +3167,25 @@
         <v>2.125</v>
       </c>
       <c r="Q20" t="n">
-        <v>27.87959866220736</v>
+        <v>28.0551839464883</v>
       </c>
       <c r="R20" t="n">
-        <v>184.5150302595955</v>
+        <v>184.811013563731</v>
       </c>
       <c r="S20" t="n">
-        <v>79.87611482720179</v>
+        <v>79.97140932738758</v>
       </c>
       <c r="T20" t="n">
-        <v>87769.23076923077</v>
+        <v>88390.18952062431</v>
       </c>
       <c r="U20" t="n">
-        <v>26452578.03790412</v>
+        <v>26566413.5079896</v>
       </c>
       <c r="V20" t="n">
-        <v>81.74673514890905</v>
+        <v>81.7117707172055</v>
       </c>
       <c r="W20" t="n">
-        <v>2.386765408504539</v>
+        <v>2.407748049052397</v>
       </c>
       <c r="X20" t="n">
         <v>25.98950216450217</v>
@@ -2359,6 +3207,54 @@
       </c>
       <c r="AD20" t="n">
         <v>1.668181818181818</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>131.6666666666667</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>158333.3333333333</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>56666666.66666666</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>133.6666666666667</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>28.55714285714286</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>186.4690476190476</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>275.1428571428572</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>388714.2857142857</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>88714285.71428572</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>279.4285714285714</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.857142857142858</v>
       </c>
     </row>
     <row r="21">
@@ -2371,25 +3267,25 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>25.9968253968254</v>
+        <v>25.8962962962963</v>
       </c>
       <c r="D21" t="n">
-        <v>183.3746031746032</v>
+        <v>182.987037037037</v>
       </c>
       <c r="E21" t="n">
-        <v>76.15079365079364</v>
+        <v>76.10925925925926</v>
       </c>
       <c r="F21" t="n">
-        <v>39747.61904761905</v>
+        <v>39538.8888888889</v>
       </c>
       <c r="G21" t="n">
-        <v>12571904.76190476</v>
+        <v>12615555.55555556</v>
       </c>
       <c r="H21" t="n">
-        <v>80.2968253968254</v>
+        <v>80.29629629629629</v>
       </c>
       <c r="I21" t="n">
-        <v>1.523809523809524</v>
+        <v>1.544444444444444</v>
       </c>
       <c r="J21" t="n">
         <v>26.50992063492064</v>
@@ -2413,25 +3309,25 @@
         <v>2.337301587301587</v>
       </c>
       <c r="Q21" t="n">
-        <v>24.65744624940277</v>
+        <v>24.88702062430323</v>
       </c>
       <c r="R21" t="n">
-        <v>181.8760973084886</v>
+        <v>182.26211352657</v>
       </c>
       <c r="S21" t="n">
-        <v>75.06624064341456</v>
+        <v>75.37728075065031</v>
       </c>
       <c r="T21" t="n">
-        <v>41072.58878802357</v>
+        <v>42211.35358602749</v>
       </c>
       <c r="U21" t="n">
-        <v>10982175.24685459</v>
+        <v>11322704.45466369</v>
       </c>
       <c r="V21" t="n">
-        <v>80.00840420449117</v>
+        <v>80.06980490523968</v>
       </c>
       <c r="W21" t="n">
-        <v>1.382473323777672</v>
+        <v>1.386218877740617</v>
       </c>
       <c r="X21" t="n">
         <v>25.24310180212436</v>
@@ -2453,6 +3349,54 @@
       </c>
       <c r="AD21" t="n">
         <v>1.820915383697339</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>68000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>179.625</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>104500</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>35750000</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -2548,6 +3492,54 @@
       <c r="AD22" t="n">
         <v>1.184736764270926</v>
       </c>
+      <c r="AE22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>35333.33333333334</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>6858333.333333333</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>23.57619047619048</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>183.0428571428571</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>318.5714285714286</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>188428.5714285714</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>43328571.42857143</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>339.4285714285714</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.285714285714286</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2642,6 +3634,54 @@
       <c r="AD23" t="n">
         <v>1.006493506493506</v>
       </c>
+      <c r="AE23" t="n">
+        <v>24.48571428571428</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>279.8571428571428</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>41142.85714285714</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>12807142.85714286</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>309.5714285714286</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>25.45714285714286</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>184.3214285714286</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>215.8571428571429</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>46285.71428571428</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>17400000</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>225.5714285714286</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.857142857142857</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2653,25 +3693,25 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>25.85984848484848</v>
+        <v>25.88194444444444</v>
       </c>
       <c r="D24" t="n">
-        <v>185.3275974025974</v>
+        <v>185.7458333333334</v>
       </c>
       <c r="E24" t="n">
-        <v>82.2504329004329</v>
+        <v>82.35277777777777</v>
       </c>
       <c r="F24" t="n">
-        <v>140371.9696969697</v>
+        <v>140843.0555555556</v>
       </c>
       <c r="G24" t="n">
-        <v>45146158.00865801</v>
+        <v>46132638.8888889</v>
       </c>
       <c r="H24" t="n">
-        <v>84.99253246753246</v>
+        <v>85.1125</v>
       </c>
       <c r="I24" t="n">
-        <v>2.791233766233766</v>
+        <v>2.8625</v>
       </c>
       <c r="J24" t="n">
         <v>27.72528409090909</v>
@@ -2695,25 +3735,25 @@
         <v>1.967613636363636</v>
       </c>
       <c r="Q24" t="n">
-        <v>24.12794535746481</v>
+        <v>23.94472412916349</v>
       </c>
       <c r="R24" t="n">
-        <v>182.6073043661144</v>
+        <v>182.6327641847093</v>
       </c>
       <c r="S24" t="n">
-        <v>77.88453118201402</v>
+        <v>77.47134698507695</v>
       </c>
       <c r="T24" t="n">
-        <v>110722.0783030852</v>
+        <v>107410.6065051145</v>
       </c>
       <c r="U24" t="n">
-        <v>28448171.74816031</v>
+        <v>27244836.73649005</v>
       </c>
       <c r="V24" t="n">
-        <v>83.21827356472666</v>
+        <v>83.02737976490836</v>
       </c>
       <c r="W24" t="n">
-        <v>1.743444960836265</v>
+        <v>1.670382757339279</v>
       </c>
       <c r="X24" t="n">
         <v>27.25707070707071</v>
@@ -2735,6 +3775,764 @@
       </c>
       <c r="AD24" t="n">
         <v>1.764030934343434</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>27.90555555555556</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>185.1805555555555</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>303.1666666666667</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>424166.6666666667</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>87495833.33333333</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>313</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>8.166666666666666</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>134500</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>20750000</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>25.02878787878788</v>
+      </c>
+      <c r="D25" t="n">
+        <v>185.0560606060606</v>
+      </c>
+      <c r="E25" t="n">
+        <v>69.98787878787878</v>
+      </c>
+      <c r="F25" t="n">
+        <v>21287.87878787879</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2915946.969696969</v>
+      </c>
+      <c r="H25" t="n">
+        <v>74.48333333333333</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>29.32121212121212</v>
+      </c>
+      <c r="K25" t="n">
+        <v>182.5712121212121</v>
+      </c>
+      <c r="L25" t="n">
+        <v>84.16060606060606</v>
+      </c>
+      <c r="M25" t="n">
+        <v>112024.2424242424</v>
+      </c>
+      <c r="N25" t="n">
+        <v>41471212.12121212</v>
+      </c>
+      <c r="O25" t="n">
+        <v>85.07575757575758</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.324242424242424</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>24.30995151156642</v>
+      </c>
+      <c r="R25" t="n">
+        <v>183.8025110913931</v>
+      </c>
+      <c r="S25" t="n">
+        <v>69.03654799996416</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23043.96202486265</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2965710.823855234</v>
+      </c>
+      <c r="V25" t="n">
+        <v>74.21144900648007</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.052853288878134</v>
+      </c>
+      <c r="X25" t="n">
+        <v>28.0551839464883</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>184.811013563731</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>79.97140932738758</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>88390.18952062431</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>26566413.5079896</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>81.7117707172055</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.407748049052397</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>25.38888888888889</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>188.0111111111111</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>366.1666666666667</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>62666.66666666666</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>14816666.66666667</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>384.3333333333333</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>181</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>131.6666666666667</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>158333.3333333333</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>56666666.66666666</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>133.6666666666667</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.666666666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>26.15324675324675</v>
+      </c>
+      <c r="D26" t="n">
+        <v>183.5246753246753</v>
+      </c>
+      <c r="E26" t="n">
+        <v>70.51948051948052</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10205.1948051948</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2728798.701298702</v>
+      </c>
+      <c r="H26" t="n">
+        <v>74.82337662337662</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.054545454545454</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26.19580176767677</v>
+      </c>
+      <c r="K26" t="n">
+        <v>185.7599116161616</v>
+      </c>
+      <c r="L26" t="n">
+        <v>71.92900883838385</v>
+      </c>
+      <c r="M26" t="n">
+        <v>15295.42297979798</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3460310.132575757</v>
+      </c>
+      <c r="O26" t="n">
+        <v>75.36392045454545</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>25.666077956042</v>
+      </c>
+      <c r="R26" t="n">
+        <v>183.3087119737986</v>
+      </c>
+      <c r="S26" t="n">
+        <v>68.25684104860305</v>
+      </c>
+      <c r="T26" t="n">
+        <v>13532.97439910712</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2064490.76530966</v>
+      </c>
+      <c r="V26" t="n">
+        <v>73.72440582917862</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.007518796992481</v>
+      </c>
+      <c r="X26" t="n">
+        <v>26.29553069927784</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>184.2339822093111</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>70.28452603325672</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>14416.18696465307</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2415782.963718998</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>74.16469180093679</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>25.54761904761904</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>180.5238095238095</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>208.5714285714286</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>28428.57142857143</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>8350000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>222.4285714285714</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>27.64285714285714</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>180.0833333333333</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>161.1428571428571</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>42571.42857142857</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>21071428.57142857</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>166.1428571428571</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>4.142857142857143</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26.61948051948052</v>
+      </c>
+      <c r="D27" t="n">
+        <v>186.6610389610389</v>
+      </c>
+      <c r="E27" t="n">
+        <v>77.96753246753246</v>
+      </c>
+      <c r="F27" t="n">
+        <v>54019.48051948052</v>
+      </c>
+      <c r="G27" t="n">
+        <v>17721818.18181818</v>
+      </c>
+      <c r="H27" t="n">
+        <v>81.41428571428571</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26.10836940836941</v>
+      </c>
+      <c r="K27" t="n">
+        <v>183.9092352092352</v>
+      </c>
+      <c r="L27" t="n">
+        <v>72.65180375180375</v>
+      </c>
+      <c r="M27" t="n">
+        <v>23415.29581529581</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5805266.955266954</v>
+      </c>
+      <c r="O27" t="n">
+        <v>76.91183261183262</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.216450216450216</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>24.79533289581748</v>
+      </c>
+      <c r="R27" t="n">
+        <v>185.4031051134295</v>
+      </c>
+      <c r="S27" t="n">
+        <v>71.8372659631241</v>
+      </c>
+      <c r="T27" t="n">
+        <v>38633.22250803742</v>
+      </c>
+      <c r="U27" t="n">
+        <v>11225391.0515682</v>
+      </c>
+      <c r="V27" t="n">
+        <v>77.97182115232997</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.47235687093003</v>
+      </c>
+      <c r="X27" t="n">
+        <v>26.95548487587255</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>182.6416653045657</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>71.94158711997385</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>34157.99405803512</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>6114575.0621759</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>76.04462889961476</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.290284502817145</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>23.98095238095238</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>192.1285714285714</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>266.8571428571428</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>180428.5714285714</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>72114285.71428572</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>285.4285714285714</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>6.142857142857143</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>27.725</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>179.9722222222222</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>291.8333333333333</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>89833.33333333333</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>22183333.33333333</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>302.3333333333333</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="E28" t="n">
+        <v>80.325</v>
+      </c>
+      <c r="F28" t="n">
+        <v>101650</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34250000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="J28" t="n">
+        <v>23.84027777777778</v>
+      </c>
+      <c r="K28" t="n">
+        <v>184.6657407407407</v>
+      </c>
+      <c r="L28" t="n">
+        <v>72.77268518518518</v>
+      </c>
+      <c r="M28" t="n">
+        <v>25998.61111111111</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5588842.592592593</v>
+      </c>
+      <c r="O28" t="n">
+        <v>78.4074074074074</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>25.98950216450217</v>
+      </c>
+      <c r="R28" t="n">
+        <v>184.0384199134199</v>
+      </c>
+      <c r="S28" t="n">
+        <v>77.19220779220778</v>
+      </c>
+      <c r="T28" t="n">
+        <v>77253.46320346321</v>
+      </c>
+      <c r="U28" t="n">
+        <v>17140454.54545454</v>
+      </c>
+      <c r="V28" t="n">
+        <v>81.01136363636364</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.668181818181818</v>
+      </c>
+      <c r="X28" t="n">
+        <v>23.9230303030303</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>182.5377272727273</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>68.77227272727272</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>22137.27272727272</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2903893.939393939</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>74.7580303030303</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>28.55714285714286</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>186.4690476190476</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>275.1428571428572</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>388714.2857142857</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>88714285.71428572</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>279.4285714285714</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>9.857142857142858</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>25.225</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>186.5222222222222</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>252.3333333333333</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>90500</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>13400000</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>266.6666666666667</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>26.92987012987013</v>
+      </c>
+      <c r="D29" t="n">
+        <v>184.4103896103896</v>
+      </c>
+      <c r="E29" t="n">
+        <v>72.98181818181818</v>
+      </c>
+      <c r="F29" t="n">
+        <v>31190.90909090909</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4401233.766233766</v>
+      </c>
+      <c r="H29" t="n">
+        <v>76.05194805194806</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.105194805194805</v>
+      </c>
+      <c r="J29" t="n">
+        <v>25.8962962962963</v>
+      </c>
+      <c r="K29" t="n">
+        <v>182.987037037037</v>
+      </c>
+      <c r="L29" t="n">
+        <v>76.10925925925926</v>
+      </c>
+      <c r="M29" t="n">
+        <v>39538.8888888889</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12615555.55555556</v>
+      </c>
+      <c r="O29" t="n">
+        <v>80.29629629629629</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.544444444444444</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>25.58428824308524</v>
+      </c>
+      <c r="R29" t="n">
+        <v>184.5033241445271</v>
+      </c>
+      <c r="S29" t="n">
+        <v>68.81353133082457</v>
+      </c>
+      <c r="T29" t="n">
+        <v>29312.19712618209</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2826285.428856857</v>
+      </c>
+      <c r="V29" t="n">
+        <v>73.4435024123746</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.136360581774116</v>
+      </c>
+      <c r="X29" t="n">
+        <v>24.88702062430323</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>182.26211352657</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>75.37728075065031</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>42211.35358602749</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>11322704.45466369</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>80.06980490523968</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.386218877740617</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>25.75555555555556</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>184.4833333333333</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>258.6666666666667</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>136666.6666666667</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>13758333.33333333</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>275.6666666666667</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>68000</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT29"/>
+  <dimension ref="A1:AT31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,54 +1220,22 @@
       <c r="AD6" t="n">
         <v>1.764030934343434</v>
       </c>
-      <c r="AE6" t="n">
-        <v>25.38888888888889</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>188.0111111111111</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>5.166666666666667</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>366.1666666666667</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>62666.66666666666</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14816666.66666667</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>384.3333333333333</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>134500</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>20750000</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>120.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1362,30 +1330,14 @@
       <c r="AD7" t="n">
         <v>1.386218877740617</v>
       </c>
-      <c r="AE7" t="n">
-        <v>24.48571428571428</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>181.5714285714286</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>279.8571428571428</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>41142.85714285714</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>12807142.85714286</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>309.5714285714286</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>4</v>
-      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
         <v>26.6</v>
       </c>
@@ -1504,54 +1456,22 @@
       <c r="AD8" t="n">
         <v>1.47235687093003</v>
       </c>
-      <c r="AE8" t="n">
-        <v>25.54761904761904</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>180.5238095238095</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>208.5714285714286</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>28428.57142857143</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>8350000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>222.4285714285714</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>3.285714285714286</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>23.98095238095238</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>192.1285714285714</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>3.428571428571428</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>266.8571428571428</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>180428.5714285714</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>72114285.71428572</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>285.4285714285714</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.142857142857143</v>
-      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -4533,6 +4453,290 @@
       </c>
       <c r="AT29" t="n">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>26.50992063492064</v>
+      </c>
+      <c r="D30" t="n">
+        <v>181.7936507936508</v>
+      </c>
+      <c r="E30" t="n">
+        <v>78.32738095238096</v>
+      </c>
+      <c r="F30" t="n">
+        <v>40069.44444444445</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20811507.93650794</v>
+      </c>
+      <c r="H30" t="n">
+        <v>81.01587301587301</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.337301587301587</v>
+      </c>
+      <c r="J30" t="n">
+        <v>27.03174603174603</v>
+      </c>
+      <c r="K30" t="n">
+        <v>185.8353174603174</v>
+      </c>
+      <c r="L30" t="n">
+        <v>74.90079365079364</v>
+      </c>
+      <c r="M30" t="n">
+        <v>38329.36507936508</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9957936.507936507</v>
+      </c>
+      <c r="O30" t="n">
+        <v>77.95436507936508</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.202380952380953</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>25.24310180212436</v>
+      </c>
+      <c r="R30" t="n">
+        <v>179.5576799140709</v>
+      </c>
+      <c r="S30" t="n">
+        <v>76.20569280343716</v>
+      </c>
+      <c r="T30" t="n">
+        <v>35859.08222938298</v>
+      </c>
+      <c r="U30" t="n">
+        <v>18635974.6091419</v>
+      </c>
+      <c r="V30" t="n">
+        <v>80.99550065640291</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.820915383697339</v>
+      </c>
+      <c r="X30" t="n">
+        <v>24.95886481939113</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>184.9158604553341</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>70.38168147641832</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>29898.04143225195</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>5682091.263999159</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>76.09647720700352</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.07012987012987</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>179.625</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>104500</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>35750000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>25966666.66666667</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>188.3333333333333</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="E31" t="n">
+        <v>74.05555555555556</v>
+      </c>
+      <c r="F31" t="n">
+        <v>23388.88888888889</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5341666.666666666</v>
+      </c>
+      <c r="H31" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="J31" t="n">
+        <v>26.82857142857143</v>
+      </c>
+      <c r="K31" t="n">
+        <v>181.8428571428572</v>
+      </c>
+      <c r="L31" t="n">
+        <v>79.37142857142855</v>
+      </c>
+      <c r="M31" t="n">
+        <v>49471.42857142857</v>
+      </c>
+      <c r="N31" t="n">
+        <v>22147142.85714286</v>
+      </c>
+      <c r="O31" t="n">
+        <v>82.15714285714286</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>28.37981975398856</v>
+      </c>
+      <c r="R31" t="n">
+        <v>182.3668345599109</v>
+      </c>
+      <c r="S31" t="n">
+        <v>72.79283278528803</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23880.77839831585</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4812961.227969448</v>
+      </c>
+      <c r="V31" t="n">
+        <v>74.09159837848183</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.266176035631644</v>
+      </c>
+      <c r="X31" t="n">
+        <v>26.84007082059877</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>182.7243916987084</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>75.53635528607579</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>38823.90548489927</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>10868628.42600809</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>79.43688997338066</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.59737027178021</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>29.83333333333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>94.66666666666667</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>29333.33333333333</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>2666666.666666667</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>94.83333333333333</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>74250</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>21250000</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>124</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AT31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,569 +574,4345 @@
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.02878787878788</v>
+        <v>26.16597222222222</v>
       </c>
       <c r="D2" t="n">
-        <v>185.0560606060606</v>
+        <v>185.9857638888889</v>
       </c>
       <c r="E2" t="n">
-        <v>69.98787878787878</v>
+        <v>71.81111111111112</v>
       </c>
       <c r="F2" t="n">
-        <v>21287.87878787879</v>
+        <v>15188.88888888889</v>
       </c>
       <c r="G2" t="n">
-        <v>2915946.969696969</v>
+        <v>3391276.041666667</v>
       </c>
       <c r="H2" t="n">
-        <v>74.48333333333333</v>
+        <v>75.315625</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>27.56915584415584</v>
+        <v>26.17727272727273</v>
       </c>
       <c r="K2" t="n">
-        <v>182.8480519480519</v>
+        <v>185.0613636363636</v>
       </c>
       <c r="L2" t="n">
-        <v>79.59318181818182</v>
+        <v>72.18068181818182</v>
       </c>
       <c r="M2" t="n">
-        <v>101898.3766233766</v>
+        <v>18135.22727272727</v>
       </c>
       <c r="N2" t="n">
-        <v>24146103.89610389</v>
+        <v>4050113.636363636</v>
       </c>
       <c r="O2" t="n">
-        <v>81.37727272727273</v>
+        <v>75.71022727272728</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.079545454545455</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.30995151156642</v>
+        <v>26.24865569927784</v>
       </c>
       <c r="R2" t="n">
-        <v>183.8025110913931</v>
+        <v>184.2589822093111</v>
       </c>
       <c r="S2" t="n">
-        <v>69.03654799996416</v>
+        <v>70.39390103325672</v>
       </c>
       <c r="T2" t="n">
-        <v>23043.96202486265</v>
+        <v>14630.24946465307</v>
       </c>
       <c r="U2" t="n">
-        <v>2965710.823855234</v>
+        <v>2481212.651218998</v>
       </c>
       <c r="V2" t="n">
-        <v>74.21144900648007</v>
+        <v>74.2443793009368</v>
       </c>
       <c r="W2" t="n">
-        <v>1.052853288878134</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>27.48427128427128</v>
+        <v>27.0748403751421</v>
       </c>
       <c r="Y2" t="n">
-        <v>182.4621753246753</v>
+        <v>182.9446865634366</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.73555194805195</v>
+        <v>70.79759507733647</v>
       </c>
       <c r="AA2" t="n">
-        <v>88061.3455988456</v>
+        <v>18960.0504667746</v>
       </c>
       <c r="AB2" t="n">
-        <v>15413449.22438672</v>
+        <v>2827900.746882428</v>
       </c>
       <c r="AC2" t="n">
-        <v>78.57536075036076</v>
+        <v>74.57742292190568</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.809686147186147</v>
+        <v>1.019418081918082</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>27.9047619047619</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>179.7738095238095</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>171.4285714285714</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>45285.71428571428</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21357142.85714286</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>176.4285714285714</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>166.3333333333333</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5787500</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>173.1666666666667</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.63333333333334</v>
+        <v>27.04340277777778</v>
       </c>
       <c r="D3" t="n">
-        <v>183.2305555555556</v>
+        <v>185.7934027777778</v>
       </c>
       <c r="E3" t="n">
-        <v>73.14166666666667</v>
+        <v>74.77256944444444</v>
       </c>
       <c r="F3" t="n">
-        <v>11919.44444444444</v>
+        <v>37944.44444444445</v>
       </c>
       <c r="G3" t="n">
-        <v>6074166.666666666</v>
+        <v>9630381.944444444</v>
       </c>
       <c r="H3" t="n">
-        <v>77.77222222222221</v>
+        <v>77.75694444444444</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.177083333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>25.8962962962963</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>182.987037037037</v>
+        <v>181.8888888888889</v>
       </c>
       <c r="L3" t="n">
-        <v>76.10925925925926</v>
+        <v>74.44444444444444</v>
       </c>
       <c r="M3" t="n">
-        <v>39538.8888888889</v>
+        <v>23777.77777777778</v>
       </c>
       <c r="N3" t="n">
-        <v>12615555.55555556</v>
+        <v>5713888.888888889</v>
       </c>
       <c r="O3" t="n">
-        <v>80.29629629629629</v>
+        <v>76.77777777777777</v>
       </c>
       <c r="P3" t="n">
-        <v>1.544444444444444</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.54878618113912</v>
+        <v>24.77234005030058</v>
       </c>
       <c r="R3" t="n">
-        <v>182.2714635854342</v>
+        <v>184.9763778984174</v>
       </c>
       <c r="S3" t="n">
-        <v>68.63990429505135</v>
+        <v>69.94230462519937</v>
       </c>
       <c r="T3" t="n">
-        <v>10271.25350140056</v>
+        <v>29177.45291988712</v>
       </c>
       <c r="U3" t="n">
-        <v>2872389.414098973</v>
+        <v>5225371.522665931</v>
       </c>
       <c r="V3" t="n">
-        <v>74.45700280112045</v>
+        <v>75.94275088946141</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.061363636363636</v>
       </c>
       <c r="X3" t="n">
-        <v>24.88702062430323</v>
+        <v>28.41553403970284</v>
       </c>
       <c r="Y3" t="n">
-        <v>182.26211352657</v>
+        <v>181.8954059884823</v>
       </c>
       <c r="Z3" t="n">
-        <v>75.37728075065031</v>
+        <v>72.94997564243089</v>
       </c>
       <c r="AA3" t="n">
-        <v>42211.35358602749</v>
+        <v>23837.9212554587</v>
       </c>
       <c r="AB3" t="n">
-        <v>11322704.45466369</v>
+        <v>4825104.085112305</v>
       </c>
       <c r="AC3" t="n">
-        <v>80.06980490523968</v>
+        <v>74.29874123562469</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.386218877740617</v>
+        <v>1.280461749917359</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>22.61904761904762</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>185.5714285714286</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>185.1428571428571</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>87714.28571428571</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>32528571.42857143</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>208.7142857142857</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>29.83333333333333</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>187.0833333333333</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>28500</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2133333.333333333</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>93.66666666666667</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.01212121212121</v>
+        <v>27.59523358585859</v>
       </c>
       <c r="D4" t="n">
-        <v>183.5287878787879</v>
+        <v>183.2003787878788</v>
       </c>
       <c r="E4" t="n">
-        <v>70.58939393939393</v>
+        <v>79.67181186868687</v>
       </c>
       <c r="F4" t="n">
-        <v>10206.0606060606</v>
+        <v>102605.523989899</v>
       </c>
       <c r="G4" t="n">
-        <v>2827348.484848485</v>
+        <v>24433396.46464647</v>
       </c>
       <c r="H4" t="n">
-        <v>74.96060606060605</v>
+        <v>81.51066919191919</v>
       </c>
       <c r="I4" t="n">
-        <v>1.046969696969697</v>
+        <v>1.95625</v>
       </c>
       <c r="J4" t="n">
-        <v>26.57121212121212</v>
+        <v>25.69444444444445</v>
       </c>
       <c r="K4" t="n">
-        <v>186.5136363636364</v>
+        <v>183.4837962962963</v>
       </c>
       <c r="L4" t="n">
-        <v>78.08333333333333</v>
+        <v>73.15972222222221</v>
       </c>
       <c r="M4" t="n">
-        <v>54401.51515151514</v>
+        <v>11974.53703703704</v>
       </c>
       <c r="N4" t="n">
-        <v>18186060.60606061</v>
+        <v>6061805.555555555</v>
       </c>
       <c r="O4" t="n">
-        <v>81.5439393939394</v>
+        <v>77.68518518518518</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71969696969697</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.69772586935058</v>
+        <v>27.47636895268474</v>
       </c>
       <c r="R4" t="n">
-        <v>183.4236560329238</v>
+        <v>182.4109823564593</v>
       </c>
       <c r="S4" t="n">
-        <v>68.41075900114801</v>
+        <v>76.63702900717703</v>
       </c>
       <c r="T4" t="n">
-        <v>13859.89870372022</v>
+        <v>87685.25634635831</v>
       </c>
       <c r="U4" t="n">
-        <v>2132143.988099365</v>
+        <v>15156340.43975944</v>
       </c>
       <c r="V4" t="n">
-        <v>73.95625124515284</v>
+        <v>78.41133539340777</v>
       </c>
       <c r="W4" t="n">
-        <v>1.008771929824561</v>
+        <v>1.780843799840511</v>
       </c>
       <c r="X4" t="n">
-        <v>25.03573151570863</v>
+        <v>24.60518790849673</v>
       </c>
       <c r="Y4" t="n">
-        <v>185.4114657695893</v>
+        <v>181.9654718137255</v>
       </c>
       <c r="Z4" t="n">
-        <v>72.31014362364476</v>
+        <v>68.83197508169934</v>
       </c>
       <c r="AA4" t="n">
-        <v>39601.50469074954</v>
+        <v>10303.52328431372</v>
       </c>
       <c r="AB4" t="n">
-        <v>11760064.06996682</v>
+        <v>2919774.560866013</v>
       </c>
       <c r="AC4" t="n">
-        <v>78.22202663850261</v>
+        <v>74.5469362745098</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.502063408241898</v>
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>31.13333333333334</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>175.8666666666666</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>144</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>166400</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>24.08095238095238</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>286.5714285714286</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>41428.57142857143</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12282142.85714286</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.142857142857143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.16363636363636</v>
+        <v>26.3</v>
       </c>
       <c r="D5" t="n">
-        <v>185.1090909090909</v>
+        <v>185.9382395382395</v>
       </c>
       <c r="E5" t="n">
-        <v>72.16753246753247</v>
+        <v>76.16998556998557</v>
       </c>
       <c r="F5" t="n">
-        <v>18128.57142857143</v>
+        <v>46856.85425685426</v>
       </c>
       <c r="G5" t="n">
-        <v>4053376.623376623</v>
+        <v>10630339.10533911</v>
       </c>
       <c r="H5" t="n">
-        <v>75.68181818181817</v>
+        <v>79.14559884559885</v>
       </c>
       <c r="I5" t="n">
-        <v>1.077922077922078</v>
+        <v>1.508369408369408</v>
       </c>
       <c r="J5" t="n">
-        <v>27.03174603174603</v>
+        <v>25.77380952380953</v>
       </c>
       <c r="K5" t="n">
-        <v>185.8353174603174</v>
+        <v>185.55</v>
       </c>
       <c r="L5" t="n">
-        <v>74.90079365079364</v>
+        <v>82.05238095238096</v>
       </c>
       <c r="M5" t="n">
-        <v>38329.36507936508</v>
+        <v>138240.4761904762</v>
       </c>
       <c r="N5" t="n">
-        <v>9957936.507936507</v>
+        <v>44349404.76190477</v>
       </c>
       <c r="O5" t="n">
-        <v>77.95436507936508</v>
+        <v>85.02499999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.202380952380953</v>
+        <v>2.757142857142857</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.99212526389866</v>
+        <v>24.34296509908311</v>
       </c>
       <c r="R5" t="n">
-        <v>182.9477736549165</v>
+        <v>185.1334472049689</v>
       </c>
       <c r="S5" t="n">
-        <v>70.67527349497793</v>
+        <v>73.39845755693581</v>
       </c>
       <c r="T5" t="n">
-        <v>18690.60712686328</v>
+        <v>39424.08015380065</v>
       </c>
       <c r="U5" t="n">
-        <v>2772133.820612885</v>
+        <v>7439809.080153801</v>
       </c>
       <c r="V5" t="n">
-        <v>74.56101081184826</v>
+        <v>78.78090505767524</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01669758812616</v>
+        <v>1.206165335699497</v>
       </c>
       <c r="X5" t="n">
-        <v>24.95886481939113</v>
+        <v>24.11690639642584</v>
       </c>
       <c r="Y5" t="n">
-        <v>184.9158604553341</v>
+        <v>183.2066550154651</v>
       </c>
       <c r="Z5" t="n">
-        <v>70.38168147641832</v>
+        <v>77.54686884435169</v>
       </c>
       <c r="AA5" t="n">
-        <v>29898.04143225195</v>
+        <v>106144.8055758124</v>
       </c>
       <c r="AB5" t="n">
-        <v>5682091.263999159</v>
+        <v>26924681.48842005</v>
       </c>
       <c r="AC5" t="n">
-        <v>76.09647720700352</v>
+        <v>82.90918265563573</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07012987012987</v>
+        <v>1.731756649147953</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>23.64965986394558</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>182.7897959183674</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>340</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>203714.2857142857</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>45085714.28571428</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>361.2857142857143</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>27.68095238095238</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>295.5714285714286</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>432142.8571428572</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>97210714.28571428</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>304.8571428571428</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.285714285714286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.63657407407408</v>
+        <v>26.61948051948052</v>
       </c>
       <c r="D6" t="n">
-        <v>181.8217592592593</v>
+        <v>186.4922077922078</v>
       </c>
       <c r="E6" t="n">
-        <v>78.31944444444444</v>
+        <v>78.21428571428571</v>
       </c>
       <c r="F6" t="n">
-        <v>40810.18518518519</v>
+        <v>55253.24675324675</v>
       </c>
       <c r="G6" t="n">
-        <v>20988425.92592593</v>
+        <v>18529610.38961039</v>
       </c>
       <c r="H6" t="n">
-        <v>80.95601851851852</v>
+        <v>81.59610389610388</v>
       </c>
       <c r="I6" t="n">
-        <v>2.372685185185185</v>
+        <v>1.733766233766233</v>
       </c>
       <c r="J6" t="n">
-        <v>29.32121212121212</v>
+        <v>25.42857142857143</v>
       </c>
       <c r="K6" t="n">
-        <v>182.5712121212121</v>
+        <v>183.2757936507937</v>
       </c>
       <c r="L6" t="n">
-        <v>84.16060606060606</v>
+        <v>72.74603174603173</v>
       </c>
       <c r="M6" t="n">
-        <v>112024.2424242424</v>
+        <v>12369.04761904762</v>
       </c>
       <c r="N6" t="n">
-        <v>41471212.12121212</v>
+        <v>4658333.333333334</v>
       </c>
       <c r="O6" t="n">
-        <v>85.07575757575758</v>
+        <v>77.0515873015873</v>
       </c>
       <c r="P6" t="n">
-        <v>3.324242424242424</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.16958368142579</v>
+        <v>25.01114649398402</v>
       </c>
       <c r="R6" t="n">
-        <v>179.4137844611529</v>
+        <v>185.3202174128948</v>
       </c>
       <c r="S6" t="n">
-        <v>76.02067669172932</v>
+        <v>72.60999323585136</v>
       </c>
       <c r="T6" t="n">
-        <v>35107.52575884155</v>
+        <v>39593.49752713597</v>
       </c>
       <c r="U6" t="n">
-        <v>17797014.23698134</v>
+        <v>11835444.52750402</v>
       </c>
       <c r="V6" t="n">
-        <v>80.85439988861042</v>
+        <v>78.52147737845678</v>
       </c>
       <c r="W6" t="n">
-        <v>1.782296017822334</v>
+        <v>1.501768635635913</v>
       </c>
       <c r="X6" t="n">
-        <v>28.0551839464883</v>
+        <v>25.93607232366631</v>
       </c>
       <c r="Y6" t="n">
-        <v>184.811013563731</v>
+        <v>183.7775689223058</v>
       </c>
       <c r="Z6" t="n">
-        <v>79.97140932738758</v>
+        <v>70.77873254564985</v>
       </c>
       <c r="AA6" t="n">
-        <v>88390.18952062431</v>
+        <v>10356.2477622628</v>
       </c>
       <c r="AB6" t="n">
-        <v>26566413.5079896</v>
+        <v>3548066.237021124</v>
       </c>
       <c r="AC6" t="n">
-        <v>81.7117707172055</v>
+        <v>75.22756892230576</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.407748049052397</v>
+        <v>1.022556390977444</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>23.98095238095238</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>192.0571428571429</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>265.5714285714286</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>174714.2857142857</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>69800000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>284.7142857142857</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>25.79047619047619</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>184.2738095238095</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>236.7142857142857</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>50571.42857142857</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>18371428.57142857</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>247</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.142857142857143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.44444444444444</v>
+        <v>23.77738095238095</v>
       </c>
       <c r="D7" t="n">
-        <v>183.4699074074074</v>
+        <v>184.3706349206349</v>
       </c>
       <c r="E7" t="n">
-        <v>72.79629629629629</v>
+        <v>72.64801587301586</v>
       </c>
       <c r="F7" t="n">
-        <v>12337.96296296296</v>
+        <v>25884.52380952381</v>
       </c>
       <c r="G7" t="n">
-        <v>4640277.777777778</v>
+        <v>5553650.793650794</v>
       </c>
       <c r="H7" t="n">
-        <v>77.06018518518518</v>
+        <v>78.36349206349207</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>26.10836940836941</v>
+        <v>24.93896103896104</v>
       </c>
       <c r="K7" t="n">
-        <v>183.9092352092352</v>
+        <v>185.0051948051948</v>
       </c>
       <c r="L7" t="n">
-        <v>72.65180375180375</v>
+        <v>69.93246753246753</v>
       </c>
       <c r="M7" t="n">
-        <v>23415.29581529581</v>
+        <v>21489.61038961039</v>
       </c>
       <c r="N7" t="n">
-        <v>5805266.955266954</v>
+        <v>2936883.116883117</v>
       </c>
       <c r="O7" t="n">
-        <v>76.91183261183262</v>
+        <v>74.58571428571429</v>
       </c>
       <c r="P7" t="n">
-        <v>1.216450216450216</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.83769841269842</v>
+        <v>23.94831168831169</v>
       </c>
       <c r="R7" t="n">
-        <v>183.9861111111111</v>
+        <v>182.7966233766234</v>
       </c>
       <c r="S7" t="n">
-        <v>70.61904761904762</v>
+        <v>68.82623376623378</v>
       </c>
       <c r="T7" t="n">
-        <v>10134.92063492064</v>
+        <v>22253.37662337662</v>
       </c>
       <c r="U7" t="n">
-        <v>3328182.53968254</v>
+        <v>2923159.090909091</v>
       </c>
       <c r="V7" t="n">
-        <v>75.17777777777778</v>
+        <v>74.73545454545454</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>26.95548487587255</v>
+        <v>24.36049328690633</v>
       </c>
       <c r="Y7" t="n">
-        <v>182.6416653045657</v>
+        <v>183.7260067287785</v>
       </c>
       <c r="Z7" t="n">
-        <v>71.94158711997385</v>
+        <v>68.88316997615911</v>
       </c>
       <c r="AA7" t="n">
-        <v>34157.99405803512</v>
+        <v>22425.37153365958</v>
       </c>
       <c r="AB7" t="n">
-        <v>6114575.0621759</v>
+        <v>2877586.256587615</v>
       </c>
       <c r="AC7" t="n">
-        <v>76.04462889961476</v>
+        <v>73.97668454733673</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.290284502817145</v>
+        <v>1.052199008720748</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>186.6619047619047</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>257.5714285714286</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>91428.57142857143</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>13771428.57142857</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>272.8571428571428</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>187.9380952380952</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>375</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>63857.14285714286</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15385714.28571429</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>393.4285714285714</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.428571428571429</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26.72857142857143</v>
+      </c>
+      <c r="D8" t="n">
+        <v>181.8428571428572</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79.37142857142855</v>
+      </c>
+      <c r="F8" t="n">
+        <v>48757.14285714286</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22368571.42857143</v>
+      </c>
+      <c r="H8" t="n">
+        <v>82.28571428571429</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.985714285714286</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>184.3931818181818</v>
+      </c>
+      <c r="L8" t="n">
+        <v>72.64318181818182</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30803.40909090909</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4272954.545454546</v>
+      </c>
+      <c r="O8" t="n">
+        <v>75.82954545454545</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.092045454545455</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>27.01030316474416</v>
+      </c>
+      <c r="R8" t="n">
+        <v>182.8603475303165</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75.57592280390416</v>
+      </c>
+      <c r="T8" t="n">
+        <v>39139.06536527654</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10651582.18722272</v>
+      </c>
+      <c r="V8" t="n">
+        <v>79.29196243714877</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.590008873114463</v>
+      </c>
+      <c r="X8" t="n">
+        <v>25.39250221269958</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>184.6279086264612</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>68.4930899144715</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>29341.92248540933</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2767531.00024975</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>73.31931461082777</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.125565509052351</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>115</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>78500</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21125000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>26.13741496598639</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>184.5163265306122</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>295.4285714285714</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>153571.4285714286</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16735714.28571429</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>312.5714285714286</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.142857142857143</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>26.14482323232323</v>
+      </c>
+      <c r="D9" t="n">
+        <v>183.8455808080808</v>
+      </c>
+      <c r="E9" t="n">
+        <v>72.75782828282829</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23300.88383838384</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5899608.585858585</v>
+      </c>
+      <c r="H9" t="n">
+        <v>76.93535353535354</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.214393939393939</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.8961038961039</v>
+      </c>
+      <c r="K9" t="n">
+        <v>183.5675324675325</v>
+      </c>
+      <c r="L9" t="n">
+        <v>70.53376623376623</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10405.1948051948</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2824870.12987013</v>
+      </c>
+      <c r="O9" t="n">
+        <v>75.02337662337663</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.054545454545455</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>26.91417426638848</v>
+      </c>
+      <c r="R9" t="n">
+        <v>182.623957141495</v>
+      </c>
+      <c r="S9" t="n">
+        <v>71.77180539664379</v>
+      </c>
+      <c r="T9" t="n">
+        <v>34258.0364674474</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6080721.929403912</v>
+      </c>
+      <c r="V9" t="n">
+        <v>75.94530028716292</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.306082273298335</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25.86947931658622</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>183.1059908853632</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>68.55922200098401</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>13622.77031747447</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2199373.418370885</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>73.94821535298816</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.007518796992481</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>27.65714285714285</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>180.2261904761905</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>292.5714285714286</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>90571.42857142857</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>22628571.42857143</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>303</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>25.21428571428572</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>180.2142857142857</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>157.2857142857143</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>21714.28571428571</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5746428.571428572</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>168.1428571428571</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.571428571428572</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>29.39220779220779</v>
+      </c>
+      <c r="D10" t="n">
+        <v>182.4766233766234</v>
+      </c>
+      <c r="E10" t="n">
+        <v>84.28051948051949</v>
+      </c>
+      <c r="F10" t="n">
+        <v>113241.5584415584</v>
+      </c>
+      <c r="G10" t="n">
+        <v>42176623.37662338</v>
+      </c>
+      <c r="H10" t="n">
+        <v>85.1168831168831</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.355844155844156</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="K10" t="n">
+        <v>185.28125</v>
+      </c>
+      <c r="L10" t="n">
+        <v>80.53125</v>
+      </c>
+      <c r="M10" t="n">
+        <v>102937.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34968750</v>
+      </c>
+      <c r="O10" t="n">
+        <v>84.40625</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>28.06515766841854</v>
+      </c>
+      <c r="R10" t="n">
+        <v>185.1296782927218</v>
+      </c>
+      <c r="S10" t="n">
+        <v>79.98739847109411</v>
+      </c>
+      <c r="T10" t="n">
+        <v>88465.4005414875</v>
+      </c>
+      <c r="U10" t="n">
+        <v>26683116.34018156</v>
+      </c>
+      <c r="V10" t="n">
+        <v>81.7469939480809</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.409022137283007</v>
+      </c>
+      <c r="X10" t="n">
+        <v>25.94307359307359</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>184.156277056277</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>77.11363636363636</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>76910.60606060606</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>16885454.54545454</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>80.97207792207791</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.63961038961039</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>25.76190476190476</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>180.952380952381</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>145.7142857142857</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>164428.5714285714</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>54357142.85714286</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>148.7142857142857</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>28.53333333333333</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>186.3619047619048</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>299.4285714285714</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>428714.2857142857</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>105928571.4285714</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>303.8571428571428</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10.85714285714286</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.73650793650794</v>
+      </c>
+      <c r="D11" t="n">
+        <v>182.8619047619048</v>
+      </c>
+      <c r="E11" t="n">
+        <v>76.06190476190477</v>
+      </c>
+      <c r="F11" t="n">
+        <v>39874.60317460318</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12814920.63492064</v>
+      </c>
+      <c r="H11" t="n">
+        <v>80.36507936507937</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.53015873015873</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.67063492063492</v>
+      </c>
+      <c r="K11" t="n">
+        <v>181.811507936508</v>
+      </c>
+      <c r="L11" t="n">
+        <v>78.50595238095239</v>
+      </c>
+      <c r="M11" t="n">
+        <v>41051.5873015873</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21766865.07936508</v>
+      </c>
+      <c r="O11" t="n">
+        <v>80.99801587301587</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.390873015873016</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24.88452699474439</v>
+      </c>
+      <c r="R11" t="n">
+        <v>182.1439233954451</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75.42897356266921</v>
+      </c>
+      <c r="T11" t="n">
+        <v>42075.5701544832</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11397566.55120242</v>
+      </c>
+      <c r="V11" t="n">
+        <v>80.13436693741041</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.374523013218665</v>
+      </c>
+      <c r="X11" t="n">
+        <v>24.90726220312687</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>179.0880057286072</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75.8843895452918</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>34330.26017424514</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17827916.96503162</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>81.09424752357083</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.756253729562</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>185.0833333333333</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>115.6666666666667</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>70166.66666666667</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>19833333.33333333</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>118.6666666666667</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>179.375</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>130500</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>40375000</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>26.17727272727273</v>
+      </c>
+      <c r="D12" t="n">
+        <v>185.0613636363636</v>
+      </c>
+      <c r="E12" t="n">
+        <v>72.18068181818182</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18135.22727272727</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4050113.636363636</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75.71022727272728</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.079545454545455</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>185.9382395382395</v>
+      </c>
+      <c r="L12" t="n">
+        <v>76.16998556998557</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46856.85425685426</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10630339.10533911</v>
+      </c>
+      <c r="O12" t="n">
+        <v>79.14559884559885</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.508369408369408</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>27.0748403751421</v>
+      </c>
+      <c r="R12" t="n">
+        <v>182.9446865634366</v>
+      </c>
+      <c r="S12" t="n">
+        <v>70.79759507733647</v>
+      </c>
+      <c r="T12" t="n">
+        <v>18960.0504667746</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2827900.746882428</v>
+      </c>
+      <c r="V12" t="n">
+        <v>74.57742292190568</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.019418081918082</v>
+      </c>
+      <c r="X12" t="n">
+        <v>24.34296509908311</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>185.1334472049689</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>73.39845755693581</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>39424.08015380065</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7439809.080153801</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>78.78090505767524</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.206165335699497</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>166.3333333333333</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>5787500</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>173.1666666666667</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>23.64965986394558</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>182.7897959183674</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>340</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>203714.2857142857</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>45085714.28571428</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>361.2857142857143</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.571428571428571</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>25.69444444444445</v>
+      </c>
+      <c r="D13" t="n">
+        <v>183.4837962962963</v>
+      </c>
+      <c r="E13" t="n">
+        <v>73.15972222222221</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11974.53703703704</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6061805.555555555</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77.68518518518518</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.42857142857143</v>
+      </c>
+      <c r="K13" t="n">
+        <v>183.2757936507937</v>
+      </c>
+      <c r="L13" t="n">
+        <v>72.74603174603173</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12369.04761904762</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4658333.333333334</v>
+      </c>
+      <c r="O13" t="n">
+        <v>77.0515873015873</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>24.60518790849673</v>
+      </c>
+      <c r="R13" t="n">
+        <v>181.9654718137255</v>
+      </c>
+      <c r="S13" t="n">
+        <v>68.83197508169934</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10303.52328431372</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2919774.560866013</v>
+      </c>
+      <c r="V13" t="n">
+        <v>74.5469362745098</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25.93607232366631</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>183.7775689223058</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70.77873254564985</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>10356.2477622628</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3548066.237021124</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>75.22756892230576</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.022556390977444</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>24.08095238095238</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>286.5714285714286</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>41428.57142857143</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>12282142.85714286</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>320</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>25.79047619047619</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>184.2738095238095</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>236.7142857142857</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>50571.42857142857</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>18371428.57142857</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>247</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.142857142857143</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>25.77380952380953</v>
+      </c>
+      <c r="D14" t="n">
+        <v>185.55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>82.05238095238096</v>
+      </c>
+      <c r="F14" t="n">
+        <v>138240.4761904762</v>
+      </c>
+      <c r="G14" t="n">
+        <v>44349404.76190477</v>
+      </c>
+      <c r="H14" t="n">
+        <v>85.02499999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.757142857142857</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27.59523358585859</v>
+      </c>
+      <c r="K14" t="n">
+        <v>183.2003787878788</v>
+      </c>
+      <c r="L14" t="n">
+        <v>79.67181186868687</v>
+      </c>
+      <c r="M14" t="n">
+        <v>102605.523989899</v>
+      </c>
+      <c r="N14" t="n">
+        <v>24433396.46464647</v>
+      </c>
+      <c r="O14" t="n">
+        <v>81.51066919191919</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95625</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>24.11690639642584</v>
+      </c>
+      <c r="R14" t="n">
+        <v>183.2066550154651</v>
+      </c>
+      <c r="S14" t="n">
+        <v>77.54686884435169</v>
+      </c>
+      <c r="T14" t="n">
+        <v>106144.8055758124</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26924681.48842005</v>
+      </c>
+      <c r="V14" t="n">
+        <v>82.90918265563573</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.731756649147953</v>
+      </c>
+      <c r="X14" t="n">
+        <v>27.47636895268474</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>182.4109823564593</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>76.63702900717703</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>87685.25634635831</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>15156340.43975944</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>78.41133539340777</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.780843799840511</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>27.68095238095238</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>295.5714285714286</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>432142.8571428572</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>97210714.28571428</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>304.8571428571428</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>8.285714285714286</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>31.13333333333334</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>175.8666666666666</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>144</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>166400</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24.93896103896104</v>
+      </c>
+      <c r="D15" t="n">
+        <v>185.0051948051948</v>
+      </c>
+      <c r="E15" t="n">
+        <v>69.93246753246753</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21489.61038961039</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2936883.116883117</v>
+      </c>
+      <c r="H15" t="n">
+        <v>74.58571428571429</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29.39220779220779</v>
+      </c>
+      <c r="K15" t="n">
+        <v>182.4766233766234</v>
+      </c>
+      <c r="L15" t="n">
+        <v>84.28051948051949</v>
+      </c>
+      <c r="M15" t="n">
+        <v>113241.5584415584</v>
+      </c>
+      <c r="N15" t="n">
+        <v>42176623.37662338</v>
+      </c>
+      <c r="O15" t="n">
+        <v>85.1168831168831</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.355844155844156</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>24.36049328690633</v>
+      </c>
+      <c r="R15" t="n">
+        <v>183.7260067287785</v>
+      </c>
+      <c r="S15" t="n">
+        <v>68.88316997615911</v>
+      </c>
+      <c r="T15" t="n">
+        <v>22425.37153365958</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2877586.256587615</v>
+      </c>
+      <c r="V15" t="n">
+        <v>73.97668454733673</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.052199008720748</v>
+      </c>
+      <c r="X15" t="n">
+        <v>28.06515766841854</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>185.1296782927218</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>79.98739847109411</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>88465.4005414875</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>26683116.34018156</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>81.7469939480809</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.409022137283007</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>187.9380952380952</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>375</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>63857.14285714286</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>15385714.28571429</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>393.4285714285714</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>25.76190476190476</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>180.952380952381</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>145.7142857142857</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>164428.5714285714</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>54357142.85714286</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>148.7142857142857</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.857142857142857</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.8961038961039</v>
+      </c>
+      <c r="D16" t="n">
+        <v>183.5675324675325</v>
+      </c>
+      <c r="E16" t="n">
+        <v>70.53376623376623</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10405.1948051948</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2824870.12987013</v>
+      </c>
+      <c r="H16" t="n">
+        <v>75.02337662337663</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.054545454545455</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.16597222222222</v>
+      </c>
+      <c r="K16" t="n">
+        <v>185.9857638888889</v>
+      </c>
+      <c r="L16" t="n">
+        <v>71.81111111111112</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15188.88888888889</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3391276.041666667</v>
+      </c>
+      <c r="O16" t="n">
+        <v>75.315625</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>25.86947931658622</v>
+      </c>
+      <c r="R16" t="n">
+        <v>183.1059908853632</v>
+      </c>
+      <c r="S16" t="n">
+        <v>68.55922200098401</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13622.77031747447</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2199373.418370885</v>
+      </c>
+      <c r="V16" t="n">
+        <v>73.94821535298816</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.007518796992481</v>
+      </c>
+      <c r="X16" t="n">
+        <v>26.24865569927784</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>184.2589822093111</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>70.39390103325672</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>14630.24946465307</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2481212.651218998</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>74.2443793009368</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>25.21428571428572</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>180.2142857142857</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>157.2857142857143</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>21714.28571428571</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>5746428.571428572</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>168.1428571428571</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>27.9047619047619</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>179.7738095238095</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>171.4285714285714</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>45285.71428571428</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>21357142.85714286</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>176.4285714285714</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.285714285714286</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.61948051948052</v>
+      </c>
+      <c r="D17" t="n">
+        <v>186.4922077922078</v>
+      </c>
+      <c r="E17" t="n">
+        <v>78.21428571428571</v>
+      </c>
+      <c r="F17" t="n">
+        <v>55253.24675324675</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18529610.38961039</v>
+      </c>
+      <c r="H17" t="n">
+        <v>81.59610389610388</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.733766233766233</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26.14482323232323</v>
+      </c>
+      <c r="K17" t="n">
+        <v>183.8455808080808</v>
+      </c>
+      <c r="L17" t="n">
+        <v>72.75782828282829</v>
+      </c>
+      <c r="M17" t="n">
+        <v>23300.88383838384</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5899608.585858585</v>
+      </c>
+      <c r="O17" t="n">
+        <v>76.93535353535354</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.214393939393939</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>25.01114649398402</v>
+      </c>
+      <c r="R17" t="n">
+        <v>185.3202174128948</v>
+      </c>
+      <c r="S17" t="n">
+        <v>72.60999323585136</v>
+      </c>
+      <c r="T17" t="n">
+        <v>39593.49752713597</v>
+      </c>
+      <c r="U17" t="n">
+        <v>11835444.52750402</v>
+      </c>
+      <c r="V17" t="n">
+        <v>78.52147737845678</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.501768635635913</v>
+      </c>
+      <c r="X17" t="n">
+        <v>26.91417426638848</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>182.623957141495</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>71.77180539664379</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>34258.0364674474</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>6080721.929403912</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>75.94530028716292</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.306082273298335</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>23.98095238095238</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>192.0571428571429</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>265.5714285714286</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>174714.2857142857</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>69800000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>284.7142857142857</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>27.65714285714285</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>180.2261904761905</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>292.5714285714286</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>90571.42857142857</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>22628571.42857143</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>303</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.428571428571429</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="D18" t="n">
+        <v>185.28125</v>
+      </c>
+      <c r="E18" t="n">
+        <v>80.53125</v>
+      </c>
+      <c r="F18" t="n">
+        <v>102937.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34968750</v>
+      </c>
+      <c r="H18" t="n">
+        <v>84.40625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23.77738095238095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>184.3706349206349</v>
+      </c>
+      <c r="L18" t="n">
+        <v>72.64801587301586</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25884.52380952381</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5553650.793650794</v>
+      </c>
+      <c r="O18" t="n">
+        <v>78.36349206349207</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>25.94307359307359</v>
+      </c>
+      <c r="R18" t="n">
+        <v>184.156277056277</v>
+      </c>
+      <c r="S18" t="n">
+        <v>77.11363636363636</v>
+      </c>
+      <c r="T18" t="n">
+        <v>76910.60606060606</v>
+      </c>
+      <c r="U18" t="n">
+        <v>16885454.54545454</v>
+      </c>
+      <c r="V18" t="n">
+        <v>80.97207792207791</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.63961038961039</v>
+      </c>
+      <c r="X18" t="n">
+        <v>23.94831168831169</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>182.7966233766234</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>68.82623376623378</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>22253.37662337662</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2923159.090909091</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>74.73545454545454</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>28.53333333333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>186.3619047619048</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>299.4285714285714</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>428714.2857142857</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>105928571.4285714</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>303.8571428571428</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>10.85714285714286</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>186.6619047619047</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>257.5714285714286</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>91428.57142857143</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13771428.57142857</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>272.8571428571428</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.571428571428572</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>184.3931818181818</v>
+      </c>
+      <c r="E19" t="n">
+        <v>72.64318181818182</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30803.40909090909</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4272954.545454546</v>
+      </c>
+      <c r="H19" t="n">
+        <v>75.82954545454545</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.092045454545455</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25.73650793650794</v>
+      </c>
+      <c r="K19" t="n">
+        <v>182.8619047619048</v>
+      </c>
+      <c r="L19" t="n">
+        <v>76.06190476190477</v>
+      </c>
+      <c r="M19" t="n">
+        <v>39874.60317460318</v>
+      </c>
+      <c r="N19" t="n">
+        <v>12814920.63492064</v>
+      </c>
+      <c r="O19" t="n">
+        <v>80.36507936507937</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.53015873015873</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>25.39250221269958</v>
+      </c>
+      <c r="R19" t="n">
+        <v>184.6279086264612</v>
+      </c>
+      <c r="S19" t="n">
+        <v>68.4930899144715</v>
+      </c>
+      <c r="T19" t="n">
+        <v>29341.92248540933</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2767531.00024975</v>
+      </c>
+      <c r="V19" t="n">
+        <v>73.31931461082777</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.125565509052351</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24.88452699474439</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>182.1439233954451</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>75.42897356266921</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>42075.5701544832</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>11397566.55120242</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>80.13436693741041</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.374523013218665</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>26.13741496598639</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>184.5163265306122</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>295.4285714285714</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>153571.4285714286</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>16735714.28571429</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>312.5714285714286</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>5.142857142857143</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>185.0833333333333</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>115.6666666666667</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>70166.66666666667</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19833333.33333333</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>118.6666666666667</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.833333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.67063492063492</v>
+      </c>
+      <c r="D20" t="n">
+        <v>181.811507936508</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78.50595238095239</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41051.5873015873</v>
+      </c>
+      <c r="G20" t="n">
+        <v>21766865.07936508</v>
+      </c>
+      <c r="H20" t="n">
+        <v>80.99801587301587</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.390873015873016</v>
+      </c>
+      <c r="J20" t="n">
+        <v>27.04340277777778</v>
+      </c>
+      <c r="K20" t="n">
+        <v>185.7934027777778</v>
+      </c>
+      <c r="L20" t="n">
+        <v>74.77256944444444</v>
+      </c>
+      <c r="M20" t="n">
+        <v>37944.44444444445</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9630381.944444444</v>
+      </c>
+      <c r="O20" t="n">
+        <v>77.75694444444444</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.177083333333333</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>24.90726220312687</v>
+      </c>
+      <c r="R20" t="n">
+        <v>179.0880057286072</v>
+      </c>
+      <c r="S20" t="n">
+        <v>75.8843895452918</v>
+      </c>
+      <c r="T20" t="n">
+        <v>34330.26017424514</v>
+      </c>
+      <c r="U20" t="n">
+        <v>17827916.96503162</v>
+      </c>
+      <c r="V20" t="n">
+        <v>81.09424752357083</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.756253729562</v>
+      </c>
+      <c r="X20" t="n">
+        <v>24.77234005030058</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>184.9763778984174</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>69.94230462519937</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>29177.45291988712</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5225371.522665931</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>75.94275088946141</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.061363636363636</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>179.375</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>130500</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>40375000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>22.61904761904762</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>185.5714285714286</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>185.1428571428571</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>87714.28571428571</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>32528571.42857143</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>208.7142857142857</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.857142857142857</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="E21" t="n">
+        <v>74.44444444444444</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23777.77777777778</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5713888.888888889</v>
+      </c>
+      <c r="H21" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.72857142857143</v>
+      </c>
+      <c r="K21" t="n">
+        <v>181.8428571428572</v>
+      </c>
+      <c r="L21" t="n">
+        <v>79.37142857142855</v>
+      </c>
+      <c r="M21" t="n">
+        <v>48757.14285714286</v>
+      </c>
+      <c r="N21" t="n">
+        <v>22368571.42857143</v>
+      </c>
+      <c r="O21" t="n">
+        <v>82.28571428571429</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.985714285714286</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>28.41553403970284</v>
+      </c>
+      <c r="R21" t="n">
+        <v>181.8954059884823</v>
+      </c>
+      <c r="S21" t="n">
+        <v>72.94997564243089</v>
+      </c>
+      <c r="T21" t="n">
+        <v>23837.9212554587</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4825104.085112305</v>
+      </c>
+      <c r="V21" t="n">
+        <v>74.29874123562469</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.280461749917359</v>
+      </c>
+      <c r="X21" t="n">
+        <v>27.01030316474416</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>182.8603475303165</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>75.57592280390416</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>39139.06536527654</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>10651582.18722272</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>79.29196243714877</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.590008873114463</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>29.83333333333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>187.0833333333333</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>28500</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2133333.333333333</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>93.66666666666667</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>115</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>78500</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>21125000</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>185.9382395382395</v>
+      </c>
+      <c r="E22" t="n">
+        <v>76.16998556998557</v>
+      </c>
+      <c r="F22" t="n">
+        <v>46856.85425685426</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10630339.10533911</v>
+      </c>
+      <c r="H22" t="n">
+        <v>79.14559884559885</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.508369408369408</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25.69444444444445</v>
+      </c>
+      <c r="K22" t="n">
+        <v>183.4837962962963</v>
+      </c>
+      <c r="L22" t="n">
+        <v>73.15972222222221</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11974.53703703704</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6061805.555555555</v>
+      </c>
+      <c r="O22" t="n">
+        <v>77.68518518518518</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>24.34296509908311</v>
+      </c>
+      <c r="R22" t="n">
+        <v>185.1334472049689</v>
+      </c>
+      <c r="S22" t="n">
+        <v>73.39845755693581</v>
+      </c>
+      <c r="T22" t="n">
+        <v>39424.08015380065</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7439809.080153801</v>
+      </c>
+      <c r="V22" t="n">
+        <v>78.78090505767524</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.206165335699497</v>
+      </c>
+      <c r="X22" t="n">
+        <v>24.60518790849673</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>181.9654718137255</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>68.83197508169934</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>10303.52328431372</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2919774.560866013</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>74.5469362745098</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>23.64965986394558</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>182.7897959183674</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>340</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>203714.2857142857</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>45085714.28571428</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>361.2857142857143</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>24.08095238095238</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>286.5714285714286</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>41428.57142857143</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>12282142.85714286</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.142857142857143</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>26.16597222222222</v>
+      </c>
+      <c r="D23" t="n">
+        <v>185.9857638888889</v>
+      </c>
+      <c r="E23" t="n">
+        <v>71.81111111111112</v>
+      </c>
+      <c r="F23" t="n">
+        <v>15188.88888888889</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3391276.041666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75.315625</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="K23" t="n">
+        <v>185.28125</v>
+      </c>
+      <c r="L23" t="n">
+        <v>80.53125</v>
+      </c>
+      <c r="M23" t="n">
+        <v>102937.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>34968750</v>
+      </c>
+      <c r="O23" t="n">
+        <v>84.40625</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>26.24865569927784</v>
+      </c>
+      <c r="R23" t="n">
+        <v>184.2589822093111</v>
+      </c>
+      <c r="S23" t="n">
+        <v>70.39390103325672</v>
+      </c>
+      <c r="T23" t="n">
+        <v>14630.24946465307</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2481212.651218998</v>
+      </c>
+      <c r="V23" t="n">
+        <v>74.2443793009368</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>25.94307359307359</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>184.156277056277</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>77.11363636363636</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>76910.60606060606</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>16885454.54545454</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>80.97207792207791</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.63961038961039</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>27.9047619047619</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>179.7738095238095</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>171.4285714285714</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>45285.71428571428</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>21357142.85714286</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>176.4285714285714</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>28.53333333333333</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>186.3619047619048</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>299.4285714285714</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>428714.2857142857</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>105928571.4285714</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>303.8571428571428</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10.85714285714286</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>26.14482323232323</v>
+      </c>
+      <c r="D24" t="n">
+        <v>183.8455808080808</v>
+      </c>
+      <c r="E24" t="n">
+        <v>72.75782828282829</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23300.88383838384</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5899608.585858585</v>
+      </c>
+      <c r="H24" t="n">
+        <v>76.93535353535354</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.214393939393939</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25.77380952380953</v>
+      </c>
+      <c r="K24" t="n">
+        <v>185.55</v>
+      </c>
+      <c r="L24" t="n">
+        <v>82.05238095238096</v>
+      </c>
+      <c r="M24" t="n">
+        <v>138240.4761904762</v>
+      </c>
+      <c r="N24" t="n">
+        <v>44349404.76190477</v>
+      </c>
+      <c r="O24" t="n">
+        <v>85.02499999999999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.757142857142857</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>26.91417426638848</v>
+      </c>
+      <c r="R24" t="n">
+        <v>182.623957141495</v>
+      </c>
+      <c r="S24" t="n">
+        <v>71.77180539664379</v>
+      </c>
+      <c r="T24" t="n">
+        <v>34258.0364674474</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6080721.929403912</v>
+      </c>
+      <c r="V24" t="n">
+        <v>75.94530028716292</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.306082273298335</v>
+      </c>
+      <c r="X24" t="n">
+        <v>24.11690639642584</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>183.2066550154651</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>77.54686884435169</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>106144.8055758124</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>26924681.48842005</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>82.90918265563573</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.731756649147953</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>27.65714285714285</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>180.2261904761905</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>292.5714285714286</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>90571.42857142857</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>22628571.42857143</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>303</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>27.68095238095238</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>295.5714285714286</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>432142.8571428572</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>97210714.28571428</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>304.8571428571428</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.285714285714286</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>27.59523358585859</v>
+      </c>
+      <c r="D25" t="n">
+        <v>183.2003787878788</v>
+      </c>
+      <c r="E25" t="n">
+        <v>79.67181186868687</v>
+      </c>
+      <c r="F25" t="n">
+        <v>102605.523989899</v>
+      </c>
+      <c r="G25" t="n">
+        <v>24433396.46464647</v>
+      </c>
+      <c r="H25" t="n">
+        <v>81.51066919191919</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.95625</v>
+      </c>
+      <c r="J25" t="n">
+        <v>26.61948051948052</v>
+      </c>
+      <c r="K25" t="n">
+        <v>186.4922077922078</v>
+      </c>
+      <c r="L25" t="n">
+        <v>78.21428571428571</v>
+      </c>
+      <c r="M25" t="n">
+        <v>55253.24675324675</v>
+      </c>
+      <c r="N25" t="n">
+        <v>18529610.38961039</v>
+      </c>
+      <c r="O25" t="n">
+        <v>81.59610389610388</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.733766233766233</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>27.47636895268474</v>
+      </c>
+      <c r="R25" t="n">
+        <v>182.4109823564593</v>
+      </c>
+      <c r="S25" t="n">
+        <v>76.63702900717703</v>
+      </c>
+      <c r="T25" t="n">
+        <v>87685.25634635831</v>
+      </c>
+      <c r="U25" t="n">
+        <v>15156340.43975944</v>
+      </c>
+      <c r="V25" t="n">
+        <v>78.41133539340777</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.780843799840511</v>
+      </c>
+      <c r="X25" t="n">
+        <v>25.01114649398402</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>185.3202174128948</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>72.60999323585136</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>39593.49752713597</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>11835444.52750402</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>78.52147737845678</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.501768635635913</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>31.13333333333334</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>175.8666666666666</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>144</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>166400</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>23.98095238095238</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>192.0571428571429</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>265.5714285714286</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>174714.2857142857</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>69800000</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>284.7142857142857</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>27.04340277777778</v>
+      </c>
+      <c r="D26" t="n">
+        <v>185.7934027777778</v>
+      </c>
+      <c r="E26" t="n">
+        <v>74.77256944444444</v>
+      </c>
+      <c r="F26" t="n">
+        <v>37944.44444444445</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9630381.944444444</v>
+      </c>
+      <c r="H26" t="n">
+        <v>77.75694444444444</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.177083333333333</v>
+      </c>
+      <c r="J26" t="n">
+        <v>25.73650793650794</v>
+      </c>
+      <c r="K26" t="n">
+        <v>182.8619047619048</v>
+      </c>
+      <c r="L26" t="n">
+        <v>76.06190476190477</v>
+      </c>
+      <c r="M26" t="n">
+        <v>39874.60317460318</v>
+      </c>
+      <c r="N26" t="n">
+        <v>12814920.63492064</v>
+      </c>
+      <c r="O26" t="n">
+        <v>80.36507936507937</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.53015873015873</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>24.77234005030058</v>
+      </c>
+      <c r="R26" t="n">
+        <v>184.9763778984174</v>
+      </c>
+      <c r="S26" t="n">
+        <v>69.94230462519937</v>
+      </c>
+      <c r="T26" t="n">
+        <v>29177.45291988712</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5225371.522665931</v>
+      </c>
+      <c r="V26" t="n">
+        <v>75.94275088946141</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.061363636363636</v>
+      </c>
+      <c r="X26" t="n">
+        <v>24.88452699474439</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>182.1439233954451</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>75.42897356266921</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>42075.5701544832</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>11397566.55120242</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>80.13436693741041</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.374523013218665</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>22.61904761904762</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>185.5714285714286</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>185.1428571428571</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>87714.28571428571</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>32528571.42857143</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>208.7142857142857</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>185.0833333333333</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>115.6666666666667</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>70166.66666666667</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>19833333.33333333</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>118.6666666666667</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.833333333333333</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>25.42857142857143</v>
+      </c>
+      <c r="D27" t="n">
+        <v>183.2757936507937</v>
+      </c>
+      <c r="E27" t="n">
+        <v>72.74603174603173</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12369.04761904762</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4658333.333333334</v>
+      </c>
+      <c r="H27" t="n">
+        <v>77.0515873015873</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26.67063492063492</v>
+      </c>
+      <c r="K27" t="n">
+        <v>181.811507936508</v>
+      </c>
+      <c r="L27" t="n">
+        <v>78.50595238095239</v>
+      </c>
+      <c r="M27" t="n">
+        <v>41051.5873015873</v>
+      </c>
+      <c r="N27" t="n">
+        <v>21766865.07936508</v>
+      </c>
+      <c r="O27" t="n">
+        <v>80.99801587301587</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.390873015873016</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>25.93607232366631</v>
+      </c>
+      <c r="R27" t="n">
+        <v>183.7775689223058</v>
+      </c>
+      <c r="S27" t="n">
+        <v>70.77873254564985</v>
+      </c>
+      <c r="T27" t="n">
+        <v>10356.2477622628</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3548066.237021124</v>
+      </c>
+      <c r="V27" t="n">
+        <v>75.22756892230576</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.022556390977444</v>
+      </c>
+      <c r="X27" t="n">
+        <v>24.90726220312687</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>179.0880057286072</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>75.8843895452918</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>34330.26017424514</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>17827916.96503162</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>81.09424752357083</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.756253729562</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>25.79047619047619</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>184.2738095238095</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>236.7142857142857</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>50571.42857142857</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>18371428.57142857</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>247</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>179.375</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>130500</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>40375000</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>29.39220779220779</v>
+      </c>
+      <c r="D28" t="n">
+        <v>182.4766233766234</v>
+      </c>
+      <c r="E28" t="n">
+        <v>84.28051948051949</v>
+      </c>
+      <c r="F28" t="n">
+        <v>113241.5584415584</v>
+      </c>
+      <c r="G28" t="n">
+        <v>42176623.37662338</v>
+      </c>
+      <c r="H28" t="n">
+        <v>85.1168831168831</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.355844155844156</v>
+      </c>
+      <c r="J28" t="n">
+        <v>25.8961038961039</v>
+      </c>
+      <c r="K28" t="n">
+        <v>183.5675324675325</v>
+      </c>
+      <c r="L28" t="n">
+        <v>70.53376623376623</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10405.1948051948</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2824870.12987013</v>
+      </c>
+      <c r="O28" t="n">
+        <v>75.02337662337663</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.054545454545455</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>28.06515766841854</v>
+      </c>
+      <c r="R28" t="n">
+        <v>185.1296782927218</v>
+      </c>
+      <c r="S28" t="n">
+        <v>79.98739847109411</v>
+      </c>
+      <c r="T28" t="n">
+        <v>88465.4005414875</v>
+      </c>
+      <c r="U28" t="n">
+        <v>26683116.34018156</v>
+      </c>
+      <c r="V28" t="n">
+        <v>81.7469939480809</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.409022137283007</v>
+      </c>
+      <c r="X28" t="n">
+        <v>25.86947931658622</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>183.1059908853632</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>68.55922200098401</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>13622.77031747447</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2199373.418370885</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>73.94821535298816</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.007518796992481</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>25.76190476190476</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>180.952380952381</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>145.7142857142857</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>164428.5714285714</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>54357142.85714286</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>148.7142857142857</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>25.21428571428572</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>180.2142857142857</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>157.2857142857143</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>21714.28571428571</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>5746428.571428572</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>168.1428571428571</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.571428571428572</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>24.93896103896104</v>
+      </c>
+      <c r="D29" t="n">
+        <v>185.0051948051948</v>
+      </c>
+      <c r="E29" t="n">
+        <v>69.93246753246753</v>
+      </c>
+      <c r="F29" t="n">
+        <v>21489.61038961039</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2936883.116883117</v>
+      </c>
+      <c r="H29" t="n">
+        <v>74.58571428571429</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>28</v>
+      </c>
+      <c r="K29" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="L29" t="n">
+        <v>74.44444444444444</v>
+      </c>
+      <c r="M29" t="n">
+        <v>23777.77777777778</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5713888.888888889</v>
+      </c>
+      <c r="O29" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>24.36049328690633</v>
+      </c>
+      <c r="R29" t="n">
+        <v>183.7260067287785</v>
+      </c>
+      <c r="S29" t="n">
+        <v>68.88316997615911</v>
+      </c>
+      <c r="T29" t="n">
+        <v>22425.37153365958</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2877586.256587615</v>
+      </c>
+      <c r="V29" t="n">
+        <v>73.97668454733673</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.052199008720748</v>
+      </c>
+      <c r="X29" t="n">
+        <v>28.41553403970284</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>181.8954059884823</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>72.94997564243089</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>23837.9212554587</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>4825104.085112305</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>74.29874123562469</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.280461749917359</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>187.9380952380952</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>375</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>63857.14285714286</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>15385714.28571429</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>393.4285714285714</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>29.83333333333333</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>187.0833333333333</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>28500</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2133333.333333333</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>93.66666666666667</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.333333333333333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>23.77738095238095</v>
+      </c>
+      <c r="D30" t="n">
+        <v>184.3706349206349</v>
+      </c>
+      <c r="E30" t="n">
+        <v>72.64801587301586</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25884.52380952381</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5553650.793650794</v>
+      </c>
+      <c r="H30" t="n">
+        <v>78.36349206349207</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>184.3931818181818</v>
+      </c>
+      <c r="L30" t="n">
+        <v>72.64318181818182</v>
+      </c>
+      <c r="M30" t="n">
+        <v>30803.40909090909</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4272954.545454546</v>
+      </c>
+      <c r="O30" t="n">
+        <v>75.82954545454545</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.092045454545455</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>23.94831168831169</v>
+      </c>
+      <c r="R30" t="n">
+        <v>182.7966233766234</v>
+      </c>
+      <c r="S30" t="n">
+        <v>68.82623376623378</v>
+      </c>
+      <c r="T30" t="n">
+        <v>22253.37662337662</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2923159.090909091</v>
+      </c>
+      <c r="V30" t="n">
+        <v>74.73545454545454</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>25.39250221269958</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>184.6279086264612</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>68.4930899144715</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>29341.92248540933</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2767531.00024975</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>73.31931461082777</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.125565509052351</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>186.6619047619047</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>257.5714285714286</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>91428.57142857143</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>13771428.57142857</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>272.8571428571428</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>26.13741496598639</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>184.5163265306122</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>295.4285714285714</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>153571.4285714286</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>16735714.28571429</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>312.5714285714286</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.142857142857143</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>26.72857142857143</v>
+      </c>
+      <c r="D31" t="n">
+        <v>181.8428571428572</v>
+      </c>
+      <c r="E31" t="n">
+        <v>79.37142857142855</v>
+      </c>
+      <c r="F31" t="n">
+        <v>48757.14285714286</v>
+      </c>
+      <c r="G31" t="n">
+        <v>22368571.42857143</v>
+      </c>
+      <c r="H31" t="n">
+        <v>82.28571428571429</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.985714285714286</v>
+      </c>
+      <c r="J31" t="n">
+        <v>26.17727272727273</v>
+      </c>
+      <c r="K31" t="n">
+        <v>185.0613636363636</v>
+      </c>
+      <c r="L31" t="n">
+        <v>72.18068181818182</v>
+      </c>
+      <c r="M31" t="n">
+        <v>18135.22727272727</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4050113.636363636</v>
+      </c>
+      <c r="O31" t="n">
+        <v>75.71022727272728</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.079545454545455</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>27.01030316474416</v>
+      </c>
+      <c r="R31" t="n">
+        <v>182.8603475303165</v>
+      </c>
+      <c r="S31" t="n">
+        <v>75.57592280390416</v>
+      </c>
+      <c r="T31" t="n">
+        <v>39139.06536527654</v>
+      </c>
+      <c r="U31" t="n">
+        <v>10651582.18722272</v>
+      </c>
+      <c r="V31" t="n">
+        <v>79.29196243714877</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.590008873114463</v>
+      </c>
+      <c r="X31" t="n">
+        <v>27.0748403751421</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>182.9446865634366</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>70.79759507733647</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>18960.0504667746</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2827900.746882428</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>74.57742292190568</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.019418081918082</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>115</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>78500</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>21125000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>166.3333333333333</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>5787500</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>173.1666666666667</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.333333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AT31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,851 +574,3983 @@
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.13253968253968</v>
+        <v>26.2</v>
       </c>
       <c r="D2" t="n">
-        <v>186.0837301587302</v>
+        <v>185.1068181818182</v>
       </c>
       <c r="E2" t="n">
-        <v>71.66984126984127</v>
+        <v>72.16931818181818</v>
       </c>
       <c r="F2" t="n">
-        <v>15115.87301587301</v>
+        <v>18896.59090909091</v>
       </c>
       <c r="G2" t="n">
-        <v>3307172.619047619</v>
+        <v>4010340.909090909</v>
       </c>
       <c r="H2" t="n">
-        <v>75.26071428571429</v>
+        <v>75.64204545454545</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1.079545454545455</v>
       </c>
       <c r="J2" t="n">
-        <v>26.17727272727273</v>
+        <v>26.21363636363636</v>
       </c>
       <c r="K2" t="n">
-        <v>185.0613636363636</v>
+        <v>185.9279461279461</v>
       </c>
       <c r="L2" t="n">
-        <v>72.18068181818182</v>
+        <v>76.13771043771044</v>
       </c>
       <c r="M2" t="n">
-        <v>18135.22727272727</v>
+        <v>46726.93602693603</v>
       </c>
       <c r="N2" t="n">
-        <v>4050113.636363636</v>
+        <v>10679335.01683502</v>
       </c>
       <c r="O2" t="n">
-        <v>75.71022727272728</v>
+        <v>79.21531986531987</v>
       </c>
       <c r="P2" t="n">
-        <v>1.079545454545455</v>
+        <v>1.502188552188552</v>
       </c>
       <c r="Q2" t="n">
-        <v>26.1475319792989</v>
+        <v>26.86402688307861</v>
       </c>
       <c r="R2" t="n">
-        <v>184.2959796677841</v>
+        <v>182.4820542883043</v>
       </c>
       <c r="S2" t="n">
-        <v>70.31352664670334</v>
+        <v>70.84157655881793</v>
       </c>
       <c r="T2" t="n">
-        <v>14658.17330121841</v>
+        <v>19007.834858309</v>
       </c>
       <c r="U2" t="n">
-        <v>2487069.116921091</v>
+        <v>2946547.406935338</v>
       </c>
       <c r="V2" t="n">
-        <v>74.25444590914516</v>
+        <v>74.74160942984219</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>1.01048951048951</v>
       </c>
       <c r="X2" t="n">
-        <v>27.0748403751421</v>
+        <v>24.32679261559696</v>
       </c>
       <c r="Y2" t="n">
-        <v>182.9446865634366</v>
+        <v>185.0423550724638</v>
       </c>
       <c r="Z2" t="n">
-        <v>70.79759507733647</v>
+        <v>73.41820048309178</v>
       </c>
       <c r="AA2" t="n">
-        <v>18960.0504667746</v>
+        <v>39348.09351276742</v>
       </c>
       <c r="AB2" t="n">
-        <v>2827900.746882428</v>
+        <v>7448110.593512769</v>
       </c>
       <c r="AC2" t="n">
-        <v>74.57742292190568</v>
+        <v>78.88438923395445</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.019418081918082</v>
-      </c>
+        <v>1.207192891649413</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.92261904761905</v>
+        <v>25.76851851851852</v>
       </c>
       <c r="D3" t="n">
-        <v>185.7956349206349</v>
+        <v>183.6689814814815</v>
       </c>
       <c r="E3" t="n">
-        <v>74.66071428571429</v>
+        <v>73.06712962962963</v>
       </c>
       <c r="F3" t="n">
-        <v>37539.68253968254</v>
+        <v>11993.05555555555</v>
       </c>
       <c r="G3" t="n">
-        <v>9468055.555555556</v>
+        <v>5959953.703703704</v>
       </c>
       <c r="H3" t="n">
-        <v>77.75396825396827</v>
+        <v>77.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.170634920634921</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>28</v>
+        <v>25.19047619047619</v>
       </c>
       <c r="K3" t="n">
-        <v>181.8888888888889</v>
+        <v>183.3710317460317</v>
       </c>
       <c r="L3" t="n">
-        <v>74.44444444444444</v>
+        <v>72.63492063492063</v>
       </c>
       <c r="M3" t="n">
-        <v>23777.77777777778</v>
+        <v>11940.47619047619</v>
       </c>
       <c r="N3" t="n">
-        <v>5713888.888888889</v>
+        <v>4691666.666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>76.77777777777777</v>
+        <v>77.08333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>1.444444444444444</v>
+        <v>1.015873015873016</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.00297509508036</v>
+        <v>25.01925040849673</v>
       </c>
       <c r="R3" t="n">
-        <v>184.9805221094695</v>
+        <v>181.6139093137255</v>
       </c>
       <c r="S3" t="n">
-        <v>70.26488949646844</v>
+        <v>69.25385008169934</v>
       </c>
       <c r="T3" t="n">
-        <v>29781.75070543491</v>
+        <v>10576.96078431372</v>
       </c>
       <c r="U3" t="n">
-        <v>5457003.544700913</v>
+        <v>2989696.435866013</v>
       </c>
       <c r="V3" t="n">
-        <v>76.01727921201605</v>
+        <v>74.41412377450982</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07012987012987</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>28.41553403970284</v>
+        <v>25.89261994271393</v>
       </c>
       <c r="Y3" t="n">
-        <v>181.8954059884823</v>
+        <v>183.5025689223058</v>
       </c>
       <c r="Z3" t="n">
-        <v>72.94997564243089</v>
+        <v>71.17278016469746</v>
       </c>
       <c r="AA3" t="n">
-        <v>23837.9212554587</v>
+        <v>10223.5096670247</v>
       </c>
       <c r="AB3" t="n">
-        <v>4825104.085112305</v>
+        <v>3875548.379878267</v>
       </c>
       <c r="AC3" t="n">
-        <v>74.29874123562469</v>
+        <v>75.64244987468672</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.280461749917359</v>
-      </c>
+        <v>1.031484962406015</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.64130591630591</v>
+        <v>25.81944444444445</v>
       </c>
       <c r="D4" t="n">
-        <v>183.3848484848484</v>
+        <v>185.7916666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>79.66388888888889</v>
+        <v>82.02777777777777</v>
       </c>
       <c r="F4" t="n">
-        <v>102847.8715728716</v>
+        <v>137347.2222222222</v>
       </c>
       <c r="G4" t="n">
-        <v>24314790.76479077</v>
+        <v>43990972.22222223</v>
       </c>
       <c r="H4" t="n">
-        <v>81.53167388167388</v>
+        <v>84.97916666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>1.962987012987013</v>
+        <v>2.75</v>
       </c>
       <c r="J4" t="n">
-        <v>25.9</v>
+        <v>27.63926767676767</v>
       </c>
       <c r="K4" t="n">
-        <v>184.025</v>
+        <v>183.8211174242424</v>
       </c>
       <c r="L4" t="n">
-        <v>73.325</v>
+        <v>79.62777777777778</v>
       </c>
       <c r="M4" t="n">
-        <v>12125</v>
+        <v>102038.7626262626</v>
       </c>
       <c r="N4" t="n">
-        <v>6107500</v>
+        <v>23733254.41919192</v>
       </c>
       <c r="O4" t="n">
-        <v>77.59999999999999</v>
+        <v>81.49646464646466</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>1.936363636363636</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.47299308878257</v>
+        <v>24.04750190694127</v>
       </c>
       <c r="R4" t="n">
-        <v>182.4607655502392</v>
+        <v>183.8410975180426</v>
       </c>
       <c r="S4" t="n">
-        <v>76.82624743677376</v>
+        <v>77.36023587396585</v>
       </c>
       <c r="T4" t="n">
-        <v>89327.79296726664</v>
+        <v>105291.1620606701</v>
       </c>
       <c r="U4" t="n">
-        <v>15978005.14543935</v>
+        <v>27348795.06982339</v>
       </c>
       <c r="V4" t="n">
-        <v>78.55938330675174</v>
+        <v>82.90515754268614</v>
       </c>
       <c r="W4" t="n">
-        <v>1.794178628389155</v>
+        <v>1.798160535117057</v>
       </c>
       <c r="X4" t="n">
-        <v>24.76307189542484</v>
+        <v>27.32834263689527</v>
       </c>
       <c r="Y4" t="n">
-        <v>181.6837535014006</v>
+        <v>182.1663277511961</v>
       </c>
       <c r="Z4" t="n">
-        <v>69.03118580765639</v>
+        <v>76.95980861244018</v>
       </c>
       <c r="AA4" t="n">
-        <v>10409.3837535014</v>
+        <v>89984.18726741095</v>
       </c>
       <c r="AB4" t="n">
-        <v>2958090.569561158</v>
+        <v>16895886.08120681</v>
       </c>
       <c r="AC4" t="n">
-        <v>74.48221288515406</v>
+        <v>78.83156565656566</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
-      </c>
+        <v>1.793590510366826</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.64696969696969</v>
+        <v>24.8974025974026</v>
       </c>
       <c r="D5" t="n">
-        <v>186.3166666666667</v>
+        <v>185.0350649350649</v>
       </c>
       <c r="E5" t="n">
-        <v>78.32575757575758</v>
+        <v>69.74675324675324</v>
       </c>
       <c r="F5" t="n">
-        <v>55871.21212121212</v>
+        <v>21372.72727272727</v>
       </c>
       <c r="G5" t="n">
-        <v>18772424.24242424</v>
+        <v>2897889.61038961</v>
       </c>
       <c r="H5" t="n">
-        <v>81.64999999999999</v>
+        <v>74.46363636363637</v>
       </c>
       <c r="I5" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>25.42857142857143</v>
+        <v>29.20779220779221</v>
       </c>
       <c r="K5" t="n">
-        <v>183.2757936507937</v>
+        <v>182.4155844155844</v>
       </c>
       <c r="L5" t="n">
-        <v>72.74603174603173</v>
+        <v>84.27272727272728</v>
       </c>
       <c r="M5" t="n">
-        <v>12369.04761904762</v>
+        <v>114064.9350649351</v>
       </c>
       <c r="N5" t="n">
-        <v>4658333.333333334</v>
+        <v>43168831.16883116</v>
       </c>
       <c r="O5" t="n">
-        <v>77.0515873015873</v>
+        <v>85.1038961038961</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>3.363636363636364</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.3901972254375</v>
+        <v>24.514034953573</v>
       </c>
       <c r="R5" t="n">
-        <v>185.1718325957456</v>
+        <v>183.8347567287785</v>
       </c>
       <c r="S5" t="n">
-        <v>73.2379745646336</v>
+        <v>68.96483664282577</v>
       </c>
       <c r="T5" t="n">
-        <v>40990.65939569372</v>
+        <v>22682.66320032624</v>
       </c>
       <c r="U5" t="n">
-        <v>12048851.94875469</v>
+        <v>2837950.839920949</v>
       </c>
       <c r="V5" t="n">
-        <v>78.78382887135747</v>
+        <v>73.83605954733673</v>
       </c>
       <c r="W5" t="n">
-        <v>1.559080952101547</v>
+        <v>1.057407342054081</v>
       </c>
       <c r="X5" t="n">
-        <v>25.93607232366631</v>
+        <v>28.10680023637689</v>
       </c>
       <c r="Y5" t="n">
-        <v>183.7775689223058</v>
+        <v>185.3072375755442</v>
       </c>
       <c r="Z5" t="n">
-        <v>70.77873254564985</v>
+        <v>79.94633427213519</v>
       </c>
       <c r="AA5" t="n">
-        <v>10356.2477622628</v>
+        <v>87918.55265253436</v>
       </c>
       <c r="AB5" t="n">
-        <v>3548066.237021124</v>
+        <v>26212757.75140192</v>
       </c>
       <c r="AC5" t="n">
-        <v>75.22756892230576</v>
+        <v>81.70477301112312</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.022556390977444</v>
-      </c>
+        <v>2.398611495293418</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>23.83287037037037</v>
+        <v>25.75324675324676</v>
       </c>
       <c r="D6" t="n">
-        <v>184.3027777777778</v>
+        <v>183.1649350649351</v>
       </c>
       <c r="E6" t="n">
-        <v>72.66342592592592</v>
+        <v>70.58571428571427</v>
       </c>
       <c r="F6" t="n">
-        <v>25957.87037037038</v>
+        <v>10651.94805194805</v>
       </c>
       <c r="G6" t="n">
-        <v>5616296.296296296</v>
+        <v>2938181.818181818</v>
       </c>
       <c r="H6" t="n">
-        <v>78.38703703703703</v>
+        <v>75.16623376623377</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1.054545454545455</v>
       </c>
       <c r="J6" t="n">
-        <v>24.91363636363637</v>
+        <v>26.21319444444444</v>
       </c>
       <c r="K6" t="n">
-        <v>184.9909090909091</v>
+        <v>186.2121527777778</v>
       </c>
       <c r="L6" t="n">
-        <v>69.75454545454545</v>
+        <v>71.76666666666668</v>
       </c>
       <c r="M6" t="n">
-        <v>21434.84848484848</v>
+        <v>15198.61111111111</v>
       </c>
       <c r="N6" t="n">
-        <v>2902121.212121212</v>
+        <v>3324331.597222222</v>
       </c>
       <c r="O6" t="n">
-        <v>74.44090909090909</v>
+        <v>75.21423611111111</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.85636363636364</v>
+        <v>26.11962047977085</v>
       </c>
       <c r="R6" t="n">
-        <v>183.1210606060606</v>
+        <v>183.0972387679155</v>
       </c>
       <c r="S6" t="n">
-        <v>68.57227272727273</v>
+        <v>68.82827903091061</v>
       </c>
       <c r="T6" t="n">
-        <v>22045.60606060606</v>
+        <v>13905.66133949593</v>
       </c>
       <c r="U6" t="n">
-        <v>2804518.939393939</v>
+        <v>2282661.108941184</v>
       </c>
       <c r="V6" t="n">
-        <v>74.61636363636363</v>
+        <v>74.06171055343988</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.014012303485988</v>
       </c>
       <c r="X6" t="n">
-        <v>24.48627804217866</v>
+        <v>26.20803785030759</v>
       </c>
       <c r="Y6" t="n">
-        <v>183.9897219757468</v>
+        <v>183.9826664198374</v>
       </c>
       <c r="Z6" t="n">
-        <v>69.0550514013247</v>
+        <v>70.29407265797067</v>
       </c>
       <c r="AA6" t="n">
-        <v>23428.99603846809</v>
+        <v>14595.63848067137</v>
       </c>
       <c r="AB6" t="n">
-        <v>2918670.007528703</v>
+        <v>2457271.003621744</v>
       </c>
       <c r="AC6" t="n">
-        <v>73.97335376838484</v>
+        <v>74.20948227576517</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.059656009966569</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>26.5</v>
+        <v>26.67142857142857</v>
       </c>
       <c r="D7" t="n">
-        <v>181.6166666666667</v>
+        <v>186.2454545454545</v>
       </c>
       <c r="E7" t="n">
-        <v>79.33333333333333</v>
+        <v>78.37012987012987</v>
       </c>
       <c r="F7" t="n">
-        <v>48350</v>
+        <v>56266.23376623377</v>
       </c>
       <c r="G7" t="n">
-        <v>22721666.66666667</v>
+        <v>18876363.63636364</v>
       </c>
       <c r="H7" t="n">
-        <v>82.46666666666667</v>
+        <v>81.68701298701298</v>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>1.746753246753247</v>
       </c>
       <c r="J7" t="n">
-        <v>26.56623376623377</v>
+        <v>26.11527777777778</v>
       </c>
       <c r="K7" t="n">
-        <v>184.4883116883117</v>
+        <v>183.7819444444444</v>
       </c>
       <c r="L7" t="n">
-        <v>72.54025974025974</v>
+        <v>72.84305555555557</v>
       </c>
       <c r="M7" t="n">
-        <v>30853.24675324676</v>
+        <v>23261.11111111111</v>
       </c>
       <c r="N7" t="n">
-        <v>4245064.935064935</v>
+        <v>6043472.222222222</v>
       </c>
       <c r="O7" t="n">
-        <v>75.79220779220779</v>
+        <v>76.98194444444444</v>
       </c>
       <c r="P7" t="n">
-        <v>1.092207792207792</v>
+        <v>1.216666666666667</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.10535369220152</v>
+        <v>25.37793302553028</v>
       </c>
       <c r="R7" t="n">
-        <v>182.9437387853692</v>
+        <v>185.2280304236826</v>
       </c>
       <c r="S7" t="n">
-        <v>75.61857660455486</v>
+        <v>73.2909347199965</v>
       </c>
       <c r="T7" t="n">
-        <v>40015.57625948929</v>
+        <v>41501.31053792381</v>
       </c>
       <c r="U7" t="n">
-        <v>10581679.2184265</v>
+        <v>12201935.21073384</v>
       </c>
       <c r="V7" t="n">
-        <v>79.29395617667357</v>
+        <v>78.77123220029398</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62167701863354</v>
+        <v>1.572379946521823</v>
       </c>
       <c r="X7" t="n">
-        <v>25.15736516616215</v>
+        <v>26.87193118338453</v>
       </c>
       <c r="Y7" t="n">
-        <v>184.6406867818898</v>
+        <v>182.6657061533527</v>
       </c>
       <c r="Z7" t="n">
-        <v>68.26133352862676</v>
+        <v>71.84591606858055</v>
       </c>
       <c r="AA7" t="n">
-        <v>28967.6916316766</v>
+        <v>35689.36057811933</v>
       </c>
       <c r="AB7" t="n">
-        <v>2731299.165120594</v>
+        <v>6310427.957071897</v>
       </c>
       <c r="AC7" t="n">
-        <v>73.30449142336361</v>
+        <v>76.09006313301272</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11053640594994</v>
-      </c>
+        <v>1.318681087527585</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.07460317460318</v>
+        <v>25.25</v>
       </c>
       <c r="D8" t="n">
-        <v>183.8365079365079</v>
+        <v>184.8125</v>
       </c>
       <c r="E8" t="n">
-        <v>72.74920634920635</v>
+        <v>80.15625</v>
       </c>
       <c r="F8" t="n">
-        <v>23369.84126984127</v>
+        <v>99468.75</v>
       </c>
       <c r="G8" t="n">
-        <v>5969682.539682539</v>
+        <v>32765625</v>
       </c>
       <c r="H8" t="n">
-        <v>76.96507936507938</v>
+        <v>84.03125</v>
       </c>
       <c r="I8" t="n">
-        <v>1.219047619047619</v>
+        <v>2.15625</v>
       </c>
       <c r="J8" t="n">
-        <v>25.77272727272727</v>
+        <v>23.8281746031746</v>
       </c>
       <c r="K8" t="n">
-        <v>183.6318181818182</v>
+        <v>184.302380952381</v>
       </c>
       <c r="L8" t="n">
-        <v>70.59242424242423</v>
+        <v>72.72579365079365</v>
       </c>
       <c r="M8" t="n">
-        <v>10457.57575757576</v>
+        <v>26063.88888888889</v>
       </c>
       <c r="N8" t="n">
-        <v>2918787.878787879</v>
+        <v>5656825.396825396</v>
       </c>
       <c r="O8" t="n">
-        <v>75.11818181818182</v>
+        <v>78.46031746031746</v>
       </c>
       <c r="P8" t="n">
-        <v>1.048484848484849</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.96402524854335</v>
+        <v>25.855772005772</v>
       </c>
       <c r="R8" t="n">
-        <v>182.6634044350005</v>
+        <v>184.1880230880231</v>
       </c>
       <c r="S8" t="n">
-        <v>71.87585213032581</v>
+        <v>77.27236652236653</v>
       </c>
       <c r="T8" t="n">
-        <v>35593.03546590261</v>
+        <v>78728.06637806639</v>
       </c>
       <c r="U8" t="n">
-        <v>6259644.937952297</v>
+        <v>17743391.05339105</v>
       </c>
       <c r="V8" t="n">
-        <v>76.01202020396259</v>
+        <v>81.17049062049061</v>
       </c>
       <c r="W8" t="n">
-        <v>1.318752411719837</v>
+        <v>1.631673881673882</v>
       </c>
       <c r="X8" t="n">
-        <v>26.09410268094479</v>
+        <v>23.88309429700734</v>
       </c>
       <c r="Y8" t="n">
-        <v>182.8482937140832</v>
+        <v>183.1223997741389</v>
       </c>
       <c r="Z8" t="n">
-        <v>68.7466285663654</v>
+        <v>68.63958780350086</v>
       </c>
       <c r="AA8" t="n">
-        <v>13965.69580516949</v>
+        <v>22119.83625070582</v>
       </c>
       <c r="AB8" t="n">
-        <v>2265718.263461684</v>
+        <v>2842382.693393563</v>
       </c>
       <c r="AC8" t="n">
-        <v>74.02654110022532</v>
+        <v>74.61526821005081</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.008771929824561</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>29.25757575757576</v>
+        <v>26.39318181818182</v>
       </c>
       <c r="D9" t="n">
-        <v>182.439393939394</v>
+        <v>184.4386363636364</v>
       </c>
       <c r="E9" t="n">
-        <v>84.22727272727273</v>
+        <v>72.41590909090908</v>
       </c>
       <c r="F9" t="n">
-        <v>113348.4848484848</v>
+        <v>30848.86363636364</v>
       </c>
       <c r="G9" t="n">
-        <v>42606060.6060606</v>
+        <v>4192272.727272728</v>
       </c>
       <c r="H9" t="n">
-        <v>85.13636363636363</v>
+        <v>75.77272727272728</v>
       </c>
       <c r="I9" t="n">
-        <v>3.348484848484848</v>
+        <v>1.080681818181818</v>
       </c>
       <c r="J9" t="n">
-        <v>25.375</v>
+        <v>25.46666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>185.28125</v>
+        <v>182.3539682539682</v>
       </c>
       <c r="L9" t="n">
-        <v>80.53125</v>
+        <v>75.93492063492064</v>
       </c>
       <c r="M9" t="n">
-        <v>102937.5</v>
+        <v>39509.52380952381</v>
       </c>
       <c r="N9" t="n">
-        <v>34968750</v>
+        <v>12910158.73015873</v>
       </c>
       <c r="O9" t="n">
-        <v>84.40625</v>
+        <v>80.46031746031746</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1875</v>
+        <v>1.561904761904762</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.22986343366778</v>
+        <v>25.22519452039189</v>
       </c>
       <c r="R9" t="n">
-        <v>185.2794964697139</v>
+        <v>184.7918509341536</v>
       </c>
       <c r="S9" t="n">
-        <v>80.13914437012262</v>
+        <v>67.97866683754842</v>
       </c>
       <c r="T9" t="n">
-        <v>89703.22370865849</v>
+        <v>28702.98017771702</v>
       </c>
       <c r="U9" t="n">
-        <v>27157866.49944259</v>
+        <v>2569418.019480519</v>
       </c>
       <c r="V9" t="n">
-        <v>81.7432878112226</v>
+        <v>73.01642999544316</v>
       </c>
       <c r="W9" t="n">
-        <v>2.438730955035303</v>
+        <v>1.102969355206197</v>
       </c>
       <c r="X9" t="n">
-        <v>25.94307359307359</v>
+        <v>25.04524128045867</v>
       </c>
       <c r="Y9" t="n">
-        <v>184.156277056277</v>
+        <v>182.1596160361378</v>
       </c>
       <c r="Z9" t="n">
-        <v>77.11363636363636</v>
+        <v>75.61025061894627</v>
       </c>
       <c r="AA9" t="n">
-        <v>76910.60606060606</v>
+        <v>42858.57881249185</v>
       </c>
       <c r="AB9" t="n">
-        <v>16885454.54545454</v>
+        <v>11397228.34773922</v>
       </c>
       <c r="AC9" t="n">
-        <v>80.97207792207791</v>
+        <v>80.09540589844937</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.63961038961039</v>
-      </c>
+        <v>1.404826043521696</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>Sp7nVfDF</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.65555555555556</v>
+        <v>26.58333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>182.4314814814815</v>
+        <v>181.9126984126984</v>
       </c>
       <c r="E10" t="n">
-        <v>76.0537037037037</v>
+        <v>78.31746031746032</v>
       </c>
       <c r="F10" t="n">
-        <v>39538.88888888889</v>
+        <v>40916.66666666666</v>
       </c>
       <c r="G10" t="n">
-        <v>12939629.62962963</v>
+        <v>21588690.47619047</v>
       </c>
       <c r="H10" t="n">
-        <v>80.37037037037037</v>
+        <v>80.95039682539684</v>
       </c>
       <c r="I10" t="n">
-        <v>1.581481481481481</v>
+        <v>2.382936507936508</v>
       </c>
       <c r="J10" t="n">
-        <v>26.59722222222222</v>
+        <v>26.92261904761905</v>
       </c>
       <c r="K10" t="n">
-        <v>181.8356481481482</v>
+        <v>185.7956349206349</v>
       </c>
       <c r="L10" t="n">
-        <v>78.34953703703704</v>
+        <v>74.66071428571429</v>
       </c>
       <c r="M10" t="n">
-        <v>40986.11111111111</v>
+        <v>37539.68253968254</v>
       </c>
       <c r="N10" t="n">
-        <v>21190972.22222222</v>
+        <v>9468055.555555556</v>
       </c>
       <c r="O10" t="n">
-        <v>80.94212962962963</v>
+        <v>77.75396825396827</v>
       </c>
       <c r="P10" t="n">
-        <v>2.363425925925926</v>
+        <v>1.170634920634921</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.96944816053512</v>
+        <v>24.95362811791383</v>
       </c>
       <c r="R10" t="n">
-        <v>182.2165217391305</v>
+        <v>178.6663265306122</v>
       </c>
       <c r="S10" t="n">
-        <v>75.59074693422519</v>
+        <v>76.30544217687074</v>
       </c>
       <c r="T10" t="n">
-        <v>42956.22073578596</v>
+        <v>35058.95691609977</v>
       </c>
       <c r="U10" t="n">
-        <v>11501501.2541806</v>
+        <v>19138568.59410431</v>
       </c>
       <c r="V10" t="n">
-        <v>80.15676142697882</v>
+        <v>81.29036281179138</v>
       </c>
       <c r="W10" t="n">
-        <v>1.381387959866221</v>
+        <v>1.81201814058957</v>
       </c>
       <c r="X10" t="n">
-        <v>24.91812169312169</v>
+        <v>25.0085555891477</v>
       </c>
       <c r="Y10" t="n">
-        <v>178.8746031746032</v>
+        <v>185.0365282743572</v>
       </c>
       <c r="Z10" t="n">
-        <v>76.02301587301586</v>
+        <v>70.07106402369561</v>
       </c>
       <c r="AA10" t="n">
-        <v>34832.67195767196</v>
+        <v>29457.84139106507</v>
       </c>
       <c r="AB10" t="n">
-        <v>18629718.91534391</v>
+        <v>5130384.053994251</v>
       </c>
       <c r="AC10" t="n">
-        <v>81.24153439153439</v>
+        <v>75.87821454860928</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.79457671957672</v>
+        <v>1.061363636363636</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>26.44285714285714</v>
+      </c>
+      <c r="K11" t="n">
+        <v>181.7285714285714</v>
+      </c>
+      <c r="L11" t="n">
+        <v>79.17142857142858</v>
+      </c>
+      <c r="M11" t="n">
+        <v>47657.14285714286</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22161428.57142857</v>
+      </c>
+      <c r="O11" t="n">
+        <v>82.39999999999999</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>28.37794005474043</v>
+      </c>
+      <c r="R11" t="n">
+        <v>180.9383705427251</v>
+      </c>
+      <c r="S11" t="n">
+        <v>73.24696812363389</v>
+      </c>
+      <c r="T11" t="n">
+        <v>24140.82136287009</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5020995.599612842</v>
+      </c>
+      <c r="V11" t="n">
+        <v>74.70744155785883</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.320203962591902</v>
+      </c>
+      <c r="X11" t="n">
+        <v>27.04030316474416</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>183.1660618160308</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75.4944942324756</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>39256.20822241939</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10399475.04436557</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>79.32339100857735</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.618580301685892</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>26.21363636363636</v>
+      </c>
+      <c r="D12" t="n">
+        <v>185.9279461279461</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76.13771043771044</v>
+      </c>
+      <c r="F12" t="n">
+        <v>46726.93602693603</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10679335.01683502</v>
+      </c>
+      <c r="H12" t="n">
+        <v>79.21531986531987</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.502188552188552</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25.76851851851852</v>
+      </c>
+      <c r="K12" t="n">
+        <v>183.6689814814815</v>
+      </c>
+      <c r="L12" t="n">
+        <v>73.06712962962963</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11993.05555555555</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5959953.703703704</v>
+      </c>
+      <c r="O12" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>24.32679261559696</v>
+      </c>
+      <c r="R12" t="n">
+        <v>185.0423550724638</v>
+      </c>
+      <c r="S12" t="n">
+        <v>73.41820048309178</v>
+      </c>
+      <c r="T12" t="n">
+        <v>39348.09351276742</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7448110.593512769</v>
+      </c>
+      <c r="V12" t="n">
+        <v>78.88438923395445</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.207192891649413</v>
+      </c>
+      <c r="X12" t="n">
+        <v>25.01925040849673</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>181.6139093137255</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>69.25385008169934</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>10576.96078431372</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2989696.435866013</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>74.41412377450982</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23.70238095238095</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>183.0880952380952</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>217000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>46983333.33333334</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>381.8333333333333</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>23.71904761904761</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>181.9214285714285</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>303.8571428571428</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>43285.71428571428</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12614285.71428571</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>341.8571428571428</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.428571428571429</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.21319444444444</v>
+      </c>
+      <c r="D13" t="n">
+        <v>186.2121527777778</v>
+      </c>
+      <c r="E13" t="n">
+        <v>71.76666666666668</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15198.61111111111</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3324331.597222222</v>
+      </c>
+      <c r="H13" t="n">
+        <v>75.21423611111111</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>184.8125</v>
+      </c>
+      <c r="L13" t="n">
+        <v>80.15625</v>
+      </c>
+      <c r="M13" t="n">
+        <v>99468.75</v>
+      </c>
+      <c r="N13" t="n">
+        <v>32765625</v>
+      </c>
+      <c r="O13" t="n">
+        <v>84.03125</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.15625</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26.20803785030759</v>
+      </c>
+      <c r="R13" t="n">
+        <v>183.9826664198374</v>
+      </c>
+      <c r="S13" t="n">
+        <v>70.29407265797067</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14595.63848067137</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2457271.003621744</v>
+      </c>
+      <c r="V13" t="n">
+        <v>74.20948227576517</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25.855772005772</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>184.1880230880231</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>77.27236652236653</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>78728.06637806639</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17743391.05339105</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>81.17049062049061</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.631673881673882</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27.95238095238095</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>180.3928571428571</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>47714.28571428572</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>21757142.85714286</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>187.4285714285714</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>28.43333333333333</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>186.3119047619048</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>312.5714285714286</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>454571.4285714286</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>120642857.1428571</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>317</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11.57142857142857</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.11527777777778</v>
+      </c>
+      <c r="D14" t="n">
+        <v>183.7819444444444</v>
+      </c>
+      <c r="E14" t="n">
+        <v>72.84305555555557</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23261.11111111111</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6043472.222222222</v>
+      </c>
+      <c r="H14" t="n">
+        <v>76.98194444444444</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.216666666666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.81944444444445</v>
+      </c>
+      <c r="K14" t="n">
+        <v>185.7916666666667</v>
+      </c>
+      <c r="L14" t="n">
+        <v>82.02777777777777</v>
+      </c>
+      <c r="M14" t="n">
+        <v>137347.2222222222</v>
+      </c>
+      <c r="N14" t="n">
+        <v>43990972.22222223</v>
+      </c>
+      <c r="O14" t="n">
+        <v>84.97916666666667</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>26.87193118338453</v>
+      </c>
+      <c r="R14" t="n">
+        <v>182.6657061533527</v>
+      </c>
+      <c r="S14" t="n">
+        <v>71.84591606858055</v>
+      </c>
+      <c r="T14" t="n">
+        <v>35689.36057811933</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6310427.957071897</v>
+      </c>
+      <c r="V14" t="n">
+        <v>76.09006313301272</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.318681087527585</v>
+      </c>
+      <c r="X14" t="n">
+        <v>24.04750190694127</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>183.8410975180426</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>77.36023587396585</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>105291.1620606701</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>27348795.06982339</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>82.90515754268614</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.798160535117057</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>27.61428571428572</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>180.6690476190476</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>302.8571428571428</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>93142.85714285714</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>22557142.85714286</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>314</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>27.04444444444444</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>318.1666666666667</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>464166.6666666667</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>107495833.3333333</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>329</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.833333333333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>27.63926767676767</v>
+      </c>
+      <c r="D15" t="n">
+        <v>183.8211174242424</v>
+      </c>
+      <c r="E15" t="n">
+        <v>79.62777777777778</v>
+      </c>
+      <c r="F15" t="n">
+        <v>102038.7626262626</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23733254.41919192</v>
+      </c>
+      <c r="H15" t="n">
+        <v>81.49646464646466</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.936363636363636</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26.67142857142857</v>
+      </c>
+      <c r="K15" t="n">
+        <v>186.2454545454545</v>
+      </c>
+      <c r="L15" t="n">
+        <v>78.37012987012987</v>
+      </c>
+      <c r="M15" t="n">
+        <v>56266.23376623377</v>
+      </c>
+      <c r="N15" t="n">
+        <v>18876363.63636364</v>
+      </c>
+      <c r="O15" t="n">
+        <v>81.68701298701298</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.746753246753247</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>27.32834263689527</v>
+      </c>
+      <c r="R15" t="n">
+        <v>182.1663277511961</v>
+      </c>
+      <c r="S15" t="n">
+        <v>76.95980861244018</v>
+      </c>
+      <c r="T15" t="n">
+        <v>89984.18726741095</v>
+      </c>
+      <c r="U15" t="n">
+        <v>16895886.08120681</v>
+      </c>
+      <c r="V15" t="n">
+        <v>78.83156565656566</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.793590510366826</v>
+      </c>
+      <c r="X15" t="n">
+        <v>25.37793302553028</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>185.2280304236826</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>73.2909347199965</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>41501.31053792381</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12201935.21073384</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>78.77123220029398</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.572379946521823</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>31.11111111111111</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>174.8888888888889</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>146.8333333333333</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>176166.6666666667</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>30583333.33333333</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>147.8333333333333</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>23.64761904761905</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>192.2952380952381</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>264.1428571428572</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>165714.2857142857</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>68485714.28571428</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>284.2857142857143</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.857142857142857</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26.92261904761905</v>
+      </c>
+      <c r="D16" t="n">
+        <v>185.7956349206349</v>
+      </c>
+      <c r="E16" t="n">
+        <v>74.66071428571429</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37539.68253968254</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9468055.555555556</v>
+      </c>
+      <c r="H16" t="n">
+        <v>77.75396825396827</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.170634920634921</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25.46666666666667</v>
+      </c>
+      <c r="K16" t="n">
+        <v>182.3539682539682</v>
+      </c>
+      <c r="L16" t="n">
+        <v>75.93492063492064</v>
+      </c>
+      <c r="M16" t="n">
+        <v>39509.52380952381</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12910158.73015873</v>
+      </c>
+      <c r="O16" t="n">
+        <v>80.46031746031746</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.561904761904762</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>25.0085555891477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>185.0365282743572</v>
+      </c>
+      <c r="S16" t="n">
+        <v>70.07106402369561</v>
+      </c>
+      <c r="T16" t="n">
+        <v>29457.84139106507</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5130384.053994251</v>
+      </c>
+      <c r="V16" t="n">
+        <v>75.87821454860928</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.061363636363636</v>
+      </c>
+      <c r="X16" t="n">
+        <v>25.04524128045867</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>182.1596160361378</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>75.61025061894627</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>42858.57881249185</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11397228.34773922</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>80.09540589844937</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.404826043521696</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>23.04761904761904</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>184.7142857142857</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>207.8571428571429</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>104571.4285714286</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>39128571.42857143</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>232.5714285714286</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>26.61111111111111</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>184.9444444444445</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>77333.33333333333</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>21833333.33333333</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>132</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.166666666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25.19047619047619</v>
+      </c>
+      <c r="D17" t="n">
+        <v>183.3710317460317</v>
+      </c>
+      <c r="E17" t="n">
+        <v>72.63492063492063</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11940.47619047619</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4691666.666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>77.08333333333333</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.015873015873016</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="K17" t="n">
+        <v>181.9126984126984</v>
+      </c>
+      <c r="L17" t="n">
+        <v>78.31746031746032</v>
+      </c>
+      <c r="M17" t="n">
+        <v>40916.66666666666</v>
+      </c>
+      <c r="N17" t="n">
+        <v>21588690.47619047</v>
+      </c>
+      <c r="O17" t="n">
+        <v>80.95039682539684</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.382936507936508</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>25.89261994271393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>183.5025689223058</v>
+      </c>
+      <c r="S17" t="n">
+        <v>71.17278016469746</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10223.5096670247</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3875548.379878267</v>
+      </c>
+      <c r="V17" t="n">
+        <v>75.64244987468672</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.031484962406015</v>
+      </c>
+      <c r="X17" t="n">
+        <v>24.95362811791383</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>178.6663265306122</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>76.30544217687074</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>35058.95691609977</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>19138568.59410431</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>81.29036281179138</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.81201814058957</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>26.0047619047619</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>184.202380952381</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>257.1428571428572</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>54428.57142857143</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>18214285.71428571</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>267.8571428571428</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>127</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>132800</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>38700000</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>129</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>29.20779220779221</v>
+      </c>
+      <c r="D18" t="n">
+        <v>182.4155844155844</v>
+      </c>
+      <c r="E18" t="n">
+        <v>84.27272727272728</v>
+      </c>
+      <c r="F18" t="n">
+        <v>114064.9350649351</v>
+      </c>
+      <c r="G18" t="n">
+        <v>43168831.16883116</v>
+      </c>
+      <c r="H18" t="n">
+        <v>85.1038961038961</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.363636363636364</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25.75324675324676</v>
+      </c>
+      <c r="K18" t="n">
+        <v>183.1649350649351</v>
+      </c>
+      <c r="L18" t="n">
+        <v>70.58571428571427</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10651.94805194805</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2938181.818181818</v>
+      </c>
+      <c r="O18" t="n">
+        <v>75.16623376623377</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.054545454545455</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>28.10680023637689</v>
+      </c>
+      <c r="R18" t="n">
+        <v>185.3072375755442</v>
+      </c>
+      <c r="S18" t="n">
+        <v>79.94633427213519</v>
+      </c>
+      <c r="T18" t="n">
+        <v>87918.55265253436</v>
+      </c>
+      <c r="U18" t="n">
+        <v>26212757.75140192</v>
+      </c>
+      <c r="V18" t="n">
+        <v>81.70477301112312</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.398611495293418</v>
+      </c>
+      <c r="X18" t="n">
+        <v>26.11962047977085</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>183.0972387679155</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>68.82827903091061</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>13905.66133949593</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2282661.108941184</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>74.06171055343988</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.014012303485988</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>26.14285714285714</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>146.1428571428571</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>157000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>46357142.85714286</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>149.2857142857143</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>180.7857142857143</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>135.5714285714286</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>18857.14285714286</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4071428.571428571</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>145.8571428571429</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.285714285714286</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>24.8974025974026</v>
+      </c>
+      <c r="D19" t="n">
+        <v>185.0350649350649</v>
+      </c>
+      <c r="E19" t="n">
+        <v>69.74675324675324</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21372.72727272727</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2897889.61038961</v>
+      </c>
+      <c r="H19" t="n">
+        <v>74.46363636363637</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>24.514034953573</v>
+      </c>
+      <c r="R19" t="n">
+        <v>183.8347567287785</v>
+      </c>
+      <c r="S19" t="n">
+        <v>68.96483664282577</v>
+      </c>
+      <c r="T19" t="n">
+        <v>22682.66320032624</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2837950.839920949</v>
+      </c>
+      <c r="V19" t="n">
+        <v>73.83605954733673</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.057407342054081</v>
+      </c>
+      <c r="X19" t="n">
+        <v>28.37794005474043</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>180.9383705427251</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>73.24696812363389</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>24140.82136287009</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5020995.599612842</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>74.70744155785883</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.320203962591902</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>25.07619047619048</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>188.052380952381</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>376.1428571428572</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>71714.28571428571</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>16557142.85714286</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>395.5714285714286</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>25600</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1760000</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>23.8281746031746</v>
+      </c>
+      <c r="D20" t="n">
+        <v>184.302380952381</v>
+      </c>
+      <c r="E20" t="n">
+        <v>72.72579365079365</v>
+      </c>
+      <c r="F20" t="n">
+        <v>26063.88888888889</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5656825.396825396</v>
+      </c>
+      <c r="H20" t="n">
+        <v>78.46031746031746</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>26.39318181818182</v>
+      </c>
+      <c r="K20" t="n">
+        <v>184.4386363636364</v>
+      </c>
+      <c r="L20" t="n">
+        <v>72.41590909090908</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30848.86363636364</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4192272.727272728</v>
+      </c>
+      <c r="O20" t="n">
+        <v>75.77272727272728</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.080681818181818</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>23.88309429700734</v>
+      </c>
+      <c r="R20" t="n">
+        <v>183.1223997741389</v>
+      </c>
+      <c r="S20" t="n">
+        <v>68.63958780350086</v>
+      </c>
+      <c r="T20" t="n">
+        <v>22119.83625070582</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2842382.693393563</v>
+      </c>
+      <c r="V20" t="n">
+        <v>74.61526821005081</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>25.22519452039189</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>184.7918509341536</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>67.97866683754842</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>28702.98017771702</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2569418.019480519</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>73.01642999544316</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.102969355206197</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>24.67857142857143</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>186.6904761904762</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>226.8571428571429</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>78428.57142857143</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>241.8571428571429</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>27.27006802721089</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>183.7612244897959</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>351.1428571428572</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>184142.8571428571</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>21328571.42857143</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>367.7142857142857</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.285714285714286</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>26.44285714285714</v>
+      </c>
+      <c r="D21" t="n">
+        <v>181.7285714285714</v>
+      </c>
+      <c r="E21" t="n">
+        <v>79.17142857142858</v>
+      </c>
+      <c r="F21" t="n">
+        <v>47657.14285714286</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22161428.57142857</v>
+      </c>
+      <c r="H21" t="n">
+        <v>82.39999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>185.1068181818182</v>
+      </c>
+      <c r="L21" t="n">
+        <v>72.16931818181818</v>
+      </c>
+      <c r="M21" t="n">
+        <v>18896.59090909091</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4010340.909090909</v>
+      </c>
+      <c r="O21" t="n">
+        <v>75.64204545454545</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.079545454545455</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>27.04030316474416</v>
+      </c>
+      <c r="R21" t="n">
+        <v>183.1660618160308</v>
+      </c>
+      <c r="S21" t="n">
+        <v>75.4944942324756</v>
+      </c>
+      <c r="T21" t="n">
+        <v>39256.20822241939</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10399475.04436557</v>
+      </c>
+      <c r="V21" t="n">
+        <v>79.32339100857735</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.618580301685892</v>
+      </c>
+      <c r="X21" t="n">
+        <v>26.86402688307861</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>182.4820542883043</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>70.84157655881793</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>19007.834858309</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2946547.406935338</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>74.74160942984219</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.01048951048951</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>27.125</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>81250</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>26875000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>122</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>26.91666666666667</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>185.0833333333333</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>178.1666666666667</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>33500</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5866666.666666667</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.39318181818182</v>
+      </c>
+      <c r="D22" t="n">
+        <v>184.4386363636364</v>
+      </c>
+      <c r="E22" t="n">
+        <v>72.41590909090908</v>
+      </c>
+      <c r="F22" t="n">
+        <v>30848.86363636364</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4192272.727272728</v>
+      </c>
+      <c r="H22" t="n">
+        <v>75.77272727272728</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.080681818181818</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>25.22519452039189</v>
+      </c>
+      <c r="R22" t="n">
+        <v>184.7918509341536</v>
+      </c>
+      <c r="S22" t="n">
+        <v>67.97866683754842</v>
+      </c>
+      <c r="T22" t="n">
+        <v>28702.98017771702</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2569418.019480519</v>
+      </c>
+      <c r="V22" t="n">
+        <v>73.01642999544316</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.102969355206197</v>
+      </c>
+      <c r="X22" t="n">
+        <v>28.37794005474043</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>180.9383705427251</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>73.24696812363389</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>24140.82136287009</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5020995.599612842</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>74.70744155785883</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.320203962591902</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>27.27006802721089</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>183.7612244897959</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>351.1428571428572</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>184142.8571428571</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>21328571.42857143</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>367.7142857142857</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>6.285714285714286</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>25600</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1760000</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25.76851851851852</v>
+      </c>
+      <c r="D23" t="n">
+        <v>183.6689814814815</v>
+      </c>
+      <c r="E23" t="n">
+        <v>73.06712962962963</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11993.05555555555</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5959953.703703704</v>
+      </c>
+      <c r="H23" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>24.8974025974026</v>
+      </c>
+      <c r="K23" t="n">
+        <v>185.0350649350649</v>
+      </c>
+      <c r="L23" t="n">
+        <v>69.74675324675324</v>
+      </c>
+      <c r="M23" t="n">
+        <v>21372.72727272727</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2897889.61038961</v>
+      </c>
+      <c r="O23" t="n">
+        <v>74.46363636363637</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>25.01925040849673</v>
+      </c>
+      <c r="R23" t="n">
+        <v>181.6139093137255</v>
+      </c>
+      <c r="S23" t="n">
+        <v>69.25385008169934</v>
+      </c>
+      <c r="T23" t="n">
+        <v>10576.96078431372</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2989696.435866013</v>
+      </c>
+      <c r="V23" t="n">
+        <v>74.41412377450982</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>24.514034953573</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>183.8347567287785</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>68.96483664282577</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>22682.66320032624</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2837950.839920949</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>73.83605954733673</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.057407342054081</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>23.71904761904761</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>181.9214285714285</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>303.8571428571428</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>43285.71428571428</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>12614285.71428571</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>341.8571428571428</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>25.07619047619048</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>188.052380952381</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>376.1428571428572</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>71714.28571428571</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>16557142.85714286</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>395.5714285714286</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.428571428571429</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25.75324675324676</v>
+      </c>
+      <c r="D24" t="n">
+        <v>183.1649350649351</v>
+      </c>
+      <c r="E24" t="n">
+        <v>70.58571428571427</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10651.94805194805</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2938181.818181818</v>
+      </c>
+      <c r="H24" t="n">
+        <v>75.16623376623377</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.054545454545455</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23.8281746031746</v>
+      </c>
+      <c r="K24" t="n">
+        <v>184.302380952381</v>
+      </c>
+      <c r="L24" t="n">
+        <v>72.72579365079365</v>
+      </c>
+      <c r="M24" t="n">
+        <v>26063.88888888889</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5656825.396825396</v>
+      </c>
+      <c r="O24" t="n">
+        <v>78.46031746031746</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>26.11962047977085</v>
+      </c>
+      <c r="R24" t="n">
+        <v>183.0972387679155</v>
+      </c>
+      <c r="S24" t="n">
+        <v>68.82827903091061</v>
+      </c>
+      <c r="T24" t="n">
+        <v>13905.66133949593</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2282661.108941184</v>
+      </c>
+      <c r="V24" t="n">
+        <v>74.06171055343988</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.014012303485988</v>
+      </c>
+      <c r="X24" t="n">
+        <v>23.88309429700734</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>183.1223997741389</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>68.63958780350086</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>22119.83625070582</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2842382.693393563</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>74.61526821005081</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>180.7857142857143</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>135.5714285714286</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>18857.14285714286</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>4071428.571428571</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>145.8571428571429</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>24.67857142857143</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>186.6904761904762</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>226.8571428571429</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>78428.57142857143</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>241.8571428571429</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.142857142857143</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>185.1068181818182</v>
+      </c>
+      <c r="E25" t="n">
+        <v>72.16931818181818</v>
+      </c>
+      <c r="F25" t="n">
+        <v>18896.59090909091</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4010340.909090909</v>
+      </c>
+      <c r="H25" t="n">
+        <v>75.64204545454545</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.079545454545455</v>
+      </c>
+      <c r="J25" t="n">
+        <v>25.81944444444445</v>
+      </c>
+      <c r="K25" t="n">
+        <v>185.7916666666667</v>
+      </c>
+      <c r="L25" t="n">
+        <v>82.02777777777777</v>
+      </c>
+      <c r="M25" t="n">
+        <v>137347.2222222222</v>
+      </c>
+      <c r="N25" t="n">
+        <v>43990972.22222223</v>
+      </c>
+      <c r="O25" t="n">
+        <v>84.97916666666667</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>26.86402688307861</v>
+      </c>
+      <c r="R25" t="n">
+        <v>182.4820542883043</v>
+      </c>
+      <c r="S25" t="n">
+        <v>70.84157655881793</v>
+      </c>
+      <c r="T25" t="n">
+        <v>19007.834858309</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2946547.406935338</v>
+      </c>
+      <c r="V25" t="n">
+        <v>74.74160942984219</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01048951048951</v>
+      </c>
+      <c r="X25" t="n">
+        <v>24.04750190694127</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>183.8410975180426</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>77.36023587396585</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>105291.1620606701</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>27348795.06982339</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>82.90515754268614</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.798160535117057</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>26.91666666666667</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>185.0833333333333</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>178.1666666666667</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>33500</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>5866666.666666667</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>27.04444444444444</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>318.1666666666667</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>464166.6666666667</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>107495833.3333333</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>329</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8.833333333333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>184.8125</v>
+      </c>
+      <c r="E26" t="n">
+        <v>80.15625</v>
+      </c>
+      <c r="F26" t="n">
+        <v>99468.75</v>
+      </c>
+      <c r="G26" t="n">
+        <v>32765625</v>
+      </c>
+      <c r="H26" t="n">
+        <v>84.03125</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.15625</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26.92261904761905</v>
+      </c>
+      <c r="K26" t="n">
+        <v>185.7956349206349</v>
+      </c>
+      <c r="L26" t="n">
+        <v>74.66071428571429</v>
+      </c>
+      <c r="M26" t="n">
+        <v>37539.68253968254</v>
+      </c>
+      <c r="N26" t="n">
+        <v>9468055.555555556</v>
+      </c>
+      <c r="O26" t="n">
+        <v>77.75396825396827</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.170634920634921</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>25.855772005772</v>
+      </c>
+      <c r="R26" t="n">
+        <v>184.1880230880231</v>
+      </c>
+      <c r="S26" t="n">
+        <v>77.27236652236653</v>
+      </c>
+      <c r="T26" t="n">
+        <v>78728.06637806639</v>
+      </c>
+      <c r="U26" t="n">
+        <v>17743391.05339105</v>
+      </c>
+      <c r="V26" t="n">
+        <v>81.17049062049061</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.631673881673882</v>
+      </c>
+      <c r="X26" t="n">
+        <v>25.0085555891477</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>185.0365282743572</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>70.07106402369561</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>29457.84139106507</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>5130384.053994251</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>75.87821454860928</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.061363636363636</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>28.43333333333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>186.3119047619048</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>312.5714285714286</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>454571.4285714286</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>120642857.1428571</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>317</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>11.57142857142857</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>23.04761904761904</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>184.7142857142857</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>207.8571428571429</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>104571.4285714286</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>39128571.42857143</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>232.5714285714286</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.428571428571428</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26.67142857142857</v>
+      </c>
+      <c r="D27" t="n">
+        <v>186.2454545454545</v>
+      </c>
+      <c r="E27" t="n">
+        <v>78.37012987012987</v>
+      </c>
+      <c r="F27" t="n">
+        <v>56266.23376623377</v>
+      </c>
+      <c r="G27" t="n">
+        <v>18876363.63636364</v>
+      </c>
+      <c r="H27" t="n">
+        <v>81.68701298701298</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.746753246753247</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26.21319444444444</v>
+      </c>
+      <c r="K27" t="n">
+        <v>186.2121527777778</v>
+      </c>
+      <c r="L27" t="n">
+        <v>71.76666666666668</v>
+      </c>
+      <c r="M27" t="n">
+        <v>15198.61111111111</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3324331.597222222</v>
+      </c>
+      <c r="O27" t="n">
+        <v>75.21423611111111</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>25.37793302553028</v>
+      </c>
+      <c r="R27" t="n">
+        <v>185.2280304236826</v>
+      </c>
+      <c r="S27" t="n">
+        <v>73.2909347199965</v>
+      </c>
+      <c r="T27" t="n">
+        <v>41501.31053792381</v>
+      </c>
+      <c r="U27" t="n">
+        <v>12201935.21073384</v>
+      </c>
+      <c r="V27" t="n">
+        <v>78.77123220029398</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.572379946521823</v>
+      </c>
+      <c r="X27" t="n">
+        <v>26.20803785030759</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>183.9826664198374</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>70.29407265797067</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>14595.63848067137</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2457271.003621744</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>74.20948227576517</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>23.64761904761905</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>192.2952380952381</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>264.1428571428572</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>165714.2857142857</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>68485714.28571428</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>284.2857142857143</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>27.95238095238095</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>180.3928571428571</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>47714.28571428572</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>21757142.85714286</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>187.4285714285714</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>4.428571428571429</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="D28" t="n">
+        <v>181.9126984126984</v>
+      </c>
+      <c r="E28" t="n">
+        <v>78.31746031746032</v>
+      </c>
+      <c r="F28" t="n">
+        <v>40916.66666666666</v>
+      </c>
+      <c r="G28" t="n">
+        <v>21588690.47619047</v>
+      </c>
+      <c r="H28" t="n">
+        <v>80.95039682539684</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.382936507936508</v>
+      </c>
+      <c r="J28" t="n">
+        <v>26.21363636363636</v>
+      </c>
+      <c r="K28" t="n">
+        <v>185.9279461279461</v>
+      </c>
+      <c r="L28" t="n">
+        <v>76.13771043771044</v>
+      </c>
+      <c r="M28" t="n">
+        <v>46726.93602693603</v>
+      </c>
+      <c r="N28" t="n">
+        <v>10679335.01683502</v>
+      </c>
+      <c r="O28" t="n">
+        <v>79.21531986531987</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.502188552188552</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>24.95362811791383</v>
+      </c>
+      <c r="R28" t="n">
+        <v>178.6663265306122</v>
+      </c>
+      <c r="S28" t="n">
+        <v>76.30544217687074</v>
+      </c>
+      <c r="T28" t="n">
+        <v>35058.95691609977</v>
+      </c>
+      <c r="U28" t="n">
+        <v>19138568.59410431</v>
+      </c>
+      <c r="V28" t="n">
+        <v>81.29036281179138</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.81201814058957</v>
+      </c>
+      <c r="X28" t="n">
+        <v>24.32679261559696</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>185.0423550724638</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>73.41820048309178</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>39348.09351276742</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7448110.593512769</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>78.88438923395445</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.207192891649413</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>127</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>132800</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>38700000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>129</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>23.70238095238095</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>183.0880952380952</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>217000</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>46983333.33333334</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>381.8333333333333</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.833333333333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>25.46666666666667</v>
+      </c>
+      <c r="D29" t="n">
+        <v>182.3539682539682</v>
+      </c>
+      <c r="E29" t="n">
+        <v>75.93492063492064</v>
+      </c>
+      <c r="F29" t="n">
+        <v>39509.52380952381</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12910158.73015873</v>
+      </c>
+      <c r="H29" t="n">
+        <v>80.46031746031746</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.561904761904762</v>
+      </c>
+      <c r="J29" t="n">
+        <v>25.19047619047619</v>
+      </c>
+      <c r="K29" t="n">
+        <v>183.3710317460317</v>
+      </c>
+      <c r="L29" t="n">
+        <v>72.63492063492063</v>
+      </c>
+      <c r="M29" t="n">
+        <v>11940.47619047619</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4691666.666666667</v>
+      </c>
+      <c r="O29" t="n">
+        <v>77.08333333333333</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.015873015873016</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>25.04524128045867</v>
+      </c>
+      <c r="R29" t="n">
+        <v>182.1596160361378</v>
+      </c>
+      <c r="S29" t="n">
+        <v>75.61025061894627</v>
+      </c>
+      <c r="T29" t="n">
+        <v>42858.57881249185</v>
+      </c>
+      <c r="U29" t="n">
+        <v>11397228.34773922</v>
+      </c>
+      <c r="V29" t="n">
+        <v>80.09540589844937</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.404826043521696</v>
+      </c>
+      <c r="X29" t="n">
+        <v>25.89261994271393</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>183.5025689223058</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>71.17278016469746</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>10223.5096670247</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>3875548.379878267</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>75.64244987468672</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.031484962406015</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>26.61111111111111</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>184.9444444444445</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>77333.33333333333</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>21833333.33333333</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>132</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>26.0047619047619</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>184.202380952381</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>257.1428571428572</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>54428.57142857143</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>18214285.71428571</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>267.8571428571428</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.285714285714286</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>26.11527777777778</v>
+      </c>
+      <c r="D30" t="n">
+        <v>183.7819444444444</v>
+      </c>
+      <c r="E30" t="n">
+        <v>72.84305555555557</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23261.11111111111</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6043472.222222222</v>
+      </c>
+      <c r="H30" t="n">
+        <v>76.98194444444444</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.216666666666667</v>
+      </c>
+      <c r="J30" t="n">
+        <v>26.44285714285714</v>
+      </c>
+      <c r="K30" t="n">
+        <v>181.7285714285714</v>
+      </c>
+      <c r="L30" t="n">
+        <v>79.17142857142858</v>
+      </c>
+      <c r="M30" t="n">
+        <v>47657.14285714286</v>
+      </c>
+      <c r="N30" t="n">
+        <v>22161428.57142857</v>
+      </c>
+      <c r="O30" t="n">
+        <v>82.39999999999999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>26.87193118338453</v>
+      </c>
+      <c r="R30" t="n">
+        <v>182.6657061533527</v>
+      </c>
+      <c r="S30" t="n">
+        <v>71.84591606858055</v>
+      </c>
+      <c r="T30" t="n">
+        <v>35689.36057811933</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6310427.957071897</v>
+      </c>
+      <c r="V30" t="n">
+        <v>76.09006313301272</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.318681087527585</v>
+      </c>
+      <c r="X30" t="n">
+        <v>27.04030316474416</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>183.1660618160308</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>75.4944942324756</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>39256.20822241939</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>10399475.04436557</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>79.32339100857735</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.618580301685892</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>27.61428571428572</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>180.6690476190476</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>302.8571428571428</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>93142.85714285714</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>22557142.85714286</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>314</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>27.125</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>81250</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>26875000</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>122</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>29.20779220779221</v>
+      </c>
+      <c r="D31" t="n">
+        <v>182.4155844155844</v>
+      </c>
+      <c r="E31" t="n">
+        <v>84.27272727272728</v>
+      </c>
+      <c r="F31" t="n">
+        <v>114064.9350649351</v>
+      </c>
+      <c r="G31" t="n">
+        <v>43168831.16883116</v>
+      </c>
+      <c r="H31" t="n">
+        <v>85.1038961038961</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.363636363636364</v>
+      </c>
+      <c r="J31" t="n">
+        <v>27.63926767676767</v>
+      </c>
+      <c r="K31" t="n">
+        <v>183.8211174242424</v>
+      </c>
+      <c r="L31" t="n">
+        <v>79.62777777777778</v>
+      </c>
+      <c r="M31" t="n">
+        <v>102038.7626262626</v>
+      </c>
+      <c r="N31" t="n">
+        <v>23733254.41919192</v>
+      </c>
+      <c r="O31" t="n">
+        <v>81.49646464646466</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.936363636363636</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>28.10680023637689</v>
+      </c>
+      <c r="R31" t="n">
+        <v>185.3072375755442</v>
+      </c>
+      <c r="S31" t="n">
+        <v>79.94633427213519</v>
+      </c>
+      <c r="T31" t="n">
+        <v>87918.55265253436</v>
+      </c>
+      <c r="U31" t="n">
+        <v>26212757.75140192</v>
+      </c>
+      <c r="V31" t="n">
+        <v>81.70477301112312</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.398611495293418</v>
+      </c>
+      <c r="X31" t="n">
+        <v>27.32834263689527</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>182.1663277511961</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>76.95980861244018</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>89984.18726741095</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>16895886.08120681</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>78.83156565656566</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.793590510366826</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>26.14285714285714</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>146.1428571428571</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>157000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>46357142.85714286</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>149.2857142857143</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>31.11111111111111</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>174.8888888888889</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>146.8333333333333</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>176166.6666666667</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>30583333.33333333</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>147.8333333333333</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -658,95 +658,81 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.39696969696969</v>
+        <v>26.32929292929293</v>
       </c>
       <c r="D2" t="n">
-        <v>185.9946127946128</v>
+        <v>184.6404040404041</v>
       </c>
       <c r="E2" t="n">
-        <v>75.98771043771043</v>
+        <v>72.12727272727273</v>
       </c>
       <c r="F2" t="n">
-        <v>46276.93602693603</v>
+        <v>30074.74747474748</v>
       </c>
       <c r="G2" t="n">
-        <v>10298085.01683502</v>
+        <v>3966969.696969697</v>
       </c>
       <c r="H2" t="n">
-        <v>79.03198653198653</v>
+        <v>75.52424242424243</v>
       </c>
       <c r="I2" t="n">
-        <v>1.468855218855219</v>
-      </c>
-      <c r="J2" t="n">
-        <v>25.78472222222222</v>
-      </c>
-      <c r="K2" t="n">
-        <v>183.5601851851852</v>
-      </c>
-      <c r="L2" t="n">
-        <v>72.99537037037037</v>
-      </c>
-      <c r="M2" t="n">
-        <v>11962.96296296296</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5907407.407407408</v>
-      </c>
-      <c r="O2" t="n">
-        <v>77.44675925925925</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
+        <v>1.061616161616162</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>24.10679261559696</v>
+        <v>25.03207747905116</v>
       </c>
       <c r="R2" t="n">
-        <v>185.2623550724637</v>
+        <v>184.8642210323789</v>
       </c>
       <c r="S2" t="n">
-        <v>73.61153381642511</v>
+        <v>67.77802017670439</v>
       </c>
       <c r="T2" t="n">
-        <v>39961.42684610076</v>
+        <v>28751.03421432368</v>
       </c>
       <c r="U2" t="n">
-        <v>7853777.260179435</v>
+        <v>2433879.77994228</v>
       </c>
       <c r="V2" t="n">
-        <v>79.11772256728777</v>
+        <v>72.8673755727703</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21385955831608</v>
+        <v>1.085713589529379</v>
       </c>
       <c r="X2" t="n">
-        <v>25.04866217320262</v>
+        <v>28.45692303809396</v>
       </c>
       <c r="Y2" t="n">
-        <v>181.5330269607843</v>
+        <v>181.1141706301132</v>
       </c>
       <c r="Z2" t="n">
-        <v>69.32737949346405</v>
+        <v>73.11254318661102</v>
       </c>
       <c r="AA2" t="n">
-        <v>10613.72549019608</v>
+        <v>24172.23830035447</v>
       </c>
       <c r="AB2" t="n">
-        <v>2998887.612336601</v>
+        <v>4845934.466654701</v>
       </c>
       <c r="AC2" t="n">
-        <v>74.3920649509804</v>
+        <v>74.44049829123105</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>1.3018287940653</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -768,1073 +754,1279 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.16319444444444</v>
+        <v>25.625</v>
       </c>
       <c r="D3" t="n">
-        <v>186.3027777777778</v>
+        <v>183.3214285714286</v>
       </c>
       <c r="E3" t="n">
-        <v>71.87291666666667</v>
+        <v>72.82142857142857</v>
       </c>
       <c r="F3" t="n">
-        <v>15214.23611111111</v>
+        <v>11841.26984126984</v>
       </c>
       <c r="G3" t="n">
-        <v>3395581.597222222</v>
+        <v>5839682.539682539</v>
       </c>
       <c r="H3" t="n">
-        <v>75.28298611111111</v>
+        <v>77.46230158730158</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>25.21875</v>
+        <v>24.96818181818182</v>
       </c>
       <c r="K3" t="n">
-        <v>184.71875</v>
+        <v>185.0011363636364</v>
       </c>
       <c r="L3" t="n">
-        <v>79.84375</v>
+        <v>69.94772727272728</v>
       </c>
       <c r="M3" t="n">
-        <v>96656.25</v>
+        <v>21722.72727272727</v>
       </c>
       <c r="N3" t="n">
-        <v>30625000</v>
+        <v>2941818.181818182</v>
       </c>
       <c r="O3" t="n">
-        <v>83.5625</v>
+        <v>74.52613636363637</v>
       </c>
       <c r="P3" t="n">
-        <v>2.125</v>
+        <v>1.011363636363636</v>
       </c>
       <c r="Q3" t="n">
-        <v>26.42212776258829</v>
+        <v>25.23933369644154</v>
       </c>
       <c r="R3" t="n">
-        <v>183.3650677356269</v>
+        <v>181.3953703703704</v>
       </c>
       <c r="S3" t="n">
-        <v>70.2803665176198</v>
+        <v>69.48708242556283</v>
       </c>
       <c r="T3" t="n">
-        <v>14658.68672628541</v>
+        <v>10708.93246187364</v>
       </c>
       <c r="U3" t="n">
-        <v>2387691.782130516</v>
+        <v>3026298.792665214</v>
       </c>
       <c r="V3" t="n">
-        <v>73.98634631085289</v>
+        <v>74.40732570806101</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>25.81075036075036</v>
+        <v>24.56522523370349</v>
       </c>
       <c r="Y3" t="n">
-        <v>184.140404040404</v>
+        <v>183.9370115928087</v>
       </c>
       <c r="Z3" t="n">
-        <v>77.02041847041846</v>
+        <v>68.74736321113134</v>
       </c>
       <c r="AA3" t="n">
-        <v>77812.91486291484</v>
+        <v>23078.89366403859</v>
       </c>
       <c r="AB3" t="n">
-        <v>16827027.41702742</v>
+        <v>2776782.62089494</v>
       </c>
       <c r="AC3" t="n">
-        <v>81.16269841269842</v>
+        <v>73.62812476037114</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.545093795093795</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+        <v>1.066180263644032</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>23.2125</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>182.24375</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>42500</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>11481250</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>346.375</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>24.73809523809524</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>187.9672619047619</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>390.625</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>74375</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17778125</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>412.25</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.20618686868687</v>
+        <v>25.6875</v>
       </c>
       <c r="D4" t="n">
-        <v>183.680808080808</v>
+        <v>182.9534090909091</v>
       </c>
       <c r="E4" t="n">
-        <v>72.73964646464647</v>
+        <v>70.49431818181819</v>
       </c>
       <c r="F4" t="n">
-        <v>24482.70202020202</v>
+        <v>10955.68181818182</v>
       </c>
       <c r="G4" t="n">
-        <v>6097904.04040404</v>
+        <v>2923863.636363637</v>
       </c>
       <c r="H4" t="n">
-        <v>76.80694444444444</v>
+        <v>75.11704545454546</v>
       </c>
       <c r="I4" t="n">
-        <v>1.237121212121212</v>
+        <v>1.048863636363636</v>
       </c>
       <c r="J4" t="n">
-        <v>25.77777777777778</v>
+        <v>23.78715277777778</v>
       </c>
       <c r="K4" t="n">
-        <v>186.1041666666667</v>
+        <v>184.1395833333333</v>
       </c>
       <c r="L4" t="n">
-        <v>81.77777777777779</v>
+        <v>72.63506944444444</v>
       </c>
       <c r="M4" t="n">
-        <v>134930.5555555555</v>
+        <v>26087.15277777778</v>
       </c>
       <c r="N4" t="n">
-        <v>42772222.22222223</v>
+        <v>5690737.847222222</v>
       </c>
       <c r="O4" t="n">
-        <v>84.875</v>
+        <v>78.40277777777777</v>
       </c>
       <c r="P4" t="n">
-        <v>2.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.78587855180558</v>
+        <v>26.11956589844176</v>
       </c>
       <c r="R4" t="n">
-        <v>182.6051798375633</v>
+        <v>182.6298493681502</v>
       </c>
       <c r="S4" t="n">
-        <v>71.96907396331738</v>
+        <v>68.8775616577676</v>
       </c>
       <c r="T4" t="n">
-        <v>34998.30794654039</v>
+        <v>13349.80493064017</v>
       </c>
       <c r="U4" t="n">
-        <v>6484454.272861371</v>
+        <v>2321393.532775863</v>
       </c>
       <c r="V4" t="n">
-        <v>76.24585260669693</v>
+        <v>74.06800083418361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.293417929632848</v>
+        <v>1.028565113376326</v>
       </c>
       <c r="X4" t="n">
-        <v>24.1308352402746</v>
+        <v>23.92256505973897</v>
       </c>
       <c r="Y4" t="n">
-        <v>183.6393431320777</v>
+        <v>183.1647493750211</v>
       </c>
       <c r="Z4" t="n">
-        <v>77.2562258489032</v>
+        <v>68.59315784658176</v>
       </c>
       <c r="AA4" t="n">
-        <v>107292.4151935022</v>
+        <v>22226.38093589181</v>
       </c>
       <c r="AB4" t="n">
-        <v>26940759.35553767</v>
+        <v>2833572.214269225</v>
       </c>
       <c r="AC4" t="n">
-        <v>82.81869137727261</v>
+        <v>74.56344515387994</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.837634219327583</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>181.3125</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>117.625</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>16125</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2825000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>23.90625</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>187.0416666666667</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>70625</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11850000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>222.25</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.875</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>27.70239898989899</v>
+        <v>26.11717171717172</v>
       </c>
       <c r="D5" t="n">
-        <v>184.2769255050505</v>
+        <v>184.8222222222222</v>
       </c>
       <c r="E5" t="n">
-        <v>79.7590909090909</v>
+        <v>72.2010101010101</v>
       </c>
       <c r="F5" t="n">
-        <v>103036.2373737374</v>
+        <v>19695.9595959596</v>
       </c>
       <c r="G5" t="n">
-        <v>24054466.54040404</v>
+        <v>4024343.434343434</v>
       </c>
       <c r="H5" t="n">
-        <v>81.60378787878788</v>
+        <v>75.85353535353536</v>
       </c>
       <c r="I5" t="n">
-        <v>1.947727272727273</v>
+        <v>1.070707070707071</v>
       </c>
       <c r="J5" t="n">
-        <v>26.64545454545454</v>
+        <v>25.6984126984127</v>
       </c>
       <c r="K5" t="n">
-        <v>186.2194805194805</v>
+        <v>185.8511904761905</v>
       </c>
       <c r="L5" t="n">
-        <v>78.56493506493507</v>
+        <v>81.66666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>57642.85714285714</v>
+        <v>134559.5238095238</v>
       </c>
       <c r="N5" t="n">
-        <v>19502337.66233766</v>
+        <v>42371428.57142857</v>
       </c>
       <c r="O5" t="n">
-        <v>81.84285714285714</v>
+        <v>84.89285714285714</v>
       </c>
       <c r="P5" t="n">
-        <v>1.746753246753247</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.14977120832384</v>
+        <v>26.70775274959183</v>
       </c>
       <c r="R5" t="n">
-        <v>181.9679150527835</v>
+        <v>182.3825156892207</v>
       </c>
       <c r="S5" t="n">
-        <v>76.84076099339256</v>
+        <v>70.8155599473607</v>
       </c>
       <c r="T5" t="n">
-        <v>89106.21107693476</v>
+        <v>18742.30177797228</v>
       </c>
       <c r="U5" t="n">
-        <v>16886833.50184173</v>
+        <v>2982268.487862358</v>
       </c>
       <c r="V5" t="n">
-        <v>78.77601010101009</v>
+        <v>74.75823579145418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.741011145287461</v>
+        <v>1.013597513597514</v>
       </c>
       <c r="X5" t="n">
-        <v>25.72434851480291</v>
+        <v>24.30763321346845</v>
       </c>
       <c r="Y5" t="n">
-        <v>185.1102910202289</v>
+        <v>183.6382339628335</v>
       </c>
       <c r="Z5" t="n">
-        <v>74.1323789900122</v>
+        <v>77.61811839680425</v>
       </c>
       <c r="AA5" t="n">
-        <v>42032.44606905935</v>
+        <v>109258.1603914229</v>
       </c>
       <c r="AB5" t="n">
-        <v>12225637.46086466</v>
+        <v>27758996.7408368</v>
       </c>
       <c r="AC5" t="n">
-        <v>79.17154617203653</v>
+        <v>82.85963020307577</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.626278428991734</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>1.89842331581462</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>26.5952380952381</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>184.8809523809524</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>182.4285714285714</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>34285.71428571428</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>6042857.142857143</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>26.52857142857143</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>182.4071428571428</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>319.1428571428572</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>468571.4285714286</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>118067857.1428571</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>330.8571428571428</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.857142857142858</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
+        <v>25.21875</v>
+      </c>
+      <c r="D6" t="n">
+        <v>184.71875</v>
+      </c>
+      <c r="E6" t="n">
+        <v>79.84375</v>
+      </c>
+      <c r="F6" t="n">
+        <v>96656.25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30625000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>83.5625</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="J6" t="n">
         <v>26.77976190476191</v>
       </c>
-      <c r="D6" t="n">
+      <c r="K6" t="n">
         <v>185.7420634920635</v>
       </c>
-      <c r="E6" t="n">
+      <c r="L6" t="n">
         <v>74.33928571428571</v>
       </c>
-      <c r="F6" t="n">
+      <c r="M6" t="n">
         <v>36682.53968253968</v>
       </c>
-      <c r="G6" t="n">
+      <c r="N6" t="n">
         <v>8864484.126984127</v>
       </c>
-      <c r="H6" t="n">
+      <c r="O6" t="n">
         <v>77.55753968253968</v>
       </c>
-      <c r="I6" t="n">
+      <c r="P6" t="n">
         <v>1.134920634920635</v>
       </c>
-      <c r="J6" t="n">
-        <v>25.29166666666667</v>
-      </c>
-      <c r="K6" t="n">
-        <v>182.0575396825397</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75.93849206349206</v>
-      </c>
-      <c r="M6" t="n">
-        <v>39470.2380952381</v>
-      </c>
-      <c r="N6" t="n">
-        <v>12944444.44444444</v>
-      </c>
-      <c r="O6" t="n">
-        <v>80.47817460317459</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.529761904761905</v>
-      </c>
       <c r="Q6" t="n">
-        <v>25.0420151851073</v>
+        <v>25.75107323232323</v>
       </c>
       <c r="R6" t="n">
-        <v>185.0630434258724</v>
+        <v>184.1645202020202</v>
       </c>
       <c r="S6" t="n">
-        <v>70.07674584187743</v>
+        <v>76.95536616161615</v>
       </c>
       <c r="T6" t="n">
-        <v>29301.27573449942</v>
+        <v>77690.46717171717</v>
       </c>
       <c r="U6" t="n">
-        <v>4961570.92268112</v>
+        <v>16608023.98989899</v>
       </c>
       <c r="V6" t="n">
-        <v>75.78856808396282</v>
+        <v>81.07986111111111</v>
       </c>
       <c r="W6" t="n">
-        <v>1.061363636363636</v>
+        <v>1.549873737373737</v>
       </c>
       <c r="X6" t="n">
-        <v>25.16388073624099</v>
+        <v>25.09554788940754</v>
       </c>
       <c r="Y6" t="n">
-        <v>182.2551262402194</v>
+        <v>184.9078904526273</v>
       </c>
       <c r="Z6" t="n">
-        <v>75.68508055091907</v>
+        <v>70.21636667426141</v>
       </c>
       <c r="AA6" t="n">
-        <v>43179.39513902246</v>
+        <v>29532.35091743864</v>
       </c>
       <c r="AB6" t="n">
-        <v>11485065.08243309</v>
+        <v>5135020.714340891</v>
       </c>
       <c r="AC6" t="n">
-        <v>80.11091610253102</v>
+        <v>75.79089649791405</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.423601553725777</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+        <v>1.054545454545454</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>28.37916666666666</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>186.3041666666667</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>315.75</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>464125</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>132687500</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>320</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>183.9583333333333</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>230</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>124125</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>46062500</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>255.125</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.125</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.06825396825397</v>
+        <v>26.7125</v>
       </c>
       <c r="D7" t="n">
-        <v>183.5329365079365</v>
+        <v>186.1920454545455</v>
       </c>
       <c r="E7" t="n">
-        <v>72.50793650793651</v>
+        <v>78.61931818181819</v>
       </c>
       <c r="F7" t="n">
-        <v>11716.66666666667</v>
+        <v>57982.95454545454</v>
       </c>
       <c r="G7" t="n">
-        <v>4701428.571428572</v>
+        <v>19615681.81818182</v>
       </c>
       <c r="H7" t="n">
-        <v>77.04047619047618</v>
+        <v>81.85113636363636</v>
       </c>
       <c r="I7" t="n">
-        <v>1.03015873015873</v>
+        <v>1.767045454545455</v>
       </c>
       <c r="J7" t="n">
-        <v>26.5</v>
+        <v>26.28950617283951</v>
       </c>
       <c r="K7" t="n">
-        <v>181.484126984127</v>
+        <v>186.2024691358025</v>
       </c>
       <c r="L7" t="n">
-        <v>78.28174603174602</v>
+        <v>71.87592592592593</v>
       </c>
       <c r="M7" t="n">
-        <v>39952.38095238095</v>
+        <v>15268.20987654321</v>
       </c>
       <c r="N7" t="n">
-        <v>22094246.03174603</v>
+        <v>3357183.641975308</v>
       </c>
       <c r="O7" t="n">
-        <v>81.00396825396827</v>
+        <v>75.16265432098766</v>
       </c>
       <c r="P7" t="n">
-        <v>2.382936507936508</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.89942266380237</v>
+        <v>25.68494131408891</v>
       </c>
       <c r="R7" t="n">
-        <v>183.4168546365915</v>
+        <v>185.1817319154276</v>
       </c>
       <c r="S7" t="n">
-        <v>71.34420873612603</v>
+        <v>74.12151343444249</v>
       </c>
       <c r="T7" t="n">
-        <v>10536.43483709273</v>
+        <v>41710.2084922451</v>
       </c>
       <c r="U7" t="n">
-        <v>4039630.012531328</v>
+        <v>12104989.59643839</v>
       </c>
       <c r="V7" t="n">
-        <v>75.82204171142141</v>
+        <v>79.1614665368956</v>
       </c>
       <c r="W7" t="n">
-        <v>1.041008771929825</v>
+        <v>1.599129989004131</v>
       </c>
       <c r="X7" t="n">
-        <v>25.22426303854875</v>
+        <v>26.42813473076631</v>
       </c>
       <c r="Y7" t="n">
-        <v>179.0536281179138</v>
+        <v>183.3086316380176</v>
       </c>
       <c r="Z7" t="n">
-        <v>76.45623582766439</v>
+        <v>70.32857976169379</v>
       </c>
       <c r="AA7" t="n">
-        <v>34783.56009070294</v>
+        <v>14664.86439161877</v>
       </c>
       <c r="AB7" t="n">
-        <v>18816405.89569161</v>
+        <v>2398715.446549877</v>
       </c>
       <c r="AC7" t="n">
-        <v>81.13163265306123</v>
+        <v>74.03548243504383</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.873129251700681</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>23.25416666666667</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>192.7875</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>230</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>138875</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>60775000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>249.25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>27.14583333333333</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>183.15625</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>177.125</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>21725000</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>185</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.375</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>29.01298701298701</v>
+        <v>26.5</v>
       </c>
       <c r="D8" t="n">
-        <v>182.5064935064935</v>
+        <v>181.484126984127</v>
       </c>
       <c r="E8" t="n">
-        <v>84.1038961038961</v>
+        <v>78.28174603174602</v>
       </c>
       <c r="F8" t="n">
-        <v>112701.2987012987</v>
+        <v>39952.38095238095</v>
       </c>
       <c r="G8" t="n">
-        <v>42922077.92207792</v>
+        <v>22094246.03174603</v>
       </c>
       <c r="H8" t="n">
-        <v>85.09090909090909</v>
+        <v>81.00396825396827</v>
       </c>
       <c r="I8" t="n">
-        <v>3.324675324675325</v>
+        <v>2.382936507936508</v>
       </c>
       <c r="J8" t="n">
-        <v>25.66883116883117</v>
+        <v>26.38311688311688</v>
       </c>
       <c r="K8" t="n">
-        <v>182.9077922077922</v>
+        <v>185.9239538239538</v>
       </c>
       <c r="L8" t="n">
-        <v>70.6038961038961</v>
+        <v>75.9037518037518</v>
       </c>
       <c r="M8" t="n">
-        <v>10897.4025974026</v>
+        <v>45980.23088023088</v>
       </c>
       <c r="N8" t="n">
-        <v>3005194.805194805</v>
+        <v>10231572.87157287</v>
       </c>
       <c r="O8" t="n">
-        <v>75.3025974025974</v>
+        <v>78.99884559884559</v>
       </c>
       <c r="P8" t="n">
-        <v>1.055844155844156</v>
+        <v>1.459018759018759</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.30203833161499</v>
+        <v>25.45280910609858</v>
       </c>
       <c r="R8" t="n">
-        <v>185.4322375755442</v>
+        <v>179.0008719715956</v>
       </c>
       <c r="S8" t="n">
-        <v>80.01657236737329</v>
+        <v>76.72815371762739</v>
       </c>
       <c r="T8" t="n">
-        <v>88395.93360491531</v>
+        <v>35632.98350041771</v>
       </c>
       <c r="U8" t="n">
-        <v>25539900.60854477</v>
+        <v>19649223.57978279</v>
       </c>
       <c r="V8" t="n">
-        <v>81.55715396350408</v>
+        <v>81.1875469924812</v>
       </c>
       <c r="W8" t="n">
-        <v>2.423611495293418</v>
+        <v>1.941619674185464</v>
       </c>
       <c r="X8" t="n">
-        <v>26.14906910132474</v>
+        <v>24.10867938479739</v>
       </c>
       <c r="Y8" t="n">
-        <v>182.6949831288177</v>
+        <v>185.1505900621118</v>
       </c>
       <c r="Z8" t="n">
-        <v>68.84143692564744</v>
+        <v>73.69560041407865</v>
       </c>
       <c r="AA8" t="n">
-        <v>13586.11246731548</v>
+        <v>40155.50872522922</v>
       </c>
       <c r="AB8" t="n">
-        <v>2280319.316961234</v>
+        <v>8154951.937296659</v>
       </c>
       <c r="AC8" t="n">
-        <v>74.00939225770053</v>
+        <v>79.26090505767525</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.014012303485988</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+        <v>1.223308192842355</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26.21428571428572</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>113</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>123428.5714285714</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>32642857.14285714</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>24.23537414965987</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>183.4755102040816</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>348.5714285714286</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>207285.7142857143</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>38485714.28571428</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>368</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.714285714285714</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>24.75584415584416</v>
+        <v>25.13020833333334</v>
       </c>
       <c r="D9" t="n">
-        <v>184.9363636363636</v>
+        <v>181.9722222222222</v>
       </c>
       <c r="E9" t="n">
-        <v>69.77142857142857</v>
+        <v>75.80555555555556</v>
       </c>
       <c r="F9" t="n">
-        <v>21501.2987012987</v>
+        <v>38802.08333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>2967272.727272727</v>
+        <v>12820138.88888889</v>
       </c>
       <c r="H9" t="n">
-        <v>74.66623376623377</v>
+        <v>80.52777777777777</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>1.510416666666667</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.18472222222222</v>
+      </c>
+      <c r="K9" t="n">
+        <v>183.5663194444444</v>
+      </c>
+      <c r="L9" t="n">
+        <v>72.66944444444444</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11752.08333333333</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4853750</v>
+      </c>
+      <c r="O9" t="n">
+        <v>77.09791666666666</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.038888888888889</v>
+      </c>
       <c r="Q9" t="n">
-        <v>24.78865616569421</v>
+        <v>25.23714564421086</v>
       </c>
       <c r="R9" t="n">
-        <v>183.9569158196875</v>
+        <v>182.3586521268587</v>
       </c>
       <c r="S9" t="n">
-        <v>68.98661694585607</v>
+        <v>75.75569548205418</v>
       </c>
       <c r="T9" t="n">
-        <v>23415.14426093231</v>
+        <v>43604.88741331133</v>
       </c>
       <c r="U9" t="n">
-        <v>2778741.559617919</v>
+        <v>11601385.07212896</v>
       </c>
       <c r="V9" t="n">
-        <v>73.59552924430642</v>
+        <v>80.12830158971464</v>
       </c>
       <c r="W9" t="n">
-        <v>1.074452796599536</v>
+        <v>1.443568026176722</v>
       </c>
       <c r="X9" t="n">
-        <v>28.49698767378806</v>
+        <v>25.85842340225564</v>
       </c>
       <c r="Y9" t="n">
-        <v>181.0296403839949</v>
+        <v>183.3468906641604</v>
       </c>
       <c r="Z9" t="n">
-        <v>73.18744431411008</v>
+        <v>71.36368264411028</v>
       </c>
       <c r="AA9" t="n">
-        <v>24045.583267632</v>
+        <v>10772.95191102757</v>
       </c>
       <c r="AB9" t="n">
-        <v>4839051.155168398</v>
+        <v>4093158.403822055</v>
       </c>
       <c r="AC9" t="n">
-        <v>74.60426695468423</v>
+        <v>75.88000078320803</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32814047052841</v>
+        <v>1.044811246867168</v>
       </c>
       <c r="AE9" t="n">
-        <v>24.76190476190476</v>
+        <v>26.47619047619048</v>
       </c>
       <c r="AF9" t="n">
-        <v>188.1666666666667</v>
+        <v>184.9047619047619</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.285714285714286</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="AH9" t="n">
-        <v>376.5714285714286</v>
+        <v>143.4285714285714</v>
       </c>
       <c r="AI9" t="n">
-        <v>69142.85714285714</v>
+        <v>87000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17200000</v>
+        <v>26142857.14285714</v>
       </c>
       <c r="AK9" t="n">
-        <v>397</v>
+        <v>147.7142857142857</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.285714285714286</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="AM9" t="n">
-        <v>29.25</v>
+        <v>26.375</v>
       </c>
       <c r="AN9" t="n">
-        <v>188.375</v>
+        <v>184.2604166666667</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.25</v>
+        <v>3.875</v>
       </c>
       <c r="AP9" t="n">
-        <v>87.5</v>
+        <v>274.875</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27000</v>
+        <v>54875</v>
       </c>
       <c r="AR9" t="n">
-        <v>1925000</v>
+        <v>16157500</v>
       </c>
       <c r="AS9" t="n">
-        <v>87.5</v>
+        <v>286.75</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.25</v>
+        <v>4.375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>23.84603174603174</v>
+        <v>26.07216610549944</v>
       </c>
       <c r="D10" t="n">
-        <v>184.1059523809524</v>
+        <v>183.5940516273849</v>
       </c>
       <c r="E10" t="n">
-        <v>72.60079365079365</v>
+        <v>72.62413019079685</v>
       </c>
       <c r="F10" t="n">
-        <v>26081.74603174604</v>
+        <v>23962.40179573513</v>
       </c>
       <c r="G10" t="n">
-        <v>5664414.682539682</v>
+        <v>5898136.924803591</v>
       </c>
       <c r="H10" t="n">
-        <v>78.33531746031746</v>
+        <v>76.86172839506172</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.221885521885522</v>
       </c>
       <c r="J10" t="n">
-        <v>26.35795454545455</v>
+        <v>26.50340909090909</v>
       </c>
       <c r="K10" t="n">
-        <v>184.5329545454546</v>
+        <v>181.9988636363636</v>
       </c>
       <c r="L10" t="n">
-        <v>72.19318181818181</v>
+        <v>78.93181818181819</v>
       </c>
       <c r="M10" t="n">
-        <v>30346.59090909091</v>
+        <v>46756.81818181818</v>
       </c>
       <c r="N10" t="n">
-        <v>4022840.909090909</v>
+        <v>21021676.13636364</v>
       </c>
       <c r="O10" t="n">
-        <v>75.52727272727273</v>
+        <v>82.24659090909091</v>
       </c>
       <c r="P10" t="n">
-        <v>1.069318181818182</v>
+        <v>1.865909090909091</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.944469958383</v>
+        <v>26.80078093493829</v>
       </c>
       <c r="R10" t="n">
-        <v>183.2322410439802</v>
+        <v>182.5690487445007</v>
       </c>
       <c r="S10" t="n">
-        <v>68.67789468180773</v>
+        <v>71.90139907850434</v>
       </c>
       <c r="T10" t="n">
-        <v>22291.68810255767</v>
+        <v>34958.49595248034</v>
       </c>
       <c r="U10" t="n">
-        <v>2853615.497626367</v>
+        <v>6478403.798098996</v>
       </c>
       <c r="V10" t="n">
-        <v>74.56701424179685</v>
+        <v>76.17409120595283</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.291927048562531</v>
       </c>
       <c r="X10" t="n">
-        <v>24.93452466393256</v>
+        <v>27.1721700310559</v>
       </c>
       <c r="Y10" t="n">
-        <v>185.2066236614263</v>
+        <v>183.1095898033126</v>
       </c>
       <c r="Z10" t="n">
-        <v>67.92214769879243</v>
+        <v>75.69458721532092</v>
       </c>
       <c r="AA10" t="n">
-        <v>28868.35099111414</v>
+        <v>39622.9917184265</v>
       </c>
       <c r="AB10" t="n">
-        <v>2527372.564935065</v>
+        <v>10893141.85429607</v>
       </c>
       <c r="AC10" t="n">
-        <v>73.09298501936659</v>
+        <v>79.39010998964804</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.088615288220551</v>
+        <v>1.642448240165632</v>
       </c>
       <c r="AE10" t="n">
-        <v>23.75</v>
+        <v>27.48541666666667</v>
       </c>
       <c r="AF10" t="n">
-        <v>186.7619047619048</v>
+        <v>180.9395833333333</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>4.625</v>
       </c>
       <c r="AH10" t="n">
-        <v>216.1428571428571</v>
+        <v>338.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>72857.14285714286</v>
+        <v>104875</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11757142.85714286</v>
+        <v>24950000</v>
       </c>
       <c r="AK10" t="n">
-        <v>231.4285714285714</v>
+        <v>350.625</v>
       </c>
       <c r="AL10" t="n">
-        <v>3</v>
+        <v>5.375</v>
       </c>
       <c r="AM10" t="n">
-        <v>27.9593537414966</v>
+        <v>27.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>183.5183673469388</v>
+        <v>177.375</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.285714285714286</v>
+        <v>1.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>384.4285714285714</v>
+        <v>120.25</v>
       </c>
       <c r="AQ10" t="n">
-        <v>198142.8571428571</v>
+        <v>94000</v>
       </c>
       <c r="AR10" t="n">
-        <v>24142857.14285714</v>
+        <v>38000000</v>
       </c>
       <c r="AS10" t="n">
-        <v>399.5714285714286</v>
+        <v>123.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.142857142857143</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.61428571428572</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>182.1285714285714</v>
+        <v>182.4772727272727</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>84.15909090909091</v>
       </c>
       <c r="F11" t="n">
-        <v>46514.28571428572</v>
+        <v>113409.0909090909</v>
       </c>
       <c r="G11" t="n">
-        <v>21154642.85714286</v>
+        <v>43375000</v>
       </c>
       <c r="H11" t="n">
-        <v>82.24285714285715</v>
+        <v>85.06818181818181</v>
       </c>
       <c r="I11" t="n">
-        <v>1.885714285714286</v>
+        <v>3.340909090909091</v>
       </c>
       <c r="J11" t="n">
-        <v>26.21136363636364</v>
+        <v>27.71077441077441</v>
       </c>
       <c r="K11" t="n">
-        <v>184.8909090909091</v>
+        <v>184.4189955106622</v>
       </c>
       <c r="L11" t="n">
-        <v>72.18068181818182</v>
+        <v>79.87227833894501</v>
       </c>
       <c r="M11" t="n">
-        <v>19362.5</v>
+        <v>103686.531986532</v>
       </c>
       <c r="N11" t="n">
-        <v>3966022.727272727</v>
+        <v>24474340.62850729</v>
       </c>
       <c r="O11" t="n">
-        <v>75.76704545454545</v>
+        <v>81.67250280583615</v>
       </c>
       <c r="P11" t="n">
-        <v>1.068181818181818</v>
+        <v>1.953535353535353</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.94506506950606</v>
+        <v>28.2860226705979</v>
       </c>
       <c r="R11" t="n">
-        <v>183.0164019520852</v>
+        <v>185.2369035307751</v>
       </c>
       <c r="S11" t="n">
-        <v>75.50809967465248</v>
+        <v>80.12319647362554</v>
       </c>
       <c r="T11" t="n">
-        <v>39514.71162377995</v>
+        <v>89275.78973038784</v>
       </c>
       <c r="U11" t="n">
-        <v>10486549.87429755</v>
+        <v>26509369.5542158</v>
       </c>
       <c r="V11" t="n">
-        <v>79.3914182194617</v>
+        <v>81.71577058763128</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59136941733215</v>
+        <v>2.457616580120871</v>
       </c>
       <c r="X11" t="n">
-        <v>26.65398046398046</v>
+        <v>27.13312996295453</v>
       </c>
       <c r="Y11" t="n">
-        <v>182.2320542883043</v>
+        <v>181.9132789887176</v>
       </c>
       <c r="Z11" t="n">
-        <v>70.84853942353942</v>
+        <v>76.78438014227487</v>
       </c>
       <c r="AA11" t="n">
-        <v>19115.26191401191</v>
+        <v>88512.39926415365</v>
       </c>
       <c r="AB11" t="n">
-        <v>3050526.186776187</v>
+        <v>16622026.60481169</v>
       </c>
       <c r="AC11" t="n">
-        <v>74.82284285159287</v>
+        <v>78.7797338464005</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.015297202797203</v>
+        <v>1.748623663535944</v>
       </c>
       <c r="AE11" t="n">
-        <v>27.5</v>
+        <v>26.47916666666666</v>
       </c>
       <c r="AF11" t="n">
-        <v>177.375</v>
+        <v>181.5625</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>2.125</v>
       </c>
       <c r="AH11" t="n">
-        <v>120.25</v>
+        <v>169</v>
       </c>
       <c r="AI11" t="n">
-        <v>94000</v>
+        <v>185875</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38000000</v>
+        <v>55000000</v>
       </c>
       <c r="AK11" t="n">
-        <v>123.25</v>
+        <v>173.125</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.5</v>
+        <v>4.375</v>
       </c>
       <c r="AM11" t="n">
-        <v>26.5952380952381</v>
+        <v>31.08333333333334</v>
       </c>
       <c r="AN11" t="n">
-        <v>184.8809523809524</v>
+        <v>173.6666666666667</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.571428571428572</v>
+        <v>1.875</v>
       </c>
       <c r="AP11" t="n">
-        <v>182.4285714285714</v>
+        <v>150.375</v>
       </c>
       <c r="AQ11" t="n">
-        <v>34285.71428571428</v>
+        <v>188375</v>
       </c>
       <c r="AR11" t="n">
-        <v>6042857.142857143</v>
+        <v>32562500</v>
       </c>
       <c r="AS11" t="n">
-        <v>190</v>
+        <v>151.125</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.571428571428572</v>
+        <v>4.625</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -1054,7 +1054,7 @@
         <v>72.2010101010101</v>
       </c>
       <c r="F5" t="n">
-        <v>19695.9595959596</v>
+        <v>19695.95959595959</v>
       </c>
       <c r="G5" t="n">
         <v>4024343.434343434</v>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT11"/>
+  <dimension ref="A1:AT12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,81 +658,95 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.32929292929293</v>
+        <v>25.625</v>
       </c>
       <c r="D2" t="n">
-        <v>184.6404040404041</v>
+        <v>183.3214285714286</v>
       </c>
       <c r="E2" t="n">
-        <v>72.12727272727273</v>
+        <v>72.82142857142857</v>
       </c>
       <c r="F2" t="n">
-        <v>30074.74747474748</v>
+        <v>11841.26984126984</v>
       </c>
       <c r="G2" t="n">
-        <v>3966969.696969697</v>
+        <v>5839682.539682539</v>
       </c>
       <c r="H2" t="n">
-        <v>75.52424242424243</v>
+        <v>77.46230158730158</v>
       </c>
       <c r="I2" t="n">
-        <v>1.061616161616162</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24.96818181818182</v>
+      </c>
+      <c r="K2" t="n">
+        <v>185.0011363636364</v>
+      </c>
+      <c r="L2" t="n">
+        <v>69.94772727272728</v>
+      </c>
+      <c r="M2" t="n">
+        <v>21722.72727272727</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2941818.181818182</v>
+      </c>
+      <c r="O2" t="n">
+        <v>74.52613636363637</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.011363636363636</v>
+      </c>
       <c r="Q2" t="n">
-        <v>25.03207747905116</v>
+        <v>25.23933369644154</v>
       </c>
       <c r="R2" t="n">
-        <v>184.8642210323789</v>
+        <v>181.3953703703704</v>
       </c>
       <c r="S2" t="n">
-        <v>67.77802017670439</v>
+        <v>69.48708242556283</v>
       </c>
       <c r="T2" t="n">
-        <v>28751.03421432368</v>
+        <v>10708.93246187364</v>
       </c>
       <c r="U2" t="n">
-        <v>2433879.77994228</v>
+        <v>3026298.792665214</v>
       </c>
       <c r="V2" t="n">
-        <v>72.8673755727703</v>
+        <v>74.40732570806101</v>
       </c>
       <c r="W2" t="n">
-        <v>1.085713589529379</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>28.45692303809396</v>
+        <v>24.56522523370349</v>
       </c>
       <c r="Y2" t="n">
-        <v>181.1141706301132</v>
+        <v>183.9370115928087</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.11254318661102</v>
+        <v>68.74736321113134</v>
       </c>
       <c r="AA2" t="n">
-        <v>24172.23830035447</v>
+        <v>23078.89366403859</v>
       </c>
       <c r="AB2" t="n">
-        <v>4845934.466654701</v>
+        <v>2776782.62089494</v>
       </c>
       <c r="AC2" t="n">
-        <v>74.44049829123105</v>
+        <v>73.62812476037114</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3018287940653</v>
+        <v>1.066180263644032</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -754,1279 +768,1165 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.625</v>
+        <v>25.6875</v>
       </c>
       <c r="D3" t="n">
-        <v>183.3214285714286</v>
+        <v>182.9534090909091</v>
       </c>
       <c r="E3" t="n">
-        <v>72.82142857142857</v>
+        <v>70.49431818181819</v>
       </c>
       <c r="F3" t="n">
-        <v>11841.26984126984</v>
+        <v>10955.68181818182</v>
       </c>
       <c r="G3" t="n">
-        <v>5839682.539682539</v>
+        <v>2923863.636363637</v>
       </c>
       <c r="H3" t="n">
-        <v>77.46230158730158</v>
+        <v>75.11704545454546</v>
       </c>
       <c r="I3" t="n">
+        <v>1.048863636363636</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.78715277777778</v>
+      </c>
+      <c r="K3" t="n">
+        <v>184.1395833333333</v>
+      </c>
+      <c r="L3" t="n">
+        <v>72.63506944444444</v>
+      </c>
+      <c r="M3" t="n">
+        <v>26087.15277777778</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5690737.847222222</v>
+      </c>
+      <c r="O3" t="n">
+        <v>78.40277777777777</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>24.96818181818182</v>
-      </c>
-      <c r="K3" t="n">
-        <v>185.0011363636364</v>
-      </c>
-      <c r="L3" t="n">
-        <v>69.94772727272728</v>
-      </c>
-      <c r="M3" t="n">
-        <v>21722.72727272727</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2941818.181818182</v>
-      </c>
-      <c r="O3" t="n">
-        <v>74.52613636363637</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.011363636363636</v>
-      </c>
       <c r="Q3" t="n">
-        <v>25.23933369644154</v>
+        <v>26.11956589844176</v>
       </c>
       <c r="R3" t="n">
-        <v>181.3953703703704</v>
+        <v>182.6298493681502</v>
       </c>
       <c r="S3" t="n">
-        <v>69.48708242556283</v>
+        <v>68.8775616577676</v>
       </c>
       <c r="T3" t="n">
-        <v>10708.93246187364</v>
+        <v>13349.80493064017</v>
       </c>
       <c r="U3" t="n">
-        <v>3026298.792665214</v>
+        <v>2321393.532775863</v>
       </c>
       <c r="V3" t="n">
-        <v>74.40732570806101</v>
+        <v>74.06800083418361</v>
       </c>
       <c r="W3" t="n">
+        <v>1.028565113376326</v>
+      </c>
+      <c r="X3" t="n">
+        <v>23.92256505973897</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>183.1647493750211</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>68.59315784658176</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>22226.38093589181</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2833572.214269225</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>74.56344515387994</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1</v>
       </c>
-      <c r="X3" t="n">
-        <v>24.56522523370349</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>183.9370115928087</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>68.74736321113134</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>23078.89366403859</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2776782.62089494</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>73.62812476037114</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.066180263644032</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>23.2125</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>182.24375</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>42500</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>11481250</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>346.375</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>24.73809523809524</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>187.9672619047619</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>390.625</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>74375</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>17778125</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>412.25</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.6875</v>
+        <v>26.11717171717172</v>
       </c>
       <c r="D4" t="n">
-        <v>182.9534090909091</v>
+        <v>184.8222222222222</v>
       </c>
       <c r="E4" t="n">
-        <v>70.49431818181819</v>
+        <v>72.2010101010101</v>
       </c>
       <c r="F4" t="n">
-        <v>10955.68181818182</v>
+        <v>19695.95959595959</v>
       </c>
       <c r="G4" t="n">
-        <v>2923863.636363637</v>
+        <v>4024343.434343434</v>
       </c>
       <c r="H4" t="n">
-        <v>75.11704545454546</v>
+        <v>75.85353535353536</v>
       </c>
       <c r="I4" t="n">
-        <v>1.048863636363636</v>
+        <v>1.070707070707071</v>
       </c>
       <c r="J4" t="n">
-        <v>23.78715277777778</v>
+        <v>25.6984126984127</v>
       </c>
       <c r="K4" t="n">
-        <v>184.1395833333333</v>
+        <v>185.8511904761905</v>
       </c>
       <c r="L4" t="n">
-        <v>72.63506944444444</v>
+        <v>81.66666666666667</v>
       </c>
       <c r="M4" t="n">
-        <v>26087.15277777778</v>
+        <v>134559.5238095238</v>
       </c>
       <c r="N4" t="n">
-        <v>5690737.847222222</v>
+        <v>42371428.57142857</v>
       </c>
       <c r="O4" t="n">
-        <v>78.40277777777777</v>
+        <v>84.89285714285714</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.11956589844176</v>
+        <v>26.70775274959183</v>
       </c>
       <c r="R4" t="n">
-        <v>182.6298493681502</v>
+        <v>182.3825156892207</v>
       </c>
       <c r="S4" t="n">
-        <v>68.8775616577676</v>
+        <v>70.8155599473607</v>
       </c>
       <c r="T4" t="n">
-        <v>13349.80493064017</v>
+        <v>18742.30177797228</v>
       </c>
       <c r="U4" t="n">
-        <v>2321393.532775863</v>
+        <v>2982268.487862358</v>
       </c>
       <c r="V4" t="n">
-        <v>74.06800083418361</v>
+        <v>74.75823579145418</v>
       </c>
       <c r="W4" t="n">
-        <v>1.028565113376326</v>
+        <v>1.013597513597514</v>
       </c>
       <c r="X4" t="n">
-        <v>23.92256505973897</v>
+        <v>24.30763321346845</v>
       </c>
       <c r="Y4" t="n">
-        <v>183.1647493750211</v>
+        <v>183.6382339628335</v>
       </c>
       <c r="Z4" t="n">
-        <v>68.59315784658176</v>
+        <v>77.61811839680425</v>
       </c>
       <c r="AA4" t="n">
-        <v>22226.38093589181</v>
+        <v>109258.1603914229</v>
       </c>
       <c r="AB4" t="n">
-        <v>2833572.214269225</v>
+        <v>27758996.7408368</v>
       </c>
       <c r="AC4" t="n">
-        <v>74.56344515387994</v>
+        <v>82.85963020307577</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>181.3125</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>117.625</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>16125</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2825000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>126.25</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>23.90625</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>187.0416666666667</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>207.75</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>70625</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11850000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>222.25</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.875</v>
-      </c>
+        <v>1.89842331581462</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.11717171717172</v>
+        <v>25.21875</v>
       </c>
       <c r="D5" t="n">
-        <v>184.8222222222222</v>
+        <v>184.71875</v>
       </c>
       <c r="E5" t="n">
-        <v>72.2010101010101</v>
+        <v>79.84375</v>
       </c>
       <c r="F5" t="n">
-        <v>19695.95959595959</v>
+        <v>96656.25</v>
       </c>
       <c r="G5" t="n">
-        <v>4024343.434343434</v>
+        <v>30625000</v>
       </c>
       <c r="H5" t="n">
-        <v>75.85353535353536</v>
+        <v>83.5625</v>
       </c>
       <c r="I5" t="n">
-        <v>1.070707070707071</v>
+        <v>2.125</v>
       </c>
       <c r="J5" t="n">
-        <v>25.6984126984127</v>
+        <v>26.77976190476191</v>
       </c>
       <c r="K5" t="n">
-        <v>185.8511904761905</v>
+        <v>185.7420634920635</v>
       </c>
       <c r="L5" t="n">
-        <v>81.66666666666667</v>
+        <v>74.33928571428571</v>
       </c>
       <c r="M5" t="n">
-        <v>134559.5238095238</v>
+        <v>36682.53968253968</v>
       </c>
       <c r="N5" t="n">
-        <v>42371428.57142857</v>
+        <v>8864484.126984127</v>
       </c>
       <c r="O5" t="n">
-        <v>84.89285714285714</v>
+        <v>77.55753968253968</v>
       </c>
       <c r="P5" t="n">
-        <v>2.619047619047619</v>
+        <v>1.134920634920635</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.70775274959183</v>
+        <v>25.75107323232323</v>
       </c>
       <c r="R5" t="n">
-        <v>182.3825156892207</v>
+        <v>184.1645202020202</v>
       </c>
       <c r="S5" t="n">
-        <v>70.8155599473607</v>
+        <v>76.95536616161615</v>
       </c>
       <c r="T5" t="n">
-        <v>18742.30177797228</v>
+        <v>77690.46717171717</v>
       </c>
       <c r="U5" t="n">
-        <v>2982268.487862358</v>
+        <v>16608023.98989899</v>
       </c>
       <c r="V5" t="n">
-        <v>74.75823579145418</v>
+        <v>81.07986111111111</v>
       </c>
       <c r="W5" t="n">
-        <v>1.013597513597514</v>
+        <v>1.549873737373737</v>
       </c>
       <c r="X5" t="n">
-        <v>24.30763321346845</v>
+        <v>25.09554788940754</v>
       </c>
       <c r="Y5" t="n">
-        <v>183.6382339628335</v>
+        <v>184.9078904526273</v>
       </c>
       <c r="Z5" t="n">
-        <v>77.61811839680425</v>
+        <v>70.21636667426141</v>
       </c>
       <c r="AA5" t="n">
-        <v>109258.1603914229</v>
+        <v>29532.35091743864</v>
       </c>
       <c r="AB5" t="n">
-        <v>27758996.7408368</v>
+        <v>5135020.714340891</v>
       </c>
       <c r="AC5" t="n">
-        <v>82.85963020307577</v>
+        <v>75.79089649791405</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.89842331581462</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>26.5952380952381</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>184.8809523809524</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.571428571428572</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>182.4285714285714</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>34285.71428571428</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>6042857.142857143</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.571428571428572</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>26.52857142857143</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>182.4071428571428</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>319.1428571428572</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>468571.4285714286</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>118067857.1428571</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>330.8571428571428</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.857142857142858</v>
-      </c>
+        <v>1.054545454545454</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.21875</v>
+        <v>26.7125</v>
       </c>
       <c r="D6" t="n">
-        <v>184.71875</v>
+        <v>186.1920454545455</v>
       </c>
       <c r="E6" t="n">
-        <v>79.84375</v>
+        <v>78.61931818181819</v>
       </c>
       <c r="F6" t="n">
-        <v>96656.25</v>
+        <v>57982.95454545454</v>
       </c>
       <c r="G6" t="n">
-        <v>30625000</v>
+        <v>19615681.81818182</v>
       </c>
       <c r="H6" t="n">
-        <v>83.5625</v>
+        <v>81.85113636363636</v>
       </c>
       <c r="I6" t="n">
-        <v>2.125</v>
+        <v>1.767045454545455</v>
       </c>
       <c r="J6" t="n">
-        <v>26.77976190476191</v>
+        <v>26.28950617283951</v>
       </c>
       <c r="K6" t="n">
-        <v>185.7420634920635</v>
+        <v>186.2024691358025</v>
       </c>
       <c r="L6" t="n">
-        <v>74.33928571428571</v>
+        <v>71.87592592592593</v>
       </c>
       <c r="M6" t="n">
-        <v>36682.53968253968</v>
+        <v>15268.20987654321</v>
       </c>
       <c r="N6" t="n">
-        <v>8864484.126984127</v>
+        <v>3357183.641975308</v>
       </c>
       <c r="O6" t="n">
-        <v>77.55753968253968</v>
+        <v>75.16265432098766</v>
       </c>
       <c r="P6" t="n">
-        <v>1.134920634920635</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.75107323232323</v>
+        <v>25.68494131408891</v>
       </c>
       <c r="R6" t="n">
-        <v>184.1645202020202</v>
+        <v>185.1817319154276</v>
       </c>
       <c r="S6" t="n">
-        <v>76.95536616161615</v>
+        <v>74.12151343444249</v>
       </c>
       <c r="T6" t="n">
-        <v>77690.46717171717</v>
+        <v>41710.2084922451</v>
       </c>
       <c r="U6" t="n">
-        <v>16608023.98989899</v>
+        <v>12104989.59643839</v>
       </c>
       <c r="V6" t="n">
-        <v>81.07986111111111</v>
+        <v>79.1614665368956</v>
       </c>
       <c r="W6" t="n">
-        <v>1.549873737373737</v>
+        <v>1.599129989004131</v>
       </c>
       <c r="X6" t="n">
-        <v>25.09554788940754</v>
+        <v>26.42813473076631</v>
       </c>
       <c r="Y6" t="n">
-        <v>184.9078904526273</v>
+        <v>183.3086316380176</v>
       </c>
       <c r="Z6" t="n">
-        <v>70.21636667426141</v>
+        <v>70.32857976169379</v>
       </c>
       <c r="AA6" t="n">
-        <v>29532.35091743864</v>
+        <v>14664.86439161877</v>
       </c>
       <c r="AB6" t="n">
-        <v>5135020.714340891</v>
+        <v>2398715.446549877</v>
       </c>
       <c r="AC6" t="n">
-        <v>75.79089649791405</v>
+        <v>74.03548243504383</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.054545454545454</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>28.37916666666666</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>186.3041666666667</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>315.75</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>464125</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>132687500</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>320</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>183.9583333333333</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>230</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>124125</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>46062500</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>255.125</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.125</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>26.7125</v>
+        <v>26.5</v>
       </c>
       <c r="D7" t="n">
-        <v>186.1920454545455</v>
+        <v>181.484126984127</v>
       </c>
       <c r="E7" t="n">
-        <v>78.61931818181819</v>
+        <v>78.28174603174602</v>
       </c>
       <c r="F7" t="n">
-        <v>57982.95454545454</v>
+        <v>39952.38095238095</v>
       </c>
       <c r="G7" t="n">
-        <v>19615681.81818182</v>
+        <v>22094246.03174603</v>
       </c>
       <c r="H7" t="n">
-        <v>81.85113636363636</v>
+        <v>81.00396825396827</v>
       </c>
       <c r="I7" t="n">
-        <v>1.767045454545455</v>
+        <v>2.382936507936508</v>
       </c>
       <c r="J7" t="n">
-        <v>26.28950617283951</v>
+        <v>26.38311688311688</v>
       </c>
       <c r="K7" t="n">
-        <v>186.2024691358025</v>
+        <v>185.9239538239538</v>
       </c>
       <c r="L7" t="n">
-        <v>71.87592592592593</v>
+        <v>75.9037518037518</v>
       </c>
       <c r="M7" t="n">
-        <v>15268.20987654321</v>
+        <v>45980.23088023088</v>
       </c>
       <c r="N7" t="n">
-        <v>3357183.641975308</v>
+        <v>10231572.87157287</v>
       </c>
       <c r="O7" t="n">
-        <v>75.16265432098766</v>
+        <v>78.99884559884559</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.459018759018759</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.68494131408891</v>
+        <v>25.45280910609858</v>
       </c>
       <c r="R7" t="n">
-        <v>185.1817319154276</v>
+        <v>179.0008719715956</v>
       </c>
       <c r="S7" t="n">
-        <v>74.12151343444249</v>
+        <v>76.72815371762739</v>
       </c>
       <c r="T7" t="n">
-        <v>41710.2084922451</v>
+        <v>35632.98350041771</v>
       </c>
       <c r="U7" t="n">
-        <v>12104989.59643839</v>
+        <v>19649223.57978279</v>
       </c>
       <c r="V7" t="n">
-        <v>79.1614665368956</v>
+        <v>81.1875469924812</v>
       </c>
       <c r="W7" t="n">
-        <v>1.599129989004131</v>
+        <v>1.941619674185464</v>
       </c>
       <c r="X7" t="n">
-        <v>26.42813473076631</v>
+        <v>24.10867938479739</v>
       </c>
       <c r="Y7" t="n">
-        <v>183.3086316380176</v>
+        <v>185.1505900621118</v>
       </c>
       <c r="Z7" t="n">
-        <v>70.32857976169379</v>
+        <v>73.69560041407865</v>
       </c>
       <c r="AA7" t="n">
-        <v>14664.86439161877</v>
+        <v>40155.50872522922</v>
       </c>
       <c r="AB7" t="n">
-        <v>2398715.446549877</v>
+        <v>8154951.937296659</v>
       </c>
       <c r="AC7" t="n">
-        <v>74.03548243504383</v>
+        <v>79.26090505767525</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>23.25416666666667</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>192.7875</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>230</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>138875</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>60775000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>249.25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5.125</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>27.14583333333333</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>183.15625</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>177.125</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>46000</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>21725000</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>185</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.375</v>
-      </c>
+        <v>1.223308192842355</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.5</v>
+        <v>25.13020833333334</v>
       </c>
       <c r="D8" t="n">
-        <v>181.484126984127</v>
+        <v>181.9722222222222</v>
       </c>
       <c r="E8" t="n">
-        <v>78.28174603174602</v>
+        <v>75.80555555555556</v>
       </c>
       <c r="F8" t="n">
-        <v>39952.38095238095</v>
+        <v>38802.08333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>22094246.03174603</v>
+        <v>12820138.88888889</v>
       </c>
       <c r="H8" t="n">
-        <v>81.00396825396827</v>
+        <v>80.52777777777777</v>
       </c>
       <c r="I8" t="n">
-        <v>2.382936507936508</v>
+        <v>1.510416666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>26.38311688311688</v>
+        <v>25.18472222222222</v>
       </c>
       <c r="K8" t="n">
-        <v>185.9239538239538</v>
+        <v>183.5663194444444</v>
       </c>
       <c r="L8" t="n">
-        <v>75.9037518037518</v>
+        <v>72.66944444444444</v>
       </c>
       <c r="M8" t="n">
-        <v>45980.23088023088</v>
+        <v>11752.08333333333</v>
       </c>
       <c r="N8" t="n">
-        <v>10231572.87157287</v>
+        <v>4853750</v>
       </c>
       <c r="O8" t="n">
-        <v>78.99884559884559</v>
+        <v>77.09791666666666</v>
       </c>
       <c r="P8" t="n">
-        <v>1.459018759018759</v>
+        <v>1.038888888888889</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.45280910609858</v>
+        <v>25.23714564421086</v>
       </c>
       <c r="R8" t="n">
-        <v>179.0008719715956</v>
+        <v>182.3586521268587</v>
       </c>
       <c r="S8" t="n">
-        <v>76.72815371762739</v>
+        <v>75.75569548205418</v>
       </c>
       <c r="T8" t="n">
-        <v>35632.98350041771</v>
+        <v>43604.88741331133</v>
       </c>
       <c r="U8" t="n">
-        <v>19649223.57978279</v>
+        <v>11601385.07212896</v>
       </c>
       <c r="V8" t="n">
-        <v>81.1875469924812</v>
+        <v>80.12830158971464</v>
       </c>
       <c r="W8" t="n">
-        <v>1.941619674185464</v>
+        <v>1.443568026176722</v>
       </c>
       <c r="X8" t="n">
-        <v>24.10867938479739</v>
+        <v>25.85842340225564</v>
       </c>
       <c r="Y8" t="n">
-        <v>185.1505900621118</v>
+        <v>183.3468906641604</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.69560041407865</v>
+        <v>71.36368264411028</v>
       </c>
       <c r="AA8" t="n">
-        <v>40155.50872522922</v>
+        <v>10772.95191102757</v>
       </c>
       <c r="AB8" t="n">
-        <v>8154951.937296659</v>
+        <v>4093158.403822055</v>
       </c>
       <c r="AC8" t="n">
-        <v>79.26090505767525</v>
+        <v>75.88000078320803</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.223308192842355</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>26.21428571428572</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>113</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>123428.5714285714</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>32642857.14285714</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>115</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.428571428571428</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>24.23537414965987</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>183.4755102040816</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>4.714285714285714</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>348.5714285714286</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>207285.7142857143</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>38485714.28571428</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>368</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.714285714285714</v>
-      </c>
+        <v>1.044811246867168</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.13020833333334</v>
+        <v>26.07216610549944</v>
       </c>
       <c r="D9" t="n">
-        <v>181.9722222222222</v>
+        <v>183.5940516273849</v>
       </c>
       <c r="E9" t="n">
-        <v>75.80555555555556</v>
+        <v>72.62413019079685</v>
       </c>
       <c r="F9" t="n">
-        <v>38802.08333333334</v>
+        <v>23962.40179573513</v>
       </c>
       <c r="G9" t="n">
-        <v>12820138.88888889</v>
+        <v>5898136.924803591</v>
       </c>
       <c r="H9" t="n">
-        <v>80.52777777777777</v>
+        <v>76.86172839506172</v>
       </c>
       <c r="I9" t="n">
-        <v>1.510416666666667</v>
+        <v>1.221885521885522</v>
       </c>
       <c r="J9" t="n">
-        <v>25.18472222222222</v>
+        <v>26.50340909090909</v>
       </c>
       <c r="K9" t="n">
-        <v>183.5663194444444</v>
+        <v>181.9988636363636</v>
       </c>
       <c r="L9" t="n">
-        <v>72.66944444444444</v>
+        <v>78.93181818181819</v>
       </c>
       <c r="M9" t="n">
-        <v>11752.08333333333</v>
+        <v>46756.81818181818</v>
       </c>
       <c r="N9" t="n">
-        <v>4853750</v>
+        <v>21021676.13636364</v>
       </c>
       <c r="O9" t="n">
-        <v>77.09791666666666</v>
+        <v>82.24659090909091</v>
       </c>
       <c r="P9" t="n">
-        <v>1.038888888888889</v>
+        <v>1.865909090909091</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.23714564421086</v>
+        <v>26.80078093493829</v>
       </c>
       <c r="R9" t="n">
-        <v>182.3586521268587</v>
+        <v>182.5690487445007</v>
       </c>
       <c r="S9" t="n">
-        <v>75.75569548205418</v>
+        <v>71.90139907850434</v>
       </c>
       <c r="T9" t="n">
-        <v>43604.88741331133</v>
+        <v>34958.49595248034</v>
       </c>
       <c r="U9" t="n">
-        <v>11601385.07212896</v>
+        <v>6478403.798098996</v>
       </c>
       <c r="V9" t="n">
-        <v>80.12830158971464</v>
+        <v>76.17409120595283</v>
       </c>
       <c r="W9" t="n">
-        <v>1.443568026176722</v>
+        <v>1.291927048562531</v>
       </c>
       <c r="X9" t="n">
-        <v>25.85842340225564</v>
+        <v>27.1721700310559</v>
       </c>
       <c r="Y9" t="n">
-        <v>183.3468906641604</v>
+        <v>183.1095898033126</v>
       </c>
       <c r="Z9" t="n">
-        <v>71.36368264411028</v>
+        <v>75.69458721532092</v>
       </c>
       <c r="AA9" t="n">
-        <v>10772.95191102757</v>
+        <v>39622.9917184265</v>
       </c>
       <c r="AB9" t="n">
-        <v>4093158.403822055</v>
+        <v>10893141.85429607</v>
       </c>
       <c r="AC9" t="n">
-        <v>75.88000078320803</v>
+        <v>79.39010998964804</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.044811246867168</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>26.47619047619048</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>184.9047619047619</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>143.4285714285714</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>87000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>26142857.14285714</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>147.7142857142857</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.428571428571428</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>26.375</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>184.2604166666667</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>274.875</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>54875</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16157500</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>286.75</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.375</v>
-      </c>
+        <v>1.642448240165632</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>26.07216610549944</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>183.5940516273849</v>
+        <v>182.4772727272727</v>
       </c>
       <c r="E10" t="n">
-        <v>72.62413019079685</v>
+        <v>84.15909090909091</v>
       </c>
       <c r="F10" t="n">
-        <v>23962.40179573513</v>
+        <v>113409.0909090909</v>
       </c>
       <c r="G10" t="n">
-        <v>5898136.924803591</v>
+        <v>43375000</v>
       </c>
       <c r="H10" t="n">
-        <v>76.86172839506172</v>
+        <v>85.06818181818181</v>
       </c>
       <c r="I10" t="n">
-        <v>1.221885521885522</v>
+        <v>3.340909090909091</v>
       </c>
       <c r="J10" t="n">
-        <v>26.50340909090909</v>
+        <v>27.71077441077441</v>
       </c>
       <c r="K10" t="n">
-        <v>181.9988636363636</v>
+        <v>184.4189955106622</v>
       </c>
       <c r="L10" t="n">
-        <v>78.93181818181819</v>
+        <v>79.87227833894501</v>
       </c>
       <c r="M10" t="n">
-        <v>46756.81818181818</v>
+        <v>103686.531986532</v>
       </c>
       <c r="N10" t="n">
-        <v>21021676.13636364</v>
+        <v>24474340.62850729</v>
       </c>
       <c r="O10" t="n">
-        <v>82.24659090909091</v>
+        <v>81.67250280583615</v>
       </c>
       <c r="P10" t="n">
-        <v>1.865909090909091</v>
+        <v>1.953535353535353</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.80078093493829</v>
+        <v>28.2860226705979</v>
       </c>
       <c r="R10" t="n">
-        <v>182.5690487445007</v>
+        <v>185.2369035307751</v>
       </c>
       <c r="S10" t="n">
-        <v>71.90139907850434</v>
+        <v>80.12319647362554</v>
       </c>
       <c r="T10" t="n">
-        <v>34958.49595248034</v>
+        <v>89275.78973038784</v>
       </c>
       <c r="U10" t="n">
-        <v>6478403.798098996</v>
+        <v>26509369.5542158</v>
       </c>
       <c r="V10" t="n">
-        <v>76.17409120595283</v>
+        <v>81.71577058763128</v>
       </c>
       <c r="W10" t="n">
-        <v>1.291927048562531</v>
+        <v>2.457616580120871</v>
       </c>
       <c r="X10" t="n">
-        <v>27.1721700310559</v>
+        <v>27.13312996295453</v>
       </c>
       <c r="Y10" t="n">
-        <v>183.1095898033126</v>
+        <v>181.9132789887176</v>
       </c>
       <c r="Z10" t="n">
-        <v>75.69458721532092</v>
+        <v>76.78438014227487</v>
       </c>
       <c r="AA10" t="n">
-        <v>39622.9917184265</v>
+        <v>88512.39926415365</v>
       </c>
       <c r="AB10" t="n">
-        <v>10893141.85429607</v>
+        <v>16622026.60481169</v>
       </c>
       <c r="AC10" t="n">
-        <v>79.39010998964804</v>
+        <v>78.7797338464005</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.642448240165632</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>27.48541666666667</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>180.9395833333333</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.625</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>338.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>104875</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>24950000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>350.625</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>5.375</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>177.375</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>120.25</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>94000</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>123.25</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.5</v>
-      </c>
+        <v>1.748623663535944</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
+        <v>25.18472222222222</v>
+      </c>
+      <c r="D11" t="n">
+        <v>183.5663194444444</v>
+      </c>
+      <c r="E11" t="n">
+        <v>72.66944444444444</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11752.08333333333</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4853750</v>
+      </c>
+      <c r="H11" t="n">
+        <v>77.09791666666666</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.038888888888889</v>
+      </c>
+      <c r="J11" t="n">
         <v>29</v>
       </c>
-      <c r="D11" t="n">
+      <c r="K11" t="n">
         <v>182.4772727272727</v>
       </c>
-      <c r="E11" t="n">
+      <c r="L11" t="n">
         <v>84.15909090909091</v>
       </c>
-      <c r="F11" t="n">
+      <c r="M11" t="n">
         <v>113409.0909090909</v>
       </c>
-      <c r="G11" t="n">
+      <c r="N11" t="n">
         <v>43375000</v>
       </c>
-      <c r="H11" t="n">
+      <c r="O11" t="n">
         <v>85.06818181818181</v>
       </c>
-      <c r="I11" t="n">
+      <c r="P11" t="n">
         <v>3.340909090909091</v>
       </c>
-      <c r="J11" t="n">
-        <v>27.71077441077441</v>
-      </c>
-      <c r="K11" t="n">
-        <v>184.4189955106622</v>
-      </c>
-      <c r="L11" t="n">
-        <v>79.87227833894501</v>
-      </c>
-      <c r="M11" t="n">
-        <v>103686.531986532</v>
-      </c>
-      <c r="N11" t="n">
-        <v>24474340.62850729</v>
-      </c>
-      <c r="O11" t="n">
-        <v>81.67250280583615</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.953535353535353</v>
-      </c>
       <c r="Q11" t="n">
+        <v>25.85842340225564</v>
+      </c>
+      <c r="R11" t="n">
+        <v>183.3468906641604</v>
+      </c>
+      <c r="S11" t="n">
+        <v>71.36368264411028</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10772.95191102757</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4093158.403822055</v>
+      </c>
+      <c r="V11" t="n">
+        <v>75.88000078320803</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.044811246867168</v>
+      </c>
+      <c r="X11" t="n">
         <v>28.2860226705979</v>
       </c>
-      <c r="R11" t="n">
+      <c r="Y11" t="n">
         <v>185.2369035307751</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Z11" t="n">
         <v>80.12319647362554</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AA11" t="n">
         <v>89275.78973038784</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AB11" t="n">
         <v>26509369.5542158</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AC11" t="n">
         <v>81.71577058763128</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AD11" t="n">
         <v>2.457616580120871</v>
       </c>
-      <c r="X11" t="n">
-        <v>27.13312996295453</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>181.9132789887176</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>76.78438014227487</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>88512.39926415365</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>16622026.60481169</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>78.7797338464005</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.748623663535944</v>
-      </c>
       <c r="AE11" t="n">
-        <v>26.47916666666666</v>
+        <v>26.375</v>
       </c>
       <c r="AF11" t="n">
-        <v>181.5625</v>
+        <v>184.2604166666667</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.125</v>
+        <v>3.875</v>
       </c>
       <c r="AH11" t="n">
-        <v>169</v>
+        <v>274.875</v>
       </c>
       <c r="AI11" t="n">
-        <v>185875</v>
+        <v>54875</v>
       </c>
       <c r="AJ11" t="n">
-        <v>55000000</v>
+        <v>16157500</v>
       </c>
       <c r="AK11" t="n">
-        <v>173.125</v>
+        <v>286.75</v>
       </c>
       <c r="AL11" t="n">
         <v>4.375</v>
       </c>
       <c r="AM11" t="n">
-        <v>31.08333333333334</v>
+        <v>26.47916666666666</v>
       </c>
       <c r="AN11" t="n">
-        <v>173.6666666666667</v>
+        <v>181.5625</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.875</v>
+        <v>2.125</v>
       </c>
       <c r="AP11" t="n">
-        <v>150.375</v>
+        <v>169</v>
       </c>
       <c r="AQ11" t="n">
-        <v>188375</v>
+        <v>185875</v>
       </c>
       <c r="AR11" t="n">
-        <v>32562500</v>
+        <v>55000000</v>
       </c>
       <c r="AS11" t="n">
-        <v>151.125</v>
+        <v>173.125</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.625</v>
+        <v>4.375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.6984126984127</v>
+      </c>
+      <c r="D12" t="n">
+        <v>185.8511904761905</v>
+      </c>
+      <c r="E12" t="n">
+        <v>81.66666666666667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>134559.5238095238</v>
+      </c>
+      <c r="G12" t="n">
+        <v>42371428.57142857</v>
+      </c>
+      <c r="H12" t="n">
+        <v>84.89285714285714</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.619047619047619</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25.21875</v>
+      </c>
+      <c r="K12" t="n">
+        <v>184.71875</v>
+      </c>
+      <c r="L12" t="n">
+        <v>79.84375</v>
+      </c>
+      <c r="M12" t="n">
+        <v>96656.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30625000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>83.5625</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>24.30763321346845</v>
+      </c>
+      <c r="R12" t="n">
+        <v>183.6382339628335</v>
+      </c>
+      <c r="S12" t="n">
+        <v>77.61811839680425</v>
+      </c>
+      <c r="T12" t="n">
+        <v>109258.1603914229</v>
+      </c>
+      <c r="U12" t="n">
+        <v>27758996.7408368</v>
+      </c>
+      <c r="V12" t="n">
+        <v>82.85963020307577</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.89842331581462</v>
+      </c>
+      <c r="X12" t="n">
+        <v>25.75107323232323</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>184.1645202020202</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>76.95536616161615</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>77690.46717171717</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>16608023.98989899</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.549873737373737</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>26.52857142857143</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>182.4071428571428</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>319.1428571428572</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>468571.4285714286</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>118067857.1428571</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>330.8571428571428</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>8.857142857142858</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>28.37916666666666</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>186.3041666666667</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>315.75</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>464125</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>132687500</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
